--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="213">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -212,6 +212,444 @@
   </si>
   <si>
     <t>K268093121</t>
+  </si>
+  <si>
+    <t>T468837</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>Downgraded</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>T468838</t>
+  </si>
+  <si>
+    <t>7246484</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7246542</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4307-304L</t>
+  </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
+    <t>7246814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 5.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7246817</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 6.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T473609</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7247036</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Polish grain 400 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7247041</t>
+  </si>
+  <si>
+    <t>7247338</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7247409</t>
+  </si>
+  <si>
+    <t>7247854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475488</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248626</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248988</t>
+  </si>
+  <si>
+    <t>Coil 1.4307-304L 2D 1.0 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>7248989</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T477742</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7249627</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Duplo polish grain 320</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481266</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481267</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T481616</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T481617</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481869</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7253484</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 240 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 240</t>
+  </si>
+  <si>
+    <t>7253485</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484088</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484797</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254248</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T485455</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254992</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T486939</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>T487305</t>
+  </si>
+  <si>
+    <t>T487411</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255816</t>
+  </si>
+  <si>
+    <t>T487947</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T487964</t>
+  </si>
+  <si>
+    <t>7256046</t>
+  </si>
+  <si>
+    <t>Coil 1.4301-304 2R 0.6 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>7256139</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>T488237</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1000.0 x 2000 mm Slit</t>
   </si>
 </sst>
 </file>
@@ -588,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB87"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -1409,6 +1847,6391 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11">
+        <v>1000</v>
+      </c>
+      <c r="K11">
+        <v>2000</v>
+      </c>
+      <c r="L11" t="s">
+        <v>74</v>
+      </c>
+      <c r="M11" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R11">
+        <v>283</v>
+      </c>
+      <c r="S11">
+        <v>283</v>
+      </c>
+      <c r="T11" t="s">
+        <v>41</v>
+      </c>
+      <c r="U11">
+        <v>5</v>
+      </c>
+      <c r="V11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X11">
+        <v>3690</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA11">
+        <v>1044.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <v>6</v>
+      </c>
+      <c r="J12">
+        <v>1000</v>
+      </c>
+      <c r="K12">
+        <v>2000</v>
+      </c>
+      <c r="L12" t="s">
+        <v>74</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>75</v>
+      </c>
+      <c r="R12">
+        <v>567</v>
+      </c>
+      <c r="S12">
+        <v>567</v>
+      </c>
+      <c r="T12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12">
+        <v>6</v>
+      </c>
+      <c r="V12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" t="s">
+        <v>43</v>
+      </c>
+      <c r="X12">
+        <v>3690</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA12">
+        <v>2092.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13">
+        <v>2.5</v>
+      </c>
+      <c r="J13">
+        <v>1500</v>
+      </c>
+      <c r="K13">
+        <v>3000</v>
+      </c>
+      <c r="L13" t="s">
+        <v>74</v>
+      </c>
+      <c r="M13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" t="s">
+        <v>38</v>
+      </c>
+      <c r="P13" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>75</v>
+      </c>
+      <c r="R13">
+        <v>554</v>
+      </c>
+      <c r="S13">
+        <v>554</v>
+      </c>
+      <c r="T13" t="s">
+        <v>41</v>
+      </c>
+      <c r="U13">
+        <v>6</v>
+      </c>
+      <c r="V13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13">
+        <v>3540</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA13">
+        <v>1961.16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14">
+        <v>6</v>
+      </c>
+      <c r="J14">
+        <v>1000</v>
+      </c>
+      <c r="K14">
+        <v>2000</v>
+      </c>
+      <c r="L14" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>75</v>
+      </c>
+      <c r="R14">
+        <v>1133</v>
+      </c>
+      <c r="S14">
+        <v>1133</v>
+      </c>
+      <c r="T14" t="s">
+        <v>41</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14" t="s">
+        <v>43</v>
+      </c>
+      <c r="W14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X14">
+        <v>2070</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA14">
+        <v>2345.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
+        <v>2000</v>
+      </c>
+      <c r="K15">
+        <v>6000</v>
+      </c>
+      <c r="L15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>75</v>
+      </c>
+      <c r="R15">
+        <v>472</v>
+      </c>
+      <c r="S15">
+        <v>472</v>
+      </c>
+      <c r="T15" t="s">
+        <v>41</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" t="s">
+        <v>43</v>
+      </c>
+      <c r="X15">
+        <v>2240</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA15">
+        <v>1057.28</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="J16">
+        <v>2000</v>
+      </c>
+      <c r="K16">
+        <v>6000</v>
+      </c>
+      <c r="L16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>75</v>
+      </c>
+      <c r="R16">
+        <v>567</v>
+      </c>
+      <c r="S16">
+        <v>567</v>
+      </c>
+      <c r="T16" t="s">
+        <v>41</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
+        <v>43</v>
+      </c>
+      <c r="W16" t="s">
+        <v>43</v>
+      </c>
+      <c r="X16">
+        <v>3560</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA16">
+        <v>2018.52</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17">
+        <v>1500</v>
+      </c>
+      <c r="K17">
+        <v>3000</v>
+      </c>
+      <c r="L17" t="s">
+        <v>74</v>
+      </c>
+      <c r="M17" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>75</v>
+      </c>
+      <c r="R17">
+        <v>212</v>
+      </c>
+      <c r="S17">
+        <v>212</v>
+      </c>
+      <c r="T17" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17">
+        <v>2</v>
+      </c>
+      <c r="V17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W17" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17">
+        <v>2170</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA17">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>1500</v>
+      </c>
+      <c r="K18">
+        <v>3000</v>
+      </c>
+      <c r="L18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18" t="s">
+        <v>93</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" t="s">
+        <v>94</v>
+      </c>
+      <c r="P18" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>75</v>
+      </c>
+      <c r="R18">
+        <v>1014</v>
+      </c>
+      <c r="S18">
+        <v>1014</v>
+      </c>
+      <c r="T18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X18">
+        <v>3540</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA18">
+        <v>3589.56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>1500</v>
+      </c>
+      <c r="K19">
+        <v>3000</v>
+      </c>
+      <c r="L19" t="s">
+        <v>74</v>
+      </c>
+      <c r="M19" t="s">
+        <v>93</v>
+      </c>
+      <c r="N19" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" t="s">
+        <v>94</v>
+      </c>
+      <c r="P19" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>75</v>
+      </c>
+      <c r="R19">
+        <v>728</v>
+      </c>
+      <c r="S19">
+        <v>728</v>
+      </c>
+      <c r="T19" t="s">
+        <v>41</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" t="s">
+        <v>43</v>
+      </c>
+      <c r="X19">
+        <v>3490</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA19">
+        <v>2540.72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20">
+        <v>1.5</v>
+      </c>
+      <c r="J20">
+        <v>1500</v>
+      </c>
+      <c r="K20">
+        <v>3000</v>
+      </c>
+      <c r="L20" t="s">
+        <v>74</v>
+      </c>
+      <c r="M20" t="s">
+        <v>98</v>
+      </c>
+      <c r="N20" t="s">
+        <v>37</v>
+      </c>
+      <c r="O20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P20" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>75</v>
+      </c>
+      <c r="R20">
+        <v>592</v>
+      </c>
+      <c r="S20">
+        <v>592</v>
+      </c>
+      <c r="T20" t="s">
+        <v>41</v>
+      </c>
+      <c r="U20">
+        <v>11</v>
+      </c>
+      <c r="V20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20">
+        <v>3490</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA20">
+        <v>2066.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21">
+        <v>2.5</v>
+      </c>
+      <c r="J21">
+        <v>1500</v>
+      </c>
+      <c r="K21">
+        <v>3000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>74</v>
+      </c>
+      <c r="M21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" t="s">
+        <v>37</v>
+      </c>
+      <c r="O21" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>75</v>
+      </c>
+      <c r="R21">
+        <v>540</v>
+      </c>
+      <c r="S21">
+        <v>540</v>
+      </c>
+      <c r="T21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U21">
+        <v>6</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21">
+        <v>3540</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>2000</v>
+      </c>
+      <c r="K22">
+        <v>4000</v>
+      </c>
+      <c r="L22" t="s">
+        <v>74</v>
+      </c>
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>75</v>
+      </c>
+      <c r="R22">
+        <v>126</v>
+      </c>
+      <c r="S22">
+        <v>126</v>
+      </c>
+      <c r="T22" t="s">
+        <v>41</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>43</v>
+      </c>
+      <c r="X22">
+        <v>2190</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23">
+        <v>2000</v>
+      </c>
+      <c r="K23">
+        <v>4000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>74</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>75</v>
+      </c>
+      <c r="R23">
+        <v>315</v>
+      </c>
+      <c r="S23">
+        <v>315</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23">
+        <v>3560</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA23">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24">
+        <v>2000</v>
+      </c>
+      <c r="K24">
+        <v>4000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>74</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>75</v>
+      </c>
+      <c r="R24">
+        <v>189</v>
+      </c>
+      <c r="S24">
+        <v>189</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>2190</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>413.91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>2.5</v>
+      </c>
+      <c r="J25">
+        <v>1000</v>
+      </c>
+      <c r="K25">
+        <v>2000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>74</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>75</v>
+      </c>
+      <c r="R25">
+        <v>312</v>
+      </c>
+      <c r="S25">
+        <v>312</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>8</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>2220</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>692.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>75</v>
+      </c>
+      <c r="R26">
+        <v>2560</v>
+      </c>
+      <c r="S26">
+        <v>2560</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>2270</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>5811.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>110</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>75</v>
+      </c>
+      <c r="R27">
+        <v>3075</v>
+      </c>
+      <c r="S27">
+        <v>3075</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>2270</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>6980.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>5</v>
+      </c>
+      <c r="J28">
+        <v>1000</v>
+      </c>
+      <c r="K28">
+        <v>2000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>84</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>75</v>
+      </c>
+      <c r="R28">
+        <v>394</v>
+      </c>
+      <c r="S28">
+        <v>394</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>2020</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
+        <v>0.8</v>
+      </c>
+      <c r="J29">
+        <v>1000</v>
+      </c>
+      <c r="K29">
+        <v>2000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>74</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>75</v>
+      </c>
+      <c r="R29">
+        <v>176</v>
+      </c>
+      <c r="S29">
+        <v>176</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>14</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>2270</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>399.52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>1250</v>
+      </c>
+      <c r="K30">
+        <v>2500</v>
+      </c>
+      <c r="L30" t="s">
+        <v>36</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>75</v>
+      </c>
+      <c r="R30">
+        <v>322</v>
+      </c>
+      <c r="S30">
+        <v>322</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>1370</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>0.8</v>
+      </c>
+      <c r="J31">
+        <v>1250</v>
+      </c>
+      <c r="K31">
+        <v>2500</v>
+      </c>
+      <c r="L31" t="s">
+        <v>74</v>
+      </c>
+      <c r="M31" t="s">
+        <v>120</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>94</v>
+      </c>
+      <c r="P31" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>75</v>
+      </c>
+      <c r="R31">
+        <v>157</v>
+      </c>
+      <c r="S31">
+        <v>157</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>8</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>2220</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>348.54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>1250</v>
+      </c>
+      <c r="K32">
+        <v>2500</v>
+      </c>
+      <c r="L32" t="s">
+        <v>36</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>75</v>
+      </c>
+      <c r="R32">
+        <v>340</v>
+      </c>
+      <c r="S32">
+        <v>340</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>7</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>1370</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" t="s">
+        <v>72</v>
+      </c>
+      <c r="G33" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>3</v>
+      </c>
+      <c r="J33">
+        <v>2000</v>
+      </c>
+      <c r="K33">
+        <v>6000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>74</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>75</v>
+      </c>
+      <c r="R33">
+        <v>283</v>
+      </c>
+      <c r="S33">
+        <v>283</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>3560</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>1007.48</v>
+      </c>
+      <c r="AB33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>6</v>
+      </c>
+      <c r="J34">
+        <v>1500</v>
+      </c>
+      <c r="K34">
+        <v>3000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>74</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>75</v>
+      </c>
+      <c r="R34">
+        <v>212</v>
+      </c>
+      <c r="S34">
+        <v>212</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>3490</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35">
+        <v>8</v>
+      </c>
+      <c r="J35">
+        <v>1250</v>
+      </c>
+      <c r="K35">
+        <v>2500</v>
+      </c>
+      <c r="L35" t="s">
+        <v>84</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>75</v>
+      </c>
+      <c r="R35">
+        <v>394</v>
+      </c>
+      <c r="S35">
+        <v>394</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>3490</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" t="s">
+        <v>130</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <v>5</v>
+      </c>
+      <c r="J36">
+        <v>2000</v>
+      </c>
+      <c r="K36">
+        <v>6000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>84</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>75</v>
+      </c>
+      <c r="R36">
+        <v>472</v>
+      </c>
+      <c r="S36">
+        <v>472</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>2190</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <v>1500</v>
+      </c>
+      <c r="K37">
+        <v>3000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>74</v>
+      </c>
+      <c r="M37" t="s">
+        <v>98</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>75</v>
+      </c>
+      <c r="R37">
+        <v>970</v>
+      </c>
+      <c r="S37">
+        <v>970</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>13</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>3490</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>133</v>
+      </c>
+      <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>2.5</v>
+      </c>
+      <c r="J38">
+        <v>1500</v>
+      </c>
+      <c r="K38">
+        <v>3000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>74</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>75</v>
+      </c>
+      <c r="R38">
+        <v>526</v>
+      </c>
+      <c r="S38">
+        <v>526</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>6</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>3540</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G39" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>5</v>
+      </c>
+      <c r="J39">
+        <v>1500</v>
+      </c>
+      <c r="K39">
+        <v>3000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>84</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>75</v>
+      </c>
+      <c r="R39">
+        <v>354</v>
+      </c>
+      <c r="S39">
+        <v>354</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>2</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>1170</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" t="s">
+        <v>72</v>
+      </c>
+      <c r="G40" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40">
+        <v>1500</v>
+      </c>
+      <c r="K40">
+        <v>3000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>74</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>75</v>
+      </c>
+      <c r="R40">
+        <v>142</v>
+      </c>
+      <c r="S40">
+        <v>142</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>2170</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>71</v>
+      </c>
+      <c r="F41" t="s">
+        <v>72</v>
+      </c>
+      <c r="G41" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41">
+        <v>1500</v>
+      </c>
+      <c r="K41">
+        <v>3000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>74</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>75</v>
+      </c>
+      <c r="R41">
+        <v>142</v>
+      </c>
+      <c r="S41">
+        <v>142</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>2170</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42">
+        <v>1.5</v>
+      </c>
+      <c r="J42">
+        <v>1250</v>
+      </c>
+      <c r="L42" t="s">
+        <v>74</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>75</v>
+      </c>
+      <c r="R42">
+        <v>1275</v>
+      </c>
+      <c r="S42">
+        <v>1275</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>3590</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" t="s">
+        <v>71</v>
+      </c>
+      <c r="F43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G43" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>1250</v>
+      </c>
+      <c r="K43">
+        <v>2500</v>
+      </c>
+      <c r="L43" t="s">
+        <v>74</v>
+      </c>
+      <c r="M43" t="s">
+        <v>37</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>75</v>
+      </c>
+      <c r="R43">
+        <v>49</v>
+      </c>
+      <c r="S43">
+        <v>49</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>2</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>2170</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" t="s">
+        <v>72</v>
+      </c>
+      <c r="G44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>1250</v>
+      </c>
+      <c r="K44">
+        <v>2500</v>
+      </c>
+      <c r="L44" t="s">
+        <v>74</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>75</v>
+      </c>
+      <c r="R44">
+        <v>49</v>
+      </c>
+      <c r="S44">
+        <v>49</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>2</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>2170</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F45" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="J45">
+        <v>1500</v>
+      </c>
+      <c r="K45">
+        <v>3000</v>
+      </c>
+      <c r="L45" t="s">
+        <v>74</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>75</v>
+      </c>
+      <c r="R45">
+        <v>210</v>
+      </c>
+      <c r="S45">
+        <v>210</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>2</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>2170</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E46" t="s">
+        <v>71</v>
+      </c>
+      <c r="F46" t="s">
+        <v>72</v>
+      </c>
+      <c r="G46" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46">
+        <v>6</v>
+      </c>
+      <c r="J46">
+        <v>1250</v>
+      </c>
+      <c r="K46">
+        <v>2500</v>
+      </c>
+      <c r="L46" t="s">
+        <v>74</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>75</v>
+      </c>
+      <c r="R46">
+        <v>148</v>
+      </c>
+      <c r="S46">
+        <v>148</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>1</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>2170</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>321.16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" t="s">
+        <v>71</v>
+      </c>
+      <c r="F47" t="s">
+        <v>72</v>
+      </c>
+      <c r="G47" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
+      <c r="J47">
+        <v>1500</v>
+      </c>
+      <c r="K47">
+        <v>3000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>74</v>
+      </c>
+      <c r="M47" t="s">
+        <v>150</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>94</v>
+      </c>
+      <c r="P47" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>75</v>
+      </c>
+      <c r="R47">
+        <v>283</v>
+      </c>
+      <c r="S47">
+        <v>283</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>1</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>2170</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" t="s">
+        <v>149</v>
+      </c>
+      <c r="E48" t="s">
+        <v>71</v>
+      </c>
+      <c r="F48" t="s">
+        <v>72</v>
+      </c>
+      <c r="G48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>1500</v>
+      </c>
+      <c r="K48">
+        <v>3000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>74</v>
+      </c>
+      <c r="M48" t="s">
+        <v>150</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>94</v>
+      </c>
+      <c r="P48" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>75</v>
+      </c>
+      <c r="R48">
+        <v>283</v>
+      </c>
+      <c r="S48">
+        <v>283</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>2170</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" t="s">
+        <v>71</v>
+      </c>
+      <c r="F49" t="s">
+        <v>72</v>
+      </c>
+      <c r="G49" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>3</v>
+      </c>
+      <c r="J49">
+        <v>1500</v>
+      </c>
+      <c r="K49">
+        <v>3000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>74</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>75</v>
+      </c>
+      <c r="R49">
+        <v>212</v>
+      </c>
+      <c r="S49">
+        <v>212</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>2</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>1320</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>154</v>
+      </c>
+      <c r="B50" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50" t="s">
+        <v>71</v>
+      </c>
+      <c r="F50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>1500</v>
+      </c>
+      <c r="K50">
+        <v>3000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>74</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>75</v>
+      </c>
+      <c r="R50">
+        <v>212</v>
+      </c>
+      <c r="S50">
+        <v>212</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>6</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>2170</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>156</v>
+      </c>
+      <c r="B51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E51" t="s">
+        <v>71</v>
+      </c>
+      <c r="F51" t="s">
+        <v>72</v>
+      </c>
+      <c r="G51" t="s">
+        <v>83</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>6</v>
+      </c>
+      <c r="J51">
+        <v>1000</v>
+      </c>
+      <c r="K51">
+        <v>2000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>74</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>75</v>
+      </c>
+      <c r="R51">
+        <v>567</v>
+      </c>
+      <c r="S51">
+        <v>567</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>6</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>2220</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>158</v>
+      </c>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" t="s">
+        <v>157</v>
+      </c>
+      <c r="E52" t="s">
+        <v>71</v>
+      </c>
+      <c r="F52" t="s">
+        <v>72</v>
+      </c>
+      <c r="G52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>6</v>
+      </c>
+      <c r="J52">
+        <v>1000</v>
+      </c>
+      <c r="K52">
+        <v>2000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>74</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>75</v>
+      </c>
+      <c r="R52">
+        <v>567</v>
+      </c>
+      <c r="S52">
+        <v>567</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>6</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>2220</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>159</v>
+      </c>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53" t="s">
+        <v>72</v>
+      </c>
+      <c r="G53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>3</v>
+      </c>
+      <c r="J53">
+        <v>1500</v>
+      </c>
+      <c r="K53">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>74</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>75</v>
+      </c>
+      <c r="R53">
+        <v>319</v>
+      </c>
+      <c r="S53">
+        <v>319</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>3</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>1370</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>160</v>
+      </c>
+      <c r="B54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" t="s">
+        <v>161</v>
+      </c>
+      <c r="E54" t="s">
+        <v>71</v>
+      </c>
+      <c r="F54" t="s">
+        <v>72</v>
+      </c>
+      <c r="G54" t="s">
+        <v>83</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+      <c r="J54">
+        <v>1250</v>
+      </c>
+      <c r="K54">
+        <v>2500</v>
+      </c>
+      <c r="L54" t="s">
+        <v>74</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>75</v>
+      </c>
+      <c r="R54">
+        <v>197</v>
+      </c>
+      <c r="S54">
+        <v>197</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>4</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>2170</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" t="s">
+        <v>161</v>
+      </c>
+      <c r="E55" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" t="s">
+        <v>72</v>
+      </c>
+      <c r="G55" t="s">
+        <v>83</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55">
+        <v>1250</v>
+      </c>
+      <c r="K55">
+        <v>2500</v>
+      </c>
+      <c r="L55" t="s">
+        <v>74</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>75</v>
+      </c>
+      <c r="R55">
+        <v>246</v>
+      </c>
+      <c r="S55">
+        <v>246</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>5</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>2170</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>163</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" t="s">
+        <v>115</v>
+      </c>
+      <c r="E56" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" t="s">
+        <v>72</v>
+      </c>
+      <c r="G56" t="s">
+        <v>83</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>0.8</v>
+      </c>
+      <c r="J56">
+        <v>1000</v>
+      </c>
+      <c r="K56">
+        <v>2000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>74</v>
+      </c>
+      <c r="M56" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>75</v>
+      </c>
+      <c r="R56">
+        <v>1498</v>
+      </c>
+      <c r="S56">
+        <v>1498</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>1</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>2370</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57" t="s">
+        <v>72</v>
+      </c>
+      <c r="G57" t="s">
+        <v>83</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>0.8</v>
+      </c>
+      <c r="J57">
+        <v>1000</v>
+      </c>
+      <c r="K57">
+        <v>2000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>74</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>75</v>
+      </c>
+      <c r="R57">
+        <v>1498</v>
+      </c>
+      <c r="S57">
+        <v>1498</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>1</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>2370</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>165</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" t="s">
+        <v>166</v>
+      </c>
+      <c r="E58" t="s">
+        <v>71</v>
+      </c>
+      <c r="F58" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" t="s">
+        <v>83</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>5</v>
+      </c>
+      <c r="J58">
+        <v>1500</v>
+      </c>
+      <c r="K58">
+        <v>3000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>74</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>75</v>
+      </c>
+      <c r="R58">
+        <v>354</v>
+      </c>
+      <c r="S58">
+        <v>354</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>1</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>2220</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>167</v>
+      </c>
+      <c r="B59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" t="s">
+        <v>101</v>
+      </c>
+      <c r="E59" t="s">
+        <v>71</v>
+      </c>
+      <c r="F59" t="s">
+        <v>72</v>
+      </c>
+      <c r="G59" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+      <c r="J59">
+        <v>2000</v>
+      </c>
+      <c r="K59">
+        <v>4000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>74</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>75</v>
+      </c>
+      <c r="R59">
+        <v>126</v>
+      </c>
+      <c r="S59">
+        <v>126</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>1</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2190</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>168</v>
+      </c>
+      <c r="B60" t="s">
+        <v>78</v>
+      </c>
+      <c r="C60" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" t="s">
+        <v>132</v>
+      </c>
+      <c r="E60" t="s">
+        <v>71</v>
+      </c>
+      <c r="F60" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" t="s">
+        <v>55</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60">
+        <v>1500</v>
+      </c>
+      <c r="K60">
+        <v>3000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>74</v>
+      </c>
+      <c r="M60" t="s">
+        <v>98</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>75</v>
+      </c>
+      <c r="R60">
+        <v>1010</v>
+      </c>
+      <c r="S60">
+        <v>1010</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>14</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>3540</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" t="s">
+        <v>170</v>
+      </c>
+      <c r="E61" t="s">
+        <v>71</v>
+      </c>
+      <c r="F61" t="s">
+        <v>72</v>
+      </c>
+      <c r="G61" t="s">
+        <v>55</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>1500</v>
+      </c>
+      <c r="K61">
+        <v>3000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>74</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>75</v>
+      </c>
+      <c r="R61">
+        <v>283</v>
+      </c>
+      <c r="S61">
+        <v>283</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>4</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>3540</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" t="s">
+        <v>172</v>
+      </c>
+      <c r="E62" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" t="s">
+        <v>173</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>0.8</v>
+      </c>
+      <c r="J62">
+        <v>1000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>174</v>
+      </c>
+      <c r="P62" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>75</v>
+      </c>
+      <c r="R62">
+        <v>1585</v>
+      </c>
+      <c r="S62">
+        <v>1585</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>1</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>2370</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>175</v>
+      </c>
+      <c r="B63" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" t="s">
+        <v>176</v>
+      </c>
+      <c r="E63" t="s">
+        <v>71</v>
+      </c>
+      <c r="F63" t="s">
+        <v>72</v>
+      </c>
+      <c r="G63" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>1.5</v>
+      </c>
+      <c r="J63">
+        <v>1500</v>
+      </c>
+      <c r="K63">
+        <v>3000</v>
+      </c>
+      <c r="L63" t="s">
+        <v>74</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>75</v>
+      </c>
+      <c r="R63">
+        <v>212</v>
+      </c>
+      <c r="S63">
+        <v>212</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>1</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>1320</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>177</v>
+      </c>
+      <c r="B64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64" t="s">
+        <v>178</v>
+      </c>
+      <c r="E64" t="s">
+        <v>71</v>
+      </c>
+      <c r="F64" t="s">
+        <v>72</v>
+      </c>
+      <c r="G64" t="s">
+        <v>83</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>3</v>
+      </c>
+      <c r="J64">
+        <v>1250</v>
+      </c>
+      <c r="K64">
+        <v>2500</v>
+      </c>
+      <c r="L64" t="s">
+        <v>74</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>75</v>
+      </c>
+      <c r="R64">
+        <v>74</v>
+      </c>
+      <c r="S64">
+        <v>74</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>1</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>2170</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>160.58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>179</v>
+      </c>
+      <c r="B65" t="s">
+        <v>78</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" t="s">
+        <v>71</v>
+      </c>
+      <c r="F65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G65" t="s">
+        <v>55</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>2.5</v>
+      </c>
+      <c r="J65">
+        <v>1500</v>
+      </c>
+      <c r="K65">
+        <v>3000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>74</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>75</v>
+      </c>
+      <c r="R65">
+        <v>540</v>
+      </c>
+      <c r="S65">
+        <v>540</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>6</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>3540</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>180</v>
+      </c>
+      <c r="B66" t="s">
+        <v>78</v>
+      </c>
+      <c r="C66" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66" t="s">
+        <v>71</v>
+      </c>
+      <c r="F66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G66" t="s">
+        <v>55</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>2.5</v>
+      </c>
+      <c r="J66">
+        <v>1500</v>
+      </c>
+      <c r="K66">
+        <v>3000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>74</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>75</v>
+      </c>
+      <c r="R66">
+        <v>520</v>
+      </c>
+      <c r="S66">
+        <v>520</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>6</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>3540</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>181</v>
+      </c>
+      <c r="B67" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" t="s">
+        <v>69</v>
+      </c>
+      <c r="D67" t="s">
+        <v>79</v>
+      </c>
+      <c r="E67" t="s">
+        <v>71</v>
+      </c>
+      <c r="F67" t="s">
+        <v>72</v>
+      </c>
+      <c r="G67" t="s">
+        <v>55</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>2.5</v>
+      </c>
+      <c r="J67">
+        <v>1500</v>
+      </c>
+      <c r="K67">
+        <v>3000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>74</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>75</v>
+      </c>
+      <c r="R67">
+        <v>530</v>
+      </c>
+      <c r="S67">
+        <v>530</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>6</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>3540</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" t="s">
+        <v>69</v>
+      </c>
+      <c r="D68" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" t="s">
+        <v>71</v>
+      </c>
+      <c r="F68" t="s">
+        <v>72</v>
+      </c>
+      <c r="G68" t="s">
+        <v>55</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>2.5</v>
+      </c>
+      <c r="J68">
+        <v>1500</v>
+      </c>
+      <c r="K68">
+        <v>3000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>74</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>75</v>
+      </c>
+      <c r="R68">
+        <v>526</v>
+      </c>
+      <c r="S68">
+        <v>526</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>6</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>3540</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>183</v>
+      </c>
+      <c r="B69" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" t="s">
+        <v>184</v>
+      </c>
+      <c r="E69" t="s">
+        <v>71</v>
+      </c>
+      <c r="F69" t="s">
+        <v>72</v>
+      </c>
+      <c r="G69" t="s">
+        <v>55</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>3</v>
+      </c>
+      <c r="J69">
+        <v>1500</v>
+      </c>
+      <c r="K69">
+        <v>3000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>74</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>75</v>
+      </c>
+      <c r="R69">
+        <v>212</v>
+      </c>
+      <c r="S69">
+        <v>212</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>1</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>3490</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>185</v>
+      </c>
+      <c r="B70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" t="s">
+        <v>184</v>
+      </c>
+      <c r="E70" t="s">
+        <v>71</v>
+      </c>
+      <c r="F70" t="s">
+        <v>72</v>
+      </c>
+      <c r="G70" t="s">
+        <v>55</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>3</v>
+      </c>
+      <c r="J70">
+        <v>1500</v>
+      </c>
+      <c r="K70">
+        <v>3000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>74</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>38</v>
+      </c>
+      <c r="P70" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>75</v>
+      </c>
+      <c r="R70">
+        <v>212</v>
+      </c>
+      <c r="S70">
+        <v>212</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>1</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>3490</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>186</v>
+      </c>
+      <c r="B71" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" t="s">
+        <v>69</v>
+      </c>
+      <c r="D71" t="s">
+        <v>187</v>
+      </c>
+      <c r="E71" t="s">
+        <v>71</v>
+      </c>
+      <c r="F71" t="s">
+        <v>72</v>
+      </c>
+      <c r="G71" t="s">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>4</v>
+      </c>
+      <c r="J71">
+        <v>1000</v>
+      </c>
+      <c r="K71">
+        <v>2000</v>
+      </c>
+      <c r="L71" t="s">
+        <v>74</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>75</v>
+      </c>
+      <c r="R71">
+        <v>315</v>
+      </c>
+      <c r="S71">
+        <v>315</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>5</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>2220</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>188</v>
+      </c>
+      <c r="B72" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" t="s">
+        <v>69</v>
+      </c>
+      <c r="D72" t="s">
+        <v>189</v>
+      </c>
+      <c r="E72" t="s">
+        <v>71</v>
+      </c>
+      <c r="F72" t="s">
+        <v>72</v>
+      </c>
+      <c r="G72" t="s">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>1.5</v>
+      </c>
+      <c r="J72">
+        <v>1250</v>
+      </c>
+      <c r="K72">
+        <v>2500</v>
+      </c>
+      <c r="L72" t="s">
+        <v>74</v>
+      </c>
+      <c r="M72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R72">
+        <v>295</v>
+      </c>
+      <c r="S72">
+        <v>295</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>8</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>2220</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>654.9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>190</v>
+      </c>
+      <c r="B73" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" t="s">
+        <v>69</v>
+      </c>
+      <c r="D73" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" t="s">
+        <v>71</v>
+      </c>
+      <c r="F73" t="s">
+        <v>72</v>
+      </c>
+      <c r="G73" t="s">
+        <v>83</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>5</v>
+      </c>
+      <c r="J73">
+        <v>1000</v>
+      </c>
+      <c r="K73">
+        <v>2000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>84</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>75</v>
+      </c>
+      <c r="R73">
+        <v>944</v>
+      </c>
+      <c r="S73">
+        <v>944</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>1</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>2020</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>191</v>
+      </c>
+      <c r="B74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C74" t="s">
+        <v>69</v>
+      </c>
+      <c r="D74" t="s">
+        <v>157</v>
+      </c>
+      <c r="E74" t="s">
+        <v>71</v>
+      </c>
+      <c r="F74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G74" t="s">
+        <v>83</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>6</v>
+      </c>
+      <c r="J74">
+        <v>1000</v>
+      </c>
+      <c r="K74">
+        <v>2000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>74</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>75</v>
+      </c>
+      <c r="R74">
+        <v>189</v>
+      </c>
+      <c r="S74">
+        <v>189</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>2</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>2170</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>410.13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>192</v>
+      </c>
+      <c r="B75" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" t="s">
+        <v>69</v>
+      </c>
+      <c r="D75" t="s">
+        <v>193</v>
+      </c>
+      <c r="E75" t="s">
+        <v>71</v>
+      </c>
+      <c r="F75" t="s">
+        <v>72</v>
+      </c>
+      <c r="G75" t="s">
+        <v>83</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>1.5</v>
+      </c>
+      <c r="J75">
+        <v>1000</v>
+      </c>
+      <c r="K75">
+        <v>2000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>74</v>
+      </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>75</v>
+      </c>
+      <c r="R75">
+        <v>260</v>
+      </c>
+      <c r="S75">
+        <v>260</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>11</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>2220</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>577.2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>194</v>
+      </c>
+      <c r="B76" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" t="s">
+        <v>69</v>
+      </c>
+      <c r="D76" t="s">
+        <v>195</v>
+      </c>
+      <c r="E76" t="s">
+        <v>71</v>
+      </c>
+      <c r="F76" t="s">
+        <v>72</v>
+      </c>
+      <c r="G76" t="s">
+        <v>55</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>1500</v>
+      </c>
+      <c r="K76">
+        <v>3000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>74</v>
+      </c>
+      <c r="M76" t="s">
+        <v>98</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>75</v>
+      </c>
+      <c r="R76">
+        <v>1224</v>
+      </c>
+      <c r="S76">
+        <v>1224</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>34</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>3540</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>196</v>
+      </c>
+      <c r="B77" t="s">
+        <v>68</v>
+      </c>
+      <c r="C77" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77" t="s">
+        <v>161</v>
+      </c>
+      <c r="E77" t="s">
+        <v>71</v>
+      </c>
+      <c r="F77" t="s">
+        <v>72</v>
+      </c>
+      <c r="G77" t="s">
+        <v>83</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>2</v>
+      </c>
+      <c r="J77">
+        <v>1250</v>
+      </c>
+      <c r="K77">
+        <v>2500</v>
+      </c>
+      <c r="L77" t="s">
+        <v>74</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>75</v>
+      </c>
+      <c r="R77">
+        <v>197</v>
+      </c>
+      <c r="S77">
+        <v>197</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>4</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>2170</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>197</v>
+      </c>
+      <c r="B78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C78" t="s">
+        <v>69</v>
+      </c>
+      <c r="D78" t="s">
+        <v>198</v>
+      </c>
+      <c r="E78" t="s">
+        <v>71</v>
+      </c>
+      <c r="F78" t="s">
+        <v>72</v>
+      </c>
+      <c r="G78" t="s">
+        <v>55</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <v>1500</v>
+      </c>
+      <c r="K78">
+        <v>3000</v>
+      </c>
+      <c r="L78" t="s">
+        <v>74</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>75</v>
+      </c>
+      <c r="R78">
+        <v>35</v>
+      </c>
+      <c r="S78">
+        <v>35</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>1</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>3490</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" t="s">
+        <v>68</v>
+      </c>
+      <c r="C79" t="s">
+        <v>69</v>
+      </c>
+      <c r="D79" t="s">
+        <v>198</v>
+      </c>
+      <c r="E79" t="s">
+        <v>71</v>
+      </c>
+      <c r="F79" t="s">
+        <v>72</v>
+      </c>
+      <c r="G79" t="s">
+        <v>55</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <v>1500</v>
+      </c>
+      <c r="K79">
+        <v>3000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>74</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>75</v>
+      </c>
+      <c r="R79">
+        <v>177</v>
+      </c>
+      <c r="S79">
+        <v>177</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>5</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>3490</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>617.73</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>200</v>
+      </c>
+      <c r="B80" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" t="s">
+        <v>69</v>
+      </c>
+      <c r="D80" t="s">
+        <v>201</v>
+      </c>
+      <c r="E80" t="s">
+        <v>71</v>
+      </c>
+      <c r="F80" t="s">
+        <v>33</v>
+      </c>
+      <c r="G80" t="s">
+        <v>202</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>0.6</v>
+      </c>
+      <c r="J80">
+        <v>1000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>36</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>75</v>
+      </c>
+      <c r="R80">
+        <v>745</v>
+      </c>
+      <c r="S80">
+        <v>745</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>1</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>2290</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>1706.05</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>203</v>
+      </c>
+      <c r="B81" t="s">
+        <v>78</v>
+      </c>
+      <c r="C81" t="s">
+        <v>69</v>
+      </c>
+      <c r="D81" t="s">
+        <v>204</v>
+      </c>
+      <c r="E81" t="s">
+        <v>71</v>
+      </c>
+      <c r="F81" t="s">
+        <v>72</v>
+      </c>
+      <c r="G81" t="s">
+        <v>34</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>1.5</v>
+      </c>
+      <c r="J81">
+        <v>1500</v>
+      </c>
+      <c r="K81">
+        <v>3000</v>
+      </c>
+      <c r="L81" t="s">
+        <v>36</v>
+      </c>
+      <c r="M81" t="s">
+        <v>98</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>75</v>
+      </c>
+      <c r="R81">
+        <v>916</v>
+      </c>
+      <c r="S81">
+        <v>916</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>18</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>1320</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>205</v>
+      </c>
+      <c r="B82" t="s">
+        <v>68</v>
+      </c>
+      <c r="C82" t="s">
+        <v>69</v>
+      </c>
+      <c r="D82" t="s">
+        <v>184</v>
+      </c>
+      <c r="E82" t="s">
+        <v>71</v>
+      </c>
+      <c r="F82" t="s">
+        <v>72</v>
+      </c>
+      <c r="G82" t="s">
+        <v>55</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>3</v>
+      </c>
+      <c r="J82">
+        <v>1500</v>
+      </c>
+      <c r="K82">
+        <v>3000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>74</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>75</v>
+      </c>
+      <c r="R82">
+        <v>319</v>
+      </c>
+      <c r="S82">
+        <v>319</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>1</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>3540</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>206</v>
+      </c>
+      <c r="B83" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83" t="s">
+        <v>69</v>
+      </c>
+      <c r="D83" t="s">
+        <v>184</v>
+      </c>
+      <c r="E83" t="s">
+        <v>71</v>
+      </c>
+      <c r="F83" t="s">
+        <v>72</v>
+      </c>
+      <c r="G83" t="s">
+        <v>55</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>3</v>
+      </c>
+      <c r="J83">
+        <v>1500</v>
+      </c>
+      <c r="K83">
+        <v>3000</v>
+      </c>
+      <c r="L83" t="s">
+        <v>74</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>75</v>
+      </c>
+      <c r="R83">
+        <v>212</v>
+      </c>
+      <c r="S83">
+        <v>212</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>1</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>3490</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>207</v>
+      </c>
+      <c r="B84" t="s">
+        <v>68</v>
+      </c>
+      <c r="C84" t="s">
+        <v>69</v>
+      </c>
+      <c r="D84" t="s">
+        <v>184</v>
+      </c>
+      <c r="E84" t="s">
+        <v>71</v>
+      </c>
+      <c r="F84" t="s">
+        <v>72</v>
+      </c>
+      <c r="G84" t="s">
+        <v>55</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>3</v>
+      </c>
+      <c r="J84">
+        <v>1500</v>
+      </c>
+      <c r="K84">
+        <v>3000</v>
+      </c>
+      <c r="L84" t="s">
+        <v>74</v>
+      </c>
+      <c r="M84" t="s">
+        <v>37</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>75</v>
+      </c>
+      <c r="R84">
+        <v>212</v>
+      </c>
+      <c r="S84">
+        <v>212</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>1</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>3490</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>208</v>
+      </c>
+      <c r="B85" t="s">
+        <v>68</v>
+      </c>
+      <c r="C85" t="s">
+        <v>69</v>
+      </c>
+      <c r="D85" t="s">
+        <v>184</v>
+      </c>
+      <c r="E85" t="s">
+        <v>71</v>
+      </c>
+      <c r="F85" t="s">
+        <v>72</v>
+      </c>
+      <c r="G85" t="s">
+        <v>55</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>3</v>
+      </c>
+      <c r="J85">
+        <v>1500</v>
+      </c>
+      <c r="K85">
+        <v>3000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>74</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>75</v>
+      </c>
+      <c r="R85">
+        <v>319</v>
+      </c>
+      <c r="S85">
+        <v>319</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>1</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>3540</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>209</v>
+      </c>
+      <c r="B86" t="s">
+        <v>81</v>
+      </c>
+      <c r="C86" t="s">
+        <v>69</v>
+      </c>
+      <c r="D86" t="s">
+        <v>210</v>
+      </c>
+      <c r="E86" t="s">
+        <v>71</v>
+      </c>
+      <c r="F86" t="s">
+        <v>72</v>
+      </c>
+      <c r="G86" t="s">
+        <v>55</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="J86">
+        <v>2000</v>
+      </c>
+      <c r="K86">
+        <v>6000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>74</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>75</v>
+      </c>
+      <c r="R86">
+        <v>189</v>
+      </c>
+      <c r="S86">
+        <v>189</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>1</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>3510</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>663.39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" t="s">
+        <v>68</v>
+      </c>
+      <c r="C87" t="s">
+        <v>69</v>
+      </c>
+      <c r="D87" t="s">
+        <v>212</v>
+      </c>
+      <c r="E87" t="s">
+        <v>71</v>
+      </c>
+      <c r="F87" t="s">
+        <v>72</v>
+      </c>
+      <c r="G87" t="s">
+        <v>83</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87">
+        <v>4</v>
+      </c>
+      <c r="J87">
+        <v>1000</v>
+      </c>
+      <c r="K87">
+        <v>2000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>74</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>75</v>
+      </c>
+      <c r="R87">
+        <v>63</v>
+      </c>
+      <c r="S87">
+        <v>63</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>1</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>2170</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>136.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="229">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -245,6 +245,459 @@
   </si>
   <si>
     <t>ASME SA 240 / ASTM A 240 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4304</t>
+  </si>
+  <si>
+    <t>T468837</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>T468838</t>
+  </si>
+  <si>
+    <t>7246484</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7246542</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
+    <t>7246814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 5.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7246817</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 6.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T473609</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7247036</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Polish grain 400 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7247041</t>
+  </si>
+  <si>
+    <t>7247338</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7247409</t>
+  </si>
+  <si>
+    <t>7247854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475488</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248626</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248988</t>
+  </si>
+  <si>
+    <t>Coil 1.4307-304L 2D 1.0 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>7248989</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T477742</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>K30/1.4016-430</t>
+  </si>
+  <si>
+    <t>7249627</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Duplo polish grain 320</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481266</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481267</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T481616</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T481617</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481869</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7253484</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 240 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 240</t>
+  </si>
+  <si>
+    <t>7253485</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484088</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484797</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254248</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T485455</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254992</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T486939</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>T487305</t>
+  </si>
+  <si>
+    <t>T487411</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255816</t>
+  </si>
+  <si>
+    <t>T487947</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T487964</t>
+  </si>
+  <si>
+    <t>7256046</t>
+  </si>
+  <si>
+    <t>Coil 1.4301-304 2R 0.6 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>7256139</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>T488237</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256367</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.2 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7256368</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Scotchbrite</t>
+  </si>
+  <si>
+    <t>T488483</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T488484</t>
   </si>
 </sst>
 </file>
@@ -621,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -1522,6 +1975,6723 @@
         <v>12553.8</v>
       </c>
     </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <v>6</v>
+      </c>
+      <c r="J12">
+        <v>1000</v>
+      </c>
+      <c r="K12">
+        <v>2000</v>
+      </c>
+      <c r="L12" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>83</v>
+      </c>
+      <c r="R12">
+        <v>283</v>
+      </c>
+      <c r="S12">
+        <v>283</v>
+      </c>
+      <c r="T12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12">
+        <v>5</v>
+      </c>
+      <c r="V12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" t="s">
+        <v>43</v>
+      </c>
+      <c r="X12">
+        <v>3690</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA12">
+        <v>1044.27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13">
+        <v>6</v>
+      </c>
+      <c r="J13">
+        <v>1000</v>
+      </c>
+      <c r="K13">
+        <v>2000</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" t="s">
+        <v>38</v>
+      </c>
+      <c r="P13" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>83</v>
+      </c>
+      <c r="R13">
+        <v>567</v>
+      </c>
+      <c r="S13">
+        <v>567</v>
+      </c>
+      <c r="T13" t="s">
+        <v>41</v>
+      </c>
+      <c r="U13">
+        <v>6</v>
+      </c>
+      <c r="V13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13">
+        <v>3690</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA13">
+        <v>2092.23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14">
+        <v>2.5</v>
+      </c>
+      <c r="J14">
+        <v>1500</v>
+      </c>
+      <c r="K14">
+        <v>3000</v>
+      </c>
+      <c r="L14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>83</v>
+      </c>
+      <c r="R14">
+        <v>554</v>
+      </c>
+      <c r="S14">
+        <v>554</v>
+      </c>
+      <c r="T14" t="s">
+        <v>41</v>
+      </c>
+      <c r="U14">
+        <v>6</v>
+      </c>
+      <c r="V14" t="s">
+        <v>43</v>
+      </c>
+      <c r="W14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X14">
+        <v>3540</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA14">
+        <v>1961.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15">
+        <v>6</v>
+      </c>
+      <c r="J15">
+        <v>1000</v>
+      </c>
+      <c r="K15">
+        <v>2000</v>
+      </c>
+      <c r="L15" t="s">
+        <v>91</v>
+      </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>83</v>
+      </c>
+      <c r="R15">
+        <v>1133</v>
+      </c>
+      <c r="S15">
+        <v>1133</v>
+      </c>
+      <c r="T15" t="s">
+        <v>41</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" t="s">
+        <v>43</v>
+      </c>
+      <c r="X15">
+        <v>2070</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA15">
+        <v>2345.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>2000</v>
+      </c>
+      <c r="K16">
+        <v>6000</v>
+      </c>
+      <c r="L16" t="s">
+        <v>36</v>
+      </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>83</v>
+      </c>
+      <c r="R16">
+        <v>472</v>
+      </c>
+      <c r="S16">
+        <v>472</v>
+      </c>
+      <c r="T16" t="s">
+        <v>41</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
+        <v>43</v>
+      </c>
+      <c r="W16" t="s">
+        <v>43</v>
+      </c>
+      <c r="X16">
+        <v>2240</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA16">
+        <v>1057.28</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17">
+        <v>6</v>
+      </c>
+      <c r="J17">
+        <v>2000</v>
+      </c>
+      <c r="K17">
+        <v>6000</v>
+      </c>
+      <c r="L17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M17" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>83</v>
+      </c>
+      <c r="R17">
+        <v>567</v>
+      </c>
+      <c r="S17">
+        <v>567</v>
+      </c>
+      <c r="T17" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W17" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17">
+        <v>3560</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA17">
+        <v>2018.52</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <v>1500</v>
+      </c>
+      <c r="K18">
+        <v>3000</v>
+      </c>
+      <c r="L18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M18" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>83</v>
+      </c>
+      <c r="R18">
+        <v>212</v>
+      </c>
+      <c r="S18">
+        <v>212</v>
+      </c>
+      <c r="T18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X18">
+        <v>2170</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA18">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>1500</v>
+      </c>
+      <c r="K19">
+        <v>3000</v>
+      </c>
+      <c r="L19" t="s">
+        <v>36</v>
+      </c>
+      <c r="M19" t="s">
+        <v>100</v>
+      </c>
+      <c r="N19" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" t="s">
+        <v>101</v>
+      </c>
+      <c r="P19" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>83</v>
+      </c>
+      <c r="R19">
+        <v>1014</v>
+      </c>
+      <c r="S19">
+        <v>1014</v>
+      </c>
+      <c r="T19" t="s">
+        <v>41</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" t="s">
+        <v>43</v>
+      </c>
+      <c r="X19">
+        <v>3540</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA19">
+        <v>3589.56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <v>1500</v>
+      </c>
+      <c r="K20">
+        <v>3000</v>
+      </c>
+      <c r="L20" t="s">
+        <v>36</v>
+      </c>
+      <c r="M20" t="s">
+        <v>100</v>
+      </c>
+      <c r="N20" t="s">
+        <v>37</v>
+      </c>
+      <c r="O20" t="s">
+        <v>101</v>
+      </c>
+      <c r="P20" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>83</v>
+      </c>
+      <c r="R20">
+        <v>728</v>
+      </c>
+      <c r="S20">
+        <v>728</v>
+      </c>
+      <c r="T20" t="s">
+        <v>41</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20">
+        <v>3490</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA20">
+        <v>2540.72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21">
+        <v>1.5</v>
+      </c>
+      <c r="J21">
+        <v>1500</v>
+      </c>
+      <c r="K21">
+        <v>3000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>36</v>
+      </c>
+      <c r="M21" t="s">
+        <v>105</v>
+      </c>
+      <c r="N21" t="s">
+        <v>37</v>
+      </c>
+      <c r="O21" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>83</v>
+      </c>
+      <c r="R21">
+        <v>592</v>
+      </c>
+      <c r="S21">
+        <v>592</v>
+      </c>
+      <c r="T21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U21">
+        <v>11</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21">
+        <v>3490</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>2066.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22">
+        <v>2.5</v>
+      </c>
+      <c r="J22">
+        <v>1500</v>
+      </c>
+      <c r="K22">
+        <v>3000</v>
+      </c>
+      <c r="L22" t="s">
+        <v>36</v>
+      </c>
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>83</v>
+      </c>
+      <c r="R22">
+        <v>540</v>
+      </c>
+      <c r="S22">
+        <v>540</v>
+      </c>
+      <c r="T22" t="s">
+        <v>41</v>
+      </c>
+      <c r="U22">
+        <v>6</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>43</v>
+      </c>
+      <c r="X22">
+        <v>3540</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>2000</v>
+      </c>
+      <c r="K23">
+        <v>4000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>83</v>
+      </c>
+      <c r="R23">
+        <v>126</v>
+      </c>
+      <c r="S23">
+        <v>126</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23">
+        <v>2190</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA23">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
+        <v>2000</v>
+      </c>
+      <c r="K24">
+        <v>4000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>36</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>83</v>
+      </c>
+      <c r="R24">
+        <v>315</v>
+      </c>
+      <c r="S24">
+        <v>315</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>3560</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>3</v>
+      </c>
+      <c r="J25">
+        <v>2000</v>
+      </c>
+      <c r="K25">
+        <v>4000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>36</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>83</v>
+      </c>
+      <c r="R25">
+        <v>189</v>
+      </c>
+      <c r="S25">
+        <v>189</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>2190</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>413.91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>2.5</v>
+      </c>
+      <c r="J26">
+        <v>1000</v>
+      </c>
+      <c r="K26">
+        <v>2000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>36</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>83</v>
+      </c>
+      <c r="R26">
+        <v>312</v>
+      </c>
+      <c r="S26">
+        <v>312</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>8</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>2220</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>692.64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" t="s">
+        <v>116</v>
+      </c>
+      <c r="E27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>117</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>83</v>
+      </c>
+      <c r="R27">
+        <v>2560</v>
+      </c>
+      <c r="S27">
+        <v>2560</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>2270</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>5811.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>117</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>83</v>
+      </c>
+      <c r="R28">
+        <v>3075</v>
+      </c>
+      <c r="S28">
+        <v>3075</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>2270</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>6980.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <v>1000</v>
+      </c>
+      <c r="K29">
+        <v>2000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>91</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>83</v>
+      </c>
+      <c r="R29">
+        <v>394</v>
+      </c>
+      <c r="S29">
+        <v>394</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>2020</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>0.8</v>
+      </c>
+      <c r="J30">
+        <v>1000</v>
+      </c>
+      <c r="K30">
+        <v>2000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>36</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>83</v>
+      </c>
+      <c r="R30">
+        <v>176</v>
+      </c>
+      <c r="S30">
+        <v>176</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>14</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>2270</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>399.52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>1250</v>
+      </c>
+      <c r="K31">
+        <v>2500</v>
+      </c>
+      <c r="L31" t="s">
+        <v>51</v>
+      </c>
+      <c r="M31" t="s">
+        <v>37</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>83</v>
+      </c>
+      <c r="R31">
+        <v>322</v>
+      </c>
+      <c r="S31">
+        <v>322</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>1</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>1370</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32">
+        <v>0.8</v>
+      </c>
+      <c r="J32">
+        <v>1250</v>
+      </c>
+      <c r="K32">
+        <v>2500</v>
+      </c>
+      <c r="L32" t="s">
+        <v>36</v>
+      </c>
+      <c r="M32" t="s">
+        <v>128</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>101</v>
+      </c>
+      <c r="P32" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>83</v>
+      </c>
+      <c r="R32">
+        <v>157</v>
+      </c>
+      <c r="S32">
+        <v>157</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>8</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>2220</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>348.54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" t="s">
+        <v>125</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>1250</v>
+      </c>
+      <c r="K33">
+        <v>2500</v>
+      </c>
+      <c r="L33" t="s">
+        <v>51</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>83</v>
+      </c>
+      <c r="R33">
+        <v>340</v>
+      </c>
+      <c r="S33">
+        <v>340</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>7</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>1370</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>2000</v>
+      </c>
+      <c r="K34">
+        <v>6000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>36</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R34">
+        <v>283</v>
+      </c>
+      <c r="S34">
+        <v>283</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>3560</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>1007.48</v>
+      </c>
+      <c r="AB34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35">
+        <v>6</v>
+      </c>
+      <c r="J35">
+        <v>1500</v>
+      </c>
+      <c r="K35">
+        <v>3000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>36</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>83</v>
+      </c>
+      <c r="R35">
+        <v>212</v>
+      </c>
+      <c r="S35">
+        <v>212</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>3490</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <v>8</v>
+      </c>
+      <c r="J36">
+        <v>1250</v>
+      </c>
+      <c r="K36">
+        <v>2500</v>
+      </c>
+      <c r="L36" t="s">
+        <v>91</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>83</v>
+      </c>
+      <c r="R36">
+        <v>394</v>
+      </c>
+      <c r="S36">
+        <v>394</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>3490</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" t="s">
+        <v>138</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37">
+        <v>2000</v>
+      </c>
+      <c r="K37">
+        <v>6000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>91</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>83</v>
+      </c>
+      <c r="R37">
+        <v>472</v>
+      </c>
+      <c r="S37">
+        <v>472</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>2190</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38">
+        <v>1500</v>
+      </c>
+      <c r="K38">
+        <v>3000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>36</v>
+      </c>
+      <c r="M38" t="s">
+        <v>105</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>83</v>
+      </c>
+      <c r="R38">
+        <v>970</v>
+      </c>
+      <c r="S38">
+        <v>970</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>13</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>3490</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" t="s">
+        <v>87</v>
+      </c>
+      <c r="E39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" t="s">
+        <v>50</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>2.5</v>
+      </c>
+      <c r="J39">
+        <v>1500</v>
+      </c>
+      <c r="K39">
+        <v>3000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>36</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>83</v>
+      </c>
+      <c r="R39">
+        <v>526</v>
+      </c>
+      <c r="S39">
+        <v>526</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>6</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>3540</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>142</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" t="s">
+        <v>125</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>5</v>
+      </c>
+      <c r="J40">
+        <v>1500</v>
+      </c>
+      <c r="K40">
+        <v>3000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>91</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>83</v>
+      </c>
+      <c r="R40">
+        <v>354</v>
+      </c>
+      <c r="S40">
+        <v>354</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>2</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>1170</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" t="s">
+        <v>62</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41">
+        <v>1500</v>
+      </c>
+      <c r="K41">
+        <v>3000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>36</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>83</v>
+      </c>
+      <c r="R41">
+        <v>142</v>
+      </c>
+      <c r="S41">
+        <v>142</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>2170</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>146</v>
+      </c>
+      <c r="B42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" t="s">
+        <v>62</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42">
+        <v>4</v>
+      </c>
+      <c r="J42">
+        <v>1500</v>
+      </c>
+      <c r="K42">
+        <v>3000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>36</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>83</v>
+      </c>
+      <c r="R42">
+        <v>142</v>
+      </c>
+      <c r="S42">
+        <v>142</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>2170</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" t="s">
+        <v>148</v>
+      </c>
+      <c r="E43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>1.5</v>
+      </c>
+      <c r="J43">
+        <v>1250</v>
+      </c>
+      <c r="L43" t="s">
+        <v>36</v>
+      </c>
+      <c r="M43" t="s">
+        <v>37</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>83</v>
+      </c>
+      <c r="R43">
+        <v>1275</v>
+      </c>
+      <c r="S43">
+        <v>1275</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>1</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>3590</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" t="s">
+        <v>150</v>
+      </c>
+      <c r="E44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F44" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" t="s">
+        <v>62</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>1250</v>
+      </c>
+      <c r="K44">
+        <v>2500</v>
+      </c>
+      <c r="L44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>83</v>
+      </c>
+      <c r="R44">
+        <v>49</v>
+      </c>
+      <c r="S44">
+        <v>49</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>2</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>2170</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" t="s">
+        <v>150</v>
+      </c>
+      <c r="E45" t="s">
+        <v>61</v>
+      </c>
+      <c r="F45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" t="s">
+        <v>62</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>1250</v>
+      </c>
+      <c r="K45">
+        <v>2500</v>
+      </c>
+      <c r="L45" t="s">
+        <v>36</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>83</v>
+      </c>
+      <c r="R45">
+        <v>49</v>
+      </c>
+      <c r="S45">
+        <v>49</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>2</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>2170</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" t="s">
+        <v>62</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>1500</v>
+      </c>
+      <c r="K46">
+        <v>3000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>83</v>
+      </c>
+      <c r="R46">
+        <v>210</v>
+      </c>
+      <c r="S46">
+        <v>210</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>2</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>2170</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>154</v>
+      </c>
+      <c r="B47" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" t="s">
+        <v>155</v>
+      </c>
+      <c r="E47" t="s">
+        <v>61</v>
+      </c>
+      <c r="F47" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47">
+        <v>6</v>
+      </c>
+      <c r="J47">
+        <v>1250</v>
+      </c>
+      <c r="K47">
+        <v>2500</v>
+      </c>
+      <c r="L47" t="s">
+        <v>36</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>83</v>
+      </c>
+      <c r="R47">
+        <v>148</v>
+      </c>
+      <c r="S47">
+        <v>148</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>1</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>2170</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>321.16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>156</v>
+      </c>
+      <c r="B48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48" t="s">
+        <v>157</v>
+      </c>
+      <c r="E48" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>1500</v>
+      </c>
+      <c r="K48">
+        <v>3000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" t="s">
+        <v>158</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>101</v>
+      </c>
+      <c r="P48" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>83</v>
+      </c>
+      <c r="R48">
+        <v>283</v>
+      </c>
+      <c r="S48">
+        <v>283</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>2170</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>159</v>
+      </c>
+      <c r="B49" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" t="s">
+        <v>61</v>
+      </c>
+      <c r="F49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>2</v>
+      </c>
+      <c r="J49">
+        <v>1500</v>
+      </c>
+      <c r="K49">
+        <v>3000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>36</v>
+      </c>
+      <c r="M49" t="s">
+        <v>158</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>101</v>
+      </c>
+      <c r="P49" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>83</v>
+      </c>
+      <c r="R49">
+        <v>283</v>
+      </c>
+      <c r="S49">
+        <v>283</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>1</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>2170</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>160</v>
+      </c>
+      <c r="B50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" t="s">
+        <v>61</v>
+      </c>
+      <c r="F50" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" t="s">
+        <v>125</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>3</v>
+      </c>
+      <c r="J50">
+        <v>1500</v>
+      </c>
+      <c r="K50">
+        <v>3000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>36</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>83</v>
+      </c>
+      <c r="R50">
+        <v>212</v>
+      </c>
+      <c r="S50">
+        <v>212</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>2</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>1320</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" t="s">
+        <v>163</v>
+      </c>
+      <c r="E51" t="s">
+        <v>61</v>
+      </c>
+      <c r="F51" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" t="s">
+        <v>62</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>1500</v>
+      </c>
+      <c r="K51">
+        <v>3000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>36</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>83</v>
+      </c>
+      <c r="R51">
+        <v>212</v>
+      </c>
+      <c r="S51">
+        <v>212</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>6</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>2170</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" t="s">
+        <v>165</v>
+      </c>
+      <c r="E52" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" t="s">
+        <v>82</v>
+      </c>
+      <c r="G52" t="s">
+        <v>62</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>6</v>
+      </c>
+      <c r="J52">
+        <v>1000</v>
+      </c>
+      <c r="K52">
+        <v>2000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>36</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>83</v>
+      </c>
+      <c r="R52">
+        <v>567</v>
+      </c>
+      <c r="S52">
+        <v>567</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>6</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>2220</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" t="s">
+        <v>165</v>
+      </c>
+      <c r="E53" t="s">
+        <v>61</v>
+      </c>
+      <c r="F53" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" t="s">
+        <v>62</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>6</v>
+      </c>
+      <c r="J53">
+        <v>1000</v>
+      </c>
+      <c r="K53">
+        <v>2000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>36</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>83</v>
+      </c>
+      <c r="R53">
+        <v>567</v>
+      </c>
+      <c r="S53">
+        <v>567</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>6</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>2220</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" t="s">
+        <v>161</v>
+      </c>
+      <c r="E54" t="s">
+        <v>61</v>
+      </c>
+      <c r="F54" t="s">
+        <v>82</v>
+      </c>
+      <c r="G54" t="s">
+        <v>125</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>3</v>
+      </c>
+      <c r="J54">
+        <v>1500</v>
+      </c>
+      <c r="K54">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>36</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>83</v>
+      </c>
+      <c r="R54">
+        <v>319</v>
+      </c>
+      <c r="S54">
+        <v>319</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>3</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>1370</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" t="s">
+        <v>80</v>
+      </c>
+      <c r="D55" t="s">
+        <v>169</v>
+      </c>
+      <c r="E55" t="s">
+        <v>61</v>
+      </c>
+      <c r="F55" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" t="s">
+        <v>62</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55">
+        <v>1250</v>
+      </c>
+      <c r="K55">
+        <v>2500</v>
+      </c>
+      <c r="L55" t="s">
+        <v>36</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>83</v>
+      </c>
+      <c r="R55">
+        <v>197</v>
+      </c>
+      <c r="S55">
+        <v>197</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>4</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>2170</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" t="s">
+        <v>169</v>
+      </c>
+      <c r="E56" t="s">
+        <v>61</v>
+      </c>
+      <c r="F56" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" t="s">
+        <v>62</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <v>1250</v>
+      </c>
+      <c r="K56">
+        <v>2500</v>
+      </c>
+      <c r="L56" t="s">
+        <v>36</v>
+      </c>
+      <c r="M56" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>83</v>
+      </c>
+      <c r="R56">
+        <v>246</v>
+      </c>
+      <c r="S56">
+        <v>246</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>5</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>2170</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" t="s">
+        <v>80</v>
+      </c>
+      <c r="D57" t="s">
+        <v>122</v>
+      </c>
+      <c r="E57" t="s">
+        <v>61</v>
+      </c>
+      <c r="F57" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s">
+        <v>62</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>0.8</v>
+      </c>
+      <c r="J57">
+        <v>1000</v>
+      </c>
+      <c r="K57">
+        <v>2000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>36</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>83</v>
+      </c>
+      <c r="R57">
+        <v>1498</v>
+      </c>
+      <c r="S57">
+        <v>1498</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>1</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>2370</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B58" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" t="s">
+        <v>122</v>
+      </c>
+      <c r="E58" t="s">
+        <v>61</v>
+      </c>
+      <c r="F58" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" t="s">
+        <v>62</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>0.8</v>
+      </c>
+      <c r="J58">
+        <v>1000</v>
+      </c>
+      <c r="K58">
+        <v>2000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>36</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>83</v>
+      </c>
+      <c r="R58">
+        <v>1498</v>
+      </c>
+      <c r="S58">
+        <v>1498</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>1</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>2370</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" t="s">
+        <v>174</v>
+      </c>
+      <c r="E59" t="s">
+        <v>61</v>
+      </c>
+      <c r="F59" t="s">
+        <v>82</v>
+      </c>
+      <c r="G59" t="s">
+        <v>62</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
+      </c>
+      <c r="J59">
+        <v>1500</v>
+      </c>
+      <c r="K59">
+        <v>3000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>36</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>83</v>
+      </c>
+      <c r="R59">
+        <v>354</v>
+      </c>
+      <c r="S59">
+        <v>354</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>1</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2220</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>175</v>
+      </c>
+      <c r="B60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" t="s">
+        <v>80</v>
+      </c>
+      <c r="D60" t="s">
+        <v>108</v>
+      </c>
+      <c r="E60" t="s">
+        <v>61</v>
+      </c>
+      <c r="F60" t="s">
+        <v>82</v>
+      </c>
+      <c r="G60" t="s">
+        <v>62</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60">
+        <v>2000</v>
+      </c>
+      <c r="K60">
+        <v>4000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>36</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>83</v>
+      </c>
+      <c r="R60">
+        <v>126</v>
+      </c>
+      <c r="S60">
+        <v>126</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>1</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>2190</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>176</v>
+      </c>
+      <c r="B61" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" t="s">
+        <v>80</v>
+      </c>
+      <c r="D61" t="s">
+        <v>140</v>
+      </c>
+      <c r="E61" t="s">
+        <v>61</v>
+      </c>
+      <c r="F61" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" t="s">
+        <v>50</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>1500</v>
+      </c>
+      <c r="K61">
+        <v>3000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>36</v>
+      </c>
+      <c r="M61" t="s">
+        <v>105</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>83</v>
+      </c>
+      <c r="R61">
+        <v>1010</v>
+      </c>
+      <c r="S61">
+        <v>1010</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>14</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>3540</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" t="s">
+        <v>80</v>
+      </c>
+      <c r="D62" t="s">
+        <v>178</v>
+      </c>
+      <c r="E62" t="s">
+        <v>61</v>
+      </c>
+      <c r="F62" t="s">
+        <v>82</v>
+      </c>
+      <c r="G62" t="s">
+        <v>50</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+      <c r="J62">
+        <v>1500</v>
+      </c>
+      <c r="K62">
+        <v>3000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>83</v>
+      </c>
+      <c r="R62">
+        <v>283</v>
+      </c>
+      <c r="S62">
+        <v>283</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>4</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>3540</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>179</v>
+      </c>
+      <c r="B63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63" t="s">
+        <v>180</v>
+      </c>
+      <c r="E63" t="s">
+        <v>61</v>
+      </c>
+      <c r="F63" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" t="s">
+        <v>181</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>0.8</v>
+      </c>
+      <c r="J63">
+        <v>1000</v>
+      </c>
+      <c r="L63" t="s">
+        <v>51</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>182</v>
+      </c>
+      <c r="P63" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>83</v>
+      </c>
+      <c r="R63">
+        <v>1585</v>
+      </c>
+      <c r="S63">
+        <v>1585</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>1</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>2370</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>183</v>
+      </c>
+      <c r="B64" t="s">
+        <v>79</v>
+      </c>
+      <c r="C64" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" t="s">
+        <v>184</v>
+      </c>
+      <c r="E64" t="s">
+        <v>61</v>
+      </c>
+      <c r="F64" t="s">
+        <v>82</v>
+      </c>
+      <c r="G64" t="s">
+        <v>125</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>1.5</v>
+      </c>
+      <c r="J64">
+        <v>1500</v>
+      </c>
+      <c r="K64">
+        <v>3000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>36</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>83</v>
+      </c>
+      <c r="R64">
+        <v>212</v>
+      </c>
+      <c r="S64">
+        <v>212</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>1</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>1320</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" t="s">
+        <v>186</v>
+      </c>
+      <c r="E65" t="s">
+        <v>61</v>
+      </c>
+      <c r="F65" t="s">
+        <v>82</v>
+      </c>
+      <c r="G65" t="s">
+        <v>62</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>3</v>
+      </c>
+      <c r="J65">
+        <v>1250</v>
+      </c>
+      <c r="K65">
+        <v>2500</v>
+      </c>
+      <c r="L65" t="s">
+        <v>36</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>83</v>
+      </c>
+      <c r="R65">
+        <v>74</v>
+      </c>
+      <c r="S65">
+        <v>74</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>1</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>2170</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>160.58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>187</v>
+      </c>
+      <c r="B66" t="s">
+        <v>86</v>
+      </c>
+      <c r="C66" t="s">
+        <v>80</v>
+      </c>
+      <c r="D66" t="s">
+        <v>87</v>
+      </c>
+      <c r="E66" t="s">
+        <v>61</v>
+      </c>
+      <c r="F66" t="s">
+        <v>82</v>
+      </c>
+      <c r="G66" t="s">
+        <v>50</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>2.5</v>
+      </c>
+      <c r="J66">
+        <v>1500</v>
+      </c>
+      <c r="K66">
+        <v>3000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>36</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>83</v>
+      </c>
+      <c r="R66">
+        <v>540</v>
+      </c>
+      <c r="S66">
+        <v>540</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>6</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>3540</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>188</v>
+      </c>
+      <c r="B67" t="s">
+        <v>86</v>
+      </c>
+      <c r="C67" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F67" t="s">
+        <v>82</v>
+      </c>
+      <c r="G67" t="s">
+        <v>50</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>2.5</v>
+      </c>
+      <c r="J67">
+        <v>1500</v>
+      </c>
+      <c r="K67">
+        <v>3000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>36</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>83</v>
+      </c>
+      <c r="R67">
+        <v>520</v>
+      </c>
+      <c r="S67">
+        <v>520</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>6</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>3540</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" t="s">
+        <v>86</v>
+      </c>
+      <c r="C68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D68" t="s">
+        <v>87</v>
+      </c>
+      <c r="E68" t="s">
+        <v>61</v>
+      </c>
+      <c r="F68" t="s">
+        <v>82</v>
+      </c>
+      <c r="G68" t="s">
+        <v>50</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>2.5</v>
+      </c>
+      <c r="J68">
+        <v>1500</v>
+      </c>
+      <c r="K68">
+        <v>3000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>36</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>83</v>
+      </c>
+      <c r="R68">
+        <v>530</v>
+      </c>
+      <c r="S68">
+        <v>530</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>6</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>3540</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>190</v>
+      </c>
+      <c r="B69" t="s">
+        <v>86</v>
+      </c>
+      <c r="C69" t="s">
+        <v>80</v>
+      </c>
+      <c r="D69" t="s">
+        <v>87</v>
+      </c>
+      <c r="E69" t="s">
+        <v>61</v>
+      </c>
+      <c r="F69" t="s">
+        <v>82</v>
+      </c>
+      <c r="G69" t="s">
+        <v>50</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>2.5</v>
+      </c>
+      <c r="J69">
+        <v>1500</v>
+      </c>
+      <c r="K69">
+        <v>3000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>36</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>83</v>
+      </c>
+      <c r="R69">
+        <v>526</v>
+      </c>
+      <c r="S69">
+        <v>526</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>6</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>3540</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>191</v>
+      </c>
+      <c r="B70" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" t="s">
+        <v>80</v>
+      </c>
+      <c r="D70" t="s">
+        <v>192</v>
+      </c>
+      <c r="E70" t="s">
+        <v>61</v>
+      </c>
+      <c r="F70" t="s">
+        <v>82</v>
+      </c>
+      <c r="G70" t="s">
+        <v>50</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>3</v>
+      </c>
+      <c r="J70">
+        <v>1500</v>
+      </c>
+      <c r="K70">
+        <v>3000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>36</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>38</v>
+      </c>
+      <c r="P70" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>83</v>
+      </c>
+      <c r="R70">
+        <v>212</v>
+      </c>
+      <c r="S70">
+        <v>212</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>1</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>3490</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>193</v>
+      </c>
+      <c r="B71" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" t="s">
+        <v>80</v>
+      </c>
+      <c r="D71" t="s">
+        <v>192</v>
+      </c>
+      <c r="E71" t="s">
+        <v>61</v>
+      </c>
+      <c r="F71" t="s">
+        <v>82</v>
+      </c>
+      <c r="G71" t="s">
+        <v>50</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>3</v>
+      </c>
+      <c r="J71">
+        <v>1500</v>
+      </c>
+      <c r="K71">
+        <v>3000</v>
+      </c>
+      <c r="L71" t="s">
+        <v>36</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>83</v>
+      </c>
+      <c r="R71">
+        <v>212</v>
+      </c>
+      <c r="S71">
+        <v>212</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>1</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>3490</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>194</v>
+      </c>
+      <c r="B72" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" t="s">
+        <v>195</v>
+      </c>
+      <c r="E72" t="s">
+        <v>61</v>
+      </c>
+      <c r="F72" t="s">
+        <v>82</v>
+      </c>
+      <c r="G72" t="s">
+        <v>62</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>4</v>
+      </c>
+      <c r="J72">
+        <v>1000</v>
+      </c>
+      <c r="K72">
+        <v>2000</v>
+      </c>
+      <c r="L72" t="s">
+        <v>36</v>
+      </c>
+      <c r="M72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>83</v>
+      </c>
+      <c r="R72">
+        <v>315</v>
+      </c>
+      <c r="S72">
+        <v>315</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>5</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>2220</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>196</v>
+      </c>
+      <c r="B73" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" t="s">
+        <v>197</v>
+      </c>
+      <c r="E73" t="s">
+        <v>61</v>
+      </c>
+      <c r="F73" t="s">
+        <v>82</v>
+      </c>
+      <c r="G73" t="s">
+        <v>62</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>1.5</v>
+      </c>
+      <c r="J73">
+        <v>1250</v>
+      </c>
+      <c r="K73">
+        <v>2500</v>
+      </c>
+      <c r="L73" t="s">
+        <v>36</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>83</v>
+      </c>
+      <c r="R73">
+        <v>295</v>
+      </c>
+      <c r="S73">
+        <v>295</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>8</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>2220</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>654.9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>198</v>
+      </c>
+      <c r="B74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" t="s">
+        <v>120</v>
+      </c>
+      <c r="E74" t="s">
+        <v>61</v>
+      </c>
+      <c r="F74" t="s">
+        <v>82</v>
+      </c>
+      <c r="G74" t="s">
+        <v>62</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>5</v>
+      </c>
+      <c r="J74">
+        <v>1000</v>
+      </c>
+      <c r="K74">
+        <v>2000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>91</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>83</v>
+      </c>
+      <c r="R74">
+        <v>944</v>
+      </c>
+      <c r="S74">
+        <v>944</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>1</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>2020</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>199</v>
+      </c>
+      <c r="B75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" t="s">
+        <v>80</v>
+      </c>
+      <c r="D75" t="s">
+        <v>165</v>
+      </c>
+      <c r="E75" t="s">
+        <v>61</v>
+      </c>
+      <c r="F75" t="s">
+        <v>82</v>
+      </c>
+      <c r="G75" t="s">
+        <v>62</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>6</v>
+      </c>
+      <c r="J75">
+        <v>1000</v>
+      </c>
+      <c r="K75">
+        <v>2000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>36</v>
+      </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>83</v>
+      </c>
+      <c r="R75">
+        <v>189</v>
+      </c>
+      <c r="S75">
+        <v>189</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>2</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>2170</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>410.13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>200</v>
+      </c>
+      <c r="B76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" t="s">
+        <v>80</v>
+      </c>
+      <c r="D76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E76" t="s">
+        <v>61</v>
+      </c>
+      <c r="F76" t="s">
+        <v>82</v>
+      </c>
+      <c r="G76" t="s">
+        <v>62</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>1.5</v>
+      </c>
+      <c r="J76">
+        <v>1000</v>
+      </c>
+      <c r="K76">
+        <v>2000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>36</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>83</v>
+      </c>
+      <c r="R76">
+        <v>260</v>
+      </c>
+      <c r="S76">
+        <v>260</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>11</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>2220</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>577.2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>202</v>
+      </c>
+      <c r="B77" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" t="s">
+        <v>80</v>
+      </c>
+      <c r="D77" t="s">
+        <v>203</v>
+      </c>
+      <c r="E77" t="s">
+        <v>61</v>
+      </c>
+      <c r="F77" t="s">
+        <v>82</v>
+      </c>
+      <c r="G77" t="s">
+        <v>50</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>1500</v>
+      </c>
+      <c r="K77">
+        <v>3000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>36</v>
+      </c>
+      <c r="M77" t="s">
+        <v>105</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>83</v>
+      </c>
+      <c r="R77">
+        <v>1224</v>
+      </c>
+      <c r="S77">
+        <v>1224</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>34</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>3540</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>204</v>
+      </c>
+      <c r="B78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" t="s">
+        <v>80</v>
+      </c>
+      <c r="D78" t="s">
+        <v>169</v>
+      </c>
+      <c r="E78" t="s">
+        <v>61</v>
+      </c>
+      <c r="F78" t="s">
+        <v>82</v>
+      </c>
+      <c r="G78" t="s">
+        <v>62</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78">
+        <v>1250</v>
+      </c>
+      <c r="K78">
+        <v>2500</v>
+      </c>
+      <c r="L78" t="s">
+        <v>36</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>83</v>
+      </c>
+      <c r="R78">
+        <v>197</v>
+      </c>
+      <c r="S78">
+        <v>197</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>4</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>2170</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>205</v>
+      </c>
+      <c r="B79" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" t="s">
+        <v>80</v>
+      </c>
+      <c r="D79" t="s">
+        <v>206</v>
+      </c>
+      <c r="E79" t="s">
+        <v>61</v>
+      </c>
+      <c r="F79" t="s">
+        <v>82</v>
+      </c>
+      <c r="G79" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <v>1500</v>
+      </c>
+      <c r="K79">
+        <v>3000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>36</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>83</v>
+      </c>
+      <c r="R79">
+        <v>35</v>
+      </c>
+      <c r="S79">
+        <v>35</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>1</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>3490</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>207</v>
+      </c>
+      <c r="B80" t="s">
+        <v>79</v>
+      </c>
+      <c r="C80" t="s">
+        <v>80</v>
+      </c>
+      <c r="D80" t="s">
+        <v>206</v>
+      </c>
+      <c r="E80" t="s">
+        <v>61</v>
+      </c>
+      <c r="F80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G80" t="s">
+        <v>50</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>1500</v>
+      </c>
+      <c r="K80">
+        <v>3000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>36</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>83</v>
+      </c>
+      <c r="R80">
+        <v>177</v>
+      </c>
+      <c r="S80">
+        <v>177</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>5</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>3490</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>617.73</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>208</v>
+      </c>
+      <c r="B81" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D81" t="s">
+        <v>209</v>
+      </c>
+      <c r="E81" t="s">
+        <v>61</v>
+      </c>
+      <c r="F81" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" t="s">
+        <v>210</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>0.6</v>
+      </c>
+      <c r="J81">
+        <v>1000</v>
+      </c>
+      <c r="L81" t="s">
+        <v>51</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>83</v>
+      </c>
+      <c r="R81">
+        <v>745</v>
+      </c>
+      <c r="S81">
+        <v>745</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>1</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>2290</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>1706.05</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>211</v>
+      </c>
+      <c r="B82" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" t="s">
+        <v>80</v>
+      </c>
+      <c r="D82" t="s">
+        <v>212</v>
+      </c>
+      <c r="E82" t="s">
+        <v>61</v>
+      </c>
+      <c r="F82" t="s">
+        <v>82</v>
+      </c>
+      <c r="G82" t="s">
+        <v>125</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>1.5</v>
+      </c>
+      <c r="J82">
+        <v>1500</v>
+      </c>
+      <c r="K82">
+        <v>3000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>51</v>
+      </c>
+      <c r="M82" t="s">
+        <v>105</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>83</v>
+      </c>
+      <c r="R82">
+        <v>916</v>
+      </c>
+      <c r="S82">
+        <v>916</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>18</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>1320</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>213</v>
+      </c>
+      <c r="B83" t="s">
+        <v>79</v>
+      </c>
+      <c r="C83" t="s">
+        <v>80</v>
+      </c>
+      <c r="D83" t="s">
+        <v>192</v>
+      </c>
+      <c r="E83" t="s">
+        <v>61</v>
+      </c>
+      <c r="F83" t="s">
+        <v>82</v>
+      </c>
+      <c r="G83" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>3</v>
+      </c>
+      <c r="J83">
+        <v>1500</v>
+      </c>
+      <c r="K83">
+        <v>3000</v>
+      </c>
+      <c r="L83" t="s">
+        <v>36</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>83</v>
+      </c>
+      <c r="R83">
+        <v>319</v>
+      </c>
+      <c r="S83">
+        <v>319</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>1</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>3540</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>214</v>
+      </c>
+      <c r="B84" t="s">
+        <v>79</v>
+      </c>
+      <c r="C84" t="s">
+        <v>80</v>
+      </c>
+      <c r="D84" t="s">
+        <v>192</v>
+      </c>
+      <c r="E84" t="s">
+        <v>61</v>
+      </c>
+      <c r="F84" t="s">
+        <v>82</v>
+      </c>
+      <c r="G84" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>3</v>
+      </c>
+      <c r="J84">
+        <v>1500</v>
+      </c>
+      <c r="K84">
+        <v>3000</v>
+      </c>
+      <c r="L84" t="s">
+        <v>36</v>
+      </c>
+      <c r="M84" t="s">
+        <v>37</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>83</v>
+      </c>
+      <c r="R84">
+        <v>212</v>
+      </c>
+      <c r="S84">
+        <v>212</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>1</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>3490</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>215</v>
+      </c>
+      <c r="B85" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" t="s">
+        <v>80</v>
+      </c>
+      <c r="D85" t="s">
+        <v>192</v>
+      </c>
+      <c r="E85" t="s">
+        <v>61</v>
+      </c>
+      <c r="F85" t="s">
+        <v>82</v>
+      </c>
+      <c r="G85" t="s">
+        <v>50</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>3</v>
+      </c>
+      <c r="J85">
+        <v>1500</v>
+      </c>
+      <c r="K85">
+        <v>3000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>36</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>83</v>
+      </c>
+      <c r="R85">
+        <v>212</v>
+      </c>
+      <c r="S85">
+        <v>212</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>1</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>3490</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>216</v>
+      </c>
+      <c r="B86" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" t="s">
+        <v>80</v>
+      </c>
+      <c r="D86" t="s">
+        <v>192</v>
+      </c>
+      <c r="E86" t="s">
+        <v>61</v>
+      </c>
+      <c r="F86" t="s">
+        <v>82</v>
+      </c>
+      <c r="G86" t="s">
+        <v>50</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>3</v>
+      </c>
+      <c r="J86">
+        <v>1500</v>
+      </c>
+      <c r="K86">
+        <v>3000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>36</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>83</v>
+      </c>
+      <c r="R86">
+        <v>319</v>
+      </c>
+      <c r="S86">
+        <v>319</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>1</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>3540</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>217</v>
+      </c>
+      <c r="B87" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" t="s">
+        <v>80</v>
+      </c>
+      <c r="D87" t="s">
+        <v>218</v>
+      </c>
+      <c r="E87" t="s">
+        <v>61</v>
+      </c>
+      <c r="F87" t="s">
+        <v>82</v>
+      </c>
+      <c r="G87" t="s">
+        <v>50</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87">
+        <v>2</v>
+      </c>
+      <c r="J87">
+        <v>2000</v>
+      </c>
+      <c r="K87">
+        <v>6000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>36</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>83</v>
+      </c>
+      <c r="R87">
+        <v>189</v>
+      </c>
+      <c r="S87">
+        <v>189</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>1</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>3510</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>663.39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>219</v>
+      </c>
+      <c r="B88" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" t="s">
+        <v>80</v>
+      </c>
+      <c r="D88" t="s">
+        <v>220</v>
+      </c>
+      <c r="E88" t="s">
+        <v>61</v>
+      </c>
+      <c r="F88" t="s">
+        <v>82</v>
+      </c>
+      <c r="G88" t="s">
+        <v>62</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88">
+        <v>4</v>
+      </c>
+      <c r="J88">
+        <v>1000</v>
+      </c>
+      <c r="K88">
+        <v>2000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>36</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>83</v>
+      </c>
+      <c r="R88">
+        <v>63</v>
+      </c>
+      <c r="S88">
+        <v>63</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>1</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>2170</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>136.71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>221</v>
+      </c>
+      <c r="B89" t="s">
+        <v>86</v>
+      </c>
+      <c r="C89" t="s">
+        <v>80</v>
+      </c>
+      <c r="D89" t="s">
+        <v>222</v>
+      </c>
+      <c r="E89" t="s">
+        <v>61</v>
+      </c>
+      <c r="F89" t="s">
+        <v>82</v>
+      </c>
+      <c r="G89" t="s">
+        <v>62</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89">
+        <v>1.2</v>
+      </c>
+      <c r="J89">
+        <v>1250</v>
+      </c>
+      <c r="K89">
+        <v>2500</v>
+      </c>
+      <c r="L89" t="s">
+        <v>36</v>
+      </c>
+      <c r="M89" t="s">
+        <v>105</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>83</v>
+      </c>
+      <c r="R89">
+        <v>568</v>
+      </c>
+      <c r="S89">
+        <v>568</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>19</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>2170</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>1232.56</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>223</v>
+      </c>
+      <c r="B90" t="s">
+        <v>86</v>
+      </c>
+      <c r="C90" t="s">
+        <v>80</v>
+      </c>
+      <c r="D90" t="s">
+        <v>224</v>
+      </c>
+      <c r="E90" t="s">
+        <v>61</v>
+      </c>
+      <c r="F90" t="s">
+        <v>82</v>
+      </c>
+      <c r="G90" t="s">
+        <v>62</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>1.2</v>
+      </c>
+      <c r="J90">
+        <v>1500</v>
+      </c>
+      <c r="K90">
+        <v>3000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>36</v>
+      </c>
+      <c r="M90" t="s">
+        <v>225</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>83</v>
+      </c>
+      <c r="R90">
+        <v>660</v>
+      </c>
+      <c r="S90">
+        <v>660</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>15</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>2170</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>1432.2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>226</v>
+      </c>
+      <c r="B91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" t="s">
+        <v>80</v>
+      </c>
+      <c r="D91" t="s">
+        <v>227</v>
+      </c>
+      <c r="E91" t="s">
+        <v>61</v>
+      </c>
+      <c r="F91" t="s">
+        <v>82</v>
+      </c>
+      <c r="G91" t="s">
+        <v>125</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91">
+        <v>1.5</v>
+      </c>
+      <c r="J91">
+        <v>1250</v>
+      </c>
+      <c r="K91">
+        <v>2500</v>
+      </c>
+      <c r="L91" t="s">
+        <v>36</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>83</v>
+      </c>
+      <c r="R91">
+        <v>148</v>
+      </c>
+      <c r="S91">
+        <v>148</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>4</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>1320</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>195.36</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>228</v>
+      </c>
+      <c r="B92" t="s">
+        <v>79</v>
+      </c>
+      <c r="C92" t="s">
+        <v>80</v>
+      </c>
+      <c r="D92" t="s">
+        <v>227</v>
+      </c>
+      <c r="E92" t="s">
+        <v>61</v>
+      </c>
+      <c r="F92" t="s">
+        <v>82</v>
+      </c>
+      <c r="G92" t="s">
+        <v>125</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92">
+        <v>1.5</v>
+      </c>
+      <c r="J92">
+        <v>1250</v>
+      </c>
+      <c r="K92">
+        <v>2500</v>
+      </c>
+      <c r="L92" t="s">
+        <v>36</v>
+      </c>
+      <c r="M92" t="s">
+        <v>37</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>38</v>
+      </c>
+      <c r="P92" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>83</v>
+      </c>
+      <c r="R92">
+        <v>148</v>
+      </c>
+      <c r="S92">
+        <v>148</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>4</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>1320</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>195.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="253">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -305,6 +305,471 @@
   </si>
   <si>
     <t>K268094252</t>
+  </si>
+  <si>
+    <t>T468837</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>T468838</t>
+  </si>
+  <si>
+    <t>7246484</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7246542</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
+    <t>7246814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 5.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7246817</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 6.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T473609</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7247036</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Polish grain 400 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7247041</t>
+  </si>
+  <si>
+    <t>7247338</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7247409</t>
+  </si>
+  <si>
+    <t>7247854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475488</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248626</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248988</t>
+  </si>
+  <si>
+    <t>Coil 1.4307-304L 2D 1.0 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7248989</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T477742</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7249627</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Duplo polish grain 320</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481266</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481267</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T481616</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T481617</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481869</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7253484</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 240 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 240</t>
+  </si>
+  <si>
+    <t>7253485</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484088</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484797</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254248</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T485455</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254992</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T486939</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>T487305</t>
+  </si>
+  <si>
+    <t>T487411</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255816</t>
+  </si>
+  <si>
+    <t>T487947</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T487964</t>
+  </si>
+  <si>
+    <t>7256046</t>
+  </si>
+  <si>
+    <t>Coil 1.4301-304 2R 0.6 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>7256139</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>T488237</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256367</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.2 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7256368</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Scotchbrite</t>
+  </si>
+  <si>
+    <t>T488483</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T488484</t>
+  </si>
+  <si>
+    <t>T488802</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T488824</t>
+  </si>
+  <si>
+    <t>T488827</t>
+  </si>
+  <si>
+    <t>7256740</t>
+  </si>
+  <si>
+    <t>Sheets 1.4301-304 2R 2.0 x 1000.0 x 2000 mm Slit</t>
   </si>
 </sst>
 </file>
@@ -681,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -2682,6 +3147,7055 @@
         <v>1</v>
       </c>
     </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" t="s">
+        <v>102</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25">
+        <v>6</v>
+      </c>
+      <c r="J25">
+        <v>1000</v>
+      </c>
+      <c r="K25">
+        <v>2000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>103</v>
+      </c>
+      <c r="R25">
+        <v>283</v>
+      </c>
+      <c r="S25">
+        <v>283</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>5</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>3690</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>1044.27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26">
+        <v>6</v>
+      </c>
+      <c r="J26">
+        <v>1000</v>
+      </c>
+      <c r="K26">
+        <v>2000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>103</v>
+      </c>
+      <c r="R26">
+        <v>567</v>
+      </c>
+      <c r="S26">
+        <v>567</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>6</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>3690</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>2092.23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" t="s">
+        <v>68</v>
+      </c>
+      <c r="H27" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27">
+        <v>2.5</v>
+      </c>
+      <c r="J27">
+        <v>1500</v>
+      </c>
+      <c r="K27">
+        <v>3000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>103</v>
+      </c>
+      <c r="R27">
+        <v>554</v>
+      </c>
+      <c r="S27">
+        <v>554</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>6</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>3540</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>1961.16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28">
+        <v>6</v>
+      </c>
+      <c r="J28">
+        <v>1000</v>
+      </c>
+      <c r="K28">
+        <v>2000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>111</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>103</v>
+      </c>
+      <c r="R28">
+        <v>1133</v>
+      </c>
+      <c r="S28">
+        <v>1133</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>2070</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>2345.31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <v>2000</v>
+      </c>
+      <c r="K29">
+        <v>6000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>58</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>103</v>
+      </c>
+      <c r="R29">
+        <v>472</v>
+      </c>
+      <c r="S29">
+        <v>472</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>2240</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>1057.28</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30">
+        <v>6</v>
+      </c>
+      <c r="J30">
+        <v>2000</v>
+      </c>
+      <c r="K30">
+        <v>6000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>103</v>
+      </c>
+      <c r="R30">
+        <v>567</v>
+      </c>
+      <c r="S30">
+        <v>567</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>3560</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>2018.52</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31" t="s">
+        <v>57</v>
+      </c>
+      <c r="H31" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>1500</v>
+      </c>
+      <c r="K31">
+        <v>3000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" t="s">
+        <v>37</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>103</v>
+      </c>
+      <c r="R31">
+        <v>212</v>
+      </c>
+      <c r="S31">
+        <v>212</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>2</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>2170</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" t="s">
+        <v>68</v>
+      </c>
+      <c r="H32" t="s">
+        <v>52</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>1500</v>
+      </c>
+      <c r="K32">
+        <v>3000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>58</v>
+      </c>
+      <c r="M32" t="s">
+        <v>120</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>121</v>
+      </c>
+      <c r="P32" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>103</v>
+      </c>
+      <c r="R32">
+        <v>1014</v>
+      </c>
+      <c r="S32">
+        <v>1014</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>1</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>3540</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>3589.56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>1500</v>
+      </c>
+      <c r="K33">
+        <v>3000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" t="s">
+        <v>120</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>121</v>
+      </c>
+      <c r="P33" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>103</v>
+      </c>
+      <c r="R33">
+        <v>728</v>
+      </c>
+      <c r="S33">
+        <v>728</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>3490</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>2540.72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" t="s">
+        <v>67</v>
+      </c>
+      <c r="G34" t="s">
+        <v>68</v>
+      </c>
+      <c r="H34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I34">
+        <v>1.5</v>
+      </c>
+      <c r="J34">
+        <v>1500</v>
+      </c>
+      <c r="K34">
+        <v>3000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>58</v>
+      </c>
+      <c r="M34" t="s">
+        <v>125</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R34">
+        <v>592</v>
+      </c>
+      <c r="S34">
+        <v>592</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>11</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>3490</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>2066.08</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" t="s">
+        <v>67</v>
+      </c>
+      <c r="G35" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35" t="s">
+        <v>52</v>
+      </c>
+      <c r="I35">
+        <v>2.5</v>
+      </c>
+      <c r="J35">
+        <v>1500</v>
+      </c>
+      <c r="K35">
+        <v>3000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>58</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>103</v>
+      </c>
+      <c r="R35">
+        <v>540</v>
+      </c>
+      <c r="S35">
+        <v>540</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>6</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>3540</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" t="s">
+        <v>67</v>
+      </c>
+      <c r="G36" t="s">
+        <v>57</v>
+      </c>
+      <c r="H36" t="s">
+        <v>52</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36">
+        <v>2000</v>
+      </c>
+      <c r="K36">
+        <v>4000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>58</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>103</v>
+      </c>
+      <c r="R36">
+        <v>126</v>
+      </c>
+      <c r="S36">
+        <v>126</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>2190</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" t="s">
+        <v>52</v>
+      </c>
+      <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37">
+        <v>2000</v>
+      </c>
+      <c r="K37">
+        <v>4000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>58</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>103</v>
+      </c>
+      <c r="R37">
+        <v>315</v>
+      </c>
+      <c r="S37">
+        <v>315</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>3560</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F38" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" t="s">
+        <v>57</v>
+      </c>
+      <c r="H38" t="s">
+        <v>52</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>2000</v>
+      </c>
+      <c r="K38">
+        <v>4000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>103</v>
+      </c>
+      <c r="R38">
+        <v>189</v>
+      </c>
+      <c r="S38">
+        <v>189</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>1</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>2190</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>413.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>133</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39" t="s">
+        <v>50</v>
+      </c>
+      <c r="F39" t="s">
+        <v>67</v>
+      </c>
+      <c r="G39" t="s">
+        <v>57</v>
+      </c>
+      <c r="H39" t="s">
+        <v>52</v>
+      </c>
+      <c r="I39">
+        <v>2.5</v>
+      </c>
+      <c r="J39">
+        <v>1000</v>
+      </c>
+      <c r="K39">
+        <v>2000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>58</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>103</v>
+      </c>
+      <c r="R39">
+        <v>312</v>
+      </c>
+      <c r="S39">
+        <v>312</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>8</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>2220</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>692.64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>135</v>
+      </c>
+      <c r="B40" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
+        <v>57</v>
+      </c>
+      <c r="H40" t="s">
+        <v>52</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>53</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>103</v>
+      </c>
+      <c r="R40">
+        <v>2560</v>
+      </c>
+      <c r="S40">
+        <v>2560</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>2270</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>5811.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E41" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" t="s">
+        <v>57</v>
+      </c>
+      <c r="H41" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>1000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>53</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>103</v>
+      </c>
+      <c r="R41">
+        <v>3075</v>
+      </c>
+      <c r="S41">
+        <v>3075</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>2270</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>6980.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" t="s">
+        <v>139</v>
+      </c>
+      <c r="E42" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" t="s">
+        <v>57</v>
+      </c>
+      <c r="H42" t="s">
+        <v>52</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>1000</v>
+      </c>
+      <c r="K42">
+        <v>2000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>111</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>103</v>
+      </c>
+      <c r="R42">
+        <v>394</v>
+      </c>
+      <c r="S42">
+        <v>394</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>2020</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F43" t="s">
+        <v>67</v>
+      </c>
+      <c r="G43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I43">
+        <v>0.8</v>
+      </c>
+      <c r="J43">
+        <v>1000</v>
+      </c>
+      <c r="K43">
+        <v>2000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>58</v>
+      </c>
+      <c r="M43" t="s">
+        <v>37</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>103</v>
+      </c>
+      <c r="R43">
+        <v>176</v>
+      </c>
+      <c r="S43">
+        <v>176</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>14</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>2270</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>399.52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>142</v>
+      </c>
+      <c r="B44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44" t="s">
+        <v>67</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>1250</v>
+      </c>
+      <c r="K44">
+        <v>2500</v>
+      </c>
+      <c r="L44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>103</v>
+      </c>
+      <c r="R44">
+        <v>322</v>
+      </c>
+      <c r="S44">
+        <v>322</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>1</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>1370</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" t="s">
+        <v>67</v>
+      </c>
+      <c r="G45" t="s">
+        <v>57</v>
+      </c>
+      <c r="H45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45">
+        <v>0.8</v>
+      </c>
+      <c r="J45">
+        <v>1250</v>
+      </c>
+      <c r="K45">
+        <v>2500</v>
+      </c>
+      <c r="L45" t="s">
+        <v>58</v>
+      </c>
+      <c r="M45" t="s">
+        <v>146</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>121</v>
+      </c>
+      <c r="P45" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>103</v>
+      </c>
+      <c r="R45">
+        <v>157</v>
+      </c>
+      <c r="S45">
+        <v>157</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>8</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>2220</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>348.54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" t="s">
+        <v>143</v>
+      </c>
+      <c r="E46" t="s">
+        <v>50</v>
+      </c>
+      <c r="F46" t="s">
+        <v>67</v>
+      </c>
+      <c r="G46" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" t="s">
+        <v>52</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+      <c r="J46">
+        <v>1250</v>
+      </c>
+      <c r="K46">
+        <v>2500</v>
+      </c>
+      <c r="L46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>103</v>
+      </c>
+      <c r="R46">
+        <v>340</v>
+      </c>
+      <c r="S46">
+        <v>340</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>7</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>1370</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" t="s">
+        <v>50</v>
+      </c>
+      <c r="F47" t="s">
+        <v>67</v>
+      </c>
+      <c r="G47" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" t="s">
+        <v>52</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>2000</v>
+      </c>
+      <c r="K47">
+        <v>6000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>58</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>103</v>
+      </c>
+      <c r="R47">
+        <v>283</v>
+      </c>
+      <c r="S47">
+        <v>283</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>1</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>3560</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>1007.48</v>
+      </c>
+      <c r="AB47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" t="s">
+        <v>50</v>
+      </c>
+      <c r="F48" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" t="s">
+        <v>68</v>
+      </c>
+      <c r="H48" t="s">
+        <v>52</v>
+      </c>
+      <c r="I48">
+        <v>6</v>
+      </c>
+      <c r="J48">
+        <v>1500</v>
+      </c>
+      <c r="K48">
+        <v>3000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>58</v>
+      </c>
+      <c r="M48" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>103</v>
+      </c>
+      <c r="R48">
+        <v>212</v>
+      </c>
+      <c r="S48">
+        <v>212</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>3490</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" t="s">
+        <v>50</v>
+      </c>
+      <c r="F49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G49" t="s">
+        <v>102</v>
+      </c>
+      <c r="H49" t="s">
+        <v>52</v>
+      </c>
+      <c r="I49">
+        <v>8</v>
+      </c>
+      <c r="J49">
+        <v>1250</v>
+      </c>
+      <c r="K49">
+        <v>2500</v>
+      </c>
+      <c r="L49" t="s">
+        <v>111</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>103</v>
+      </c>
+      <c r="R49">
+        <v>394</v>
+      </c>
+      <c r="S49">
+        <v>394</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>1</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>3490</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>154</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F50" t="s">
+        <v>67</v>
+      </c>
+      <c r="G50" t="s">
+        <v>156</v>
+      </c>
+      <c r="H50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I50">
+        <v>5</v>
+      </c>
+      <c r="J50">
+        <v>2000</v>
+      </c>
+      <c r="K50">
+        <v>6000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>111</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>103</v>
+      </c>
+      <c r="R50">
+        <v>472</v>
+      </c>
+      <c r="S50">
+        <v>472</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>2190</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>157</v>
+      </c>
+      <c r="B51" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" t="s">
+        <v>158</v>
+      </c>
+      <c r="E51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F51" t="s">
+        <v>67</v>
+      </c>
+      <c r="G51" t="s">
+        <v>68</v>
+      </c>
+      <c r="H51" t="s">
+        <v>52</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+      <c r="J51">
+        <v>1500</v>
+      </c>
+      <c r="K51">
+        <v>3000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>58</v>
+      </c>
+      <c r="M51" t="s">
+        <v>125</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>103</v>
+      </c>
+      <c r="R51">
+        <v>970</v>
+      </c>
+      <c r="S51">
+        <v>970</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>13</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>3490</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>159</v>
+      </c>
+      <c r="B52" t="s">
+        <v>106</v>
+      </c>
+      <c r="C52" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" t="s">
+        <v>107</v>
+      </c>
+      <c r="E52" t="s">
+        <v>50</v>
+      </c>
+      <c r="F52" t="s">
+        <v>67</v>
+      </c>
+      <c r="G52" t="s">
+        <v>68</v>
+      </c>
+      <c r="H52" t="s">
+        <v>52</v>
+      </c>
+      <c r="I52">
+        <v>2.5</v>
+      </c>
+      <c r="J52">
+        <v>1500</v>
+      </c>
+      <c r="K52">
+        <v>3000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>58</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>103</v>
+      </c>
+      <c r="R52">
+        <v>526</v>
+      </c>
+      <c r="S52">
+        <v>526</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>6</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>3540</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>160</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" t="s">
+        <v>161</v>
+      </c>
+      <c r="E53" t="s">
+        <v>50</v>
+      </c>
+      <c r="F53" t="s">
+        <v>67</v>
+      </c>
+      <c r="G53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" t="s">
+        <v>52</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>1500</v>
+      </c>
+      <c r="K53">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>111</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>103</v>
+      </c>
+      <c r="R53">
+        <v>354</v>
+      </c>
+      <c r="S53">
+        <v>354</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>2</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>1170</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" t="s">
+        <v>99</v>
+      </c>
+      <c r="C54" t="s">
+        <v>100</v>
+      </c>
+      <c r="D54" t="s">
+        <v>163</v>
+      </c>
+      <c r="E54" t="s">
+        <v>50</v>
+      </c>
+      <c r="F54" t="s">
+        <v>67</v>
+      </c>
+      <c r="G54" t="s">
+        <v>57</v>
+      </c>
+      <c r="H54" t="s">
+        <v>52</v>
+      </c>
+      <c r="I54">
+        <v>4</v>
+      </c>
+      <c r="J54">
+        <v>1500</v>
+      </c>
+      <c r="K54">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>58</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>103</v>
+      </c>
+      <c r="R54">
+        <v>142</v>
+      </c>
+      <c r="S54">
+        <v>142</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>1</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>2170</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" t="s">
+        <v>99</v>
+      </c>
+      <c r="C55" t="s">
+        <v>100</v>
+      </c>
+      <c r="D55" t="s">
+        <v>163</v>
+      </c>
+      <c r="E55" t="s">
+        <v>50</v>
+      </c>
+      <c r="F55" t="s">
+        <v>67</v>
+      </c>
+      <c r="G55" t="s">
+        <v>57</v>
+      </c>
+      <c r="H55" t="s">
+        <v>52</v>
+      </c>
+      <c r="I55">
+        <v>4</v>
+      </c>
+      <c r="J55">
+        <v>1500</v>
+      </c>
+      <c r="K55">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>58</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>103</v>
+      </c>
+      <c r="R55">
+        <v>142</v>
+      </c>
+      <c r="S55">
+        <v>142</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>1</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>2170</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" t="s">
+        <v>100</v>
+      </c>
+      <c r="D56" t="s">
+        <v>166</v>
+      </c>
+      <c r="E56" t="s">
+        <v>50</v>
+      </c>
+      <c r="F56" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" t="s">
+        <v>68</v>
+      </c>
+      <c r="H56" t="s">
+        <v>52</v>
+      </c>
+      <c r="I56">
+        <v>1.5</v>
+      </c>
+      <c r="J56">
+        <v>1250</v>
+      </c>
+      <c r="L56" t="s">
+        <v>58</v>
+      </c>
+      <c r="M56" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>103</v>
+      </c>
+      <c r="R56">
+        <v>1275</v>
+      </c>
+      <c r="S56">
+        <v>1275</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>1</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>3590</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C57" t="s">
+        <v>100</v>
+      </c>
+      <c r="D57" t="s">
+        <v>168</v>
+      </c>
+      <c r="E57" t="s">
+        <v>50</v>
+      </c>
+      <c r="F57" t="s">
+        <v>67</v>
+      </c>
+      <c r="G57" t="s">
+        <v>57</v>
+      </c>
+      <c r="H57" t="s">
+        <v>52</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>1250</v>
+      </c>
+      <c r="K57">
+        <v>2500</v>
+      </c>
+      <c r="L57" t="s">
+        <v>58</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>103</v>
+      </c>
+      <c r="R57">
+        <v>49</v>
+      </c>
+      <c r="S57">
+        <v>49</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>2</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>2170</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>169</v>
+      </c>
+      <c r="B58" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" t="s">
+        <v>168</v>
+      </c>
+      <c r="E58" t="s">
+        <v>50</v>
+      </c>
+      <c r="F58" t="s">
+        <v>67</v>
+      </c>
+      <c r="G58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H58" t="s">
+        <v>52</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <v>1250</v>
+      </c>
+      <c r="K58">
+        <v>2500</v>
+      </c>
+      <c r="L58" t="s">
+        <v>58</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>103</v>
+      </c>
+      <c r="R58">
+        <v>49</v>
+      </c>
+      <c r="S58">
+        <v>49</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>2</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>2170</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" t="s">
+        <v>100</v>
+      </c>
+      <c r="D59" t="s">
+        <v>171</v>
+      </c>
+      <c r="E59" t="s">
+        <v>50</v>
+      </c>
+      <c r="F59" t="s">
+        <v>67</v>
+      </c>
+      <c r="G59" t="s">
+        <v>57</v>
+      </c>
+      <c r="H59" t="s">
+        <v>52</v>
+      </c>
+      <c r="I59">
+        <v>3</v>
+      </c>
+      <c r="J59">
+        <v>1500</v>
+      </c>
+      <c r="K59">
+        <v>3000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>58</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>103</v>
+      </c>
+      <c r="R59">
+        <v>210</v>
+      </c>
+      <c r="S59">
+        <v>210</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>2</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2170</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>172</v>
+      </c>
+      <c r="B60" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" t="s">
+        <v>100</v>
+      </c>
+      <c r="D60" t="s">
+        <v>173</v>
+      </c>
+      <c r="E60" t="s">
+        <v>50</v>
+      </c>
+      <c r="F60" t="s">
+        <v>67</v>
+      </c>
+      <c r="G60" t="s">
+        <v>57</v>
+      </c>
+      <c r="H60" t="s">
+        <v>52</v>
+      </c>
+      <c r="I60">
+        <v>6</v>
+      </c>
+      <c r="J60">
+        <v>1250</v>
+      </c>
+      <c r="K60">
+        <v>2500</v>
+      </c>
+      <c r="L60" t="s">
+        <v>58</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>103</v>
+      </c>
+      <c r="R60">
+        <v>148</v>
+      </c>
+      <c r="S60">
+        <v>148</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>1</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>2170</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>321.16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" t="s">
+        <v>175</v>
+      </c>
+      <c r="E61" t="s">
+        <v>50</v>
+      </c>
+      <c r="F61" t="s">
+        <v>67</v>
+      </c>
+      <c r="G61" t="s">
+        <v>57</v>
+      </c>
+      <c r="H61" t="s">
+        <v>52</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>1500</v>
+      </c>
+      <c r="K61">
+        <v>3000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>58</v>
+      </c>
+      <c r="M61" t="s">
+        <v>176</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>121</v>
+      </c>
+      <c r="P61" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>103</v>
+      </c>
+      <c r="R61">
+        <v>283</v>
+      </c>
+      <c r="S61">
+        <v>283</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>1</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>2170</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" t="s">
+        <v>99</v>
+      </c>
+      <c r="C62" t="s">
+        <v>100</v>
+      </c>
+      <c r="D62" t="s">
+        <v>175</v>
+      </c>
+      <c r="E62" t="s">
+        <v>50</v>
+      </c>
+      <c r="F62" t="s">
+        <v>67</v>
+      </c>
+      <c r="G62" t="s">
+        <v>57</v>
+      </c>
+      <c r="H62" t="s">
+        <v>52</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+      <c r="J62">
+        <v>1500</v>
+      </c>
+      <c r="K62">
+        <v>3000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>58</v>
+      </c>
+      <c r="M62" t="s">
+        <v>176</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>121</v>
+      </c>
+      <c r="P62" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>103</v>
+      </c>
+      <c r="R62">
+        <v>283</v>
+      </c>
+      <c r="S62">
+        <v>283</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>1</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>2170</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>178</v>
+      </c>
+      <c r="B63" t="s">
+        <v>99</v>
+      </c>
+      <c r="C63" t="s">
+        <v>100</v>
+      </c>
+      <c r="D63" t="s">
+        <v>179</v>
+      </c>
+      <c r="E63" t="s">
+        <v>50</v>
+      </c>
+      <c r="F63" t="s">
+        <v>67</v>
+      </c>
+      <c r="G63" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" t="s">
+        <v>52</v>
+      </c>
+      <c r="I63">
+        <v>3</v>
+      </c>
+      <c r="J63">
+        <v>1500</v>
+      </c>
+      <c r="K63">
+        <v>3000</v>
+      </c>
+      <c r="L63" t="s">
+        <v>58</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>103</v>
+      </c>
+      <c r="R63">
+        <v>212</v>
+      </c>
+      <c r="S63">
+        <v>212</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>2</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>1320</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>180</v>
+      </c>
+      <c r="B64" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" t="s">
+        <v>100</v>
+      </c>
+      <c r="D64" t="s">
+        <v>181</v>
+      </c>
+      <c r="E64" t="s">
+        <v>50</v>
+      </c>
+      <c r="F64" t="s">
+        <v>67</v>
+      </c>
+      <c r="G64" t="s">
+        <v>57</v>
+      </c>
+      <c r="H64" t="s">
+        <v>52</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>1500</v>
+      </c>
+      <c r="K64">
+        <v>3000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>58</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>103</v>
+      </c>
+      <c r="R64">
+        <v>212</v>
+      </c>
+      <c r="S64">
+        <v>212</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>6</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>2170</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>182</v>
+      </c>
+      <c r="B65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" t="s">
+        <v>183</v>
+      </c>
+      <c r="E65" t="s">
+        <v>50</v>
+      </c>
+      <c r="F65" t="s">
+        <v>67</v>
+      </c>
+      <c r="G65" t="s">
+        <v>57</v>
+      </c>
+      <c r="H65" t="s">
+        <v>52</v>
+      </c>
+      <c r="I65">
+        <v>6</v>
+      </c>
+      <c r="J65">
+        <v>1000</v>
+      </c>
+      <c r="K65">
+        <v>2000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>58</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>103</v>
+      </c>
+      <c r="R65">
+        <v>567</v>
+      </c>
+      <c r="S65">
+        <v>567</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>6</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>2220</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>184</v>
+      </c>
+      <c r="B66" t="s">
+        <v>99</v>
+      </c>
+      <c r="C66" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" t="s">
+        <v>183</v>
+      </c>
+      <c r="E66" t="s">
+        <v>50</v>
+      </c>
+      <c r="F66" t="s">
+        <v>67</v>
+      </c>
+      <c r="G66" t="s">
+        <v>57</v>
+      </c>
+      <c r="H66" t="s">
+        <v>52</v>
+      </c>
+      <c r="I66">
+        <v>6</v>
+      </c>
+      <c r="J66">
+        <v>1000</v>
+      </c>
+      <c r="K66">
+        <v>2000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>58</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>103</v>
+      </c>
+      <c r="R66">
+        <v>567</v>
+      </c>
+      <c r="S66">
+        <v>567</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>6</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>2220</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>185</v>
+      </c>
+      <c r="B67" t="s">
+        <v>99</v>
+      </c>
+      <c r="C67" t="s">
+        <v>100</v>
+      </c>
+      <c r="D67" t="s">
+        <v>179</v>
+      </c>
+      <c r="E67" t="s">
+        <v>50</v>
+      </c>
+      <c r="F67" t="s">
+        <v>67</v>
+      </c>
+      <c r="G67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" t="s">
+        <v>52</v>
+      </c>
+      <c r="I67">
+        <v>3</v>
+      </c>
+      <c r="J67">
+        <v>1500</v>
+      </c>
+      <c r="K67">
+        <v>3000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>58</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>103</v>
+      </c>
+      <c r="R67">
+        <v>319</v>
+      </c>
+      <c r="S67">
+        <v>319</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>3</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>1370</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>186</v>
+      </c>
+      <c r="B68" t="s">
+        <v>99</v>
+      </c>
+      <c r="C68" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" t="s">
+        <v>187</v>
+      </c>
+      <c r="E68" t="s">
+        <v>50</v>
+      </c>
+      <c r="F68" t="s">
+        <v>67</v>
+      </c>
+      <c r="G68" t="s">
+        <v>57</v>
+      </c>
+      <c r="H68" t="s">
+        <v>52</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+      <c r="J68">
+        <v>1250</v>
+      </c>
+      <c r="K68">
+        <v>2500</v>
+      </c>
+      <c r="L68" t="s">
+        <v>58</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>103</v>
+      </c>
+      <c r="R68">
+        <v>197</v>
+      </c>
+      <c r="S68">
+        <v>197</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>4</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>2170</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>188</v>
+      </c>
+      <c r="B69" t="s">
+        <v>99</v>
+      </c>
+      <c r="C69" t="s">
+        <v>100</v>
+      </c>
+      <c r="D69" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" t="s">
+        <v>50</v>
+      </c>
+      <c r="F69" t="s">
+        <v>67</v>
+      </c>
+      <c r="G69" t="s">
+        <v>57</v>
+      </c>
+      <c r="H69" t="s">
+        <v>52</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69">
+        <v>1250</v>
+      </c>
+      <c r="K69">
+        <v>2500</v>
+      </c>
+      <c r="L69" t="s">
+        <v>58</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>103</v>
+      </c>
+      <c r="R69">
+        <v>246</v>
+      </c>
+      <c r="S69">
+        <v>246</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>5</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>2170</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" t="s">
+        <v>100</v>
+      </c>
+      <c r="D70" t="s">
+        <v>141</v>
+      </c>
+      <c r="E70" t="s">
+        <v>50</v>
+      </c>
+      <c r="F70" t="s">
+        <v>67</v>
+      </c>
+      <c r="G70" t="s">
+        <v>57</v>
+      </c>
+      <c r="H70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I70">
+        <v>0.8</v>
+      </c>
+      <c r="J70">
+        <v>1000</v>
+      </c>
+      <c r="K70">
+        <v>2000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>58</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>38</v>
+      </c>
+      <c r="P70" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>103</v>
+      </c>
+      <c r="R70">
+        <v>1498</v>
+      </c>
+      <c r="S70">
+        <v>1498</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>1</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>2370</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>190</v>
+      </c>
+      <c r="B71" t="s">
+        <v>99</v>
+      </c>
+      <c r="C71" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" t="s">
+        <v>141</v>
+      </c>
+      <c r="E71" t="s">
+        <v>50</v>
+      </c>
+      <c r="F71" t="s">
+        <v>67</v>
+      </c>
+      <c r="G71" t="s">
+        <v>57</v>
+      </c>
+      <c r="H71" t="s">
+        <v>52</v>
+      </c>
+      <c r="I71">
+        <v>0.8</v>
+      </c>
+      <c r="J71">
+        <v>1000</v>
+      </c>
+      <c r="K71">
+        <v>2000</v>
+      </c>
+      <c r="L71" t="s">
+        <v>58</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>103</v>
+      </c>
+      <c r="R71">
+        <v>1498</v>
+      </c>
+      <c r="S71">
+        <v>1498</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>1</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>2370</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>191</v>
+      </c>
+      <c r="B72" t="s">
+        <v>99</v>
+      </c>
+      <c r="C72" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" t="s">
+        <v>192</v>
+      </c>
+      <c r="E72" t="s">
+        <v>50</v>
+      </c>
+      <c r="F72" t="s">
+        <v>67</v>
+      </c>
+      <c r="G72" t="s">
+        <v>57</v>
+      </c>
+      <c r="H72" t="s">
+        <v>52</v>
+      </c>
+      <c r="I72">
+        <v>5</v>
+      </c>
+      <c r="J72">
+        <v>1500</v>
+      </c>
+      <c r="K72">
+        <v>3000</v>
+      </c>
+      <c r="L72" t="s">
+        <v>58</v>
+      </c>
+      <c r="M72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>103</v>
+      </c>
+      <c r="R72">
+        <v>354</v>
+      </c>
+      <c r="S72">
+        <v>354</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>1</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>2220</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>193</v>
+      </c>
+      <c r="B73" t="s">
+        <v>99</v>
+      </c>
+      <c r="C73" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" t="s">
+        <v>128</v>
+      </c>
+      <c r="E73" t="s">
+        <v>50</v>
+      </c>
+      <c r="F73" t="s">
+        <v>67</v>
+      </c>
+      <c r="G73" t="s">
+        <v>57</v>
+      </c>
+      <c r="H73" t="s">
+        <v>52</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="J73">
+        <v>2000</v>
+      </c>
+      <c r="K73">
+        <v>4000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>58</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>103</v>
+      </c>
+      <c r="R73">
+        <v>126</v>
+      </c>
+      <c r="S73">
+        <v>126</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>1</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>2190</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>194</v>
+      </c>
+      <c r="B74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" t="s">
+        <v>158</v>
+      </c>
+      <c r="E74" t="s">
+        <v>50</v>
+      </c>
+      <c r="F74" t="s">
+        <v>67</v>
+      </c>
+      <c r="G74" t="s">
+        <v>68</v>
+      </c>
+      <c r="H74" t="s">
+        <v>52</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+      <c r="J74">
+        <v>1500</v>
+      </c>
+      <c r="K74">
+        <v>3000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>58</v>
+      </c>
+      <c r="M74" t="s">
+        <v>125</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>103</v>
+      </c>
+      <c r="R74">
+        <v>1010</v>
+      </c>
+      <c r="S74">
+        <v>1010</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>14</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>3540</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>195</v>
+      </c>
+      <c r="B75" t="s">
+        <v>99</v>
+      </c>
+      <c r="C75" t="s">
+        <v>100</v>
+      </c>
+      <c r="D75" t="s">
+        <v>196</v>
+      </c>
+      <c r="E75" t="s">
+        <v>50</v>
+      </c>
+      <c r="F75" t="s">
+        <v>67</v>
+      </c>
+      <c r="G75" t="s">
+        <v>68</v>
+      </c>
+      <c r="H75" t="s">
+        <v>52</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+      <c r="J75">
+        <v>1500</v>
+      </c>
+      <c r="K75">
+        <v>3000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>58</v>
+      </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>103</v>
+      </c>
+      <c r="R75">
+        <v>283</v>
+      </c>
+      <c r="S75">
+        <v>283</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>4</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>3540</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>197</v>
+      </c>
+      <c r="B76" t="s">
+        <v>106</v>
+      </c>
+      <c r="C76" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" t="s">
+        <v>198</v>
+      </c>
+      <c r="E76" t="s">
+        <v>50</v>
+      </c>
+      <c r="F76" t="s">
+        <v>33</v>
+      </c>
+      <c r="G76" t="s">
+        <v>199</v>
+      </c>
+      <c r="H76" t="s">
+        <v>52</v>
+      </c>
+      <c r="I76">
+        <v>0.8</v>
+      </c>
+      <c r="J76">
+        <v>1000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>36</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>200</v>
+      </c>
+      <c r="P76" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>103</v>
+      </c>
+      <c r="R76">
+        <v>1585</v>
+      </c>
+      <c r="S76">
+        <v>1585</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>1</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>2370</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>201</v>
+      </c>
+      <c r="B77" t="s">
+        <v>99</v>
+      </c>
+      <c r="C77" t="s">
+        <v>100</v>
+      </c>
+      <c r="D77" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" t="s">
+        <v>50</v>
+      </c>
+      <c r="F77" t="s">
+        <v>67</v>
+      </c>
+      <c r="G77" t="s">
+        <v>34</v>
+      </c>
+      <c r="H77" t="s">
+        <v>52</v>
+      </c>
+      <c r="I77">
+        <v>1.5</v>
+      </c>
+      <c r="J77">
+        <v>1500</v>
+      </c>
+      <c r="K77">
+        <v>3000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>58</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>103</v>
+      </c>
+      <c r="R77">
+        <v>212</v>
+      </c>
+      <c r="S77">
+        <v>212</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>1</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>1320</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>203</v>
+      </c>
+      <c r="B78" t="s">
+        <v>99</v>
+      </c>
+      <c r="C78" t="s">
+        <v>100</v>
+      </c>
+      <c r="D78" t="s">
+        <v>204</v>
+      </c>
+      <c r="E78" t="s">
+        <v>50</v>
+      </c>
+      <c r="F78" t="s">
+        <v>67</v>
+      </c>
+      <c r="G78" t="s">
+        <v>57</v>
+      </c>
+      <c r="H78" t="s">
+        <v>52</v>
+      </c>
+      <c r="I78">
+        <v>3</v>
+      </c>
+      <c r="J78">
+        <v>1250</v>
+      </c>
+      <c r="K78">
+        <v>2500</v>
+      </c>
+      <c r="L78" t="s">
+        <v>58</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>103</v>
+      </c>
+      <c r="R78">
+        <v>74</v>
+      </c>
+      <c r="S78">
+        <v>74</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>1</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>2170</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>160.58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>205</v>
+      </c>
+      <c r="B79" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" t="s">
+        <v>107</v>
+      </c>
+      <c r="E79" t="s">
+        <v>50</v>
+      </c>
+      <c r="F79" t="s">
+        <v>67</v>
+      </c>
+      <c r="G79" t="s">
+        <v>68</v>
+      </c>
+      <c r="H79" t="s">
+        <v>52</v>
+      </c>
+      <c r="I79">
+        <v>2.5</v>
+      </c>
+      <c r="J79">
+        <v>1500</v>
+      </c>
+      <c r="K79">
+        <v>3000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>58</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>103</v>
+      </c>
+      <c r="R79">
+        <v>540</v>
+      </c>
+      <c r="S79">
+        <v>540</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>6</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>3540</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>206</v>
+      </c>
+      <c r="B80" t="s">
+        <v>106</v>
+      </c>
+      <c r="C80" t="s">
+        <v>100</v>
+      </c>
+      <c r="D80" t="s">
+        <v>107</v>
+      </c>
+      <c r="E80" t="s">
+        <v>50</v>
+      </c>
+      <c r="F80" t="s">
+        <v>67</v>
+      </c>
+      <c r="G80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H80" t="s">
+        <v>52</v>
+      </c>
+      <c r="I80">
+        <v>2.5</v>
+      </c>
+      <c r="J80">
+        <v>1500</v>
+      </c>
+      <c r="K80">
+        <v>3000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>58</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>103</v>
+      </c>
+      <c r="R80">
+        <v>520</v>
+      </c>
+      <c r="S80">
+        <v>520</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>6</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>3540</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>207</v>
+      </c>
+      <c r="B81" t="s">
+        <v>106</v>
+      </c>
+      <c r="C81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" t="s">
+        <v>107</v>
+      </c>
+      <c r="E81" t="s">
+        <v>50</v>
+      </c>
+      <c r="F81" t="s">
+        <v>67</v>
+      </c>
+      <c r="G81" t="s">
+        <v>68</v>
+      </c>
+      <c r="H81" t="s">
+        <v>52</v>
+      </c>
+      <c r="I81">
+        <v>2.5</v>
+      </c>
+      <c r="J81">
+        <v>1500</v>
+      </c>
+      <c r="K81">
+        <v>3000</v>
+      </c>
+      <c r="L81" t="s">
+        <v>58</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>103</v>
+      </c>
+      <c r="R81">
+        <v>530</v>
+      </c>
+      <c r="S81">
+        <v>530</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>6</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>3540</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>208</v>
+      </c>
+      <c r="B82" t="s">
+        <v>106</v>
+      </c>
+      <c r="C82" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82" t="s">
+        <v>107</v>
+      </c>
+      <c r="E82" t="s">
+        <v>50</v>
+      </c>
+      <c r="F82" t="s">
+        <v>67</v>
+      </c>
+      <c r="G82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H82" t="s">
+        <v>52</v>
+      </c>
+      <c r="I82">
+        <v>2.5</v>
+      </c>
+      <c r="J82">
+        <v>1500</v>
+      </c>
+      <c r="K82">
+        <v>3000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>58</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>103</v>
+      </c>
+      <c r="R82">
+        <v>526</v>
+      </c>
+      <c r="S82">
+        <v>526</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>6</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>3540</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>209</v>
+      </c>
+      <c r="B83" t="s">
+        <v>99</v>
+      </c>
+      <c r="C83" t="s">
+        <v>100</v>
+      </c>
+      <c r="D83" t="s">
+        <v>210</v>
+      </c>
+      <c r="E83" t="s">
+        <v>50</v>
+      </c>
+      <c r="F83" t="s">
+        <v>67</v>
+      </c>
+      <c r="G83" t="s">
+        <v>68</v>
+      </c>
+      <c r="H83" t="s">
+        <v>52</v>
+      </c>
+      <c r="I83">
+        <v>3</v>
+      </c>
+      <c r="J83">
+        <v>1500</v>
+      </c>
+      <c r="K83">
+        <v>3000</v>
+      </c>
+      <c r="L83" t="s">
+        <v>58</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>103</v>
+      </c>
+      <c r="R83">
+        <v>212</v>
+      </c>
+      <c r="S83">
+        <v>212</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>1</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>3490</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>211</v>
+      </c>
+      <c r="B84" t="s">
+        <v>99</v>
+      </c>
+      <c r="C84" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" t="s">
+        <v>210</v>
+      </c>
+      <c r="E84" t="s">
+        <v>50</v>
+      </c>
+      <c r="F84" t="s">
+        <v>67</v>
+      </c>
+      <c r="G84" t="s">
+        <v>68</v>
+      </c>
+      <c r="H84" t="s">
+        <v>52</v>
+      </c>
+      <c r="I84">
+        <v>3</v>
+      </c>
+      <c r="J84">
+        <v>1500</v>
+      </c>
+      <c r="K84">
+        <v>3000</v>
+      </c>
+      <c r="L84" t="s">
+        <v>58</v>
+      </c>
+      <c r="M84" t="s">
+        <v>37</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>103</v>
+      </c>
+      <c r="R84">
+        <v>212</v>
+      </c>
+      <c r="S84">
+        <v>212</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>1</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>3490</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>212</v>
+      </c>
+      <c r="B85" t="s">
+        <v>109</v>
+      </c>
+      <c r="C85" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85" t="s">
+        <v>213</v>
+      </c>
+      <c r="E85" t="s">
+        <v>50</v>
+      </c>
+      <c r="F85" t="s">
+        <v>67</v>
+      </c>
+      <c r="G85" t="s">
+        <v>57</v>
+      </c>
+      <c r="H85" t="s">
+        <v>52</v>
+      </c>
+      <c r="I85">
+        <v>4</v>
+      </c>
+      <c r="J85">
+        <v>1000</v>
+      </c>
+      <c r="K85">
+        <v>2000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>58</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>103</v>
+      </c>
+      <c r="R85">
+        <v>315</v>
+      </c>
+      <c r="S85">
+        <v>315</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>5</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>2220</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>214</v>
+      </c>
+      <c r="B86" t="s">
+        <v>99</v>
+      </c>
+      <c r="C86" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86" t="s">
+        <v>215</v>
+      </c>
+      <c r="E86" t="s">
+        <v>50</v>
+      </c>
+      <c r="F86" t="s">
+        <v>67</v>
+      </c>
+      <c r="G86" t="s">
+        <v>57</v>
+      </c>
+      <c r="H86" t="s">
+        <v>52</v>
+      </c>
+      <c r="I86">
+        <v>1.5</v>
+      </c>
+      <c r="J86">
+        <v>1250</v>
+      </c>
+      <c r="K86">
+        <v>2500</v>
+      </c>
+      <c r="L86" t="s">
+        <v>58</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>103</v>
+      </c>
+      <c r="R86">
+        <v>295</v>
+      </c>
+      <c r="S86">
+        <v>295</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>8</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>2220</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>654.9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>216</v>
+      </c>
+      <c r="B87" t="s">
+        <v>99</v>
+      </c>
+      <c r="C87" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" t="s">
+        <v>139</v>
+      </c>
+      <c r="E87" t="s">
+        <v>50</v>
+      </c>
+      <c r="F87" t="s">
+        <v>67</v>
+      </c>
+      <c r="G87" t="s">
+        <v>57</v>
+      </c>
+      <c r="H87" t="s">
+        <v>52</v>
+      </c>
+      <c r="I87">
+        <v>5</v>
+      </c>
+      <c r="J87">
+        <v>1000</v>
+      </c>
+      <c r="K87">
+        <v>2000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>111</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>103</v>
+      </c>
+      <c r="R87">
+        <v>944</v>
+      </c>
+      <c r="S87">
+        <v>944</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>1</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>2020</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" t="s">
+        <v>99</v>
+      </c>
+      <c r="C88" t="s">
+        <v>100</v>
+      </c>
+      <c r="D88" t="s">
+        <v>183</v>
+      </c>
+      <c r="E88" t="s">
+        <v>50</v>
+      </c>
+      <c r="F88" t="s">
+        <v>67</v>
+      </c>
+      <c r="G88" t="s">
+        <v>57</v>
+      </c>
+      <c r="H88" t="s">
+        <v>52</v>
+      </c>
+      <c r="I88">
+        <v>6</v>
+      </c>
+      <c r="J88">
+        <v>1000</v>
+      </c>
+      <c r="K88">
+        <v>2000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>58</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>103</v>
+      </c>
+      <c r="R88">
+        <v>189</v>
+      </c>
+      <c r="S88">
+        <v>189</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>2</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>2170</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>410.13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>218</v>
+      </c>
+      <c r="B89" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" t="s">
+        <v>219</v>
+      </c>
+      <c r="E89" t="s">
+        <v>50</v>
+      </c>
+      <c r="F89" t="s">
+        <v>67</v>
+      </c>
+      <c r="G89" t="s">
+        <v>57</v>
+      </c>
+      <c r="H89" t="s">
+        <v>52</v>
+      </c>
+      <c r="I89">
+        <v>1.5</v>
+      </c>
+      <c r="J89">
+        <v>1000</v>
+      </c>
+      <c r="K89">
+        <v>2000</v>
+      </c>
+      <c r="L89" t="s">
+        <v>58</v>
+      </c>
+      <c r="M89" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>103</v>
+      </c>
+      <c r="R89">
+        <v>260</v>
+      </c>
+      <c r="S89">
+        <v>260</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>11</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>2220</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>577.2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>220</v>
+      </c>
+      <c r="B90" t="s">
+        <v>106</v>
+      </c>
+      <c r="C90" t="s">
+        <v>100</v>
+      </c>
+      <c r="D90" t="s">
+        <v>221</v>
+      </c>
+      <c r="E90" t="s">
+        <v>50</v>
+      </c>
+      <c r="F90" t="s">
+        <v>67</v>
+      </c>
+      <c r="G90" t="s">
+        <v>68</v>
+      </c>
+      <c r="H90" t="s">
+        <v>52</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>1500</v>
+      </c>
+      <c r="K90">
+        <v>3000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>58</v>
+      </c>
+      <c r="M90" t="s">
+        <v>125</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>103</v>
+      </c>
+      <c r="R90">
+        <v>1224</v>
+      </c>
+      <c r="S90">
+        <v>1224</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>34</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>3540</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>222</v>
+      </c>
+      <c r="B91" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" t="s">
+        <v>100</v>
+      </c>
+      <c r="D91" t="s">
+        <v>187</v>
+      </c>
+      <c r="E91" t="s">
+        <v>50</v>
+      </c>
+      <c r="F91" t="s">
+        <v>67</v>
+      </c>
+      <c r="G91" t="s">
+        <v>57</v>
+      </c>
+      <c r="H91" t="s">
+        <v>52</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
+      </c>
+      <c r="J91">
+        <v>1250</v>
+      </c>
+      <c r="K91">
+        <v>2500</v>
+      </c>
+      <c r="L91" t="s">
+        <v>58</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>103</v>
+      </c>
+      <c r="R91">
+        <v>197</v>
+      </c>
+      <c r="S91">
+        <v>197</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>4</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>2170</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>223</v>
+      </c>
+      <c r="B92" t="s">
+        <v>99</v>
+      </c>
+      <c r="C92" t="s">
+        <v>100</v>
+      </c>
+      <c r="D92" t="s">
+        <v>224</v>
+      </c>
+      <c r="E92" t="s">
+        <v>50</v>
+      </c>
+      <c r="F92" t="s">
+        <v>67</v>
+      </c>
+      <c r="G92" t="s">
+        <v>68</v>
+      </c>
+      <c r="H92" t="s">
+        <v>52</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>1500</v>
+      </c>
+      <c r="K92">
+        <v>3000</v>
+      </c>
+      <c r="L92" t="s">
+        <v>58</v>
+      </c>
+      <c r="M92" t="s">
+        <v>37</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>38</v>
+      </c>
+      <c r="P92" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>103</v>
+      </c>
+      <c r="R92">
+        <v>35</v>
+      </c>
+      <c r="S92">
+        <v>35</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>1</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>3490</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>225</v>
+      </c>
+      <c r="B93" t="s">
+        <v>99</v>
+      </c>
+      <c r="C93" t="s">
+        <v>100</v>
+      </c>
+      <c r="D93" t="s">
+        <v>224</v>
+      </c>
+      <c r="E93" t="s">
+        <v>50</v>
+      </c>
+      <c r="F93" t="s">
+        <v>67</v>
+      </c>
+      <c r="G93" t="s">
+        <v>68</v>
+      </c>
+      <c r="H93" t="s">
+        <v>52</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1500</v>
+      </c>
+      <c r="K93">
+        <v>3000</v>
+      </c>
+      <c r="L93" t="s">
+        <v>58</v>
+      </c>
+      <c r="M93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" t="s">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>103</v>
+      </c>
+      <c r="R93">
+        <v>177</v>
+      </c>
+      <c r="S93">
+        <v>177</v>
+      </c>
+      <c r="T93" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93">
+        <v>5</v>
+      </c>
+      <c r="V93" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93">
+        <v>3490</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA93">
+        <v>617.73</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>226</v>
+      </c>
+      <c r="B94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C94" t="s">
+        <v>100</v>
+      </c>
+      <c r="D94" t="s">
+        <v>227</v>
+      </c>
+      <c r="E94" t="s">
+        <v>50</v>
+      </c>
+      <c r="F94" t="s">
+        <v>33</v>
+      </c>
+      <c r="G94" t="s">
+        <v>228</v>
+      </c>
+      <c r="H94" t="s">
+        <v>52</v>
+      </c>
+      <c r="I94">
+        <v>0.6</v>
+      </c>
+      <c r="J94">
+        <v>1000</v>
+      </c>
+      <c r="L94" t="s">
+        <v>36</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
+      </c>
+      <c r="N94" t="s">
+        <v>37</v>
+      </c>
+      <c r="O94" t="s">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>103</v>
+      </c>
+      <c r="R94">
+        <v>745</v>
+      </c>
+      <c r="S94">
+        <v>745</v>
+      </c>
+      <c r="T94" t="s">
+        <v>41</v>
+      </c>
+      <c r="U94">
+        <v>1</v>
+      </c>
+      <c r="V94" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94">
+        <v>2290</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA94">
+        <v>1706.05</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>229</v>
+      </c>
+      <c r="B95" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95" t="s">
+        <v>100</v>
+      </c>
+      <c r="D95" t="s">
+        <v>230</v>
+      </c>
+      <c r="E95" t="s">
+        <v>50</v>
+      </c>
+      <c r="F95" t="s">
+        <v>67</v>
+      </c>
+      <c r="G95" t="s">
+        <v>34</v>
+      </c>
+      <c r="H95" t="s">
+        <v>52</v>
+      </c>
+      <c r="I95">
+        <v>1.5</v>
+      </c>
+      <c r="J95">
+        <v>1500</v>
+      </c>
+      <c r="K95">
+        <v>3000</v>
+      </c>
+      <c r="L95" t="s">
+        <v>36</v>
+      </c>
+      <c r="M95" t="s">
+        <v>125</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>103</v>
+      </c>
+      <c r="R95">
+        <v>916</v>
+      </c>
+      <c r="S95">
+        <v>916</v>
+      </c>
+      <c r="T95" t="s">
+        <v>41</v>
+      </c>
+      <c r="U95">
+        <v>18</v>
+      </c>
+      <c r="V95" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95">
+        <v>1320</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA95">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>231</v>
+      </c>
+      <c r="B96" t="s">
+        <v>99</v>
+      </c>
+      <c r="C96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D96" t="s">
+        <v>210</v>
+      </c>
+      <c r="E96" t="s">
+        <v>50</v>
+      </c>
+      <c r="F96" t="s">
+        <v>67</v>
+      </c>
+      <c r="G96" t="s">
+        <v>68</v>
+      </c>
+      <c r="H96" t="s">
+        <v>52</v>
+      </c>
+      <c r="I96">
+        <v>3</v>
+      </c>
+      <c r="J96">
+        <v>1500</v>
+      </c>
+      <c r="K96">
+        <v>3000</v>
+      </c>
+      <c r="L96" t="s">
+        <v>58</v>
+      </c>
+      <c r="M96" t="s">
+        <v>37</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
+      </c>
+      <c r="P96" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>103</v>
+      </c>
+      <c r="R96">
+        <v>319</v>
+      </c>
+      <c r="S96">
+        <v>319</v>
+      </c>
+      <c r="T96" t="s">
+        <v>41</v>
+      </c>
+      <c r="U96">
+        <v>1</v>
+      </c>
+      <c r="V96" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X96">
+        <v>3540</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA96">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>232</v>
+      </c>
+      <c r="B97" t="s">
+        <v>99</v>
+      </c>
+      <c r="C97" t="s">
+        <v>100</v>
+      </c>
+      <c r="D97" t="s">
+        <v>210</v>
+      </c>
+      <c r="E97" t="s">
+        <v>50</v>
+      </c>
+      <c r="F97" t="s">
+        <v>67</v>
+      </c>
+      <c r="G97" t="s">
+        <v>68</v>
+      </c>
+      <c r="H97" t="s">
+        <v>52</v>
+      </c>
+      <c r="I97">
+        <v>3</v>
+      </c>
+      <c r="J97">
+        <v>1500</v>
+      </c>
+      <c r="K97">
+        <v>3000</v>
+      </c>
+      <c r="L97" t="s">
+        <v>58</v>
+      </c>
+      <c r="M97" t="s">
+        <v>37</v>
+      </c>
+      <c r="N97" t="s">
+        <v>37</v>
+      </c>
+      <c r="O97" t="s">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>103</v>
+      </c>
+      <c r="R97">
+        <v>212</v>
+      </c>
+      <c r="S97">
+        <v>212</v>
+      </c>
+      <c r="T97" t="s">
+        <v>41</v>
+      </c>
+      <c r="U97">
+        <v>1</v>
+      </c>
+      <c r="V97" t="s">
+        <v>43</v>
+      </c>
+      <c r="W97" t="s">
+        <v>43</v>
+      </c>
+      <c r="X97">
+        <v>3490</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA97">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>233</v>
+      </c>
+      <c r="B98" t="s">
+        <v>99</v>
+      </c>
+      <c r="C98" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98" t="s">
+        <v>210</v>
+      </c>
+      <c r="E98" t="s">
+        <v>50</v>
+      </c>
+      <c r="F98" t="s">
+        <v>67</v>
+      </c>
+      <c r="G98" t="s">
+        <v>68</v>
+      </c>
+      <c r="H98" t="s">
+        <v>52</v>
+      </c>
+      <c r="I98">
+        <v>3</v>
+      </c>
+      <c r="J98">
+        <v>1500</v>
+      </c>
+      <c r="K98">
+        <v>3000</v>
+      </c>
+      <c r="L98" t="s">
+        <v>58</v>
+      </c>
+      <c r="M98" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" t="s">
+        <v>38</v>
+      </c>
+      <c r="P98" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>103</v>
+      </c>
+      <c r="R98">
+        <v>212</v>
+      </c>
+      <c r="S98">
+        <v>212</v>
+      </c>
+      <c r="T98" t="s">
+        <v>41</v>
+      </c>
+      <c r="U98">
+        <v>1</v>
+      </c>
+      <c r="V98" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98">
+        <v>3490</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA98">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>234</v>
+      </c>
+      <c r="B99" t="s">
+        <v>99</v>
+      </c>
+      <c r="C99" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" t="s">
+        <v>210</v>
+      </c>
+      <c r="E99" t="s">
+        <v>50</v>
+      </c>
+      <c r="F99" t="s">
+        <v>67</v>
+      </c>
+      <c r="G99" t="s">
+        <v>68</v>
+      </c>
+      <c r="H99" t="s">
+        <v>52</v>
+      </c>
+      <c r="I99">
+        <v>3</v>
+      </c>
+      <c r="J99">
+        <v>1500</v>
+      </c>
+      <c r="K99">
+        <v>3000</v>
+      </c>
+      <c r="L99" t="s">
+        <v>58</v>
+      </c>
+      <c r="M99" t="s">
+        <v>37</v>
+      </c>
+      <c r="N99" t="s">
+        <v>37</v>
+      </c>
+      <c r="O99" t="s">
+        <v>38</v>
+      </c>
+      <c r="P99" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>103</v>
+      </c>
+      <c r="R99">
+        <v>319</v>
+      </c>
+      <c r="S99">
+        <v>319</v>
+      </c>
+      <c r="T99" t="s">
+        <v>41</v>
+      </c>
+      <c r="U99">
+        <v>1</v>
+      </c>
+      <c r="V99" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99">
+        <v>3540</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA99">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>235</v>
+      </c>
+      <c r="B100" t="s">
+        <v>109</v>
+      </c>
+      <c r="C100" t="s">
+        <v>100</v>
+      </c>
+      <c r="D100" t="s">
+        <v>236</v>
+      </c>
+      <c r="E100" t="s">
+        <v>50</v>
+      </c>
+      <c r="F100" t="s">
+        <v>67</v>
+      </c>
+      <c r="G100" t="s">
+        <v>68</v>
+      </c>
+      <c r="H100" t="s">
+        <v>52</v>
+      </c>
+      <c r="I100">
+        <v>2</v>
+      </c>
+      <c r="J100">
+        <v>2000</v>
+      </c>
+      <c r="K100">
+        <v>6000</v>
+      </c>
+      <c r="L100" t="s">
+        <v>58</v>
+      </c>
+      <c r="M100" t="s">
+        <v>37</v>
+      </c>
+      <c r="N100" t="s">
+        <v>37</v>
+      </c>
+      <c r="O100" t="s">
+        <v>38</v>
+      </c>
+      <c r="P100" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>103</v>
+      </c>
+      <c r="R100">
+        <v>189</v>
+      </c>
+      <c r="S100">
+        <v>189</v>
+      </c>
+      <c r="T100" t="s">
+        <v>41</v>
+      </c>
+      <c r="U100">
+        <v>1</v>
+      </c>
+      <c r="V100" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100">
+        <v>3510</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA100">
+        <v>663.39</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>237</v>
+      </c>
+      <c r="B101" t="s">
+        <v>99</v>
+      </c>
+      <c r="C101" t="s">
+        <v>100</v>
+      </c>
+      <c r="D101" t="s">
+        <v>238</v>
+      </c>
+      <c r="E101" t="s">
+        <v>50</v>
+      </c>
+      <c r="F101" t="s">
+        <v>67</v>
+      </c>
+      <c r="G101" t="s">
+        <v>57</v>
+      </c>
+      <c r="H101" t="s">
+        <v>52</v>
+      </c>
+      <c r="I101">
+        <v>4</v>
+      </c>
+      <c r="J101">
+        <v>1000</v>
+      </c>
+      <c r="K101">
+        <v>2000</v>
+      </c>
+      <c r="L101" t="s">
+        <v>58</v>
+      </c>
+      <c r="M101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N101" t="s">
+        <v>37</v>
+      </c>
+      <c r="O101" t="s">
+        <v>38</v>
+      </c>
+      <c r="P101" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>103</v>
+      </c>
+      <c r="R101">
+        <v>63</v>
+      </c>
+      <c r="S101">
+        <v>63</v>
+      </c>
+      <c r="T101" t="s">
+        <v>41</v>
+      </c>
+      <c r="U101">
+        <v>1</v>
+      </c>
+      <c r="V101" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101">
+        <v>2170</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA101">
+        <v>136.71</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>239</v>
+      </c>
+      <c r="B102" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102" t="s">
+        <v>100</v>
+      </c>
+      <c r="D102" t="s">
+        <v>240</v>
+      </c>
+      <c r="E102" t="s">
+        <v>50</v>
+      </c>
+      <c r="F102" t="s">
+        <v>67</v>
+      </c>
+      <c r="G102" t="s">
+        <v>57</v>
+      </c>
+      <c r="H102" t="s">
+        <v>52</v>
+      </c>
+      <c r="I102">
+        <v>1.2</v>
+      </c>
+      <c r="J102">
+        <v>1250</v>
+      </c>
+      <c r="K102">
+        <v>2500</v>
+      </c>
+      <c r="L102" t="s">
+        <v>58</v>
+      </c>
+      <c r="M102" t="s">
+        <v>125</v>
+      </c>
+      <c r="N102" t="s">
+        <v>37</v>
+      </c>
+      <c r="O102" t="s">
+        <v>38</v>
+      </c>
+      <c r="P102" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>103</v>
+      </c>
+      <c r="R102">
+        <v>568</v>
+      </c>
+      <c r="S102">
+        <v>568</v>
+      </c>
+      <c r="T102" t="s">
+        <v>41</v>
+      </c>
+      <c r="U102">
+        <v>19</v>
+      </c>
+      <c r="V102" t="s">
+        <v>43</v>
+      </c>
+      <c r="W102" t="s">
+        <v>43</v>
+      </c>
+      <c r="X102">
+        <v>2170</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA102">
+        <v>1232.56</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>241</v>
+      </c>
+      <c r="B103" t="s">
+        <v>106</v>
+      </c>
+      <c r="C103" t="s">
+        <v>100</v>
+      </c>
+      <c r="D103" t="s">
+        <v>242</v>
+      </c>
+      <c r="E103" t="s">
+        <v>50</v>
+      </c>
+      <c r="F103" t="s">
+        <v>67</v>
+      </c>
+      <c r="G103" t="s">
+        <v>57</v>
+      </c>
+      <c r="H103" t="s">
+        <v>52</v>
+      </c>
+      <c r="I103">
+        <v>1.2</v>
+      </c>
+      <c r="J103">
+        <v>1500</v>
+      </c>
+      <c r="K103">
+        <v>3000</v>
+      </c>
+      <c r="L103" t="s">
+        <v>58</v>
+      </c>
+      <c r="M103" t="s">
+        <v>243</v>
+      </c>
+      <c r="N103" t="s">
+        <v>37</v>
+      </c>
+      <c r="O103" t="s">
+        <v>38</v>
+      </c>
+      <c r="P103" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>103</v>
+      </c>
+      <c r="R103">
+        <v>660</v>
+      </c>
+      <c r="S103">
+        <v>660</v>
+      </c>
+      <c r="T103" t="s">
+        <v>41</v>
+      </c>
+      <c r="U103">
+        <v>15</v>
+      </c>
+      <c r="V103" t="s">
+        <v>43</v>
+      </c>
+      <c r="W103" t="s">
+        <v>43</v>
+      </c>
+      <c r="X103">
+        <v>2170</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA103">
+        <v>1432.2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>244</v>
+      </c>
+      <c r="B104" t="s">
+        <v>99</v>
+      </c>
+      <c r="C104" t="s">
+        <v>100</v>
+      </c>
+      <c r="D104" t="s">
+        <v>245</v>
+      </c>
+      <c r="E104" t="s">
+        <v>50</v>
+      </c>
+      <c r="F104" t="s">
+        <v>67</v>
+      </c>
+      <c r="G104" t="s">
+        <v>34</v>
+      </c>
+      <c r="H104" t="s">
+        <v>52</v>
+      </c>
+      <c r="I104">
+        <v>1.5</v>
+      </c>
+      <c r="J104">
+        <v>1250</v>
+      </c>
+      <c r="K104">
+        <v>2500</v>
+      </c>
+      <c r="L104" t="s">
+        <v>58</v>
+      </c>
+      <c r="M104" t="s">
+        <v>37</v>
+      </c>
+      <c r="N104" t="s">
+        <v>37</v>
+      </c>
+      <c r="O104" t="s">
+        <v>38</v>
+      </c>
+      <c r="P104" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>103</v>
+      </c>
+      <c r="R104">
+        <v>148</v>
+      </c>
+      <c r="S104">
+        <v>148</v>
+      </c>
+      <c r="T104" t="s">
+        <v>41</v>
+      </c>
+      <c r="U104">
+        <v>4</v>
+      </c>
+      <c r="V104" t="s">
+        <v>43</v>
+      </c>
+      <c r="W104" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104">
+        <v>1320</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA104">
+        <v>195.36</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>246</v>
+      </c>
+      <c r="B105" t="s">
+        <v>99</v>
+      </c>
+      <c r="C105" t="s">
+        <v>100</v>
+      </c>
+      <c r="D105" t="s">
+        <v>245</v>
+      </c>
+      <c r="E105" t="s">
+        <v>50</v>
+      </c>
+      <c r="F105" t="s">
+        <v>67</v>
+      </c>
+      <c r="G105" t="s">
+        <v>34</v>
+      </c>
+      <c r="H105" t="s">
+        <v>52</v>
+      </c>
+      <c r="I105">
+        <v>1.5</v>
+      </c>
+      <c r="J105">
+        <v>1250</v>
+      </c>
+      <c r="K105">
+        <v>2500</v>
+      </c>
+      <c r="L105" t="s">
+        <v>58</v>
+      </c>
+      <c r="M105" t="s">
+        <v>37</v>
+      </c>
+      <c r="N105" t="s">
+        <v>37</v>
+      </c>
+      <c r="O105" t="s">
+        <v>38</v>
+      </c>
+      <c r="P105" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>103</v>
+      </c>
+      <c r="R105">
+        <v>148</v>
+      </c>
+      <c r="S105">
+        <v>148</v>
+      </c>
+      <c r="T105" t="s">
+        <v>41</v>
+      </c>
+      <c r="U105">
+        <v>4</v>
+      </c>
+      <c r="V105" t="s">
+        <v>43</v>
+      </c>
+      <c r="W105" t="s">
+        <v>43</v>
+      </c>
+      <c r="X105">
+        <v>1320</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA105">
+        <v>195.36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>247</v>
+      </c>
+      <c r="B106" t="s">
+        <v>99</v>
+      </c>
+      <c r="C106" t="s">
+        <v>100</v>
+      </c>
+      <c r="D106" t="s">
+        <v>248</v>
+      </c>
+      <c r="E106" t="s">
+        <v>50</v>
+      </c>
+      <c r="F106" t="s">
+        <v>67</v>
+      </c>
+      <c r="G106" t="s">
+        <v>57</v>
+      </c>
+      <c r="H106" t="s">
+        <v>52</v>
+      </c>
+      <c r="I106">
+        <v>6</v>
+      </c>
+      <c r="J106">
+        <v>2000</v>
+      </c>
+      <c r="K106">
+        <v>4000</v>
+      </c>
+      <c r="L106" t="s">
+        <v>58</v>
+      </c>
+      <c r="M106" t="s">
+        <v>37</v>
+      </c>
+      <c r="N106" t="s">
+        <v>37</v>
+      </c>
+      <c r="O106" t="s">
+        <v>38</v>
+      </c>
+      <c r="P106" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>103</v>
+      </c>
+      <c r="R106">
+        <v>756</v>
+      </c>
+      <c r="S106">
+        <v>756</v>
+      </c>
+      <c r="T106" t="s">
+        <v>41</v>
+      </c>
+      <c r="U106">
+        <v>2</v>
+      </c>
+      <c r="V106" t="s">
+        <v>43</v>
+      </c>
+      <c r="W106" t="s">
+        <v>43</v>
+      </c>
+      <c r="X106">
+        <v>2240</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA106">
+        <v>1693.44</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>249</v>
+      </c>
+      <c r="B107" t="s">
+        <v>99</v>
+      </c>
+      <c r="C107" t="s">
+        <v>100</v>
+      </c>
+      <c r="D107" t="s">
+        <v>181</v>
+      </c>
+      <c r="E107" t="s">
+        <v>50</v>
+      </c>
+      <c r="F107" t="s">
+        <v>67</v>
+      </c>
+      <c r="G107" t="s">
+        <v>57</v>
+      </c>
+      <c r="H107" t="s">
+        <v>52</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107">
+        <v>1500</v>
+      </c>
+      <c r="K107">
+        <v>3000</v>
+      </c>
+      <c r="L107" t="s">
+        <v>58</v>
+      </c>
+      <c r="M107" t="s">
+        <v>37</v>
+      </c>
+      <c r="N107" t="s">
+        <v>37</v>
+      </c>
+      <c r="O107" t="s">
+        <v>38</v>
+      </c>
+      <c r="P107" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>103</v>
+      </c>
+      <c r="R107">
+        <v>35</v>
+      </c>
+      <c r="S107">
+        <v>35</v>
+      </c>
+      <c r="T107" t="s">
+        <v>41</v>
+      </c>
+      <c r="U107">
+        <v>1</v>
+      </c>
+      <c r="V107" t="s">
+        <v>43</v>
+      </c>
+      <c r="W107" t="s">
+        <v>43</v>
+      </c>
+      <c r="X107">
+        <v>2170</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA107">
+        <v>75.95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>250</v>
+      </c>
+      <c r="B108" t="s">
+        <v>99</v>
+      </c>
+      <c r="C108" t="s">
+        <v>100</v>
+      </c>
+      <c r="D108" t="s">
+        <v>181</v>
+      </c>
+      <c r="E108" t="s">
+        <v>50</v>
+      </c>
+      <c r="F108" t="s">
+        <v>67</v>
+      </c>
+      <c r="G108" t="s">
+        <v>57</v>
+      </c>
+      <c r="H108" t="s">
+        <v>52</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>1500</v>
+      </c>
+      <c r="K108">
+        <v>3000</v>
+      </c>
+      <c r="L108" t="s">
+        <v>58</v>
+      </c>
+      <c r="M108" t="s">
+        <v>37</v>
+      </c>
+      <c r="N108" t="s">
+        <v>37</v>
+      </c>
+      <c r="O108" t="s">
+        <v>38</v>
+      </c>
+      <c r="P108" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>103</v>
+      </c>
+      <c r="R108">
+        <v>35</v>
+      </c>
+      <c r="S108">
+        <v>35</v>
+      </c>
+      <c r="T108" t="s">
+        <v>41</v>
+      </c>
+      <c r="U108">
+        <v>1</v>
+      </c>
+      <c r="V108" t="s">
+        <v>43</v>
+      </c>
+      <c r="W108" t="s">
+        <v>43</v>
+      </c>
+      <c r="X108">
+        <v>2170</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA108">
+        <v>75.95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>251</v>
+      </c>
+      <c r="B109" t="s">
+        <v>106</v>
+      </c>
+      <c r="C109" t="s">
+        <v>100</v>
+      </c>
+      <c r="D109" t="s">
+        <v>252</v>
+      </c>
+      <c r="E109" t="s">
+        <v>50</v>
+      </c>
+      <c r="F109" t="s">
+        <v>67</v>
+      </c>
+      <c r="G109" t="s">
+        <v>228</v>
+      </c>
+      <c r="H109" t="s">
+        <v>52</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+      <c r="J109">
+        <v>1000</v>
+      </c>
+      <c r="K109">
+        <v>2000</v>
+      </c>
+      <c r="L109" t="s">
+        <v>36</v>
+      </c>
+      <c r="M109" t="s">
+        <v>37</v>
+      </c>
+      <c r="N109" t="s">
+        <v>37</v>
+      </c>
+      <c r="O109" t="s">
+        <v>38</v>
+      </c>
+      <c r="P109" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>103</v>
+      </c>
+      <c r="R109">
+        <v>544</v>
+      </c>
+      <c r="S109">
+        <v>544</v>
+      </c>
+      <c r="T109" t="s">
+        <v>41</v>
+      </c>
+      <c r="U109">
+        <v>1</v>
+      </c>
+      <c r="V109" t="s">
+        <v>43</v>
+      </c>
+      <c r="W109" t="s">
+        <v>43</v>
+      </c>
+      <c r="X109">
+        <v>2220</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA109">
+        <v>1207.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="258">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -184,16 +184,607 @@
     <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4304</t>
   </si>
   <si>
-    <t>K260258898</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 2B without paper 1.53 x 385.0 mm Unslit not marked</t>
-  </si>
-  <si>
-    <t>V1 - Coil eye to the sky + Unalit</t>
-  </si>
-  <si>
-    <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305</t>
+    <t>T468837</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>Slit</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>T468838</t>
+  </si>
+  <si>
+    <t>7246484</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4404-316L</t>
+  </si>
+  <si>
+    <t>7246542</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7246814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 5.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7246817</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 6.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T473609</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7247036</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Polish grain 400 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7247041</t>
+  </si>
+  <si>
+    <t>7247338</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7247409</t>
+  </si>
+  <si>
+    <t>7247854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475488</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248626</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248988</t>
+  </si>
+  <si>
+    <t>Coil 1.4307-304L 2D 1.0 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>7248989</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T477742</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>K30/1.4016-430</t>
+  </si>
+  <si>
+    <t>7249627</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Duplo polish grain 320</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481266</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481267</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T481616</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T481617</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481869</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7253484</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 240 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 240</t>
+  </si>
+  <si>
+    <t>7253485</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484088</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484797</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254248</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T485455</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254992</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T486939</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>T487305</t>
+  </si>
+  <si>
+    <t>T487411</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255816</t>
+  </si>
+  <si>
+    <t>T487947</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T487964</t>
+  </si>
+  <si>
+    <t>7256046</t>
+  </si>
+  <si>
+    <t>Coil 1.4301-304 2R 0.6 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>T488237</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256367</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.2 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7256368</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Scotchbrite</t>
+  </si>
+  <si>
+    <t>T488483</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T488484</t>
+  </si>
+  <si>
+    <t>T488802</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T488824</t>
+  </si>
+  <si>
+    <t>T488827</t>
+  </si>
+  <si>
+    <t>7256740</t>
+  </si>
+  <si>
+    <t>Sheets 1.4301-304 2R 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256746</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7256751</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2R 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256753</t>
+  </si>
+  <si>
+    <t>7256757</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256760</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R with paper 0.8 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256809</t>
+  </si>
+  <si>
+    <t>7256813</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 240 Nov 4228 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256815</t>
+  </si>
+  <si>
+    <t>7256817</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256819</t>
+  </si>
+  <si>
+    <t>7256820</t>
+  </si>
+  <si>
+    <t>7256821</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>7256837</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 4.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256838</t>
+  </si>
+  <si>
+    <t>7256839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 6.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T488986</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256940</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed Nov 4228 0.8 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256941</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489089</t>
+  </si>
+  <si>
+    <t>7257077</t>
   </si>
 </sst>
 </file>
@@ -570,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB115"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -916,31 +1507,34 @@
         <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="I5">
-        <v>1.53</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>385</v>
+        <v>1000</v>
+      </c>
+      <c r="K5">
+        <v>2000</v>
       </c>
       <c r="L5" t="s">
         <v>50</v>
@@ -955,43 +1549,9167 @@
         <v>38</v>
       </c>
       <c r="P5" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>64</v>
+      </c>
+      <c r="R5">
+        <v>283</v>
+      </c>
+      <c r="S5">
+        <v>283</v>
+      </c>
+      <c r="T5" t="s">
+        <v>41</v>
+      </c>
+      <c r="U5">
+        <v>5</v>
+      </c>
+      <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5">
+        <v>3690</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA5">
+        <v>1044.27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>2000</v>
+      </c>
+      <c r="L6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>64</v>
+      </c>
+      <c r="R6">
+        <v>567</v>
+      </c>
+      <c r="S6">
+        <v>567</v>
+      </c>
+      <c r="T6" t="s">
+        <v>41</v>
+      </c>
+      <c r="U6">
+        <v>6</v>
+      </c>
+      <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6">
+        <v>3690</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA6">
+        <v>2092.23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>2.5</v>
+      </c>
+      <c r="J7">
+        <v>1500</v>
+      </c>
+      <c r="K7">
+        <v>3000</v>
+      </c>
+      <c r="L7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R7">
+        <v>554</v>
+      </c>
+      <c r="S7">
+        <v>554</v>
+      </c>
+      <c r="T7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U7">
+        <v>6</v>
+      </c>
+      <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7">
+        <v>3540</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA7">
+        <v>1961.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>1000</v>
+      </c>
+      <c r="K8">
+        <v>2000</v>
+      </c>
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>64</v>
+      </c>
+      <c r="R8">
+        <v>1133</v>
+      </c>
+      <c r="S8">
+        <v>1133</v>
+      </c>
+      <c r="T8" t="s">
+        <v>41</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8" t="s">
+        <v>43</v>
+      </c>
+      <c r="W8" t="s">
+        <v>43</v>
+      </c>
+      <c r="X8">
+        <v>2070</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA8">
+        <v>2345.31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9">
+        <v>2000</v>
+      </c>
+      <c r="K9">
+        <v>6000</v>
+      </c>
+      <c r="L9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>64</v>
+      </c>
+      <c r="R9">
+        <v>472</v>
+      </c>
+      <c r="S9">
+        <v>472</v>
+      </c>
+      <c r="T9" t="s">
+        <v>41</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9" t="s">
+        <v>43</v>
+      </c>
+      <c r="W9" t="s">
+        <v>43</v>
+      </c>
+      <c r="X9">
+        <v>2240</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA9">
+        <v>1057.28</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+      <c r="J10">
+        <v>2000</v>
+      </c>
+      <c r="K10">
+        <v>6000</v>
+      </c>
+      <c r="L10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R10">
+        <v>567</v>
+      </c>
+      <c r="S10">
+        <v>567</v>
+      </c>
+      <c r="T10" t="s">
+        <v>41</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10" t="s">
+        <v>43</v>
+      </c>
+      <c r="W10" t="s">
+        <v>43</v>
+      </c>
+      <c r="X10">
+        <v>3560</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA10">
+        <v>2018.52</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>1500</v>
+      </c>
+      <c r="K11">
+        <v>3000</v>
+      </c>
+      <c r="L11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>64</v>
+      </c>
+      <c r="R11">
+        <v>212</v>
+      </c>
+      <c r="S11">
+        <v>212</v>
+      </c>
+      <c r="T11" t="s">
+        <v>41</v>
+      </c>
+      <c r="U11">
+        <v>2</v>
+      </c>
+      <c r="V11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X11">
+        <v>2170</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA11">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>1500</v>
+      </c>
+      <c r="K12">
+        <v>3000</v>
+      </c>
+      <c r="L12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" t="s">
+        <v>81</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" t="s">
+        <v>82</v>
+      </c>
+      <c r="P12" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>64</v>
+      </c>
+      <c r="R12">
+        <v>1014</v>
+      </c>
+      <c r="S12">
+        <v>1014</v>
+      </c>
+      <c r="T12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" t="s">
+        <v>43</v>
+      </c>
+      <c r="X12">
+        <v>3540</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA12">
+        <v>3589.56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>1500</v>
+      </c>
+      <c r="K13">
+        <v>3000</v>
+      </c>
+      <c r="L13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N13" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>64</v>
+      </c>
+      <c r="R13">
+        <v>728</v>
+      </c>
+      <c r="S13">
+        <v>728</v>
+      </c>
+      <c r="T13" t="s">
+        <v>41</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13">
+        <v>3490</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA13">
+        <v>2540.72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14">
+        <v>1.5</v>
+      </c>
+      <c r="J14">
+        <v>1500</v>
+      </c>
+      <c r="K14">
+        <v>3000</v>
+      </c>
+      <c r="L14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" t="s">
+        <v>86</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>64</v>
+      </c>
+      <c r="R14">
+        <v>592</v>
+      </c>
+      <c r="S14">
+        <v>592</v>
+      </c>
+      <c r="T14" t="s">
+        <v>41</v>
+      </c>
+      <c r="U14">
+        <v>11</v>
+      </c>
+      <c r="V14" t="s">
+        <v>43</v>
+      </c>
+      <c r="W14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X14">
+        <v>3490</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA14">
+        <v>2066.08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15">
+        <v>2.5</v>
+      </c>
+      <c r="J15">
+        <v>1500</v>
+      </c>
+      <c r="K15">
+        <v>3000</v>
+      </c>
+      <c r="L15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>64</v>
+      </c>
+      <c r="R15">
+        <v>540</v>
+      </c>
+      <c r="S15">
+        <v>540</v>
+      </c>
+      <c r="T15" t="s">
+        <v>41</v>
+      </c>
+      <c r="U15">
+        <v>6</v>
+      </c>
+      <c r="V15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" t="s">
+        <v>43</v>
+      </c>
+      <c r="X15">
+        <v>3540</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA15">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>2000</v>
+      </c>
+      <c r="K16">
+        <v>4000</v>
+      </c>
+      <c r="L16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>64</v>
+      </c>
+      <c r="R16">
+        <v>126</v>
+      </c>
+      <c r="S16">
+        <v>126</v>
+      </c>
+      <c r="T16" t="s">
+        <v>41</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
+        <v>43</v>
+      </c>
+      <c r="W16" t="s">
+        <v>43</v>
+      </c>
+      <c r="X16">
+        <v>2190</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA16">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
+        <v>2000</v>
+      </c>
+      <c r="K17">
+        <v>4000</v>
+      </c>
+      <c r="L17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>64</v>
+      </c>
+      <c r="R17">
+        <v>315</v>
+      </c>
+      <c r="S17">
+        <v>315</v>
+      </c>
+      <c r="T17" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W17" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17">
+        <v>3560</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA17">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <v>2000</v>
+      </c>
+      <c r="K18">
+        <v>4000</v>
+      </c>
+      <c r="L18" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>64</v>
+      </c>
+      <c r="R18">
+        <v>189</v>
+      </c>
+      <c r="S18">
+        <v>189</v>
+      </c>
+      <c r="T18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X18">
+        <v>2190</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA18">
+        <v>413.91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19">
+        <v>2.5</v>
+      </c>
+      <c r="J19">
+        <v>1000</v>
+      </c>
+      <c r="K19">
+        <v>2000</v>
+      </c>
+      <c r="L19" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>64</v>
+      </c>
+      <c r="R19">
+        <v>312</v>
+      </c>
+      <c r="S19">
+        <v>312</v>
+      </c>
+      <c r="T19" t="s">
+        <v>41</v>
+      </c>
+      <c r="U19">
+        <v>8</v>
+      </c>
+      <c r="V19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" t="s">
+        <v>43</v>
+      </c>
+      <c r="X19">
+        <v>2220</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA19">
+        <v>692.64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" t="s">
+        <v>63</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1000</v>
+      </c>
+      <c r="L20" t="s">
+        <v>98</v>
+      </c>
+      <c r="M20" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" t="s">
+        <v>37</v>
+      </c>
+      <c r="O20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P20" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>64</v>
+      </c>
+      <c r="R20">
+        <v>2560</v>
+      </c>
+      <c r="S20">
+        <v>2560</v>
+      </c>
+      <c r="T20" t="s">
+        <v>41</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20">
+        <v>2270</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA20">
+        <v>5811.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>98</v>
+      </c>
+      <c r="M21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" t="s">
+        <v>37</v>
+      </c>
+      <c r="O21" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>64</v>
+      </c>
+      <c r="R21">
+        <v>3075</v>
+      </c>
+      <c r="S21">
+        <v>3075</v>
+      </c>
+      <c r="T21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21">
+        <v>2270</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>6980.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22">
+        <v>1000</v>
+      </c>
+      <c r="K22">
+        <v>2000</v>
+      </c>
+      <c r="L22" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>64</v>
+      </c>
+      <c r="R22">
+        <v>394</v>
+      </c>
+      <c r="S22">
+        <v>394</v>
+      </c>
+      <c r="T22" t="s">
+        <v>41</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>43</v>
+      </c>
+      <c r="X22">
+        <v>2020</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" t="s">
+        <v>63</v>
+      </c>
+      <c r="I23">
+        <v>0.8</v>
+      </c>
+      <c r="J23">
+        <v>1000</v>
+      </c>
+      <c r="K23">
+        <v>2000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>64</v>
+      </c>
+      <c r="R23">
+        <v>176</v>
+      </c>
+      <c r="S23">
+        <v>176</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23">
+        <v>14</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23">
+        <v>2270</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA23">
+        <v>399.52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <v>1250</v>
+      </c>
+      <c r="K24">
+        <v>2500</v>
+      </c>
+      <c r="L24" t="s">
+        <v>36</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>64</v>
+      </c>
+      <c r="R24">
+        <v>322</v>
+      </c>
+      <c r="S24">
+        <v>322</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>1370</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" t="s">
+        <v>63</v>
+      </c>
+      <c r="I25">
+        <v>0.8</v>
+      </c>
+      <c r="J25">
+        <v>1250</v>
+      </c>
+      <c r="K25">
+        <v>2500</v>
+      </c>
+      <c r="L25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" t="s">
+        <v>109</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>82</v>
+      </c>
+      <c r="P25" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>64</v>
+      </c>
+      <c r="R25">
+        <v>157</v>
+      </c>
+      <c r="S25">
+        <v>157</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>8</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>2220</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>348.54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" t="s">
+        <v>63</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>1250</v>
+      </c>
+      <c r="K26">
+        <v>2500</v>
+      </c>
+      <c r="L26" t="s">
+        <v>36</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>64</v>
+      </c>
+      <c r="R26">
+        <v>340</v>
+      </c>
+      <c r="S26">
+        <v>340</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>7</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>1370</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" t="s">
+        <v>63</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>2000</v>
+      </c>
+      <c r="K27">
+        <v>6000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>64</v>
+      </c>
+      <c r="R27">
+        <v>283</v>
+      </c>
+      <c r="S27">
+        <v>283</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>3560</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>1007.48</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" t="s">
+        <v>69</v>
+      </c>
+      <c r="H28" t="s">
+        <v>63</v>
+      </c>
+      <c r="I28">
+        <v>6</v>
+      </c>
+      <c r="J28">
+        <v>1500</v>
+      </c>
+      <c r="K28">
+        <v>3000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>64</v>
+      </c>
+      <c r="R28">
+        <v>212</v>
+      </c>
+      <c r="S28">
+        <v>212</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>3490</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" t="s">
+        <v>63</v>
+      </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
+      <c r="J29">
+        <v>1250</v>
+      </c>
+      <c r="K29">
+        <v>2500</v>
+      </c>
+      <c r="L29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>64</v>
+      </c>
+      <c r="R29">
+        <v>394</v>
+      </c>
+      <c r="S29">
+        <v>394</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>3490</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30">
+        <v>2000</v>
+      </c>
+      <c r="K30">
+        <v>6000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>64</v>
+      </c>
+      <c r="R30">
+        <v>472</v>
+      </c>
+      <c r="S30">
+        <v>472</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>2190</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>1500</v>
+      </c>
+      <c r="K31">
+        <v>3000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" t="s">
+        <v>86</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>64</v>
+      </c>
+      <c r="R31">
+        <v>970</v>
+      </c>
+      <c r="S31">
+        <v>970</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>13</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>3490</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" t="s">
+        <v>63</v>
+      </c>
+      <c r="I32">
+        <v>2.5</v>
+      </c>
+      <c r="J32">
+        <v>1500</v>
+      </c>
+      <c r="K32">
+        <v>3000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>64</v>
+      </c>
+      <c r="R32">
+        <v>526</v>
+      </c>
+      <c r="S32">
+        <v>526</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>6</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>3540</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" t="s">
+        <v>106</v>
+      </c>
+      <c r="H33" t="s">
+        <v>63</v>
+      </c>
+      <c r="I33">
+        <v>5</v>
+      </c>
+      <c r="J33">
+        <v>1500</v>
+      </c>
+      <c r="K33">
+        <v>3000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>64</v>
+      </c>
+      <c r="R33">
+        <v>354</v>
+      </c>
+      <c r="S33">
+        <v>354</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>2</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>1170</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" t="s">
+        <v>63</v>
+      </c>
+      <c r="I34">
+        <v>4</v>
+      </c>
+      <c r="J34">
+        <v>1500</v>
+      </c>
+      <c r="K34">
+        <v>3000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>64</v>
+      </c>
+      <c r="R34">
+        <v>142</v>
+      </c>
+      <c r="S34">
+        <v>142</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>2170</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35" t="s">
+        <v>63</v>
+      </c>
+      <c r="I35">
+        <v>4</v>
+      </c>
+      <c r="J35">
+        <v>1500</v>
+      </c>
+      <c r="K35">
+        <v>3000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>64</v>
+      </c>
+      <c r="R35">
+        <v>142</v>
+      </c>
+      <c r="S35">
+        <v>142</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>2170</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" t="s">
+        <v>69</v>
+      </c>
+      <c r="H36" t="s">
+        <v>63</v>
+      </c>
+      <c r="I36">
+        <v>1.5</v>
+      </c>
+      <c r="J36">
+        <v>1250</v>
+      </c>
+      <c r="L36" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>64</v>
+      </c>
+      <c r="R36">
+        <v>1275</v>
+      </c>
+      <c r="S36">
+        <v>1275</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>3590</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" t="s">
+        <v>63</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>1250</v>
+      </c>
+      <c r="K37">
+        <v>2500</v>
+      </c>
+      <c r="L37" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>64</v>
+      </c>
+      <c r="R37">
+        <v>49</v>
+      </c>
+      <c r="S37">
+        <v>49</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>2</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>2170</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38" t="s">
+        <v>63</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>1250</v>
+      </c>
+      <c r="K38">
+        <v>2500</v>
+      </c>
+      <c r="L38" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>64</v>
+      </c>
+      <c r="R38">
+        <v>49</v>
+      </c>
+      <c r="S38">
+        <v>49</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>2</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>2170</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>133</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39" t="s">
+        <v>63</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>1500</v>
+      </c>
+      <c r="K39">
+        <v>3000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>64</v>
+      </c>
+      <c r="R39">
+        <v>210</v>
+      </c>
+      <c r="S39">
+        <v>210</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>2</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>2170</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>135</v>
+      </c>
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40" t="s">
+        <v>61</v>
+      </c>
+      <c r="G40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" t="s">
+        <v>63</v>
+      </c>
+      <c r="I40">
+        <v>6</v>
+      </c>
+      <c r="J40">
+        <v>1250</v>
+      </c>
+      <c r="K40">
+        <v>2500</v>
+      </c>
+      <c r="L40" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>64</v>
+      </c>
+      <c r="R40">
+        <v>148</v>
+      </c>
+      <c r="S40">
+        <v>148</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>2170</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>321.16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" t="s">
+        <v>138</v>
+      </c>
+      <c r="E41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F41" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" t="s">
+        <v>63</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41">
+        <v>1500</v>
+      </c>
+      <c r="K41">
+        <v>3000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" t="s">
+        <v>139</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>82</v>
+      </c>
+      <c r="P41" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>64</v>
+      </c>
+      <c r="R41">
+        <v>283</v>
+      </c>
+      <c r="S41">
+        <v>283</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>2170</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" t="s">
+        <v>61</v>
+      </c>
+      <c r="G42" t="s">
+        <v>49</v>
+      </c>
+      <c r="H42" t="s">
+        <v>63</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>1500</v>
+      </c>
+      <c r="K42">
+        <v>3000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" t="s">
+        <v>139</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>82</v>
+      </c>
+      <c r="P42" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>64</v>
+      </c>
+      <c r="R42">
+        <v>283</v>
+      </c>
+      <c r="S42">
+        <v>283</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>2170</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" t="s">
+        <v>61</v>
+      </c>
+      <c r="G43" t="s">
+        <v>106</v>
+      </c>
+      <c r="H43" t="s">
+        <v>63</v>
+      </c>
+      <c r="I43">
+        <v>3</v>
+      </c>
+      <c r="J43">
+        <v>1500</v>
+      </c>
+      <c r="K43">
+        <v>3000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" t="s">
+        <v>37</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>64</v>
+      </c>
+      <c r="R43">
+        <v>212</v>
+      </c>
+      <c r="S43">
+        <v>212</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>2</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>1320</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" t="s">
+        <v>61</v>
+      </c>
+      <c r="G44" t="s">
+        <v>49</v>
+      </c>
+      <c r="H44" t="s">
+        <v>63</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>1500</v>
+      </c>
+      <c r="K44">
+        <v>3000</v>
+      </c>
+      <c r="L44" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>64</v>
+      </c>
+      <c r="R44">
+        <v>212</v>
+      </c>
+      <c r="S44">
+        <v>212</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>6</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>2170</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" t="s">
+        <v>61</v>
+      </c>
+      <c r="G45" t="s">
+        <v>49</v>
+      </c>
+      <c r="H45" t="s">
+        <v>63</v>
+      </c>
+      <c r="I45">
+        <v>6</v>
+      </c>
+      <c r="J45">
+        <v>1000</v>
+      </c>
+      <c r="K45">
+        <v>2000</v>
+      </c>
+      <c r="L45" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>64</v>
+      </c>
+      <c r="R45">
+        <v>567</v>
+      </c>
+      <c r="S45">
+        <v>567</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>6</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>2220</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" t="s">
+        <v>146</v>
+      </c>
+      <c r="E46" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" t="s">
+        <v>61</v>
+      </c>
+      <c r="G46" t="s">
+        <v>49</v>
+      </c>
+      <c r="H46" t="s">
+        <v>63</v>
+      </c>
+      <c r="I46">
+        <v>6</v>
+      </c>
+      <c r="J46">
+        <v>1000</v>
+      </c>
+      <c r="K46">
+        <v>2000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>64</v>
+      </c>
+      <c r="R46">
+        <v>567</v>
+      </c>
+      <c r="S46">
+        <v>567</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>6</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>2220</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47" t="s">
+        <v>106</v>
+      </c>
+      <c r="H47" t="s">
+        <v>63</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>1500</v>
+      </c>
+      <c r="K47">
+        <v>3000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>64</v>
+      </c>
+      <c r="R47">
+        <v>319</v>
+      </c>
+      <c r="S47">
+        <v>319</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>3</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>1370</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" t="s">
+        <v>150</v>
+      </c>
+      <c r="E48" t="s">
+        <v>48</v>
+      </c>
+      <c r="F48" t="s">
+        <v>61</v>
+      </c>
+      <c r="G48" t="s">
+        <v>49</v>
+      </c>
+      <c r="H48" t="s">
+        <v>63</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>1250</v>
+      </c>
+      <c r="K48">
+        <v>2500</v>
+      </c>
+      <c r="L48" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>64</v>
+      </c>
+      <c r="R48">
+        <v>197</v>
+      </c>
+      <c r="S48">
+        <v>197</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>4</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>2170</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>151</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" t="s">
+        <v>150</v>
+      </c>
+      <c r="E49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" t="s">
+        <v>61</v>
+      </c>
+      <c r="G49" t="s">
+        <v>49</v>
+      </c>
+      <c r="H49" t="s">
+        <v>63</v>
+      </c>
+      <c r="I49">
+        <v>2</v>
+      </c>
+      <c r="J49">
+        <v>1250</v>
+      </c>
+      <c r="K49">
+        <v>2500</v>
+      </c>
+      <c r="L49" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>64</v>
+      </c>
+      <c r="R49">
+        <v>246</v>
+      </c>
+      <c r="S49">
+        <v>246</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>5</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>2170</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" t="s">
+        <v>103</v>
+      </c>
+      <c r="E50" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" t="s">
+        <v>61</v>
+      </c>
+      <c r="G50" t="s">
+        <v>49</v>
+      </c>
+      <c r="H50" t="s">
+        <v>63</v>
+      </c>
+      <c r="I50">
+        <v>0.8</v>
+      </c>
+      <c r="J50">
+        <v>1000</v>
+      </c>
+      <c r="K50">
+        <v>2000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>64</v>
+      </c>
+      <c r="R50">
+        <v>1498</v>
+      </c>
+      <c r="S50">
+        <v>1498</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>2370</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" t="s">
+        <v>48</v>
+      </c>
+      <c r="F51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51" t="s">
+        <v>49</v>
+      </c>
+      <c r="H51" t="s">
+        <v>63</v>
+      </c>
+      <c r="I51">
+        <v>0.8</v>
+      </c>
+      <c r="J51">
+        <v>1000</v>
+      </c>
+      <c r="K51">
+        <v>2000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>64</v>
+      </c>
+      <c r="R51">
+        <v>1498</v>
+      </c>
+      <c r="S51">
+        <v>1498</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>1</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>2370</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" t="s">
+        <v>48</v>
+      </c>
+      <c r="F52" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52" t="s">
+        <v>49</v>
+      </c>
+      <c r="H52" t="s">
+        <v>63</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
+      </c>
+      <c r="J52">
+        <v>1500</v>
+      </c>
+      <c r="K52">
+        <v>3000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>64</v>
+      </c>
+      <c r="R52">
+        <v>354</v>
+      </c>
+      <c r="S52">
+        <v>354</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>1</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>2220</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53" t="s">
+        <v>61</v>
+      </c>
+      <c r="G53" t="s">
+        <v>49</v>
+      </c>
+      <c r="H53" t="s">
+        <v>63</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+      <c r="J53">
+        <v>2000</v>
+      </c>
+      <c r="K53">
+        <v>4000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>64</v>
+      </c>
+      <c r="R53">
+        <v>126</v>
+      </c>
+      <c r="S53">
+        <v>126</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>1</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>2190</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" t="s">
+        <v>48</v>
+      </c>
+      <c r="F54" t="s">
+        <v>61</v>
+      </c>
+      <c r="G54" t="s">
+        <v>69</v>
+      </c>
+      <c r="H54" t="s">
+        <v>63</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+      <c r="J54">
+        <v>1500</v>
+      </c>
+      <c r="K54">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" t="s">
+        <v>86</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>64</v>
+      </c>
+      <c r="R54">
+        <v>1010</v>
+      </c>
+      <c r="S54">
+        <v>1010</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>14</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>3540</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" t="s">
+        <v>159</v>
+      </c>
+      <c r="E55" t="s">
+        <v>48</v>
+      </c>
+      <c r="F55" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" t="s">
+        <v>69</v>
+      </c>
+      <c r="H55" t="s">
+        <v>63</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55">
+        <v>1500</v>
+      </c>
+      <c r="K55">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>64</v>
+      </c>
+      <c r="R55">
+        <v>283</v>
+      </c>
+      <c r="S55">
+        <v>283</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>4</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>3540</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" t="s">
+        <v>161</v>
+      </c>
+      <c r="E56" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" t="s">
+        <v>162</v>
+      </c>
+      <c r="H56" t="s">
+        <v>63</v>
+      </c>
+      <c r="I56">
+        <v>0.8</v>
+      </c>
+      <c r="J56">
+        <v>1000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>36</v>
+      </c>
+      <c r="M56" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>163</v>
+      </c>
+      <c r="P56" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>64</v>
+      </c>
+      <c r="R56">
+        <v>1585</v>
+      </c>
+      <c r="S56">
+        <v>1585</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>1</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>2370</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57" t="s">
+        <v>165</v>
+      </c>
+      <c r="E57" t="s">
+        <v>48</v>
+      </c>
+      <c r="F57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H57" t="s">
+        <v>63</v>
+      </c>
+      <c r="I57">
+        <v>1.5</v>
+      </c>
+      <c r="J57">
+        <v>1500</v>
+      </c>
+      <c r="K57">
+        <v>3000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>64</v>
+      </c>
+      <c r="R57">
+        <v>212</v>
+      </c>
+      <c r="S57">
+        <v>212</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>1</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>1320</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>166</v>
+      </c>
+      <c r="B58" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" t="s">
+        <v>59</v>
+      </c>
+      <c r="D58" t="s">
+        <v>167</v>
+      </c>
+      <c r="E58" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" t="s">
+        <v>61</v>
+      </c>
+      <c r="G58" t="s">
+        <v>49</v>
+      </c>
+      <c r="H58" t="s">
+        <v>63</v>
+      </c>
+      <c r="I58">
+        <v>3</v>
+      </c>
+      <c r="J58">
+        <v>1250</v>
+      </c>
+      <c r="K58">
+        <v>2500</v>
+      </c>
+      <c r="L58" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>64</v>
+      </c>
+      <c r="R58">
+        <v>74</v>
+      </c>
+      <c r="S58">
+        <v>74</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>1</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>2170</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>160.58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>168</v>
+      </c>
+      <c r="B59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" t="s">
+        <v>68</v>
+      </c>
+      <c r="E59" t="s">
+        <v>48</v>
+      </c>
+      <c r="F59" t="s">
+        <v>61</v>
+      </c>
+      <c r="G59" t="s">
+        <v>69</v>
+      </c>
+      <c r="H59" t="s">
+        <v>63</v>
+      </c>
+      <c r="I59">
+        <v>2.5</v>
+      </c>
+      <c r="J59">
+        <v>1500</v>
+      </c>
+      <c r="K59">
+        <v>3000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>64</v>
+      </c>
+      <c r="R59">
+        <v>540</v>
+      </c>
+      <c r="S59">
+        <v>540</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>6</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>3540</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" t="s">
+        <v>59</v>
+      </c>
+      <c r="D60" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60" t="s">
+        <v>48</v>
+      </c>
+      <c r="F60" t="s">
+        <v>61</v>
+      </c>
+      <c r="G60" t="s">
+        <v>69</v>
+      </c>
+      <c r="H60" t="s">
+        <v>63</v>
+      </c>
+      <c r="I60">
+        <v>2.5</v>
+      </c>
+      <c r="J60">
+        <v>1500</v>
+      </c>
+      <c r="K60">
+        <v>3000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>64</v>
+      </c>
+      <c r="R60">
+        <v>520</v>
+      </c>
+      <c r="S60">
+        <v>520</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>6</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>3540</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61" t="s">
+        <v>69</v>
+      </c>
+      <c r="H61" t="s">
+        <v>63</v>
+      </c>
+      <c r="I61">
+        <v>2.5</v>
+      </c>
+      <c r="J61">
+        <v>1500</v>
+      </c>
+      <c r="K61">
+        <v>3000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>64</v>
+      </c>
+      <c r="R61">
+        <v>530</v>
+      </c>
+      <c r="S61">
+        <v>530</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>6</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>3540</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" t="s">
+        <v>67</v>
+      </c>
+      <c r="C62" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" t="s">
+        <v>48</v>
+      </c>
+      <c r="F62" t="s">
+        <v>61</v>
+      </c>
+      <c r="G62" t="s">
+        <v>69</v>
+      </c>
+      <c r="H62" t="s">
+        <v>63</v>
+      </c>
+      <c r="I62">
+        <v>2.5</v>
+      </c>
+      <c r="J62">
+        <v>1500</v>
+      </c>
+      <c r="K62">
+        <v>3000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>64</v>
+      </c>
+      <c r="R62">
+        <v>526</v>
+      </c>
+      <c r="S62">
+        <v>526</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>6</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>3540</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>172</v>
+      </c>
+      <c r="B63" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F63" t="s">
+        <v>61</v>
+      </c>
+      <c r="G63" t="s">
+        <v>69</v>
+      </c>
+      <c r="H63" t="s">
+        <v>63</v>
+      </c>
+      <c r="I63">
+        <v>3</v>
+      </c>
+      <c r="J63">
+        <v>1500</v>
+      </c>
+      <c r="K63">
+        <v>3000</v>
+      </c>
+      <c r="L63" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>64</v>
+      </c>
+      <c r="R63">
+        <v>212</v>
+      </c>
+      <c r="S63">
+        <v>212</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>1</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>3490</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>174</v>
+      </c>
+      <c r="B64" t="s">
+        <v>58</v>
+      </c>
+      <c r="C64" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" t="s">
+        <v>61</v>
+      </c>
+      <c r="G64" t="s">
+        <v>69</v>
+      </c>
+      <c r="H64" t="s">
+        <v>63</v>
+      </c>
+      <c r="I64">
+        <v>3</v>
+      </c>
+      <c r="J64">
+        <v>1500</v>
+      </c>
+      <c r="K64">
+        <v>3000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>64</v>
+      </c>
+      <c r="R64">
+        <v>212</v>
+      </c>
+      <c r="S64">
+        <v>212</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>1</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>3490</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>175</v>
+      </c>
+      <c r="B65" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" t="s">
+        <v>176</v>
+      </c>
+      <c r="E65" t="s">
+        <v>48</v>
+      </c>
+      <c r="F65" t="s">
+        <v>61</v>
+      </c>
+      <c r="G65" t="s">
+        <v>49</v>
+      </c>
+      <c r="H65" t="s">
+        <v>63</v>
+      </c>
+      <c r="I65">
+        <v>4</v>
+      </c>
+      <c r="J65">
+        <v>1000</v>
+      </c>
+      <c r="K65">
+        <v>2000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
         <v>55</v>
       </c>
-      <c r="Q5" t="s">
-        <v>59</v>
-      </c>
-      <c r="R5">
-        <v>6471</v>
-      </c>
-      <c r="S5">
-        <v>6531</v>
-      </c>
-      <c r="T5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U5">
+      <c r="Q65" t="s">
+        <v>64</v>
+      </c>
+      <c r="R65">
+        <v>315</v>
+      </c>
+      <c r="S65">
+        <v>315</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>5</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>2220</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>177</v>
+      </c>
+      <c r="B66" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" t="s">
+        <v>59</v>
+      </c>
+      <c r="D66" t="s">
+        <v>178</v>
+      </c>
+      <c r="E66" t="s">
+        <v>48</v>
+      </c>
+      <c r="F66" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66" t="s">
+        <v>49</v>
+      </c>
+      <c r="H66" t="s">
+        <v>63</v>
+      </c>
+      <c r="I66">
+        <v>1.5</v>
+      </c>
+      <c r="J66">
+        <v>1250</v>
+      </c>
+      <c r="K66">
+        <v>2500</v>
+      </c>
+      <c r="L66" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>64</v>
+      </c>
+      <c r="R66">
+        <v>295</v>
+      </c>
+      <c r="S66">
+        <v>295</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>8</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>2220</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>654.9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>179</v>
+      </c>
+      <c r="B67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" t="s">
+        <v>101</v>
+      </c>
+      <c r="E67" t="s">
+        <v>48</v>
+      </c>
+      <c r="F67" t="s">
+        <v>61</v>
+      </c>
+      <c r="G67" t="s">
+        <v>49</v>
+      </c>
+      <c r="H67" t="s">
+        <v>63</v>
+      </c>
+      <c r="I67">
+        <v>5</v>
+      </c>
+      <c r="J67">
+        <v>1000</v>
+      </c>
+      <c r="K67">
+        <v>2000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>54</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>64</v>
+      </c>
+      <c r="R67">
+        <v>944</v>
+      </c>
+      <c r="S67">
+        <v>944</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
         <v>1</v>
       </c>
-      <c r="V5" t="s">
-        <v>60</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5">
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>2020</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>180</v>
+      </c>
+      <c r="B68" t="s">
+        <v>58</v>
+      </c>
+      <c r="C68" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" t="s">
+        <v>146</v>
+      </c>
+      <c r="E68" t="s">
+        <v>48</v>
+      </c>
+      <c r="F68" t="s">
+        <v>61</v>
+      </c>
+      <c r="G68" t="s">
+        <v>49</v>
+      </c>
+      <c r="H68" t="s">
+        <v>63</v>
+      </c>
+      <c r="I68">
+        <v>6</v>
+      </c>
+      <c r="J68">
+        <v>1000</v>
+      </c>
+      <c r="K68">
+        <v>2000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>50</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>64</v>
+      </c>
+      <c r="R68">
+        <v>189</v>
+      </c>
+      <c r="S68">
+        <v>189</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>2</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
         <v>2170</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5">
-        <v>14042.07</v>
-      </c>
-      <c r="AB5" t="b">
-        <v>0</v>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>410.13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>181</v>
+      </c>
+      <c r="B69" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" t="s">
+        <v>182</v>
+      </c>
+      <c r="E69" t="s">
+        <v>48</v>
+      </c>
+      <c r="F69" t="s">
+        <v>61</v>
+      </c>
+      <c r="G69" t="s">
+        <v>49</v>
+      </c>
+      <c r="H69" t="s">
+        <v>63</v>
+      </c>
+      <c r="I69">
+        <v>1.5</v>
+      </c>
+      <c r="J69">
+        <v>1000</v>
+      </c>
+      <c r="K69">
+        <v>2000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>64</v>
+      </c>
+      <c r="R69">
+        <v>260</v>
+      </c>
+      <c r="S69">
+        <v>260</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>11</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>2220</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>577.2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>183</v>
+      </c>
+      <c r="B70" t="s">
+        <v>67</v>
+      </c>
+      <c r="C70" t="s">
+        <v>59</v>
+      </c>
+      <c r="D70" t="s">
+        <v>184</v>
+      </c>
+      <c r="E70" t="s">
+        <v>48</v>
+      </c>
+      <c r="F70" t="s">
+        <v>61</v>
+      </c>
+      <c r="G70" t="s">
+        <v>69</v>
+      </c>
+      <c r="H70" t="s">
+        <v>63</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>1500</v>
+      </c>
+      <c r="K70">
+        <v>3000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" t="s">
+        <v>86</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>38</v>
+      </c>
+      <c r="P70" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>64</v>
+      </c>
+      <c r="R70">
+        <v>1224</v>
+      </c>
+      <c r="S70">
+        <v>1224</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>34</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>3540</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>185</v>
+      </c>
+      <c r="B71" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" t="s">
+        <v>59</v>
+      </c>
+      <c r="D71" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" t="s">
+        <v>48</v>
+      </c>
+      <c r="F71" t="s">
+        <v>61</v>
+      </c>
+      <c r="G71" t="s">
+        <v>49</v>
+      </c>
+      <c r="H71" t="s">
+        <v>63</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+      <c r="J71">
+        <v>1250</v>
+      </c>
+      <c r="K71">
+        <v>2500</v>
+      </c>
+      <c r="L71" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>64</v>
+      </c>
+      <c r="R71">
+        <v>197</v>
+      </c>
+      <c r="S71">
+        <v>197</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>4</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>2170</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>186</v>
+      </c>
+      <c r="B72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" t="s">
+        <v>59</v>
+      </c>
+      <c r="D72" t="s">
+        <v>187</v>
+      </c>
+      <c r="E72" t="s">
+        <v>48</v>
+      </c>
+      <c r="F72" t="s">
+        <v>61</v>
+      </c>
+      <c r="G72" t="s">
+        <v>69</v>
+      </c>
+      <c r="H72" t="s">
+        <v>63</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1500</v>
+      </c>
+      <c r="K72">
+        <v>3000</v>
+      </c>
+      <c r="L72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>64</v>
+      </c>
+      <c r="R72">
+        <v>35</v>
+      </c>
+      <c r="S72">
+        <v>35</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>1</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>3490</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>188</v>
+      </c>
+      <c r="B73" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73" t="s">
+        <v>59</v>
+      </c>
+      <c r="D73" t="s">
+        <v>187</v>
+      </c>
+      <c r="E73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F73" t="s">
+        <v>61</v>
+      </c>
+      <c r="G73" t="s">
+        <v>69</v>
+      </c>
+      <c r="H73" t="s">
+        <v>63</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73">
+        <v>1500</v>
+      </c>
+      <c r="K73">
+        <v>3000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>64</v>
+      </c>
+      <c r="R73">
+        <v>177</v>
+      </c>
+      <c r="S73">
+        <v>177</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>5</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>3490</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>617.73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>189</v>
+      </c>
+      <c r="B74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C74" t="s">
+        <v>59</v>
+      </c>
+      <c r="D74" t="s">
+        <v>190</v>
+      </c>
+      <c r="E74" t="s">
+        <v>48</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" t="s">
+        <v>191</v>
+      </c>
+      <c r="H74" t="s">
+        <v>63</v>
+      </c>
+      <c r="I74">
+        <v>0.6</v>
+      </c>
+      <c r="J74">
+        <v>1000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>36</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>64</v>
+      </c>
+      <c r="R74">
+        <v>745</v>
+      </c>
+      <c r="S74">
+        <v>745</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>1</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>2290</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>1706.05</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>192</v>
+      </c>
+      <c r="B75" t="s">
+        <v>67</v>
+      </c>
+      <c r="C75" t="s">
+        <v>59</v>
+      </c>
+      <c r="D75" t="s">
+        <v>193</v>
+      </c>
+      <c r="E75" t="s">
+        <v>48</v>
+      </c>
+      <c r="F75" t="s">
+        <v>61</v>
+      </c>
+      <c r="G75" t="s">
+        <v>106</v>
+      </c>
+      <c r="H75" t="s">
+        <v>63</v>
+      </c>
+      <c r="I75">
+        <v>1.5</v>
+      </c>
+      <c r="J75">
+        <v>1500</v>
+      </c>
+      <c r="K75">
+        <v>3000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>36</v>
+      </c>
+      <c r="M75" t="s">
+        <v>86</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>64</v>
+      </c>
+      <c r="R75">
+        <v>916</v>
+      </c>
+      <c r="S75">
+        <v>916</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>18</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>1320</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>194</v>
+      </c>
+      <c r="B76" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" t="s">
+        <v>59</v>
+      </c>
+      <c r="D76" t="s">
+        <v>173</v>
+      </c>
+      <c r="E76" t="s">
+        <v>48</v>
+      </c>
+      <c r="F76" t="s">
+        <v>61</v>
+      </c>
+      <c r="G76" t="s">
+        <v>69</v>
+      </c>
+      <c r="H76" t="s">
+        <v>63</v>
+      </c>
+      <c r="I76">
+        <v>3</v>
+      </c>
+      <c r="J76">
+        <v>1500</v>
+      </c>
+      <c r="K76">
+        <v>3000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>64</v>
+      </c>
+      <c r="R76">
+        <v>319</v>
+      </c>
+      <c r="S76">
+        <v>319</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>1</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>3540</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>195</v>
+      </c>
+      <c r="B77" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" t="s">
+        <v>59</v>
+      </c>
+      <c r="D77" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" t="s">
+        <v>48</v>
+      </c>
+      <c r="F77" t="s">
+        <v>61</v>
+      </c>
+      <c r="G77" t="s">
+        <v>69</v>
+      </c>
+      <c r="H77" t="s">
+        <v>63</v>
+      </c>
+      <c r="I77">
+        <v>3</v>
+      </c>
+      <c r="J77">
+        <v>1500</v>
+      </c>
+      <c r="K77">
+        <v>3000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>64</v>
+      </c>
+      <c r="R77">
+        <v>212</v>
+      </c>
+      <c r="S77">
+        <v>212</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>1</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>3490</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>196</v>
+      </c>
+      <c r="B78" t="s">
+        <v>58</v>
+      </c>
+      <c r="C78" t="s">
+        <v>59</v>
+      </c>
+      <c r="D78" t="s">
+        <v>173</v>
+      </c>
+      <c r="E78" t="s">
+        <v>48</v>
+      </c>
+      <c r="F78" t="s">
+        <v>61</v>
+      </c>
+      <c r="G78" t="s">
+        <v>69</v>
+      </c>
+      <c r="H78" t="s">
+        <v>63</v>
+      </c>
+      <c r="I78">
+        <v>3</v>
+      </c>
+      <c r="J78">
+        <v>1500</v>
+      </c>
+      <c r="K78">
+        <v>3000</v>
+      </c>
+      <c r="L78" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>64</v>
+      </c>
+      <c r="R78">
+        <v>212</v>
+      </c>
+      <c r="S78">
+        <v>212</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>1</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>3490</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>197</v>
+      </c>
+      <c r="B79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" t="s">
+        <v>59</v>
+      </c>
+      <c r="D79" t="s">
+        <v>173</v>
+      </c>
+      <c r="E79" t="s">
+        <v>48</v>
+      </c>
+      <c r="F79" t="s">
+        <v>61</v>
+      </c>
+      <c r="G79" t="s">
+        <v>69</v>
+      </c>
+      <c r="H79" t="s">
+        <v>63</v>
+      </c>
+      <c r="I79">
+        <v>3</v>
+      </c>
+      <c r="J79">
+        <v>1500</v>
+      </c>
+      <c r="K79">
+        <v>3000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>64</v>
+      </c>
+      <c r="R79">
+        <v>319</v>
+      </c>
+      <c r="S79">
+        <v>319</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>1</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>3540</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>198</v>
+      </c>
+      <c r="B80" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" t="s">
+        <v>59</v>
+      </c>
+      <c r="D80" t="s">
+        <v>199</v>
+      </c>
+      <c r="E80" t="s">
+        <v>48</v>
+      </c>
+      <c r="F80" t="s">
+        <v>61</v>
+      </c>
+      <c r="G80" t="s">
+        <v>49</v>
+      </c>
+      <c r="H80" t="s">
+        <v>63</v>
+      </c>
+      <c r="I80">
+        <v>4</v>
+      </c>
+      <c r="J80">
+        <v>1000</v>
+      </c>
+      <c r="K80">
+        <v>2000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>50</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>64</v>
+      </c>
+      <c r="R80">
+        <v>63</v>
+      </c>
+      <c r="S80">
+        <v>63</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>1</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>2170</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>136.71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>200</v>
+      </c>
+      <c r="B81" t="s">
+        <v>67</v>
+      </c>
+      <c r="C81" t="s">
+        <v>59</v>
+      </c>
+      <c r="D81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E81" t="s">
+        <v>48</v>
+      </c>
+      <c r="F81" t="s">
+        <v>61</v>
+      </c>
+      <c r="G81" t="s">
+        <v>49</v>
+      </c>
+      <c r="H81" t="s">
+        <v>63</v>
+      </c>
+      <c r="I81">
+        <v>1.2</v>
+      </c>
+      <c r="J81">
+        <v>1250</v>
+      </c>
+      <c r="K81">
+        <v>2500</v>
+      </c>
+      <c r="L81" t="s">
+        <v>50</v>
+      </c>
+      <c r="M81" t="s">
+        <v>86</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>64</v>
+      </c>
+      <c r="R81">
+        <v>568</v>
+      </c>
+      <c r="S81">
+        <v>568</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>19</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>2170</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>1232.56</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>202</v>
+      </c>
+      <c r="B82" t="s">
+        <v>67</v>
+      </c>
+      <c r="C82" t="s">
+        <v>59</v>
+      </c>
+      <c r="D82" t="s">
+        <v>203</v>
+      </c>
+      <c r="E82" t="s">
+        <v>48</v>
+      </c>
+      <c r="F82" t="s">
+        <v>61</v>
+      </c>
+      <c r="G82" t="s">
+        <v>49</v>
+      </c>
+      <c r="H82" t="s">
+        <v>63</v>
+      </c>
+      <c r="I82">
+        <v>1.2</v>
+      </c>
+      <c r="J82">
+        <v>1500</v>
+      </c>
+      <c r="K82">
+        <v>3000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>50</v>
+      </c>
+      <c r="M82" t="s">
+        <v>204</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>64</v>
+      </c>
+      <c r="R82">
+        <v>660</v>
+      </c>
+      <c r="S82">
+        <v>660</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>15</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>2170</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>1432.2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>205</v>
+      </c>
+      <c r="B83" t="s">
+        <v>58</v>
+      </c>
+      <c r="C83" t="s">
+        <v>59</v>
+      </c>
+      <c r="D83" t="s">
+        <v>206</v>
+      </c>
+      <c r="E83" t="s">
+        <v>48</v>
+      </c>
+      <c r="F83" t="s">
+        <v>61</v>
+      </c>
+      <c r="G83" t="s">
+        <v>106</v>
+      </c>
+      <c r="H83" t="s">
+        <v>63</v>
+      </c>
+      <c r="I83">
+        <v>1.5</v>
+      </c>
+      <c r="J83">
+        <v>1250</v>
+      </c>
+      <c r="K83">
+        <v>2500</v>
+      </c>
+      <c r="L83" t="s">
+        <v>50</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>64</v>
+      </c>
+      <c r="R83">
+        <v>148</v>
+      </c>
+      <c r="S83">
+        <v>148</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>4</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>1320</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>195.36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>207</v>
+      </c>
+      <c r="B84" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" t="s">
+        <v>59</v>
+      </c>
+      <c r="D84" t="s">
+        <v>206</v>
+      </c>
+      <c r="E84" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" t="s">
+        <v>61</v>
+      </c>
+      <c r="G84" t="s">
+        <v>106</v>
+      </c>
+      <c r="H84" t="s">
+        <v>63</v>
+      </c>
+      <c r="I84">
+        <v>1.5</v>
+      </c>
+      <c r="J84">
+        <v>1250</v>
+      </c>
+      <c r="K84">
+        <v>2500</v>
+      </c>
+      <c r="L84" t="s">
+        <v>50</v>
+      </c>
+      <c r="M84" t="s">
+        <v>37</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>64</v>
+      </c>
+      <c r="R84">
+        <v>148</v>
+      </c>
+      <c r="S84">
+        <v>148</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>4</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>1320</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>195.36</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>208</v>
+      </c>
+      <c r="B85" t="s">
+        <v>58</v>
+      </c>
+      <c r="C85" t="s">
+        <v>59</v>
+      </c>
+      <c r="D85" t="s">
+        <v>209</v>
+      </c>
+      <c r="E85" t="s">
+        <v>48</v>
+      </c>
+      <c r="F85" t="s">
+        <v>61</v>
+      </c>
+      <c r="G85" t="s">
+        <v>49</v>
+      </c>
+      <c r="H85" t="s">
+        <v>63</v>
+      </c>
+      <c r="I85">
+        <v>6</v>
+      </c>
+      <c r="J85">
+        <v>2000</v>
+      </c>
+      <c r="K85">
+        <v>4000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>50</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>64</v>
+      </c>
+      <c r="R85">
+        <v>756</v>
+      </c>
+      <c r="S85">
+        <v>756</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>2</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>2240</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>1693.44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>210</v>
+      </c>
+      <c r="B86" t="s">
+        <v>58</v>
+      </c>
+      <c r="C86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D86" t="s">
+        <v>144</v>
+      </c>
+      <c r="E86" t="s">
+        <v>48</v>
+      </c>
+      <c r="F86" t="s">
+        <v>61</v>
+      </c>
+      <c r="G86" t="s">
+        <v>49</v>
+      </c>
+      <c r="H86" t="s">
+        <v>63</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
+        <v>1500</v>
+      </c>
+      <c r="K86">
+        <v>3000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>50</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>64</v>
+      </c>
+      <c r="R86">
+        <v>35</v>
+      </c>
+      <c r="S86">
+        <v>35</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>1</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>2170</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>75.95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" t="s">
+        <v>58</v>
+      </c>
+      <c r="C87" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" t="s">
+        <v>144</v>
+      </c>
+      <c r="E87" t="s">
+        <v>48</v>
+      </c>
+      <c r="F87" t="s">
+        <v>61</v>
+      </c>
+      <c r="G87" t="s">
+        <v>49</v>
+      </c>
+      <c r="H87" t="s">
+        <v>63</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>1500</v>
+      </c>
+      <c r="K87">
+        <v>3000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>50</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>64</v>
+      </c>
+      <c r="R87">
+        <v>35</v>
+      </c>
+      <c r="S87">
+        <v>35</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>1</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>2170</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>75.95</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>212</v>
+      </c>
+      <c r="B88" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" t="s">
+        <v>59</v>
+      </c>
+      <c r="D88" t="s">
+        <v>213</v>
+      </c>
+      <c r="E88" t="s">
+        <v>48</v>
+      </c>
+      <c r="F88" t="s">
+        <v>61</v>
+      </c>
+      <c r="G88" t="s">
+        <v>191</v>
+      </c>
+      <c r="H88" t="s">
+        <v>63</v>
+      </c>
+      <c r="I88">
+        <v>2</v>
+      </c>
+      <c r="J88">
+        <v>1000</v>
+      </c>
+      <c r="K88">
+        <v>2000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>36</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>64</v>
+      </c>
+      <c r="R88">
+        <v>544</v>
+      </c>
+      <c r="S88">
+        <v>544</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>1</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>2220</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>1207.68</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>214</v>
+      </c>
+      <c r="B89" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" t="s">
+        <v>59</v>
+      </c>
+      <c r="D89" t="s">
+        <v>215</v>
+      </c>
+      <c r="E89" t="s">
+        <v>48</v>
+      </c>
+      <c r="F89" t="s">
+        <v>61</v>
+      </c>
+      <c r="G89" t="s">
+        <v>106</v>
+      </c>
+      <c r="H89" t="s">
+        <v>63</v>
+      </c>
+      <c r="I89">
+        <v>1.5</v>
+      </c>
+      <c r="J89">
+        <v>1250</v>
+      </c>
+      <c r="K89">
+        <v>2500</v>
+      </c>
+      <c r="L89" t="s">
+        <v>36</v>
+      </c>
+      <c r="M89" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>64</v>
+      </c>
+      <c r="R89">
+        <v>898</v>
+      </c>
+      <c r="S89">
+        <v>898</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>1</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>1370</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>1230.26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>216</v>
+      </c>
+      <c r="B90" t="s">
+        <v>67</v>
+      </c>
+      <c r="C90" t="s">
+        <v>59</v>
+      </c>
+      <c r="D90" t="s">
+        <v>217</v>
+      </c>
+      <c r="E90" t="s">
+        <v>48</v>
+      </c>
+      <c r="F90" t="s">
+        <v>61</v>
+      </c>
+      <c r="G90" t="s">
+        <v>49</v>
+      </c>
+      <c r="H90" t="s">
+        <v>63</v>
+      </c>
+      <c r="I90">
+        <v>1.5</v>
+      </c>
+      <c r="J90">
+        <v>1500</v>
+      </c>
+      <c r="K90">
+        <v>3000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>36</v>
+      </c>
+      <c r="M90" t="s">
+        <v>37</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>64</v>
+      </c>
+      <c r="R90">
+        <v>212</v>
+      </c>
+      <c r="S90">
+        <v>212</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>1</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>2170</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>218</v>
+      </c>
+      <c r="B91" t="s">
+        <v>67</v>
+      </c>
+      <c r="C91" t="s">
+        <v>59</v>
+      </c>
+      <c r="D91" t="s">
+        <v>217</v>
+      </c>
+      <c r="E91" t="s">
+        <v>48</v>
+      </c>
+      <c r="F91" t="s">
+        <v>61</v>
+      </c>
+      <c r="G91" t="s">
+        <v>49</v>
+      </c>
+      <c r="H91" t="s">
+        <v>63</v>
+      </c>
+      <c r="I91">
+        <v>1.5</v>
+      </c>
+      <c r="J91">
+        <v>1500</v>
+      </c>
+      <c r="K91">
+        <v>3000</v>
+      </c>
+      <c r="L91" t="s">
+        <v>36</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>64</v>
+      </c>
+      <c r="R91">
+        <v>278</v>
+      </c>
+      <c r="S91">
+        <v>278</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>1</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>2220</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>617.16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>219</v>
+      </c>
+      <c r="B92" t="s">
+        <v>67</v>
+      </c>
+      <c r="C92" t="s">
+        <v>59</v>
+      </c>
+      <c r="D92" t="s">
+        <v>220</v>
+      </c>
+      <c r="E92" t="s">
+        <v>48</v>
+      </c>
+      <c r="F92" t="s">
+        <v>61</v>
+      </c>
+      <c r="G92" t="s">
+        <v>49</v>
+      </c>
+      <c r="H92" t="s">
+        <v>63</v>
+      </c>
+      <c r="I92">
+        <v>1.5</v>
+      </c>
+      <c r="J92">
+        <v>1500</v>
+      </c>
+      <c r="K92">
+        <v>3000</v>
+      </c>
+      <c r="L92" t="s">
+        <v>50</v>
+      </c>
+      <c r="M92" t="s">
+        <v>37</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>38</v>
+      </c>
+      <c r="P92" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>64</v>
+      </c>
+      <c r="R92">
+        <v>318</v>
+      </c>
+      <c r="S92">
+        <v>318</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>6</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>2220</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>705.96</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>221</v>
+      </c>
+      <c r="B93" t="s">
+        <v>67</v>
+      </c>
+      <c r="C93" t="s">
+        <v>59</v>
+      </c>
+      <c r="D93" t="s">
+        <v>222</v>
+      </c>
+      <c r="E93" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93" t="s">
+        <v>106</v>
+      </c>
+      <c r="H93" t="s">
+        <v>63</v>
+      </c>
+      <c r="I93">
+        <v>0.8</v>
+      </c>
+      <c r="J93">
+        <v>1250</v>
+      </c>
+      <c r="L93" t="s">
+        <v>36</v>
+      </c>
+      <c r="M93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" t="s">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>64</v>
+      </c>
+      <c r="R93">
+        <v>2650</v>
+      </c>
+      <c r="S93">
+        <v>2650</v>
+      </c>
+      <c r="T93" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93">
+        <v>1</v>
+      </c>
+      <c r="V93" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93">
+        <v>1520</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA93">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>223</v>
+      </c>
+      <c r="B94" t="s">
+        <v>67</v>
+      </c>
+      <c r="C94" t="s">
+        <v>59</v>
+      </c>
+      <c r="D94" t="s">
+        <v>224</v>
+      </c>
+      <c r="E94" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" t="s">
+        <v>33</v>
+      </c>
+      <c r="G94" t="s">
+        <v>162</v>
+      </c>
+      <c r="H94" t="s">
+        <v>63</v>
+      </c>
+      <c r="I94">
+        <v>0.8</v>
+      </c>
+      <c r="J94">
+        <v>1000</v>
+      </c>
+      <c r="L94" t="s">
+        <v>36</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
+      </c>
+      <c r="N94" t="s">
+        <v>37</v>
+      </c>
+      <c r="O94" t="s">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>64</v>
+      </c>
+      <c r="R94">
+        <v>1000</v>
+      </c>
+      <c r="S94">
+        <v>1000</v>
+      </c>
+      <c r="T94" t="s">
+        <v>41</v>
+      </c>
+      <c r="U94">
+        <v>1</v>
+      </c>
+      <c r="V94" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94">
+        <v>2370</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA94">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>225</v>
+      </c>
+      <c r="B95" t="s">
+        <v>58</v>
+      </c>
+      <c r="C95" t="s">
+        <v>59</v>
+      </c>
+      <c r="D95" t="s">
+        <v>178</v>
+      </c>
+      <c r="E95" t="s">
+        <v>48</v>
+      </c>
+      <c r="F95" t="s">
+        <v>61</v>
+      </c>
+      <c r="G95" t="s">
+        <v>49</v>
+      </c>
+      <c r="H95" t="s">
+        <v>63</v>
+      </c>
+      <c r="I95">
+        <v>1.5</v>
+      </c>
+      <c r="J95">
+        <v>1250</v>
+      </c>
+      <c r="K95">
+        <v>2500</v>
+      </c>
+      <c r="L95" t="s">
+        <v>50</v>
+      </c>
+      <c r="M95" t="s">
+        <v>37</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>64</v>
+      </c>
+      <c r="R95">
+        <v>258</v>
+      </c>
+      <c r="S95">
+        <v>258</v>
+      </c>
+      <c r="T95" t="s">
+        <v>41</v>
+      </c>
+      <c r="U95">
+        <v>7</v>
+      </c>
+      <c r="V95" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95">
+        <v>2220</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA95">
+        <v>572.76</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>226</v>
+      </c>
+      <c r="B96" t="s">
+        <v>58</v>
+      </c>
+      <c r="C96" t="s">
+        <v>59</v>
+      </c>
+      <c r="D96" t="s">
+        <v>227</v>
+      </c>
+      <c r="E96" t="s">
+        <v>48</v>
+      </c>
+      <c r="F96" t="s">
+        <v>61</v>
+      </c>
+      <c r="G96" t="s">
+        <v>49</v>
+      </c>
+      <c r="H96" t="s">
+        <v>63</v>
+      </c>
+      <c r="I96">
+        <v>1.5</v>
+      </c>
+      <c r="J96">
+        <v>1500</v>
+      </c>
+      <c r="K96">
+        <v>3000</v>
+      </c>
+      <c r="L96" t="s">
+        <v>50</v>
+      </c>
+      <c r="M96" t="s">
+        <v>109</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" t="s">
+        <v>82</v>
+      </c>
+      <c r="P96" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>64</v>
+      </c>
+      <c r="R96">
+        <v>319</v>
+      </c>
+      <c r="S96">
+        <v>319</v>
+      </c>
+      <c r="T96" t="s">
+        <v>41</v>
+      </c>
+      <c r="U96">
+        <v>6</v>
+      </c>
+      <c r="V96" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X96">
+        <v>2170</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA96">
+        <v>692.23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>228</v>
+      </c>
+      <c r="B97" t="s">
+        <v>58</v>
+      </c>
+      <c r="C97" t="s">
+        <v>59</v>
+      </c>
+      <c r="D97" t="s">
+        <v>229</v>
+      </c>
+      <c r="E97" t="s">
+        <v>48</v>
+      </c>
+      <c r="F97" t="s">
+        <v>61</v>
+      </c>
+      <c r="G97" t="s">
+        <v>49</v>
+      </c>
+      <c r="H97" t="s">
+        <v>63</v>
+      </c>
+      <c r="I97">
+        <v>1.5</v>
+      </c>
+      <c r="J97">
+        <v>1500</v>
+      </c>
+      <c r="K97">
+        <v>3000</v>
+      </c>
+      <c r="L97" t="s">
+        <v>50</v>
+      </c>
+      <c r="M97" t="s">
+        <v>139</v>
+      </c>
+      <c r="N97" t="s">
+        <v>37</v>
+      </c>
+      <c r="O97" t="s">
+        <v>82</v>
+      </c>
+      <c r="P97" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>64</v>
+      </c>
+      <c r="R97">
+        <v>266</v>
+      </c>
+      <c r="S97">
+        <v>266</v>
+      </c>
+      <c r="T97" t="s">
+        <v>41</v>
+      </c>
+      <c r="U97">
+        <v>5</v>
+      </c>
+      <c r="V97" t="s">
+        <v>43</v>
+      </c>
+      <c r="W97" t="s">
+        <v>43</v>
+      </c>
+      <c r="X97">
+        <v>2170</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA97">
+        <v>577.22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>230</v>
+      </c>
+      <c r="B98" t="s">
+        <v>58</v>
+      </c>
+      <c r="C98" t="s">
+        <v>59</v>
+      </c>
+      <c r="D98" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" t="s">
+        <v>48</v>
+      </c>
+      <c r="F98" t="s">
+        <v>61</v>
+      </c>
+      <c r="G98" t="s">
+        <v>49</v>
+      </c>
+      <c r="H98" t="s">
+        <v>63</v>
+      </c>
+      <c r="I98">
+        <v>1.5</v>
+      </c>
+      <c r="J98">
+        <v>1500</v>
+      </c>
+      <c r="K98">
+        <v>3000</v>
+      </c>
+      <c r="L98" t="s">
+        <v>50</v>
+      </c>
+      <c r="M98" t="s">
+        <v>139</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" t="s">
+        <v>82</v>
+      </c>
+      <c r="P98" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>64</v>
+      </c>
+      <c r="R98">
+        <v>319</v>
+      </c>
+      <c r="S98">
+        <v>319</v>
+      </c>
+      <c r="T98" t="s">
+        <v>41</v>
+      </c>
+      <c r="U98">
+        <v>6</v>
+      </c>
+      <c r="V98" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98">
+        <v>2170</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA98">
+        <v>692.23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>231</v>
+      </c>
+      <c r="B99" t="s">
+        <v>58</v>
+      </c>
+      <c r="C99" t="s">
+        <v>59</v>
+      </c>
+      <c r="D99" t="s">
+        <v>232</v>
+      </c>
+      <c r="E99" t="s">
+        <v>48</v>
+      </c>
+      <c r="F99" t="s">
+        <v>61</v>
+      </c>
+      <c r="G99" t="s">
+        <v>49</v>
+      </c>
+      <c r="H99" t="s">
+        <v>63</v>
+      </c>
+      <c r="I99">
+        <v>2</v>
+      </c>
+      <c r="J99">
+        <v>1500</v>
+      </c>
+      <c r="K99">
+        <v>3000</v>
+      </c>
+      <c r="L99" t="s">
+        <v>50</v>
+      </c>
+      <c r="M99" t="s">
+        <v>109</v>
+      </c>
+      <c r="N99" t="s">
+        <v>37</v>
+      </c>
+      <c r="O99" t="s">
+        <v>82</v>
+      </c>
+      <c r="P99" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>64</v>
+      </c>
+      <c r="R99">
+        <v>496</v>
+      </c>
+      <c r="S99">
+        <v>496</v>
+      </c>
+      <c r="T99" t="s">
+        <v>41</v>
+      </c>
+      <c r="U99">
+        <v>7</v>
+      </c>
+      <c r="V99" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99">
+        <v>2170</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA99">
+        <v>1076.32</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>233</v>
+      </c>
+      <c r="B100" t="s">
+        <v>58</v>
+      </c>
+      <c r="C100" t="s">
+        <v>59</v>
+      </c>
+      <c r="D100" t="s">
+        <v>234</v>
+      </c>
+      <c r="E100" t="s">
+        <v>48</v>
+      </c>
+      <c r="F100" t="s">
+        <v>61</v>
+      </c>
+      <c r="G100" t="s">
+        <v>49</v>
+      </c>
+      <c r="H100" t="s">
+        <v>63</v>
+      </c>
+      <c r="I100">
+        <v>2.5</v>
+      </c>
+      <c r="J100">
+        <v>1500</v>
+      </c>
+      <c r="K100">
+        <v>3000</v>
+      </c>
+      <c r="L100" t="s">
+        <v>50</v>
+      </c>
+      <c r="M100" t="s">
+        <v>37</v>
+      </c>
+      <c r="N100" t="s">
+        <v>37</v>
+      </c>
+      <c r="O100" t="s">
+        <v>38</v>
+      </c>
+      <c r="P100" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>64</v>
+      </c>
+      <c r="R100">
+        <v>266</v>
+      </c>
+      <c r="S100">
+        <v>266</v>
+      </c>
+      <c r="T100" t="s">
+        <v>41</v>
+      </c>
+      <c r="U100">
+        <v>3</v>
+      </c>
+      <c r="V100" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100">
+        <v>2220</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA100">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>235</v>
+      </c>
+      <c r="B101" t="s">
+        <v>58</v>
+      </c>
+      <c r="C101" t="s">
+        <v>59</v>
+      </c>
+      <c r="D101" t="s">
+        <v>234</v>
+      </c>
+      <c r="E101" t="s">
+        <v>48</v>
+      </c>
+      <c r="F101" t="s">
+        <v>61</v>
+      </c>
+      <c r="G101" t="s">
+        <v>49</v>
+      </c>
+      <c r="H101" t="s">
+        <v>63</v>
+      </c>
+      <c r="I101">
+        <v>2.5</v>
+      </c>
+      <c r="J101">
+        <v>1500</v>
+      </c>
+      <c r="K101">
+        <v>3000</v>
+      </c>
+      <c r="L101" t="s">
+        <v>50</v>
+      </c>
+      <c r="M101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N101" t="s">
+        <v>37</v>
+      </c>
+      <c r="O101" t="s">
+        <v>38</v>
+      </c>
+      <c r="P101" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>64</v>
+      </c>
+      <c r="R101">
+        <v>354</v>
+      </c>
+      <c r="S101">
+        <v>354</v>
+      </c>
+      <c r="T101" t="s">
+        <v>41</v>
+      </c>
+      <c r="U101">
+        <v>4</v>
+      </c>
+      <c r="V101" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101">
+        <v>2220</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA101">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>236</v>
+      </c>
+      <c r="B102" t="s">
+        <v>58</v>
+      </c>
+      <c r="C102" t="s">
+        <v>59</v>
+      </c>
+      <c r="D102" t="s">
+        <v>234</v>
+      </c>
+      <c r="E102" t="s">
+        <v>48</v>
+      </c>
+      <c r="F102" t="s">
+        <v>61</v>
+      </c>
+      <c r="G102" t="s">
+        <v>49</v>
+      </c>
+      <c r="H102" t="s">
+        <v>63</v>
+      </c>
+      <c r="I102">
+        <v>2.5</v>
+      </c>
+      <c r="J102">
+        <v>1500</v>
+      </c>
+      <c r="K102">
+        <v>3000</v>
+      </c>
+      <c r="L102" t="s">
+        <v>50</v>
+      </c>
+      <c r="M102" t="s">
+        <v>37</v>
+      </c>
+      <c r="N102" t="s">
+        <v>37</v>
+      </c>
+      <c r="O102" t="s">
+        <v>38</v>
+      </c>
+      <c r="P102" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>64</v>
+      </c>
+      <c r="R102">
+        <v>620</v>
+      </c>
+      <c r="S102">
+        <v>620</v>
+      </c>
+      <c r="T102" t="s">
+        <v>41</v>
+      </c>
+      <c r="U102">
+        <v>7</v>
+      </c>
+      <c r="V102" t="s">
+        <v>43</v>
+      </c>
+      <c r="W102" t="s">
+        <v>43</v>
+      </c>
+      <c r="X102">
+        <v>2220</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA102">
+        <v>1376.4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>237</v>
+      </c>
+      <c r="B103" t="s">
+        <v>58</v>
+      </c>
+      <c r="C103" t="s">
+        <v>59</v>
+      </c>
+      <c r="D103" t="s">
+        <v>238</v>
+      </c>
+      <c r="E103" t="s">
+        <v>48</v>
+      </c>
+      <c r="F103" t="s">
+        <v>61</v>
+      </c>
+      <c r="G103" t="s">
+        <v>69</v>
+      </c>
+      <c r="H103" t="s">
+        <v>63</v>
+      </c>
+      <c r="I103">
+        <v>1.5</v>
+      </c>
+      <c r="J103">
+        <v>1500</v>
+      </c>
+      <c r="K103">
+        <v>3000</v>
+      </c>
+      <c r="L103" t="s">
+        <v>50</v>
+      </c>
+      <c r="M103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N103" t="s">
+        <v>37</v>
+      </c>
+      <c r="O103" t="s">
+        <v>38</v>
+      </c>
+      <c r="P103" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>64</v>
+      </c>
+      <c r="R103">
+        <v>266</v>
+      </c>
+      <c r="S103">
+        <v>266</v>
+      </c>
+      <c r="T103" t="s">
+        <v>41</v>
+      </c>
+      <c r="U103">
+        <v>5</v>
+      </c>
+      <c r="V103" t="s">
+        <v>43</v>
+      </c>
+      <c r="W103" t="s">
+        <v>43</v>
+      </c>
+      <c r="X103">
+        <v>3540</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA103">
+        <v>941.64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>239</v>
+      </c>
+      <c r="B104" t="s">
+        <v>58</v>
+      </c>
+      <c r="C104" t="s">
+        <v>59</v>
+      </c>
+      <c r="D104" t="s">
+        <v>240</v>
+      </c>
+      <c r="E104" t="s">
+        <v>48</v>
+      </c>
+      <c r="F104" t="s">
+        <v>61</v>
+      </c>
+      <c r="G104" t="s">
+        <v>69</v>
+      </c>
+      <c r="H104" t="s">
+        <v>63</v>
+      </c>
+      <c r="I104">
+        <v>2.5</v>
+      </c>
+      <c r="J104">
+        <v>2000</v>
+      </c>
+      <c r="K104">
+        <v>4000</v>
+      </c>
+      <c r="L104" t="s">
+        <v>50</v>
+      </c>
+      <c r="M104" t="s">
+        <v>37</v>
+      </c>
+      <c r="N104" t="s">
+        <v>37</v>
+      </c>
+      <c r="O104" t="s">
+        <v>38</v>
+      </c>
+      <c r="P104" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>64</v>
+      </c>
+      <c r="R104">
+        <v>315</v>
+      </c>
+      <c r="S104">
+        <v>315</v>
+      </c>
+      <c r="T104" t="s">
+        <v>41</v>
+      </c>
+      <c r="U104">
+        <v>2</v>
+      </c>
+      <c r="V104" t="s">
+        <v>43</v>
+      </c>
+      <c r="W104" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104">
+        <v>3560</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA104">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>241</v>
+      </c>
+      <c r="B105" t="s">
+        <v>58</v>
+      </c>
+      <c r="C105" t="s">
+        <v>59</v>
+      </c>
+      <c r="D105" t="s">
+        <v>240</v>
+      </c>
+      <c r="E105" t="s">
+        <v>48</v>
+      </c>
+      <c r="F105" t="s">
+        <v>61</v>
+      </c>
+      <c r="G105" t="s">
+        <v>69</v>
+      </c>
+      <c r="H105" t="s">
+        <v>63</v>
+      </c>
+      <c r="I105">
+        <v>2.5</v>
+      </c>
+      <c r="J105">
+        <v>2000</v>
+      </c>
+      <c r="K105">
+        <v>4000</v>
+      </c>
+      <c r="L105" t="s">
+        <v>50</v>
+      </c>
+      <c r="M105" t="s">
+        <v>37</v>
+      </c>
+      <c r="N105" t="s">
+        <v>37</v>
+      </c>
+      <c r="O105" t="s">
+        <v>38</v>
+      </c>
+      <c r="P105" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>64</v>
+      </c>
+      <c r="R105">
+        <v>315</v>
+      </c>
+      <c r="S105">
+        <v>315</v>
+      </c>
+      <c r="T105" t="s">
+        <v>41</v>
+      </c>
+      <c r="U105">
+        <v>2</v>
+      </c>
+      <c r="V105" t="s">
+        <v>43</v>
+      </c>
+      <c r="W105" t="s">
+        <v>43</v>
+      </c>
+      <c r="X105">
+        <v>3560</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA105">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>242</v>
+      </c>
+      <c r="B106" t="s">
+        <v>58</v>
+      </c>
+      <c r="C106" t="s">
+        <v>59</v>
+      </c>
+      <c r="D106" t="s">
+        <v>243</v>
+      </c>
+      <c r="E106" t="s">
+        <v>48</v>
+      </c>
+      <c r="F106" t="s">
+        <v>61</v>
+      </c>
+      <c r="G106" t="s">
+        <v>69</v>
+      </c>
+      <c r="H106" t="s">
+        <v>63</v>
+      </c>
+      <c r="I106">
+        <v>4</v>
+      </c>
+      <c r="J106">
+        <v>2000</v>
+      </c>
+      <c r="K106">
+        <v>4000</v>
+      </c>
+      <c r="L106" t="s">
+        <v>50</v>
+      </c>
+      <c r="M106" t="s">
+        <v>37</v>
+      </c>
+      <c r="N106" t="s">
+        <v>37</v>
+      </c>
+      <c r="O106" t="s">
+        <v>38</v>
+      </c>
+      <c r="P106" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>64</v>
+      </c>
+      <c r="R106">
+        <v>252</v>
+      </c>
+      <c r="S106">
+        <v>252</v>
+      </c>
+      <c r="T106" t="s">
+        <v>41</v>
+      </c>
+      <c r="U106">
+        <v>1</v>
+      </c>
+      <c r="V106" t="s">
+        <v>43</v>
+      </c>
+      <c r="W106" t="s">
+        <v>43</v>
+      </c>
+      <c r="X106">
+        <v>3560</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA106">
+        <v>897.12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>244</v>
+      </c>
+      <c r="B107" t="s">
+        <v>58</v>
+      </c>
+      <c r="C107" t="s">
+        <v>59</v>
+      </c>
+      <c r="D107" t="s">
+        <v>243</v>
+      </c>
+      <c r="E107" t="s">
+        <v>48</v>
+      </c>
+      <c r="F107" t="s">
+        <v>61</v>
+      </c>
+      <c r="G107" t="s">
+        <v>69</v>
+      </c>
+      <c r="H107" t="s">
+        <v>63</v>
+      </c>
+      <c r="I107">
+        <v>4</v>
+      </c>
+      <c r="J107">
+        <v>2000</v>
+      </c>
+      <c r="K107">
+        <v>4000</v>
+      </c>
+      <c r="L107" t="s">
+        <v>50</v>
+      </c>
+      <c r="M107" t="s">
+        <v>37</v>
+      </c>
+      <c r="N107" t="s">
+        <v>37</v>
+      </c>
+      <c r="O107" t="s">
+        <v>38</v>
+      </c>
+      <c r="P107" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>64</v>
+      </c>
+      <c r="R107">
+        <v>252</v>
+      </c>
+      <c r="S107">
+        <v>252</v>
+      </c>
+      <c r="T107" t="s">
+        <v>41</v>
+      </c>
+      <c r="U107">
+        <v>1</v>
+      </c>
+      <c r="V107" t="s">
+        <v>43</v>
+      </c>
+      <c r="W107" t="s">
+        <v>43</v>
+      </c>
+      <c r="X107">
+        <v>3560</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA107">
+        <v>897.12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>245</v>
+      </c>
+      <c r="B108" t="s">
+        <v>58</v>
+      </c>
+      <c r="C108" t="s">
+        <v>59</v>
+      </c>
+      <c r="D108" t="s">
+        <v>246</v>
+      </c>
+      <c r="E108" t="s">
+        <v>48</v>
+      </c>
+      <c r="F108" t="s">
+        <v>61</v>
+      </c>
+      <c r="G108" t="s">
+        <v>62</v>
+      </c>
+      <c r="H108" t="s">
+        <v>63</v>
+      </c>
+      <c r="I108">
+        <v>6</v>
+      </c>
+      <c r="J108">
+        <v>1250</v>
+      </c>
+      <c r="K108">
+        <v>2500</v>
+      </c>
+      <c r="L108" t="s">
+        <v>50</v>
+      </c>
+      <c r="M108" t="s">
+        <v>37</v>
+      </c>
+      <c r="N108" t="s">
+        <v>37</v>
+      </c>
+      <c r="O108" t="s">
+        <v>38</v>
+      </c>
+      <c r="P108" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>64</v>
+      </c>
+      <c r="R108">
+        <v>147</v>
+      </c>
+      <c r="S108">
+        <v>147</v>
+      </c>
+      <c r="T108" t="s">
+        <v>41</v>
+      </c>
+      <c r="U108">
+        <v>1</v>
+      </c>
+      <c r="V108" t="s">
+        <v>43</v>
+      </c>
+      <c r="W108" t="s">
+        <v>43</v>
+      </c>
+      <c r="X108">
+        <v>3640</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA108">
+        <v>535.08</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>247</v>
+      </c>
+      <c r="B109" t="s">
+        <v>58</v>
+      </c>
+      <c r="C109" t="s">
+        <v>59</v>
+      </c>
+      <c r="D109" t="s">
+        <v>248</v>
+      </c>
+      <c r="E109" t="s">
+        <v>48</v>
+      </c>
+      <c r="F109" t="s">
+        <v>61</v>
+      </c>
+      <c r="G109" t="s">
+        <v>49</v>
+      </c>
+      <c r="H109" t="s">
+        <v>63</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+      <c r="J109">
+        <v>1500</v>
+      </c>
+      <c r="K109">
+        <v>3000</v>
+      </c>
+      <c r="L109" t="s">
+        <v>50</v>
+      </c>
+      <c r="M109" t="s">
+        <v>37</v>
+      </c>
+      <c r="N109" t="s">
+        <v>37</v>
+      </c>
+      <c r="O109" t="s">
+        <v>38</v>
+      </c>
+      <c r="P109" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>64</v>
+      </c>
+      <c r="R109">
+        <v>283</v>
+      </c>
+      <c r="S109">
+        <v>283</v>
+      </c>
+      <c r="T109" t="s">
+        <v>41</v>
+      </c>
+      <c r="U109">
+        <v>4</v>
+      </c>
+      <c r="V109" t="s">
+        <v>43</v>
+      </c>
+      <c r="W109" t="s">
+        <v>43</v>
+      </c>
+      <c r="X109">
+        <v>2220</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA109">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>249</v>
+      </c>
+      <c r="B110" t="s">
+        <v>67</v>
+      </c>
+      <c r="C110" t="s">
+        <v>59</v>
+      </c>
+      <c r="D110" t="s">
+        <v>250</v>
+      </c>
+      <c r="E110" t="s">
+        <v>48</v>
+      </c>
+      <c r="F110" t="s">
+        <v>61</v>
+      </c>
+      <c r="G110" t="s">
+        <v>49</v>
+      </c>
+      <c r="H110" t="s">
+        <v>63</v>
+      </c>
+      <c r="I110">
+        <v>0.8</v>
+      </c>
+      <c r="J110">
+        <v>1500</v>
+      </c>
+      <c r="K110">
+        <v>3000</v>
+      </c>
+      <c r="L110" t="s">
+        <v>50</v>
+      </c>
+      <c r="M110" t="s">
+        <v>86</v>
+      </c>
+      <c r="N110" t="s">
+        <v>37</v>
+      </c>
+      <c r="O110" t="s">
+        <v>82</v>
+      </c>
+      <c r="P110" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>64</v>
+      </c>
+      <c r="R110">
+        <v>833</v>
+      </c>
+      <c r="S110">
+        <v>833</v>
+      </c>
+      <c r="T110" t="s">
+        <v>41</v>
+      </c>
+      <c r="U110">
+        <v>29</v>
+      </c>
+      <c r="V110" t="s">
+        <v>43</v>
+      </c>
+      <c r="W110" t="s">
+        <v>43</v>
+      </c>
+      <c r="X110">
+        <v>2270</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA110">
+        <v>1890.91</v>
+      </c>
+      <c r="AB110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>251</v>
+      </c>
+      <c r="B111" t="s">
+        <v>67</v>
+      </c>
+      <c r="C111" t="s">
+        <v>59</v>
+      </c>
+      <c r="D111" t="s">
+        <v>250</v>
+      </c>
+      <c r="E111" t="s">
+        <v>48</v>
+      </c>
+      <c r="F111" t="s">
+        <v>61</v>
+      </c>
+      <c r="G111" t="s">
+        <v>49</v>
+      </c>
+      <c r="H111" t="s">
+        <v>63</v>
+      </c>
+      <c r="I111">
+        <v>0.8</v>
+      </c>
+      <c r="J111">
+        <v>1500</v>
+      </c>
+      <c r="K111">
+        <v>3000</v>
+      </c>
+      <c r="L111" t="s">
+        <v>50</v>
+      </c>
+      <c r="M111" t="s">
+        <v>86</v>
+      </c>
+      <c r="N111" t="s">
+        <v>37</v>
+      </c>
+      <c r="O111" t="s">
+        <v>82</v>
+      </c>
+      <c r="P111" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>64</v>
+      </c>
+      <c r="R111">
+        <v>805</v>
+      </c>
+      <c r="S111">
+        <v>805</v>
+      </c>
+      <c r="T111" t="s">
+        <v>41</v>
+      </c>
+      <c r="U111">
+        <v>28</v>
+      </c>
+      <c r="V111" t="s">
+        <v>43</v>
+      </c>
+      <c r="W111" t="s">
+        <v>43</v>
+      </c>
+      <c r="X111">
+        <v>2270</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA111">
+        <v>1827.35</v>
+      </c>
+      <c r="AB111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>252</v>
+      </c>
+      <c r="B112" t="s">
+        <v>67</v>
+      </c>
+      <c r="C112" t="s">
+        <v>59</v>
+      </c>
+      <c r="D112" t="s">
+        <v>253</v>
+      </c>
+      <c r="E112" t="s">
+        <v>48</v>
+      </c>
+      <c r="F112" t="s">
+        <v>61</v>
+      </c>
+      <c r="G112" t="s">
+        <v>49</v>
+      </c>
+      <c r="H112" t="s">
+        <v>63</v>
+      </c>
+      <c r="I112">
+        <v>2</v>
+      </c>
+      <c r="J112">
+        <v>1000</v>
+      </c>
+      <c r="K112">
+        <v>2000</v>
+      </c>
+      <c r="L112" t="s">
+        <v>50</v>
+      </c>
+      <c r="M112" t="s">
+        <v>37</v>
+      </c>
+      <c r="N112" t="s">
+        <v>37</v>
+      </c>
+      <c r="O112" t="s">
+        <v>38</v>
+      </c>
+      <c r="P112" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>64</v>
+      </c>
+      <c r="R112">
+        <v>1448</v>
+      </c>
+      <c r="S112">
+        <v>1448</v>
+      </c>
+      <c r="T112" t="s">
+        <v>41</v>
+      </c>
+      <c r="U112">
+        <v>1</v>
+      </c>
+      <c r="V112" t="s">
+        <v>43</v>
+      </c>
+      <c r="W112" t="s">
+        <v>43</v>
+      </c>
+      <c r="X112">
+        <v>2270</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA112">
+        <v>3286.96</v>
+      </c>
+      <c r="AB112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>254</v>
+      </c>
+      <c r="B113" t="s">
+        <v>71</v>
+      </c>
+      <c r="C113" t="s">
+        <v>59</v>
+      </c>
+      <c r="D113" t="s">
+        <v>255</v>
+      </c>
+      <c r="E113" t="s">
+        <v>48</v>
+      </c>
+      <c r="F113" t="s">
+        <v>61</v>
+      </c>
+      <c r="G113" t="s">
+        <v>106</v>
+      </c>
+      <c r="H113" t="s">
+        <v>63</v>
+      </c>
+      <c r="I113">
+        <v>4</v>
+      </c>
+      <c r="J113">
+        <v>1000</v>
+      </c>
+      <c r="K113">
+        <v>2000</v>
+      </c>
+      <c r="L113" t="s">
+        <v>50</v>
+      </c>
+      <c r="M113" t="s">
+        <v>37</v>
+      </c>
+      <c r="N113" t="s">
+        <v>37</v>
+      </c>
+      <c r="O113" t="s">
+        <v>38</v>
+      </c>
+      <c r="P113" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>64</v>
+      </c>
+      <c r="R113">
+        <v>384</v>
+      </c>
+      <c r="S113">
+        <v>384</v>
+      </c>
+      <c r="T113" t="s">
+        <v>41</v>
+      </c>
+      <c r="U113">
+        <v>6</v>
+      </c>
+      <c r="V113" t="s">
+        <v>43</v>
+      </c>
+      <c r="W113" t="s">
+        <v>43</v>
+      </c>
+      <c r="X113">
+        <v>1370</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA113">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>256</v>
+      </c>
+      <c r="B114" t="s">
+        <v>58</v>
+      </c>
+      <c r="C114" t="s">
+        <v>59</v>
+      </c>
+      <c r="D114" t="s">
+        <v>114</v>
+      </c>
+      <c r="E114" t="s">
+        <v>48</v>
+      </c>
+      <c r="F114" t="s">
+        <v>61</v>
+      </c>
+      <c r="G114" t="s">
+        <v>69</v>
+      </c>
+      <c r="H114" t="s">
+        <v>63</v>
+      </c>
+      <c r="I114">
+        <v>6</v>
+      </c>
+      <c r="J114">
+        <v>1500</v>
+      </c>
+      <c r="K114">
+        <v>3000</v>
+      </c>
+      <c r="L114" t="s">
+        <v>50</v>
+      </c>
+      <c r="M114" t="s">
+        <v>37</v>
+      </c>
+      <c r="N114" t="s">
+        <v>37</v>
+      </c>
+      <c r="O114" t="s">
+        <v>38</v>
+      </c>
+      <c r="P114" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>64</v>
+      </c>
+      <c r="R114">
+        <v>850</v>
+      </c>
+      <c r="S114">
+        <v>850</v>
+      </c>
+      <c r="T114" t="s">
+        <v>41</v>
+      </c>
+      <c r="U114">
+        <v>4</v>
+      </c>
+      <c r="V114" t="s">
+        <v>43</v>
+      </c>
+      <c r="W114" t="s">
+        <v>43</v>
+      </c>
+      <c r="X114">
+        <v>3540</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA114">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>257</v>
+      </c>
+      <c r="B115" t="s">
+        <v>67</v>
+      </c>
+      <c r="C115" t="s">
+        <v>59</v>
+      </c>
+      <c r="D115" t="s">
+        <v>78</v>
+      </c>
+      <c r="E115" t="s">
+        <v>48</v>
+      </c>
+      <c r="F115" t="s">
+        <v>61</v>
+      </c>
+      <c r="G115" t="s">
+        <v>49</v>
+      </c>
+      <c r="H115" t="s">
+        <v>63</v>
+      </c>
+      <c r="I115">
+        <v>3</v>
+      </c>
+      <c r="J115">
+        <v>1500</v>
+      </c>
+      <c r="K115">
+        <v>3000</v>
+      </c>
+      <c r="L115" t="s">
+        <v>50</v>
+      </c>
+      <c r="M115" t="s">
+        <v>37</v>
+      </c>
+      <c r="N115" t="s">
+        <v>37</v>
+      </c>
+      <c r="O115" t="s">
+        <v>38</v>
+      </c>
+      <c r="P115" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>64</v>
+      </c>
+      <c r="R115">
+        <v>632</v>
+      </c>
+      <c r="S115">
+        <v>632</v>
+      </c>
+      <c r="T115" t="s">
+        <v>41</v>
+      </c>
+      <c r="U115">
+        <v>6</v>
+      </c>
+      <c r="V115" t="s">
+        <v>43</v>
+      </c>
+      <c r="W115" t="s">
+        <v>43</v>
+      </c>
+      <c r="X115">
+        <v>2220</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA115">
+        <v>1403.04</v>
       </c>
     </row>
   </sheetData>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="291">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -296,6 +296,594 @@
   </si>
   <si>
     <t>Coil 1.4404-316L 2B with paper 1.42 x 1301.0 mm Unslit marked</t>
+  </si>
+  <si>
+    <t>7246484</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>7246542</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
+    <t>7246814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 5.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7246817</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 6.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T473609</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7247036</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Polish grain 400 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7247041</t>
+  </si>
+  <si>
+    <t>7247338</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7247409</t>
+  </si>
+  <si>
+    <t>7247854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475488</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T475814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248626</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7248988</t>
+  </si>
+  <si>
+    <t>Coil 1.4307-304L 2D 1.0 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7248989</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T477742</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>K30/1.4016-430</t>
+  </si>
+  <si>
+    <t>7249627</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Duplo polish grain 320</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481266</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481267</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T481616</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T481617</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T481869</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7253484</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 240 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 240</t>
+  </si>
+  <si>
+    <t>7253485</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484088</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484797</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254248</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T485455</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254992</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T486939</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>T487305</t>
+  </si>
+  <si>
+    <t>T487411</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255816</t>
+  </si>
+  <si>
+    <t>T487947</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T487964</t>
+  </si>
+  <si>
+    <t>7256046</t>
+  </si>
+  <si>
+    <t>Coil 1.4301-304 2R 0.6 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>T488237</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256367</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.2 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7256368</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Scotchbrite</t>
+  </si>
+  <si>
+    <t>T488483</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T488484</t>
+  </si>
+  <si>
+    <t>T488802</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>T488824</t>
+  </si>
+  <si>
+    <t>T488827</t>
+  </si>
+  <si>
+    <t>7256740</t>
+  </si>
+  <si>
+    <t>Sheets 1.4301-304 2R 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256746</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7256751</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2R 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256753</t>
+  </si>
+  <si>
+    <t>7256757</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256760</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R with paper 0.8 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256809</t>
+  </si>
+  <si>
+    <t>7256813</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256814</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 240 Nov 4228 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256815</t>
+  </si>
+  <si>
+    <t>7256817</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256819</t>
+  </si>
+  <si>
+    <t>7256820</t>
+  </si>
+  <si>
+    <t>7256821</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>7256837</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 4.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256838</t>
+  </si>
+  <si>
+    <t>7256839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 6.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T488986</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256940</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed Nov 4228 0.8 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256941</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489089</t>
+  </si>
+  <si>
+    <t>7257077</t>
   </si>
 </sst>
 </file>
@@ -672,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -2329,6 +2917,9050 @@
         <v>1</v>
       </c>
     </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21">
+        <v>2.5</v>
+      </c>
+      <c r="J21">
+        <v>1500</v>
+      </c>
+      <c r="K21">
+        <v>3000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>36</v>
+      </c>
+      <c r="M21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" t="s">
+        <v>37</v>
+      </c>
+      <c r="O21" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>554</v>
+      </c>
+      <c r="S21">
+        <v>554</v>
+      </c>
+      <c r="T21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U21">
+        <v>6</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21">
+        <v>3540</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>1961.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22">
+        <v>6</v>
+      </c>
+      <c r="J22">
+        <v>1000</v>
+      </c>
+      <c r="K22">
+        <v>2000</v>
+      </c>
+      <c r="L22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>100</v>
+      </c>
+      <c r="R22">
+        <v>1133</v>
+      </c>
+      <c r="S22">
+        <v>1133</v>
+      </c>
+      <c r="T22" t="s">
+        <v>41</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>43</v>
+      </c>
+      <c r="X22">
+        <v>2070</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22">
+        <v>2345.31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23">
+        <v>2000</v>
+      </c>
+      <c r="K23">
+        <v>6000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>100</v>
+      </c>
+      <c r="R23">
+        <v>472</v>
+      </c>
+      <c r="S23">
+        <v>472</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23">
+        <v>2240</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA23">
+        <v>1057.28</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>6</v>
+      </c>
+      <c r="J24">
+        <v>2000</v>
+      </c>
+      <c r="K24">
+        <v>6000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>36</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>100</v>
+      </c>
+      <c r="R24">
+        <v>567</v>
+      </c>
+      <c r="S24">
+        <v>567</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>3560</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>2018.52</v>
+      </c>
+      <c r="AB24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>3</v>
+      </c>
+      <c r="J25">
+        <v>1500</v>
+      </c>
+      <c r="K25">
+        <v>3000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>36</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>212</v>
+      </c>
+      <c r="S25">
+        <v>212</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>2</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>2170</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>1500</v>
+      </c>
+      <c r="K26">
+        <v>3000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>36</v>
+      </c>
+      <c r="M26" t="s">
+        <v>114</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>115</v>
+      </c>
+      <c r="P26" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>100</v>
+      </c>
+      <c r="R26">
+        <v>1014</v>
+      </c>
+      <c r="S26">
+        <v>1014</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>3540</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>3589.56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>1500</v>
+      </c>
+      <c r="K27">
+        <v>3000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>36</v>
+      </c>
+      <c r="M27" t="s">
+        <v>114</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>115</v>
+      </c>
+      <c r="P27" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>100</v>
+      </c>
+      <c r="R27">
+        <v>728</v>
+      </c>
+      <c r="S27">
+        <v>728</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>3490</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>2540.72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>1.5</v>
+      </c>
+      <c r="J28">
+        <v>1500</v>
+      </c>
+      <c r="K28">
+        <v>3000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>36</v>
+      </c>
+      <c r="M28" t="s">
+        <v>119</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>100</v>
+      </c>
+      <c r="R28">
+        <v>592</v>
+      </c>
+      <c r="S28">
+        <v>592</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>11</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>3490</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>2066.08</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
+        <v>2.5</v>
+      </c>
+      <c r="J29">
+        <v>1500</v>
+      </c>
+      <c r="K29">
+        <v>3000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>36</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>100</v>
+      </c>
+      <c r="R29">
+        <v>540</v>
+      </c>
+      <c r="S29">
+        <v>540</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>6</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>3540</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" t="s">
+        <v>99</v>
+      </c>
+      <c r="G30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>2000</v>
+      </c>
+      <c r="K30">
+        <v>4000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>36</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>100</v>
+      </c>
+      <c r="R30">
+        <v>126</v>
+      </c>
+      <c r="S30">
+        <v>126</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>2190</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>5</v>
+      </c>
+      <c r="J31">
+        <v>2000</v>
+      </c>
+      <c r="K31">
+        <v>4000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>36</v>
+      </c>
+      <c r="M31" t="s">
+        <v>37</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>100</v>
+      </c>
+      <c r="R31">
+        <v>315</v>
+      </c>
+      <c r="S31">
+        <v>315</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>1</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>3560</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
+        <v>2000</v>
+      </c>
+      <c r="K32">
+        <v>4000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>36</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>100</v>
+      </c>
+      <c r="R32">
+        <v>189</v>
+      </c>
+      <c r="S32">
+        <v>189</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>1</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>2190</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>413.91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" t="s">
+        <v>128</v>
+      </c>
+      <c r="E33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>2.5</v>
+      </c>
+      <c r="J33">
+        <v>1000</v>
+      </c>
+      <c r="K33">
+        <v>2000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>36</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>100</v>
+      </c>
+      <c r="R33">
+        <v>312</v>
+      </c>
+      <c r="S33">
+        <v>312</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>8</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>2220</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>692.64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
+        <v>53</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>1000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>100</v>
+      </c>
+      <c r="R34">
+        <v>2560</v>
+      </c>
+      <c r="S34">
+        <v>2560</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>2270</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>5811.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H35" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>1000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>66</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>100</v>
+      </c>
+      <c r="R35">
+        <v>3075</v>
+      </c>
+      <c r="S35">
+        <v>3075</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>2270</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>6980.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <v>5</v>
+      </c>
+      <c r="J36">
+        <v>1000</v>
+      </c>
+      <c r="K36">
+        <v>2000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>104</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>100</v>
+      </c>
+      <c r="R36">
+        <v>394</v>
+      </c>
+      <c r="S36">
+        <v>394</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>2020</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" t="s">
+        <v>53</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>0.8</v>
+      </c>
+      <c r="J37">
+        <v>1000</v>
+      </c>
+      <c r="K37">
+        <v>2000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>36</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>100</v>
+      </c>
+      <c r="R37">
+        <v>176</v>
+      </c>
+      <c r="S37">
+        <v>176</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>14</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>2270</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>399.52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G38" t="s">
+        <v>138</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38">
+        <v>1250</v>
+      </c>
+      <c r="K38">
+        <v>2500</v>
+      </c>
+      <c r="L38" t="s">
+        <v>75</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>100</v>
+      </c>
+      <c r="R38">
+        <v>322</v>
+      </c>
+      <c r="S38">
+        <v>322</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>1</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>1370</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>139</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+      <c r="G39" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>0.8</v>
+      </c>
+      <c r="J39">
+        <v>1250</v>
+      </c>
+      <c r="K39">
+        <v>2500</v>
+      </c>
+      <c r="L39" t="s">
+        <v>36</v>
+      </c>
+      <c r="M39" t="s">
+        <v>141</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>115</v>
+      </c>
+      <c r="P39" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>100</v>
+      </c>
+      <c r="R39">
+        <v>157</v>
+      </c>
+      <c r="S39">
+        <v>157</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>8</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>2220</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>348.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>142</v>
+      </c>
+      <c r="B40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40" t="s">
+        <v>99</v>
+      </c>
+      <c r="G40" t="s">
+        <v>138</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="J40">
+        <v>1250</v>
+      </c>
+      <c r="K40">
+        <v>2500</v>
+      </c>
+      <c r="L40" t="s">
+        <v>75</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>100</v>
+      </c>
+      <c r="R40">
+        <v>340</v>
+      </c>
+      <c r="S40">
+        <v>340</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>7</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>1370</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>143</v>
+      </c>
+      <c r="B41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" t="s">
+        <v>144</v>
+      </c>
+      <c r="E41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>3</v>
+      </c>
+      <c r="J41">
+        <v>2000</v>
+      </c>
+      <c r="K41">
+        <v>6000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>36</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>100</v>
+      </c>
+      <c r="R41">
+        <v>283</v>
+      </c>
+      <c r="S41">
+        <v>283</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>3560</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>1007.48</v>
+      </c>
+      <c r="AB41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" t="s">
+        <v>99</v>
+      </c>
+      <c r="G42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42">
+        <v>6</v>
+      </c>
+      <c r="J42">
+        <v>1500</v>
+      </c>
+      <c r="K42">
+        <v>3000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>36</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>100</v>
+      </c>
+      <c r="R42">
+        <v>212</v>
+      </c>
+      <c r="S42">
+        <v>212</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>3490</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" t="s">
+        <v>148</v>
+      </c>
+      <c r="E43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" t="s">
+        <v>99</v>
+      </c>
+      <c r="G43" t="s">
+        <v>149</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>8</v>
+      </c>
+      <c r="J43">
+        <v>1250</v>
+      </c>
+      <c r="K43">
+        <v>2500</v>
+      </c>
+      <c r="L43" t="s">
+        <v>104</v>
+      </c>
+      <c r="M43" t="s">
+        <v>37</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>100</v>
+      </c>
+      <c r="R43">
+        <v>394</v>
+      </c>
+      <c r="S43">
+        <v>394</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>1</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>3490</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>150</v>
+      </c>
+      <c r="B44" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" t="s">
+        <v>99</v>
+      </c>
+      <c r="G44" t="s">
+        <v>152</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="J44">
+        <v>2000</v>
+      </c>
+      <c r="K44">
+        <v>6000</v>
+      </c>
+      <c r="L44" t="s">
+        <v>104</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>100</v>
+      </c>
+      <c r="R44">
+        <v>472</v>
+      </c>
+      <c r="S44">
+        <v>472</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>1</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>2190</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>153</v>
+      </c>
+      <c r="B45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" t="s">
+        <v>154</v>
+      </c>
+      <c r="E45" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" t="s">
+        <v>99</v>
+      </c>
+      <c r="G45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="J45">
+        <v>1500</v>
+      </c>
+      <c r="K45">
+        <v>3000</v>
+      </c>
+      <c r="L45" t="s">
+        <v>36</v>
+      </c>
+      <c r="M45" t="s">
+        <v>119</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>100</v>
+      </c>
+      <c r="R45">
+        <v>970</v>
+      </c>
+      <c r="S45">
+        <v>970</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>13</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>3490</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>155</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" t="s">
+        <v>98</v>
+      </c>
+      <c r="E46" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" t="s">
+        <v>99</v>
+      </c>
+      <c r="G46" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46">
+        <v>2.5</v>
+      </c>
+      <c r="J46">
+        <v>1500</v>
+      </c>
+      <c r="K46">
+        <v>3000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>100</v>
+      </c>
+      <c r="R46">
+        <v>526</v>
+      </c>
+      <c r="S46">
+        <v>526</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>6</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>3540</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>156</v>
+      </c>
+      <c r="B47" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" t="s">
+        <v>157</v>
+      </c>
+      <c r="E47" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" t="s">
+        <v>99</v>
+      </c>
+      <c r="G47" t="s">
+        <v>138</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47">
+        <v>5</v>
+      </c>
+      <c r="J47">
+        <v>1500</v>
+      </c>
+      <c r="K47">
+        <v>3000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>104</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>100</v>
+      </c>
+      <c r="R47">
+        <v>354</v>
+      </c>
+      <c r="S47">
+        <v>354</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>2</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>1170</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>158</v>
+      </c>
+      <c r="B48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" t="s">
+        <v>159</v>
+      </c>
+      <c r="E48" t="s">
+        <v>48</v>
+      </c>
+      <c r="F48" t="s">
+        <v>99</v>
+      </c>
+      <c r="G48" t="s">
+        <v>53</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>4</v>
+      </c>
+      <c r="J48">
+        <v>1500</v>
+      </c>
+      <c r="K48">
+        <v>3000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>100</v>
+      </c>
+      <c r="R48">
+        <v>142</v>
+      </c>
+      <c r="S48">
+        <v>142</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>2170</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>160</v>
+      </c>
+      <c r="B49" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" t="s">
+        <v>99</v>
+      </c>
+      <c r="G49" t="s">
+        <v>53</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>4</v>
+      </c>
+      <c r="J49">
+        <v>1500</v>
+      </c>
+      <c r="K49">
+        <v>3000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>36</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>100</v>
+      </c>
+      <c r="R49">
+        <v>142</v>
+      </c>
+      <c r="S49">
+        <v>142</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>1</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>2170</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" t="s">
+        <v>162</v>
+      </c>
+      <c r="E50" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>1.5</v>
+      </c>
+      <c r="J50">
+        <v>1250</v>
+      </c>
+      <c r="L50" t="s">
+        <v>36</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>100</v>
+      </c>
+      <c r="R50">
+        <v>1275</v>
+      </c>
+      <c r="S50">
+        <v>1275</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>3590</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" t="s">
+        <v>164</v>
+      </c>
+      <c r="E51" t="s">
+        <v>48</v>
+      </c>
+      <c r="F51" t="s">
+        <v>99</v>
+      </c>
+      <c r="G51" t="s">
+        <v>53</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>1250</v>
+      </c>
+      <c r="K51">
+        <v>2500</v>
+      </c>
+      <c r="L51" t="s">
+        <v>36</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>100</v>
+      </c>
+      <c r="R51">
+        <v>49</v>
+      </c>
+      <c r="S51">
+        <v>49</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>2</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>2170</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E52" t="s">
+        <v>48</v>
+      </c>
+      <c r="F52" t="s">
+        <v>99</v>
+      </c>
+      <c r="G52" t="s">
+        <v>53</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>1250</v>
+      </c>
+      <c r="K52">
+        <v>2500</v>
+      </c>
+      <c r="L52" t="s">
+        <v>36</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>100</v>
+      </c>
+      <c r="R52">
+        <v>49</v>
+      </c>
+      <c r="S52">
+        <v>49</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>2</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>2170</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>106.33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" t="s">
+        <v>167</v>
+      </c>
+      <c r="E53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53" t="s">
+        <v>99</v>
+      </c>
+      <c r="G53" t="s">
+        <v>53</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>3</v>
+      </c>
+      <c r="J53">
+        <v>1500</v>
+      </c>
+      <c r="K53">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>36</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>100</v>
+      </c>
+      <c r="R53">
+        <v>210</v>
+      </c>
+      <c r="S53">
+        <v>210</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>2</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>2170</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" t="s">
+        <v>169</v>
+      </c>
+      <c r="E54" t="s">
+        <v>48</v>
+      </c>
+      <c r="F54" t="s">
+        <v>99</v>
+      </c>
+      <c r="G54" t="s">
+        <v>53</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>6</v>
+      </c>
+      <c r="J54">
+        <v>1250</v>
+      </c>
+      <c r="K54">
+        <v>2500</v>
+      </c>
+      <c r="L54" t="s">
+        <v>36</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>100</v>
+      </c>
+      <c r="R54">
+        <v>148</v>
+      </c>
+      <c r="S54">
+        <v>148</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>1</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>2170</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>321.16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>170</v>
+      </c>
+      <c r="B55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" t="s">
+        <v>48</v>
+      </c>
+      <c r="F55" t="s">
+        <v>99</v>
+      </c>
+      <c r="G55" t="s">
+        <v>53</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55">
+        <v>1500</v>
+      </c>
+      <c r="K55">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>36</v>
+      </c>
+      <c r="M55" t="s">
+        <v>172</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>115</v>
+      </c>
+      <c r="P55" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>100</v>
+      </c>
+      <c r="R55">
+        <v>283</v>
+      </c>
+      <c r="S55">
+        <v>283</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>1</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>2170</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>173</v>
+      </c>
+      <c r="B56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" t="s">
+        <v>97</v>
+      </c>
+      <c r="D56" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56" t="s">
+        <v>99</v>
+      </c>
+      <c r="G56" t="s">
+        <v>53</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <v>1500</v>
+      </c>
+      <c r="K56">
+        <v>3000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>36</v>
+      </c>
+      <c r="M56" t="s">
+        <v>172</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>115</v>
+      </c>
+      <c r="P56" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>100</v>
+      </c>
+      <c r="R56">
+        <v>283</v>
+      </c>
+      <c r="S56">
+        <v>283</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>1</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>2170</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>174</v>
+      </c>
+      <c r="B57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" t="s">
+        <v>175</v>
+      </c>
+      <c r="E57" t="s">
+        <v>48</v>
+      </c>
+      <c r="F57" t="s">
+        <v>99</v>
+      </c>
+      <c r="G57" t="s">
+        <v>138</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>3</v>
+      </c>
+      <c r="J57">
+        <v>1500</v>
+      </c>
+      <c r="K57">
+        <v>3000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>36</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>100</v>
+      </c>
+      <c r="R57">
+        <v>212</v>
+      </c>
+      <c r="S57">
+        <v>212</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>2</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>1320</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>176</v>
+      </c>
+      <c r="B58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" t="s">
+        <v>99</v>
+      </c>
+      <c r="G58" t="s">
+        <v>53</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <v>1500</v>
+      </c>
+      <c r="K58">
+        <v>3000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>36</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>100</v>
+      </c>
+      <c r="R58">
+        <v>212</v>
+      </c>
+      <c r="S58">
+        <v>212</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>6</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>2170</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>178</v>
+      </c>
+      <c r="B59" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" t="s">
+        <v>179</v>
+      </c>
+      <c r="E59" t="s">
+        <v>48</v>
+      </c>
+      <c r="F59" t="s">
+        <v>99</v>
+      </c>
+      <c r="G59" t="s">
+        <v>53</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>6</v>
+      </c>
+      <c r="J59">
+        <v>1000</v>
+      </c>
+      <c r="K59">
+        <v>2000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>36</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>100</v>
+      </c>
+      <c r="R59">
+        <v>567</v>
+      </c>
+      <c r="S59">
+        <v>567</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>6</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2220</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>180</v>
+      </c>
+      <c r="B60" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" t="s">
+        <v>97</v>
+      </c>
+      <c r="D60" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" t="s">
+        <v>48</v>
+      </c>
+      <c r="F60" t="s">
+        <v>99</v>
+      </c>
+      <c r="G60" t="s">
+        <v>53</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>6</v>
+      </c>
+      <c r="J60">
+        <v>1000</v>
+      </c>
+      <c r="K60">
+        <v>2000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>36</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>100</v>
+      </c>
+      <c r="R60">
+        <v>567</v>
+      </c>
+      <c r="S60">
+        <v>567</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>6</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>2220</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>181</v>
+      </c>
+      <c r="B61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61" t="s">
+        <v>175</v>
+      </c>
+      <c r="E61" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" t="s">
+        <v>99</v>
+      </c>
+      <c r="G61" t="s">
+        <v>138</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>3</v>
+      </c>
+      <c r="J61">
+        <v>1500</v>
+      </c>
+      <c r="K61">
+        <v>3000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>36</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>100</v>
+      </c>
+      <c r="R61">
+        <v>319</v>
+      </c>
+      <c r="S61">
+        <v>319</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>3</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>1370</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62" t="s">
+        <v>183</v>
+      </c>
+      <c r="E62" t="s">
+        <v>48</v>
+      </c>
+      <c r="F62" t="s">
+        <v>99</v>
+      </c>
+      <c r="G62" t="s">
+        <v>53</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+      <c r="J62">
+        <v>1250</v>
+      </c>
+      <c r="K62">
+        <v>2500</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>100</v>
+      </c>
+      <c r="R62">
+        <v>197</v>
+      </c>
+      <c r="S62">
+        <v>197</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>4</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>2170</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" t="s">
+        <v>110</v>
+      </c>
+      <c r="C63" t="s">
+        <v>97</v>
+      </c>
+      <c r="D63" t="s">
+        <v>183</v>
+      </c>
+      <c r="E63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F63" t="s">
+        <v>99</v>
+      </c>
+      <c r="G63" t="s">
+        <v>53</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>1250</v>
+      </c>
+      <c r="K63">
+        <v>2500</v>
+      </c>
+      <c r="L63" t="s">
+        <v>36</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>100</v>
+      </c>
+      <c r="R63">
+        <v>246</v>
+      </c>
+      <c r="S63">
+        <v>246</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>5</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>2170</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" t="s">
+        <v>97</v>
+      </c>
+      <c r="D64" t="s">
+        <v>135</v>
+      </c>
+      <c r="E64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" t="s">
+        <v>99</v>
+      </c>
+      <c r="G64" t="s">
+        <v>53</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>0.8</v>
+      </c>
+      <c r="J64">
+        <v>1000</v>
+      </c>
+      <c r="K64">
+        <v>2000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>36</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>100</v>
+      </c>
+      <c r="R64">
+        <v>1498</v>
+      </c>
+      <c r="S64">
+        <v>1498</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>1</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>2370</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" t="s">
+        <v>97</v>
+      </c>
+      <c r="D65" t="s">
+        <v>135</v>
+      </c>
+      <c r="E65" t="s">
+        <v>48</v>
+      </c>
+      <c r="F65" t="s">
+        <v>99</v>
+      </c>
+      <c r="G65" t="s">
+        <v>53</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>0.8</v>
+      </c>
+      <c r="J65">
+        <v>1000</v>
+      </c>
+      <c r="K65">
+        <v>2000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>36</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>100</v>
+      </c>
+      <c r="R65">
+        <v>1498</v>
+      </c>
+      <c r="S65">
+        <v>1498</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>1</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>2370</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>187</v>
+      </c>
+      <c r="B66" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" t="s">
+        <v>97</v>
+      </c>
+      <c r="D66" t="s">
+        <v>188</v>
+      </c>
+      <c r="E66" t="s">
+        <v>48</v>
+      </c>
+      <c r="F66" t="s">
+        <v>99</v>
+      </c>
+      <c r="G66" t="s">
+        <v>53</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>5</v>
+      </c>
+      <c r="J66">
+        <v>1500</v>
+      </c>
+      <c r="K66">
+        <v>3000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>36</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>100</v>
+      </c>
+      <c r="R66">
+        <v>354</v>
+      </c>
+      <c r="S66">
+        <v>354</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>1</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>2220</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" t="s">
+        <v>110</v>
+      </c>
+      <c r="C67" t="s">
+        <v>97</v>
+      </c>
+      <c r="D67" t="s">
+        <v>122</v>
+      </c>
+      <c r="E67" t="s">
+        <v>48</v>
+      </c>
+      <c r="F67" t="s">
+        <v>99</v>
+      </c>
+      <c r="G67" t="s">
+        <v>53</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>2000</v>
+      </c>
+      <c r="K67">
+        <v>4000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>36</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>100</v>
+      </c>
+      <c r="R67">
+        <v>126</v>
+      </c>
+      <c r="S67">
+        <v>126</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>1</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>2190</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" t="s">
+        <v>97</v>
+      </c>
+      <c r="D68" t="s">
+        <v>154</v>
+      </c>
+      <c r="E68" t="s">
+        <v>48</v>
+      </c>
+      <c r="F68" t="s">
+        <v>99</v>
+      </c>
+      <c r="G68" t="s">
+        <v>34</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+      <c r="J68">
+        <v>1500</v>
+      </c>
+      <c r="K68">
+        <v>3000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>36</v>
+      </c>
+      <c r="M68" t="s">
+        <v>119</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>100</v>
+      </c>
+      <c r="R68">
+        <v>1010</v>
+      </c>
+      <c r="S68">
+        <v>1010</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>14</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>3540</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>191</v>
+      </c>
+      <c r="B69" t="s">
+        <v>110</v>
+      </c>
+      <c r="C69" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69" t="s">
+        <v>192</v>
+      </c>
+      <c r="E69" t="s">
+        <v>48</v>
+      </c>
+      <c r="F69" t="s">
+        <v>99</v>
+      </c>
+      <c r="G69" t="s">
+        <v>34</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69">
+        <v>1500</v>
+      </c>
+      <c r="K69">
+        <v>3000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>36</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>100</v>
+      </c>
+      <c r="R69">
+        <v>283</v>
+      </c>
+      <c r="S69">
+        <v>283</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>4</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>3540</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" t="s">
+        <v>194</v>
+      </c>
+      <c r="E70" t="s">
+        <v>48</v>
+      </c>
+      <c r="F70" t="s">
+        <v>33</v>
+      </c>
+      <c r="G70" t="s">
+        <v>195</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>0.8</v>
+      </c>
+      <c r="J70">
+        <v>1000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>75</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>196</v>
+      </c>
+      <c r="P70" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>100</v>
+      </c>
+      <c r="R70">
+        <v>1585</v>
+      </c>
+      <c r="S70">
+        <v>1585</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>1</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>2370</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>197</v>
+      </c>
+      <c r="B71" t="s">
+        <v>110</v>
+      </c>
+      <c r="C71" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" t="s">
+        <v>198</v>
+      </c>
+      <c r="E71" t="s">
+        <v>48</v>
+      </c>
+      <c r="F71" t="s">
+        <v>99</v>
+      </c>
+      <c r="G71" t="s">
+        <v>138</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>1.5</v>
+      </c>
+      <c r="J71">
+        <v>1500</v>
+      </c>
+      <c r="K71">
+        <v>3000</v>
+      </c>
+      <c r="L71" t="s">
+        <v>36</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>100</v>
+      </c>
+      <c r="R71">
+        <v>212</v>
+      </c>
+      <c r="S71">
+        <v>212</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>1</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>1320</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>199</v>
+      </c>
+      <c r="B72" t="s">
+        <v>110</v>
+      </c>
+      <c r="C72" t="s">
+        <v>97</v>
+      </c>
+      <c r="D72" t="s">
+        <v>200</v>
+      </c>
+      <c r="E72" t="s">
+        <v>48</v>
+      </c>
+      <c r="F72" t="s">
+        <v>99</v>
+      </c>
+      <c r="G72" t="s">
+        <v>53</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>3</v>
+      </c>
+      <c r="J72">
+        <v>1250</v>
+      </c>
+      <c r="K72">
+        <v>2500</v>
+      </c>
+      <c r="L72" t="s">
+        <v>36</v>
+      </c>
+      <c r="M72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>100</v>
+      </c>
+      <c r="R72">
+        <v>74</v>
+      </c>
+      <c r="S72">
+        <v>74</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>1</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>2170</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>160.58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>201</v>
+      </c>
+      <c r="B73" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D73" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F73" t="s">
+        <v>99</v>
+      </c>
+      <c r="G73" t="s">
+        <v>34</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>2.5</v>
+      </c>
+      <c r="J73">
+        <v>1500</v>
+      </c>
+      <c r="K73">
+        <v>3000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>36</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>100</v>
+      </c>
+      <c r="R73">
+        <v>540</v>
+      </c>
+      <c r="S73">
+        <v>540</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>6</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>3540</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>202</v>
+      </c>
+      <c r="B74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74" t="s">
+        <v>97</v>
+      </c>
+      <c r="D74" t="s">
+        <v>98</v>
+      </c>
+      <c r="E74" t="s">
+        <v>48</v>
+      </c>
+      <c r="F74" t="s">
+        <v>99</v>
+      </c>
+      <c r="G74" t="s">
+        <v>34</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>2.5</v>
+      </c>
+      <c r="J74">
+        <v>1500</v>
+      </c>
+      <c r="K74">
+        <v>3000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>36</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>100</v>
+      </c>
+      <c r="R74">
+        <v>520</v>
+      </c>
+      <c r="S74">
+        <v>520</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>6</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>3540</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>203</v>
+      </c>
+      <c r="B75" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75" t="s">
+        <v>97</v>
+      </c>
+      <c r="D75" t="s">
+        <v>98</v>
+      </c>
+      <c r="E75" t="s">
+        <v>48</v>
+      </c>
+      <c r="F75" t="s">
+        <v>99</v>
+      </c>
+      <c r="G75" t="s">
+        <v>34</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>2.5</v>
+      </c>
+      <c r="J75">
+        <v>1500</v>
+      </c>
+      <c r="K75">
+        <v>3000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>36</v>
+      </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>100</v>
+      </c>
+      <c r="R75">
+        <v>530</v>
+      </c>
+      <c r="S75">
+        <v>530</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>6</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>3540</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>204</v>
+      </c>
+      <c r="B76" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" t="s">
+        <v>97</v>
+      </c>
+      <c r="D76" t="s">
+        <v>98</v>
+      </c>
+      <c r="E76" t="s">
+        <v>48</v>
+      </c>
+      <c r="F76" t="s">
+        <v>99</v>
+      </c>
+      <c r="G76" t="s">
+        <v>34</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>2.5</v>
+      </c>
+      <c r="J76">
+        <v>1500</v>
+      </c>
+      <c r="K76">
+        <v>3000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>36</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>100</v>
+      </c>
+      <c r="R76">
+        <v>526</v>
+      </c>
+      <c r="S76">
+        <v>526</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>6</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>3540</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>205</v>
+      </c>
+      <c r="B77" t="s">
+        <v>110</v>
+      </c>
+      <c r="C77" t="s">
+        <v>97</v>
+      </c>
+      <c r="D77" t="s">
+        <v>206</v>
+      </c>
+      <c r="E77" t="s">
+        <v>48</v>
+      </c>
+      <c r="F77" t="s">
+        <v>99</v>
+      </c>
+      <c r="G77" t="s">
+        <v>34</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>3</v>
+      </c>
+      <c r="J77">
+        <v>1500</v>
+      </c>
+      <c r="K77">
+        <v>3000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>36</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>100</v>
+      </c>
+      <c r="R77">
+        <v>212</v>
+      </c>
+      <c r="S77">
+        <v>212</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>1</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>3490</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>207</v>
+      </c>
+      <c r="B78" t="s">
+        <v>110</v>
+      </c>
+      <c r="C78" t="s">
+        <v>97</v>
+      </c>
+      <c r="D78" t="s">
+        <v>206</v>
+      </c>
+      <c r="E78" t="s">
+        <v>48</v>
+      </c>
+      <c r="F78" t="s">
+        <v>99</v>
+      </c>
+      <c r="G78" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>3</v>
+      </c>
+      <c r="J78">
+        <v>1500</v>
+      </c>
+      <c r="K78">
+        <v>3000</v>
+      </c>
+      <c r="L78" t="s">
+        <v>36</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>100</v>
+      </c>
+      <c r="R78">
+        <v>212</v>
+      </c>
+      <c r="S78">
+        <v>212</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>1</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>3490</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>208</v>
+      </c>
+      <c r="B79" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79" t="s">
+        <v>97</v>
+      </c>
+      <c r="D79" t="s">
+        <v>209</v>
+      </c>
+      <c r="E79" t="s">
+        <v>48</v>
+      </c>
+      <c r="F79" t="s">
+        <v>99</v>
+      </c>
+      <c r="G79" t="s">
+        <v>53</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>4</v>
+      </c>
+      <c r="J79">
+        <v>1000</v>
+      </c>
+      <c r="K79">
+        <v>2000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>36</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>100</v>
+      </c>
+      <c r="R79">
+        <v>315</v>
+      </c>
+      <c r="S79">
+        <v>315</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>5</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>2220</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>210</v>
+      </c>
+      <c r="B80" t="s">
+        <v>110</v>
+      </c>
+      <c r="C80" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" t="s">
+        <v>48</v>
+      </c>
+      <c r="F80" t="s">
+        <v>99</v>
+      </c>
+      <c r="G80" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>1.5</v>
+      </c>
+      <c r="J80">
+        <v>1250</v>
+      </c>
+      <c r="K80">
+        <v>2500</v>
+      </c>
+      <c r="L80" t="s">
+        <v>36</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>100</v>
+      </c>
+      <c r="R80">
+        <v>295</v>
+      </c>
+      <c r="S80">
+        <v>295</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>8</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>2220</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>654.9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>212</v>
+      </c>
+      <c r="B81" t="s">
+        <v>110</v>
+      </c>
+      <c r="C81" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" t="s">
+        <v>48</v>
+      </c>
+      <c r="F81" t="s">
+        <v>99</v>
+      </c>
+      <c r="G81" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>5</v>
+      </c>
+      <c r="J81">
+        <v>1000</v>
+      </c>
+      <c r="K81">
+        <v>2000</v>
+      </c>
+      <c r="L81" t="s">
+        <v>104</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>100</v>
+      </c>
+      <c r="R81">
+        <v>944</v>
+      </c>
+      <c r="S81">
+        <v>944</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>1</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>2020</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>213</v>
+      </c>
+      <c r="B82" t="s">
+        <v>110</v>
+      </c>
+      <c r="C82" t="s">
+        <v>97</v>
+      </c>
+      <c r="D82" t="s">
+        <v>179</v>
+      </c>
+      <c r="E82" t="s">
+        <v>48</v>
+      </c>
+      <c r="F82" t="s">
+        <v>99</v>
+      </c>
+      <c r="G82" t="s">
+        <v>53</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>6</v>
+      </c>
+      <c r="J82">
+        <v>1000</v>
+      </c>
+      <c r="K82">
+        <v>2000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>36</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>100</v>
+      </c>
+      <c r="R82">
+        <v>189</v>
+      </c>
+      <c r="S82">
+        <v>189</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>2</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>2170</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>410.13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>214</v>
+      </c>
+      <c r="B83" t="s">
+        <v>110</v>
+      </c>
+      <c r="C83" t="s">
+        <v>97</v>
+      </c>
+      <c r="D83" t="s">
+        <v>215</v>
+      </c>
+      <c r="E83" t="s">
+        <v>48</v>
+      </c>
+      <c r="F83" t="s">
+        <v>99</v>
+      </c>
+      <c r="G83" t="s">
+        <v>53</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>1.5</v>
+      </c>
+      <c r="J83">
+        <v>1000</v>
+      </c>
+      <c r="K83">
+        <v>2000</v>
+      </c>
+      <c r="L83" t="s">
+        <v>36</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>100</v>
+      </c>
+      <c r="R83">
+        <v>260</v>
+      </c>
+      <c r="S83">
+        <v>260</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>11</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>2220</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>577.2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>216</v>
+      </c>
+      <c r="B84" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" t="s">
+        <v>97</v>
+      </c>
+      <c r="D84" t="s">
+        <v>217</v>
+      </c>
+      <c r="E84" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" t="s">
+        <v>99</v>
+      </c>
+      <c r="G84" t="s">
+        <v>34</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>1500</v>
+      </c>
+      <c r="K84">
+        <v>3000</v>
+      </c>
+      <c r="L84" t="s">
+        <v>36</v>
+      </c>
+      <c r="M84" t="s">
+        <v>119</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>100</v>
+      </c>
+      <c r="R84">
+        <v>1224</v>
+      </c>
+      <c r="S84">
+        <v>1224</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>34</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>3540</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>218</v>
+      </c>
+      <c r="B85" t="s">
+        <v>110</v>
+      </c>
+      <c r="C85" t="s">
+        <v>97</v>
+      </c>
+      <c r="D85" t="s">
+        <v>183</v>
+      </c>
+      <c r="E85" t="s">
+        <v>48</v>
+      </c>
+      <c r="F85" t="s">
+        <v>99</v>
+      </c>
+      <c r="G85" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>2</v>
+      </c>
+      <c r="J85">
+        <v>1250</v>
+      </c>
+      <c r="K85">
+        <v>2500</v>
+      </c>
+      <c r="L85" t="s">
+        <v>36</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>100</v>
+      </c>
+      <c r="R85">
+        <v>197</v>
+      </c>
+      <c r="S85">
+        <v>197</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>4</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>2170</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>427.49</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>219</v>
+      </c>
+      <c r="B86" t="s">
+        <v>110</v>
+      </c>
+      <c r="C86" t="s">
+        <v>97</v>
+      </c>
+      <c r="D86" t="s">
+        <v>220</v>
+      </c>
+      <c r="E86" t="s">
+        <v>48</v>
+      </c>
+      <c r="F86" t="s">
+        <v>99</v>
+      </c>
+      <c r="G86" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
+        <v>1500</v>
+      </c>
+      <c r="K86">
+        <v>3000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>36</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>100</v>
+      </c>
+      <c r="R86">
+        <v>35</v>
+      </c>
+      <c r="S86">
+        <v>35</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>1</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>3490</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>221</v>
+      </c>
+      <c r="B87" t="s">
+        <v>110</v>
+      </c>
+      <c r="C87" t="s">
+        <v>97</v>
+      </c>
+      <c r="D87" t="s">
+        <v>220</v>
+      </c>
+      <c r="E87" t="s">
+        <v>48</v>
+      </c>
+      <c r="F87" t="s">
+        <v>99</v>
+      </c>
+      <c r="G87" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>1500</v>
+      </c>
+      <c r="K87">
+        <v>3000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>36</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>100</v>
+      </c>
+      <c r="R87">
+        <v>177</v>
+      </c>
+      <c r="S87">
+        <v>177</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>5</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>3490</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>617.73</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>222</v>
+      </c>
+      <c r="B88" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D88" t="s">
+        <v>223</v>
+      </c>
+      <c r="E88" t="s">
+        <v>48</v>
+      </c>
+      <c r="F88" t="s">
+        <v>33</v>
+      </c>
+      <c r="G88" t="s">
+        <v>224</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88">
+        <v>0.6</v>
+      </c>
+      <c r="J88">
+        <v>1000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>75</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>100</v>
+      </c>
+      <c r="R88">
+        <v>745</v>
+      </c>
+      <c r="S88">
+        <v>745</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>1</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>2290</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>1706.05</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>225</v>
+      </c>
+      <c r="B89" t="s">
+        <v>96</v>
+      </c>
+      <c r="C89" t="s">
+        <v>97</v>
+      </c>
+      <c r="D89" t="s">
+        <v>226</v>
+      </c>
+      <c r="E89" t="s">
+        <v>48</v>
+      </c>
+      <c r="F89" t="s">
+        <v>99</v>
+      </c>
+      <c r="G89" t="s">
+        <v>138</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89">
+        <v>1.5</v>
+      </c>
+      <c r="J89">
+        <v>1500</v>
+      </c>
+      <c r="K89">
+        <v>3000</v>
+      </c>
+      <c r="L89" t="s">
+        <v>75</v>
+      </c>
+      <c r="M89" t="s">
+        <v>119</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>100</v>
+      </c>
+      <c r="R89">
+        <v>916</v>
+      </c>
+      <c r="S89">
+        <v>916</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>18</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>1320</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>227</v>
+      </c>
+      <c r="B90" t="s">
+        <v>110</v>
+      </c>
+      <c r="C90" t="s">
+        <v>97</v>
+      </c>
+      <c r="D90" t="s">
+        <v>206</v>
+      </c>
+      <c r="E90" t="s">
+        <v>48</v>
+      </c>
+      <c r="F90" t="s">
+        <v>99</v>
+      </c>
+      <c r="G90" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>3</v>
+      </c>
+      <c r="J90">
+        <v>1500</v>
+      </c>
+      <c r="K90">
+        <v>3000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>36</v>
+      </c>
+      <c r="M90" t="s">
+        <v>37</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>100</v>
+      </c>
+      <c r="R90">
+        <v>319</v>
+      </c>
+      <c r="S90">
+        <v>319</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>1</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>3540</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>228</v>
+      </c>
+      <c r="B91" t="s">
+        <v>110</v>
+      </c>
+      <c r="C91" t="s">
+        <v>97</v>
+      </c>
+      <c r="D91" t="s">
+        <v>206</v>
+      </c>
+      <c r="E91" t="s">
+        <v>48</v>
+      </c>
+      <c r="F91" t="s">
+        <v>99</v>
+      </c>
+      <c r="G91" t="s">
+        <v>34</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91">
+        <v>3</v>
+      </c>
+      <c r="J91">
+        <v>1500</v>
+      </c>
+      <c r="K91">
+        <v>3000</v>
+      </c>
+      <c r="L91" t="s">
+        <v>36</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>100</v>
+      </c>
+      <c r="R91">
+        <v>212</v>
+      </c>
+      <c r="S91">
+        <v>212</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>1</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>3490</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>229</v>
+      </c>
+      <c r="B92" t="s">
+        <v>110</v>
+      </c>
+      <c r="C92" t="s">
+        <v>97</v>
+      </c>
+      <c r="D92" t="s">
+        <v>206</v>
+      </c>
+      <c r="E92" t="s">
+        <v>48</v>
+      </c>
+      <c r="F92" t="s">
+        <v>99</v>
+      </c>
+      <c r="G92" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92">
+        <v>3</v>
+      </c>
+      <c r="J92">
+        <v>1500</v>
+      </c>
+      <c r="K92">
+        <v>3000</v>
+      </c>
+      <c r="L92" t="s">
+        <v>36</v>
+      </c>
+      <c r="M92" t="s">
+        <v>37</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>38</v>
+      </c>
+      <c r="P92" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>100</v>
+      </c>
+      <c r="R92">
+        <v>212</v>
+      </c>
+      <c r="S92">
+        <v>212</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>1</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>3490</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>230</v>
+      </c>
+      <c r="B93" t="s">
+        <v>110</v>
+      </c>
+      <c r="C93" t="s">
+        <v>97</v>
+      </c>
+      <c r="D93" t="s">
+        <v>206</v>
+      </c>
+      <c r="E93" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" t="s">
+        <v>99</v>
+      </c>
+      <c r="G93" t="s">
+        <v>34</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93">
+        <v>3</v>
+      </c>
+      <c r="J93">
+        <v>1500</v>
+      </c>
+      <c r="K93">
+        <v>3000</v>
+      </c>
+      <c r="L93" t="s">
+        <v>36</v>
+      </c>
+      <c r="M93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" t="s">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>100</v>
+      </c>
+      <c r="R93">
+        <v>319</v>
+      </c>
+      <c r="S93">
+        <v>319</v>
+      </c>
+      <c r="T93" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93">
+        <v>1</v>
+      </c>
+      <c r="V93" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93">
+        <v>3540</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA93">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>231</v>
+      </c>
+      <c r="B94" t="s">
+        <v>110</v>
+      </c>
+      <c r="C94" t="s">
+        <v>97</v>
+      </c>
+      <c r="D94" t="s">
+        <v>232</v>
+      </c>
+      <c r="E94" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" t="s">
+        <v>99</v>
+      </c>
+      <c r="G94" t="s">
+        <v>53</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94">
+        <v>4</v>
+      </c>
+      <c r="J94">
+        <v>1000</v>
+      </c>
+      <c r="K94">
+        <v>2000</v>
+      </c>
+      <c r="L94" t="s">
+        <v>36</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
+      </c>
+      <c r="N94" t="s">
+        <v>37</v>
+      </c>
+      <c r="O94" t="s">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>100</v>
+      </c>
+      <c r="R94">
+        <v>63</v>
+      </c>
+      <c r="S94">
+        <v>63</v>
+      </c>
+      <c r="T94" t="s">
+        <v>41</v>
+      </c>
+      <c r="U94">
+        <v>1</v>
+      </c>
+      <c r="V94" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94">
+        <v>2170</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA94">
+        <v>136.71</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>233</v>
+      </c>
+      <c r="B95" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95" t="s">
+        <v>97</v>
+      </c>
+      <c r="D95" t="s">
+        <v>234</v>
+      </c>
+      <c r="E95" t="s">
+        <v>48</v>
+      </c>
+      <c r="F95" t="s">
+        <v>99</v>
+      </c>
+      <c r="G95" t="s">
+        <v>53</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95">
+        <v>1.2</v>
+      </c>
+      <c r="J95">
+        <v>1250</v>
+      </c>
+      <c r="K95">
+        <v>2500</v>
+      </c>
+      <c r="L95" t="s">
+        <v>36</v>
+      </c>
+      <c r="M95" t="s">
+        <v>119</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>100</v>
+      </c>
+      <c r="R95">
+        <v>568</v>
+      </c>
+      <c r="S95">
+        <v>568</v>
+      </c>
+      <c r="T95" t="s">
+        <v>41</v>
+      </c>
+      <c r="U95">
+        <v>19</v>
+      </c>
+      <c r="V95" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95">
+        <v>2170</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA95">
+        <v>1232.56</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>235</v>
+      </c>
+      <c r="B96" t="s">
+        <v>96</v>
+      </c>
+      <c r="C96" t="s">
+        <v>97</v>
+      </c>
+      <c r="D96" t="s">
+        <v>236</v>
+      </c>
+      <c r="E96" t="s">
+        <v>48</v>
+      </c>
+      <c r="F96" t="s">
+        <v>99</v>
+      </c>
+      <c r="G96" t="s">
+        <v>53</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96">
+        <v>1.2</v>
+      </c>
+      <c r="J96">
+        <v>1500</v>
+      </c>
+      <c r="K96">
+        <v>3000</v>
+      </c>
+      <c r="L96" t="s">
+        <v>36</v>
+      </c>
+      <c r="M96" t="s">
+        <v>237</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
+      </c>
+      <c r="P96" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>100</v>
+      </c>
+      <c r="R96">
+        <v>660</v>
+      </c>
+      <c r="S96">
+        <v>660</v>
+      </c>
+      <c r="T96" t="s">
+        <v>41</v>
+      </c>
+      <c r="U96">
+        <v>15</v>
+      </c>
+      <c r="V96" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X96">
+        <v>2170</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA96">
+        <v>1432.2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>238</v>
+      </c>
+      <c r="B97" t="s">
+        <v>110</v>
+      </c>
+      <c r="C97" t="s">
+        <v>97</v>
+      </c>
+      <c r="D97" t="s">
+        <v>239</v>
+      </c>
+      <c r="E97" t="s">
+        <v>48</v>
+      </c>
+      <c r="F97" t="s">
+        <v>99</v>
+      </c>
+      <c r="G97" t="s">
+        <v>138</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97">
+        <v>1.5</v>
+      </c>
+      <c r="J97">
+        <v>1250</v>
+      </c>
+      <c r="K97">
+        <v>2500</v>
+      </c>
+      <c r="L97" t="s">
+        <v>36</v>
+      </c>
+      <c r="M97" t="s">
+        <v>37</v>
+      </c>
+      <c r="N97" t="s">
+        <v>37</v>
+      </c>
+      <c r="O97" t="s">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>100</v>
+      </c>
+      <c r="R97">
+        <v>148</v>
+      </c>
+      <c r="S97">
+        <v>148</v>
+      </c>
+      <c r="T97" t="s">
+        <v>41</v>
+      </c>
+      <c r="U97">
+        <v>4</v>
+      </c>
+      <c r="V97" t="s">
+        <v>43</v>
+      </c>
+      <c r="W97" t="s">
+        <v>43</v>
+      </c>
+      <c r="X97">
+        <v>1320</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA97">
+        <v>195.36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>240</v>
+      </c>
+      <c r="B98" t="s">
+        <v>110</v>
+      </c>
+      <c r="C98" t="s">
+        <v>97</v>
+      </c>
+      <c r="D98" t="s">
+        <v>239</v>
+      </c>
+      <c r="E98" t="s">
+        <v>48</v>
+      </c>
+      <c r="F98" t="s">
+        <v>99</v>
+      </c>
+      <c r="G98" t="s">
+        <v>138</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98">
+        <v>1.5</v>
+      </c>
+      <c r="J98">
+        <v>1250</v>
+      </c>
+      <c r="K98">
+        <v>2500</v>
+      </c>
+      <c r="L98" t="s">
+        <v>36</v>
+      </c>
+      <c r="M98" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" t="s">
+        <v>38</v>
+      </c>
+      <c r="P98" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>100</v>
+      </c>
+      <c r="R98">
+        <v>148</v>
+      </c>
+      <c r="S98">
+        <v>148</v>
+      </c>
+      <c r="T98" t="s">
+        <v>41</v>
+      </c>
+      <c r="U98">
+        <v>4</v>
+      </c>
+      <c r="V98" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98">
+        <v>1320</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA98">
+        <v>195.36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>241</v>
+      </c>
+      <c r="B99" t="s">
+        <v>110</v>
+      </c>
+      <c r="C99" t="s">
+        <v>97</v>
+      </c>
+      <c r="D99" t="s">
+        <v>242</v>
+      </c>
+      <c r="E99" t="s">
+        <v>48</v>
+      </c>
+      <c r="F99" t="s">
+        <v>99</v>
+      </c>
+      <c r="G99" t="s">
+        <v>53</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99">
+        <v>6</v>
+      </c>
+      <c r="J99">
+        <v>2000</v>
+      </c>
+      <c r="K99">
+        <v>4000</v>
+      </c>
+      <c r="L99" t="s">
+        <v>36</v>
+      </c>
+      <c r="M99" t="s">
+        <v>37</v>
+      </c>
+      <c r="N99" t="s">
+        <v>37</v>
+      </c>
+      <c r="O99" t="s">
+        <v>38</v>
+      </c>
+      <c r="P99" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>100</v>
+      </c>
+      <c r="R99">
+        <v>756</v>
+      </c>
+      <c r="S99">
+        <v>756</v>
+      </c>
+      <c r="T99" t="s">
+        <v>41</v>
+      </c>
+      <c r="U99">
+        <v>2</v>
+      </c>
+      <c r="V99" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99">
+        <v>2240</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA99">
+        <v>1693.44</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>243</v>
+      </c>
+      <c r="B100" t="s">
+        <v>110</v>
+      </c>
+      <c r="C100" t="s">
+        <v>97</v>
+      </c>
+      <c r="D100" t="s">
+        <v>177</v>
+      </c>
+      <c r="E100" t="s">
+        <v>48</v>
+      </c>
+      <c r="F100" t="s">
+        <v>99</v>
+      </c>
+      <c r="G100" t="s">
+        <v>53</v>
+      </c>
+      <c r="H100" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>1500</v>
+      </c>
+      <c r="K100">
+        <v>3000</v>
+      </c>
+      <c r="L100" t="s">
+        <v>36</v>
+      </c>
+      <c r="M100" t="s">
+        <v>37</v>
+      </c>
+      <c r="N100" t="s">
+        <v>37</v>
+      </c>
+      <c r="O100" t="s">
+        <v>38</v>
+      </c>
+      <c r="P100" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>100</v>
+      </c>
+      <c r="R100">
+        <v>35</v>
+      </c>
+      <c r="S100">
+        <v>35</v>
+      </c>
+      <c r="T100" t="s">
+        <v>41</v>
+      </c>
+      <c r="U100">
+        <v>1</v>
+      </c>
+      <c r="V100" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100">
+        <v>2170</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA100">
+        <v>75.95</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>244</v>
+      </c>
+      <c r="B101" t="s">
+        <v>110</v>
+      </c>
+      <c r="C101" t="s">
+        <v>97</v>
+      </c>
+      <c r="D101" t="s">
+        <v>177</v>
+      </c>
+      <c r="E101" t="s">
+        <v>48</v>
+      </c>
+      <c r="F101" t="s">
+        <v>99</v>
+      </c>
+      <c r="G101" t="s">
+        <v>53</v>
+      </c>
+      <c r="H101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>1500</v>
+      </c>
+      <c r="K101">
+        <v>3000</v>
+      </c>
+      <c r="L101" t="s">
+        <v>36</v>
+      </c>
+      <c r="M101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N101" t="s">
+        <v>37</v>
+      </c>
+      <c r="O101" t="s">
+        <v>38</v>
+      </c>
+      <c r="P101" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>100</v>
+      </c>
+      <c r="R101">
+        <v>35</v>
+      </c>
+      <c r="S101">
+        <v>35</v>
+      </c>
+      <c r="T101" t="s">
+        <v>41</v>
+      </c>
+      <c r="U101">
+        <v>1</v>
+      </c>
+      <c r="V101" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101">
+        <v>2170</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA101">
+        <v>75.95</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>245</v>
+      </c>
+      <c r="B102" t="s">
+        <v>96</v>
+      </c>
+      <c r="C102" t="s">
+        <v>97</v>
+      </c>
+      <c r="D102" t="s">
+        <v>246</v>
+      </c>
+      <c r="E102" t="s">
+        <v>48</v>
+      </c>
+      <c r="F102" t="s">
+        <v>99</v>
+      </c>
+      <c r="G102" t="s">
+        <v>224</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
+      </c>
+      <c r="J102">
+        <v>1000</v>
+      </c>
+      <c r="K102">
+        <v>2000</v>
+      </c>
+      <c r="L102" t="s">
+        <v>75</v>
+      </c>
+      <c r="M102" t="s">
+        <v>37</v>
+      </c>
+      <c r="N102" t="s">
+        <v>37</v>
+      </c>
+      <c r="O102" t="s">
+        <v>38</v>
+      </c>
+      <c r="P102" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>100</v>
+      </c>
+      <c r="R102">
+        <v>544</v>
+      </c>
+      <c r="S102">
+        <v>544</v>
+      </c>
+      <c r="T102" t="s">
+        <v>41</v>
+      </c>
+      <c r="U102">
+        <v>1</v>
+      </c>
+      <c r="V102" t="s">
+        <v>43</v>
+      </c>
+      <c r="W102" t="s">
+        <v>43</v>
+      </c>
+      <c r="X102">
+        <v>2220</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA102">
+        <v>1207.68</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>247</v>
+      </c>
+      <c r="B103" t="s">
+        <v>96</v>
+      </c>
+      <c r="C103" t="s">
+        <v>97</v>
+      </c>
+      <c r="D103" t="s">
+        <v>248</v>
+      </c>
+      <c r="E103" t="s">
+        <v>48</v>
+      </c>
+      <c r="F103" t="s">
+        <v>99</v>
+      </c>
+      <c r="G103" t="s">
+        <v>138</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103">
+        <v>1.5</v>
+      </c>
+      <c r="J103">
+        <v>1250</v>
+      </c>
+      <c r="K103">
+        <v>2500</v>
+      </c>
+      <c r="L103" t="s">
+        <v>75</v>
+      </c>
+      <c r="M103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N103" t="s">
+        <v>37</v>
+      </c>
+      <c r="O103" t="s">
+        <v>38</v>
+      </c>
+      <c r="P103" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>100</v>
+      </c>
+      <c r="R103">
+        <v>898</v>
+      </c>
+      <c r="S103">
+        <v>898</v>
+      </c>
+      <c r="T103" t="s">
+        <v>41</v>
+      </c>
+      <c r="U103">
+        <v>1</v>
+      </c>
+      <c r="V103" t="s">
+        <v>43</v>
+      </c>
+      <c r="W103" t="s">
+        <v>43</v>
+      </c>
+      <c r="X103">
+        <v>1370</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA103">
+        <v>1230.26</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>249</v>
+      </c>
+      <c r="B104" t="s">
+        <v>96</v>
+      </c>
+      <c r="C104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D104" t="s">
+        <v>250</v>
+      </c>
+      <c r="E104" t="s">
+        <v>48</v>
+      </c>
+      <c r="F104" t="s">
+        <v>99</v>
+      </c>
+      <c r="G104" t="s">
+        <v>53</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104">
+        <v>1.5</v>
+      </c>
+      <c r="J104">
+        <v>1500</v>
+      </c>
+      <c r="K104">
+        <v>3000</v>
+      </c>
+      <c r="L104" t="s">
+        <v>75</v>
+      </c>
+      <c r="M104" t="s">
+        <v>37</v>
+      </c>
+      <c r="N104" t="s">
+        <v>37</v>
+      </c>
+      <c r="O104" t="s">
+        <v>38</v>
+      </c>
+      <c r="P104" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>100</v>
+      </c>
+      <c r="R104">
+        <v>212</v>
+      </c>
+      <c r="S104">
+        <v>212</v>
+      </c>
+      <c r="T104" t="s">
+        <v>41</v>
+      </c>
+      <c r="U104">
+        <v>1</v>
+      </c>
+      <c r="V104" t="s">
+        <v>43</v>
+      </c>
+      <c r="W104" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104">
+        <v>2170</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA104">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>251</v>
+      </c>
+      <c r="B105" t="s">
+        <v>96</v>
+      </c>
+      <c r="C105" t="s">
+        <v>97</v>
+      </c>
+      <c r="D105" t="s">
+        <v>250</v>
+      </c>
+      <c r="E105" t="s">
+        <v>48</v>
+      </c>
+      <c r="F105" t="s">
+        <v>99</v>
+      </c>
+      <c r="G105" t="s">
+        <v>53</v>
+      </c>
+      <c r="H105" t="s">
+        <v>35</v>
+      </c>
+      <c r="I105">
+        <v>1.5</v>
+      </c>
+      <c r="J105">
+        <v>1500</v>
+      </c>
+      <c r="K105">
+        <v>3000</v>
+      </c>
+      <c r="L105" t="s">
+        <v>75</v>
+      </c>
+      <c r="M105" t="s">
+        <v>37</v>
+      </c>
+      <c r="N105" t="s">
+        <v>37</v>
+      </c>
+      <c r="O105" t="s">
+        <v>38</v>
+      </c>
+      <c r="P105" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>100</v>
+      </c>
+      <c r="R105">
+        <v>278</v>
+      </c>
+      <c r="S105">
+        <v>278</v>
+      </c>
+      <c r="T105" t="s">
+        <v>41</v>
+      </c>
+      <c r="U105">
+        <v>1</v>
+      </c>
+      <c r="V105" t="s">
+        <v>43</v>
+      </c>
+      <c r="W105" t="s">
+        <v>43</v>
+      </c>
+      <c r="X105">
+        <v>2220</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA105">
+        <v>617.16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>252</v>
+      </c>
+      <c r="B106" t="s">
+        <v>96</v>
+      </c>
+      <c r="C106" t="s">
+        <v>97</v>
+      </c>
+      <c r="D106" t="s">
+        <v>253</v>
+      </c>
+      <c r="E106" t="s">
+        <v>48</v>
+      </c>
+      <c r="F106" t="s">
+        <v>99</v>
+      </c>
+      <c r="G106" t="s">
+        <v>53</v>
+      </c>
+      <c r="H106" t="s">
+        <v>35</v>
+      </c>
+      <c r="I106">
+        <v>1.5</v>
+      </c>
+      <c r="J106">
+        <v>1500</v>
+      </c>
+      <c r="K106">
+        <v>3000</v>
+      </c>
+      <c r="L106" t="s">
+        <v>36</v>
+      </c>
+      <c r="M106" t="s">
+        <v>37</v>
+      </c>
+      <c r="N106" t="s">
+        <v>37</v>
+      </c>
+      <c r="O106" t="s">
+        <v>38</v>
+      </c>
+      <c r="P106" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>100</v>
+      </c>
+      <c r="R106">
+        <v>318</v>
+      </c>
+      <c r="S106">
+        <v>318</v>
+      </c>
+      <c r="T106" t="s">
+        <v>41</v>
+      </c>
+      <c r="U106">
+        <v>6</v>
+      </c>
+      <c r="V106" t="s">
+        <v>43</v>
+      </c>
+      <c r="W106" t="s">
+        <v>43</v>
+      </c>
+      <c r="X106">
+        <v>2220</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA106">
+        <v>705.96</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>254</v>
+      </c>
+      <c r="B107" t="s">
+        <v>96</v>
+      </c>
+      <c r="C107" t="s">
+        <v>97</v>
+      </c>
+      <c r="D107" t="s">
+        <v>255</v>
+      </c>
+      <c r="E107" t="s">
+        <v>48</v>
+      </c>
+      <c r="F107" t="s">
+        <v>33</v>
+      </c>
+      <c r="G107" t="s">
+        <v>138</v>
+      </c>
+      <c r="H107" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107">
+        <v>0.8</v>
+      </c>
+      <c r="J107">
+        <v>1250</v>
+      </c>
+      <c r="L107" t="s">
+        <v>75</v>
+      </c>
+      <c r="M107" t="s">
+        <v>37</v>
+      </c>
+      <c r="N107" t="s">
+        <v>37</v>
+      </c>
+      <c r="O107" t="s">
+        <v>38</v>
+      </c>
+      <c r="P107" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>100</v>
+      </c>
+      <c r="R107">
+        <v>2650</v>
+      </c>
+      <c r="S107">
+        <v>2650</v>
+      </c>
+      <c r="T107" t="s">
+        <v>41</v>
+      </c>
+      <c r="U107">
+        <v>1</v>
+      </c>
+      <c r="V107" t="s">
+        <v>43</v>
+      </c>
+      <c r="W107" t="s">
+        <v>43</v>
+      </c>
+      <c r="X107">
+        <v>1520</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA107">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>256</v>
+      </c>
+      <c r="B108" t="s">
+        <v>96</v>
+      </c>
+      <c r="C108" t="s">
+        <v>97</v>
+      </c>
+      <c r="D108" t="s">
+        <v>257</v>
+      </c>
+      <c r="E108" t="s">
+        <v>48</v>
+      </c>
+      <c r="F108" t="s">
+        <v>33</v>
+      </c>
+      <c r="G108" t="s">
+        <v>195</v>
+      </c>
+      <c r="H108" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108">
+        <v>0.8</v>
+      </c>
+      <c r="J108">
+        <v>1000</v>
+      </c>
+      <c r="L108" t="s">
+        <v>75</v>
+      </c>
+      <c r="M108" t="s">
+        <v>37</v>
+      </c>
+      <c r="N108" t="s">
+        <v>37</v>
+      </c>
+      <c r="O108" t="s">
+        <v>38</v>
+      </c>
+      <c r="P108" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>100</v>
+      </c>
+      <c r="R108">
+        <v>1000</v>
+      </c>
+      <c r="S108">
+        <v>1000</v>
+      </c>
+      <c r="T108" t="s">
+        <v>41</v>
+      </c>
+      <c r="U108">
+        <v>1</v>
+      </c>
+      <c r="V108" t="s">
+        <v>43</v>
+      </c>
+      <c r="W108" t="s">
+        <v>43</v>
+      </c>
+      <c r="X108">
+        <v>2370</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA108">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>258</v>
+      </c>
+      <c r="B109" t="s">
+        <v>110</v>
+      </c>
+      <c r="C109" t="s">
+        <v>97</v>
+      </c>
+      <c r="D109" t="s">
+        <v>211</v>
+      </c>
+      <c r="E109" t="s">
+        <v>48</v>
+      </c>
+      <c r="F109" t="s">
+        <v>99</v>
+      </c>
+      <c r="G109" t="s">
+        <v>53</v>
+      </c>
+      <c r="H109" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109">
+        <v>1.5</v>
+      </c>
+      <c r="J109">
+        <v>1250</v>
+      </c>
+      <c r="K109">
+        <v>2500</v>
+      </c>
+      <c r="L109" t="s">
+        <v>36</v>
+      </c>
+      <c r="M109" t="s">
+        <v>37</v>
+      </c>
+      <c r="N109" t="s">
+        <v>37</v>
+      </c>
+      <c r="O109" t="s">
+        <v>38</v>
+      </c>
+      <c r="P109" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>100</v>
+      </c>
+      <c r="R109">
+        <v>258</v>
+      </c>
+      <c r="S109">
+        <v>258</v>
+      </c>
+      <c r="T109" t="s">
+        <v>41</v>
+      </c>
+      <c r="U109">
+        <v>7</v>
+      </c>
+      <c r="V109" t="s">
+        <v>43</v>
+      </c>
+      <c r="W109" t="s">
+        <v>43</v>
+      </c>
+      <c r="X109">
+        <v>2220</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA109">
+        <v>572.76</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>259</v>
+      </c>
+      <c r="B110" t="s">
+        <v>110</v>
+      </c>
+      <c r="C110" t="s">
+        <v>97</v>
+      </c>
+      <c r="D110" t="s">
+        <v>260</v>
+      </c>
+      <c r="E110" t="s">
+        <v>48</v>
+      </c>
+      <c r="F110" t="s">
+        <v>99</v>
+      </c>
+      <c r="G110" t="s">
+        <v>53</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110">
+        <v>1.5</v>
+      </c>
+      <c r="J110">
+        <v>1500</v>
+      </c>
+      <c r="K110">
+        <v>3000</v>
+      </c>
+      <c r="L110" t="s">
+        <v>36</v>
+      </c>
+      <c r="M110" t="s">
+        <v>141</v>
+      </c>
+      <c r="N110" t="s">
+        <v>37</v>
+      </c>
+      <c r="O110" t="s">
+        <v>115</v>
+      </c>
+      <c r="P110" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>100</v>
+      </c>
+      <c r="R110">
+        <v>319</v>
+      </c>
+      <c r="S110">
+        <v>319</v>
+      </c>
+      <c r="T110" t="s">
+        <v>41</v>
+      </c>
+      <c r="U110">
+        <v>6</v>
+      </c>
+      <c r="V110" t="s">
+        <v>43</v>
+      </c>
+      <c r="W110" t="s">
+        <v>43</v>
+      </c>
+      <c r="X110">
+        <v>2170</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA110">
+        <v>692.23</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>261</v>
+      </c>
+      <c r="B111" t="s">
+        <v>110</v>
+      </c>
+      <c r="C111" t="s">
+        <v>97</v>
+      </c>
+      <c r="D111" t="s">
+        <v>262</v>
+      </c>
+      <c r="E111" t="s">
+        <v>48</v>
+      </c>
+      <c r="F111" t="s">
+        <v>99</v>
+      </c>
+      <c r="G111" t="s">
+        <v>53</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111">
+        <v>1.5</v>
+      </c>
+      <c r="J111">
+        <v>1500</v>
+      </c>
+      <c r="K111">
+        <v>3000</v>
+      </c>
+      <c r="L111" t="s">
+        <v>36</v>
+      </c>
+      <c r="M111" t="s">
+        <v>172</v>
+      </c>
+      <c r="N111" t="s">
+        <v>37</v>
+      </c>
+      <c r="O111" t="s">
+        <v>115</v>
+      </c>
+      <c r="P111" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>100</v>
+      </c>
+      <c r="R111">
+        <v>266</v>
+      </c>
+      <c r="S111">
+        <v>266</v>
+      </c>
+      <c r="T111" t="s">
+        <v>41</v>
+      </c>
+      <c r="U111">
+        <v>5</v>
+      </c>
+      <c r="V111" t="s">
+        <v>43</v>
+      </c>
+      <c r="W111" t="s">
+        <v>43</v>
+      </c>
+      <c r="X111">
+        <v>2170</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA111">
+        <v>577.22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>263</v>
+      </c>
+      <c r="B112" t="s">
+        <v>110</v>
+      </c>
+      <c r="C112" t="s">
+        <v>97</v>
+      </c>
+      <c r="D112" t="s">
+        <v>262</v>
+      </c>
+      <c r="E112" t="s">
+        <v>48</v>
+      </c>
+      <c r="F112" t="s">
+        <v>99</v>
+      </c>
+      <c r="G112" t="s">
+        <v>53</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112">
+        <v>1.5</v>
+      </c>
+      <c r="J112">
+        <v>1500</v>
+      </c>
+      <c r="K112">
+        <v>3000</v>
+      </c>
+      <c r="L112" t="s">
+        <v>36</v>
+      </c>
+      <c r="M112" t="s">
+        <v>172</v>
+      </c>
+      <c r="N112" t="s">
+        <v>37</v>
+      </c>
+      <c r="O112" t="s">
+        <v>115</v>
+      </c>
+      <c r="P112" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>100</v>
+      </c>
+      <c r="R112">
+        <v>319</v>
+      </c>
+      <c r="S112">
+        <v>319</v>
+      </c>
+      <c r="T112" t="s">
+        <v>41</v>
+      </c>
+      <c r="U112">
+        <v>6</v>
+      </c>
+      <c r="V112" t="s">
+        <v>43</v>
+      </c>
+      <c r="W112" t="s">
+        <v>43</v>
+      </c>
+      <c r="X112">
+        <v>2170</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA112">
+        <v>692.23</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>264</v>
+      </c>
+      <c r="B113" t="s">
+        <v>110</v>
+      </c>
+      <c r="C113" t="s">
+        <v>97</v>
+      </c>
+      <c r="D113" t="s">
+        <v>265</v>
+      </c>
+      <c r="E113" t="s">
+        <v>48</v>
+      </c>
+      <c r="F113" t="s">
+        <v>99</v>
+      </c>
+      <c r="G113" t="s">
+        <v>53</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113">
+        <v>1500</v>
+      </c>
+      <c r="K113">
+        <v>3000</v>
+      </c>
+      <c r="L113" t="s">
+        <v>36</v>
+      </c>
+      <c r="M113" t="s">
+        <v>141</v>
+      </c>
+      <c r="N113" t="s">
+        <v>37</v>
+      </c>
+      <c r="O113" t="s">
+        <v>115</v>
+      </c>
+      <c r="P113" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>100</v>
+      </c>
+      <c r="R113">
+        <v>496</v>
+      </c>
+      <c r="S113">
+        <v>496</v>
+      </c>
+      <c r="T113" t="s">
+        <v>41</v>
+      </c>
+      <c r="U113">
+        <v>7</v>
+      </c>
+      <c r="V113" t="s">
+        <v>43</v>
+      </c>
+      <c r="W113" t="s">
+        <v>43</v>
+      </c>
+      <c r="X113">
+        <v>2170</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA113">
+        <v>1076.32</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>266</v>
+      </c>
+      <c r="B114" t="s">
+        <v>110</v>
+      </c>
+      <c r="C114" t="s">
+        <v>97</v>
+      </c>
+      <c r="D114" t="s">
+        <v>267</v>
+      </c>
+      <c r="E114" t="s">
+        <v>48</v>
+      </c>
+      <c r="F114" t="s">
+        <v>99</v>
+      </c>
+      <c r="G114" t="s">
+        <v>53</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114">
+        <v>2.5</v>
+      </c>
+      <c r="J114">
+        <v>1500</v>
+      </c>
+      <c r="K114">
+        <v>3000</v>
+      </c>
+      <c r="L114" t="s">
+        <v>36</v>
+      </c>
+      <c r="M114" t="s">
+        <v>37</v>
+      </c>
+      <c r="N114" t="s">
+        <v>37</v>
+      </c>
+      <c r="O114" t="s">
+        <v>38</v>
+      </c>
+      <c r="P114" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>100</v>
+      </c>
+      <c r="R114">
+        <v>266</v>
+      </c>
+      <c r="S114">
+        <v>266</v>
+      </c>
+      <c r="T114" t="s">
+        <v>41</v>
+      </c>
+      <c r="U114">
+        <v>3</v>
+      </c>
+      <c r="V114" t="s">
+        <v>43</v>
+      </c>
+      <c r="W114" t="s">
+        <v>43</v>
+      </c>
+      <c r="X114">
+        <v>2220</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA114">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>268</v>
+      </c>
+      <c r="B115" t="s">
+        <v>110</v>
+      </c>
+      <c r="C115" t="s">
+        <v>97</v>
+      </c>
+      <c r="D115" t="s">
+        <v>267</v>
+      </c>
+      <c r="E115" t="s">
+        <v>48</v>
+      </c>
+      <c r="F115" t="s">
+        <v>99</v>
+      </c>
+      <c r="G115" t="s">
+        <v>53</v>
+      </c>
+      <c r="H115" t="s">
+        <v>35</v>
+      </c>
+      <c r="I115">
+        <v>2.5</v>
+      </c>
+      <c r="J115">
+        <v>1500</v>
+      </c>
+      <c r="K115">
+        <v>3000</v>
+      </c>
+      <c r="L115" t="s">
+        <v>36</v>
+      </c>
+      <c r="M115" t="s">
+        <v>37</v>
+      </c>
+      <c r="N115" t="s">
+        <v>37</v>
+      </c>
+      <c r="O115" t="s">
+        <v>38</v>
+      </c>
+      <c r="P115" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>100</v>
+      </c>
+      <c r="R115">
+        <v>354</v>
+      </c>
+      <c r="S115">
+        <v>354</v>
+      </c>
+      <c r="T115" t="s">
+        <v>41</v>
+      </c>
+      <c r="U115">
+        <v>4</v>
+      </c>
+      <c r="V115" t="s">
+        <v>43</v>
+      </c>
+      <c r="W115" t="s">
+        <v>43</v>
+      </c>
+      <c r="X115">
+        <v>2220</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA115">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>269</v>
+      </c>
+      <c r="B116" t="s">
+        <v>110</v>
+      </c>
+      <c r="C116" t="s">
+        <v>97</v>
+      </c>
+      <c r="D116" t="s">
+        <v>267</v>
+      </c>
+      <c r="E116" t="s">
+        <v>48</v>
+      </c>
+      <c r="F116" t="s">
+        <v>99</v>
+      </c>
+      <c r="G116" t="s">
+        <v>53</v>
+      </c>
+      <c r="H116" t="s">
+        <v>35</v>
+      </c>
+      <c r="I116">
+        <v>2.5</v>
+      </c>
+      <c r="J116">
+        <v>1500</v>
+      </c>
+      <c r="K116">
+        <v>3000</v>
+      </c>
+      <c r="L116" t="s">
+        <v>36</v>
+      </c>
+      <c r="M116" t="s">
+        <v>37</v>
+      </c>
+      <c r="N116" t="s">
+        <v>37</v>
+      </c>
+      <c r="O116" t="s">
+        <v>38</v>
+      </c>
+      <c r="P116" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>100</v>
+      </c>
+      <c r="R116">
+        <v>620</v>
+      </c>
+      <c r="S116">
+        <v>620</v>
+      </c>
+      <c r="T116" t="s">
+        <v>41</v>
+      </c>
+      <c r="U116">
+        <v>7</v>
+      </c>
+      <c r="V116" t="s">
+        <v>43</v>
+      </c>
+      <c r="W116" t="s">
+        <v>43</v>
+      </c>
+      <c r="X116">
+        <v>2220</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA116">
+        <v>1376.4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>270</v>
+      </c>
+      <c r="B117" t="s">
+        <v>110</v>
+      </c>
+      <c r="C117" t="s">
+        <v>97</v>
+      </c>
+      <c r="D117" t="s">
+        <v>271</v>
+      </c>
+      <c r="E117" t="s">
+        <v>48</v>
+      </c>
+      <c r="F117" t="s">
+        <v>99</v>
+      </c>
+      <c r="G117" t="s">
+        <v>34</v>
+      </c>
+      <c r="H117" t="s">
+        <v>35</v>
+      </c>
+      <c r="I117">
+        <v>1.5</v>
+      </c>
+      <c r="J117">
+        <v>1500</v>
+      </c>
+      <c r="K117">
+        <v>3000</v>
+      </c>
+      <c r="L117" t="s">
+        <v>36</v>
+      </c>
+      <c r="M117" t="s">
+        <v>37</v>
+      </c>
+      <c r="N117" t="s">
+        <v>37</v>
+      </c>
+      <c r="O117" t="s">
+        <v>38</v>
+      </c>
+      <c r="P117" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>100</v>
+      </c>
+      <c r="R117">
+        <v>266</v>
+      </c>
+      <c r="S117">
+        <v>266</v>
+      </c>
+      <c r="T117" t="s">
+        <v>41</v>
+      </c>
+      <c r="U117">
+        <v>5</v>
+      </c>
+      <c r="V117" t="s">
+        <v>43</v>
+      </c>
+      <c r="W117" t="s">
+        <v>43</v>
+      </c>
+      <c r="X117">
+        <v>3540</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA117">
+        <v>941.64</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>272</v>
+      </c>
+      <c r="B118" t="s">
+        <v>110</v>
+      </c>
+      <c r="C118" t="s">
+        <v>97</v>
+      </c>
+      <c r="D118" t="s">
+        <v>273</v>
+      </c>
+      <c r="E118" t="s">
+        <v>48</v>
+      </c>
+      <c r="F118" t="s">
+        <v>99</v>
+      </c>
+      <c r="G118" t="s">
+        <v>34</v>
+      </c>
+      <c r="H118" t="s">
+        <v>35</v>
+      </c>
+      <c r="I118">
+        <v>2.5</v>
+      </c>
+      <c r="J118">
+        <v>2000</v>
+      </c>
+      <c r="K118">
+        <v>4000</v>
+      </c>
+      <c r="L118" t="s">
+        <v>36</v>
+      </c>
+      <c r="M118" t="s">
+        <v>37</v>
+      </c>
+      <c r="N118" t="s">
+        <v>37</v>
+      </c>
+      <c r="O118" t="s">
+        <v>38</v>
+      </c>
+      <c r="P118" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>100</v>
+      </c>
+      <c r="R118">
+        <v>315</v>
+      </c>
+      <c r="S118">
+        <v>315</v>
+      </c>
+      <c r="T118" t="s">
+        <v>41</v>
+      </c>
+      <c r="U118">
+        <v>2</v>
+      </c>
+      <c r="V118" t="s">
+        <v>43</v>
+      </c>
+      <c r="W118" t="s">
+        <v>43</v>
+      </c>
+      <c r="X118">
+        <v>3560</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA118">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>274</v>
+      </c>
+      <c r="B119" t="s">
+        <v>110</v>
+      </c>
+      <c r="C119" t="s">
+        <v>97</v>
+      </c>
+      <c r="D119" t="s">
+        <v>273</v>
+      </c>
+      <c r="E119" t="s">
+        <v>48</v>
+      </c>
+      <c r="F119" t="s">
+        <v>99</v>
+      </c>
+      <c r="G119" t="s">
+        <v>34</v>
+      </c>
+      <c r="H119" t="s">
+        <v>35</v>
+      </c>
+      <c r="I119">
+        <v>2.5</v>
+      </c>
+      <c r="J119">
+        <v>2000</v>
+      </c>
+      <c r="K119">
+        <v>4000</v>
+      </c>
+      <c r="L119" t="s">
+        <v>36</v>
+      </c>
+      <c r="M119" t="s">
+        <v>37</v>
+      </c>
+      <c r="N119" t="s">
+        <v>37</v>
+      </c>
+      <c r="O119" t="s">
+        <v>38</v>
+      </c>
+      <c r="P119" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>100</v>
+      </c>
+      <c r="R119">
+        <v>315</v>
+      </c>
+      <c r="S119">
+        <v>315</v>
+      </c>
+      <c r="T119" t="s">
+        <v>41</v>
+      </c>
+      <c r="U119">
+        <v>2</v>
+      </c>
+      <c r="V119" t="s">
+        <v>43</v>
+      </c>
+      <c r="W119" t="s">
+        <v>43</v>
+      </c>
+      <c r="X119">
+        <v>3560</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA119">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>275</v>
+      </c>
+      <c r="B120" t="s">
+        <v>110</v>
+      </c>
+      <c r="C120" t="s">
+        <v>97</v>
+      </c>
+      <c r="D120" t="s">
+        <v>276</v>
+      </c>
+      <c r="E120" t="s">
+        <v>48</v>
+      </c>
+      <c r="F120" t="s">
+        <v>99</v>
+      </c>
+      <c r="G120" t="s">
+        <v>34</v>
+      </c>
+      <c r="H120" t="s">
+        <v>35</v>
+      </c>
+      <c r="I120">
+        <v>4</v>
+      </c>
+      <c r="J120">
+        <v>2000</v>
+      </c>
+      <c r="K120">
+        <v>4000</v>
+      </c>
+      <c r="L120" t="s">
+        <v>36</v>
+      </c>
+      <c r="M120" t="s">
+        <v>37</v>
+      </c>
+      <c r="N120" t="s">
+        <v>37</v>
+      </c>
+      <c r="O120" t="s">
+        <v>38</v>
+      </c>
+      <c r="P120" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>100</v>
+      </c>
+      <c r="R120">
+        <v>252</v>
+      </c>
+      <c r="S120">
+        <v>252</v>
+      </c>
+      <c r="T120" t="s">
+        <v>41</v>
+      </c>
+      <c r="U120">
+        <v>1</v>
+      </c>
+      <c r="V120" t="s">
+        <v>43</v>
+      </c>
+      <c r="W120" t="s">
+        <v>43</v>
+      </c>
+      <c r="X120">
+        <v>3560</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA120">
+        <v>897.12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>277</v>
+      </c>
+      <c r="B121" t="s">
+        <v>110</v>
+      </c>
+      <c r="C121" t="s">
+        <v>97</v>
+      </c>
+      <c r="D121" t="s">
+        <v>276</v>
+      </c>
+      <c r="E121" t="s">
+        <v>48</v>
+      </c>
+      <c r="F121" t="s">
+        <v>99</v>
+      </c>
+      <c r="G121" t="s">
+        <v>34</v>
+      </c>
+      <c r="H121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I121">
+        <v>4</v>
+      </c>
+      <c r="J121">
+        <v>2000</v>
+      </c>
+      <c r="K121">
+        <v>4000</v>
+      </c>
+      <c r="L121" t="s">
+        <v>36</v>
+      </c>
+      <c r="M121" t="s">
+        <v>37</v>
+      </c>
+      <c r="N121" t="s">
+        <v>37</v>
+      </c>
+      <c r="O121" t="s">
+        <v>38</v>
+      </c>
+      <c r="P121" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>100</v>
+      </c>
+      <c r="R121">
+        <v>252</v>
+      </c>
+      <c r="S121">
+        <v>252</v>
+      </c>
+      <c r="T121" t="s">
+        <v>41</v>
+      </c>
+      <c r="U121">
+        <v>1</v>
+      </c>
+      <c r="V121" t="s">
+        <v>43</v>
+      </c>
+      <c r="W121" t="s">
+        <v>43</v>
+      </c>
+      <c r="X121">
+        <v>3560</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA121">
+        <v>897.12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>278</v>
+      </c>
+      <c r="B122" t="s">
+        <v>110</v>
+      </c>
+      <c r="C122" t="s">
+        <v>97</v>
+      </c>
+      <c r="D122" t="s">
+        <v>279</v>
+      </c>
+      <c r="E122" t="s">
+        <v>48</v>
+      </c>
+      <c r="F122" t="s">
+        <v>99</v>
+      </c>
+      <c r="G122" t="s">
+        <v>149</v>
+      </c>
+      <c r="H122" t="s">
+        <v>35</v>
+      </c>
+      <c r="I122">
+        <v>6</v>
+      </c>
+      <c r="J122">
+        <v>1250</v>
+      </c>
+      <c r="K122">
+        <v>2500</v>
+      </c>
+      <c r="L122" t="s">
+        <v>36</v>
+      </c>
+      <c r="M122" t="s">
+        <v>37</v>
+      </c>
+      <c r="N122" t="s">
+        <v>37</v>
+      </c>
+      <c r="O122" t="s">
+        <v>38</v>
+      </c>
+      <c r="P122" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>100</v>
+      </c>
+      <c r="R122">
+        <v>147</v>
+      </c>
+      <c r="S122">
+        <v>147</v>
+      </c>
+      <c r="T122" t="s">
+        <v>41</v>
+      </c>
+      <c r="U122">
+        <v>1</v>
+      </c>
+      <c r="V122" t="s">
+        <v>43</v>
+      </c>
+      <c r="W122" t="s">
+        <v>43</v>
+      </c>
+      <c r="X122">
+        <v>3640</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA122">
+        <v>535.08</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>280</v>
+      </c>
+      <c r="B123" t="s">
+        <v>110</v>
+      </c>
+      <c r="C123" t="s">
+        <v>97</v>
+      </c>
+      <c r="D123" t="s">
+        <v>281</v>
+      </c>
+      <c r="E123" t="s">
+        <v>48</v>
+      </c>
+      <c r="F123" t="s">
+        <v>99</v>
+      </c>
+      <c r="G123" t="s">
+        <v>53</v>
+      </c>
+      <c r="H123" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123">
+        <v>2</v>
+      </c>
+      <c r="J123">
+        <v>1500</v>
+      </c>
+      <c r="K123">
+        <v>3000</v>
+      </c>
+      <c r="L123" t="s">
+        <v>36</v>
+      </c>
+      <c r="M123" t="s">
+        <v>37</v>
+      </c>
+      <c r="N123" t="s">
+        <v>37</v>
+      </c>
+      <c r="O123" t="s">
+        <v>38</v>
+      </c>
+      <c r="P123" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>100</v>
+      </c>
+      <c r="R123">
+        <v>283</v>
+      </c>
+      <c r="S123">
+        <v>283</v>
+      </c>
+      <c r="T123" t="s">
+        <v>41</v>
+      </c>
+      <c r="U123">
+        <v>4</v>
+      </c>
+      <c r="V123" t="s">
+        <v>43</v>
+      </c>
+      <c r="W123" t="s">
+        <v>43</v>
+      </c>
+      <c r="X123">
+        <v>2220</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA123">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>282</v>
+      </c>
+      <c r="B124" t="s">
+        <v>96</v>
+      </c>
+      <c r="C124" t="s">
+        <v>97</v>
+      </c>
+      <c r="D124" t="s">
+        <v>283</v>
+      </c>
+      <c r="E124" t="s">
+        <v>48</v>
+      </c>
+      <c r="F124" t="s">
+        <v>99</v>
+      </c>
+      <c r="G124" t="s">
+        <v>53</v>
+      </c>
+      <c r="H124" t="s">
+        <v>35</v>
+      </c>
+      <c r="I124">
+        <v>0.8</v>
+      </c>
+      <c r="J124">
+        <v>1500</v>
+      </c>
+      <c r="K124">
+        <v>3000</v>
+      </c>
+      <c r="L124" t="s">
+        <v>36</v>
+      </c>
+      <c r="M124" t="s">
+        <v>119</v>
+      </c>
+      <c r="N124" t="s">
+        <v>37</v>
+      </c>
+      <c r="O124" t="s">
+        <v>115</v>
+      </c>
+      <c r="P124" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>100</v>
+      </c>
+      <c r="R124">
+        <v>833</v>
+      </c>
+      <c r="S124">
+        <v>833</v>
+      </c>
+      <c r="T124" t="s">
+        <v>41</v>
+      </c>
+      <c r="U124">
+        <v>29</v>
+      </c>
+      <c r="V124" t="s">
+        <v>43</v>
+      </c>
+      <c r="W124" t="s">
+        <v>43</v>
+      </c>
+      <c r="X124">
+        <v>2270</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA124">
+        <v>1890.91</v>
+      </c>
+      <c r="AB124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>284</v>
+      </c>
+      <c r="B125" t="s">
+        <v>96</v>
+      </c>
+      <c r="C125" t="s">
+        <v>97</v>
+      </c>
+      <c r="D125" t="s">
+        <v>283</v>
+      </c>
+      <c r="E125" t="s">
+        <v>48</v>
+      </c>
+      <c r="F125" t="s">
+        <v>99</v>
+      </c>
+      <c r="G125" t="s">
+        <v>53</v>
+      </c>
+      <c r="H125" t="s">
+        <v>35</v>
+      </c>
+      <c r="I125">
+        <v>0.8</v>
+      </c>
+      <c r="J125">
+        <v>1500</v>
+      </c>
+      <c r="K125">
+        <v>3000</v>
+      </c>
+      <c r="L125" t="s">
+        <v>36</v>
+      </c>
+      <c r="M125" t="s">
+        <v>119</v>
+      </c>
+      <c r="N125" t="s">
+        <v>37</v>
+      </c>
+      <c r="O125" t="s">
+        <v>115</v>
+      </c>
+      <c r="P125" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>100</v>
+      </c>
+      <c r="R125">
+        <v>805</v>
+      </c>
+      <c r="S125">
+        <v>805</v>
+      </c>
+      <c r="T125" t="s">
+        <v>41</v>
+      </c>
+      <c r="U125">
+        <v>28</v>
+      </c>
+      <c r="V125" t="s">
+        <v>43</v>
+      </c>
+      <c r="W125" t="s">
+        <v>43</v>
+      </c>
+      <c r="X125">
+        <v>2270</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA125">
+        <v>1827.35</v>
+      </c>
+      <c r="AB125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>285</v>
+      </c>
+      <c r="B126" t="s">
+        <v>96</v>
+      </c>
+      <c r="C126" t="s">
+        <v>97</v>
+      </c>
+      <c r="D126" t="s">
+        <v>286</v>
+      </c>
+      <c r="E126" t="s">
+        <v>48</v>
+      </c>
+      <c r="F126" t="s">
+        <v>99</v>
+      </c>
+      <c r="G126" t="s">
+        <v>53</v>
+      </c>
+      <c r="H126" t="s">
+        <v>35</v>
+      </c>
+      <c r="I126">
+        <v>2</v>
+      </c>
+      <c r="J126">
+        <v>1000</v>
+      </c>
+      <c r="K126">
+        <v>2000</v>
+      </c>
+      <c r="L126" t="s">
+        <v>36</v>
+      </c>
+      <c r="M126" t="s">
+        <v>37</v>
+      </c>
+      <c r="N126" t="s">
+        <v>37</v>
+      </c>
+      <c r="O126" t="s">
+        <v>38</v>
+      </c>
+      <c r="P126" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>100</v>
+      </c>
+      <c r="R126">
+        <v>1448</v>
+      </c>
+      <c r="S126">
+        <v>1448</v>
+      </c>
+      <c r="T126" t="s">
+        <v>41</v>
+      </c>
+      <c r="U126">
+        <v>1</v>
+      </c>
+      <c r="V126" t="s">
+        <v>43</v>
+      </c>
+      <c r="W126" t="s">
+        <v>43</v>
+      </c>
+      <c r="X126">
+        <v>2270</v>
+      </c>
+      <c r="Y126" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA126">
+        <v>3286.96</v>
+      </c>
+      <c r="AB126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>287</v>
+      </c>
+      <c r="B127" t="s">
+        <v>102</v>
+      </c>
+      <c r="C127" t="s">
+        <v>97</v>
+      </c>
+      <c r="D127" t="s">
+        <v>288</v>
+      </c>
+      <c r="E127" t="s">
+        <v>48</v>
+      </c>
+      <c r="F127" t="s">
+        <v>99</v>
+      </c>
+      <c r="G127" t="s">
+        <v>138</v>
+      </c>
+      <c r="H127" t="s">
+        <v>35</v>
+      </c>
+      <c r="I127">
+        <v>4</v>
+      </c>
+      <c r="J127">
+        <v>1000</v>
+      </c>
+      <c r="K127">
+        <v>2000</v>
+      </c>
+      <c r="L127" t="s">
+        <v>36</v>
+      </c>
+      <c r="M127" t="s">
+        <v>37</v>
+      </c>
+      <c r="N127" t="s">
+        <v>37</v>
+      </c>
+      <c r="O127" t="s">
+        <v>38</v>
+      </c>
+      <c r="P127" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>100</v>
+      </c>
+      <c r="R127">
+        <v>384</v>
+      </c>
+      <c r="S127">
+        <v>384</v>
+      </c>
+      <c r="T127" t="s">
+        <v>41</v>
+      </c>
+      <c r="U127">
+        <v>6</v>
+      </c>
+      <c r="V127" t="s">
+        <v>43</v>
+      </c>
+      <c r="W127" t="s">
+        <v>43</v>
+      </c>
+      <c r="X127">
+        <v>1370</v>
+      </c>
+      <c r="Y127" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA127">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>289</v>
+      </c>
+      <c r="B128" t="s">
+        <v>110</v>
+      </c>
+      <c r="C128" t="s">
+        <v>97</v>
+      </c>
+      <c r="D128" t="s">
+        <v>146</v>
+      </c>
+      <c r="E128" t="s">
+        <v>48</v>
+      </c>
+      <c r="F128" t="s">
+        <v>99</v>
+      </c>
+      <c r="G128" t="s">
+        <v>34</v>
+      </c>
+      <c r="H128" t="s">
+        <v>35</v>
+      </c>
+      <c r="I128">
+        <v>6</v>
+      </c>
+      <c r="J128">
+        <v>1500</v>
+      </c>
+      <c r="K128">
+        <v>3000</v>
+      </c>
+      <c r="L128" t="s">
+        <v>36</v>
+      </c>
+      <c r="M128" t="s">
+        <v>37</v>
+      </c>
+      <c r="N128" t="s">
+        <v>37</v>
+      </c>
+      <c r="O128" t="s">
+        <v>38</v>
+      </c>
+      <c r="P128" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>100</v>
+      </c>
+      <c r="R128">
+        <v>850</v>
+      </c>
+      <c r="S128">
+        <v>850</v>
+      </c>
+      <c r="T128" t="s">
+        <v>41</v>
+      </c>
+      <c r="U128">
+        <v>4</v>
+      </c>
+      <c r="V128" t="s">
+        <v>43</v>
+      </c>
+      <c r="W128" t="s">
+        <v>43</v>
+      </c>
+      <c r="X128">
+        <v>3540</v>
+      </c>
+      <c r="Y128" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA128">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>290</v>
+      </c>
+      <c r="B129" t="s">
+        <v>96</v>
+      </c>
+      <c r="C129" t="s">
+        <v>97</v>
+      </c>
+      <c r="D129" t="s">
+        <v>111</v>
+      </c>
+      <c r="E129" t="s">
+        <v>48</v>
+      </c>
+      <c r="F129" t="s">
+        <v>99</v>
+      </c>
+      <c r="G129" t="s">
+        <v>53</v>
+      </c>
+      <c r="H129" t="s">
+        <v>35</v>
+      </c>
+      <c r="I129">
+        <v>3</v>
+      </c>
+      <c r="J129">
+        <v>1500</v>
+      </c>
+      <c r="K129">
+        <v>3000</v>
+      </c>
+      <c r="L129" t="s">
+        <v>36</v>
+      </c>
+      <c r="M129" t="s">
+        <v>37</v>
+      </c>
+      <c r="N129" t="s">
+        <v>37</v>
+      </c>
+      <c r="O129" t="s">
+        <v>38</v>
+      </c>
+      <c r="P129" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>100</v>
+      </c>
+      <c r="R129">
+        <v>632</v>
+      </c>
+      <c r="S129">
+        <v>632</v>
+      </c>
+      <c r="T129" t="s">
+        <v>41</v>
+      </c>
+      <c r="U129">
+        <v>6</v>
+      </c>
+      <c r="V129" t="s">
+        <v>43</v>
+      </c>
+      <c r="W129" t="s">
+        <v>43</v>
+      </c>
+      <c r="X129">
+        <v>2220</v>
+      </c>
+      <c r="Y129" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA129">
+        <v>1403.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="273">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -224,6 +224,612 @@
   </si>
   <si>
     <t>K268099989</t>
+  </si>
+  <si>
+    <t>7248626</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>7248988</t>
+  </si>
+  <si>
+    <t>Coil 1.4307-304L 2D 1.0 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>7248989</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>K30/1.4016-430</t>
+  </si>
+  <si>
+    <t>2R</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>1.4404-316L</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7253484</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 240 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 240</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7253485</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484088</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254248</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T486939</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>T487411</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>7256367</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.2 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7256368</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Scotchbrite</t>
+  </si>
+  <si>
+    <t>T488802</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256740</t>
+  </si>
+  <si>
+    <t>Sheets 1.4301-304 2R 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256746</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7256760</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R with paper 0.8 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256809</t>
+  </si>
+  <si>
+    <t>7256817</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Duplo polish grain 320 Nov 4228 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Duplo polish grain 320</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256819</t>
+  </si>
+  <si>
+    <t>7256820</t>
+  </si>
+  <si>
+    <t>7256821</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>T488986</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256940</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed Nov 4228 0.8 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256941</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489089</t>
+  </si>
+  <si>
+    <t>7257077</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257260</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7257261</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T489700</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489750</t>
+  </si>
+  <si>
+    <t>7257569</t>
+  </si>
+  <si>
+    <t>7257570</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257703</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2E 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>2E</t>
+  </si>
+  <si>
+    <t>T490582</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257842</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 2000.0 x 4000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257845</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 0.8 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257850</t>
+  </si>
+  <si>
+    <t>7257852</t>
+  </si>
+  <si>
+    <t>7257854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Nov 4228 6.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257864</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257865</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 400 NOV 4204 RB 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>NOV 4204 RB</t>
+  </si>
+  <si>
+    <t>7257875</t>
+  </si>
+  <si>
+    <t>Sheets 1.4301-304 2B 0.6 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7257894</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T490920</t>
+  </si>
+  <si>
+    <t>T490921</t>
+  </si>
+  <si>
+    <t>S139218</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 12.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491064</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T491065</t>
+  </si>
+  <si>
+    <t>7258091</t>
+  </si>
+  <si>
+    <t>7258100</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258149</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491370</t>
+  </si>
+  <si>
+    <t>T491483</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258233</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T491760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258350</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T492123</t>
+  </si>
+  <si>
+    <t>T492124</t>
+  </si>
+  <si>
+    <t>7258489</t>
+  </si>
+  <si>
+    <t>7258526</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258529</t>
+  </si>
+  <si>
+    <t>7258730</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258760</t>
+  </si>
+  <si>
+    <t>7258767</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 5.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7258862</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258863</t>
+  </si>
+  <si>
+    <t>7258908</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258919</t>
   </si>
 </sst>
 </file>
@@ -600,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB119"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -1359,6 +1965,9145 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10">
+        <v>2.5</v>
+      </c>
+      <c r="J10">
+        <v>1000</v>
+      </c>
+      <c r="K10">
+        <v>2000</v>
+      </c>
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>75</v>
+      </c>
+      <c r="R10">
+        <v>312</v>
+      </c>
+      <c r="S10">
+        <v>312</v>
+      </c>
+      <c r="T10" t="s">
+        <v>41</v>
+      </c>
+      <c r="U10">
+        <v>8</v>
+      </c>
+      <c r="V10" t="s">
+        <v>43</v>
+      </c>
+      <c r="W10" t="s">
+        <v>43</v>
+      </c>
+      <c r="X10">
+        <v>2220</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA10">
+        <v>692.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M11" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R11">
+        <v>2560</v>
+      </c>
+      <c r="S11">
+        <v>2560</v>
+      </c>
+      <c r="T11" t="s">
+        <v>41</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X11">
+        <v>2270</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA11">
+        <v>5811.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="s">
+        <v>78</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>75</v>
+      </c>
+      <c r="R12">
+        <v>3075</v>
+      </c>
+      <c r="S12">
+        <v>3075</v>
+      </c>
+      <c r="T12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" t="s">
+        <v>43</v>
+      </c>
+      <c r="X12">
+        <v>2270</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA12">
+        <v>6980.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>1000</v>
+      </c>
+      <c r="K13">
+        <v>2000</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" t="s">
+        <v>38</v>
+      </c>
+      <c r="P13" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>75</v>
+      </c>
+      <c r="R13">
+        <v>394</v>
+      </c>
+      <c r="S13">
+        <v>394</v>
+      </c>
+      <c r="T13" t="s">
+        <v>41</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13">
+        <v>2020</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA13">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>1250</v>
+      </c>
+      <c r="K14">
+        <v>2500</v>
+      </c>
+      <c r="L14" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>75</v>
+      </c>
+      <c r="R14">
+        <v>322</v>
+      </c>
+      <c r="S14">
+        <v>322</v>
+      </c>
+      <c r="T14" t="s">
+        <v>41</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14" t="s">
+        <v>43</v>
+      </c>
+      <c r="W14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X14">
+        <v>1370</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA14">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>1250</v>
+      </c>
+      <c r="K15">
+        <v>2500</v>
+      </c>
+      <c r="L15" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>75</v>
+      </c>
+      <c r="R15">
+        <v>340</v>
+      </c>
+      <c r="S15">
+        <v>340</v>
+      </c>
+      <c r="T15" t="s">
+        <v>41</v>
+      </c>
+      <c r="U15">
+        <v>7</v>
+      </c>
+      <c r="V15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" t="s">
+        <v>43</v>
+      </c>
+      <c r="X15">
+        <v>1370</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA15">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16">
+        <v>2000</v>
+      </c>
+      <c r="K16">
+        <v>6000</v>
+      </c>
+      <c r="L16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>75</v>
+      </c>
+      <c r="R16">
+        <v>283</v>
+      </c>
+      <c r="S16">
+        <v>283</v>
+      </c>
+      <c r="T16" t="s">
+        <v>41</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
+        <v>43</v>
+      </c>
+      <c r="W16" t="s">
+        <v>43</v>
+      </c>
+      <c r="X16">
+        <v>3560</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA16">
+        <v>1007.48</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17">
+        <v>6</v>
+      </c>
+      <c r="J17">
+        <v>1500</v>
+      </c>
+      <c r="K17">
+        <v>3000</v>
+      </c>
+      <c r="L17" t="s">
+        <v>65</v>
+      </c>
+      <c r="M17" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>75</v>
+      </c>
+      <c r="R17">
+        <v>212</v>
+      </c>
+      <c r="S17">
+        <v>212</v>
+      </c>
+      <c r="T17" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W17" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17">
+        <v>3490</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA17">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>8</v>
+      </c>
+      <c r="J18">
+        <v>1250</v>
+      </c>
+      <c r="K18">
+        <v>2500</v>
+      </c>
+      <c r="L18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M18" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>75</v>
+      </c>
+      <c r="R18">
+        <v>394</v>
+      </c>
+      <c r="S18">
+        <v>394</v>
+      </c>
+      <c r="T18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X18">
+        <v>3490</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA18">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19">
+        <v>5</v>
+      </c>
+      <c r="J19">
+        <v>2000</v>
+      </c>
+      <c r="K19">
+        <v>6000</v>
+      </c>
+      <c r="L19" t="s">
+        <v>36</v>
+      </c>
+      <c r="M19" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>75</v>
+      </c>
+      <c r="R19">
+        <v>472</v>
+      </c>
+      <c r="S19">
+        <v>472</v>
+      </c>
+      <c r="T19" t="s">
+        <v>41</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" t="s">
+        <v>43</v>
+      </c>
+      <c r="X19">
+        <v>2190</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA19">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <v>1500</v>
+      </c>
+      <c r="K20">
+        <v>3000</v>
+      </c>
+      <c r="L20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" t="s">
+        <v>101</v>
+      </c>
+      <c r="N20" t="s">
+        <v>37</v>
+      </c>
+      <c r="O20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P20" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>75</v>
+      </c>
+      <c r="R20">
+        <v>970</v>
+      </c>
+      <c r="S20">
+        <v>970</v>
+      </c>
+      <c r="T20" t="s">
+        <v>41</v>
+      </c>
+      <c r="U20">
+        <v>13</v>
+      </c>
+      <c r="V20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20">
+        <v>3490</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA20">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21">
+        <v>2.5</v>
+      </c>
+      <c r="J21">
+        <v>1500</v>
+      </c>
+      <c r="K21">
+        <v>3000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" t="s">
+        <v>37</v>
+      </c>
+      <c r="O21" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>75</v>
+      </c>
+      <c r="R21">
+        <v>526</v>
+      </c>
+      <c r="S21">
+        <v>526</v>
+      </c>
+      <c r="T21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U21">
+        <v>6</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21">
+        <v>3540</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22">
+        <v>1500</v>
+      </c>
+      <c r="K22">
+        <v>3000</v>
+      </c>
+      <c r="L22" t="s">
+        <v>36</v>
+      </c>
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>75</v>
+      </c>
+      <c r="R22">
+        <v>354</v>
+      </c>
+      <c r="S22">
+        <v>354</v>
+      </c>
+      <c r="T22" t="s">
+        <v>41</v>
+      </c>
+      <c r="U22">
+        <v>2</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>43</v>
+      </c>
+      <c r="X22">
+        <v>1170</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23">
+        <v>1.5</v>
+      </c>
+      <c r="J23">
+        <v>1250</v>
+      </c>
+      <c r="L23" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>75</v>
+      </c>
+      <c r="R23">
+        <v>1275</v>
+      </c>
+      <c r="S23">
+        <v>1275</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23">
+        <v>3590</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA23">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24">
+        <v>1500</v>
+      </c>
+      <c r="K24">
+        <v>3000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>75</v>
+      </c>
+      <c r="R24">
+        <v>210</v>
+      </c>
+      <c r="S24">
+        <v>210</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>2</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>2170</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>1500</v>
+      </c>
+      <c r="K25">
+        <v>3000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" t="s">
+        <v>112</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>113</v>
+      </c>
+      <c r="P25" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>75</v>
+      </c>
+      <c r="R25">
+        <v>283</v>
+      </c>
+      <c r="S25">
+        <v>283</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>2170</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>1500</v>
+      </c>
+      <c r="K26">
+        <v>3000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" t="s">
+        <v>112</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>113</v>
+      </c>
+      <c r="P26" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>75</v>
+      </c>
+      <c r="R26">
+        <v>283</v>
+      </c>
+      <c r="S26">
+        <v>283</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>2170</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>614.11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" t="s">
+        <v>116</v>
+      </c>
+      <c r="E27" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>1500</v>
+      </c>
+      <c r="K27">
+        <v>3000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>75</v>
+      </c>
+      <c r="R27">
+        <v>212</v>
+      </c>
+      <c r="S27">
+        <v>212</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>2</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>1320</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1500</v>
+      </c>
+      <c r="K28">
+        <v>3000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>75</v>
+      </c>
+      <c r="R28">
+        <v>212</v>
+      </c>
+      <c r="S28">
+        <v>212</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>6</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>2170</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>460.04</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
+        <v>6</v>
+      </c>
+      <c r="J29">
+        <v>1000</v>
+      </c>
+      <c r="K29">
+        <v>2000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>65</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>75</v>
+      </c>
+      <c r="R29">
+        <v>567</v>
+      </c>
+      <c r="S29">
+        <v>567</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>6</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>2220</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>6</v>
+      </c>
+      <c r="J30">
+        <v>1000</v>
+      </c>
+      <c r="K30">
+        <v>2000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>75</v>
+      </c>
+      <c r="R30">
+        <v>567</v>
+      </c>
+      <c r="S30">
+        <v>567</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>6</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>2220</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" t="s">
+        <v>85</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>1500</v>
+      </c>
+      <c r="K31">
+        <v>3000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" t="s">
+        <v>37</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>75</v>
+      </c>
+      <c r="R31">
+        <v>319</v>
+      </c>
+      <c r="S31">
+        <v>319</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>3</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>1370</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>1250</v>
+      </c>
+      <c r="K32">
+        <v>2500</v>
+      </c>
+      <c r="L32" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>75</v>
+      </c>
+      <c r="R32">
+        <v>246</v>
+      </c>
+      <c r="S32">
+        <v>246</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>5</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>2170</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>0.8</v>
+      </c>
+      <c r="J33">
+        <v>1000</v>
+      </c>
+      <c r="K33">
+        <v>2000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>75</v>
+      </c>
+      <c r="R33">
+        <v>1498</v>
+      </c>
+      <c r="S33">
+        <v>1498</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>2370</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" t="s">
+        <v>53</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>0.8</v>
+      </c>
+      <c r="J34">
+        <v>1000</v>
+      </c>
+      <c r="K34">
+        <v>2000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>75</v>
+      </c>
+      <c r="R34">
+        <v>1498</v>
+      </c>
+      <c r="S34">
+        <v>1498</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>2370</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H35" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+      <c r="J35">
+        <v>1500</v>
+      </c>
+      <c r="K35">
+        <v>3000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>65</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>75</v>
+      </c>
+      <c r="R35">
+        <v>354</v>
+      </c>
+      <c r="S35">
+        <v>354</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>2220</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36">
+        <v>1500</v>
+      </c>
+      <c r="K36">
+        <v>3000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" t="s">
+        <v>101</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>75</v>
+      </c>
+      <c r="R36">
+        <v>1010</v>
+      </c>
+      <c r="S36">
+        <v>1010</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>14</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>3540</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" t="s">
+        <v>59</v>
+      </c>
+      <c r="G37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <v>1500</v>
+      </c>
+      <c r="K37">
+        <v>3000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>75</v>
+      </c>
+      <c r="R37">
+        <v>283</v>
+      </c>
+      <c r="S37">
+        <v>283</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>4</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>3540</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>133</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
+        <v>135</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>0.8</v>
+      </c>
+      <c r="J38">
+        <v>1000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>86</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>136</v>
+      </c>
+      <c r="P38" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>75</v>
+      </c>
+      <c r="R38">
+        <v>1585</v>
+      </c>
+      <c r="S38">
+        <v>1585</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>1</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>2370</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>137</v>
+      </c>
+      <c r="B39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" t="s">
+        <v>52</v>
+      </c>
+      <c r="F39" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" t="s">
+        <v>85</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>1.5</v>
+      </c>
+      <c r="J39">
+        <v>1500</v>
+      </c>
+      <c r="K39">
+        <v>3000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>75</v>
+      </c>
+      <c r="R39">
+        <v>212</v>
+      </c>
+      <c r="S39">
+        <v>212</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>1</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>1320</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>2.5</v>
+      </c>
+      <c r="J40">
+        <v>1500</v>
+      </c>
+      <c r="K40">
+        <v>3000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>65</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>75</v>
+      </c>
+      <c r="R40">
+        <v>540</v>
+      </c>
+      <c r="S40">
+        <v>540</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>6</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>3540</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" t="s">
+        <v>73</v>
+      </c>
+      <c r="D41" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>2.5</v>
+      </c>
+      <c r="J41">
+        <v>1500</v>
+      </c>
+      <c r="K41">
+        <v>3000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>65</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>75</v>
+      </c>
+      <c r="R41">
+        <v>520</v>
+      </c>
+      <c r="S41">
+        <v>520</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>6</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>3540</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>141</v>
+      </c>
+      <c r="B42" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" t="s">
+        <v>91</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42">
+        <v>2.5</v>
+      </c>
+      <c r="J42">
+        <v>1500</v>
+      </c>
+      <c r="K42">
+        <v>3000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>65</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>75</v>
+      </c>
+      <c r="R42">
+        <v>530</v>
+      </c>
+      <c r="S42">
+        <v>530</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>6</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>3540</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>142</v>
+      </c>
+      <c r="B43" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>2.5</v>
+      </c>
+      <c r="J43">
+        <v>1500</v>
+      </c>
+      <c r="K43">
+        <v>3000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>65</v>
+      </c>
+      <c r="M43" t="s">
+        <v>37</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>75</v>
+      </c>
+      <c r="R43">
+        <v>526</v>
+      </c>
+      <c r="S43">
+        <v>526</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>6</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>3540</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>1500</v>
+      </c>
+      <c r="K44">
+        <v>3000</v>
+      </c>
+      <c r="L44" t="s">
+        <v>65</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>75</v>
+      </c>
+      <c r="R44">
+        <v>212</v>
+      </c>
+      <c r="S44">
+        <v>212</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>1</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>3490</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45" t="s">
+        <v>52</v>
+      </c>
+      <c r="F45" t="s">
+        <v>59</v>
+      </c>
+      <c r="G45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="J45">
+        <v>1500</v>
+      </c>
+      <c r="K45">
+        <v>3000</v>
+      </c>
+      <c r="L45" t="s">
+        <v>65</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>75</v>
+      </c>
+      <c r="R45">
+        <v>212</v>
+      </c>
+      <c r="S45">
+        <v>212</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>3490</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E46" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46">
+        <v>4</v>
+      </c>
+      <c r="J46">
+        <v>1000</v>
+      </c>
+      <c r="K46">
+        <v>2000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>65</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>75</v>
+      </c>
+      <c r="R46">
+        <v>315</v>
+      </c>
+      <c r="S46">
+        <v>315</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>5</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>2220</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" t="s">
+        <v>52</v>
+      </c>
+      <c r="F47" t="s">
+        <v>59</v>
+      </c>
+      <c r="G47" t="s">
+        <v>53</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47">
+        <v>1.5</v>
+      </c>
+      <c r="J47">
+        <v>1250</v>
+      </c>
+      <c r="K47">
+        <v>2500</v>
+      </c>
+      <c r="L47" t="s">
+        <v>65</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>75</v>
+      </c>
+      <c r="R47">
+        <v>295</v>
+      </c>
+      <c r="S47">
+        <v>295</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>8</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>2220</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>654.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" t="s">
+        <v>52</v>
+      </c>
+      <c r="F48" t="s">
+        <v>59</v>
+      </c>
+      <c r="G48" t="s">
+        <v>53</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>5</v>
+      </c>
+      <c r="J48">
+        <v>1000</v>
+      </c>
+      <c r="K48">
+        <v>2000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>75</v>
+      </c>
+      <c r="R48">
+        <v>944</v>
+      </c>
+      <c r="S48">
+        <v>944</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>2020</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>151</v>
+      </c>
+      <c r="B49" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" t="s">
+        <v>59</v>
+      </c>
+      <c r="G49" t="s">
+        <v>53</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>1.5</v>
+      </c>
+      <c r="J49">
+        <v>1000</v>
+      </c>
+      <c r="K49">
+        <v>2000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>65</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>75</v>
+      </c>
+      <c r="R49">
+        <v>260</v>
+      </c>
+      <c r="S49">
+        <v>260</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>11</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>2220</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>577.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" t="s">
+        <v>73</v>
+      </c>
+      <c r="D50" t="s">
+        <v>154</v>
+      </c>
+      <c r="E50" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" t="s">
+        <v>59</v>
+      </c>
+      <c r="G50" t="s">
+        <v>91</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>1500</v>
+      </c>
+      <c r="K50">
+        <v>3000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>65</v>
+      </c>
+      <c r="M50" t="s">
+        <v>101</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>75</v>
+      </c>
+      <c r="R50">
+        <v>1224</v>
+      </c>
+      <c r="S50">
+        <v>1224</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>34</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>3540</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>155</v>
+      </c>
+      <c r="B51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" t="s">
+        <v>52</v>
+      </c>
+      <c r="F51" t="s">
+        <v>59</v>
+      </c>
+      <c r="G51" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>1.5</v>
+      </c>
+      <c r="J51">
+        <v>1500</v>
+      </c>
+      <c r="K51">
+        <v>3000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>86</v>
+      </c>
+      <c r="M51" t="s">
+        <v>101</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>75</v>
+      </c>
+      <c r="R51">
+        <v>916</v>
+      </c>
+      <c r="S51">
+        <v>916</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>18</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>1320</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>157</v>
+      </c>
+      <c r="B52" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" t="s">
+        <v>52</v>
+      </c>
+      <c r="F52" t="s">
+        <v>59</v>
+      </c>
+      <c r="G52" t="s">
+        <v>91</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>3</v>
+      </c>
+      <c r="J52">
+        <v>1500</v>
+      </c>
+      <c r="K52">
+        <v>3000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>65</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>75</v>
+      </c>
+      <c r="R52">
+        <v>319</v>
+      </c>
+      <c r="S52">
+        <v>319</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>1</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>3540</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" t="s">
+        <v>59</v>
+      </c>
+      <c r="G53" t="s">
+        <v>91</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>3</v>
+      </c>
+      <c r="J53">
+        <v>1500</v>
+      </c>
+      <c r="K53">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>65</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>75</v>
+      </c>
+      <c r="R53">
+        <v>212</v>
+      </c>
+      <c r="S53">
+        <v>212</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>1</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>3490</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" t="s">
+        <v>52</v>
+      </c>
+      <c r="F54" t="s">
+        <v>59</v>
+      </c>
+      <c r="G54" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>3</v>
+      </c>
+      <c r="J54">
+        <v>1500</v>
+      </c>
+      <c r="K54">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>65</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>75</v>
+      </c>
+      <c r="R54">
+        <v>212</v>
+      </c>
+      <c r="S54">
+        <v>212</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>1</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>3490</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" t="s">
+        <v>144</v>
+      </c>
+      <c r="E55" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55" t="s">
+        <v>59</v>
+      </c>
+      <c r="G55" t="s">
+        <v>91</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>3</v>
+      </c>
+      <c r="J55">
+        <v>1500</v>
+      </c>
+      <c r="K55">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>65</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>75</v>
+      </c>
+      <c r="R55">
+        <v>319</v>
+      </c>
+      <c r="S55">
+        <v>319</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>1</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>3540</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>161</v>
+      </c>
+      <c r="B56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56" t="s">
+        <v>162</v>
+      </c>
+      <c r="E56" t="s">
+        <v>52</v>
+      </c>
+      <c r="F56" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56" t="s">
+        <v>53</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>1.2</v>
+      </c>
+      <c r="J56">
+        <v>1250</v>
+      </c>
+      <c r="K56">
+        <v>2500</v>
+      </c>
+      <c r="L56" t="s">
+        <v>65</v>
+      </c>
+      <c r="M56" t="s">
+        <v>101</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>75</v>
+      </c>
+      <c r="R56">
+        <v>568</v>
+      </c>
+      <c r="S56">
+        <v>568</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>19</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>2170</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>1232.56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>163</v>
+      </c>
+      <c r="B57" t="s">
+        <v>72</v>
+      </c>
+      <c r="C57" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" t="s">
+        <v>164</v>
+      </c>
+      <c r="E57" t="s">
+        <v>52</v>
+      </c>
+      <c r="F57" t="s">
+        <v>59</v>
+      </c>
+      <c r="G57" t="s">
+        <v>53</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>1.2</v>
+      </c>
+      <c r="J57">
+        <v>1500</v>
+      </c>
+      <c r="K57">
+        <v>3000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>65</v>
+      </c>
+      <c r="M57" t="s">
+        <v>165</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>75</v>
+      </c>
+      <c r="R57">
+        <v>660</v>
+      </c>
+      <c r="S57">
+        <v>660</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>15</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>2170</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>1432.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>166</v>
+      </c>
+      <c r="B58" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" t="s">
+        <v>167</v>
+      </c>
+      <c r="E58" t="s">
+        <v>52</v>
+      </c>
+      <c r="F58" t="s">
+        <v>59</v>
+      </c>
+      <c r="G58" t="s">
+        <v>53</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>6</v>
+      </c>
+      <c r="J58">
+        <v>2000</v>
+      </c>
+      <c r="K58">
+        <v>4000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>65</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>75</v>
+      </c>
+      <c r="R58">
+        <v>756</v>
+      </c>
+      <c r="S58">
+        <v>756</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>2</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>2240</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>1693.44</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>168</v>
+      </c>
+      <c r="B59" t="s">
+        <v>72</v>
+      </c>
+      <c r="C59" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59" t="s">
+        <v>169</v>
+      </c>
+      <c r="E59" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59" t="s">
+        <v>59</v>
+      </c>
+      <c r="G59" t="s">
+        <v>170</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+      <c r="J59">
+        <v>1000</v>
+      </c>
+      <c r="K59">
+        <v>2000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>86</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>75</v>
+      </c>
+      <c r="R59">
+        <v>544</v>
+      </c>
+      <c r="S59">
+        <v>544</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>1</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2220</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>1207.68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>171</v>
+      </c>
+      <c r="B60" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" t="s">
+        <v>172</v>
+      </c>
+      <c r="E60" t="s">
+        <v>52</v>
+      </c>
+      <c r="F60" t="s">
+        <v>59</v>
+      </c>
+      <c r="G60" t="s">
+        <v>85</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>1.5</v>
+      </c>
+      <c r="J60">
+        <v>1250</v>
+      </c>
+      <c r="K60">
+        <v>2500</v>
+      </c>
+      <c r="L60" t="s">
+        <v>86</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>75</v>
+      </c>
+      <c r="R60">
+        <v>898</v>
+      </c>
+      <c r="S60">
+        <v>898</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>1</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>1370</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>1230.26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>173</v>
+      </c>
+      <c r="B61" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" t="s">
+        <v>174</v>
+      </c>
+      <c r="E61" t="s">
+        <v>52</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>85</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>0.8</v>
+      </c>
+      <c r="J61">
+        <v>1250</v>
+      </c>
+      <c r="L61" t="s">
+        <v>86</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>75</v>
+      </c>
+      <c r="R61">
+        <v>2650</v>
+      </c>
+      <c r="S61">
+        <v>2650</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>1</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>1520</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>175</v>
+      </c>
+      <c r="B62" t="s">
+        <v>72</v>
+      </c>
+      <c r="C62" t="s">
+        <v>73</v>
+      </c>
+      <c r="D62" t="s">
+        <v>176</v>
+      </c>
+      <c r="E62" t="s">
+        <v>52</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" t="s">
+        <v>135</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>0.8</v>
+      </c>
+      <c r="J62">
+        <v>1000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>86</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>75</v>
+      </c>
+      <c r="R62">
+        <v>1000</v>
+      </c>
+      <c r="S62">
+        <v>1000</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>1</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>2370</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>177</v>
+      </c>
+      <c r="B63" t="s">
+        <v>81</v>
+      </c>
+      <c r="C63" t="s">
+        <v>73</v>
+      </c>
+      <c r="D63" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" t="s">
+        <v>52</v>
+      </c>
+      <c r="F63" t="s">
+        <v>59</v>
+      </c>
+      <c r="G63" t="s">
+        <v>53</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>1.5</v>
+      </c>
+      <c r="J63">
+        <v>1250</v>
+      </c>
+      <c r="K63">
+        <v>2500</v>
+      </c>
+      <c r="L63" t="s">
+        <v>65</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>75</v>
+      </c>
+      <c r="R63">
+        <v>258</v>
+      </c>
+      <c r="S63">
+        <v>258</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>7</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>2220</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>572.76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>178</v>
+      </c>
+      <c r="B64" t="s">
+        <v>81</v>
+      </c>
+      <c r="C64" t="s">
+        <v>73</v>
+      </c>
+      <c r="D64" t="s">
+        <v>179</v>
+      </c>
+      <c r="E64" t="s">
+        <v>52</v>
+      </c>
+      <c r="F64" t="s">
+        <v>59</v>
+      </c>
+      <c r="G64" t="s">
+        <v>53</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>2</v>
+      </c>
+      <c r="J64">
+        <v>1500</v>
+      </c>
+      <c r="K64">
+        <v>3000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>65</v>
+      </c>
+      <c r="M64" t="s">
+        <v>180</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>113</v>
+      </c>
+      <c r="P64" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>75</v>
+      </c>
+      <c r="R64">
+        <v>496</v>
+      </c>
+      <c r="S64">
+        <v>496</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>7</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>2170</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>1076.32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>181</v>
+      </c>
+      <c r="B65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C65" t="s">
+        <v>73</v>
+      </c>
+      <c r="D65" t="s">
+        <v>182</v>
+      </c>
+      <c r="E65" t="s">
+        <v>52</v>
+      </c>
+      <c r="F65" t="s">
+        <v>59</v>
+      </c>
+      <c r="G65" t="s">
+        <v>53</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>2.5</v>
+      </c>
+      <c r="J65">
+        <v>1500</v>
+      </c>
+      <c r="K65">
+        <v>3000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>65</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>75</v>
+      </c>
+      <c r="R65">
+        <v>266</v>
+      </c>
+      <c r="S65">
+        <v>266</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>3</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>2220</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>183</v>
+      </c>
+      <c r="B66" t="s">
+        <v>81</v>
+      </c>
+      <c r="C66" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" t="s">
+        <v>182</v>
+      </c>
+      <c r="E66" t="s">
+        <v>52</v>
+      </c>
+      <c r="F66" t="s">
+        <v>59</v>
+      </c>
+      <c r="G66" t="s">
+        <v>53</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>2.5</v>
+      </c>
+      <c r="J66">
+        <v>1500</v>
+      </c>
+      <c r="K66">
+        <v>3000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>65</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>75</v>
+      </c>
+      <c r="R66">
+        <v>354</v>
+      </c>
+      <c r="S66">
+        <v>354</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>4</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>2220</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" t="s">
+        <v>81</v>
+      </c>
+      <c r="C67" t="s">
+        <v>73</v>
+      </c>
+      <c r="D67" t="s">
+        <v>182</v>
+      </c>
+      <c r="E67" t="s">
+        <v>52</v>
+      </c>
+      <c r="F67" t="s">
+        <v>59</v>
+      </c>
+      <c r="G67" t="s">
+        <v>53</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>2.5</v>
+      </c>
+      <c r="J67">
+        <v>1500</v>
+      </c>
+      <c r="K67">
+        <v>3000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>65</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>75</v>
+      </c>
+      <c r="R67">
+        <v>620</v>
+      </c>
+      <c r="S67">
+        <v>620</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>7</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>2220</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>1376.4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>185</v>
+      </c>
+      <c r="B68" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" t="s">
+        <v>73</v>
+      </c>
+      <c r="D68" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" t="s">
+        <v>52</v>
+      </c>
+      <c r="F68" t="s">
+        <v>59</v>
+      </c>
+      <c r="G68" t="s">
+        <v>91</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>1.5</v>
+      </c>
+      <c r="J68">
+        <v>1500</v>
+      </c>
+      <c r="K68">
+        <v>3000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>65</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>75</v>
+      </c>
+      <c r="R68">
+        <v>266</v>
+      </c>
+      <c r="S68">
+        <v>266</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>5</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>3540</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>941.64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>187</v>
+      </c>
+      <c r="B69" t="s">
+        <v>81</v>
+      </c>
+      <c r="C69" t="s">
+        <v>73</v>
+      </c>
+      <c r="D69" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" t="s">
+        <v>52</v>
+      </c>
+      <c r="F69" t="s">
+        <v>59</v>
+      </c>
+      <c r="G69" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>2.5</v>
+      </c>
+      <c r="J69">
+        <v>2000</v>
+      </c>
+      <c r="K69">
+        <v>4000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>65</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>75</v>
+      </c>
+      <c r="R69">
+        <v>315</v>
+      </c>
+      <c r="S69">
+        <v>315</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>2</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>3560</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C70" t="s">
+        <v>73</v>
+      </c>
+      <c r="D70" t="s">
+        <v>188</v>
+      </c>
+      <c r="E70" t="s">
+        <v>52</v>
+      </c>
+      <c r="F70" t="s">
+        <v>59</v>
+      </c>
+      <c r="G70" t="s">
+        <v>91</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>2.5</v>
+      </c>
+      <c r="J70">
+        <v>2000</v>
+      </c>
+      <c r="K70">
+        <v>4000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>65</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>38</v>
+      </c>
+      <c r="P70" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>75</v>
+      </c>
+      <c r="R70">
+        <v>315</v>
+      </c>
+      <c r="S70">
+        <v>315</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>2</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>3560</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>190</v>
+      </c>
+      <c r="B71" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" t="s">
+        <v>73</v>
+      </c>
+      <c r="D71" t="s">
+        <v>191</v>
+      </c>
+      <c r="E71" t="s">
+        <v>52</v>
+      </c>
+      <c r="F71" t="s">
+        <v>59</v>
+      </c>
+      <c r="G71" t="s">
+        <v>53</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+      <c r="J71">
+        <v>1500</v>
+      </c>
+      <c r="K71">
+        <v>3000</v>
+      </c>
+      <c r="L71" t="s">
+        <v>65</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>75</v>
+      </c>
+      <c r="R71">
+        <v>283</v>
+      </c>
+      <c r="S71">
+        <v>283</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>4</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>2220</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>192</v>
+      </c>
+      <c r="B72" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" t="s">
+        <v>73</v>
+      </c>
+      <c r="D72" t="s">
+        <v>193</v>
+      </c>
+      <c r="E72" t="s">
+        <v>52</v>
+      </c>
+      <c r="F72" t="s">
+        <v>59</v>
+      </c>
+      <c r="G72" t="s">
+        <v>53</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>0.8</v>
+      </c>
+      <c r="J72">
+        <v>1500</v>
+      </c>
+      <c r="K72">
+        <v>3000</v>
+      </c>
+      <c r="L72" t="s">
+        <v>65</v>
+      </c>
+      <c r="M72" t="s">
+        <v>101</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>113</v>
+      </c>
+      <c r="P72" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R72">
+        <v>833</v>
+      </c>
+      <c r="S72">
+        <v>833</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>29</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>2270</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>1890.91</v>
+      </c>
+      <c r="AB72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>194</v>
+      </c>
+      <c r="B73" t="s">
+        <v>72</v>
+      </c>
+      <c r="C73" t="s">
+        <v>73</v>
+      </c>
+      <c r="D73" t="s">
+        <v>193</v>
+      </c>
+      <c r="E73" t="s">
+        <v>52</v>
+      </c>
+      <c r="F73" t="s">
+        <v>59</v>
+      </c>
+      <c r="G73" t="s">
+        <v>53</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>0.8</v>
+      </c>
+      <c r="J73">
+        <v>1500</v>
+      </c>
+      <c r="K73">
+        <v>3000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>65</v>
+      </c>
+      <c r="M73" t="s">
+        <v>101</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>113</v>
+      </c>
+      <c r="P73" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>75</v>
+      </c>
+      <c r="R73">
+        <v>805</v>
+      </c>
+      <c r="S73">
+        <v>805</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>28</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>2270</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>1827.35</v>
+      </c>
+      <c r="AB73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>195</v>
+      </c>
+      <c r="B74" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" t="s">
+        <v>73</v>
+      </c>
+      <c r="D74" t="s">
+        <v>196</v>
+      </c>
+      <c r="E74" t="s">
+        <v>52</v>
+      </c>
+      <c r="F74" t="s">
+        <v>59</v>
+      </c>
+      <c r="G74" t="s">
+        <v>53</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+      <c r="J74">
+        <v>1000</v>
+      </c>
+      <c r="K74">
+        <v>2000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>65</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>75</v>
+      </c>
+      <c r="R74">
+        <v>1448</v>
+      </c>
+      <c r="S74">
+        <v>1448</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>1</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>2270</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>3286.96</v>
+      </c>
+      <c r="AB74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>197</v>
+      </c>
+      <c r="B75" t="s">
+        <v>89</v>
+      </c>
+      <c r="C75" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75" t="s">
+        <v>198</v>
+      </c>
+      <c r="E75" t="s">
+        <v>52</v>
+      </c>
+      <c r="F75" t="s">
+        <v>59</v>
+      </c>
+      <c r="G75" t="s">
+        <v>85</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>4</v>
+      </c>
+      <c r="J75">
+        <v>1000</v>
+      </c>
+      <c r="K75">
+        <v>2000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>65</v>
+      </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>75</v>
+      </c>
+      <c r="R75">
+        <v>384</v>
+      </c>
+      <c r="S75">
+        <v>384</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>6</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>1370</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>199</v>
+      </c>
+      <c r="B76" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" t="s">
+        <v>73</v>
+      </c>
+      <c r="D76" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" t="s">
+        <v>52</v>
+      </c>
+      <c r="F76" t="s">
+        <v>59</v>
+      </c>
+      <c r="G76" t="s">
+        <v>91</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>6</v>
+      </c>
+      <c r="J76">
+        <v>1500</v>
+      </c>
+      <c r="K76">
+        <v>3000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>65</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>75</v>
+      </c>
+      <c r="R76">
+        <v>850</v>
+      </c>
+      <c r="S76">
+        <v>850</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>4</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>3540</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>200</v>
+      </c>
+      <c r="B77" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D77" t="s">
+        <v>201</v>
+      </c>
+      <c r="E77" t="s">
+        <v>52</v>
+      </c>
+      <c r="F77" t="s">
+        <v>59</v>
+      </c>
+      <c r="G77" t="s">
+        <v>53</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>3</v>
+      </c>
+      <c r="J77">
+        <v>1500</v>
+      </c>
+      <c r="K77">
+        <v>3000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>65</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>75</v>
+      </c>
+      <c r="R77">
+        <v>632</v>
+      </c>
+      <c r="S77">
+        <v>632</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>6</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>2220</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>1403.04</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>202</v>
+      </c>
+      <c r="B78" t="s">
+        <v>72</v>
+      </c>
+      <c r="C78" t="s">
+        <v>73</v>
+      </c>
+      <c r="D78" t="s">
+        <v>203</v>
+      </c>
+      <c r="E78" t="s">
+        <v>52</v>
+      </c>
+      <c r="F78" t="s">
+        <v>59</v>
+      </c>
+      <c r="G78" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>3</v>
+      </c>
+      <c r="J78">
+        <v>1250</v>
+      </c>
+      <c r="K78">
+        <v>2500</v>
+      </c>
+      <c r="L78" t="s">
+        <v>65</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>75</v>
+      </c>
+      <c r="R78">
+        <v>450</v>
+      </c>
+      <c r="S78">
+        <v>450</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>6</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>2220</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>204</v>
+      </c>
+      <c r="B79" t="s">
+        <v>72</v>
+      </c>
+      <c r="C79" t="s">
+        <v>73</v>
+      </c>
+      <c r="D79" t="s">
+        <v>205</v>
+      </c>
+      <c r="E79" t="s">
+        <v>52</v>
+      </c>
+      <c r="F79" t="s">
+        <v>59</v>
+      </c>
+      <c r="G79" t="s">
+        <v>53</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>0.8</v>
+      </c>
+      <c r="J79">
+        <v>1250</v>
+      </c>
+      <c r="K79">
+        <v>2500</v>
+      </c>
+      <c r="L79" t="s">
+        <v>65</v>
+      </c>
+      <c r="M79" t="s">
+        <v>165</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>75</v>
+      </c>
+      <c r="R79">
+        <v>430</v>
+      </c>
+      <c r="S79">
+        <v>430</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>21</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>2270</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>976.1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>206</v>
+      </c>
+      <c r="B80" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" t="s">
+        <v>73</v>
+      </c>
+      <c r="D80" t="s">
+        <v>207</v>
+      </c>
+      <c r="E80" t="s">
+        <v>52</v>
+      </c>
+      <c r="F80" t="s">
+        <v>59</v>
+      </c>
+      <c r="G80" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+      <c r="J80">
+        <v>1000</v>
+      </c>
+      <c r="K80">
+        <v>2000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>65</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>75</v>
+      </c>
+      <c r="R80">
+        <v>283</v>
+      </c>
+      <c r="S80">
+        <v>283</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>9</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>2220</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>208</v>
+      </c>
+      <c r="B81" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" t="s">
+        <v>73</v>
+      </c>
+      <c r="D81" t="s">
+        <v>116</v>
+      </c>
+      <c r="E81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F81" t="s">
+        <v>59</v>
+      </c>
+      <c r="G81" t="s">
+        <v>85</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>3</v>
+      </c>
+      <c r="J81">
+        <v>1500</v>
+      </c>
+      <c r="K81">
+        <v>3000</v>
+      </c>
+      <c r="L81" t="s">
+        <v>65</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>75</v>
+      </c>
+      <c r="R81">
+        <v>637</v>
+      </c>
+      <c r="S81">
+        <v>637</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>6</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>1370</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>872.69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>209</v>
+      </c>
+      <c r="B82" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82" t="s">
+        <v>73</v>
+      </c>
+      <c r="D82" t="s">
+        <v>201</v>
+      </c>
+      <c r="E82" t="s">
+        <v>52</v>
+      </c>
+      <c r="F82" t="s">
+        <v>59</v>
+      </c>
+      <c r="G82" t="s">
+        <v>53</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>3</v>
+      </c>
+      <c r="J82">
+        <v>1500</v>
+      </c>
+      <c r="K82">
+        <v>3000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>65</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>75</v>
+      </c>
+      <c r="R82">
+        <v>636</v>
+      </c>
+      <c r="S82">
+        <v>636</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>6</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>2220</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>1411.92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>210</v>
+      </c>
+      <c r="B83" t="s">
+        <v>72</v>
+      </c>
+      <c r="C83" t="s">
+        <v>73</v>
+      </c>
+      <c r="D83" t="s">
+        <v>211</v>
+      </c>
+      <c r="E83" t="s">
+        <v>52</v>
+      </c>
+      <c r="F83" t="s">
+        <v>59</v>
+      </c>
+      <c r="G83" t="s">
+        <v>53</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>1000</v>
+      </c>
+      <c r="K83">
+        <v>2000</v>
+      </c>
+      <c r="L83" t="s">
+        <v>65</v>
+      </c>
+      <c r="M83" t="s">
+        <v>101</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>75</v>
+      </c>
+      <c r="R83">
+        <v>1482</v>
+      </c>
+      <c r="S83">
+        <v>1482</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>1</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>2220</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>3290.04</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>212</v>
+      </c>
+      <c r="B84" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" t="s">
+        <v>73</v>
+      </c>
+      <c r="D84" t="s">
+        <v>213</v>
+      </c>
+      <c r="E84" t="s">
+        <v>52</v>
+      </c>
+      <c r="F84" t="s">
+        <v>59</v>
+      </c>
+      <c r="G84" t="s">
+        <v>96</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>4</v>
+      </c>
+      <c r="J84">
+        <v>1500</v>
+      </c>
+      <c r="K84">
+        <v>3000</v>
+      </c>
+      <c r="L84" t="s">
+        <v>214</v>
+      </c>
+      <c r="M84" t="s">
+        <v>37</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>75</v>
+      </c>
+      <c r="R84">
+        <v>1133</v>
+      </c>
+      <c r="S84">
+        <v>1133</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>8</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>3540</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>4010.82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>215</v>
+      </c>
+      <c r="B85" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" t="s">
+        <v>73</v>
+      </c>
+      <c r="D85" t="s">
+        <v>216</v>
+      </c>
+      <c r="E85" t="s">
+        <v>52</v>
+      </c>
+      <c r="F85" t="s">
+        <v>59</v>
+      </c>
+      <c r="G85" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>5</v>
+      </c>
+      <c r="J85">
+        <v>2000</v>
+      </c>
+      <c r="K85">
+        <v>4000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>65</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>75</v>
+      </c>
+      <c r="R85">
+        <v>1259</v>
+      </c>
+      <c r="S85">
+        <v>1259</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>4</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>2290</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>2883.11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>217</v>
+      </c>
+      <c r="B86" t="s">
+        <v>89</v>
+      </c>
+      <c r="C86" t="s">
+        <v>73</v>
+      </c>
+      <c r="D86" t="s">
+        <v>218</v>
+      </c>
+      <c r="E86" t="s">
+        <v>52</v>
+      </c>
+      <c r="F86" t="s">
+        <v>59</v>
+      </c>
+      <c r="G86" t="s">
+        <v>53</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>4</v>
+      </c>
+      <c r="J86">
+        <v>2000</v>
+      </c>
+      <c r="K86">
+        <v>4000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>65</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>75</v>
+      </c>
+      <c r="R86">
+        <v>1007</v>
+      </c>
+      <c r="S86">
+        <v>1007</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>4</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>2290</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>2306.03</v>
+      </c>
+      <c r="AB86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>219</v>
+      </c>
+      <c r="B87" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" t="s">
+        <v>73</v>
+      </c>
+      <c r="D87" t="s">
+        <v>220</v>
+      </c>
+      <c r="E87" t="s">
+        <v>52</v>
+      </c>
+      <c r="F87" t="s">
+        <v>59</v>
+      </c>
+      <c r="G87" t="s">
+        <v>53</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87">
+        <v>0.8</v>
+      </c>
+      <c r="J87">
+        <v>1500</v>
+      </c>
+      <c r="K87">
+        <v>3000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>65</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>75</v>
+      </c>
+      <c r="R87">
+        <v>737</v>
+      </c>
+      <c r="S87">
+        <v>737</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>26</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>2320</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>1709.84</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>221</v>
+      </c>
+      <c r="B88" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88" t="s">
+        <v>73</v>
+      </c>
+      <c r="D88" t="s">
+        <v>220</v>
+      </c>
+      <c r="E88" t="s">
+        <v>52</v>
+      </c>
+      <c r="F88" t="s">
+        <v>59</v>
+      </c>
+      <c r="G88" t="s">
+        <v>53</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88">
+        <v>0.8</v>
+      </c>
+      <c r="J88">
+        <v>1500</v>
+      </c>
+      <c r="K88">
+        <v>3000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>65</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>75</v>
+      </c>
+      <c r="R88">
+        <v>1020</v>
+      </c>
+      <c r="S88">
+        <v>1020</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>36</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>2370</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>2417.4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>222</v>
+      </c>
+      <c r="B89" t="s">
+        <v>89</v>
+      </c>
+      <c r="C89" t="s">
+        <v>73</v>
+      </c>
+      <c r="D89" t="s">
+        <v>220</v>
+      </c>
+      <c r="E89" t="s">
+        <v>52</v>
+      </c>
+      <c r="F89" t="s">
+        <v>59</v>
+      </c>
+      <c r="G89" t="s">
+        <v>53</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89">
+        <v>0.8</v>
+      </c>
+      <c r="J89">
+        <v>1500</v>
+      </c>
+      <c r="K89">
+        <v>3000</v>
+      </c>
+      <c r="L89" t="s">
+        <v>65</v>
+      </c>
+      <c r="M89" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>75</v>
+      </c>
+      <c r="R89">
+        <v>1020</v>
+      </c>
+      <c r="S89">
+        <v>1020</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>36</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>2370</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>2417.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>223</v>
+      </c>
+      <c r="B90" t="s">
+        <v>89</v>
+      </c>
+      <c r="C90" t="s">
+        <v>73</v>
+      </c>
+      <c r="D90" t="s">
+        <v>224</v>
+      </c>
+      <c r="E90" t="s">
+        <v>52</v>
+      </c>
+      <c r="F90" t="s">
+        <v>59</v>
+      </c>
+      <c r="G90" t="s">
+        <v>53</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>6</v>
+      </c>
+      <c r="J90">
+        <v>1500</v>
+      </c>
+      <c r="K90">
+        <v>3000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>65</v>
+      </c>
+      <c r="M90" t="s">
+        <v>37</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>113</v>
+      </c>
+      <c r="P90" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>75</v>
+      </c>
+      <c r="R90">
+        <v>1487</v>
+      </c>
+      <c r="S90">
+        <v>1487</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>7</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>2270</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>3375.49</v>
+      </c>
+      <c r="AB90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>225</v>
+      </c>
+      <c r="B91" t="s">
+        <v>81</v>
+      </c>
+      <c r="C91" t="s">
+        <v>73</v>
+      </c>
+      <c r="D91" t="s">
+        <v>226</v>
+      </c>
+      <c r="E91" t="s">
+        <v>52</v>
+      </c>
+      <c r="F91" t="s">
+        <v>59</v>
+      </c>
+      <c r="G91" t="s">
+        <v>53</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91">
+        <v>8</v>
+      </c>
+      <c r="J91">
+        <v>2000</v>
+      </c>
+      <c r="K91">
+        <v>6000</v>
+      </c>
+      <c r="L91" t="s">
+        <v>36</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>75</v>
+      </c>
+      <c r="R91">
+        <v>755</v>
+      </c>
+      <c r="S91">
+        <v>755</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>1</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>2040</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>1540.2</v>
+      </c>
+      <c r="AB91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>227</v>
+      </c>
+      <c r="B92" t="s">
+        <v>72</v>
+      </c>
+      <c r="C92" t="s">
+        <v>73</v>
+      </c>
+      <c r="D92" t="s">
+        <v>228</v>
+      </c>
+      <c r="E92" t="s">
+        <v>52</v>
+      </c>
+      <c r="F92" t="s">
+        <v>59</v>
+      </c>
+      <c r="G92" t="s">
+        <v>53</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>1250</v>
+      </c>
+      <c r="K92">
+        <v>2500</v>
+      </c>
+      <c r="L92" t="s">
+        <v>65</v>
+      </c>
+      <c r="M92" t="s">
+        <v>229</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>230</v>
+      </c>
+      <c r="P92" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>75</v>
+      </c>
+      <c r="R92">
+        <v>1019</v>
+      </c>
+      <c r="S92">
+        <v>1019</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>41</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>2220</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>2262.18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>231</v>
+      </c>
+      <c r="B93" t="s">
+        <v>72</v>
+      </c>
+      <c r="C93" t="s">
+        <v>73</v>
+      </c>
+      <c r="D93" t="s">
+        <v>232</v>
+      </c>
+      <c r="E93" t="s">
+        <v>52</v>
+      </c>
+      <c r="F93" t="s">
+        <v>59</v>
+      </c>
+      <c r="G93" t="s">
+        <v>170</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93">
+        <v>0.6</v>
+      </c>
+      <c r="J93">
+        <v>1250</v>
+      </c>
+      <c r="K93">
+        <v>2500</v>
+      </c>
+      <c r="L93" t="s">
+        <v>65</v>
+      </c>
+      <c r="M93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" t="s">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>75</v>
+      </c>
+      <c r="R93">
+        <v>794</v>
+      </c>
+      <c r="S93">
+        <v>794</v>
+      </c>
+      <c r="T93" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93">
+        <v>54</v>
+      </c>
+      <c r="V93" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93">
+        <v>2320</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA93">
+        <v>1842.08</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>233</v>
+      </c>
+      <c r="B94" t="s">
+        <v>89</v>
+      </c>
+      <c r="C94" t="s">
+        <v>73</v>
+      </c>
+      <c r="D94" t="s">
+        <v>234</v>
+      </c>
+      <c r="E94" t="s">
+        <v>52</v>
+      </c>
+      <c r="F94" t="s">
+        <v>59</v>
+      </c>
+      <c r="G94" t="s">
+        <v>53</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94">
+        <v>8</v>
+      </c>
+      <c r="J94">
+        <v>1000</v>
+      </c>
+      <c r="K94">
+        <v>2000</v>
+      </c>
+      <c r="L94" t="s">
+        <v>36</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
+      </c>
+      <c r="N94" t="s">
+        <v>37</v>
+      </c>
+      <c r="O94" t="s">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>75</v>
+      </c>
+      <c r="R94">
+        <v>504</v>
+      </c>
+      <c r="S94">
+        <v>504</v>
+      </c>
+      <c r="T94" t="s">
+        <v>41</v>
+      </c>
+      <c r="U94">
+        <v>4</v>
+      </c>
+      <c r="V94" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94">
+        <v>2020</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA94">
+        <v>1018.08</v>
+      </c>
+      <c r="AB94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>235</v>
+      </c>
+      <c r="B95" t="s">
+        <v>81</v>
+      </c>
+      <c r="C95" t="s">
+        <v>73</v>
+      </c>
+      <c r="D95" t="s">
+        <v>191</v>
+      </c>
+      <c r="E95" t="s">
+        <v>52</v>
+      </c>
+      <c r="F95" t="s">
+        <v>59</v>
+      </c>
+      <c r="G95" t="s">
+        <v>53</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95">
+        <v>1500</v>
+      </c>
+      <c r="K95">
+        <v>3000</v>
+      </c>
+      <c r="L95" t="s">
+        <v>65</v>
+      </c>
+      <c r="M95" t="s">
+        <v>37</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>75</v>
+      </c>
+      <c r="R95">
+        <v>1133</v>
+      </c>
+      <c r="S95">
+        <v>1133</v>
+      </c>
+      <c r="T95" t="s">
+        <v>41</v>
+      </c>
+      <c r="U95">
+        <v>16</v>
+      </c>
+      <c r="V95" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95">
+        <v>2270</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA95">
+        <v>2571.91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>236</v>
+      </c>
+      <c r="B96" t="s">
+        <v>81</v>
+      </c>
+      <c r="C96" t="s">
+        <v>73</v>
+      </c>
+      <c r="D96" t="s">
+        <v>191</v>
+      </c>
+      <c r="E96" t="s">
+        <v>52</v>
+      </c>
+      <c r="F96" t="s">
+        <v>59</v>
+      </c>
+      <c r="G96" t="s">
+        <v>53</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
+        <v>1500</v>
+      </c>
+      <c r="K96">
+        <v>3000</v>
+      </c>
+      <c r="L96" t="s">
+        <v>65</v>
+      </c>
+      <c r="M96" t="s">
+        <v>37</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
+      </c>
+      <c r="P96" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>75</v>
+      </c>
+      <c r="R96">
+        <v>1204</v>
+      </c>
+      <c r="S96">
+        <v>1204</v>
+      </c>
+      <c r="T96" t="s">
+        <v>41</v>
+      </c>
+      <c r="U96">
+        <v>17</v>
+      </c>
+      <c r="V96" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X96">
+        <v>2270</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA96">
+        <v>2733.08</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>237</v>
+      </c>
+      <c r="B97" t="s">
+        <v>81</v>
+      </c>
+      <c r="C97" t="s">
+        <v>73</v>
+      </c>
+      <c r="D97" t="s">
+        <v>238</v>
+      </c>
+      <c r="E97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F97" t="s">
+        <v>59</v>
+      </c>
+      <c r="G97" t="s">
+        <v>53</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97">
+        <v>12</v>
+      </c>
+      <c r="J97">
+        <v>1000</v>
+      </c>
+      <c r="K97">
+        <v>2000</v>
+      </c>
+      <c r="L97" t="s">
+        <v>36</v>
+      </c>
+      <c r="M97" t="s">
+        <v>37</v>
+      </c>
+      <c r="N97" t="s">
+        <v>37</v>
+      </c>
+      <c r="O97" t="s">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>75</v>
+      </c>
+      <c r="R97">
+        <v>1322</v>
+      </c>
+      <c r="S97">
+        <v>1322</v>
+      </c>
+      <c r="T97" t="s">
+        <v>41</v>
+      </c>
+      <c r="U97">
+        <v>7</v>
+      </c>
+      <c r="V97" t="s">
+        <v>43</v>
+      </c>
+      <c r="W97" t="s">
+        <v>43</v>
+      </c>
+      <c r="X97">
+        <v>2070</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA97">
+        <v>2736.54</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>239</v>
+      </c>
+      <c r="B98" t="s">
+        <v>81</v>
+      </c>
+      <c r="C98" t="s">
+        <v>73</v>
+      </c>
+      <c r="D98" t="s">
+        <v>240</v>
+      </c>
+      <c r="E98" t="s">
+        <v>52</v>
+      </c>
+      <c r="F98" t="s">
+        <v>59</v>
+      </c>
+      <c r="G98" t="s">
+        <v>53</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>1250</v>
+      </c>
+      <c r="K98">
+        <v>2500</v>
+      </c>
+      <c r="L98" t="s">
+        <v>65</v>
+      </c>
+      <c r="M98" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" t="s">
+        <v>38</v>
+      </c>
+      <c r="P98" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>75</v>
+      </c>
+      <c r="R98">
+        <v>615</v>
+      </c>
+      <c r="S98">
+        <v>615</v>
+      </c>
+      <c r="T98" t="s">
+        <v>41</v>
+      </c>
+      <c r="U98">
+        <v>25</v>
+      </c>
+      <c r="V98" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98">
+        <v>2220</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA98">
+        <v>1365.3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>241</v>
+      </c>
+      <c r="B99" t="s">
+        <v>81</v>
+      </c>
+      <c r="C99" t="s">
+        <v>73</v>
+      </c>
+      <c r="D99" t="s">
+        <v>240</v>
+      </c>
+      <c r="E99" t="s">
+        <v>52</v>
+      </c>
+      <c r="F99" t="s">
+        <v>59</v>
+      </c>
+      <c r="G99" t="s">
+        <v>53</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>1250</v>
+      </c>
+      <c r="K99">
+        <v>2500</v>
+      </c>
+      <c r="L99" t="s">
+        <v>65</v>
+      </c>
+      <c r="M99" t="s">
+        <v>37</v>
+      </c>
+      <c r="N99" t="s">
+        <v>37</v>
+      </c>
+      <c r="O99" t="s">
+        <v>38</v>
+      </c>
+      <c r="P99" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>75</v>
+      </c>
+      <c r="R99">
+        <v>590</v>
+      </c>
+      <c r="S99">
+        <v>590</v>
+      </c>
+      <c r="T99" t="s">
+        <v>41</v>
+      </c>
+      <c r="U99">
+        <v>24</v>
+      </c>
+      <c r="V99" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99">
+        <v>2220</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA99">
+        <v>1309.8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>242</v>
+      </c>
+      <c r="B100" t="s">
+        <v>72</v>
+      </c>
+      <c r="C100" t="s">
+        <v>73</v>
+      </c>
+      <c r="D100" t="s">
+        <v>103</v>
+      </c>
+      <c r="E100" t="s">
+        <v>52</v>
+      </c>
+      <c r="F100" t="s">
+        <v>59</v>
+      </c>
+      <c r="G100" t="s">
+        <v>91</v>
+      </c>
+      <c r="H100" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100">
+        <v>2.5</v>
+      </c>
+      <c r="J100">
+        <v>1500</v>
+      </c>
+      <c r="K100">
+        <v>3000</v>
+      </c>
+      <c r="L100" t="s">
+        <v>65</v>
+      </c>
+      <c r="M100" t="s">
+        <v>37</v>
+      </c>
+      <c r="N100" t="s">
+        <v>37</v>
+      </c>
+      <c r="O100" t="s">
+        <v>38</v>
+      </c>
+      <c r="P100" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>75</v>
+      </c>
+      <c r="R100">
+        <v>534</v>
+      </c>
+      <c r="S100">
+        <v>534</v>
+      </c>
+      <c r="T100" t="s">
+        <v>41</v>
+      </c>
+      <c r="U100">
+        <v>6</v>
+      </c>
+      <c r="V100" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100">
+        <v>3540</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA100">
+        <v>1890.36</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>243</v>
+      </c>
+      <c r="B101" t="s">
+        <v>72</v>
+      </c>
+      <c r="C101" t="s">
+        <v>73</v>
+      </c>
+      <c r="D101" t="s">
+        <v>244</v>
+      </c>
+      <c r="E101" t="s">
+        <v>52</v>
+      </c>
+      <c r="F101" t="s">
+        <v>59</v>
+      </c>
+      <c r="G101" t="s">
+        <v>53</v>
+      </c>
+      <c r="H101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101">
+        <v>0.8</v>
+      </c>
+      <c r="J101">
+        <v>1250</v>
+      </c>
+      <c r="K101">
+        <v>2500</v>
+      </c>
+      <c r="L101" t="s">
+        <v>65</v>
+      </c>
+      <c r="M101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N101" t="s">
+        <v>37</v>
+      </c>
+      <c r="O101" t="s">
+        <v>38</v>
+      </c>
+      <c r="P101" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>75</v>
+      </c>
+      <c r="R101">
+        <v>2033</v>
+      </c>
+      <c r="S101">
+        <v>2033</v>
+      </c>
+      <c r="T101" t="s">
+        <v>41</v>
+      </c>
+      <c r="U101">
+        <v>101</v>
+      </c>
+      <c r="V101" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101">
+        <v>2370</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA101">
+        <v>4818.21</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>245</v>
+      </c>
+      <c r="B102" t="s">
+        <v>72</v>
+      </c>
+      <c r="C102" t="s">
+        <v>73</v>
+      </c>
+      <c r="D102" t="s">
+        <v>246</v>
+      </c>
+      <c r="E102" t="s">
+        <v>52</v>
+      </c>
+      <c r="F102" t="s">
+        <v>59</v>
+      </c>
+      <c r="G102" t="s">
+        <v>91</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
+      </c>
+      <c r="J102">
+        <v>1000</v>
+      </c>
+      <c r="K102">
+        <v>2000</v>
+      </c>
+      <c r="L102" t="s">
+        <v>65</v>
+      </c>
+      <c r="M102" t="s">
+        <v>101</v>
+      </c>
+      <c r="N102" t="s">
+        <v>37</v>
+      </c>
+      <c r="O102" t="s">
+        <v>38</v>
+      </c>
+      <c r="P102" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>75</v>
+      </c>
+      <c r="R102">
+        <v>1046</v>
+      </c>
+      <c r="S102">
+        <v>1046</v>
+      </c>
+      <c r="T102" t="s">
+        <v>41</v>
+      </c>
+      <c r="U102">
+        <v>33</v>
+      </c>
+      <c r="V102" t="s">
+        <v>43</v>
+      </c>
+      <c r="W102" t="s">
+        <v>43</v>
+      </c>
+      <c r="X102">
+        <v>3540</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA102">
+        <v>3702.84</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>247</v>
+      </c>
+      <c r="B103" t="s">
+        <v>81</v>
+      </c>
+      <c r="C103" t="s">
+        <v>73</v>
+      </c>
+      <c r="D103" t="s">
+        <v>191</v>
+      </c>
+      <c r="E103" t="s">
+        <v>52</v>
+      </c>
+      <c r="F103" t="s">
+        <v>59</v>
+      </c>
+      <c r="G103" t="s">
+        <v>53</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103">
+        <v>2</v>
+      </c>
+      <c r="J103">
+        <v>1500</v>
+      </c>
+      <c r="K103">
+        <v>3000</v>
+      </c>
+      <c r="L103" t="s">
+        <v>65</v>
+      </c>
+      <c r="M103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N103" t="s">
+        <v>37</v>
+      </c>
+      <c r="O103" t="s">
+        <v>38</v>
+      </c>
+      <c r="P103" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>75</v>
+      </c>
+      <c r="R103">
+        <v>2125</v>
+      </c>
+      <c r="S103">
+        <v>2125</v>
+      </c>
+      <c r="T103" t="s">
+        <v>41</v>
+      </c>
+      <c r="U103">
+        <v>30</v>
+      </c>
+      <c r="V103" t="s">
+        <v>43</v>
+      </c>
+      <c r="W103" t="s">
+        <v>43</v>
+      </c>
+      <c r="X103">
+        <v>2270</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA103">
+        <v>4823.75</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>248</v>
+      </c>
+      <c r="B104" t="s">
+        <v>81</v>
+      </c>
+      <c r="C104" t="s">
+        <v>73</v>
+      </c>
+      <c r="D104" t="s">
+        <v>249</v>
+      </c>
+      <c r="E104" t="s">
+        <v>52</v>
+      </c>
+      <c r="F104" t="s">
+        <v>59</v>
+      </c>
+      <c r="G104" t="s">
+        <v>53</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104">
+        <v>4</v>
+      </c>
+      <c r="J104">
+        <v>1500</v>
+      </c>
+      <c r="K104">
+        <v>3000</v>
+      </c>
+      <c r="L104" t="s">
+        <v>65</v>
+      </c>
+      <c r="M104" t="s">
+        <v>37</v>
+      </c>
+      <c r="N104" t="s">
+        <v>37</v>
+      </c>
+      <c r="O104" t="s">
+        <v>38</v>
+      </c>
+      <c r="P104" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>75</v>
+      </c>
+      <c r="R104">
+        <v>142</v>
+      </c>
+      <c r="S104">
+        <v>142</v>
+      </c>
+      <c r="T104" t="s">
+        <v>41</v>
+      </c>
+      <c r="U104">
+        <v>1</v>
+      </c>
+      <c r="V104" t="s">
+        <v>43</v>
+      </c>
+      <c r="W104" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104">
+        <v>2170</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA104">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>250</v>
+      </c>
+      <c r="B105" t="s">
+        <v>72</v>
+      </c>
+      <c r="C105" t="s">
+        <v>73</v>
+      </c>
+      <c r="D105" t="s">
+        <v>251</v>
+      </c>
+      <c r="E105" t="s">
+        <v>52</v>
+      </c>
+      <c r="F105" t="s">
+        <v>59</v>
+      </c>
+      <c r="G105" t="s">
+        <v>53</v>
+      </c>
+      <c r="H105" t="s">
+        <v>35</v>
+      </c>
+      <c r="I105">
+        <v>1.5</v>
+      </c>
+      <c r="J105">
+        <v>1250</v>
+      </c>
+      <c r="K105">
+        <v>2500</v>
+      </c>
+      <c r="L105" t="s">
+        <v>65</v>
+      </c>
+      <c r="M105" t="s">
+        <v>165</v>
+      </c>
+      <c r="N105" t="s">
+        <v>37</v>
+      </c>
+      <c r="O105" t="s">
+        <v>38</v>
+      </c>
+      <c r="P105" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>75</v>
+      </c>
+      <c r="R105">
+        <v>1140</v>
+      </c>
+      <c r="S105">
+        <v>1140</v>
+      </c>
+      <c r="T105" t="s">
+        <v>41</v>
+      </c>
+      <c r="U105">
+        <v>31</v>
+      </c>
+      <c r="V105" t="s">
+        <v>43</v>
+      </c>
+      <c r="W105" t="s">
+        <v>43</v>
+      </c>
+      <c r="X105">
+        <v>2220</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA105">
+        <v>2530.8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>252</v>
+      </c>
+      <c r="B106" t="s">
+        <v>81</v>
+      </c>
+      <c r="C106" t="s">
+        <v>73</v>
+      </c>
+      <c r="D106" t="s">
+        <v>253</v>
+      </c>
+      <c r="E106" t="s">
+        <v>52</v>
+      </c>
+      <c r="F106" t="s">
+        <v>59</v>
+      </c>
+      <c r="G106" t="s">
+        <v>53</v>
+      </c>
+      <c r="H106" t="s">
+        <v>35</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
+      </c>
+      <c r="J106">
+        <v>2000</v>
+      </c>
+      <c r="K106">
+        <v>4000</v>
+      </c>
+      <c r="L106" t="s">
+        <v>65</v>
+      </c>
+      <c r="M106" t="s">
+        <v>37</v>
+      </c>
+      <c r="N106" t="s">
+        <v>37</v>
+      </c>
+      <c r="O106" t="s">
+        <v>38</v>
+      </c>
+      <c r="P106" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>75</v>
+      </c>
+      <c r="R106">
+        <v>126</v>
+      </c>
+      <c r="S106">
+        <v>126</v>
+      </c>
+      <c r="T106" t="s">
+        <v>41</v>
+      </c>
+      <c r="U106">
+        <v>1</v>
+      </c>
+      <c r="V106" t="s">
+        <v>43</v>
+      </c>
+      <c r="W106" t="s">
+        <v>43</v>
+      </c>
+      <c r="X106">
+        <v>2190</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA106">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>254</v>
+      </c>
+      <c r="B107" t="s">
+        <v>72</v>
+      </c>
+      <c r="C107" t="s">
+        <v>73</v>
+      </c>
+      <c r="D107" t="s">
+        <v>255</v>
+      </c>
+      <c r="E107" t="s">
+        <v>52</v>
+      </c>
+      <c r="F107" t="s">
+        <v>59</v>
+      </c>
+      <c r="G107" t="s">
+        <v>53</v>
+      </c>
+      <c r="H107" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107">
+        <v>0.8</v>
+      </c>
+      <c r="J107">
+        <v>1000</v>
+      </c>
+      <c r="K107">
+        <v>2000</v>
+      </c>
+      <c r="L107" t="s">
+        <v>65</v>
+      </c>
+      <c r="M107" t="s">
+        <v>101</v>
+      </c>
+      <c r="N107" t="s">
+        <v>37</v>
+      </c>
+      <c r="O107" t="s">
+        <v>38</v>
+      </c>
+      <c r="P107" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>75</v>
+      </c>
+      <c r="R107">
+        <v>1216</v>
+      </c>
+      <c r="S107">
+        <v>1216</v>
+      </c>
+      <c r="T107" t="s">
+        <v>41</v>
+      </c>
+      <c r="U107">
+        <v>96</v>
+      </c>
+      <c r="V107" t="s">
+        <v>43</v>
+      </c>
+      <c r="W107" t="s">
+        <v>43</v>
+      </c>
+      <c r="X107">
+        <v>2320</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA107">
+        <v>2821.12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>256</v>
+      </c>
+      <c r="B108" t="s">
+        <v>81</v>
+      </c>
+      <c r="C108" t="s">
+        <v>73</v>
+      </c>
+      <c r="D108" t="s">
+        <v>244</v>
+      </c>
+      <c r="E108" t="s">
+        <v>52</v>
+      </c>
+      <c r="F108" t="s">
+        <v>59</v>
+      </c>
+      <c r="G108" t="s">
+        <v>53</v>
+      </c>
+      <c r="H108" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108">
+        <v>0.8</v>
+      </c>
+      <c r="J108">
+        <v>1250</v>
+      </c>
+      <c r="K108">
+        <v>2500</v>
+      </c>
+      <c r="L108" t="s">
+        <v>65</v>
+      </c>
+      <c r="M108" t="s">
+        <v>37</v>
+      </c>
+      <c r="N108" t="s">
+        <v>37</v>
+      </c>
+      <c r="O108" t="s">
+        <v>38</v>
+      </c>
+      <c r="P108" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>75</v>
+      </c>
+      <c r="R108">
+        <v>334</v>
+      </c>
+      <c r="S108">
+        <v>334</v>
+      </c>
+      <c r="T108" t="s">
+        <v>41</v>
+      </c>
+      <c r="U108">
+        <v>17</v>
+      </c>
+      <c r="V108" t="s">
+        <v>43</v>
+      </c>
+      <c r="W108" t="s">
+        <v>43</v>
+      </c>
+      <c r="X108">
+        <v>2320</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA108">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>257</v>
+      </c>
+      <c r="B109" t="s">
+        <v>81</v>
+      </c>
+      <c r="C109" t="s">
+        <v>73</v>
+      </c>
+      <c r="D109" t="s">
+        <v>244</v>
+      </c>
+      <c r="E109" t="s">
+        <v>52</v>
+      </c>
+      <c r="F109" t="s">
+        <v>59</v>
+      </c>
+      <c r="G109" t="s">
+        <v>53</v>
+      </c>
+      <c r="H109" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109">
+        <v>0.8</v>
+      </c>
+      <c r="J109">
+        <v>1250</v>
+      </c>
+      <c r="K109">
+        <v>2500</v>
+      </c>
+      <c r="L109" t="s">
+        <v>65</v>
+      </c>
+      <c r="M109" t="s">
+        <v>37</v>
+      </c>
+      <c r="N109" t="s">
+        <v>37</v>
+      </c>
+      <c r="O109" t="s">
+        <v>38</v>
+      </c>
+      <c r="P109" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>75</v>
+      </c>
+      <c r="R109">
+        <v>334</v>
+      </c>
+      <c r="S109">
+        <v>334</v>
+      </c>
+      <c r="T109" t="s">
+        <v>41</v>
+      </c>
+      <c r="U109">
+        <v>17</v>
+      </c>
+      <c r="V109" t="s">
+        <v>43</v>
+      </c>
+      <c r="W109" t="s">
+        <v>43</v>
+      </c>
+      <c r="X109">
+        <v>2320</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA109">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>258</v>
+      </c>
+      <c r="B110" t="s">
+        <v>81</v>
+      </c>
+      <c r="C110" t="s">
+        <v>73</v>
+      </c>
+      <c r="D110" t="s">
+        <v>244</v>
+      </c>
+      <c r="E110" t="s">
+        <v>52</v>
+      </c>
+      <c r="F110" t="s">
+        <v>59</v>
+      </c>
+      <c r="G110" t="s">
+        <v>53</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110">
+        <v>0.8</v>
+      </c>
+      <c r="J110">
+        <v>1250</v>
+      </c>
+      <c r="K110">
+        <v>2500</v>
+      </c>
+      <c r="L110" t="s">
+        <v>65</v>
+      </c>
+      <c r="M110" t="s">
+        <v>37</v>
+      </c>
+      <c r="N110" t="s">
+        <v>37</v>
+      </c>
+      <c r="O110" t="s">
+        <v>38</v>
+      </c>
+      <c r="P110" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>75</v>
+      </c>
+      <c r="R110">
+        <v>551</v>
+      </c>
+      <c r="S110">
+        <v>551</v>
+      </c>
+      <c r="T110" t="s">
+        <v>41</v>
+      </c>
+      <c r="U110">
+        <v>28</v>
+      </c>
+      <c r="V110" t="s">
+        <v>43</v>
+      </c>
+      <c r="W110" t="s">
+        <v>43</v>
+      </c>
+      <c r="X110">
+        <v>2320</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA110">
+        <v>1278.32</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>259</v>
+      </c>
+      <c r="B111" t="s">
+        <v>72</v>
+      </c>
+      <c r="C111" t="s">
+        <v>73</v>
+      </c>
+      <c r="D111" t="s">
+        <v>260</v>
+      </c>
+      <c r="E111" t="s">
+        <v>52</v>
+      </c>
+      <c r="F111" t="s">
+        <v>59</v>
+      </c>
+      <c r="G111" t="s">
+        <v>91</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111">
+        <v>2</v>
+      </c>
+      <c r="J111">
+        <v>1250</v>
+      </c>
+      <c r="K111">
+        <v>2500</v>
+      </c>
+      <c r="L111" t="s">
+        <v>65</v>
+      </c>
+      <c r="M111" t="s">
+        <v>101</v>
+      </c>
+      <c r="N111" t="s">
+        <v>37</v>
+      </c>
+      <c r="O111" t="s">
+        <v>38</v>
+      </c>
+      <c r="P111" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>75</v>
+      </c>
+      <c r="R111">
+        <v>612</v>
+      </c>
+      <c r="S111">
+        <v>612</v>
+      </c>
+      <c r="T111" t="s">
+        <v>41</v>
+      </c>
+      <c r="U111">
+        <v>12</v>
+      </c>
+      <c r="V111" t="s">
+        <v>43</v>
+      </c>
+      <c r="W111" t="s">
+        <v>43</v>
+      </c>
+      <c r="X111">
+        <v>3490</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA111">
+        <v>2135.88</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>261</v>
+      </c>
+      <c r="B112" t="s">
+        <v>72</v>
+      </c>
+      <c r="C112" t="s">
+        <v>73</v>
+      </c>
+      <c r="D112" t="s">
+        <v>211</v>
+      </c>
+      <c r="E112" t="s">
+        <v>52</v>
+      </c>
+      <c r="F112" t="s">
+        <v>59</v>
+      </c>
+      <c r="G112" t="s">
+        <v>53</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112">
+        <v>1000</v>
+      </c>
+      <c r="K112">
+        <v>2000</v>
+      </c>
+      <c r="L112" t="s">
+        <v>65</v>
+      </c>
+      <c r="M112" t="s">
+        <v>101</v>
+      </c>
+      <c r="N112" t="s">
+        <v>37</v>
+      </c>
+      <c r="O112" t="s">
+        <v>38</v>
+      </c>
+      <c r="P112" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>75</v>
+      </c>
+      <c r="R112">
+        <v>752</v>
+      </c>
+      <c r="S112">
+        <v>752</v>
+      </c>
+      <c r="T112" t="s">
+        <v>41</v>
+      </c>
+      <c r="U112">
+        <v>48</v>
+      </c>
+      <c r="V112" t="s">
+        <v>43</v>
+      </c>
+      <c r="W112" t="s">
+        <v>43</v>
+      </c>
+      <c r="X112">
+        <v>2170</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA112">
+        <v>1631.84</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>262</v>
+      </c>
+      <c r="B113" t="s">
+        <v>89</v>
+      </c>
+      <c r="C113" t="s">
+        <v>73</v>
+      </c>
+      <c r="D113" t="s">
+        <v>263</v>
+      </c>
+      <c r="E113" t="s">
+        <v>52</v>
+      </c>
+      <c r="F113" t="s">
+        <v>59</v>
+      </c>
+      <c r="G113" t="s">
+        <v>96</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113">
+        <v>3</v>
+      </c>
+      <c r="J113">
+        <v>1500</v>
+      </c>
+      <c r="K113">
+        <v>3000</v>
+      </c>
+      <c r="L113" t="s">
+        <v>65</v>
+      </c>
+      <c r="M113" t="s">
+        <v>37</v>
+      </c>
+      <c r="N113" t="s">
+        <v>37</v>
+      </c>
+      <c r="O113" t="s">
+        <v>38</v>
+      </c>
+      <c r="P113" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>75</v>
+      </c>
+      <c r="R113">
+        <v>106</v>
+      </c>
+      <c r="S113">
+        <v>106</v>
+      </c>
+      <c r="T113" t="s">
+        <v>41</v>
+      </c>
+      <c r="U113">
+        <v>1</v>
+      </c>
+      <c r="V113" t="s">
+        <v>43</v>
+      </c>
+      <c r="W113" t="s">
+        <v>43</v>
+      </c>
+      <c r="X113">
+        <v>3640</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA113">
+        <v>385.84</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>264</v>
+      </c>
+      <c r="B114" t="s">
+        <v>72</v>
+      </c>
+      <c r="C114" t="s">
+        <v>73</v>
+      </c>
+      <c r="D114" t="s">
+        <v>186</v>
+      </c>
+      <c r="E114" t="s">
+        <v>52</v>
+      </c>
+      <c r="F114" t="s">
+        <v>59</v>
+      </c>
+      <c r="G114" t="s">
+        <v>91</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114">
+        <v>1.5</v>
+      </c>
+      <c r="J114">
+        <v>1500</v>
+      </c>
+      <c r="K114">
+        <v>3000</v>
+      </c>
+      <c r="L114" t="s">
+        <v>65</v>
+      </c>
+      <c r="M114" t="s">
+        <v>37</v>
+      </c>
+      <c r="N114" t="s">
+        <v>37</v>
+      </c>
+      <c r="O114" t="s">
+        <v>38</v>
+      </c>
+      <c r="P114" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>75</v>
+      </c>
+      <c r="R114">
+        <v>330</v>
+      </c>
+      <c r="S114">
+        <v>330</v>
+      </c>
+      <c r="T114" t="s">
+        <v>41</v>
+      </c>
+      <c r="U114">
+        <v>6</v>
+      </c>
+      <c r="V114" t="s">
+        <v>43</v>
+      </c>
+      <c r="W114" t="s">
+        <v>43</v>
+      </c>
+      <c r="X114">
+        <v>3540</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA114">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>265</v>
+      </c>
+      <c r="B115" t="s">
+        <v>81</v>
+      </c>
+      <c r="C115" t="s">
+        <v>73</v>
+      </c>
+      <c r="D115" t="s">
+        <v>266</v>
+      </c>
+      <c r="E115" t="s">
+        <v>52</v>
+      </c>
+      <c r="F115" t="s">
+        <v>59</v>
+      </c>
+      <c r="G115" t="s">
+        <v>53</v>
+      </c>
+      <c r="H115" t="s">
+        <v>35</v>
+      </c>
+      <c r="I115">
+        <v>5</v>
+      </c>
+      <c r="J115">
+        <v>1500</v>
+      </c>
+      <c r="K115">
+        <v>3000</v>
+      </c>
+      <c r="L115" t="s">
+        <v>65</v>
+      </c>
+      <c r="M115" t="s">
+        <v>37</v>
+      </c>
+      <c r="N115" t="s">
+        <v>37</v>
+      </c>
+      <c r="O115" t="s">
+        <v>38</v>
+      </c>
+      <c r="P115" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>75</v>
+      </c>
+      <c r="R115">
+        <v>885</v>
+      </c>
+      <c r="S115">
+        <v>885</v>
+      </c>
+      <c r="T115" t="s">
+        <v>41</v>
+      </c>
+      <c r="U115">
+        <v>5</v>
+      </c>
+      <c r="V115" t="s">
+        <v>43</v>
+      </c>
+      <c r="W115" t="s">
+        <v>43</v>
+      </c>
+      <c r="X115">
+        <v>2220</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA115">
+        <v>1964.7</v>
+      </c>
+      <c r="AB115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>267</v>
+      </c>
+      <c r="B116" t="s">
+        <v>81</v>
+      </c>
+      <c r="C116" t="s">
+        <v>73</v>
+      </c>
+      <c r="D116" t="s">
+        <v>268</v>
+      </c>
+      <c r="E116" t="s">
+        <v>52</v>
+      </c>
+      <c r="F116" t="s">
+        <v>59</v>
+      </c>
+      <c r="G116" t="s">
+        <v>53</v>
+      </c>
+      <c r="H116" t="s">
+        <v>35</v>
+      </c>
+      <c r="I116">
+        <v>3</v>
+      </c>
+      <c r="J116">
+        <v>1000</v>
+      </c>
+      <c r="K116">
+        <v>2000</v>
+      </c>
+      <c r="L116" t="s">
+        <v>65</v>
+      </c>
+      <c r="M116" t="s">
+        <v>37</v>
+      </c>
+      <c r="N116" t="s">
+        <v>37</v>
+      </c>
+      <c r="O116" t="s">
+        <v>38</v>
+      </c>
+      <c r="P116" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>75</v>
+      </c>
+      <c r="R116">
+        <v>1464</v>
+      </c>
+      <c r="S116">
+        <v>1464</v>
+      </c>
+      <c r="T116" t="s">
+        <v>41</v>
+      </c>
+      <c r="U116">
+        <v>31</v>
+      </c>
+      <c r="V116" t="s">
+        <v>43</v>
+      </c>
+      <c r="W116" t="s">
+        <v>43</v>
+      </c>
+      <c r="X116">
+        <v>2270</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA116">
+        <v>3323.28</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>269</v>
+      </c>
+      <c r="B117" t="s">
+        <v>81</v>
+      </c>
+      <c r="C117" t="s">
+        <v>73</v>
+      </c>
+      <c r="D117" t="s">
+        <v>268</v>
+      </c>
+      <c r="E117" t="s">
+        <v>52</v>
+      </c>
+      <c r="F117" t="s">
+        <v>59</v>
+      </c>
+      <c r="G117" t="s">
+        <v>53</v>
+      </c>
+      <c r="H117" t="s">
+        <v>35</v>
+      </c>
+      <c r="I117">
+        <v>3</v>
+      </c>
+      <c r="J117">
+        <v>1000</v>
+      </c>
+      <c r="K117">
+        <v>2000</v>
+      </c>
+      <c r="L117" t="s">
+        <v>65</v>
+      </c>
+      <c r="M117" t="s">
+        <v>37</v>
+      </c>
+      <c r="N117" t="s">
+        <v>37</v>
+      </c>
+      <c r="O117" t="s">
+        <v>38</v>
+      </c>
+      <c r="P117" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>75</v>
+      </c>
+      <c r="R117">
+        <v>94</v>
+      </c>
+      <c r="S117">
+        <v>94</v>
+      </c>
+      <c r="T117" t="s">
+        <v>41</v>
+      </c>
+      <c r="U117">
+        <v>2</v>
+      </c>
+      <c r="V117" t="s">
+        <v>43</v>
+      </c>
+      <c r="W117" t="s">
+        <v>43</v>
+      </c>
+      <c r="X117">
+        <v>2170</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA117">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>270</v>
+      </c>
+      <c r="B118" t="s">
+        <v>72</v>
+      </c>
+      <c r="C118" t="s">
+        <v>73</v>
+      </c>
+      <c r="D118" t="s">
+        <v>271</v>
+      </c>
+      <c r="E118" t="s">
+        <v>52</v>
+      </c>
+      <c r="F118" t="s">
+        <v>59</v>
+      </c>
+      <c r="G118" t="s">
+        <v>53</v>
+      </c>
+      <c r="H118" t="s">
+        <v>35</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>1000</v>
+      </c>
+      <c r="K118">
+        <v>2000</v>
+      </c>
+      <c r="L118" t="s">
+        <v>65</v>
+      </c>
+      <c r="M118" t="s">
+        <v>37</v>
+      </c>
+      <c r="N118" t="s">
+        <v>37</v>
+      </c>
+      <c r="O118" t="s">
+        <v>38</v>
+      </c>
+      <c r="P118" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>75</v>
+      </c>
+      <c r="R118">
+        <v>846</v>
+      </c>
+      <c r="S118">
+        <v>846</v>
+      </c>
+      <c r="T118" t="s">
+        <v>41</v>
+      </c>
+      <c r="U118">
+        <v>53</v>
+      </c>
+      <c r="V118" t="s">
+        <v>43</v>
+      </c>
+      <c r="W118" t="s">
+        <v>43</v>
+      </c>
+      <c r="X118">
+        <v>2220</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA118">
+        <v>1878.12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>272</v>
+      </c>
+      <c r="B119" t="s">
+        <v>72</v>
+      </c>
+      <c r="C119" t="s">
+        <v>73</v>
+      </c>
+      <c r="D119" t="s">
+        <v>240</v>
+      </c>
+      <c r="E119" t="s">
+        <v>52</v>
+      </c>
+      <c r="F119" t="s">
+        <v>59</v>
+      </c>
+      <c r="G119" t="s">
+        <v>53</v>
+      </c>
+      <c r="H119" t="s">
+        <v>35</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>1250</v>
+      </c>
+      <c r="K119">
+        <v>2500</v>
+      </c>
+      <c r="L119" t="s">
+        <v>65</v>
+      </c>
+      <c r="M119" t="s">
+        <v>37</v>
+      </c>
+      <c r="N119" t="s">
+        <v>37</v>
+      </c>
+      <c r="O119" t="s">
+        <v>38</v>
+      </c>
+      <c r="P119" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>75</v>
+      </c>
+      <c r="R119">
+        <v>354</v>
+      </c>
+      <c r="S119">
+        <v>354</v>
+      </c>
+      <c r="T119" t="s">
+        <v>41</v>
+      </c>
+      <c r="U119">
+        <v>14</v>
+      </c>
+      <c r="V119" t="s">
+        <v>43</v>
+      </c>
+      <c r="W119" t="s">
+        <v>43</v>
+      </c>
+      <c r="X119">
+        <v>2220</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA119">
+        <v>785.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="243">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -172,33 +172,21 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>K260271816</t>
-  </si>
-  <si>
-    <t>Coil K41/1.4509-441 2B with paper 0.99 x 1278.0 mm Unslit not marked</t>
+    <t>K268101304</t>
+  </si>
+  <si>
+    <t>Coil 1.4682-316A 2B without paper 3.44 x 340.0 mm Slit marked</t>
   </si>
   <si>
     <t>Excess Prime</t>
   </si>
   <si>
-    <t>K41/1.4509-441</t>
+    <t>1.4682-316A</t>
   </si>
   <si>
     <t>2B</t>
   </si>
   <si>
-    <t>ASME SA 240 / ASTM A 240 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305</t>
-  </si>
-  <si>
-    <t>K268101304</t>
-  </si>
-  <si>
-    <t>Coil 1.4682-316A 2B without paper 3.44 x 340.0 mm Slit marked</t>
-  </si>
-  <si>
-    <t>1.4682-316A</t>
-  </si>
-  <si>
     <t>V1 - Coil eye to the sky + Unalit</t>
   </si>
   <si>
@@ -254,6 +242,504 @@
   </si>
   <si>
     <t>K268101594</t>
+  </si>
+  <si>
+    <t>7248626</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>1.4404-316L</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>T488802</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256740</t>
+  </si>
+  <si>
+    <t>Sheets 1.4301-304 2R 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256819</t>
+  </si>
+  <si>
+    <t>7256820</t>
+  </si>
+  <si>
+    <t>7256821</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>7256940</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed Nov 4228 0.8 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7256941</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489089</t>
+  </si>
+  <si>
+    <t>7257261</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Scotchbrite</t>
+  </si>
+  <si>
+    <t>T489700</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489750</t>
+  </si>
+  <si>
+    <t>7257570</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257703</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2E 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T490582</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257842</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 2000.0 x 4000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Nov 4228 6.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257864</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257865</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 400 NOV 4204 RB 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>NOV 4204 RB</t>
+  </si>
+  <si>
+    <t>7257894</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>S139218</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 12.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258091</t>
+  </si>
+  <si>
+    <t>7258100</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258149</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491483</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258350</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T492123</t>
+  </si>
+  <si>
+    <t>T492124</t>
+  </si>
+  <si>
+    <t>7258489</t>
+  </si>
+  <si>
+    <t>7258526</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258529</t>
+  </si>
+  <si>
+    <t>7258730</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258760</t>
+  </si>
+  <si>
+    <t>7258862</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258863</t>
+  </si>
+  <si>
+    <t>7259015</t>
+  </si>
+  <si>
+    <t>Coil 1.4520-430Ti 2B 1.2 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4520-430Ti</t>
+  </si>
+  <si>
+    <t>7259028</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R without paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259050</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R NOV 4241/4513 0.8 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>NOV 4241/4513</t>
+  </si>
+  <si>
+    <t>7259145</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259182</t>
+  </si>
+  <si>
+    <t>T492642</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259417</t>
+  </si>
+  <si>
+    <t>7259437</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259438</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B with paper 1.0 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7259439</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R with paper 1.5 x 1250.0 x 2500 mm Slit</t>
   </si>
 </sst>
 </file>
@@ -630,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -908,13 +1394,13 @@
         <v>56</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I4">
-        <v>0.99</v>
+        <v>3.44</v>
       </c>
       <c r="J4">
-        <v>1278</v>
+        <v>340</v>
       </c>
       <c r="L4" t="s">
         <v>57</v>
@@ -929,16 +1415,16 @@
         <v>38</v>
       </c>
       <c r="P4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q4" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="R4">
-        <v>2620</v>
+        <v>1664</v>
       </c>
       <c r="S4">
-        <v>2641</v>
+        <v>1684</v>
       </c>
       <c r="T4" t="s">
         <v>41</v>
@@ -947,13 +1433,13 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W4" t="s">
         <v>42</v>
       </c>
       <c r="X4">
-        <v>1770</v>
+        <v>3190</v>
       </c>
       <c r="Y4" t="s">
         <v>43</v>
@@ -962,15 +1448,15 @@
         <v>44</v>
       </c>
       <c r="AA4">
-        <v>4637.4</v>
+        <v>5308.16</v>
       </c>
       <c r="AB4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
@@ -979,28 +1465,28 @@
         <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>3.44</v>
+        <v>4.99</v>
       </c>
       <c r="J5">
-        <v>340</v>
+        <v>1347</v>
       </c>
       <c r="L5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M5" t="s">
         <v>37</v>
@@ -1015,13 +1501,13 @@
         <v>39</v>
       </c>
       <c r="Q5" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="R5">
-        <v>1664</v>
+        <v>3230</v>
       </c>
       <c r="S5">
-        <v>1684</v>
+        <v>3251</v>
       </c>
       <c r="T5" t="s">
         <v>41</v>
@@ -1030,13 +1516,13 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="W5" t="s">
         <v>42</v>
       </c>
       <c r="X5">
-        <v>3190</v>
+        <v>2120</v>
       </c>
       <c r="Y5" t="s">
         <v>43</v>
@@ -1045,10 +1531,10 @@
         <v>44</v>
       </c>
       <c r="AA5">
-        <v>5308.16</v>
+        <v>6847.6</v>
       </c>
       <c r="AB5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -1065,7 +1551,7 @@
         <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F6" t="s">
         <v>33</v>
@@ -1074,16 +1560,16 @@
         <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I6">
-        <v>4.99</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1347</v>
+        <v>220</v>
       </c>
       <c r="L6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M6" t="s">
         <v>37</v>
@@ -1098,13 +1584,13 @@
         <v>39</v>
       </c>
       <c r="Q6" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="R6">
-        <v>3230</v>
+        <v>3560</v>
       </c>
       <c r="S6">
-        <v>3251</v>
+        <v>3620</v>
       </c>
       <c r="T6" t="s">
         <v>41</v>
@@ -1113,13 +1599,13 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="W6" t="s">
         <v>42</v>
       </c>
       <c r="X6">
-        <v>2120</v>
+        <v>2020</v>
       </c>
       <c r="Y6" t="s">
         <v>43</v>
@@ -1128,7 +1614,7 @@
         <v>44</v>
       </c>
       <c r="AA6">
-        <v>6847.6</v>
+        <v>7191.2</v>
       </c>
       <c r="AB6" t="b">
         <v>0</v>
@@ -1148,25 +1634,25 @@
         <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
         <v>33</v>
       </c>
       <c r="G7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7">
+        <v>3.95</v>
+      </c>
+      <c r="J7">
+        <v>2044</v>
+      </c>
+      <c r="L7" t="s">
         <v>70</v>
-      </c>
-      <c r="H7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>220</v>
-      </c>
-      <c r="L7" t="s">
-        <v>67</v>
       </c>
       <c r="M7" t="s">
         <v>37</v>
@@ -1181,13 +1667,13 @@
         <v>39</v>
       </c>
       <c r="Q7" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="R7">
-        <v>3560</v>
+        <v>6120</v>
       </c>
       <c r="S7">
-        <v>3620</v>
+        <v>6145</v>
       </c>
       <c r="T7" t="s">
         <v>41</v>
@@ -1196,13 +1682,13 @@
         <v>1</v>
       </c>
       <c r="V7" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="W7" t="s">
         <v>42</v>
       </c>
       <c r="X7">
-        <v>2020</v>
+        <v>2320</v>
       </c>
       <c r="Y7" t="s">
         <v>43</v>
@@ -1211,7 +1697,7 @@
         <v>44</v>
       </c>
       <c r="AA7">
-        <v>7191.2</v>
+        <v>14198.4</v>
       </c>
       <c r="AB7" t="b">
         <v>0</v>
@@ -1219,37 +1705,37 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>73</v>
-      </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
         <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I8">
-        <v>3.95</v>
+        <v>0.49</v>
       </c>
       <c r="J8">
-        <v>2044</v>
+        <v>380</v>
       </c>
       <c r="L8" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="M8" t="s">
         <v>37</v>
@@ -1261,16 +1747,16 @@
         <v>38</v>
       </c>
       <c r="P8" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q8" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="R8">
-        <v>6120</v>
+        <v>2320</v>
       </c>
       <c r="S8">
-        <v>6145</v>
+        <v>2332</v>
       </c>
       <c r="T8" t="s">
         <v>41</v>
@@ -1279,13 +1765,13 @@
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="W8" t="s">
         <v>42</v>
       </c>
       <c r="X8">
-        <v>2320</v>
+        <v>1620</v>
       </c>
       <c r="Y8" t="s">
         <v>43</v>
@@ -1294,15 +1780,12 @@
         <v>44</v>
       </c>
       <c r="AA8">
-        <v>14198.4</v>
-      </c>
-      <c r="AB8" t="b">
-        <v>0</v>
+        <v>3758.4</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1311,7 +1794,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
         <v>55</v>
@@ -1344,16 +1827,16 @@
         <v>38</v>
       </c>
       <c r="P9" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R9">
-        <v>2320</v>
+        <v>2395</v>
       </c>
       <c r="S9">
-        <v>2332</v>
+        <v>2407</v>
       </c>
       <c r="T9" t="s">
         <v>41</v>
@@ -1362,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="V9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="W9" t="s">
         <v>42</v>
@@ -1377,21 +1860,21 @@
         <v>44</v>
       </c>
       <c r="AA9">
-        <v>3758.4</v>
+        <v>3879.9</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>55</v>
@@ -1400,19 +1883,19 @@
         <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
         <v>35</v>
       </c>
       <c r="I10">
-        <v>0.49</v>
+        <v>3.44</v>
       </c>
       <c r="J10">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="L10" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="M10" t="s">
         <v>37</v>
@@ -1427,13 +1910,13 @@
         <v>39</v>
       </c>
       <c r="Q10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R10">
-        <v>2395</v>
+        <v>2112</v>
       </c>
       <c r="S10">
-        <v>2407</v>
+        <v>2132</v>
       </c>
       <c r="T10" t="s">
         <v>41</v>
@@ -1442,13 +1925,13 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="W10" t="s">
         <v>42</v>
       </c>
       <c r="X10">
-        <v>1620</v>
+        <v>3190</v>
       </c>
       <c r="Y10" t="s">
         <v>43</v>
@@ -1457,39 +1940,45 @@
         <v>44</v>
       </c>
       <c r="AA10">
-        <v>3879.9</v>
+        <v>6737.28</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
         <v>80</v>
       </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
         <v>35</v>
       </c>
       <c r="I11">
-        <v>3.44</v>
+        <v>2.5</v>
       </c>
       <c r="J11">
-        <v>340</v>
+        <v>1000</v>
+      </c>
+      <c r="K11">
+        <v>2000</v>
       </c>
       <c r="L11" t="s">
         <v>57</v>
@@ -1504,43 +1993,7353 @@
         <v>38</v>
       </c>
       <c r="P11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>82</v>
+      </c>
+      <c r="R11">
+        <v>312</v>
+      </c>
+      <c r="S11">
+        <v>312</v>
+      </c>
+      <c r="T11" t="s">
+        <v>41</v>
+      </c>
+      <c r="U11">
+        <v>8</v>
+      </c>
+      <c r="V11" t="s">
+        <v>42</v>
+      </c>
+      <c r="W11" t="s">
+        <v>42</v>
+      </c>
+      <c r="X11">
+        <v>2220</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA11">
+        <v>692.64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>1000</v>
+      </c>
+      <c r="K12">
+        <v>2000</v>
+      </c>
+      <c r="L12" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>82</v>
+      </c>
+      <c r="R12">
+        <v>394</v>
+      </c>
+      <c r="S12">
+        <v>394</v>
+      </c>
+      <c r="T12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12" t="s">
+        <v>42</v>
+      </c>
+      <c r="W12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X12">
+        <v>2020</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA12">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>1250</v>
+      </c>
+      <c r="K13">
+        <v>2500</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" t="s">
+        <v>38</v>
+      </c>
+      <c r="P13" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>82</v>
+      </c>
+      <c r="R13">
+        <v>322</v>
+      </c>
+      <c r="S13">
+        <v>322</v>
+      </c>
+      <c r="T13" t="s">
+        <v>41</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13" t="s">
+        <v>42</v>
+      </c>
+      <c r="W13" t="s">
+        <v>42</v>
+      </c>
+      <c r="X13">
+        <v>1370</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA13">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>1250</v>
+      </c>
+      <c r="K14">
+        <v>2500</v>
+      </c>
+      <c r="L14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>82</v>
+      </c>
+      <c r="R14">
+        <v>340</v>
+      </c>
+      <c r="S14">
+        <v>340</v>
+      </c>
+      <c r="T14" t="s">
+        <v>41</v>
+      </c>
+      <c r="U14">
+        <v>7</v>
+      </c>
+      <c r="V14" t="s">
+        <v>42</v>
+      </c>
+      <c r="W14" t="s">
+        <v>42</v>
+      </c>
+      <c r="X14">
+        <v>1370</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA14">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <v>2000</v>
+      </c>
+      <c r="K15">
+        <v>6000</v>
+      </c>
+      <c r="L15" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>82</v>
+      </c>
+      <c r="R15">
+        <v>283</v>
+      </c>
+      <c r="S15">
+        <v>283</v>
+      </c>
+      <c r="T15" t="s">
+        <v>41</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15" t="s">
+        <v>42</v>
+      </c>
+      <c r="W15" t="s">
+        <v>42</v>
+      </c>
+      <c r="X15">
+        <v>3560</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA15">
+        <v>1007.48</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="J16">
+        <v>1500</v>
+      </c>
+      <c r="K16">
+        <v>3000</v>
+      </c>
+      <c r="L16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>82</v>
+      </c>
+      <c r="R16">
+        <v>212</v>
+      </c>
+      <c r="S16">
+        <v>212</v>
+      </c>
+      <c r="T16" t="s">
+        <v>41</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
+        <v>42</v>
+      </c>
+      <c r="W16" t="s">
+        <v>42</v>
+      </c>
+      <c r="X16">
+        <v>3490</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA16">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17">
+        <v>8</v>
+      </c>
+      <c r="J17">
+        <v>1250</v>
+      </c>
+      <c r="K17">
+        <v>2500</v>
+      </c>
+      <c r="L17" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>82</v>
+      </c>
+      <c r="R17">
+        <v>394</v>
+      </c>
+      <c r="S17">
+        <v>394</v>
+      </c>
+      <c r="T17" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17" t="s">
+        <v>42</v>
+      </c>
+      <c r="W17" t="s">
+        <v>42</v>
+      </c>
+      <c r="X17">
+        <v>3490</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA17">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>2000</v>
+      </c>
+      <c r="K18">
+        <v>6000</v>
+      </c>
+      <c r="L18" t="s">
+        <v>63</v>
+      </c>
+      <c r="M18" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>82</v>
+      </c>
+      <c r="R18">
+        <v>472</v>
+      </c>
+      <c r="S18">
+        <v>472</v>
+      </c>
+      <c r="T18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18" t="s">
+        <v>42</v>
+      </c>
+      <c r="W18" t="s">
+        <v>42</v>
+      </c>
+      <c r="X18">
+        <v>2190</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA18">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>1500</v>
+      </c>
+      <c r="K19">
+        <v>3000</v>
+      </c>
+      <c r="L19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" t="s">
+        <v>103</v>
+      </c>
+      <c r="N19" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>82</v>
+      </c>
+      <c r="R19">
+        <v>970</v>
+      </c>
+      <c r="S19">
+        <v>970</v>
+      </c>
+      <c r="T19" t="s">
+        <v>41</v>
+      </c>
+      <c r="U19">
+        <v>13</v>
+      </c>
+      <c r="V19" t="s">
+        <v>42</v>
+      </c>
+      <c r="W19" t="s">
+        <v>42</v>
+      </c>
+      <c r="X19">
+        <v>3490</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA19">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20">
+        <v>2.5</v>
+      </c>
+      <c r="J20">
+        <v>1500</v>
+      </c>
+      <c r="K20">
+        <v>3000</v>
+      </c>
+      <c r="L20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" t="s">
+        <v>37</v>
+      </c>
+      <c r="O20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>82</v>
+      </c>
+      <c r="R20">
+        <v>526</v>
+      </c>
+      <c r="S20">
+        <v>526</v>
+      </c>
+      <c r="T20" t="s">
+        <v>41</v>
+      </c>
+      <c r="U20">
+        <v>6</v>
+      </c>
+      <c r="V20" t="s">
+        <v>42</v>
+      </c>
+      <c r="W20" t="s">
+        <v>42</v>
+      </c>
+      <c r="X20">
+        <v>3540</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA20">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>1500</v>
+      </c>
+      <c r="K21">
+        <v>3000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" t="s">
+        <v>37</v>
+      </c>
+      <c r="O21" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>82</v>
+      </c>
+      <c r="R21">
+        <v>354</v>
+      </c>
+      <c r="S21">
+        <v>354</v>
+      </c>
+      <c r="T21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U21">
+        <v>2</v>
+      </c>
+      <c r="V21" t="s">
+        <v>42</v>
+      </c>
+      <c r="W21" t="s">
+        <v>42</v>
+      </c>
+      <c r="X21">
+        <v>1170</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA21">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22">
+        <v>1.5</v>
+      </c>
+      <c r="J22">
+        <v>1250</v>
+      </c>
+      <c r="L22" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>82</v>
+      </c>
+      <c r="R22">
+        <v>1275</v>
+      </c>
+      <c r="S22">
+        <v>1275</v>
+      </c>
+      <c r="T22" t="s">
+        <v>41</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
+        <v>42</v>
+      </c>
+      <c r="W22" t="s">
+        <v>42</v>
+      </c>
+      <c r="X22">
+        <v>3590</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA22">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="J23">
+        <v>1500</v>
+      </c>
+      <c r="K23">
+        <v>3000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>82</v>
+      </c>
+      <c r="R23">
+        <v>210</v>
+      </c>
+      <c r="S23">
+        <v>210</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23">
+        <v>2</v>
+      </c>
+      <c r="V23" t="s">
+        <v>42</v>
+      </c>
+      <c r="W23" t="s">
+        <v>42</v>
+      </c>
+      <c r="X23">
+        <v>2170</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA23">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24">
+        <v>1500</v>
+      </c>
+      <c r="K24">
+        <v>3000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>82</v>
+      </c>
+      <c r="R24">
+        <v>212</v>
+      </c>
+      <c r="S24">
+        <v>212</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>2</v>
+      </c>
+      <c r="V24" t="s">
+        <v>42</v>
+      </c>
+      <c r="W24" t="s">
+        <v>42</v>
+      </c>
+      <c r="X24">
+        <v>1320</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA24">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>6</v>
+      </c>
+      <c r="J25">
+        <v>1000</v>
+      </c>
+      <c r="K25">
+        <v>2000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>82</v>
+      </c>
+      <c r="R25">
+        <v>567</v>
+      </c>
+      <c r="S25">
+        <v>567</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>6</v>
+      </c>
+      <c r="V25" t="s">
+        <v>42</v>
+      </c>
+      <c r="W25" t="s">
+        <v>42</v>
+      </c>
+      <c r="X25">
+        <v>2220</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA25">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" t="s">
+        <v>66</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>6</v>
+      </c>
+      <c r="J26">
+        <v>1000</v>
+      </c>
+      <c r="K26">
+        <v>2000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>82</v>
+      </c>
+      <c r="R26">
+        <v>567</v>
+      </c>
+      <c r="S26">
+        <v>567</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>6</v>
+      </c>
+      <c r="V26" t="s">
+        <v>42</v>
+      </c>
+      <c r="W26" t="s">
+        <v>42</v>
+      </c>
+      <c r="X26">
+        <v>2220</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA26">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>1500</v>
+      </c>
+      <c r="K27">
+        <v>3000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>82</v>
+      </c>
+      <c r="R27">
+        <v>319</v>
+      </c>
+      <c r="S27">
+        <v>319</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>3</v>
+      </c>
+      <c r="V27" t="s">
+        <v>42</v>
+      </c>
+      <c r="W27" t="s">
+        <v>42</v>
+      </c>
+      <c r="X27">
+        <v>1370</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA27">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28">
+        <v>1250</v>
+      </c>
+      <c r="K28">
+        <v>2500</v>
+      </c>
+      <c r="L28" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>82</v>
+      </c>
+      <c r="R28">
+        <v>246</v>
+      </c>
+      <c r="S28">
+        <v>246</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>5</v>
+      </c>
+      <c r="V28" t="s">
+        <v>42</v>
+      </c>
+      <c r="W28" t="s">
+        <v>42</v>
+      </c>
+      <c r="X28">
+        <v>2170</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA28">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
+        <v>0.8</v>
+      </c>
+      <c r="J29">
+        <v>1000</v>
+      </c>
+      <c r="K29">
+        <v>2000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>82</v>
+      </c>
+      <c r="R29">
+        <v>1498</v>
+      </c>
+      <c r="S29">
+        <v>1498</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>42</v>
+      </c>
+      <c r="W29" t="s">
+        <v>42</v>
+      </c>
+      <c r="X29">
+        <v>2370</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA29">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>0.8</v>
+      </c>
+      <c r="J30">
+        <v>1000</v>
+      </c>
+      <c r="K30">
+        <v>2000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>82</v>
+      </c>
+      <c r="R30">
+        <v>1498</v>
+      </c>
+      <c r="S30">
+        <v>1498</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>42</v>
+      </c>
+      <c r="W30" t="s">
+        <v>42</v>
+      </c>
+      <c r="X30">
+        <v>2370</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA30">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>1500</v>
+      </c>
+      <c r="K31">
+        <v>3000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" t="s">
+        <v>103</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>82</v>
+      </c>
+      <c r="R31">
+        <v>1010</v>
+      </c>
+      <c r="S31">
+        <v>1010</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>14</v>
+      </c>
+      <c r="V31" t="s">
+        <v>42</v>
+      </c>
+      <c r="W31" t="s">
+        <v>42</v>
+      </c>
+      <c r="X31">
+        <v>3540</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA31">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>1500</v>
+      </c>
+      <c r="K32">
+        <v>3000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>82</v>
+      </c>
+      <c r="R32">
+        <v>283</v>
+      </c>
+      <c r="S32">
+        <v>283</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>4</v>
+      </c>
+      <c r="V32" t="s">
+        <v>42</v>
+      </c>
+      <c r="W32" t="s">
+        <v>42</v>
+      </c>
+      <c r="X32">
+        <v>3540</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA32">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>0.8</v>
+      </c>
+      <c r="J33">
+        <v>1000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>36</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>128</v>
+      </c>
+      <c r="P33" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>82</v>
+      </c>
+      <c r="R33">
+        <v>1585</v>
+      </c>
+      <c r="S33">
+        <v>1585</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
+        <v>42</v>
+      </c>
+      <c r="W33" t="s">
+        <v>42</v>
+      </c>
+      <c r="X33">
+        <v>2370</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA33">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>1.5</v>
+      </c>
+      <c r="J34">
+        <v>1500</v>
+      </c>
+      <c r="K34">
+        <v>3000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>82</v>
+      </c>
+      <c r="R34">
+        <v>212</v>
+      </c>
+      <c r="S34">
+        <v>212</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>42</v>
+      </c>
+      <c r="W34" t="s">
+        <v>42</v>
+      </c>
+      <c r="X34">
+        <v>1320</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA34">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>81</v>
+      </c>
+      <c r="G35" t="s">
+        <v>92</v>
+      </c>
+      <c r="H35" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35">
+        <v>2.5</v>
+      </c>
+      <c r="J35">
+        <v>1500</v>
+      </c>
+      <c r="K35">
+        <v>3000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>82</v>
+      </c>
+      <c r="R35">
+        <v>540</v>
+      </c>
+      <c r="S35">
+        <v>540</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>6</v>
+      </c>
+      <c r="V35" t="s">
+        <v>42</v>
+      </c>
+      <c r="W35" t="s">
+        <v>42</v>
+      </c>
+      <c r="X35">
+        <v>3540</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA35">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <v>2.5</v>
+      </c>
+      <c r="J36">
+        <v>1500</v>
+      </c>
+      <c r="K36">
+        <v>3000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>82</v>
+      </c>
+      <c r="R36">
+        <v>520</v>
+      </c>
+      <c r="S36">
+        <v>520</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>6</v>
+      </c>
+      <c r="V36" t="s">
+        <v>42</v>
+      </c>
+      <c r="W36" t="s">
+        <v>42</v>
+      </c>
+      <c r="X36">
+        <v>3540</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA36">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" t="s">
+        <v>105</v>
+      </c>
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
+        <v>81</v>
+      </c>
+      <c r="G37" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>2.5</v>
+      </c>
+      <c r="J37">
+        <v>1500</v>
+      </c>
+      <c r="K37">
+        <v>3000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>57</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>82</v>
+      </c>
+      <c r="R37">
+        <v>530</v>
+      </c>
+      <c r="S37">
+        <v>530</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>6</v>
+      </c>
+      <c r="V37" t="s">
+        <v>42</v>
+      </c>
+      <c r="W37" t="s">
+        <v>42</v>
+      </c>
+      <c r="X37">
+        <v>3540</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA37">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>2.5</v>
+      </c>
+      <c r="J38">
+        <v>1500</v>
+      </c>
+      <c r="K38">
+        <v>3000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>82</v>
+      </c>
+      <c r="R38">
+        <v>526</v>
+      </c>
+      <c r="S38">
+        <v>526</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>6</v>
+      </c>
+      <c r="V38" t="s">
+        <v>42</v>
+      </c>
+      <c r="W38" t="s">
+        <v>42</v>
+      </c>
+      <c r="X38">
+        <v>3540</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA38">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
+        <v>81</v>
+      </c>
+      <c r="G39" t="s">
+        <v>92</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>1500</v>
+      </c>
+      <c r="K39">
+        <v>3000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>82</v>
+      </c>
+      <c r="R39">
+        <v>212</v>
+      </c>
+      <c r="S39">
+        <v>212</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>1</v>
+      </c>
+      <c r="V39" t="s">
+        <v>42</v>
+      </c>
+      <c r="W39" t="s">
+        <v>42</v>
+      </c>
+      <c r="X39">
+        <v>3490</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA39">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G40" t="s">
+        <v>92</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>1500</v>
+      </c>
+      <c r="K40">
+        <v>3000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>57</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>82</v>
+      </c>
+      <c r="R40">
+        <v>212</v>
+      </c>
+      <c r="S40">
+        <v>212</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40" t="s">
+        <v>42</v>
+      </c>
+      <c r="W40" t="s">
+        <v>42</v>
+      </c>
+      <c r="X40">
+        <v>3490</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA40">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" t="s">
+        <v>81</v>
+      </c>
+      <c r="G41" t="s">
+        <v>66</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41">
+        <v>1000</v>
+      </c>
+      <c r="K41">
+        <v>2000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
         <v>39</v>
       </c>
-      <c r="Q11" t="s">
-        <v>62</v>
-      </c>
-      <c r="R11">
-        <v>2112</v>
-      </c>
-      <c r="S11">
-        <v>2132</v>
-      </c>
-      <c r="T11" t="s">
-        <v>41</v>
-      </c>
-      <c r="U11">
+      <c r="Q41" t="s">
+        <v>82</v>
+      </c>
+      <c r="R41">
+        <v>315</v>
+      </c>
+      <c r="S41">
+        <v>315</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>5</v>
+      </c>
+      <c r="V41" t="s">
+        <v>42</v>
+      </c>
+      <c r="W41" t="s">
+        <v>42</v>
+      </c>
+      <c r="X41">
+        <v>2220</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA41">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>81</v>
+      </c>
+      <c r="G42" t="s">
+        <v>66</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>1000</v>
+      </c>
+      <c r="K42">
+        <v>2000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>63</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>82</v>
+      </c>
+      <c r="R42">
+        <v>944</v>
+      </c>
+      <c r="S42">
+        <v>944</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
         <v>1</v>
       </c>
-      <c r="V11" t="s">
+      <c r="V42" t="s">
+        <v>42</v>
+      </c>
+      <c r="W42" t="s">
+        <v>42</v>
+      </c>
+      <c r="X42">
+        <v>2020</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA42">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" t="s">
+        <v>81</v>
+      </c>
+      <c r="G43" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>1500</v>
+      </c>
+      <c r="K43">
+        <v>3000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>57</v>
+      </c>
+      <c r="M43" t="s">
+        <v>103</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>82</v>
+      </c>
+      <c r="R43">
+        <v>1224</v>
+      </c>
+      <c r="S43">
+        <v>1224</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>34</v>
+      </c>
+      <c r="V43" t="s">
+        <v>42</v>
+      </c>
+      <c r="W43" t="s">
+        <v>42</v>
+      </c>
+      <c r="X43">
+        <v>3540</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA43">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>1.5</v>
+      </c>
+      <c r="J44">
+        <v>1500</v>
+      </c>
+      <c r="K44">
+        <v>3000</v>
+      </c>
+      <c r="L44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M44" t="s">
+        <v>103</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>82</v>
+      </c>
+      <c r="R44">
+        <v>916</v>
+      </c>
+      <c r="S44">
+        <v>916</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>18</v>
+      </c>
+      <c r="V44" t="s">
+        <v>42</v>
+      </c>
+      <c r="W44" t="s">
+        <v>42</v>
+      </c>
+      <c r="X44">
+        <v>1320</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA44">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" t="s">
+        <v>81</v>
+      </c>
+      <c r="G45" t="s">
+        <v>92</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="J45">
+        <v>1500</v>
+      </c>
+      <c r="K45">
+        <v>3000</v>
+      </c>
+      <c r="L45" t="s">
+        <v>57</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>82</v>
+      </c>
+      <c r="R45">
+        <v>319</v>
+      </c>
+      <c r="S45">
+        <v>319</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45" t="s">
+        <v>42</v>
+      </c>
+      <c r="W45" t="s">
+        <v>42</v>
+      </c>
+      <c r="X45">
+        <v>3540</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA45">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" t="s">
+        <v>136</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" t="s">
+        <v>81</v>
+      </c>
+      <c r="G46" t="s">
+        <v>92</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>1500</v>
+      </c>
+      <c r="K46">
+        <v>3000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>57</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>82</v>
+      </c>
+      <c r="R46">
+        <v>212</v>
+      </c>
+      <c r="S46">
+        <v>212</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>1</v>
+      </c>
+      <c r="V46" t="s">
+        <v>42</v>
+      </c>
+      <c r="W46" t="s">
+        <v>42</v>
+      </c>
+      <c r="X46">
+        <v>3490</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA46">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>81</v>
+      </c>
+      <c r="G47" t="s">
+        <v>92</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>1500</v>
+      </c>
+      <c r="K47">
+        <v>3000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>57</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R47">
+        <v>212</v>
+      </c>
+      <c r="S47">
+        <v>212</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>1</v>
+      </c>
+      <c r="V47" t="s">
+        <v>42</v>
+      </c>
+      <c r="W47" t="s">
+        <v>42</v>
+      </c>
+      <c r="X47">
+        <v>3490</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA47">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>148</v>
+      </c>
+      <c r="B48" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" t="s">
+        <v>81</v>
+      </c>
+      <c r="G48" t="s">
+        <v>92</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>3</v>
+      </c>
+      <c r="J48">
+        <v>1500</v>
+      </c>
+      <c r="K48">
+        <v>3000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>57</v>
+      </c>
+      <c r="M48" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>82</v>
+      </c>
+      <c r="R48">
+        <v>319</v>
+      </c>
+      <c r="S48">
+        <v>319</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
+        <v>42</v>
+      </c>
+      <c r="W48" t="s">
+        <v>42</v>
+      </c>
+      <c r="X48">
+        <v>3540</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA48">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" t="s">
+        <v>150</v>
+      </c>
+      <c r="E49" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" t="s">
+        <v>81</v>
+      </c>
+      <c r="G49" t="s">
+        <v>66</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>6</v>
+      </c>
+      <c r="J49">
+        <v>2000</v>
+      </c>
+      <c r="K49">
+        <v>4000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>82</v>
+      </c>
+      <c r="R49">
+        <v>756</v>
+      </c>
+      <c r="S49">
+        <v>756</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>2</v>
+      </c>
+      <c r="V49" t="s">
+        <v>42</v>
+      </c>
+      <c r="W49" t="s">
+        <v>42</v>
+      </c>
+      <c r="X49">
+        <v>2240</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA49">
+        <v>1693.44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" t="s">
+        <v>152</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" t="s">
+        <v>81</v>
+      </c>
+      <c r="G50" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50">
+        <v>1000</v>
+      </c>
+      <c r="K50">
+        <v>2000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>36</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>82</v>
+      </c>
+      <c r="R50">
+        <v>544</v>
+      </c>
+      <c r="S50">
+        <v>544</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>42</v>
+      </c>
+      <c r="W50" t="s">
+        <v>42</v>
+      </c>
+      <c r="X50">
+        <v>2220</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA50">
+        <v>1207.68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" t="s">
+        <v>155</v>
+      </c>
+      <c r="E51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" t="s">
+        <v>49</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>0.8</v>
+      </c>
+      <c r="J51">
+        <v>1000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>36</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>82</v>
+      </c>
+      <c r="R51">
+        <v>1000</v>
+      </c>
+      <c r="S51">
+        <v>1000</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>1</v>
+      </c>
+      <c r="V51" t="s">
+        <v>42</v>
+      </c>
+      <c r="W51" t="s">
+        <v>42</v>
+      </c>
+      <c r="X51">
+        <v>2370</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA51">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>156</v>
+      </c>
+      <c r="B52" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" t="s">
+        <v>157</v>
+      </c>
+      <c r="E52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52" t="s">
+        <v>66</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>2.5</v>
+      </c>
+      <c r="J52">
+        <v>1500</v>
+      </c>
+      <c r="K52">
+        <v>3000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>57</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>82</v>
+      </c>
+      <c r="R52">
+        <v>266</v>
+      </c>
+      <c r="S52">
+        <v>266</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>3</v>
+      </c>
+      <c r="V52" t="s">
+        <v>42</v>
+      </c>
+      <c r="W52" t="s">
+        <v>42</v>
+      </c>
+      <c r="X52">
+        <v>2220</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA52">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" t="s">
+        <v>157</v>
+      </c>
+      <c r="E53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" t="s">
+        <v>81</v>
+      </c>
+      <c r="G53" t="s">
+        <v>66</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>2.5</v>
+      </c>
+      <c r="J53">
+        <v>1500</v>
+      </c>
+      <c r="K53">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>57</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>82</v>
+      </c>
+      <c r="R53">
+        <v>354</v>
+      </c>
+      <c r="S53">
+        <v>354</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>4</v>
+      </c>
+      <c r="V53" t="s">
+        <v>42</v>
+      </c>
+      <c r="W53" t="s">
+        <v>42</v>
+      </c>
+      <c r="X53">
+        <v>2220</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA53">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" t="s">
+        <v>81</v>
+      </c>
+      <c r="G54" t="s">
+        <v>66</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>2.5</v>
+      </c>
+      <c r="J54">
+        <v>1500</v>
+      </c>
+      <c r="K54">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>57</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>82</v>
+      </c>
+      <c r="R54">
+        <v>620</v>
+      </c>
+      <c r="S54">
+        <v>620</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>7</v>
+      </c>
+      <c r="V54" t="s">
+        <v>42</v>
+      </c>
+      <c r="W54" t="s">
+        <v>42</v>
+      </c>
+      <c r="X54">
+        <v>2220</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA54">
+        <v>1376.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" t="s">
+        <v>161</v>
+      </c>
+      <c r="E55" t="s">
+        <v>32</v>
+      </c>
+      <c r="F55" t="s">
+        <v>81</v>
+      </c>
+      <c r="G55" t="s">
+        <v>92</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>1.5</v>
+      </c>
+      <c r="J55">
+        <v>1500</v>
+      </c>
+      <c r="K55">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>57</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>82</v>
+      </c>
+      <c r="R55">
+        <v>266</v>
+      </c>
+      <c r="S55">
+        <v>266</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>5</v>
+      </c>
+      <c r="V55" t="s">
+        <v>42</v>
+      </c>
+      <c r="W55" t="s">
+        <v>42</v>
+      </c>
+      <c r="X55">
+        <v>3540</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA55">
+        <v>941.64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" t="s">
+        <v>163</v>
+      </c>
+      <c r="E56" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" t="s">
+        <v>81</v>
+      </c>
+      <c r="G56" t="s">
+        <v>92</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>2.5</v>
+      </c>
+      <c r="J56">
+        <v>2000</v>
+      </c>
+      <c r="K56">
+        <v>4000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>57</v>
+      </c>
+      <c r="M56" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>82</v>
+      </c>
+      <c r="R56">
+        <v>315</v>
+      </c>
+      <c r="S56">
+        <v>315</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>2</v>
+      </c>
+      <c r="V56" t="s">
+        <v>42</v>
+      </c>
+      <c r="W56" t="s">
+        <v>42</v>
+      </c>
+      <c r="X56">
+        <v>3560</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA56">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" t="s">
+        <v>163</v>
+      </c>
+      <c r="E57" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" t="s">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s">
+        <v>92</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>2.5</v>
+      </c>
+      <c r="J57">
+        <v>2000</v>
+      </c>
+      <c r="K57">
+        <v>4000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>57</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>82</v>
+      </c>
+      <c r="R57">
+        <v>315</v>
+      </c>
+      <c r="S57">
+        <v>315</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>2</v>
+      </c>
+      <c r="V57" t="s">
+        <v>42</v>
+      </c>
+      <c r="W57" t="s">
+        <v>42</v>
+      </c>
+      <c r="X57">
+        <v>3560</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA57">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>165</v>
+      </c>
+      <c r="B58" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" t="s">
+        <v>79</v>
+      </c>
+      <c r="D58" t="s">
+        <v>166</v>
+      </c>
+      <c r="E58" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" t="s">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s">
+        <v>66</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>0.8</v>
+      </c>
+      <c r="J58">
+        <v>1500</v>
+      </c>
+      <c r="K58">
+        <v>3000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>57</v>
+      </c>
+      <c r="M58" t="s">
+        <v>103</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>167</v>
+      </c>
+      <c r="P58" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>82</v>
+      </c>
+      <c r="R58">
+        <v>833</v>
+      </c>
+      <c r="S58">
+        <v>833</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>29</v>
+      </c>
+      <c r="V58" t="s">
+        <v>42</v>
+      </c>
+      <c r="W58" t="s">
+        <v>42</v>
+      </c>
+      <c r="X58">
+        <v>2270</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA58">
+        <v>1890.91</v>
+      </c>
+      <c r="AB58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>168</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" t="s">
+        <v>79</v>
+      </c>
+      <c r="D59" t="s">
+        <v>166</v>
+      </c>
+      <c r="E59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59" t="s">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s">
+        <v>66</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>0.8</v>
+      </c>
+      <c r="J59">
+        <v>1500</v>
+      </c>
+      <c r="K59">
+        <v>3000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>57</v>
+      </c>
+      <c r="M59" t="s">
+        <v>103</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>167</v>
+      </c>
+      <c r="P59" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>82</v>
+      </c>
+      <c r="R59">
+        <v>805</v>
+      </c>
+      <c r="S59">
+        <v>805</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>28</v>
+      </c>
+      <c r="V59" t="s">
+        <v>42</v>
+      </c>
+      <c r="W59" t="s">
+        <v>42</v>
+      </c>
+      <c r="X59">
+        <v>2270</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA59">
+        <v>1827.35</v>
+      </c>
+      <c r="AB59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" t="s">
+        <v>78</v>
+      </c>
+      <c r="C60" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60" t="s">
+        <v>170</v>
+      </c>
+      <c r="E60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60" t="s">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s">
+        <v>66</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60">
+        <v>1000</v>
+      </c>
+      <c r="K60">
+        <v>2000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>57</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>82</v>
+      </c>
+      <c r="R60">
+        <v>1448</v>
+      </c>
+      <c r="S60">
+        <v>1448</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>1</v>
+      </c>
+      <c r="V60" t="s">
+        <v>42</v>
+      </c>
+      <c r="W60" t="s">
+        <v>42</v>
+      </c>
+      <c r="X60">
+        <v>2270</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA60">
+        <v>3286.96</v>
+      </c>
+      <c r="AB60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" t="s">
+        <v>172</v>
+      </c>
+      <c r="E61" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" t="s">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>4</v>
+      </c>
+      <c r="J61">
+        <v>1000</v>
+      </c>
+      <c r="K61">
+        <v>2000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>57</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>82</v>
+      </c>
+      <c r="R61">
+        <v>384</v>
+      </c>
+      <c r="S61">
+        <v>384</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>6</v>
+      </c>
+      <c r="V61" t="s">
+        <v>42</v>
+      </c>
+      <c r="W61" t="s">
+        <v>42</v>
+      </c>
+      <c r="X61">
+        <v>1370</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA61">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>173</v>
+      </c>
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" t="s">
+        <v>94</v>
+      </c>
+      <c r="E62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62" t="s">
+        <v>81</v>
+      </c>
+      <c r="G62" t="s">
+        <v>92</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>6</v>
+      </c>
+      <c r="J62">
+        <v>1500</v>
+      </c>
+      <c r="K62">
+        <v>3000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>57</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>82</v>
+      </c>
+      <c r="R62">
+        <v>850</v>
+      </c>
+      <c r="S62">
+        <v>850</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>4</v>
+      </c>
+      <c r="V62" t="s">
+        <v>42</v>
+      </c>
+      <c r="W62" t="s">
+        <v>42</v>
+      </c>
+      <c r="X62">
+        <v>3540</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA62">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>174</v>
+      </c>
+      <c r="B63" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" t="s">
+        <v>79</v>
+      </c>
+      <c r="D63" t="s">
+        <v>175</v>
+      </c>
+      <c r="E63" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" t="s">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s">
+        <v>66</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>0.8</v>
+      </c>
+      <c r="J63">
+        <v>1250</v>
+      </c>
+      <c r="K63">
+        <v>2500</v>
+      </c>
+      <c r="L63" t="s">
+        <v>57</v>
+      </c>
+      <c r="M63" t="s">
+        <v>176</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>82</v>
+      </c>
+      <c r="R63">
+        <v>430</v>
+      </c>
+      <c r="S63">
+        <v>430</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s">
+        <v>42</v>
+      </c>
+      <c r="W63" t="s">
+        <v>42</v>
+      </c>
+      <c r="X63">
+        <v>2270</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA63">
+        <v>976.1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>177</v>
+      </c>
+      <c r="B64" t="s">
+        <v>84</v>
+      </c>
+      <c r="C64" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" t="s">
+        <v>178</v>
+      </c>
+      <c r="E64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64" t="s">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s">
+        <v>66</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>2</v>
+      </c>
+      <c r="J64">
+        <v>1000</v>
+      </c>
+      <c r="K64">
+        <v>2000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>57</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>82</v>
+      </c>
+      <c r="R64">
+        <v>283</v>
+      </c>
+      <c r="S64">
+        <v>283</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>9</v>
+      </c>
+      <c r="V64" t="s">
+        <v>42</v>
+      </c>
+      <c r="W64" t="s">
+        <v>42</v>
+      </c>
+      <c r="X64">
+        <v>2220</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA64">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>179</v>
+      </c>
+      <c r="B65" t="s">
+        <v>84</v>
+      </c>
+      <c r="C65" t="s">
+        <v>79</v>
+      </c>
+      <c r="D65" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65" t="s">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s">
+        <v>34</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>3</v>
+      </c>
+      <c r="J65">
+        <v>1500</v>
+      </c>
+      <c r="K65">
+        <v>3000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>57</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>82</v>
+      </c>
+      <c r="R65">
+        <v>637</v>
+      </c>
+      <c r="S65">
+        <v>637</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>6</v>
+      </c>
+      <c r="V65" t="s">
+        <v>42</v>
+      </c>
+      <c r="W65" t="s">
+        <v>42</v>
+      </c>
+      <c r="X65">
+        <v>1370</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA65">
+        <v>872.69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>180</v>
+      </c>
+      <c r="B66" t="s">
+        <v>78</v>
+      </c>
+      <c r="C66" t="s">
+        <v>79</v>
+      </c>
+      <c r="D66" t="s">
+        <v>181</v>
+      </c>
+      <c r="E66" t="s">
+        <v>32</v>
+      </c>
+      <c r="F66" t="s">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s">
+        <v>66</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <v>1000</v>
+      </c>
+      <c r="K66">
+        <v>2000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>57</v>
+      </c>
+      <c r="M66" t="s">
+        <v>103</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>82</v>
+      </c>
+      <c r="R66">
+        <v>1482</v>
+      </c>
+      <c r="S66">
+        <v>1482</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>1</v>
+      </c>
+      <c r="V66" t="s">
+        <v>42</v>
+      </c>
+      <c r="W66" t="s">
+        <v>42</v>
+      </c>
+      <c r="X66">
+        <v>2220</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA66">
+        <v>3290.04</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>182</v>
+      </c>
+      <c r="B67" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" t="s">
+        <v>79</v>
+      </c>
+      <c r="D67" t="s">
+        <v>183</v>
+      </c>
+      <c r="E67" t="s">
+        <v>32</v>
+      </c>
+      <c r="F67" t="s">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s">
+        <v>97</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>4</v>
+      </c>
+      <c r="J67">
+        <v>1500</v>
+      </c>
+      <c r="K67">
+        <v>3000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>70</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>82</v>
+      </c>
+      <c r="R67">
+        <v>1133</v>
+      </c>
+      <c r="S67">
+        <v>1133</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>8</v>
+      </c>
+      <c r="V67" t="s">
+        <v>42</v>
+      </c>
+      <c r="W67" t="s">
+        <v>42</v>
+      </c>
+      <c r="X67">
+        <v>3540</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA67">
+        <v>4010.82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>184</v>
+      </c>
+      <c r="B68" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" t="s">
+        <v>79</v>
+      </c>
+      <c r="D68" t="s">
+        <v>185</v>
+      </c>
+      <c r="E68" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68" t="s">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s">
+        <v>66</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>5</v>
+      </c>
+      <c r="J68">
+        <v>2000</v>
+      </c>
+      <c r="K68">
+        <v>4000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>57</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>82</v>
+      </c>
+      <c r="R68">
+        <v>1259</v>
+      </c>
+      <c r="S68">
+        <v>1259</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>4</v>
+      </c>
+      <c r="V68" t="s">
+        <v>42</v>
+      </c>
+      <c r="W68" t="s">
+        <v>42</v>
+      </c>
+      <c r="X68">
+        <v>2290</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA68">
+        <v>2883.11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>186</v>
+      </c>
+      <c r="B69" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" t="s">
+        <v>79</v>
+      </c>
+      <c r="D69" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" t="s">
+        <v>32</v>
+      </c>
+      <c r="F69" t="s">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s">
+        <v>66</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>4</v>
+      </c>
+      <c r="J69">
+        <v>2000</v>
+      </c>
+      <c r="K69">
+        <v>4000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>57</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>82</v>
+      </c>
+      <c r="R69">
+        <v>1007</v>
+      </c>
+      <c r="S69">
+        <v>1007</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>4</v>
+      </c>
+      <c r="V69" t="s">
+        <v>42</v>
+      </c>
+      <c r="W69" t="s">
+        <v>42</v>
+      </c>
+      <c r="X69">
+        <v>2290</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA69">
+        <v>2306.03</v>
+      </c>
+      <c r="AB69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>188</v>
+      </c>
+      <c r="B70" t="s">
+        <v>90</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>189</v>
+      </c>
+      <c r="E70" t="s">
+        <v>32</v>
+      </c>
+      <c r="F70" t="s">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s">
+        <v>66</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>6</v>
+      </c>
+      <c r="J70">
+        <v>1500</v>
+      </c>
+      <c r="K70">
+        <v>3000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>57</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>167</v>
+      </c>
+      <c r="P70" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>82</v>
+      </c>
+      <c r="R70">
+        <v>1487</v>
+      </c>
+      <c r="S70">
+        <v>1487</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>7</v>
+      </c>
+      <c r="V70" t="s">
+        <v>42</v>
+      </c>
+      <c r="W70" t="s">
+        <v>42</v>
+      </c>
+      <c r="X70">
+        <v>2270</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA70">
+        <v>3375.49</v>
+      </c>
+      <c r="AB70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>190</v>
+      </c>
+      <c r="B71" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71" t="s">
+        <v>191</v>
+      </c>
+      <c r="E71" t="s">
+        <v>32</v>
+      </c>
+      <c r="F71" t="s">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s">
+        <v>66</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>8</v>
+      </c>
+      <c r="J71">
+        <v>2000</v>
+      </c>
+      <c r="K71">
+        <v>6000</v>
+      </c>
+      <c r="L71" t="s">
         <v>63</v>
       </c>
-      <c r="W11" t="s">
-        <v>42</v>
-      </c>
-      <c r="X11">
-        <v>3190</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA11">
-        <v>6737.28</v>
-      </c>
-      <c r="AB11" t="b">
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>82</v>
+      </c>
+      <c r="R71">
+        <v>755</v>
+      </c>
+      <c r="S71">
+        <v>755</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
         <v>1</v>
+      </c>
+      <c r="V71" t="s">
+        <v>42</v>
+      </c>
+      <c r="W71" t="s">
+        <v>42</v>
+      </c>
+      <c r="X71">
+        <v>2040</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA71">
+        <v>1540.2</v>
+      </c>
+      <c r="AB71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>192</v>
+      </c>
+      <c r="B72" t="s">
+        <v>78</v>
+      </c>
+      <c r="C72" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" t="s">
+        <v>193</v>
+      </c>
+      <c r="E72" t="s">
+        <v>32</v>
+      </c>
+      <c r="F72" t="s">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s">
+        <v>66</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1250</v>
+      </c>
+      <c r="K72">
+        <v>2500</v>
+      </c>
+      <c r="L72" t="s">
+        <v>57</v>
+      </c>
+      <c r="M72" t="s">
+        <v>194</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>195</v>
+      </c>
+      <c r="P72" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>82</v>
+      </c>
+      <c r="R72">
+        <v>1019</v>
+      </c>
+      <c r="S72">
+        <v>1019</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>41</v>
+      </c>
+      <c r="V72" t="s">
+        <v>42</v>
+      </c>
+      <c r="W72" t="s">
+        <v>42</v>
+      </c>
+      <c r="X72">
+        <v>2220</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA72">
+        <v>2262.18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>196</v>
+      </c>
+      <c r="B73" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73" t="s">
+        <v>197</v>
+      </c>
+      <c r="E73" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" t="s">
+        <v>81</v>
+      </c>
+      <c r="G73" t="s">
+        <v>66</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>8</v>
+      </c>
+      <c r="J73">
+        <v>1000</v>
+      </c>
+      <c r="K73">
+        <v>2000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>63</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>82</v>
+      </c>
+      <c r="R73">
+        <v>504</v>
+      </c>
+      <c r="S73">
+        <v>504</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>4</v>
+      </c>
+      <c r="V73" t="s">
+        <v>42</v>
+      </c>
+      <c r="W73" t="s">
+        <v>42</v>
+      </c>
+      <c r="X73">
+        <v>2020</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA73">
+        <v>1018.08</v>
+      </c>
+      <c r="AB73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>198</v>
+      </c>
+      <c r="B74" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74" t="s">
+        <v>79</v>
+      </c>
+      <c r="D74" t="s">
+        <v>199</v>
+      </c>
+      <c r="E74" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" t="s">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s">
+        <v>66</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>12</v>
+      </c>
+      <c r="J74">
+        <v>1000</v>
+      </c>
+      <c r="K74">
+        <v>2000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>63</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>82</v>
+      </c>
+      <c r="R74">
+        <v>1322</v>
+      </c>
+      <c r="S74">
+        <v>1322</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>7</v>
+      </c>
+      <c r="V74" t="s">
+        <v>42</v>
+      </c>
+      <c r="W74" t="s">
+        <v>42</v>
+      </c>
+      <c r="X74">
+        <v>2070</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA74">
+        <v>2736.54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>200</v>
+      </c>
+      <c r="B75" t="s">
+        <v>78</v>
+      </c>
+      <c r="C75" t="s">
+        <v>79</v>
+      </c>
+      <c r="D75" t="s">
+        <v>105</v>
+      </c>
+      <c r="E75" t="s">
+        <v>32</v>
+      </c>
+      <c r="F75" t="s">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s">
+        <v>92</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>2.5</v>
+      </c>
+      <c r="J75">
+        <v>1500</v>
+      </c>
+      <c r="K75">
+        <v>3000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>57</v>
+      </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>82</v>
+      </c>
+      <c r="R75">
+        <v>534</v>
+      </c>
+      <c r="S75">
+        <v>534</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>6</v>
+      </c>
+      <c r="V75" t="s">
+        <v>42</v>
+      </c>
+      <c r="W75" t="s">
+        <v>42</v>
+      </c>
+      <c r="X75">
+        <v>3540</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA75">
+        <v>1890.36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>201</v>
+      </c>
+      <c r="B76" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" t="s">
+        <v>79</v>
+      </c>
+      <c r="D76" t="s">
+        <v>202</v>
+      </c>
+      <c r="E76" t="s">
+        <v>32</v>
+      </c>
+      <c r="F76" t="s">
+        <v>81</v>
+      </c>
+      <c r="G76" t="s">
+        <v>66</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>0.8</v>
+      </c>
+      <c r="J76">
+        <v>1250</v>
+      </c>
+      <c r="K76">
+        <v>2500</v>
+      </c>
+      <c r="L76" t="s">
+        <v>57</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>82</v>
+      </c>
+      <c r="R76">
+        <v>2033</v>
+      </c>
+      <c r="S76">
+        <v>2033</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>101</v>
+      </c>
+      <c r="V76" t="s">
+        <v>42</v>
+      </c>
+      <c r="W76" t="s">
+        <v>42</v>
+      </c>
+      <c r="X76">
+        <v>2370</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA76">
+        <v>4818.21</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>203</v>
+      </c>
+      <c r="B77" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" t="s">
+        <v>204</v>
+      </c>
+      <c r="E77" t="s">
+        <v>32</v>
+      </c>
+      <c r="F77" t="s">
+        <v>81</v>
+      </c>
+      <c r="G77" t="s">
+        <v>92</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>2</v>
+      </c>
+      <c r="J77">
+        <v>1000</v>
+      </c>
+      <c r="K77">
+        <v>2000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>57</v>
+      </c>
+      <c r="M77" t="s">
+        <v>103</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>82</v>
+      </c>
+      <c r="R77">
+        <v>1046</v>
+      </c>
+      <c r="S77">
+        <v>1046</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>33</v>
+      </c>
+      <c r="V77" t="s">
+        <v>42</v>
+      </c>
+      <c r="W77" t="s">
+        <v>42</v>
+      </c>
+      <c r="X77">
+        <v>3540</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA77">
+        <v>3702.84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>205</v>
+      </c>
+      <c r="B78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" t="s">
+        <v>206</v>
+      </c>
+      <c r="E78" t="s">
+        <v>32</v>
+      </c>
+      <c r="F78" t="s">
+        <v>81</v>
+      </c>
+      <c r="G78" t="s">
+        <v>66</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>4</v>
+      </c>
+      <c r="J78">
+        <v>1500</v>
+      </c>
+      <c r="K78">
+        <v>3000</v>
+      </c>
+      <c r="L78" t="s">
+        <v>57</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>82</v>
+      </c>
+      <c r="R78">
+        <v>142</v>
+      </c>
+      <c r="S78">
+        <v>142</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>1</v>
+      </c>
+      <c r="V78" t="s">
+        <v>42</v>
+      </c>
+      <c r="W78" t="s">
+        <v>42</v>
+      </c>
+      <c r="X78">
+        <v>2170</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA78">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>207</v>
+      </c>
+      <c r="B79" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79" t="s">
+        <v>79</v>
+      </c>
+      <c r="D79" t="s">
+        <v>208</v>
+      </c>
+      <c r="E79" t="s">
+        <v>32</v>
+      </c>
+      <c r="F79" t="s">
+        <v>81</v>
+      </c>
+      <c r="G79" t="s">
+        <v>66</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>2</v>
+      </c>
+      <c r="J79">
+        <v>2000</v>
+      </c>
+      <c r="K79">
+        <v>4000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>57</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>82</v>
+      </c>
+      <c r="R79">
+        <v>126</v>
+      </c>
+      <c r="S79">
+        <v>126</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>1</v>
+      </c>
+      <c r="V79" t="s">
+        <v>42</v>
+      </c>
+      <c r="W79" t="s">
+        <v>42</v>
+      </c>
+      <c r="X79">
+        <v>2190</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA79">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>209</v>
+      </c>
+      <c r="B80" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" t="s">
+        <v>79</v>
+      </c>
+      <c r="D80" t="s">
+        <v>210</v>
+      </c>
+      <c r="E80" t="s">
+        <v>32</v>
+      </c>
+      <c r="F80" t="s">
+        <v>81</v>
+      </c>
+      <c r="G80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>0.8</v>
+      </c>
+      <c r="J80">
+        <v>1000</v>
+      </c>
+      <c r="K80">
+        <v>2000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>57</v>
+      </c>
+      <c r="M80" t="s">
+        <v>103</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>82</v>
+      </c>
+      <c r="R80">
+        <v>1216</v>
+      </c>
+      <c r="S80">
+        <v>1216</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>96</v>
+      </c>
+      <c r="V80" t="s">
+        <v>42</v>
+      </c>
+      <c r="W80" t="s">
+        <v>42</v>
+      </c>
+      <c r="X80">
+        <v>2320</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA80">
+        <v>2821.12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>211</v>
+      </c>
+      <c r="B81" t="s">
+        <v>84</v>
+      </c>
+      <c r="C81" t="s">
+        <v>79</v>
+      </c>
+      <c r="D81" t="s">
+        <v>202</v>
+      </c>
+      <c r="E81" t="s">
+        <v>32</v>
+      </c>
+      <c r="F81" t="s">
+        <v>81</v>
+      </c>
+      <c r="G81" t="s">
+        <v>66</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>0.8</v>
+      </c>
+      <c r="J81">
+        <v>1250</v>
+      </c>
+      <c r="K81">
+        <v>2500</v>
+      </c>
+      <c r="L81" t="s">
+        <v>57</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>82</v>
+      </c>
+      <c r="R81">
+        <v>334</v>
+      </c>
+      <c r="S81">
+        <v>334</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>17</v>
+      </c>
+      <c r="V81" t="s">
+        <v>42</v>
+      </c>
+      <c r="W81" t="s">
+        <v>42</v>
+      </c>
+      <c r="X81">
+        <v>2320</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA81">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>212</v>
+      </c>
+      <c r="B82" t="s">
+        <v>84</v>
+      </c>
+      <c r="C82" t="s">
+        <v>79</v>
+      </c>
+      <c r="D82" t="s">
+        <v>202</v>
+      </c>
+      <c r="E82" t="s">
+        <v>32</v>
+      </c>
+      <c r="F82" t="s">
+        <v>81</v>
+      </c>
+      <c r="G82" t="s">
+        <v>66</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>0.8</v>
+      </c>
+      <c r="J82">
+        <v>1250</v>
+      </c>
+      <c r="K82">
+        <v>2500</v>
+      </c>
+      <c r="L82" t="s">
+        <v>57</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>82</v>
+      </c>
+      <c r="R82">
+        <v>334</v>
+      </c>
+      <c r="S82">
+        <v>334</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>17</v>
+      </c>
+      <c r="V82" t="s">
+        <v>42</v>
+      </c>
+      <c r="W82" t="s">
+        <v>42</v>
+      </c>
+      <c r="X82">
+        <v>2320</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA82">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>213</v>
+      </c>
+      <c r="B83" t="s">
+        <v>84</v>
+      </c>
+      <c r="C83" t="s">
+        <v>79</v>
+      </c>
+      <c r="D83" t="s">
+        <v>202</v>
+      </c>
+      <c r="E83" t="s">
+        <v>32</v>
+      </c>
+      <c r="F83" t="s">
+        <v>81</v>
+      </c>
+      <c r="G83" t="s">
+        <v>66</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>0.8</v>
+      </c>
+      <c r="J83">
+        <v>1250</v>
+      </c>
+      <c r="K83">
+        <v>2500</v>
+      </c>
+      <c r="L83" t="s">
+        <v>57</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>82</v>
+      </c>
+      <c r="R83">
+        <v>551</v>
+      </c>
+      <c r="S83">
+        <v>551</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>28</v>
+      </c>
+      <c r="V83" t="s">
+        <v>42</v>
+      </c>
+      <c r="W83" t="s">
+        <v>42</v>
+      </c>
+      <c r="X83">
+        <v>2320</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA83">
+        <v>1278.32</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>214</v>
+      </c>
+      <c r="B84" t="s">
+        <v>78</v>
+      </c>
+      <c r="C84" t="s">
+        <v>79</v>
+      </c>
+      <c r="D84" t="s">
+        <v>215</v>
+      </c>
+      <c r="E84" t="s">
+        <v>32</v>
+      </c>
+      <c r="F84" t="s">
+        <v>81</v>
+      </c>
+      <c r="G84" t="s">
+        <v>92</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84">
+        <v>1250</v>
+      </c>
+      <c r="K84">
+        <v>2500</v>
+      </c>
+      <c r="L84" t="s">
+        <v>57</v>
+      </c>
+      <c r="M84" t="s">
+        <v>103</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>82</v>
+      </c>
+      <c r="R84">
+        <v>612</v>
+      </c>
+      <c r="S84">
+        <v>612</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>12</v>
+      </c>
+      <c r="V84" t="s">
+        <v>42</v>
+      </c>
+      <c r="W84" t="s">
+        <v>42</v>
+      </c>
+      <c r="X84">
+        <v>3490</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA84">
+        <v>2135.88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>216</v>
+      </c>
+      <c r="B85" t="s">
+        <v>78</v>
+      </c>
+      <c r="C85" t="s">
+        <v>79</v>
+      </c>
+      <c r="D85" t="s">
+        <v>181</v>
+      </c>
+      <c r="E85" t="s">
+        <v>32</v>
+      </c>
+      <c r="F85" t="s">
+        <v>81</v>
+      </c>
+      <c r="G85" t="s">
+        <v>66</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>1000</v>
+      </c>
+      <c r="K85">
+        <v>2000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>57</v>
+      </c>
+      <c r="M85" t="s">
+        <v>103</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>82</v>
+      </c>
+      <c r="R85">
+        <v>752</v>
+      </c>
+      <c r="S85">
+        <v>752</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>48</v>
+      </c>
+      <c r="V85" t="s">
+        <v>42</v>
+      </c>
+      <c r="W85" t="s">
+        <v>42</v>
+      </c>
+      <c r="X85">
+        <v>2170</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA85">
+        <v>1631.84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>217</v>
+      </c>
+      <c r="B86" t="s">
+        <v>90</v>
+      </c>
+      <c r="C86" t="s">
+        <v>79</v>
+      </c>
+      <c r="D86" t="s">
+        <v>218</v>
+      </c>
+      <c r="E86" t="s">
+        <v>32</v>
+      </c>
+      <c r="F86" t="s">
+        <v>81</v>
+      </c>
+      <c r="G86" t="s">
+        <v>97</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>3</v>
+      </c>
+      <c r="J86">
+        <v>1500</v>
+      </c>
+      <c r="K86">
+        <v>3000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>57</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>82</v>
+      </c>
+      <c r="R86">
+        <v>106</v>
+      </c>
+      <c r="S86">
+        <v>106</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>1</v>
+      </c>
+      <c r="V86" t="s">
+        <v>42</v>
+      </c>
+      <c r="W86" t="s">
+        <v>42</v>
+      </c>
+      <c r="X86">
+        <v>3640</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA86">
+        <v>385.84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>219</v>
+      </c>
+      <c r="B87" t="s">
+        <v>78</v>
+      </c>
+      <c r="C87" t="s">
+        <v>79</v>
+      </c>
+      <c r="D87" t="s">
+        <v>161</v>
+      </c>
+      <c r="E87" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" t="s">
+        <v>81</v>
+      </c>
+      <c r="G87" t="s">
+        <v>92</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87">
+        <v>1.5</v>
+      </c>
+      <c r="J87">
+        <v>1500</v>
+      </c>
+      <c r="K87">
+        <v>3000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>57</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>82</v>
+      </c>
+      <c r="R87">
+        <v>330</v>
+      </c>
+      <c r="S87">
+        <v>330</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>6</v>
+      </c>
+      <c r="V87" t="s">
+        <v>42</v>
+      </c>
+      <c r="W87" t="s">
+        <v>42</v>
+      </c>
+      <c r="X87">
+        <v>3540</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA87">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>220</v>
+      </c>
+      <c r="B88" t="s">
+        <v>84</v>
+      </c>
+      <c r="C88" t="s">
+        <v>79</v>
+      </c>
+      <c r="D88" t="s">
+        <v>221</v>
+      </c>
+      <c r="E88" t="s">
+        <v>32</v>
+      </c>
+      <c r="F88" t="s">
+        <v>81</v>
+      </c>
+      <c r="G88" t="s">
+        <v>66</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88">
+        <v>3</v>
+      </c>
+      <c r="J88">
+        <v>1000</v>
+      </c>
+      <c r="K88">
+        <v>2000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>57</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>82</v>
+      </c>
+      <c r="R88">
+        <v>1464</v>
+      </c>
+      <c r="S88">
+        <v>1464</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>31</v>
+      </c>
+      <c r="V88" t="s">
+        <v>42</v>
+      </c>
+      <c r="W88" t="s">
+        <v>42</v>
+      </c>
+      <c r="X88">
+        <v>2270</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA88">
+        <v>3323.28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>222</v>
+      </c>
+      <c r="B89" t="s">
+        <v>84</v>
+      </c>
+      <c r="C89" t="s">
+        <v>79</v>
+      </c>
+      <c r="D89" t="s">
+        <v>221</v>
+      </c>
+      <c r="E89" t="s">
+        <v>32</v>
+      </c>
+      <c r="F89" t="s">
+        <v>81</v>
+      </c>
+      <c r="G89" t="s">
+        <v>66</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89">
+        <v>3</v>
+      </c>
+      <c r="J89">
+        <v>1000</v>
+      </c>
+      <c r="K89">
+        <v>2000</v>
+      </c>
+      <c r="L89" t="s">
+        <v>57</v>
+      </c>
+      <c r="M89" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>82</v>
+      </c>
+      <c r="R89">
+        <v>94</v>
+      </c>
+      <c r="S89">
+        <v>94</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>2</v>
+      </c>
+      <c r="V89" t="s">
+        <v>42</v>
+      </c>
+      <c r="W89" t="s">
+        <v>42</v>
+      </c>
+      <c r="X89">
+        <v>2170</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA89">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>223</v>
+      </c>
+      <c r="B90" t="s">
+        <v>78</v>
+      </c>
+      <c r="C90" t="s">
+        <v>79</v>
+      </c>
+      <c r="D90" t="s">
+        <v>224</v>
+      </c>
+      <c r="E90" t="s">
+        <v>32</v>
+      </c>
+      <c r="F90" t="s">
+        <v>33</v>
+      </c>
+      <c r="G90" t="s">
+        <v>225</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>1.2</v>
+      </c>
+      <c r="J90">
+        <v>1250</v>
+      </c>
+      <c r="L90" t="s">
+        <v>57</v>
+      </c>
+      <c r="M90" t="s">
+        <v>37</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>82</v>
+      </c>
+      <c r="R90">
+        <v>1420</v>
+      </c>
+      <c r="S90">
+        <v>1420</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>1</v>
+      </c>
+      <c r="V90" t="s">
+        <v>42</v>
+      </c>
+      <c r="W90" t="s">
+        <v>42</v>
+      </c>
+      <c r="X90">
+        <v>1420</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA90">
+        <v>2016.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>226</v>
+      </c>
+      <c r="B91" t="s">
+        <v>78</v>
+      </c>
+      <c r="C91" t="s">
+        <v>79</v>
+      </c>
+      <c r="D91" t="s">
+        <v>227</v>
+      </c>
+      <c r="E91" t="s">
+        <v>32</v>
+      </c>
+      <c r="F91" t="s">
+        <v>81</v>
+      </c>
+      <c r="G91" t="s">
+        <v>34</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91">
+        <v>1500</v>
+      </c>
+      <c r="K91">
+        <v>3000</v>
+      </c>
+      <c r="L91" t="s">
+        <v>36</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>82</v>
+      </c>
+      <c r="R91">
+        <v>414</v>
+      </c>
+      <c r="S91">
+        <v>414</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>12</v>
+      </c>
+      <c r="V91" t="s">
+        <v>42</v>
+      </c>
+      <c r="W91" t="s">
+        <v>42</v>
+      </c>
+      <c r="X91">
+        <v>1370</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA91">
+        <v>567.18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>228</v>
+      </c>
+      <c r="B92" t="s">
+        <v>78</v>
+      </c>
+      <c r="C92" t="s">
+        <v>79</v>
+      </c>
+      <c r="D92" t="s">
+        <v>229</v>
+      </c>
+      <c r="E92" t="s">
+        <v>32</v>
+      </c>
+      <c r="F92" t="s">
+        <v>81</v>
+      </c>
+      <c r="G92" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92">
+        <v>0.8</v>
+      </c>
+      <c r="J92">
+        <v>1500</v>
+      </c>
+      <c r="K92">
+        <v>3000</v>
+      </c>
+      <c r="L92" t="s">
+        <v>36</v>
+      </c>
+      <c r="M92" t="s">
+        <v>37</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>230</v>
+      </c>
+      <c r="P92" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>82</v>
+      </c>
+      <c r="R92">
+        <v>2584</v>
+      </c>
+      <c r="S92">
+        <v>2584</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>94</v>
+      </c>
+      <c r="V92" t="s">
+        <v>42</v>
+      </c>
+      <c r="W92" t="s">
+        <v>42</v>
+      </c>
+      <c r="X92">
+        <v>1520</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA92">
+        <v>3927.68</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>231</v>
+      </c>
+      <c r="B93" t="s">
+        <v>78</v>
+      </c>
+      <c r="C93" t="s">
+        <v>79</v>
+      </c>
+      <c r="D93" t="s">
+        <v>232</v>
+      </c>
+      <c r="E93" t="s">
+        <v>32</v>
+      </c>
+      <c r="F93" t="s">
+        <v>81</v>
+      </c>
+      <c r="G93" t="s">
+        <v>34</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1250</v>
+      </c>
+      <c r="K93">
+        <v>2500</v>
+      </c>
+      <c r="L93" t="s">
+        <v>36</v>
+      </c>
+      <c r="M93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" t="s">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>82</v>
+      </c>
+      <c r="R93">
+        <v>668</v>
+      </c>
+      <c r="S93">
+        <v>668</v>
+      </c>
+      <c r="T93" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93">
+        <v>1</v>
+      </c>
+      <c r="V93" t="s">
+        <v>42</v>
+      </c>
+      <c r="W93" t="s">
+        <v>42</v>
+      </c>
+      <c r="X93">
+        <v>1370</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA93">
+        <v>915.16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>233</v>
+      </c>
+      <c r="B94" t="s">
+        <v>78</v>
+      </c>
+      <c r="C94" t="s">
+        <v>79</v>
+      </c>
+      <c r="D94" t="s">
+        <v>119</v>
+      </c>
+      <c r="E94" t="s">
+        <v>32</v>
+      </c>
+      <c r="F94" t="s">
+        <v>81</v>
+      </c>
+      <c r="G94" t="s">
+        <v>66</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94">
+        <v>2</v>
+      </c>
+      <c r="J94">
+        <v>1250</v>
+      </c>
+      <c r="K94">
+        <v>2500</v>
+      </c>
+      <c r="L94" t="s">
+        <v>57</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
+      </c>
+      <c r="N94" t="s">
+        <v>37</v>
+      </c>
+      <c r="O94" t="s">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>82</v>
+      </c>
+      <c r="R94">
+        <v>358</v>
+      </c>
+      <c r="S94">
+        <v>358</v>
+      </c>
+      <c r="T94" t="s">
+        <v>41</v>
+      </c>
+      <c r="U94">
+        <v>7</v>
+      </c>
+      <c r="V94" t="s">
+        <v>42</v>
+      </c>
+      <c r="W94" t="s">
+        <v>42</v>
+      </c>
+      <c r="X94">
+        <v>2220</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA94">
+        <v>794.76</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>234</v>
+      </c>
+      <c r="B95" t="s">
+        <v>84</v>
+      </c>
+      <c r="C95" t="s">
+        <v>79</v>
+      </c>
+      <c r="D95" t="s">
+        <v>235</v>
+      </c>
+      <c r="E95" t="s">
+        <v>32</v>
+      </c>
+      <c r="F95" t="s">
+        <v>81</v>
+      </c>
+      <c r="G95" t="s">
+        <v>92</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95">
+        <v>3</v>
+      </c>
+      <c r="J95">
+        <v>2000</v>
+      </c>
+      <c r="K95">
+        <v>4000</v>
+      </c>
+      <c r="L95" t="s">
+        <v>57</v>
+      </c>
+      <c r="M95" t="s">
+        <v>37</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>82</v>
+      </c>
+      <c r="R95">
+        <v>189</v>
+      </c>
+      <c r="S95">
+        <v>189</v>
+      </c>
+      <c r="T95" t="s">
+        <v>41</v>
+      </c>
+      <c r="U95">
+        <v>1</v>
+      </c>
+      <c r="V95" t="s">
+        <v>42</v>
+      </c>
+      <c r="W95" t="s">
+        <v>42</v>
+      </c>
+      <c r="X95">
+        <v>3510</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA95">
+        <v>663.39</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>236</v>
+      </c>
+      <c r="B96" t="s">
+        <v>78</v>
+      </c>
+      <c r="C96" t="s">
+        <v>79</v>
+      </c>
+      <c r="D96" t="s">
+        <v>87</v>
+      </c>
+      <c r="E96" t="s">
+        <v>32</v>
+      </c>
+      <c r="F96" t="s">
+        <v>81</v>
+      </c>
+      <c r="G96" t="s">
+        <v>34</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
+        <v>1250</v>
+      </c>
+      <c r="K96">
+        <v>2500</v>
+      </c>
+      <c r="L96" t="s">
+        <v>36</v>
+      </c>
+      <c r="M96" t="s">
+        <v>37</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
+      </c>
+      <c r="P96" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>82</v>
+      </c>
+      <c r="R96">
+        <v>1554</v>
+      </c>
+      <c r="S96">
+        <v>1554</v>
+      </c>
+      <c r="T96" t="s">
+        <v>41</v>
+      </c>
+      <c r="U96">
+        <v>1</v>
+      </c>
+      <c r="V96" t="s">
+        <v>42</v>
+      </c>
+      <c r="W96" t="s">
+        <v>42</v>
+      </c>
+      <c r="X96">
+        <v>1420</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA96">
+        <v>2206.68</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>237</v>
+      </c>
+      <c r="B97" t="s">
+        <v>78</v>
+      </c>
+      <c r="C97" t="s">
+        <v>79</v>
+      </c>
+      <c r="D97" t="s">
+        <v>238</v>
+      </c>
+      <c r="E97" t="s">
+        <v>32</v>
+      </c>
+      <c r="F97" t="s">
+        <v>81</v>
+      </c>
+      <c r="G97" t="s">
+        <v>34</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>1500</v>
+      </c>
+      <c r="K97">
+        <v>3000</v>
+      </c>
+      <c r="L97" t="s">
+        <v>57</v>
+      </c>
+      <c r="M97" t="s">
+        <v>37</v>
+      </c>
+      <c r="N97" t="s">
+        <v>37</v>
+      </c>
+      <c r="O97" t="s">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>82</v>
+      </c>
+      <c r="R97">
+        <v>2210</v>
+      </c>
+      <c r="S97">
+        <v>2210</v>
+      </c>
+      <c r="T97" t="s">
+        <v>41</v>
+      </c>
+      <c r="U97">
+        <v>1</v>
+      </c>
+      <c r="V97" t="s">
+        <v>42</v>
+      </c>
+      <c r="W97" t="s">
+        <v>42</v>
+      </c>
+      <c r="X97">
+        <v>1420</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA97">
+        <v>3138.2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>239</v>
+      </c>
+      <c r="B98" t="s">
+        <v>78</v>
+      </c>
+      <c r="C98" t="s">
+        <v>79</v>
+      </c>
+      <c r="D98" t="s">
+        <v>240</v>
+      </c>
+      <c r="E98" t="s">
+        <v>32</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
+      </c>
+      <c r="G98" t="s">
+        <v>34</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>1500</v>
+      </c>
+      <c r="L98" t="s">
+        <v>57</v>
+      </c>
+      <c r="M98" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" t="s">
+        <v>38</v>
+      </c>
+      <c r="P98" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>82</v>
+      </c>
+      <c r="R98">
+        <v>3350</v>
+      </c>
+      <c r="S98">
+        <v>3350</v>
+      </c>
+      <c r="T98" t="s">
+        <v>41</v>
+      </c>
+      <c r="U98">
+        <v>1</v>
+      </c>
+      <c r="V98" t="s">
+        <v>42</v>
+      </c>
+      <c r="W98" t="s">
+        <v>42</v>
+      </c>
+      <c r="X98">
+        <v>1420</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA98">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>241</v>
+      </c>
+      <c r="B99" t="s">
+        <v>78</v>
+      </c>
+      <c r="C99" t="s">
+        <v>79</v>
+      </c>
+      <c r="D99" t="s">
+        <v>242</v>
+      </c>
+      <c r="E99" t="s">
+        <v>32</v>
+      </c>
+      <c r="F99" t="s">
+        <v>81</v>
+      </c>
+      <c r="G99" t="s">
+        <v>34</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99">
+        <v>1.5</v>
+      </c>
+      <c r="J99">
+        <v>1250</v>
+      </c>
+      <c r="K99">
+        <v>2500</v>
+      </c>
+      <c r="L99" t="s">
+        <v>36</v>
+      </c>
+      <c r="M99" t="s">
+        <v>37</v>
+      </c>
+      <c r="N99" t="s">
+        <v>37</v>
+      </c>
+      <c r="O99" t="s">
+        <v>38</v>
+      </c>
+      <c r="P99" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>82</v>
+      </c>
+      <c r="R99">
+        <v>944</v>
+      </c>
+      <c r="S99">
+        <v>944</v>
+      </c>
+      <c r="T99" t="s">
+        <v>41</v>
+      </c>
+      <c r="U99">
+        <v>26</v>
+      </c>
+      <c r="V99" t="s">
+        <v>42</v>
+      </c>
+      <c r="W99" t="s">
+        <v>42</v>
+      </c>
+      <c r="X99">
+        <v>1370</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA99">
+        <v>1293.28</v>
       </c>
     </row>
   </sheetData>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="255">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -251,6 +251,531 @@
   </si>
   <si>
     <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10088-2 / IS 6911 / JIS G 4305</t>
+  </si>
+  <si>
+    <t>7248626</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>1.4307-304L</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>K30/1.4016-430</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>T488802</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256740</t>
+  </si>
+  <si>
+    <t>Sheets 1.4301-304 2R 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256819</t>
+  </si>
+  <si>
+    <t>7256820</t>
+  </si>
+  <si>
+    <t>7256821</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>7256940</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed Nov 4228 0.8 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7256941</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489089</t>
+  </si>
+  <si>
+    <t>7257261</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Scotchbrite</t>
+  </si>
+  <si>
+    <t>T489700</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489750</t>
+  </si>
+  <si>
+    <t>7257570</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257703</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2E 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>2E</t>
+  </si>
+  <si>
+    <t>T490582</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257842</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 2000.0 x 4000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Nov 4228 6.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257864</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257865</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 400 NOV 4204 RB 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>NOV 4204 RB</t>
+  </si>
+  <si>
+    <t>7257894</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>S139218</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 12.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258091</t>
+  </si>
+  <si>
+    <t>7258100</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258149</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491483</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258350</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T492123</t>
+  </si>
+  <si>
+    <t>T492124</t>
+  </si>
+  <si>
+    <t>7258489</t>
+  </si>
+  <si>
+    <t>7258526</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258529</t>
+  </si>
+  <si>
+    <t>7258730</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258760</t>
+  </si>
+  <si>
+    <t>7258862</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258863</t>
+  </si>
+  <si>
+    <t>7259015</t>
+  </si>
+  <si>
+    <t>Coil 1.4520-430Ti 2B 1.2 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4520-430Ti</t>
+  </si>
+  <si>
+    <t>7259028</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R without paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259050</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R NOV 4241/4513 0.8 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>NOV 4241/4513</t>
+  </si>
+  <si>
+    <t>7259145</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259182</t>
+  </si>
+  <si>
+    <t>T492642</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259417</t>
+  </si>
+  <si>
+    <t>7259437</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259438</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B with paper 1.0 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7259439</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R with paper 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259445</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259447</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T493044</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.2 x 1500.0 x 3000 mm Slit</t>
   </si>
 </sst>
 </file>
@@ -627,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -1374,6 +1899,7651 @@
         <v>6637.62</v>
       </c>
     </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10">
+        <v>2.5</v>
+      </c>
+      <c r="J10">
+        <v>1000</v>
+      </c>
+      <c r="K10">
+        <v>2000</v>
+      </c>
+      <c r="L10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P10" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10">
+        <v>312</v>
+      </c>
+      <c r="S10">
+        <v>312</v>
+      </c>
+      <c r="T10" t="s">
+        <v>42</v>
+      </c>
+      <c r="U10">
+        <v>8</v>
+      </c>
+      <c r="V10" t="s">
+        <v>43</v>
+      </c>
+      <c r="W10" t="s">
+        <v>43</v>
+      </c>
+      <c r="X10">
+        <v>2220</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA10">
+        <v>692.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <v>1000</v>
+      </c>
+      <c r="K11">
+        <v>2000</v>
+      </c>
+      <c r="L11" t="s">
+        <v>69</v>
+      </c>
+      <c r="M11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>86</v>
+      </c>
+      <c r="R11">
+        <v>394</v>
+      </c>
+      <c r="S11">
+        <v>394</v>
+      </c>
+      <c r="T11" t="s">
+        <v>42</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X11">
+        <v>2020</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA11">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>1250</v>
+      </c>
+      <c r="K12">
+        <v>2500</v>
+      </c>
+      <c r="L12" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N12" t="s">
+        <v>38</v>
+      </c>
+      <c r="O12" t="s">
+        <v>39</v>
+      </c>
+      <c r="P12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>86</v>
+      </c>
+      <c r="R12">
+        <v>322</v>
+      </c>
+      <c r="S12">
+        <v>322</v>
+      </c>
+      <c r="T12" t="s">
+        <v>42</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" t="s">
+        <v>43</v>
+      </c>
+      <c r="X12">
+        <v>1370</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA12">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>1250</v>
+      </c>
+      <c r="K13">
+        <v>2500</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>38</v>
+      </c>
+      <c r="N13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>86</v>
+      </c>
+      <c r="R13">
+        <v>340</v>
+      </c>
+      <c r="S13">
+        <v>340</v>
+      </c>
+      <c r="T13" t="s">
+        <v>42</v>
+      </c>
+      <c r="U13">
+        <v>7</v>
+      </c>
+      <c r="V13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13">
+        <v>1370</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA13">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>2000</v>
+      </c>
+      <c r="K14">
+        <v>6000</v>
+      </c>
+      <c r="L14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" t="s">
+        <v>38</v>
+      </c>
+      <c r="N14" t="s">
+        <v>38</v>
+      </c>
+      <c r="O14" t="s">
+        <v>39</v>
+      </c>
+      <c r="P14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R14">
+        <v>283</v>
+      </c>
+      <c r="S14">
+        <v>283</v>
+      </c>
+      <c r="T14" t="s">
+        <v>42</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14" t="s">
+        <v>43</v>
+      </c>
+      <c r="W14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X14">
+        <v>3560</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA14">
+        <v>1007.48</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15">
+        <v>6</v>
+      </c>
+      <c r="J15">
+        <v>1500</v>
+      </c>
+      <c r="K15">
+        <v>3000</v>
+      </c>
+      <c r="L15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M15" t="s">
+        <v>38</v>
+      </c>
+      <c r="N15" t="s">
+        <v>38</v>
+      </c>
+      <c r="O15" t="s">
+        <v>39</v>
+      </c>
+      <c r="P15" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>86</v>
+      </c>
+      <c r="R15">
+        <v>212</v>
+      </c>
+      <c r="S15">
+        <v>212</v>
+      </c>
+      <c r="T15" t="s">
+        <v>42</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" t="s">
+        <v>43</v>
+      </c>
+      <c r="X15">
+        <v>3490</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA15">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+      <c r="J16">
+        <v>1250</v>
+      </c>
+      <c r="K16">
+        <v>2500</v>
+      </c>
+      <c r="L16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16" t="s">
+        <v>38</v>
+      </c>
+      <c r="N16" t="s">
+        <v>38</v>
+      </c>
+      <c r="O16" t="s">
+        <v>39</v>
+      </c>
+      <c r="P16" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>86</v>
+      </c>
+      <c r="R16">
+        <v>394</v>
+      </c>
+      <c r="S16">
+        <v>394</v>
+      </c>
+      <c r="T16" t="s">
+        <v>42</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
+        <v>43</v>
+      </c>
+      <c r="W16" t="s">
+        <v>43</v>
+      </c>
+      <c r="X16">
+        <v>3490</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA16">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
+        <v>2000</v>
+      </c>
+      <c r="K17">
+        <v>6000</v>
+      </c>
+      <c r="L17" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" t="s">
+        <v>38</v>
+      </c>
+      <c r="N17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O17" t="s">
+        <v>39</v>
+      </c>
+      <c r="P17" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>86</v>
+      </c>
+      <c r="R17">
+        <v>472</v>
+      </c>
+      <c r="S17">
+        <v>472</v>
+      </c>
+      <c r="T17" t="s">
+        <v>42</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W17" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17">
+        <v>2190</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA17">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>1500</v>
+      </c>
+      <c r="K18">
+        <v>3000</v>
+      </c>
+      <c r="L18" t="s">
+        <v>53</v>
+      </c>
+      <c r="M18" t="s">
+        <v>107</v>
+      </c>
+      <c r="N18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O18" t="s">
+        <v>39</v>
+      </c>
+      <c r="P18" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>86</v>
+      </c>
+      <c r="R18">
+        <v>970</v>
+      </c>
+      <c r="S18">
+        <v>970</v>
+      </c>
+      <c r="T18" t="s">
+        <v>42</v>
+      </c>
+      <c r="U18">
+        <v>13</v>
+      </c>
+      <c r="V18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X18">
+        <v>3490</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA18">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19">
+        <v>2.5</v>
+      </c>
+      <c r="J19">
+        <v>1500</v>
+      </c>
+      <c r="K19">
+        <v>3000</v>
+      </c>
+      <c r="L19" t="s">
+        <v>53</v>
+      </c>
+      <c r="M19" t="s">
+        <v>38</v>
+      </c>
+      <c r="N19" t="s">
+        <v>38</v>
+      </c>
+      <c r="O19" t="s">
+        <v>39</v>
+      </c>
+      <c r="P19" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>86</v>
+      </c>
+      <c r="R19">
+        <v>526</v>
+      </c>
+      <c r="S19">
+        <v>526</v>
+      </c>
+      <c r="T19" t="s">
+        <v>42</v>
+      </c>
+      <c r="U19">
+        <v>6</v>
+      </c>
+      <c r="V19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" t="s">
+        <v>43</v>
+      </c>
+      <c r="X19">
+        <v>3540</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA19">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>1500</v>
+      </c>
+      <c r="K20">
+        <v>3000</v>
+      </c>
+      <c r="L20" t="s">
+        <v>69</v>
+      </c>
+      <c r="M20" t="s">
+        <v>38</v>
+      </c>
+      <c r="N20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O20" t="s">
+        <v>39</v>
+      </c>
+      <c r="P20" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>86</v>
+      </c>
+      <c r="R20">
+        <v>354</v>
+      </c>
+      <c r="S20">
+        <v>354</v>
+      </c>
+      <c r="T20" t="s">
+        <v>42</v>
+      </c>
+      <c r="U20">
+        <v>2</v>
+      </c>
+      <c r="V20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20">
+        <v>1170</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA20">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21">
+        <v>1.5</v>
+      </c>
+      <c r="J21">
+        <v>1250</v>
+      </c>
+      <c r="L21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M21" t="s">
+        <v>38</v>
+      </c>
+      <c r="N21" t="s">
+        <v>38</v>
+      </c>
+      <c r="O21" t="s">
+        <v>39</v>
+      </c>
+      <c r="P21" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>86</v>
+      </c>
+      <c r="R21">
+        <v>1275</v>
+      </c>
+      <c r="S21">
+        <v>1275</v>
+      </c>
+      <c r="T21" t="s">
+        <v>42</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21">
+        <v>3590</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>1500</v>
+      </c>
+      <c r="K22">
+        <v>3000</v>
+      </c>
+      <c r="L22" t="s">
+        <v>53</v>
+      </c>
+      <c r="M22" t="s">
+        <v>38</v>
+      </c>
+      <c r="N22" t="s">
+        <v>38</v>
+      </c>
+      <c r="O22" t="s">
+        <v>39</v>
+      </c>
+      <c r="P22" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>86</v>
+      </c>
+      <c r="R22">
+        <v>210</v>
+      </c>
+      <c r="S22">
+        <v>210</v>
+      </c>
+      <c r="T22" t="s">
+        <v>42</v>
+      </c>
+      <c r="U22">
+        <v>2</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>43</v>
+      </c>
+      <c r="X22">
+        <v>2170</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="J23">
+        <v>1500</v>
+      </c>
+      <c r="K23">
+        <v>3000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" t="s">
+        <v>38</v>
+      </c>
+      <c r="N23" t="s">
+        <v>38</v>
+      </c>
+      <c r="O23" t="s">
+        <v>39</v>
+      </c>
+      <c r="P23" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>86</v>
+      </c>
+      <c r="R23">
+        <v>212</v>
+      </c>
+      <c r="S23">
+        <v>212</v>
+      </c>
+      <c r="T23" t="s">
+        <v>42</v>
+      </c>
+      <c r="U23">
+        <v>2</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23">
+        <v>1320</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA23">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24">
+        <v>6</v>
+      </c>
+      <c r="J24">
+        <v>1000</v>
+      </c>
+      <c r="K24">
+        <v>2000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>53</v>
+      </c>
+      <c r="M24" t="s">
+        <v>38</v>
+      </c>
+      <c r="N24" t="s">
+        <v>38</v>
+      </c>
+      <c r="O24" t="s">
+        <v>39</v>
+      </c>
+      <c r="P24" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>86</v>
+      </c>
+      <c r="R24">
+        <v>567</v>
+      </c>
+      <c r="S24">
+        <v>567</v>
+      </c>
+      <c r="T24" t="s">
+        <v>42</v>
+      </c>
+      <c r="U24">
+        <v>6</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>2220</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25">
+        <v>6</v>
+      </c>
+      <c r="J25">
+        <v>1000</v>
+      </c>
+      <c r="K25">
+        <v>2000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" t="s">
+        <v>38</v>
+      </c>
+      <c r="N25" t="s">
+        <v>38</v>
+      </c>
+      <c r="O25" t="s">
+        <v>39</v>
+      </c>
+      <c r="P25" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>86</v>
+      </c>
+      <c r="R25">
+        <v>567</v>
+      </c>
+      <c r="S25">
+        <v>567</v>
+      </c>
+      <c r="T25" t="s">
+        <v>42</v>
+      </c>
+      <c r="U25">
+        <v>6</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>2220</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26">
+        <v>3</v>
+      </c>
+      <c r="J26">
+        <v>1500</v>
+      </c>
+      <c r="K26">
+        <v>3000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>53</v>
+      </c>
+      <c r="M26" t="s">
+        <v>38</v>
+      </c>
+      <c r="N26" t="s">
+        <v>38</v>
+      </c>
+      <c r="O26" t="s">
+        <v>39</v>
+      </c>
+      <c r="P26" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>86</v>
+      </c>
+      <c r="R26">
+        <v>319</v>
+      </c>
+      <c r="S26">
+        <v>319</v>
+      </c>
+      <c r="T26" t="s">
+        <v>42</v>
+      </c>
+      <c r="U26">
+        <v>3</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>1370</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>1250</v>
+      </c>
+      <c r="K27">
+        <v>2500</v>
+      </c>
+      <c r="L27" t="s">
+        <v>53</v>
+      </c>
+      <c r="M27" t="s">
+        <v>38</v>
+      </c>
+      <c r="N27" t="s">
+        <v>38</v>
+      </c>
+      <c r="O27" t="s">
+        <v>39</v>
+      </c>
+      <c r="P27" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>86</v>
+      </c>
+      <c r="R27">
+        <v>246</v>
+      </c>
+      <c r="S27">
+        <v>246</v>
+      </c>
+      <c r="T27" t="s">
+        <v>42</v>
+      </c>
+      <c r="U27">
+        <v>5</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>2170</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28">
+        <v>0.8</v>
+      </c>
+      <c r="J28">
+        <v>1000</v>
+      </c>
+      <c r="K28">
+        <v>2000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>53</v>
+      </c>
+      <c r="M28" t="s">
+        <v>38</v>
+      </c>
+      <c r="N28" t="s">
+        <v>38</v>
+      </c>
+      <c r="O28" t="s">
+        <v>39</v>
+      </c>
+      <c r="P28" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>86</v>
+      </c>
+      <c r="R28">
+        <v>1498</v>
+      </c>
+      <c r="S28">
+        <v>1498</v>
+      </c>
+      <c r="T28" t="s">
+        <v>42</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>2370</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29">
+        <v>0.8</v>
+      </c>
+      <c r="J29">
+        <v>1000</v>
+      </c>
+      <c r="K29">
+        <v>2000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>53</v>
+      </c>
+      <c r="M29" t="s">
+        <v>38</v>
+      </c>
+      <c r="N29" t="s">
+        <v>38</v>
+      </c>
+      <c r="O29" t="s">
+        <v>39</v>
+      </c>
+      <c r="P29" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>86</v>
+      </c>
+      <c r="R29">
+        <v>1498</v>
+      </c>
+      <c r="S29">
+        <v>1498</v>
+      </c>
+      <c r="T29" t="s">
+        <v>42</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>2370</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>1500</v>
+      </c>
+      <c r="K30">
+        <v>3000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" t="s">
+        <v>107</v>
+      </c>
+      <c r="N30" t="s">
+        <v>38</v>
+      </c>
+      <c r="O30" t="s">
+        <v>39</v>
+      </c>
+      <c r="P30" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>86</v>
+      </c>
+      <c r="R30">
+        <v>1010</v>
+      </c>
+      <c r="S30">
+        <v>1010</v>
+      </c>
+      <c r="T30" t="s">
+        <v>42</v>
+      </c>
+      <c r="U30">
+        <v>14</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>3540</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>1500</v>
+      </c>
+      <c r="K31">
+        <v>3000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" t="s">
+        <v>38</v>
+      </c>
+      <c r="N31" t="s">
+        <v>38</v>
+      </c>
+      <c r="O31" t="s">
+        <v>39</v>
+      </c>
+      <c r="P31" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>86</v>
+      </c>
+      <c r="R31">
+        <v>283</v>
+      </c>
+      <c r="S31">
+        <v>283</v>
+      </c>
+      <c r="T31" t="s">
+        <v>42</v>
+      </c>
+      <c r="U31">
+        <v>4</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>3540</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" t="s">
+        <v>132</v>
+      </c>
+      <c r="H32" t="s">
+        <v>52</v>
+      </c>
+      <c r="I32">
+        <v>0.8</v>
+      </c>
+      <c r="J32">
+        <v>1000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>36</v>
+      </c>
+      <c r="M32" t="s">
+        <v>38</v>
+      </c>
+      <c r="N32" t="s">
+        <v>38</v>
+      </c>
+      <c r="O32" t="s">
+        <v>133</v>
+      </c>
+      <c r="P32" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>86</v>
+      </c>
+      <c r="R32">
+        <v>1585</v>
+      </c>
+      <c r="S32">
+        <v>1585</v>
+      </c>
+      <c r="T32" t="s">
+        <v>42</v>
+      </c>
+      <c r="U32">
+        <v>1</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>2370</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33">
+        <v>1.5</v>
+      </c>
+      <c r="J33">
+        <v>1500</v>
+      </c>
+      <c r="K33">
+        <v>3000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>53</v>
+      </c>
+      <c r="M33" t="s">
+        <v>38</v>
+      </c>
+      <c r="N33" t="s">
+        <v>38</v>
+      </c>
+      <c r="O33" t="s">
+        <v>39</v>
+      </c>
+      <c r="P33" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>86</v>
+      </c>
+      <c r="R33">
+        <v>212</v>
+      </c>
+      <c r="S33">
+        <v>212</v>
+      </c>
+      <c r="T33" t="s">
+        <v>42</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>1320</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G34" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I34">
+        <v>2.5</v>
+      </c>
+      <c r="J34">
+        <v>1500</v>
+      </c>
+      <c r="K34">
+        <v>3000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>53</v>
+      </c>
+      <c r="M34" t="s">
+        <v>38</v>
+      </c>
+      <c r="N34" t="s">
+        <v>38</v>
+      </c>
+      <c r="O34" t="s">
+        <v>39</v>
+      </c>
+      <c r="P34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>86</v>
+      </c>
+      <c r="R34">
+        <v>540</v>
+      </c>
+      <c r="S34">
+        <v>540</v>
+      </c>
+      <c r="T34" t="s">
+        <v>42</v>
+      </c>
+      <c r="U34">
+        <v>6</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>3540</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" t="s">
+        <v>52</v>
+      </c>
+      <c r="I35">
+        <v>2.5</v>
+      </c>
+      <c r="J35">
+        <v>1500</v>
+      </c>
+      <c r="K35">
+        <v>3000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>53</v>
+      </c>
+      <c r="M35" t="s">
+        <v>38</v>
+      </c>
+      <c r="N35" t="s">
+        <v>38</v>
+      </c>
+      <c r="O35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P35" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>86</v>
+      </c>
+      <c r="R35">
+        <v>520</v>
+      </c>
+      <c r="S35">
+        <v>520</v>
+      </c>
+      <c r="T35" t="s">
+        <v>42</v>
+      </c>
+      <c r="U35">
+        <v>6</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>3540</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" t="s">
+        <v>109</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G36" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" t="s">
+        <v>52</v>
+      </c>
+      <c r="I36">
+        <v>2.5</v>
+      </c>
+      <c r="J36">
+        <v>1500</v>
+      </c>
+      <c r="K36">
+        <v>3000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>53</v>
+      </c>
+      <c r="M36" t="s">
+        <v>38</v>
+      </c>
+      <c r="N36" t="s">
+        <v>38</v>
+      </c>
+      <c r="O36" t="s">
+        <v>39</v>
+      </c>
+      <c r="P36" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>86</v>
+      </c>
+      <c r="R36">
+        <v>530</v>
+      </c>
+      <c r="S36">
+        <v>530</v>
+      </c>
+      <c r="T36" t="s">
+        <v>42</v>
+      </c>
+      <c r="U36">
+        <v>6</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>3540</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G37" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" t="s">
+        <v>52</v>
+      </c>
+      <c r="I37">
+        <v>2.5</v>
+      </c>
+      <c r="J37">
+        <v>1500</v>
+      </c>
+      <c r="K37">
+        <v>3000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>53</v>
+      </c>
+      <c r="M37" t="s">
+        <v>38</v>
+      </c>
+      <c r="N37" t="s">
+        <v>38</v>
+      </c>
+      <c r="O37" t="s">
+        <v>39</v>
+      </c>
+      <c r="P37" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>86</v>
+      </c>
+      <c r="R37">
+        <v>526</v>
+      </c>
+      <c r="S37">
+        <v>526</v>
+      </c>
+      <c r="T37" t="s">
+        <v>42</v>
+      </c>
+      <c r="U37">
+        <v>6</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>3540</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H38" t="s">
+        <v>52</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>1500</v>
+      </c>
+      <c r="K38">
+        <v>3000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>53</v>
+      </c>
+      <c r="M38" t="s">
+        <v>38</v>
+      </c>
+      <c r="N38" t="s">
+        <v>38</v>
+      </c>
+      <c r="O38" t="s">
+        <v>39</v>
+      </c>
+      <c r="P38" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>86</v>
+      </c>
+      <c r="R38">
+        <v>212</v>
+      </c>
+      <c r="S38">
+        <v>212</v>
+      </c>
+      <c r="T38" t="s">
+        <v>42</v>
+      </c>
+      <c r="U38">
+        <v>1</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>3490</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
+        <v>84</v>
+      </c>
+      <c r="G39" t="s">
+        <v>51</v>
+      </c>
+      <c r="H39" t="s">
+        <v>52</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>1500</v>
+      </c>
+      <c r="K39">
+        <v>3000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>53</v>
+      </c>
+      <c r="M39" t="s">
+        <v>38</v>
+      </c>
+      <c r="N39" t="s">
+        <v>38</v>
+      </c>
+      <c r="O39" t="s">
+        <v>39</v>
+      </c>
+      <c r="P39" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>86</v>
+      </c>
+      <c r="R39">
+        <v>212</v>
+      </c>
+      <c r="S39">
+        <v>212</v>
+      </c>
+      <c r="T39" t="s">
+        <v>42</v>
+      </c>
+      <c r="U39">
+        <v>1</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>3490</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
+        <v>84</v>
+      </c>
+      <c r="G40" t="s">
+        <v>85</v>
+      </c>
+      <c r="H40" t="s">
+        <v>52</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40">
+        <v>1000</v>
+      </c>
+      <c r="K40">
+        <v>2000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>53</v>
+      </c>
+      <c r="M40" t="s">
+        <v>38</v>
+      </c>
+      <c r="N40" t="s">
+        <v>38</v>
+      </c>
+      <c r="O40" t="s">
+        <v>39</v>
+      </c>
+      <c r="P40" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>86</v>
+      </c>
+      <c r="R40">
+        <v>315</v>
+      </c>
+      <c r="S40">
+        <v>315</v>
+      </c>
+      <c r="T40" t="s">
+        <v>42</v>
+      </c>
+      <c r="U40">
+        <v>5</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>2220</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>145</v>
+      </c>
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" t="s">
+        <v>84</v>
+      </c>
+      <c r="G41" t="s">
+        <v>85</v>
+      </c>
+      <c r="H41" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41">
+        <v>5</v>
+      </c>
+      <c r="J41">
+        <v>1000</v>
+      </c>
+      <c r="K41">
+        <v>2000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>69</v>
+      </c>
+      <c r="M41" t="s">
+        <v>38</v>
+      </c>
+      <c r="N41" t="s">
+        <v>38</v>
+      </c>
+      <c r="O41" t="s">
+        <v>39</v>
+      </c>
+      <c r="P41" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>86</v>
+      </c>
+      <c r="R41">
+        <v>944</v>
+      </c>
+      <c r="S41">
+        <v>944</v>
+      </c>
+      <c r="T41" t="s">
+        <v>42</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>2020</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>146</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>84</v>
+      </c>
+      <c r="G42" t="s">
+        <v>51</v>
+      </c>
+      <c r="H42" t="s">
+        <v>52</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>1500</v>
+      </c>
+      <c r="K42">
+        <v>3000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>53</v>
+      </c>
+      <c r="M42" t="s">
+        <v>107</v>
+      </c>
+      <c r="N42" t="s">
+        <v>38</v>
+      </c>
+      <c r="O42" t="s">
+        <v>39</v>
+      </c>
+      <c r="P42" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>86</v>
+      </c>
+      <c r="R42">
+        <v>1224</v>
+      </c>
+      <c r="S42">
+        <v>1224</v>
+      </c>
+      <c r="T42" t="s">
+        <v>42</v>
+      </c>
+      <c r="U42">
+        <v>34</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>3540</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" t="s">
+        <v>149</v>
+      </c>
+      <c r="E43" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" t="s">
+        <v>84</v>
+      </c>
+      <c r="G43" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I43">
+        <v>1.5</v>
+      </c>
+      <c r="J43">
+        <v>1500</v>
+      </c>
+      <c r="K43">
+        <v>3000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>36</v>
+      </c>
+      <c r="M43" t="s">
+        <v>107</v>
+      </c>
+      <c r="N43" t="s">
+        <v>38</v>
+      </c>
+      <c r="O43" t="s">
+        <v>39</v>
+      </c>
+      <c r="P43" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>86</v>
+      </c>
+      <c r="R43">
+        <v>916</v>
+      </c>
+      <c r="S43">
+        <v>916</v>
+      </c>
+      <c r="T43" t="s">
+        <v>42</v>
+      </c>
+      <c r="U43">
+        <v>18</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>1320</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>150</v>
+      </c>
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44" t="s">
+        <v>51</v>
+      </c>
+      <c r="H44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>1500</v>
+      </c>
+      <c r="K44">
+        <v>3000</v>
+      </c>
+      <c r="L44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M44" t="s">
+        <v>38</v>
+      </c>
+      <c r="N44" t="s">
+        <v>38</v>
+      </c>
+      <c r="O44" t="s">
+        <v>39</v>
+      </c>
+      <c r="P44" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>86</v>
+      </c>
+      <c r="R44">
+        <v>319</v>
+      </c>
+      <c r="S44">
+        <v>319</v>
+      </c>
+      <c r="T44" t="s">
+        <v>42</v>
+      </c>
+      <c r="U44">
+        <v>1</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>3540</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" t="s">
+        <v>84</v>
+      </c>
+      <c r="G45" t="s">
+        <v>51</v>
+      </c>
+      <c r="H45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="J45">
+        <v>1500</v>
+      </c>
+      <c r="K45">
+        <v>3000</v>
+      </c>
+      <c r="L45" t="s">
+        <v>53</v>
+      </c>
+      <c r="M45" t="s">
+        <v>38</v>
+      </c>
+      <c r="N45" t="s">
+        <v>38</v>
+      </c>
+      <c r="O45" t="s">
+        <v>39</v>
+      </c>
+      <c r="P45" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>86</v>
+      </c>
+      <c r="R45">
+        <v>212</v>
+      </c>
+      <c r="S45">
+        <v>212</v>
+      </c>
+      <c r="T45" t="s">
+        <v>42</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>3490</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" t="s">
+        <v>84</v>
+      </c>
+      <c r="G46" t="s">
+        <v>51</v>
+      </c>
+      <c r="H46" t="s">
+        <v>52</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>1500</v>
+      </c>
+      <c r="K46">
+        <v>3000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>53</v>
+      </c>
+      <c r="M46" t="s">
+        <v>38</v>
+      </c>
+      <c r="N46" t="s">
+        <v>38</v>
+      </c>
+      <c r="O46" t="s">
+        <v>39</v>
+      </c>
+      <c r="P46" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>86</v>
+      </c>
+      <c r="R46">
+        <v>212</v>
+      </c>
+      <c r="S46">
+        <v>212</v>
+      </c>
+      <c r="T46" t="s">
+        <v>42</v>
+      </c>
+      <c r="U46">
+        <v>1</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>3490</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>84</v>
+      </c>
+      <c r="G47" t="s">
+        <v>51</v>
+      </c>
+      <c r="H47" t="s">
+        <v>52</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>1500</v>
+      </c>
+      <c r="K47">
+        <v>3000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>53</v>
+      </c>
+      <c r="M47" t="s">
+        <v>38</v>
+      </c>
+      <c r="N47" t="s">
+        <v>38</v>
+      </c>
+      <c r="O47" t="s">
+        <v>39</v>
+      </c>
+      <c r="P47" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>86</v>
+      </c>
+      <c r="R47">
+        <v>319</v>
+      </c>
+      <c r="S47">
+        <v>319</v>
+      </c>
+      <c r="T47" t="s">
+        <v>42</v>
+      </c>
+      <c r="U47">
+        <v>1</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>3540</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>154</v>
+      </c>
+      <c r="B48" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" t="s">
+        <v>82</v>
+      </c>
+      <c r="D48" t="s">
+        <v>155</v>
+      </c>
+      <c r="E48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48" t="s">
+        <v>85</v>
+      </c>
+      <c r="H48" t="s">
+        <v>52</v>
+      </c>
+      <c r="I48">
+        <v>6</v>
+      </c>
+      <c r="J48">
+        <v>2000</v>
+      </c>
+      <c r="K48">
+        <v>4000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>53</v>
+      </c>
+      <c r="M48" t="s">
+        <v>38</v>
+      </c>
+      <c r="N48" t="s">
+        <v>38</v>
+      </c>
+      <c r="O48" t="s">
+        <v>39</v>
+      </c>
+      <c r="P48" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>86</v>
+      </c>
+      <c r="R48">
+        <v>756</v>
+      </c>
+      <c r="S48">
+        <v>756</v>
+      </c>
+      <c r="T48" t="s">
+        <v>42</v>
+      </c>
+      <c r="U48">
+        <v>2</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>2240</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>1693.44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" t="s">
+        <v>84</v>
+      </c>
+      <c r="G49" t="s">
+        <v>158</v>
+      </c>
+      <c r="H49" t="s">
+        <v>52</v>
+      </c>
+      <c r="I49">
+        <v>2</v>
+      </c>
+      <c r="J49">
+        <v>1000</v>
+      </c>
+      <c r="K49">
+        <v>2000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>36</v>
+      </c>
+      <c r="M49" t="s">
+        <v>38</v>
+      </c>
+      <c r="N49" t="s">
+        <v>38</v>
+      </c>
+      <c r="O49" t="s">
+        <v>39</v>
+      </c>
+      <c r="P49" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>86</v>
+      </c>
+      <c r="R49">
+        <v>544</v>
+      </c>
+      <c r="S49">
+        <v>544</v>
+      </c>
+      <c r="T49" t="s">
+        <v>42</v>
+      </c>
+      <c r="U49">
+        <v>1</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>2220</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>1207.68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" t="s">
+        <v>132</v>
+      </c>
+      <c r="H50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I50">
+        <v>0.8</v>
+      </c>
+      <c r="J50">
+        <v>1000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>36</v>
+      </c>
+      <c r="M50" t="s">
+        <v>38</v>
+      </c>
+      <c r="N50" t="s">
+        <v>38</v>
+      </c>
+      <c r="O50" t="s">
+        <v>39</v>
+      </c>
+      <c r="P50" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>86</v>
+      </c>
+      <c r="R50">
+        <v>1000</v>
+      </c>
+      <c r="S50">
+        <v>1000</v>
+      </c>
+      <c r="T50" t="s">
+        <v>42</v>
+      </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>2370</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>161</v>
+      </c>
+      <c r="B51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" t="s">
+        <v>162</v>
+      </c>
+      <c r="E51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" t="s">
+        <v>84</v>
+      </c>
+      <c r="G51" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" t="s">
+        <v>52</v>
+      </c>
+      <c r="I51">
+        <v>2.5</v>
+      </c>
+      <c r="J51">
+        <v>1500</v>
+      </c>
+      <c r="K51">
+        <v>3000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>53</v>
+      </c>
+      <c r="M51" t="s">
+        <v>38</v>
+      </c>
+      <c r="N51" t="s">
+        <v>38</v>
+      </c>
+      <c r="O51" t="s">
+        <v>39</v>
+      </c>
+      <c r="P51" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>86</v>
+      </c>
+      <c r="R51">
+        <v>266</v>
+      </c>
+      <c r="S51">
+        <v>266</v>
+      </c>
+      <c r="T51" t="s">
+        <v>42</v>
+      </c>
+      <c r="U51">
+        <v>3</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>2220</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>163</v>
+      </c>
+      <c r="B52" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" t="s">
+        <v>82</v>
+      </c>
+      <c r="D52" t="s">
+        <v>162</v>
+      </c>
+      <c r="E52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" t="s">
+        <v>84</v>
+      </c>
+      <c r="G52" t="s">
+        <v>85</v>
+      </c>
+      <c r="H52" t="s">
+        <v>52</v>
+      </c>
+      <c r="I52">
+        <v>2.5</v>
+      </c>
+      <c r="J52">
+        <v>1500</v>
+      </c>
+      <c r="K52">
+        <v>3000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>53</v>
+      </c>
+      <c r="M52" t="s">
+        <v>38</v>
+      </c>
+      <c r="N52" t="s">
+        <v>38</v>
+      </c>
+      <c r="O52" t="s">
+        <v>39</v>
+      </c>
+      <c r="P52" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>86</v>
+      </c>
+      <c r="R52">
+        <v>354</v>
+      </c>
+      <c r="S52">
+        <v>354</v>
+      </c>
+      <c r="T52" t="s">
+        <v>42</v>
+      </c>
+      <c r="U52">
+        <v>4</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>2220</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" t="s">
+        <v>162</v>
+      </c>
+      <c r="E53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H53" t="s">
+        <v>52</v>
+      </c>
+      <c r="I53">
+        <v>2.5</v>
+      </c>
+      <c r="J53">
+        <v>1500</v>
+      </c>
+      <c r="K53">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>53</v>
+      </c>
+      <c r="M53" t="s">
+        <v>38</v>
+      </c>
+      <c r="N53" t="s">
+        <v>38</v>
+      </c>
+      <c r="O53" t="s">
+        <v>39</v>
+      </c>
+      <c r="P53" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>86</v>
+      </c>
+      <c r="R53">
+        <v>620</v>
+      </c>
+      <c r="S53">
+        <v>620</v>
+      </c>
+      <c r="T53" t="s">
+        <v>42</v>
+      </c>
+      <c r="U53">
+        <v>7</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>2220</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>1376.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>165</v>
+      </c>
+      <c r="B54" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" t="s">
+        <v>166</v>
+      </c>
+      <c r="E54" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" t="s">
+        <v>84</v>
+      </c>
+      <c r="G54" t="s">
+        <v>51</v>
+      </c>
+      <c r="H54" t="s">
+        <v>52</v>
+      </c>
+      <c r="I54">
+        <v>1.5</v>
+      </c>
+      <c r="J54">
+        <v>1500</v>
+      </c>
+      <c r="K54">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>53</v>
+      </c>
+      <c r="M54" t="s">
+        <v>38</v>
+      </c>
+      <c r="N54" t="s">
+        <v>38</v>
+      </c>
+      <c r="O54" t="s">
+        <v>39</v>
+      </c>
+      <c r="P54" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>86</v>
+      </c>
+      <c r="R54">
+        <v>266</v>
+      </c>
+      <c r="S54">
+        <v>266</v>
+      </c>
+      <c r="T54" t="s">
+        <v>42</v>
+      </c>
+      <c r="U54">
+        <v>5</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>3540</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>941.64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" t="s">
+        <v>168</v>
+      </c>
+      <c r="E55" t="s">
+        <v>32</v>
+      </c>
+      <c r="F55" t="s">
+        <v>84</v>
+      </c>
+      <c r="G55" t="s">
+        <v>51</v>
+      </c>
+      <c r="H55" t="s">
+        <v>52</v>
+      </c>
+      <c r="I55">
+        <v>2.5</v>
+      </c>
+      <c r="J55">
+        <v>2000</v>
+      </c>
+      <c r="K55">
+        <v>4000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>53</v>
+      </c>
+      <c r="M55" t="s">
+        <v>38</v>
+      </c>
+      <c r="N55" t="s">
+        <v>38</v>
+      </c>
+      <c r="O55" t="s">
+        <v>39</v>
+      </c>
+      <c r="P55" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>86</v>
+      </c>
+      <c r="R55">
+        <v>315</v>
+      </c>
+      <c r="S55">
+        <v>315</v>
+      </c>
+      <c r="T55" t="s">
+        <v>42</v>
+      </c>
+      <c r="U55">
+        <v>2</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>3560</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>169</v>
+      </c>
+      <c r="B56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" t="s">
+        <v>82</v>
+      </c>
+      <c r="D56" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" t="s">
+        <v>84</v>
+      </c>
+      <c r="G56" t="s">
+        <v>51</v>
+      </c>
+      <c r="H56" t="s">
+        <v>52</v>
+      </c>
+      <c r="I56">
+        <v>2.5</v>
+      </c>
+      <c r="J56">
+        <v>2000</v>
+      </c>
+      <c r="K56">
+        <v>4000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>53</v>
+      </c>
+      <c r="M56" t="s">
+        <v>38</v>
+      </c>
+      <c r="N56" t="s">
+        <v>38</v>
+      </c>
+      <c r="O56" t="s">
+        <v>39</v>
+      </c>
+      <c r="P56" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>86</v>
+      </c>
+      <c r="R56">
+        <v>315</v>
+      </c>
+      <c r="S56">
+        <v>315</v>
+      </c>
+      <c r="T56" t="s">
+        <v>42</v>
+      </c>
+      <c r="U56">
+        <v>2</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>3560</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" t="s">
+        <v>171</v>
+      </c>
+      <c r="E57" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" t="s">
+        <v>84</v>
+      </c>
+      <c r="G57" t="s">
+        <v>85</v>
+      </c>
+      <c r="H57" t="s">
+        <v>52</v>
+      </c>
+      <c r="I57">
+        <v>0.8</v>
+      </c>
+      <c r="J57">
+        <v>1500</v>
+      </c>
+      <c r="K57">
+        <v>3000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>53</v>
+      </c>
+      <c r="M57" t="s">
+        <v>107</v>
+      </c>
+      <c r="N57" t="s">
+        <v>38</v>
+      </c>
+      <c r="O57" t="s">
+        <v>172</v>
+      </c>
+      <c r="P57" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>86</v>
+      </c>
+      <c r="R57">
+        <v>833</v>
+      </c>
+      <c r="S57">
+        <v>833</v>
+      </c>
+      <c r="T57" t="s">
+        <v>42</v>
+      </c>
+      <c r="U57">
+        <v>29</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>2270</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>1890.91</v>
+      </c>
+      <c r="AB57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>173</v>
+      </c>
+      <c r="B58" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" t="s">
+        <v>171</v>
+      </c>
+      <c r="E58" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" t="s">
+        <v>84</v>
+      </c>
+      <c r="G58" t="s">
+        <v>85</v>
+      </c>
+      <c r="H58" t="s">
+        <v>52</v>
+      </c>
+      <c r="I58">
+        <v>0.8</v>
+      </c>
+      <c r="J58">
+        <v>1500</v>
+      </c>
+      <c r="K58">
+        <v>3000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>53</v>
+      </c>
+      <c r="M58" t="s">
+        <v>107</v>
+      </c>
+      <c r="N58" t="s">
+        <v>38</v>
+      </c>
+      <c r="O58" t="s">
+        <v>172</v>
+      </c>
+      <c r="P58" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>86</v>
+      </c>
+      <c r="R58">
+        <v>805</v>
+      </c>
+      <c r="S58">
+        <v>805</v>
+      </c>
+      <c r="T58" t="s">
+        <v>42</v>
+      </c>
+      <c r="U58">
+        <v>28</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>2270</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>1827.35</v>
+      </c>
+      <c r="AB58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59" t="s">
+        <v>175</v>
+      </c>
+      <c r="E59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59" t="s">
+        <v>84</v>
+      </c>
+      <c r="G59" t="s">
+        <v>85</v>
+      </c>
+      <c r="H59" t="s">
+        <v>52</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+      <c r="J59">
+        <v>1000</v>
+      </c>
+      <c r="K59">
+        <v>2000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>53</v>
+      </c>
+      <c r="M59" t="s">
+        <v>38</v>
+      </c>
+      <c r="N59" t="s">
+        <v>38</v>
+      </c>
+      <c r="O59" t="s">
+        <v>39</v>
+      </c>
+      <c r="P59" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>86</v>
+      </c>
+      <c r="R59">
+        <v>1448</v>
+      </c>
+      <c r="S59">
+        <v>1448</v>
+      </c>
+      <c r="T59" t="s">
+        <v>42</v>
+      </c>
+      <c r="U59">
+        <v>1</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2270</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>3286.96</v>
+      </c>
+      <c r="AB59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" t="s">
+        <v>177</v>
+      </c>
+      <c r="E60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60" t="s">
+        <v>84</v>
+      </c>
+      <c r="G60" t="s">
+        <v>92</v>
+      </c>
+      <c r="H60" t="s">
+        <v>52</v>
+      </c>
+      <c r="I60">
+        <v>4</v>
+      </c>
+      <c r="J60">
+        <v>1000</v>
+      </c>
+      <c r="K60">
+        <v>2000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>53</v>
+      </c>
+      <c r="M60" t="s">
+        <v>38</v>
+      </c>
+      <c r="N60" t="s">
+        <v>38</v>
+      </c>
+      <c r="O60" t="s">
+        <v>39</v>
+      </c>
+      <c r="P60" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>86</v>
+      </c>
+      <c r="R60">
+        <v>384</v>
+      </c>
+      <c r="S60">
+        <v>384</v>
+      </c>
+      <c r="T60" t="s">
+        <v>42</v>
+      </c>
+      <c r="U60">
+        <v>6</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>1370</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" t="s">
+        <v>84</v>
+      </c>
+      <c r="G61" t="s">
+        <v>51</v>
+      </c>
+      <c r="H61" t="s">
+        <v>52</v>
+      </c>
+      <c r="I61">
+        <v>6</v>
+      </c>
+      <c r="J61">
+        <v>1500</v>
+      </c>
+      <c r="K61">
+        <v>3000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>53</v>
+      </c>
+      <c r="M61" t="s">
+        <v>38</v>
+      </c>
+      <c r="N61" t="s">
+        <v>38</v>
+      </c>
+      <c r="O61" t="s">
+        <v>39</v>
+      </c>
+      <c r="P61" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>86</v>
+      </c>
+      <c r="R61">
+        <v>850</v>
+      </c>
+      <c r="S61">
+        <v>850</v>
+      </c>
+      <c r="T61" t="s">
+        <v>42</v>
+      </c>
+      <c r="U61">
+        <v>4</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>3540</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" t="s">
+        <v>81</v>
+      </c>
+      <c r="C62" t="s">
+        <v>82</v>
+      </c>
+      <c r="D62" t="s">
+        <v>180</v>
+      </c>
+      <c r="E62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62" t="s">
+        <v>84</v>
+      </c>
+      <c r="G62" t="s">
+        <v>85</v>
+      </c>
+      <c r="H62" t="s">
+        <v>52</v>
+      </c>
+      <c r="I62">
+        <v>0.8</v>
+      </c>
+      <c r="J62">
+        <v>1250</v>
+      </c>
+      <c r="K62">
+        <v>2500</v>
+      </c>
+      <c r="L62" t="s">
+        <v>53</v>
+      </c>
+      <c r="M62" t="s">
+        <v>181</v>
+      </c>
+      <c r="N62" t="s">
+        <v>38</v>
+      </c>
+      <c r="O62" t="s">
+        <v>39</v>
+      </c>
+      <c r="P62" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>86</v>
+      </c>
+      <c r="R62">
+        <v>430</v>
+      </c>
+      <c r="S62">
+        <v>430</v>
+      </c>
+      <c r="T62" t="s">
+        <v>42</v>
+      </c>
+      <c r="U62">
+        <v>21</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>2270</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>976.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" t="s">
+        <v>183</v>
+      </c>
+      <c r="E63" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" t="s">
+        <v>84</v>
+      </c>
+      <c r="G63" t="s">
+        <v>85</v>
+      </c>
+      <c r="H63" t="s">
+        <v>52</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>1000</v>
+      </c>
+      <c r="K63">
+        <v>2000</v>
+      </c>
+      <c r="L63" t="s">
+        <v>53</v>
+      </c>
+      <c r="M63" t="s">
+        <v>38</v>
+      </c>
+      <c r="N63" t="s">
+        <v>38</v>
+      </c>
+      <c r="O63" t="s">
+        <v>39</v>
+      </c>
+      <c r="P63" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>86</v>
+      </c>
+      <c r="R63">
+        <v>283</v>
+      </c>
+      <c r="S63">
+        <v>283</v>
+      </c>
+      <c r="T63" t="s">
+        <v>42</v>
+      </c>
+      <c r="U63">
+        <v>9</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>2220</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" t="s">
+        <v>82</v>
+      </c>
+      <c r="D64" t="s">
+        <v>117</v>
+      </c>
+      <c r="E64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64" t="s">
+        <v>84</v>
+      </c>
+      <c r="G64" t="s">
+        <v>92</v>
+      </c>
+      <c r="H64" t="s">
+        <v>52</v>
+      </c>
+      <c r="I64">
+        <v>3</v>
+      </c>
+      <c r="J64">
+        <v>1500</v>
+      </c>
+      <c r="K64">
+        <v>3000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>53</v>
+      </c>
+      <c r="M64" t="s">
+        <v>38</v>
+      </c>
+      <c r="N64" t="s">
+        <v>38</v>
+      </c>
+      <c r="O64" t="s">
+        <v>39</v>
+      </c>
+      <c r="P64" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>86</v>
+      </c>
+      <c r="R64">
+        <v>637</v>
+      </c>
+      <c r="S64">
+        <v>637</v>
+      </c>
+      <c r="T64" t="s">
+        <v>42</v>
+      </c>
+      <c r="U64">
+        <v>6</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>1370</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>872.69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C65" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" t="s">
+        <v>186</v>
+      </c>
+      <c r="E65" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65" t="s">
+        <v>84</v>
+      </c>
+      <c r="G65" t="s">
+        <v>85</v>
+      </c>
+      <c r="H65" t="s">
+        <v>52</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>1000</v>
+      </c>
+      <c r="K65">
+        <v>2000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>53</v>
+      </c>
+      <c r="M65" t="s">
+        <v>107</v>
+      </c>
+      <c r="N65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O65" t="s">
+        <v>39</v>
+      </c>
+      <c r="P65" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>86</v>
+      </c>
+      <c r="R65">
+        <v>1482</v>
+      </c>
+      <c r="S65">
+        <v>1482</v>
+      </c>
+      <c r="T65" t="s">
+        <v>42</v>
+      </c>
+      <c r="U65">
+        <v>1</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>2220</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>3290.04</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>187</v>
+      </c>
+      <c r="B66" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" t="s">
+        <v>82</v>
+      </c>
+      <c r="D66" t="s">
+        <v>188</v>
+      </c>
+      <c r="E66" t="s">
+        <v>32</v>
+      </c>
+      <c r="F66" t="s">
+        <v>84</v>
+      </c>
+      <c r="G66" t="s">
+        <v>101</v>
+      </c>
+      <c r="H66" t="s">
+        <v>52</v>
+      </c>
+      <c r="I66">
+        <v>4</v>
+      </c>
+      <c r="J66">
+        <v>1500</v>
+      </c>
+      <c r="K66">
+        <v>3000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>189</v>
+      </c>
+      <c r="M66" t="s">
+        <v>38</v>
+      </c>
+      <c r="N66" t="s">
+        <v>38</v>
+      </c>
+      <c r="O66" t="s">
+        <v>39</v>
+      </c>
+      <c r="P66" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>86</v>
+      </c>
+      <c r="R66">
+        <v>1133</v>
+      </c>
+      <c r="S66">
+        <v>1133</v>
+      </c>
+      <c r="T66" t="s">
+        <v>42</v>
+      </c>
+      <c r="U66">
+        <v>8</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>3540</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>4010.82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" t="s">
+        <v>191</v>
+      </c>
+      <c r="E67" t="s">
+        <v>32</v>
+      </c>
+      <c r="F67" t="s">
+        <v>84</v>
+      </c>
+      <c r="G67" t="s">
+        <v>85</v>
+      </c>
+      <c r="H67" t="s">
+        <v>52</v>
+      </c>
+      <c r="I67">
+        <v>5</v>
+      </c>
+      <c r="J67">
+        <v>2000</v>
+      </c>
+      <c r="K67">
+        <v>4000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>53</v>
+      </c>
+      <c r="M67" t="s">
+        <v>38</v>
+      </c>
+      <c r="N67" t="s">
+        <v>38</v>
+      </c>
+      <c r="O67" t="s">
+        <v>39</v>
+      </c>
+      <c r="P67" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>86</v>
+      </c>
+      <c r="R67">
+        <v>1259</v>
+      </c>
+      <c r="S67">
+        <v>1259</v>
+      </c>
+      <c r="T67" t="s">
+        <v>42</v>
+      </c>
+      <c r="U67">
+        <v>4</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>2290</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>2883.11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>192</v>
+      </c>
+      <c r="B68" t="s">
+        <v>95</v>
+      </c>
+      <c r="C68" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" t="s">
+        <v>193</v>
+      </c>
+      <c r="E68" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68" t="s">
+        <v>84</v>
+      </c>
+      <c r="G68" t="s">
+        <v>85</v>
+      </c>
+      <c r="H68" t="s">
+        <v>52</v>
+      </c>
+      <c r="I68">
+        <v>4</v>
+      </c>
+      <c r="J68">
+        <v>2000</v>
+      </c>
+      <c r="K68">
+        <v>4000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>53</v>
+      </c>
+      <c r="M68" t="s">
+        <v>38</v>
+      </c>
+      <c r="N68" t="s">
+        <v>38</v>
+      </c>
+      <c r="O68" t="s">
+        <v>39</v>
+      </c>
+      <c r="P68" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>86</v>
+      </c>
+      <c r="R68">
+        <v>1007</v>
+      </c>
+      <c r="S68">
+        <v>1007</v>
+      </c>
+      <c r="T68" t="s">
+        <v>42</v>
+      </c>
+      <c r="U68">
+        <v>4</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>2290</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>2306.03</v>
+      </c>
+      <c r="AB68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>194</v>
+      </c>
+      <c r="B69" t="s">
+        <v>95</v>
+      </c>
+      <c r="C69" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" t="s">
+        <v>32</v>
+      </c>
+      <c r="F69" t="s">
+        <v>84</v>
+      </c>
+      <c r="G69" t="s">
+        <v>85</v>
+      </c>
+      <c r="H69" t="s">
+        <v>52</v>
+      </c>
+      <c r="I69">
+        <v>6</v>
+      </c>
+      <c r="J69">
+        <v>1500</v>
+      </c>
+      <c r="K69">
+        <v>3000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>53</v>
+      </c>
+      <c r="M69" t="s">
+        <v>38</v>
+      </c>
+      <c r="N69" t="s">
+        <v>38</v>
+      </c>
+      <c r="O69" t="s">
+        <v>172</v>
+      </c>
+      <c r="P69" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>86</v>
+      </c>
+      <c r="R69">
+        <v>1487</v>
+      </c>
+      <c r="S69">
+        <v>1487</v>
+      </c>
+      <c r="T69" t="s">
+        <v>42</v>
+      </c>
+      <c r="U69">
+        <v>7</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>2270</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>3375.49</v>
+      </c>
+      <c r="AB69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>196</v>
+      </c>
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70" t="s">
+        <v>197</v>
+      </c>
+      <c r="E70" t="s">
+        <v>32</v>
+      </c>
+      <c r="F70" t="s">
+        <v>84</v>
+      </c>
+      <c r="G70" t="s">
+        <v>85</v>
+      </c>
+      <c r="H70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I70">
+        <v>8</v>
+      </c>
+      <c r="J70">
+        <v>2000</v>
+      </c>
+      <c r="K70">
+        <v>6000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>69</v>
+      </c>
+      <c r="M70" t="s">
+        <v>38</v>
+      </c>
+      <c r="N70" t="s">
+        <v>38</v>
+      </c>
+      <c r="O70" t="s">
+        <v>39</v>
+      </c>
+      <c r="P70" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>86</v>
+      </c>
+      <c r="R70">
+        <v>755</v>
+      </c>
+      <c r="S70">
+        <v>755</v>
+      </c>
+      <c r="T70" t="s">
+        <v>42</v>
+      </c>
+      <c r="U70">
+        <v>1</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>2040</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>1540.2</v>
+      </c>
+      <c r="AB70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>198</v>
+      </c>
+      <c r="B71" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" t="s">
+        <v>82</v>
+      </c>
+      <c r="D71" t="s">
+        <v>199</v>
+      </c>
+      <c r="E71" t="s">
+        <v>32</v>
+      </c>
+      <c r="F71" t="s">
+        <v>84</v>
+      </c>
+      <c r="G71" t="s">
+        <v>85</v>
+      </c>
+      <c r="H71" t="s">
+        <v>52</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>1250</v>
+      </c>
+      <c r="K71">
+        <v>2500</v>
+      </c>
+      <c r="L71" t="s">
+        <v>53</v>
+      </c>
+      <c r="M71" t="s">
+        <v>200</v>
+      </c>
+      <c r="N71" t="s">
+        <v>38</v>
+      </c>
+      <c r="O71" t="s">
+        <v>201</v>
+      </c>
+      <c r="P71" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>86</v>
+      </c>
+      <c r="R71">
+        <v>1019</v>
+      </c>
+      <c r="S71">
+        <v>1019</v>
+      </c>
+      <c r="T71" t="s">
+        <v>42</v>
+      </c>
+      <c r="U71">
+        <v>41</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>2220</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>2262.18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>202</v>
+      </c>
+      <c r="B72" t="s">
+        <v>95</v>
+      </c>
+      <c r="C72" t="s">
+        <v>82</v>
+      </c>
+      <c r="D72" t="s">
+        <v>203</v>
+      </c>
+      <c r="E72" t="s">
+        <v>32</v>
+      </c>
+      <c r="F72" t="s">
+        <v>84</v>
+      </c>
+      <c r="G72" t="s">
+        <v>85</v>
+      </c>
+      <c r="H72" t="s">
+        <v>52</v>
+      </c>
+      <c r="I72">
+        <v>8</v>
+      </c>
+      <c r="J72">
+        <v>1000</v>
+      </c>
+      <c r="K72">
+        <v>2000</v>
+      </c>
+      <c r="L72" t="s">
+        <v>69</v>
+      </c>
+      <c r="M72" t="s">
+        <v>38</v>
+      </c>
+      <c r="N72" t="s">
+        <v>38</v>
+      </c>
+      <c r="O72" t="s">
+        <v>39</v>
+      </c>
+      <c r="P72" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>86</v>
+      </c>
+      <c r="R72">
+        <v>504</v>
+      </c>
+      <c r="S72">
+        <v>504</v>
+      </c>
+      <c r="T72" t="s">
+        <v>42</v>
+      </c>
+      <c r="U72">
+        <v>4</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>2020</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>1018.08</v>
+      </c>
+      <c r="AB72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>204</v>
+      </c>
+      <c r="B73" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" t="s">
+        <v>205</v>
+      </c>
+      <c r="E73" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" t="s">
+        <v>84</v>
+      </c>
+      <c r="G73" t="s">
+        <v>85</v>
+      </c>
+      <c r="H73" t="s">
+        <v>52</v>
+      </c>
+      <c r="I73">
+        <v>12</v>
+      </c>
+      <c r="J73">
+        <v>1000</v>
+      </c>
+      <c r="K73">
+        <v>2000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>69</v>
+      </c>
+      <c r="M73" t="s">
+        <v>38</v>
+      </c>
+      <c r="N73" t="s">
+        <v>38</v>
+      </c>
+      <c r="O73" t="s">
+        <v>39</v>
+      </c>
+      <c r="P73" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>86</v>
+      </c>
+      <c r="R73">
+        <v>1322</v>
+      </c>
+      <c r="S73">
+        <v>1322</v>
+      </c>
+      <c r="T73" t="s">
+        <v>42</v>
+      </c>
+      <c r="U73">
+        <v>7</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>2070</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>2736.54</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>206</v>
+      </c>
+      <c r="B74" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" t="s">
+        <v>82</v>
+      </c>
+      <c r="D74" t="s">
+        <v>109</v>
+      </c>
+      <c r="E74" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" t="s">
+        <v>84</v>
+      </c>
+      <c r="G74" t="s">
+        <v>51</v>
+      </c>
+      <c r="H74" t="s">
+        <v>52</v>
+      </c>
+      <c r="I74">
+        <v>2.5</v>
+      </c>
+      <c r="J74">
+        <v>1500</v>
+      </c>
+      <c r="K74">
+        <v>3000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>53</v>
+      </c>
+      <c r="M74" t="s">
+        <v>38</v>
+      </c>
+      <c r="N74" t="s">
+        <v>38</v>
+      </c>
+      <c r="O74" t="s">
+        <v>39</v>
+      </c>
+      <c r="P74" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>86</v>
+      </c>
+      <c r="R74">
+        <v>534</v>
+      </c>
+      <c r="S74">
+        <v>534</v>
+      </c>
+      <c r="T74" t="s">
+        <v>42</v>
+      </c>
+      <c r="U74">
+        <v>6</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>3540</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>1890.36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>207</v>
+      </c>
+      <c r="B75" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E75" t="s">
+        <v>32</v>
+      </c>
+      <c r="F75" t="s">
+        <v>84</v>
+      </c>
+      <c r="G75" t="s">
+        <v>85</v>
+      </c>
+      <c r="H75" t="s">
+        <v>52</v>
+      </c>
+      <c r="I75">
+        <v>0.8</v>
+      </c>
+      <c r="J75">
+        <v>1250</v>
+      </c>
+      <c r="K75">
+        <v>2500</v>
+      </c>
+      <c r="L75" t="s">
+        <v>53</v>
+      </c>
+      <c r="M75" t="s">
+        <v>38</v>
+      </c>
+      <c r="N75" t="s">
+        <v>38</v>
+      </c>
+      <c r="O75" t="s">
+        <v>39</v>
+      </c>
+      <c r="P75" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>86</v>
+      </c>
+      <c r="R75">
+        <v>2033</v>
+      </c>
+      <c r="S75">
+        <v>2033</v>
+      </c>
+      <c r="T75" t="s">
+        <v>42</v>
+      </c>
+      <c r="U75">
+        <v>101</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>2370</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>4818.21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>209</v>
+      </c>
+      <c r="B76" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" t="s">
+        <v>82</v>
+      </c>
+      <c r="D76" t="s">
+        <v>210</v>
+      </c>
+      <c r="E76" t="s">
+        <v>32</v>
+      </c>
+      <c r="F76" t="s">
+        <v>84</v>
+      </c>
+      <c r="G76" t="s">
+        <v>51</v>
+      </c>
+      <c r="H76" t="s">
+        <v>52</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+      <c r="J76">
+        <v>1000</v>
+      </c>
+      <c r="K76">
+        <v>2000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>53</v>
+      </c>
+      <c r="M76" t="s">
+        <v>107</v>
+      </c>
+      <c r="N76" t="s">
+        <v>38</v>
+      </c>
+      <c r="O76" t="s">
+        <v>39</v>
+      </c>
+      <c r="P76" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>86</v>
+      </c>
+      <c r="R76">
+        <v>1046</v>
+      </c>
+      <c r="S76">
+        <v>1046</v>
+      </c>
+      <c r="T76" t="s">
+        <v>42</v>
+      </c>
+      <c r="U76">
+        <v>33</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>3540</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>3702.84</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>211</v>
+      </c>
+      <c r="B77" t="s">
+        <v>88</v>
+      </c>
+      <c r="C77" t="s">
+        <v>82</v>
+      </c>
+      <c r="D77" t="s">
+        <v>212</v>
+      </c>
+      <c r="E77" t="s">
+        <v>32</v>
+      </c>
+      <c r="F77" t="s">
+        <v>84</v>
+      </c>
+      <c r="G77" t="s">
+        <v>85</v>
+      </c>
+      <c r="H77" t="s">
+        <v>52</v>
+      </c>
+      <c r="I77">
+        <v>4</v>
+      </c>
+      <c r="J77">
+        <v>1500</v>
+      </c>
+      <c r="K77">
+        <v>3000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>53</v>
+      </c>
+      <c r="M77" t="s">
+        <v>38</v>
+      </c>
+      <c r="N77" t="s">
+        <v>38</v>
+      </c>
+      <c r="O77" t="s">
+        <v>39</v>
+      </c>
+      <c r="P77" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>86</v>
+      </c>
+      <c r="R77">
+        <v>142</v>
+      </c>
+      <c r="S77">
+        <v>142</v>
+      </c>
+      <c r="T77" t="s">
+        <v>42</v>
+      </c>
+      <c r="U77">
+        <v>1</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>2170</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>213</v>
+      </c>
+      <c r="B78" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" t="s">
+        <v>82</v>
+      </c>
+      <c r="D78" t="s">
+        <v>214</v>
+      </c>
+      <c r="E78" t="s">
+        <v>32</v>
+      </c>
+      <c r="F78" t="s">
+        <v>84</v>
+      </c>
+      <c r="G78" t="s">
+        <v>85</v>
+      </c>
+      <c r="H78" t="s">
+        <v>52</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78">
+        <v>2000</v>
+      </c>
+      <c r="K78">
+        <v>4000</v>
+      </c>
+      <c r="L78" t="s">
+        <v>53</v>
+      </c>
+      <c r="M78" t="s">
+        <v>38</v>
+      </c>
+      <c r="N78" t="s">
+        <v>38</v>
+      </c>
+      <c r="O78" t="s">
+        <v>39</v>
+      </c>
+      <c r="P78" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>86</v>
+      </c>
+      <c r="R78">
+        <v>126</v>
+      </c>
+      <c r="S78">
+        <v>126</v>
+      </c>
+      <c r="T78" t="s">
+        <v>42</v>
+      </c>
+      <c r="U78">
+        <v>1</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>2190</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>215</v>
+      </c>
+      <c r="B79" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79" t="s">
+        <v>216</v>
+      </c>
+      <c r="E79" t="s">
+        <v>32</v>
+      </c>
+      <c r="F79" t="s">
+        <v>84</v>
+      </c>
+      <c r="G79" t="s">
+        <v>85</v>
+      </c>
+      <c r="H79" t="s">
+        <v>52</v>
+      </c>
+      <c r="I79">
+        <v>0.8</v>
+      </c>
+      <c r="J79">
+        <v>1000</v>
+      </c>
+      <c r="K79">
+        <v>2000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>53</v>
+      </c>
+      <c r="M79" t="s">
+        <v>107</v>
+      </c>
+      <c r="N79" t="s">
+        <v>38</v>
+      </c>
+      <c r="O79" t="s">
+        <v>39</v>
+      </c>
+      <c r="P79" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>86</v>
+      </c>
+      <c r="R79">
+        <v>1216</v>
+      </c>
+      <c r="S79">
+        <v>1216</v>
+      </c>
+      <c r="T79" t="s">
+        <v>42</v>
+      </c>
+      <c r="U79">
+        <v>96</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>2320</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>2821.12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>217</v>
+      </c>
+      <c r="B80" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" t="s">
+        <v>32</v>
+      </c>
+      <c r="F80" t="s">
+        <v>84</v>
+      </c>
+      <c r="G80" t="s">
+        <v>85</v>
+      </c>
+      <c r="H80" t="s">
+        <v>52</v>
+      </c>
+      <c r="I80">
+        <v>0.8</v>
+      </c>
+      <c r="J80">
+        <v>1250</v>
+      </c>
+      <c r="K80">
+        <v>2500</v>
+      </c>
+      <c r="L80" t="s">
+        <v>53</v>
+      </c>
+      <c r="M80" t="s">
+        <v>38</v>
+      </c>
+      <c r="N80" t="s">
+        <v>38</v>
+      </c>
+      <c r="O80" t="s">
+        <v>39</v>
+      </c>
+      <c r="P80" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>86</v>
+      </c>
+      <c r="R80">
+        <v>334</v>
+      </c>
+      <c r="S80">
+        <v>334</v>
+      </c>
+      <c r="T80" t="s">
+        <v>42</v>
+      </c>
+      <c r="U80">
+        <v>17</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>2320</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>218</v>
+      </c>
+      <c r="B81" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" t="s">
+        <v>82</v>
+      </c>
+      <c r="D81" t="s">
+        <v>208</v>
+      </c>
+      <c r="E81" t="s">
+        <v>32</v>
+      </c>
+      <c r="F81" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81" t="s">
+        <v>85</v>
+      </c>
+      <c r="H81" t="s">
+        <v>52</v>
+      </c>
+      <c r="I81">
+        <v>0.8</v>
+      </c>
+      <c r="J81">
+        <v>1250</v>
+      </c>
+      <c r="K81">
+        <v>2500</v>
+      </c>
+      <c r="L81" t="s">
+        <v>53</v>
+      </c>
+      <c r="M81" t="s">
+        <v>38</v>
+      </c>
+      <c r="N81" t="s">
+        <v>38</v>
+      </c>
+      <c r="O81" t="s">
+        <v>39</v>
+      </c>
+      <c r="P81" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>86</v>
+      </c>
+      <c r="R81">
+        <v>334</v>
+      </c>
+      <c r="S81">
+        <v>334</v>
+      </c>
+      <c r="T81" t="s">
+        <v>42</v>
+      </c>
+      <c r="U81">
+        <v>17</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>2320</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>219</v>
+      </c>
+      <c r="B82" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" t="s">
+        <v>208</v>
+      </c>
+      <c r="E82" t="s">
+        <v>32</v>
+      </c>
+      <c r="F82" t="s">
+        <v>84</v>
+      </c>
+      <c r="G82" t="s">
+        <v>85</v>
+      </c>
+      <c r="H82" t="s">
+        <v>52</v>
+      </c>
+      <c r="I82">
+        <v>0.8</v>
+      </c>
+      <c r="J82">
+        <v>1250</v>
+      </c>
+      <c r="K82">
+        <v>2500</v>
+      </c>
+      <c r="L82" t="s">
+        <v>53</v>
+      </c>
+      <c r="M82" t="s">
+        <v>38</v>
+      </c>
+      <c r="N82" t="s">
+        <v>38</v>
+      </c>
+      <c r="O82" t="s">
+        <v>39</v>
+      </c>
+      <c r="P82" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>86</v>
+      </c>
+      <c r="R82">
+        <v>551</v>
+      </c>
+      <c r="S82">
+        <v>551</v>
+      </c>
+      <c r="T82" t="s">
+        <v>42</v>
+      </c>
+      <c r="U82">
+        <v>28</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>2320</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>1278.32</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>220</v>
+      </c>
+      <c r="B83" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" t="s">
+        <v>221</v>
+      </c>
+      <c r="E83" t="s">
+        <v>32</v>
+      </c>
+      <c r="F83" t="s">
+        <v>84</v>
+      </c>
+      <c r="G83" t="s">
+        <v>51</v>
+      </c>
+      <c r="H83" t="s">
+        <v>52</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="J83">
+        <v>1250</v>
+      </c>
+      <c r="K83">
+        <v>2500</v>
+      </c>
+      <c r="L83" t="s">
+        <v>53</v>
+      </c>
+      <c r="M83" t="s">
+        <v>107</v>
+      </c>
+      <c r="N83" t="s">
+        <v>38</v>
+      </c>
+      <c r="O83" t="s">
+        <v>39</v>
+      </c>
+      <c r="P83" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>86</v>
+      </c>
+      <c r="R83">
+        <v>612</v>
+      </c>
+      <c r="S83">
+        <v>612</v>
+      </c>
+      <c r="T83" t="s">
+        <v>42</v>
+      </c>
+      <c r="U83">
+        <v>12</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>3490</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>2135.88</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>222</v>
+      </c>
+      <c r="B84" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" t="s">
+        <v>82</v>
+      </c>
+      <c r="D84" t="s">
+        <v>186</v>
+      </c>
+      <c r="E84" t="s">
+        <v>32</v>
+      </c>
+      <c r="F84" t="s">
+        <v>84</v>
+      </c>
+      <c r="G84" t="s">
+        <v>85</v>
+      </c>
+      <c r="H84" t="s">
+        <v>52</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>1000</v>
+      </c>
+      <c r="K84">
+        <v>2000</v>
+      </c>
+      <c r="L84" t="s">
+        <v>53</v>
+      </c>
+      <c r="M84" t="s">
+        <v>107</v>
+      </c>
+      <c r="N84" t="s">
+        <v>38</v>
+      </c>
+      <c r="O84" t="s">
+        <v>39</v>
+      </c>
+      <c r="P84" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>86</v>
+      </c>
+      <c r="R84">
+        <v>752</v>
+      </c>
+      <c r="S84">
+        <v>752</v>
+      </c>
+      <c r="T84" t="s">
+        <v>42</v>
+      </c>
+      <c r="U84">
+        <v>48</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>2170</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>1631.84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>223</v>
+      </c>
+      <c r="B85" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" t="s">
+        <v>82</v>
+      </c>
+      <c r="D85" t="s">
+        <v>224</v>
+      </c>
+      <c r="E85" t="s">
+        <v>32</v>
+      </c>
+      <c r="F85" t="s">
+        <v>84</v>
+      </c>
+      <c r="G85" t="s">
+        <v>101</v>
+      </c>
+      <c r="H85" t="s">
+        <v>52</v>
+      </c>
+      <c r="I85">
+        <v>3</v>
+      </c>
+      <c r="J85">
+        <v>1500</v>
+      </c>
+      <c r="K85">
+        <v>3000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>53</v>
+      </c>
+      <c r="M85" t="s">
+        <v>38</v>
+      </c>
+      <c r="N85" t="s">
+        <v>38</v>
+      </c>
+      <c r="O85" t="s">
+        <v>39</v>
+      </c>
+      <c r="P85" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>86</v>
+      </c>
+      <c r="R85">
+        <v>106</v>
+      </c>
+      <c r="S85">
+        <v>106</v>
+      </c>
+      <c r="T85" t="s">
+        <v>42</v>
+      </c>
+      <c r="U85">
+        <v>1</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>3640</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>385.84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>225</v>
+      </c>
+      <c r="B86" t="s">
+        <v>81</v>
+      </c>
+      <c r="C86" t="s">
+        <v>82</v>
+      </c>
+      <c r="D86" t="s">
+        <v>166</v>
+      </c>
+      <c r="E86" t="s">
+        <v>32</v>
+      </c>
+      <c r="F86" t="s">
+        <v>84</v>
+      </c>
+      <c r="G86" t="s">
+        <v>51</v>
+      </c>
+      <c r="H86" t="s">
+        <v>52</v>
+      </c>
+      <c r="I86">
+        <v>1.5</v>
+      </c>
+      <c r="J86">
+        <v>1500</v>
+      </c>
+      <c r="K86">
+        <v>3000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>53</v>
+      </c>
+      <c r="M86" t="s">
+        <v>38</v>
+      </c>
+      <c r="N86" t="s">
+        <v>38</v>
+      </c>
+      <c r="O86" t="s">
+        <v>39</v>
+      </c>
+      <c r="P86" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>86</v>
+      </c>
+      <c r="R86">
+        <v>330</v>
+      </c>
+      <c r="S86">
+        <v>330</v>
+      </c>
+      <c r="T86" t="s">
+        <v>42</v>
+      </c>
+      <c r="U86">
+        <v>6</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>3540</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>226</v>
+      </c>
+      <c r="B87" t="s">
+        <v>88</v>
+      </c>
+      <c r="C87" t="s">
+        <v>82</v>
+      </c>
+      <c r="D87" t="s">
+        <v>227</v>
+      </c>
+      <c r="E87" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" t="s">
+        <v>84</v>
+      </c>
+      <c r="G87" t="s">
+        <v>85</v>
+      </c>
+      <c r="H87" t="s">
+        <v>52</v>
+      </c>
+      <c r="I87">
+        <v>3</v>
+      </c>
+      <c r="J87">
+        <v>1000</v>
+      </c>
+      <c r="K87">
+        <v>2000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>53</v>
+      </c>
+      <c r="M87" t="s">
+        <v>38</v>
+      </c>
+      <c r="N87" t="s">
+        <v>38</v>
+      </c>
+      <c r="O87" t="s">
+        <v>39</v>
+      </c>
+      <c r="P87" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>86</v>
+      </c>
+      <c r="R87">
+        <v>1464</v>
+      </c>
+      <c r="S87">
+        <v>1464</v>
+      </c>
+      <c r="T87" t="s">
+        <v>42</v>
+      </c>
+      <c r="U87">
+        <v>31</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>2270</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>3323.28</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>228</v>
+      </c>
+      <c r="B88" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" t="s">
+        <v>82</v>
+      </c>
+      <c r="D88" t="s">
+        <v>227</v>
+      </c>
+      <c r="E88" t="s">
+        <v>32</v>
+      </c>
+      <c r="F88" t="s">
+        <v>84</v>
+      </c>
+      <c r="G88" t="s">
+        <v>85</v>
+      </c>
+      <c r="H88" t="s">
+        <v>52</v>
+      </c>
+      <c r="I88">
+        <v>3</v>
+      </c>
+      <c r="J88">
+        <v>1000</v>
+      </c>
+      <c r="K88">
+        <v>2000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>53</v>
+      </c>
+      <c r="M88" t="s">
+        <v>38</v>
+      </c>
+      <c r="N88" t="s">
+        <v>38</v>
+      </c>
+      <c r="O88" t="s">
+        <v>39</v>
+      </c>
+      <c r="P88" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>86</v>
+      </c>
+      <c r="R88">
+        <v>94</v>
+      </c>
+      <c r="S88">
+        <v>94</v>
+      </c>
+      <c r="T88" t="s">
+        <v>42</v>
+      </c>
+      <c r="U88">
+        <v>2</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>2170</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>229</v>
+      </c>
+      <c r="B89" t="s">
+        <v>81</v>
+      </c>
+      <c r="C89" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" t="s">
+        <v>230</v>
+      </c>
+      <c r="E89" t="s">
+        <v>32</v>
+      </c>
+      <c r="F89" t="s">
+        <v>33</v>
+      </c>
+      <c r="G89" t="s">
+        <v>231</v>
+      </c>
+      <c r="H89" t="s">
+        <v>52</v>
+      </c>
+      <c r="I89">
+        <v>1.2</v>
+      </c>
+      <c r="J89">
+        <v>1250</v>
+      </c>
+      <c r="L89" t="s">
+        <v>53</v>
+      </c>
+      <c r="M89" t="s">
+        <v>38</v>
+      </c>
+      <c r="N89" t="s">
+        <v>38</v>
+      </c>
+      <c r="O89" t="s">
+        <v>39</v>
+      </c>
+      <c r="P89" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>86</v>
+      </c>
+      <c r="R89">
+        <v>1420</v>
+      </c>
+      <c r="S89">
+        <v>1420</v>
+      </c>
+      <c r="T89" t="s">
+        <v>42</v>
+      </c>
+      <c r="U89">
+        <v>1</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>1420</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>2016.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>232</v>
+      </c>
+      <c r="B90" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" t="s">
+        <v>82</v>
+      </c>
+      <c r="D90" t="s">
+        <v>233</v>
+      </c>
+      <c r="E90" t="s">
+        <v>32</v>
+      </c>
+      <c r="F90" t="s">
+        <v>84</v>
+      </c>
+      <c r="G90" t="s">
+        <v>92</v>
+      </c>
+      <c r="H90" t="s">
+        <v>52</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>1500</v>
+      </c>
+      <c r="K90">
+        <v>3000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>36</v>
+      </c>
+      <c r="M90" t="s">
+        <v>38</v>
+      </c>
+      <c r="N90" t="s">
+        <v>38</v>
+      </c>
+      <c r="O90" t="s">
+        <v>39</v>
+      </c>
+      <c r="P90" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>86</v>
+      </c>
+      <c r="R90">
+        <v>414</v>
+      </c>
+      <c r="S90">
+        <v>414</v>
+      </c>
+      <c r="T90" t="s">
+        <v>42</v>
+      </c>
+      <c r="U90">
+        <v>12</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>1370</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>567.18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>234</v>
+      </c>
+      <c r="B91" t="s">
+        <v>81</v>
+      </c>
+      <c r="C91" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" t="s">
+        <v>235</v>
+      </c>
+      <c r="E91" t="s">
+        <v>32</v>
+      </c>
+      <c r="F91" t="s">
+        <v>84</v>
+      </c>
+      <c r="G91" t="s">
+        <v>92</v>
+      </c>
+      <c r="H91" t="s">
+        <v>52</v>
+      </c>
+      <c r="I91">
+        <v>0.8</v>
+      </c>
+      <c r="J91">
+        <v>1500</v>
+      </c>
+      <c r="K91">
+        <v>3000</v>
+      </c>
+      <c r="L91" t="s">
+        <v>36</v>
+      </c>
+      <c r="M91" t="s">
+        <v>38</v>
+      </c>
+      <c r="N91" t="s">
+        <v>38</v>
+      </c>
+      <c r="O91" t="s">
+        <v>236</v>
+      </c>
+      <c r="P91" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>86</v>
+      </c>
+      <c r="R91">
+        <v>2584</v>
+      </c>
+      <c r="S91">
+        <v>2584</v>
+      </c>
+      <c r="T91" t="s">
+        <v>42</v>
+      </c>
+      <c r="U91">
+        <v>94</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>1520</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>3927.68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>237</v>
+      </c>
+      <c r="B92" t="s">
+        <v>81</v>
+      </c>
+      <c r="C92" t="s">
+        <v>82</v>
+      </c>
+      <c r="D92" t="s">
+        <v>238</v>
+      </c>
+      <c r="E92" t="s">
+        <v>32</v>
+      </c>
+      <c r="F92" t="s">
+        <v>84</v>
+      </c>
+      <c r="G92" t="s">
+        <v>92</v>
+      </c>
+      <c r="H92" t="s">
+        <v>52</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>1250</v>
+      </c>
+      <c r="K92">
+        <v>2500</v>
+      </c>
+      <c r="L92" t="s">
+        <v>36</v>
+      </c>
+      <c r="M92" t="s">
+        <v>38</v>
+      </c>
+      <c r="N92" t="s">
+        <v>38</v>
+      </c>
+      <c r="O92" t="s">
+        <v>39</v>
+      </c>
+      <c r="P92" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>86</v>
+      </c>
+      <c r="R92">
+        <v>668</v>
+      </c>
+      <c r="S92">
+        <v>668</v>
+      </c>
+      <c r="T92" t="s">
+        <v>42</v>
+      </c>
+      <c r="U92">
+        <v>1</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>1370</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>915.16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>239</v>
+      </c>
+      <c r="B93" t="s">
+        <v>81</v>
+      </c>
+      <c r="C93" t="s">
+        <v>82</v>
+      </c>
+      <c r="D93" t="s">
+        <v>123</v>
+      </c>
+      <c r="E93" t="s">
+        <v>32</v>
+      </c>
+      <c r="F93" t="s">
+        <v>84</v>
+      </c>
+      <c r="G93" t="s">
+        <v>85</v>
+      </c>
+      <c r="H93" t="s">
+        <v>52</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+      <c r="J93">
+        <v>1250</v>
+      </c>
+      <c r="K93">
+        <v>2500</v>
+      </c>
+      <c r="L93" t="s">
+        <v>53</v>
+      </c>
+      <c r="M93" t="s">
+        <v>38</v>
+      </c>
+      <c r="N93" t="s">
+        <v>38</v>
+      </c>
+      <c r="O93" t="s">
+        <v>39</v>
+      </c>
+      <c r="P93" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>86</v>
+      </c>
+      <c r="R93">
+        <v>358</v>
+      </c>
+      <c r="S93">
+        <v>358</v>
+      </c>
+      <c r="T93" t="s">
+        <v>42</v>
+      </c>
+      <c r="U93">
+        <v>7</v>
+      </c>
+      <c r="V93" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93">
+        <v>2220</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA93">
+        <v>794.76</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>240</v>
+      </c>
+      <c r="B94" t="s">
+        <v>88</v>
+      </c>
+      <c r="C94" t="s">
+        <v>82</v>
+      </c>
+      <c r="D94" t="s">
+        <v>241</v>
+      </c>
+      <c r="E94" t="s">
+        <v>32</v>
+      </c>
+      <c r="F94" t="s">
+        <v>84</v>
+      </c>
+      <c r="G94" t="s">
+        <v>51</v>
+      </c>
+      <c r="H94" t="s">
+        <v>52</v>
+      </c>
+      <c r="I94">
+        <v>3</v>
+      </c>
+      <c r="J94">
+        <v>2000</v>
+      </c>
+      <c r="K94">
+        <v>4000</v>
+      </c>
+      <c r="L94" t="s">
+        <v>53</v>
+      </c>
+      <c r="M94" t="s">
+        <v>38</v>
+      </c>
+      <c r="N94" t="s">
+        <v>38</v>
+      </c>
+      <c r="O94" t="s">
+        <v>39</v>
+      </c>
+      <c r="P94" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>86</v>
+      </c>
+      <c r="R94">
+        <v>189</v>
+      </c>
+      <c r="S94">
+        <v>189</v>
+      </c>
+      <c r="T94" t="s">
+        <v>42</v>
+      </c>
+      <c r="U94">
+        <v>1</v>
+      </c>
+      <c r="V94" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94">
+        <v>3510</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA94">
+        <v>663.39</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>242</v>
+      </c>
+      <c r="B95" t="s">
+        <v>81</v>
+      </c>
+      <c r="C95" t="s">
+        <v>82</v>
+      </c>
+      <c r="D95" t="s">
+        <v>91</v>
+      </c>
+      <c r="E95" t="s">
+        <v>32</v>
+      </c>
+      <c r="F95" t="s">
+        <v>84</v>
+      </c>
+      <c r="G95" t="s">
+        <v>92</v>
+      </c>
+      <c r="H95" t="s">
+        <v>52</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95">
+        <v>1250</v>
+      </c>
+      <c r="K95">
+        <v>2500</v>
+      </c>
+      <c r="L95" t="s">
+        <v>36</v>
+      </c>
+      <c r="M95" t="s">
+        <v>38</v>
+      </c>
+      <c r="N95" t="s">
+        <v>38</v>
+      </c>
+      <c r="O95" t="s">
+        <v>39</v>
+      </c>
+      <c r="P95" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>86</v>
+      </c>
+      <c r="R95">
+        <v>1554</v>
+      </c>
+      <c r="S95">
+        <v>1554</v>
+      </c>
+      <c r="T95" t="s">
+        <v>42</v>
+      </c>
+      <c r="U95">
+        <v>1</v>
+      </c>
+      <c r="V95" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95">
+        <v>1420</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA95">
+        <v>2206.68</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>243</v>
+      </c>
+      <c r="B96" t="s">
+        <v>81</v>
+      </c>
+      <c r="C96" t="s">
+        <v>82</v>
+      </c>
+      <c r="D96" t="s">
+        <v>244</v>
+      </c>
+      <c r="E96" t="s">
+        <v>32</v>
+      </c>
+      <c r="F96" t="s">
+        <v>84</v>
+      </c>
+      <c r="G96" t="s">
+        <v>92</v>
+      </c>
+      <c r="H96" t="s">
+        <v>52</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>1500</v>
+      </c>
+      <c r="K96">
+        <v>3000</v>
+      </c>
+      <c r="L96" t="s">
+        <v>53</v>
+      </c>
+      <c r="M96" t="s">
+        <v>38</v>
+      </c>
+      <c r="N96" t="s">
+        <v>38</v>
+      </c>
+      <c r="O96" t="s">
+        <v>39</v>
+      </c>
+      <c r="P96" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>86</v>
+      </c>
+      <c r="R96">
+        <v>2210</v>
+      </c>
+      <c r="S96">
+        <v>2210</v>
+      </c>
+      <c r="T96" t="s">
+        <v>42</v>
+      </c>
+      <c r="U96">
+        <v>1</v>
+      </c>
+      <c r="V96" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X96">
+        <v>1420</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA96">
+        <v>3138.2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>245</v>
+      </c>
+      <c r="B97" t="s">
+        <v>81</v>
+      </c>
+      <c r="C97" t="s">
+        <v>82</v>
+      </c>
+      <c r="D97" t="s">
+        <v>246</v>
+      </c>
+      <c r="E97" t="s">
+        <v>32</v>
+      </c>
+      <c r="F97" t="s">
+        <v>33</v>
+      </c>
+      <c r="G97" t="s">
+        <v>92</v>
+      </c>
+      <c r="H97" t="s">
+        <v>52</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>1500</v>
+      </c>
+      <c r="L97" t="s">
+        <v>53</v>
+      </c>
+      <c r="M97" t="s">
+        <v>38</v>
+      </c>
+      <c r="N97" t="s">
+        <v>38</v>
+      </c>
+      <c r="O97" t="s">
+        <v>39</v>
+      </c>
+      <c r="P97" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>86</v>
+      </c>
+      <c r="R97">
+        <v>3350</v>
+      </c>
+      <c r="S97">
+        <v>3350</v>
+      </c>
+      <c r="T97" t="s">
+        <v>42</v>
+      </c>
+      <c r="U97">
+        <v>1</v>
+      </c>
+      <c r="V97" t="s">
+        <v>43</v>
+      </c>
+      <c r="W97" t="s">
+        <v>43</v>
+      </c>
+      <c r="X97">
+        <v>1420</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA97">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>247</v>
+      </c>
+      <c r="B98" t="s">
+        <v>81</v>
+      </c>
+      <c r="C98" t="s">
+        <v>82</v>
+      </c>
+      <c r="D98" t="s">
+        <v>248</v>
+      </c>
+      <c r="E98" t="s">
+        <v>32</v>
+      </c>
+      <c r="F98" t="s">
+        <v>84</v>
+      </c>
+      <c r="G98" t="s">
+        <v>92</v>
+      </c>
+      <c r="H98" t="s">
+        <v>52</v>
+      </c>
+      <c r="I98">
+        <v>1.5</v>
+      </c>
+      <c r="J98">
+        <v>1250</v>
+      </c>
+      <c r="K98">
+        <v>2500</v>
+      </c>
+      <c r="L98" t="s">
+        <v>36</v>
+      </c>
+      <c r="M98" t="s">
+        <v>38</v>
+      </c>
+      <c r="N98" t="s">
+        <v>38</v>
+      </c>
+      <c r="O98" t="s">
+        <v>39</v>
+      </c>
+      <c r="P98" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>86</v>
+      </c>
+      <c r="R98">
+        <v>944</v>
+      </c>
+      <c r="S98">
+        <v>944</v>
+      </c>
+      <c r="T98" t="s">
+        <v>42</v>
+      </c>
+      <c r="U98">
+        <v>26</v>
+      </c>
+      <c r="V98" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98">
+        <v>1370</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA98">
+        <v>1293.28</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>249</v>
+      </c>
+      <c r="B99" t="s">
+        <v>81</v>
+      </c>
+      <c r="C99" t="s">
+        <v>82</v>
+      </c>
+      <c r="D99" t="s">
+        <v>250</v>
+      </c>
+      <c r="E99" t="s">
+        <v>32</v>
+      </c>
+      <c r="F99" t="s">
+        <v>84</v>
+      </c>
+      <c r="G99" t="s">
+        <v>85</v>
+      </c>
+      <c r="H99" t="s">
+        <v>52</v>
+      </c>
+      <c r="I99">
+        <v>3</v>
+      </c>
+      <c r="J99">
+        <v>1500</v>
+      </c>
+      <c r="K99">
+        <v>3000</v>
+      </c>
+      <c r="L99" t="s">
+        <v>53</v>
+      </c>
+      <c r="M99" t="s">
+        <v>38</v>
+      </c>
+      <c r="N99" t="s">
+        <v>38</v>
+      </c>
+      <c r="O99" t="s">
+        <v>39</v>
+      </c>
+      <c r="P99" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>86</v>
+      </c>
+      <c r="R99">
+        <v>634</v>
+      </c>
+      <c r="S99">
+        <v>634</v>
+      </c>
+      <c r="T99" t="s">
+        <v>42</v>
+      </c>
+      <c r="U99">
+        <v>6</v>
+      </c>
+      <c r="V99" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99">
+        <v>2220</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA99">
+        <v>1407.48</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>251</v>
+      </c>
+      <c r="B100" t="s">
+        <v>81</v>
+      </c>
+      <c r="C100" t="s">
+        <v>82</v>
+      </c>
+      <c r="D100" t="s">
+        <v>252</v>
+      </c>
+      <c r="E100" t="s">
+        <v>32</v>
+      </c>
+      <c r="F100" t="s">
+        <v>84</v>
+      </c>
+      <c r="G100" t="s">
+        <v>92</v>
+      </c>
+      <c r="H100" t="s">
+        <v>52</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>1500</v>
+      </c>
+      <c r="K100">
+        <v>3000</v>
+      </c>
+      <c r="L100" t="s">
+        <v>36</v>
+      </c>
+      <c r="M100" t="s">
+        <v>38</v>
+      </c>
+      <c r="N100" t="s">
+        <v>38</v>
+      </c>
+      <c r="O100" t="s">
+        <v>39</v>
+      </c>
+      <c r="P100" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>86</v>
+      </c>
+      <c r="R100">
+        <v>1923</v>
+      </c>
+      <c r="S100">
+        <v>1923</v>
+      </c>
+      <c r="T100" t="s">
+        <v>42</v>
+      </c>
+      <c r="U100">
+        <v>1</v>
+      </c>
+      <c r="V100" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100">
+        <v>1420</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA100">
+        <v>2730.66</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>253</v>
+      </c>
+      <c r="B101" t="s">
+        <v>88</v>
+      </c>
+      <c r="C101" t="s">
+        <v>82</v>
+      </c>
+      <c r="D101" t="s">
+        <v>254</v>
+      </c>
+      <c r="E101" t="s">
+        <v>32</v>
+      </c>
+      <c r="F101" t="s">
+        <v>84</v>
+      </c>
+      <c r="G101" t="s">
+        <v>85</v>
+      </c>
+      <c r="H101" t="s">
+        <v>52</v>
+      </c>
+      <c r="I101">
+        <v>1.2</v>
+      </c>
+      <c r="J101">
+        <v>1500</v>
+      </c>
+      <c r="K101">
+        <v>3000</v>
+      </c>
+      <c r="L101" t="s">
+        <v>53</v>
+      </c>
+      <c r="M101" t="s">
+        <v>38</v>
+      </c>
+      <c r="N101" t="s">
+        <v>38</v>
+      </c>
+      <c r="O101" t="s">
+        <v>39</v>
+      </c>
+      <c r="P101" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>86</v>
+      </c>
+      <c r="R101">
+        <v>42</v>
+      </c>
+      <c r="S101">
+        <v>42</v>
+      </c>
+      <c r="T101" t="s">
+        <v>42</v>
+      </c>
+      <c r="U101">
+        <v>1</v>
+      </c>
+      <c r="V101" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101">
+        <v>2170</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA101">
+        <v>91.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="253">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -160,39 +160,42 @@
     <t>K30/1.4016-430</t>
   </si>
   <si>
+    <t>H1 - Coil eye to the side on pallet + corner protect.</t>
+  </si>
+  <si>
+    <t>ASME SA 240 / ASTM A 240 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305</t>
+  </si>
+  <si>
+    <t>G26RJS73</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R without paper 0.49 x 140.0 mm Slit</t>
+  </si>
+  <si>
+    <t>K260274399</t>
+  </si>
+  <si>
+    <t>Genk</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>Coil 1.4307-304L 1D without paper 4.98 x 847.0 mm Unslit not marked</t>
+  </si>
+  <si>
+    <t>1.4307-304L</t>
+  </si>
+  <si>
+    <t>Unslit</t>
+  </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
     <t>Horiz. without pallet, road tr</t>
   </si>
   <si>
-    <t>ASME SA 240 / ASTM A 240 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305</t>
-  </si>
-  <si>
-    <t>G26RJS73</t>
-  </si>
-  <si>
-    <t>Coil K30/1.4016-430 2R without paper 0.49 x 140.0 mm Slit</t>
-  </si>
-  <si>
-    <t>K260274399</t>
-  </si>
-  <si>
-    <t>Genk</t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 1D without paper 4.98 x 847.0 mm Unslit not marked</t>
-  </si>
-  <si>
-    <t>1.4307-304L</t>
-  </si>
-  <si>
-    <t>Unslit</t>
-  </si>
-  <si>
-    <t>1D</t>
-  </si>
-  <si>
     <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4304</t>
   </si>
   <si>
@@ -214,9 +217,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>H1 - Coil eye to the side on pallet + corner protect.</t>
-  </si>
-  <si>
     <t>K268103623</t>
   </si>
   <si>
@@ -239,6 +239,537 @@
   </si>
   <si>
     <t>K41/1.4509-441</t>
+  </si>
+  <si>
+    <t>7248626</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>1.4404-316L</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>T488802</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256740</t>
+  </si>
+  <si>
+    <t>Sheets 1.4301-304 2R 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256819</t>
+  </si>
+  <si>
+    <t>7256820</t>
+  </si>
+  <si>
+    <t>7256821</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>7256940</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed Nov 4228 0.8 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7256941</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489089</t>
+  </si>
+  <si>
+    <t>7257261</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Scotchbrite</t>
+  </si>
+  <si>
+    <t>T489700</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489750</t>
+  </si>
+  <si>
+    <t>7257570</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257703</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2E 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>2E</t>
+  </si>
+  <si>
+    <t>T490582</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257842</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 2000.0 x 4000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Nov 4228 6.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257864</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257865</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 400 NOV 4204 RB 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>NOV 4204 RB</t>
+  </si>
+  <si>
+    <t>7257894</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>S139218</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 12.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258091</t>
+  </si>
+  <si>
+    <t>7258100</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258149</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491483</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258350</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T492123</t>
+  </si>
+  <si>
+    <t>T492124</t>
+  </si>
+  <si>
+    <t>7258489</t>
+  </si>
+  <si>
+    <t>7258526</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258529</t>
+  </si>
+  <si>
+    <t>7258730</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258760</t>
+  </si>
+  <si>
+    <t>7258862</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258863</t>
+  </si>
+  <si>
+    <t>7259015</t>
+  </si>
+  <si>
+    <t>Coil 1.4520-430Ti 2B 1.2 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4520-430Ti</t>
+  </si>
+  <si>
+    <t>7259028</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R without paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259050</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R NOV 4241/4513 0.8 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>NOV 4241/4513</t>
+  </si>
+  <si>
+    <t>7259145</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259182</t>
+  </si>
+  <si>
+    <t>T492642</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259417</t>
+  </si>
+  <si>
+    <t>7259437</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259438</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B with paper 1.0 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7259439</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R with paper 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259445</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259447</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T493044</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259661</t>
+  </si>
+  <si>
+    <t>7259677</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B without paper 8.0 x 1500.0 x 3000 mm Slit marked</t>
   </si>
 </sst>
 </file>
@@ -615,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB104"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -994,7 +1525,7 @@
         <v>39</v>
       </c>
       <c r="Q5" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="R5">
         <v>6150</v>
@@ -1009,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W5" t="s">
         <v>43</v>
@@ -1032,7 +1563,7 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -1041,7 +1572,7 @@
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -1077,7 +1608,7 @@
         <v>39</v>
       </c>
       <c r="Q6" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="R6">
         <v>5870</v>
@@ -1092,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W6" t="s">
         <v>43</v>
@@ -1115,7 +1646,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
@@ -1124,7 +1655,7 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
@@ -1145,7 +1676,7 @@
         <v>731</v>
       </c>
       <c r="L7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M7" t="s">
         <v>37</v>
@@ -1157,10 +1688,10 @@
         <v>38</v>
       </c>
       <c r="P7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q7" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="R7">
         <v>3720</v>
@@ -1228,7 +1759,7 @@
         <v>1518</v>
       </c>
       <c r="L8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
         <v>37</v>
@@ -1240,10 +1771,10 @@
         <v>38</v>
       </c>
       <c r="P8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q8" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="R8">
         <v>1620</v>
@@ -1311,7 +1842,7 @@
         <v>1520</v>
       </c>
       <c r="L9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M9" t="s">
         <v>37</v>
@@ -1323,10 +1854,10 @@
         <v>38</v>
       </c>
       <c r="P9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q9" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="R9">
         <v>2190</v>
@@ -1394,7 +1925,7 @@
         <v>1277</v>
       </c>
       <c r="L10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M10" t="s">
         <v>37</v>
@@ -1406,10 +1937,10 @@
         <v>38</v>
       </c>
       <c r="P10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q10" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="R10">
         <v>7000</v>
@@ -1443,6 +1974,7820 @@
       </c>
       <c r="AB10" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11">
+        <v>2.5</v>
+      </c>
+      <c r="J11">
+        <v>1000</v>
+      </c>
+      <c r="K11">
+        <v>2000</v>
+      </c>
+      <c r="L11" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>81</v>
+      </c>
+      <c r="R11">
+        <v>312</v>
+      </c>
+      <c r="S11">
+        <v>312</v>
+      </c>
+      <c r="T11" t="s">
+        <v>41</v>
+      </c>
+      <c r="U11">
+        <v>8</v>
+      </c>
+      <c r="V11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X11">
+        <v>2220</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA11">
+        <v>692.64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>1000</v>
+      </c>
+      <c r="K12">
+        <v>2000</v>
+      </c>
+      <c r="L12" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>81</v>
+      </c>
+      <c r="R12">
+        <v>394</v>
+      </c>
+      <c r="S12">
+        <v>394</v>
+      </c>
+      <c r="T12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" t="s">
+        <v>43</v>
+      </c>
+      <c r="X12">
+        <v>2020</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA12">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>1250</v>
+      </c>
+      <c r="K13">
+        <v>2500</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" t="s">
+        <v>38</v>
+      </c>
+      <c r="P13" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>81</v>
+      </c>
+      <c r="R13">
+        <v>322</v>
+      </c>
+      <c r="S13">
+        <v>322</v>
+      </c>
+      <c r="T13" t="s">
+        <v>41</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13">
+        <v>1370</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA13">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>1250</v>
+      </c>
+      <c r="K14">
+        <v>2500</v>
+      </c>
+      <c r="L14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>81</v>
+      </c>
+      <c r="R14">
+        <v>340</v>
+      </c>
+      <c r="S14">
+        <v>340</v>
+      </c>
+      <c r="T14" t="s">
+        <v>41</v>
+      </c>
+      <c r="U14">
+        <v>7</v>
+      </c>
+      <c r="V14" t="s">
+        <v>43</v>
+      </c>
+      <c r="W14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X14">
+        <v>1370</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA14">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <v>2000</v>
+      </c>
+      <c r="K15">
+        <v>6000</v>
+      </c>
+      <c r="L15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>81</v>
+      </c>
+      <c r="R15">
+        <v>283</v>
+      </c>
+      <c r="S15">
+        <v>283</v>
+      </c>
+      <c r="T15" t="s">
+        <v>41</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" t="s">
+        <v>43</v>
+      </c>
+      <c r="X15">
+        <v>3560</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA15">
+        <v>1007.48</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="J16">
+        <v>1500</v>
+      </c>
+      <c r="K16">
+        <v>3000</v>
+      </c>
+      <c r="L16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>81</v>
+      </c>
+      <c r="R16">
+        <v>212</v>
+      </c>
+      <c r="S16">
+        <v>212</v>
+      </c>
+      <c r="T16" t="s">
+        <v>41</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
+        <v>43</v>
+      </c>
+      <c r="W16" t="s">
+        <v>43</v>
+      </c>
+      <c r="X16">
+        <v>3490</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA16">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17">
+        <v>8</v>
+      </c>
+      <c r="J17">
+        <v>1250</v>
+      </c>
+      <c r="K17">
+        <v>2500</v>
+      </c>
+      <c r="L17" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>81</v>
+      </c>
+      <c r="R17">
+        <v>394</v>
+      </c>
+      <c r="S17">
+        <v>394</v>
+      </c>
+      <c r="T17" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W17" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17">
+        <v>3490</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA17">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>2000</v>
+      </c>
+      <c r="K18">
+        <v>6000</v>
+      </c>
+      <c r="L18" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>81</v>
+      </c>
+      <c r="R18">
+        <v>472</v>
+      </c>
+      <c r="S18">
+        <v>472</v>
+      </c>
+      <c r="T18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X18">
+        <v>2190</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA18">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>1500</v>
+      </c>
+      <c r="K19">
+        <v>3000</v>
+      </c>
+      <c r="L19" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" t="s">
+        <v>102</v>
+      </c>
+      <c r="N19" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>81</v>
+      </c>
+      <c r="R19">
+        <v>970</v>
+      </c>
+      <c r="S19">
+        <v>970</v>
+      </c>
+      <c r="T19" t="s">
+        <v>41</v>
+      </c>
+      <c r="U19">
+        <v>13</v>
+      </c>
+      <c r="V19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" t="s">
+        <v>43</v>
+      </c>
+      <c r="X19">
+        <v>3490</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA19">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20">
+        <v>2.5</v>
+      </c>
+      <c r="J20">
+        <v>1500</v>
+      </c>
+      <c r="K20">
+        <v>3000</v>
+      </c>
+      <c r="L20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" t="s">
+        <v>37</v>
+      </c>
+      <c r="O20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P20" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>81</v>
+      </c>
+      <c r="R20">
+        <v>526</v>
+      </c>
+      <c r="S20">
+        <v>526</v>
+      </c>
+      <c r="T20" t="s">
+        <v>41</v>
+      </c>
+      <c r="U20">
+        <v>6</v>
+      </c>
+      <c r="V20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20">
+        <v>3540</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA20">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>1500</v>
+      </c>
+      <c r="K21">
+        <v>3000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" t="s">
+        <v>37</v>
+      </c>
+      <c r="O21" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>81</v>
+      </c>
+      <c r="R21">
+        <v>354</v>
+      </c>
+      <c r="S21">
+        <v>354</v>
+      </c>
+      <c r="T21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U21">
+        <v>2</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21">
+        <v>1170</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22">
+        <v>1.5</v>
+      </c>
+      <c r="J22">
+        <v>1250</v>
+      </c>
+      <c r="L22" t="s">
+        <v>66</v>
+      </c>
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>81</v>
+      </c>
+      <c r="R22">
+        <v>1275</v>
+      </c>
+      <c r="S22">
+        <v>1275</v>
+      </c>
+      <c r="T22" t="s">
+        <v>41</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>43</v>
+      </c>
+      <c r="X22">
+        <v>3590</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="J23">
+        <v>1500</v>
+      </c>
+      <c r="K23">
+        <v>3000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>81</v>
+      </c>
+      <c r="R23">
+        <v>210</v>
+      </c>
+      <c r="S23">
+        <v>210</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23">
+        <v>2</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23">
+        <v>2170</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA23">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24">
+        <v>1500</v>
+      </c>
+      <c r="K24">
+        <v>3000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>81</v>
+      </c>
+      <c r="R24">
+        <v>212</v>
+      </c>
+      <c r="S24">
+        <v>212</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>2</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>1320</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>6</v>
+      </c>
+      <c r="J25">
+        <v>1000</v>
+      </c>
+      <c r="K25">
+        <v>2000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>66</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>81</v>
+      </c>
+      <c r="R25">
+        <v>567</v>
+      </c>
+      <c r="S25">
+        <v>567</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>6</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>2220</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>6</v>
+      </c>
+      <c r="J26">
+        <v>1000</v>
+      </c>
+      <c r="K26">
+        <v>2000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>66</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>81</v>
+      </c>
+      <c r="R26">
+        <v>567</v>
+      </c>
+      <c r="S26">
+        <v>567</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>6</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>2220</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>1500</v>
+      </c>
+      <c r="K27">
+        <v>3000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>66</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>81</v>
+      </c>
+      <c r="R27">
+        <v>319</v>
+      </c>
+      <c r="S27">
+        <v>319</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>3</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>1370</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28">
+        <v>1250</v>
+      </c>
+      <c r="K28">
+        <v>2500</v>
+      </c>
+      <c r="L28" t="s">
+        <v>66</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>81</v>
+      </c>
+      <c r="R28">
+        <v>246</v>
+      </c>
+      <c r="S28">
+        <v>246</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>5</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>2170</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
+        <v>0.8</v>
+      </c>
+      <c r="J29">
+        <v>1000</v>
+      </c>
+      <c r="K29">
+        <v>2000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>66</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>81</v>
+      </c>
+      <c r="R29">
+        <v>1498</v>
+      </c>
+      <c r="S29">
+        <v>1498</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>2370</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>0.8</v>
+      </c>
+      <c r="J30">
+        <v>1000</v>
+      </c>
+      <c r="K30">
+        <v>2000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>66</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>81</v>
+      </c>
+      <c r="R30">
+        <v>1498</v>
+      </c>
+      <c r="S30">
+        <v>1498</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>2370</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>1500</v>
+      </c>
+      <c r="K31">
+        <v>3000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M31" t="s">
+        <v>102</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>81</v>
+      </c>
+      <c r="R31">
+        <v>1010</v>
+      </c>
+      <c r="S31">
+        <v>1010</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>14</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>3540</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>1500</v>
+      </c>
+      <c r="K32">
+        <v>3000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>66</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>81</v>
+      </c>
+      <c r="R32">
+        <v>283</v>
+      </c>
+      <c r="S32">
+        <v>283</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>4</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>3540</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" t="s">
+        <v>127</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>0.8</v>
+      </c>
+      <c r="J33">
+        <v>1000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>36</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>128</v>
+      </c>
+      <c r="P33" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>81</v>
+      </c>
+      <c r="R33">
+        <v>1585</v>
+      </c>
+      <c r="S33">
+        <v>1585</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>2370</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" t="s">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s">
+        <v>48</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>1.5</v>
+      </c>
+      <c r="J34">
+        <v>1500</v>
+      </c>
+      <c r="K34">
+        <v>3000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>81</v>
+      </c>
+      <c r="R34">
+        <v>212</v>
+      </c>
+      <c r="S34">
+        <v>212</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>1320</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" t="s">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35">
+        <v>2.5</v>
+      </c>
+      <c r="J35">
+        <v>1500</v>
+      </c>
+      <c r="K35">
+        <v>3000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>66</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>81</v>
+      </c>
+      <c r="R35">
+        <v>540</v>
+      </c>
+      <c r="S35">
+        <v>540</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>6</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>3540</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <v>2.5</v>
+      </c>
+      <c r="J36">
+        <v>1500</v>
+      </c>
+      <c r="K36">
+        <v>3000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>66</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>81</v>
+      </c>
+      <c r="R36">
+        <v>520</v>
+      </c>
+      <c r="S36">
+        <v>520</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>6</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>3540</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" t="s">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>2.5</v>
+      </c>
+      <c r="J37">
+        <v>1500</v>
+      </c>
+      <c r="K37">
+        <v>3000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>66</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>81</v>
+      </c>
+      <c r="R37">
+        <v>530</v>
+      </c>
+      <c r="S37">
+        <v>530</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>6</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>3540</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" t="s">
+        <v>74</v>
+      </c>
+      <c r="F38" t="s">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s">
+        <v>91</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>2.5</v>
+      </c>
+      <c r="J38">
+        <v>1500</v>
+      </c>
+      <c r="K38">
+        <v>3000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>66</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>81</v>
+      </c>
+      <c r="R38">
+        <v>526</v>
+      </c>
+      <c r="S38">
+        <v>526</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>6</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>3540</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s">
+        <v>91</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>1500</v>
+      </c>
+      <c r="K39">
+        <v>3000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>66</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>81</v>
+      </c>
+      <c r="R39">
+        <v>212</v>
+      </c>
+      <c r="S39">
+        <v>212</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>1</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>3490</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" t="s">
+        <v>74</v>
+      </c>
+      <c r="F40" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>1500</v>
+      </c>
+      <c r="K40">
+        <v>3000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>81</v>
+      </c>
+      <c r="R40">
+        <v>212</v>
+      </c>
+      <c r="S40">
+        <v>212</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>3490</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" t="s">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s">
+        <v>57</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41">
+        <v>1000</v>
+      </c>
+      <c r="K41">
+        <v>2000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>66</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>81</v>
+      </c>
+      <c r="R41">
+        <v>315</v>
+      </c>
+      <c r="S41">
+        <v>315</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>5</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>2220</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" t="s">
+        <v>84</v>
+      </c>
+      <c r="E42" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" t="s">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s">
+        <v>57</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>1000</v>
+      </c>
+      <c r="K42">
+        <v>2000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>59</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>81</v>
+      </c>
+      <c r="R42">
+        <v>944</v>
+      </c>
+      <c r="S42">
+        <v>944</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>2020</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" t="s">
+        <v>74</v>
+      </c>
+      <c r="F43" t="s">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>1500</v>
+      </c>
+      <c r="K43">
+        <v>3000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>66</v>
+      </c>
+      <c r="M43" t="s">
+        <v>102</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>81</v>
+      </c>
+      <c r="R43">
+        <v>1224</v>
+      </c>
+      <c r="S43">
+        <v>1224</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>34</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>3540</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F44" t="s">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s">
+        <v>48</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>1.5</v>
+      </c>
+      <c r="J44">
+        <v>1500</v>
+      </c>
+      <c r="K44">
+        <v>3000</v>
+      </c>
+      <c r="L44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M44" t="s">
+        <v>102</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>81</v>
+      </c>
+      <c r="R44">
+        <v>916</v>
+      </c>
+      <c r="S44">
+        <v>916</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>18</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>1320</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" t="s">
+        <v>74</v>
+      </c>
+      <c r="F45" t="s">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="J45">
+        <v>1500</v>
+      </c>
+      <c r="K45">
+        <v>3000</v>
+      </c>
+      <c r="L45" t="s">
+        <v>66</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>81</v>
+      </c>
+      <c r="R45">
+        <v>319</v>
+      </c>
+      <c r="S45">
+        <v>319</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>3540</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" t="s">
+        <v>136</v>
+      </c>
+      <c r="E46" t="s">
+        <v>74</v>
+      </c>
+      <c r="F46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s">
+        <v>91</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>1500</v>
+      </c>
+      <c r="K46">
+        <v>3000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>66</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>81</v>
+      </c>
+      <c r="R46">
+        <v>212</v>
+      </c>
+      <c r="S46">
+        <v>212</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>1</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>3490</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" t="s">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>1500</v>
+      </c>
+      <c r="K47">
+        <v>3000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>66</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>81</v>
+      </c>
+      <c r="R47">
+        <v>212</v>
+      </c>
+      <c r="S47">
+        <v>212</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>1</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>3490</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>148</v>
+      </c>
+      <c r="B48" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" t="s">
+        <v>74</v>
+      </c>
+      <c r="F48" t="s">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s">
+        <v>91</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>3</v>
+      </c>
+      <c r="J48">
+        <v>1500</v>
+      </c>
+      <c r="K48">
+        <v>3000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>66</v>
+      </c>
+      <c r="M48" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>81</v>
+      </c>
+      <c r="R48">
+        <v>319</v>
+      </c>
+      <c r="S48">
+        <v>319</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>3540</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" t="s">
+        <v>150</v>
+      </c>
+      <c r="E49" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" t="s">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s">
+        <v>57</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>6</v>
+      </c>
+      <c r="J49">
+        <v>2000</v>
+      </c>
+      <c r="K49">
+        <v>4000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>66</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>81</v>
+      </c>
+      <c r="R49">
+        <v>756</v>
+      </c>
+      <c r="S49">
+        <v>756</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>2</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>2240</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>1693.44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" t="s">
+        <v>152</v>
+      </c>
+      <c r="E50" t="s">
+        <v>74</v>
+      </c>
+      <c r="F50" t="s">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50">
+        <v>1000</v>
+      </c>
+      <c r="K50">
+        <v>2000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>36</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>81</v>
+      </c>
+      <c r="R50">
+        <v>544</v>
+      </c>
+      <c r="S50">
+        <v>544</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>2220</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>1207.68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" t="s">
+        <v>155</v>
+      </c>
+      <c r="E51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" t="s">
+        <v>127</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>0.8</v>
+      </c>
+      <c r="J51">
+        <v>1000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>36</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>81</v>
+      </c>
+      <c r="R51">
+        <v>1000</v>
+      </c>
+      <c r="S51">
+        <v>1000</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>1</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>2370</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>156</v>
+      </c>
+      <c r="B52" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" t="s">
+        <v>78</v>
+      </c>
+      <c r="D52" t="s">
+        <v>157</v>
+      </c>
+      <c r="E52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52" t="s">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s">
+        <v>57</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>2.5</v>
+      </c>
+      <c r="J52">
+        <v>1500</v>
+      </c>
+      <c r="K52">
+        <v>3000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>66</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>81</v>
+      </c>
+      <c r="R52">
+        <v>266</v>
+      </c>
+      <c r="S52">
+        <v>266</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>3</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>2220</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" t="s">
+        <v>83</v>
+      </c>
+      <c r="C53" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" t="s">
+        <v>157</v>
+      </c>
+      <c r="E53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F53" t="s">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s">
+        <v>57</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>2.5</v>
+      </c>
+      <c r="J53">
+        <v>1500</v>
+      </c>
+      <c r="K53">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>66</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>81</v>
+      </c>
+      <c r="R53">
+        <v>354</v>
+      </c>
+      <c r="S53">
+        <v>354</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>4</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>2220</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" t="s">
+        <v>74</v>
+      </c>
+      <c r="F54" t="s">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s">
+        <v>57</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>2.5</v>
+      </c>
+      <c r="J54">
+        <v>1500</v>
+      </c>
+      <c r="K54">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>66</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>81</v>
+      </c>
+      <c r="R54">
+        <v>620</v>
+      </c>
+      <c r="S54">
+        <v>620</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>7</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>2220</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>1376.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" t="s">
+        <v>78</v>
+      </c>
+      <c r="D55" t="s">
+        <v>161</v>
+      </c>
+      <c r="E55" t="s">
+        <v>74</v>
+      </c>
+      <c r="F55" t="s">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s">
+        <v>91</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>1.5</v>
+      </c>
+      <c r="J55">
+        <v>1500</v>
+      </c>
+      <c r="K55">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>66</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>81</v>
+      </c>
+      <c r="R55">
+        <v>266</v>
+      </c>
+      <c r="S55">
+        <v>266</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>5</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>3540</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>941.64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" t="s">
+        <v>163</v>
+      </c>
+      <c r="E56" t="s">
+        <v>74</v>
+      </c>
+      <c r="F56" t="s">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s">
+        <v>91</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>2.5</v>
+      </c>
+      <c r="J56">
+        <v>2000</v>
+      </c>
+      <c r="K56">
+        <v>4000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>66</v>
+      </c>
+      <c r="M56" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>81</v>
+      </c>
+      <c r="R56">
+        <v>315</v>
+      </c>
+      <c r="S56">
+        <v>315</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>2</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>3560</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" t="s">
+        <v>83</v>
+      </c>
+      <c r="C57" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" t="s">
+        <v>163</v>
+      </c>
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" t="s">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s">
+        <v>91</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>2.5</v>
+      </c>
+      <c r="J57">
+        <v>2000</v>
+      </c>
+      <c r="K57">
+        <v>4000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>66</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>81</v>
+      </c>
+      <c r="R57">
+        <v>315</v>
+      </c>
+      <c r="S57">
+        <v>315</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>2</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>3560</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>165</v>
+      </c>
+      <c r="B58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D58" t="s">
+        <v>166</v>
+      </c>
+      <c r="E58" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" t="s">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>0.8</v>
+      </c>
+      <c r="J58">
+        <v>1500</v>
+      </c>
+      <c r="K58">
+        <v>3000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>66</v>
+      </c>
+      <c r="M58" t="s">
+        <v>102</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>167</v>
+      </c>
+      <c r="P58" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>81</v>
+      </c>
+      <c r="R58">
+        <v>833</v>
+      </c>
+      <c r="S58">
+        <v>833</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>29</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>2270</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>1890.91</v>
+      </c>
+      <c r="AB58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>168</v>
+      </c>
+      <c r="B59" t="s">
+        <v>77</v>
+      </c>
+      <c r="C59" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59" t="s">
+        <v>166</v>
+      </c>
+      <c r="E59" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" t="s">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s">
+        <v>57</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>0.8</v>
+      </c>
+      <c r="J59">
+        <v>1500</v>
+      </c>
+      <c r="K59">
+        <v>3000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>66</v>
+      </c>
+      <c r="M59" t="s">
+        <v>102</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>167</v>
+      </c>
+      <c r="P59" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>81</v>
+      </c>
+      <c r="R59">
+        <v>805</v>
+      </c>
+      <c r="S59">
+        <v>805</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>28</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2270</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>1827.35</v>
+      </c>
+      <c r="AB59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" t="s">
+        <v>77</v>
+      </c>
+      <c r="C60" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" t="s">
+        <v>170</v>
+      </c>
+      <c r="E60" t="s">
+        <v>74</v>
+      </c>
+      <c r="F60" t="s">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s">
+        <v>57</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60">
+        <v>1000</v>
+      </c>
+      <c r="K60">
+        <v>2000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>66</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>81</v>
+      </c>
+      <c r="R60">
+        <v>1448</v>
+      </c>
+      <c r="S60">
+        <v>1448</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>1</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>2270</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>3286.96</v>
+      </c>
+      <c r="AB60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61" t="s">
+        <v>172</v>
+      </c>
+      <c r="E61" t="s">
+        <v>74</v>
+      </c>
+      <c r="F61" t="s">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s">
+        <v>48</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>4</v>
+      </c>
+      <c r="J61">
+        <v>1000</v>
+      </c>
+      <c r="K61">
+        <v>2000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>66</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>81</v>
+      </c>
+      <c r="R61">
+        <v>384</v>
+      </c>
+      <c r="S61">
+        <v>384</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>6</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>1370</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>173</v>
+      </c>
+      <c r="B62" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" t="s">
+        <v>78</v>
+      </c>
+      <c r="D62" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" t="s">
+        <v>74</v>
+      </c>
+      <c r="F62" t="s">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>6</v>
+      </c>
+      <c r="J62">
+        <v>1500</v>
+      </c>
+      <c r="K62">
+        <v>3000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>66</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>81</v>
+      </c>
+      <c r="R62">
+        <v>850</v>
+      </c>
+      <c r="S62">
+        <v>850</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>4</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>3540</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>174</v>
+      </c>
+      <c r="B63" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" t="s">
+        <v>78</v>
+      </c>
+      <c r="D63" t="s">
+        <v>175</v>
+      </c>
+      <c r="E63" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" t="s">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s">
+        <v>57</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>0.8</v>
+      </c>
+      <c r="J63">
+        <v>1250</v>
+      </c>
+      <c r="K63">
+        <v>2500</v>
+      </c>
+      <c r="L63" t="s">
+        <v>66</v>
+      </c>
+      <c r="M63" t="s">
+        <v>176</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>81</v>
+      </c>
+      <c r="R63">
+        <v>430</v>
+      </c>
+      <c r="S63">
+        <v>430</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>2270</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>976.1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>177</v>
+      </c>
+      <c r="B64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" t="s">
+        <v>78</v>
+      </c>
+      <c r="D64" t="s">
+        <v>178</v>
+      </c>
+      <c r="E64" t="s">
+        <v>74</v>
+      </c>
+      <c r="F64" t="s">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s">
+        <v>57</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>2</v>
+      </c>
+      <c r="J64">
+        <v>1000</v>
+      </c>
+      <c r="K64">
+        <v>2000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>66</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>81</v>
+      </c>
+      <c r="R64">
+        <v>283</v>
+      </c>
+      <c r="S64">
+        <v>283</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>9</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>2220</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>179</v>
+      </c>
+      <c r="B65" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" t="s">
+        <v>78</v>
+      </c>
+      <c r="D65" t="s">
+        <v>112</v>
+      </c>
+      <c r="E65" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65" t="s">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s">
+        <v>48</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>3</v>
+      </c>
+      <c r="J65">
+        <v>1500</v>
+      </c>
+      <c r="K65">
+        <v>3000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>66</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>81</v>
+      </c>
+      <c r="R65">
+        <v>637</v>
+      </c>
+      <c r="S65">
+        <v>637</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>6</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>1370</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>872.69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>180</v>
+      </c>
+      <c r="B66" t="s">
+        <v>77</v>
+      </c>
+      <c r="C66" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66" t="s">
+        <v>181</v>
+      </c>
+      <c r="E66" t="s">
+        <v>74</v>
+      </c>
+      <c r="F66" t="s">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s">
+        <v>57</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <v>1000</v>
+      </c>
+      <c r="K66">
+        <v>2000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>66</v>
+      </c>
+      <c r="M66" t="s">
+        <v>102</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>81</v>
+      </c>
+      <c r="R66">
+        <v>1482</v>
+      </c>
+      <c r="S66">
+        <v>1482</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>1</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>2220</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>3290.04</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>182</v>
+      </c>
+      <c r="B67" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" t="s">
+        <v>78</v>
+      </c>
+      <c r="D67" t="s">
+        <v>183</v>
+      </c>
+      <c r="E67" t="s">
+        <v>74</v>
+      </c>
+      <c r="F67" t="s">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s">
+        <v>96</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>4</v>
+      </c>
+      <c r="J67">
+        <v>1500</v>
+      </c>
+      <c r="K67">
+        <v>3000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>184</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>81</v>
+      </c>
+      <c r="R67">
+        <v>1133</v>
+      </c>
+      <c r="S67">
+        <v>1133</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>8</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>3540</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>4010.82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>185</v>
+      </c>
+      <c r="B68" t="s">
+        <v>83</v>
+      </c>
+      <c r="C68" t="s">
+        <v>78</v>
+      </c>
+      <c r="D68" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" t="s">
+        <v>74</v>
+      </c>
+      <c r="F68" t="s">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s">
+        <v>57</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>5</v>
+      </c>
+      <c r="J68">
+        <v>2000</v>
+      </c>
+      <c r="K68">
+        <v>4000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>66</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>81</v>
+      </c>
+      <c r="R68">
+        <v>1259</v>
+      </c>
+      <c r="S68">
+        <v>1259</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>4</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>2290</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>2883.11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>187</v>
+      </c>
+      <c r="B69" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" t="s">
+        <v>78</v>
+      </c>
+      <c r="D69" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" t="s">
+        <v>74</v>
+      </c>
+      <c r="F69" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s">
+        <v>57</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>4</v>
+      </c>
+      <c r="J69">
+        <v>2000</v>
+      </c>
+      <c r="K69">
+        <v>4000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>66</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>81</v>
+      </c>
+      <c r="R69">
+        <v>1007</v>
+      </c>
+      <c r="S69">
+        <v>1007</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>4</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>2290</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>2306.03</v>
+      </c>
+      <c r="AB69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" t="s">
+        <v>78</v>
+      </c>
+      <c r="D70" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" t="s">
+        <v>74</v>
+      </c>
+      <c r="F70" t="s">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s">
+        <v>57</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>6</v>
+      </c>
+      <c r="J70">
+        <v>1500</v>
+      </c>
+      <c r="K70">
+        <v>3000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>66</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>167</v>
+      </c>
+      <c r="P70" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>81</v>
+      </c>
+      <c r="R70">
+        <v>1487</v>
+      </c>
+      <c r="S70">
+        <v>1487</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>7</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>2270</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>3375.49</v>
+      </c>
+      <c r="AB70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>191</v>
+      </c>
+      <c r="B71" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71" t="s">
+        <v>192</v>
+      </c>
+      <c r="E71" t="s">
+        <v>74</v>
+      </c>
+      <c r="F71" t="s">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s">
+        <v>57</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>8</v>
+      </c>
+      <c r="J71">
+        <v>2000</v>
+      </c>
+      <c r="K71">
+        <v>6000</v>
+      </c>
+      <c r="L71" t="s">
+        <v>59</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>81</v>
+      </c>
+      <c r="R71">
+        <v>755</v>
+      </c>
+      <c r="S71">
+        <v>755</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>1</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>2040</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>1540.2</v>
+      </c>
+      <c r="AB71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>193</v>
+      </c>
+      <c r="B72" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72" t="s">
+        <v>194</v>
+      </c>
+      <c r="E72" t="s">
+        <v>74</v>
+      </c>
+      <c r="F72" t="s">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s">
+        <v>57</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1250</v>
+      </c>
+      <c r="K72">
+        <v>2500</v>
+      </c>
+      <c r="L72" t="s">
+        <v>66</v>
+      </c>
+      <c r="M72" t="s">
+        <v>195</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>196</v>
+      </c>
+      <c r="P72" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>81</v>
+      </c>
+      <c r="R72">
+        <v>1019</v>
+      </c>
+      <c r="S72">
+        <v>1019</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>41</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>2220</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>2262.18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>197</v>
+      </c>
+      <c r="B73" t="s">
+        <v>89</v>
+      </c>
+      <c r="C73" t="s">
+        <v>78</v>
+      </c>
+      <c r="D73" t="s">
+        <v>198</v>
+      </c>
+      <c r="E73" t="s">
+        <v>74</v>
+      </c>
+      <c r="F73" t="s">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s">
+        <v>57</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>8</v>
+      </c>
+      <c r="J73">
+        <v>1000</v>
+      </c>
+      <c r="K73">
+        <v>2000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>59</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>81</v>
+      </c>
+      <c r="R73">
+        <v>504</v>
+      </c>
+      <c r="S73">
+        <v>504</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>4</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>2020</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>1018.08</v>
+      </c>
+      <c r="AB73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>199</v>
+      </c>
+      <c r="B74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" t="s">
+        <v>78</v>
+      </c>
+      <c r="D74" t="s">
+        <v>200</v>
+      </c>
+      <c r="E74" t="s">
+        <v>74</v>
+      </c>
+      <c r="F74" t="s">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>12</v>
+      </c>
+      <c r="J74">
+        <v>1000</v>
+      </c>
+      <c r="K74">
+        <v>2000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>59</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>81</v>
+      </c>
+      <c r="R74">
+        <v>1322</v>
+      </c>
+      <c r="S74">
+        <v>1322</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>7</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>2070</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>2736.54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>201</v>
+      </c>
+      <c r="B75" t="s">
+        <v>77</v>
+      </c>
+      <c r="C75" t="s">
+        <v>78</v>
+      </c>
+      <c r="D75" t="s">
+        <v>104</v>
+      </c>
+      <c r="E75" t="s">
+        <v>74</v>
+      </c>
+      <c r="F75" t="s">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s">
+        <v>91</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>2.5</v>
+      </c>
+      <c r="J75">
+        <v>1500</v>
+      </c>
+      <c r="K75">
+        <v>3000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>66</v>
+      </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>81</v>
+      </c>
+      <c r="R75">
+        <v>534</v>
+      </c>
+      <c r="S75">
+        <v>534</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>6</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>3540</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>1890.36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>202</v>
+      </c>
+      <c r="B76" t="s">
+        <v>77</v>
+      </c>
+      <c r="C76" t="s">
+        <v>78</v>
+      </c>
+      <c r="D76" t="s">
+        <v>203</v>
+      </c>
+      <c r="E76" t="s">
+        <v>74</v>
+      </c>
+      <c r="F76" t="s">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s">
+        <v>57</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>0.8</v>
+      </c>
+      <c r="J76">
+        <v>1250</v>
+      </c>
+      <c r="K76">
+        <v>2500</v>
+      </c>
+      <c r="L76" t="s">
+        <v>66</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>81</v>
+      </c>
+      <c r="R76">
+        <v>2033</v>
+      </c>
+      <c r="S76">
+        <v>2033</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>101</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>2370</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>4818.21</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>204</v>
+      </c>
+      <c r="B77" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" t="s">
+        <v>78</v>
+      </c>
+      <c r="D77" t="s">
+        <v>205</v>
+      </c>
+      <c r="E77" t="s">
+        <v>74</v>
+      </c>
+      <c r="F77" t="s">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>2</v>
+      </c>
+      <c r="J77">
+        <v>1000</v>
+      </c>
+      <c r="K77">
+        <v>2000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>66</v>
+      </c>
+      <c r="M77" t="s">
+        <v>102</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>81</v>
+      </c>
+      <c r="R77">
+        <v>1046</v>
+      </c>
+      <c r="S77">
+        <v>1046</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>33</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>3540</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>3702.84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>206</v>
+      </c>
+      <c r="B78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" t="s">
+        <v>78</v>
+      </c>
+      <c r="D78" t="s">
+        <v>207</v>
+      </c>
+      <c r="E78" t="s">
+        <v>74</v>
+      </c>
+      <c r="F78" t="s">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s">
+        <v>57</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>4</v>
+      </c>
+      <c r="J78">
+        <v>1500</v>
+      </c>
+      <c r="K78">
+        <v>3000</v>
+      </c>
+      <c r="L78" t="s">
+        <v>66</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>81</v>
+      </c>
+      <c r="R78">
+        <v>142</v>
+      </c>
+      <c r="S78">
+        <v>142</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>1</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>2170</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>208</v>
+      </c>
+      <c r="B79" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D79" t="s">
+        <v>209</v>
+      </c>
+      <c r="E79" t="s">
+        <v>74</v>
+      </c>
+      <c r="F79" t="s">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s">
+        <v>57</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>2</v>
+      </c>
+      <c r="J79">
+        <v>2000</v>
+      </c>
+      <c r="K79">
+        <v>4000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>66</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>81</v>
+      </c>
+      <c r="R79">
+        <v>126</v>
+      </c>
+      <c r="S79">
+        <v>126</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>1</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>2190</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>210</v>
+      </c>
+      <c r="B80" t="s">
+        <v>77</v>
+      </c>
+      <c r="C80" t="s">
+        <v>78</v>
+      </c>
+      <c r="D80" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" t="s">
+        <v>74</v>
+      </c>
+      <c r="F80" t="s">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s">
+        <v>57</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>0.8</v>
+      </c>
+      <c r="J80">
+        <v>1000</v>
+      </c>
+      <c r="K80">
+        <v>2000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>66</v>
+      </c>
+      <c r="M80" t="s">
+        <v>102</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>81</v>
+      </c>
+      <c r="R80">
+        <v>1216</v>
+      </c>
+      <c r="S80">
+        <v>1216</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>96</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>2320</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>2821.12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>212</v>
+      </c>
+      <c r="B81" t="s">
+        <v>83</v>
+      </c>
+      <c r="C81" t="s">
+        <v>78</v>
+      </c>
+      <c r="D81" t="s">
+        <v>203</v>
+      </c>
+      <c r="E81" t="s">
+        <v>74</v>
+      </c>
+      <c r="F81" t="s">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s">
+        <v>57</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>0.8</v>
+      </c>
+      <c r="J81">
+        <v>1250</v>
+      </c>
+      <c r="K81">
+        <v>2500</v>
+      </c>
+      <c r="L81" t="s">
+        <v>66</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>81</v>
+      </c>
+      <c r="R81">
+        <v>334</v>
+      </c>
+      <c r="S81">
+        <v>334</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>17</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>2320</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>213</v>
+      </c>
+      <c r="B82" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" t="s">
+        <v>78</v>
+      </c>
+      <c r="D82" t="s">
+        <v>203</v>
+      </c>
+      <c r="E82" t="s">
+        <v>74</v>
+      </c>
+      <c r="F82" t="s">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s">
+        <v>57</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>0.8</v>
+      </c>
+      <c r="J82">
+        <v>1250</v>
+      </c>
+      <c r="K82">
+        <v>2500</v>
+      </c>
+      <c r="L82" t="s">
+        <v>66</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>81</v>
+      </c>
+      <c r="R82">
+        <v>334</v>
+      </c>
+      <c r="S82">
+        <v>334</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>17</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>2320</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>214</v>
+      </c>
+      <c r="B83" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" t="s">
+        <v>78</v>
+      </c>
+      <c r="D83" t="s">
+        <v>203</v>
+      </c>
+      <c r="E83" t="s">
+        <v>74</v>
+      </c>
+      <c r="F83" t="s">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s">
+        <v>57</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>0.8</v>
+      </c>
+      <c r="J83">
+        <v>1250</v>
+      </c>
+      <c r="K83">
+        <v>2500</v>
+      </c>
+      <c r="L83" t="s">
+        <v>66</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>81</v>
+      </c>
+      <c r="R83">
+        <v>551</v>
+      </c>
+      <c r="S83">
+        <v>551</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>28</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>2320</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>1278.32</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>215</v>
+      </c>
+      <c r="B84" t="s">
+        <v>77</v>
+      </c>
+      <c r="C84" t="s">
+        <v>78</v>
+      </c>
+      <c r="D84" t="s">
+        <v>216</v>
+      </c>
+      <c r="E84" t="s">
+        <v>74</v>
+      </c>
+      <c r="F84" t="s">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s">
+        <v>91</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84">
+        <v>1250</v>
+      </c>
+      <c r="K84">
+        <v>2500</v>
+      </c>
+      <c r="L84" t="s">
+        <v>66</v>
+      </c>
+      <c r="M84" t="s">
+        <v>102</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>81</v>
+      </c>
+      <c r="R84">
+        <v>612</v>
+      </c>
+      <c r="S84">
+        <v>612</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>12</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>3490</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>2135.88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>217</v>
+      </c>
+      <c r="B85" t="s">
+        <v>77</v>
+      </c>
+      <c r="C85" t="s">
+        <v>78</v>
+      </c>
+      <c r="D85" t="s">
+        <v>181</v>
+      </c>
+      <c r="E85" t="s">
+        <v>74</v>
+      </c>
+      <c r="F85" t="s">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s">
+        <v>57</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>1000</v>
+      </c>
+      <c r="K85">
+        <v>2000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>66</v>
+      </c>
+      <c r="M85" t="s">
+        <v>102</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>81</v>
+      </c>
+      <c r="R85">
+        <v>752</v>
+      </c>
+      <c r="S85">
+        <v>752</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>48</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>2170</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>1631.84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>218</v>
+      </c>
+      <c r="B86" t="s">
+        <v>89</v>
+      </c>
+      <c r="C86" t="s">
+        <v>78</v>
+      </c>
+      <c r="D86" t="s">
+        <v>219</v>
+      </c>
+      <c r="E86" t="s">
+        <v>74</v>
+      </c>
+      <c r="F86" t="s">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s">
+        <v>96</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>3</v>
+      </c>
+      <c r="J86">
+        <v>1500</v>
+      </c>
+      <c r="K86">
+        <v>3000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>66</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>81</v>
+      </c>
+      <c r="R86">
+        <v>106</v>
+      </c>
+      <c r="S86">
+        <v>106</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>1</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>3640</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>385.84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>220</v>
+      </c>
+      <c r="B87" t="s">
+        <v>77</v>
+      </c>
+      <c r="C87" t="s">
+        <v>78</v>
+      </c>
+      <c r="D87" t="s">
+        <v>161</v>
+      </c>
+      <c r="E87" t="s">
+        <v>74</v>
+      </c>
+      <c r="F87" t="s">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s">
+        <v>91</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87">
+        <v>1.5</v>
+      </c>
+      <c r="J87">
+        <v>1500</v>
+      </c>
+      <c r="K87">
+        <v>3000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>66</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>81</v>
+      </c>
+      <c r="R87">
+        <v>330</v>
+      </c>
+      <c r="S87">
+        <v>330</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>6</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>3540</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>221</v>
+      </c>
+      <c r="B88" t="s">
+        <v>83</v>
+      </c>
+      <c r="C88" t="s">
+        <v>78</v>
+      </c>
+      <c r="D88" t="s">
+        <v>222</v>
+      </c>
+      <c r="E88" t="s">
+        <v>74</v>
+      </c>
+      <c r="F88" t="s">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s">
+        <v>57</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88">
+        <v>3</v>
+      </c>
+      <c r="J88">
+        <v>1000</v>
+      </c>
+      <c r="K88">
+        <v>2000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>66</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>81</v>
+      </c>
+      <c r="R88">
+        <v>1464</v>
+      </c>
+      <c r="S88">
+        <v>1464</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>31</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>2270</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>3323.28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>223</v>
+      </c>
+      <c r="B89" t="s">
+        <v>83</v>
+      </c>
+      <c r="C89" t="s">
+        <v>78</v>
+      </c>
+      <c r="D89" t="s">
+        <v>222</v>
+      </c>
+      <c r="E89" t="s">
+        <v>74</v>
+      </c>
+      <c r="F89" t="s">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s">
+        <v>57</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89">
+        <v>3</v>
+      </c>
+      <c r="J89">
+        <v>1000</v>
+      </c>
+      <c r="K89">
+        <v>2000</v>
+      </c>
+      <c r="L89" t="s">
+        <v>66</v>
+      </c>
+      <c r="M89" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>81</v>
+      </c>
+      <c r="R89">
+        <v>94</v>
+      </c>
+      <c r="S89">
+        <v>94</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>2</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>2170</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>224</v>
+      </c>
+      <c r="B90" t="s">
+        <v>77</v>
+      </c>
+      <c r="C90" t="s">
+        <v>78</v>
+      </c>
+      <c r="D90" t="s">
+        <v>225</v>
+      </c>
+      <c r="E90" t="s">
+        <v>74</v>
+      </c>
+      <c r="F90" t="s">
+        <v>33</v>
+      </c>
+      <c r="G90" t="s">
+        <v>226</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>1.2</v>
+      </c>
+      <c r="J90">
+        <v>1250</v>
+      </c>
+      <c r="L90" t="s">
+        <v>66</v>
+      </c>
+      <c r="M90" t="s">
+        <v>37</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>81</v>
+      </c>
+      <c r="R90">
+        <v>1420</v>
+      </c>
+      <c r="S90">
+        <v>1420</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>1</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>1420</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>2016.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>227</v>
+      </c>
+      <c r="B91" t="s">
+        <v>77</v>
+      </c>
+      <c r="C91" t="s">
+        <v>78</v>
+      </c>
+      <c r="D91" t="s">
+        <v>228</v>
+      </c>
+      <c r="E91" t="s">
+        <v>74</v>
+      </c>
+      <c r="F91" t="s">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s">
+        <v>48</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91">
+        <v>1500</v>
+      </c>
+      <c r="K91">
+        <v>3000</v>
+      </c>
+      <c r="L91" t="s">
+        <v>36</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>81</v>
+      </c>
+      <c r="R91">
+        <v>414</v>
+      </c>
+      <c r="S91">
+        <v>414</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>12</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>1370</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>567.18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>229</v>
+      </c>
+      <c r="B92" t="s">
+        <v>77</v>
+      </c>
+      <c r="C92" t="s">
+        <v>78</v>
+      </c>
+      <c r="D92" t="s">
+        <v>230</v>
+      </c>
+      <c r="E92" t="s">
+        <v>74</v>
+      </c>
+      <c r="F92" t="s">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s">
+        <v>48</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92">
+        <v>0.8</v>
+      </c>
+      <c r="J92">
+        <v>1500</v>
+      </c>
+      <c r="K92">
+        <v>3000</v>
+      </c>
+      <c r="L92" t="s">
+        <v>36</v>
+      </c>
+      <c r="M92" t="s">
+        <v>37</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>231</v>
+      </c>
+      <c r="P92" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>81</v>
+      </c>
+      <c r="R92">
+        <v>2584</v>
+      </c>
+      <c r="S92">
+        <v>2584</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>94</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>1520</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>3927.68</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>232</v>
+      </c>
+      <c r="B93" t="s">
+        <v>77</v>
+      </c>
+      <c r="C93" t="s">
+        <v>78</v>
+      </c>
+      <c r="D93" t="s">
+        <v>233</v>
+      </c>
+      <c r="E93" t="s">
+        <v>74</v>
+      </c>
+      <c r="F93" t="s">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s">
+        <v>48</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1250</v>
+      </c>
+      <c r="K93">
+        <v>2500</v>
+      </c>
+      <c r="L93" t="s">
+        <v>36</v>
+      </c>
+      <c r="M93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" t="s">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>81</v>
+      </c>
+      <c r="R93">
+        <v>668</v>
+      </c>
+      <c r="S93">
+        <v>668</v>
+      </c>
+      <c r="T93" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93">
+        <v>1</v>
+      </c>
+      <c r="V93" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93">
+        <v>1370</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA93">
+        <v>915.16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>234</v>
+      </c>
+      <c r="B94" t="s">
+        <v>77</v>
+      </c>
+      <c r="C94" t="s">
+        <v>78</v>
+      </c>
+      <c r="D94" t="s">
+        <v>118</v>
+      </c>
+      <c r="E94" t="s">
+        <v>74</v>
+      </c>
+      <c r="F94" t="s">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s">
+        <v>57</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94">
+        <v>2</v>
+      </c>
+      <c r="J94">
+        <v>1250</v>
+      </c>
+      <c r="K94">
+        <v>2500</v>
+      </c>
+      <c r="L94" t="s">
+        <v>66</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
+      </c>
+      <c r="N94" t="s">
+        <v>37</v>
+      </c>
+      <c r="O94" t="s">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>81</v>
+      </c>
+      <c r="R94">
+        <v>358</v>
+      </c>
+      <c r="S94">
+        <v>358</v>
+      </c>
+      <c r="T94" t="s">
+        <v>41</v>
+      </c>
+      <c r="U94">
+        <v>7</v>
+      </c>
+      <c r="V94" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94">
+        <v>2220</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA94">
+        <v>794.76</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>235</v>
+      </c>
+      <c r="B95" t="s">
+        <v>83</v>
+      </c>
+      <c r="C95" t="s">
+        <v>78</v>
+      </c>
+      <c r="D95" t="s">
+        <v>236</v>
+      </c>
+      <c r="E95" t="s">
+        <v>74</v>
+      </c>
+      <c r="F95" t="s">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s">
+        <v>91</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95">
+        <v>3</v>
+      </c>
+      <c r="J95">
+        <v>2000</v>
+      </c>
+      <c r="K95">
+        <v>4000</v>
+      </c>
+      <c r="L95" t="s">
+        <v>66</v>
+      </c>
+      <c r="M95" t="s">
+        <v>37</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>81</v>
+      </c>
+      <c r="R95">
+        <v>189</v>
+      </c>
+      <c r="S95">
+        <v>189</v>
+      </c>
+      <c r="T95" t="s">
+        <v>41</v>
+      </c>
+      <c r="U95">
+        <v>1</v>
+      </c>
+      <c r="V95" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95">
+        <v>3510</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA95">
+        <v>663.39</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>237</v>
+      </c>
+      <c r="B96" t="s">
+        <v>77</v>
+      </c>
+      <c r="C96" t="s">
+        <v>78</v>
+      </c>
+      <c r="D96" t="s">
+        <v>86</v>
+      </c>
+      <c r="E96" t="s">
+        <v>74</v>
+      </c>
+      <c r="F96" t="s">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s">
+        <v>48</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
+        <v>1250</v>
+      </c>
+      <c r="K96">
+        <v>2500</v>
+      </c>
+      <c r="L96" t="s">
+        <v>36</v>
+      </c>
+      <c r="M96" t="s">
+        <v>37</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
+      </c>
+      <c r="P96" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>81</v>
+      </c>
+      <c r="R96">
+        <v>1554</v>
+      </c>
+      <c r="S96">
+        <v>1554</v>
+      </c>
+      <c r="T96" t="s">
+        <v>41</v>
+      </c>
+      <c r="U96">
+        <v>1</v>
+      </c>
+      <c r="V96" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X96">
+        <v>1420</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA96">
+        <v>2206.68</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>238</v>
+      </c>
+      <c r="B97" t="s">
+        <v>77</v>
+      </c>
+      <c r="C97" t="s">
+        <v>78</v>
+      </c>
+      <c r="D97" t="s">
+        <v>239</v>
+      </c>
+      <c r="E97" t="s">
+        <v>74</v>
+      </c>
+      <c r="F97" t="s">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s">
+        <v>48</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>1500</v>
+      </c>
+      <c r="K97">
+        <v>3000</v>
+      </c>
+      <c r="L97" t="s">
+        <v>66</v>
+      </c>
+      <c r="M97" t="s">
+        <v>37</v>
+      </c>
+      <c r="N97" t="s">
+        <v>37</v>
+      </c>
+      <c r="O97" t="s">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>81</v>
+      </c>
+      <c r="R97">
+        <v>2210</v>
+      </c>
+      <c r="S97">
+        <v>2210</v>
+      </c>
+      <c r="T97" t="s">
+        <v>41</v>
+      </c>
+      <c r="U97">
+        <v>1</v>
+      </c>
+      <c r="V97" t="s">
+        <v>43</v>
+      </c>
+      <c r="W97" t="s">
+        <v>43</v>
+      </c>
+      <c r="X97">
+        <v>1420</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA97">
+        <v>3138.2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>240</v>
+      </c>
+      <c r="B98" t="s">
+        <v>77</v>
+      </c>
+      <c r="C98" t="s">
+        <v>78</v>
+      </c>
+      <c r="D98" t="s">
+        <v>241</v>
+      </c>
+      <c r="E98" t="s">
+        <v>74</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
+      </c>
+      <c r="G98" t="s">
+        <v>48</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>1500</v>
+      </c>
+      <c r="L98" t="s">
+        <v>66</v>
+      </c>
+      <c r="M98" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" t="s">
+        <v>38</v>
+      </c>
+      <c r="P98" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>81</v>
+      </c>
+      <c r="R98">
+        <v>3350</v>
+      </c>
+      <c r="S98">
+        <v>3350</v>
+      </c>
+      <c r="T98" t="s">
+        <v>41</v>
+      </c>
+      <c r="U98">
+        <v>1</v>
+      </c>
+      <c r="V98" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98">
+        <v>1420</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA98">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>242</v>
+      </c>
+      <c r="B99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C99" t="s">
+        <v>78</v>
+      </c>
+      <c r="D99" t="s">
+        <v>243</v>
+      </c>
+      <c r="E99" t="s">
+        <v>74</v>
+      </c>
+      <c r="F99" t="s">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s">
+        <v>48</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99">
+        <v>1.5</v>
+      </c>
+      <c r="J99">
+        <v>1250</v>
+      </c>
+      <c r="K99">
+        <v>2500</v>
+      </c>
+      <c r="L99" t="s">
+        <v>36</v>
+      </c>
+      <c r="M99" t="s">
+        <v>37</v>
+      </c>
+      <c r="N99" t="s">
+        <v>37</v>
+      </c>
+      <c r="O99" t="s">
+        <v>38</v>
+      </c>
+      <c r="P99" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>81</v>
+      </c>
+      <c r="R99">
+        <v>944</v>
+      </c>
+      <c r="S99">
+        <v>944</v>
+      </c>
+      <c r="T99" t="s">
+        <v>41</v>
+      </c>
+      <c r="U99">
+        <v>26</v>
+      </c>
+      <c r="V99" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99">
+        <v>1370</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA99">
+        <v>1293.28</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>244</v>
+      </c>
+      <c r="B100" t="s">
+        <v>77</v>
+      </c>
+      <c r="C100" t="s">
+        <v>78</v>
+      </c>
+      <c r="D100" t="s">
+        <v>245</v>
+      </c>
+      <c r="E100" t="s">
+        <v>74</v>
+      </c>
+      <c r="F100" t="s">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s">
+        <v>57</v>
+      </c>
+      <c r="H100" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100">
+        <v>3</v>
+      </c>
+      <c r="J100">
+        <v>1500</v>
+      </c>
+      <c r="K100">
+        <v>3000</v>
+      </c>
+      <c r="L100" t="s">
+        <v>66</v>
+      </c>
+      <c r="M100" t="s">
+        <v>37</v>
+      </c>
+      <c r="N100" t="s">
+        <v>37</v>
+      </c>
+      <c r="O100" t="s">
+        <v>38</v>
+      </c>
+      <c r="P100" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>81</v>
+      </c>
+      <c r="R100">
+        <v>634</v>
+      </c>
+      <c r="S100">
+        <v>634</v>
+      </c>
+      <c r="T100" t="s">
+        <v>41</v>
+      </c>
+      <c r="U100">
+        <v>6</v>
+      </c>
+      <c r="V100" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100">
+        <v>2220</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA100">
+        <v>1407.48</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>246</v>
+      </c>
+      <c r="B101" t="s">
+        <v>77</v>
+      </c>
+      <c r="C101" t="s">
+        <v>78</v>
+      </c>
+      <c r="D101" t="s">
+        <v>247</v>
+      </c>
+      <c r="E101" t="s">
+        <v>74</v>
+      </c>
+      <c r="F101" t="s">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s">
+        <v>48</v>
+      </c>
+      <c r="H101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>1500</v>
+      </c>
+      <c r="K101">
+        <v>3000</v>
+      </c>
+      <c r="L101" t="s">
+        <v>36</v>
+      </c>
+      <c r="M101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N101" t="s">
+        <v>37</v>
+      </c>
+      <c r="O101" t="s">
+        <v>38</v>
+      </c>
+      <c r="P101" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>81</v>
+      </c>
+      <c r="R101">
+        <v>1923</v>
+      </c>
+      <c r="S101">
+        <v>1923</v>
+      </c>
+      <c r="T101" t="s">
+        <v>41</v>
+      </c>
+      <c r="U101">
+        <v>1</v>
+      </c>
+      <c r="V101" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101">
+        <v>1420</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA101">
+        <v>2730.66</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>248</v>
+      </c>
+      <c r="B102" t="s">
+        <v>83</v>
+      </c>
+      <c r="C102" t="s">
+        <v>78</v>
+      </c>
+      <c r="D102" t="s">
+        <v>249</v>
+      </c>
+      <c r="E102" t="s">
+        <v>74</v>
+      </c>
+      <c r="F102" t="s">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s">
+        <v>57</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102">
+        <v>1.2</v>
+      </c>
+      <c r="J102">
+        <v>1500</v>
+      </c>
+      <c r="K102">
+        <v>3000</v>
+      </c>
+      <c r="L102" t="s">
+        <v>66</v>
+      </c>
+      <c r="M102" t="s">
+        <v>37</v>
+      </c>
+      <c r="N102" t="s">
+        <v>37</v>
+      </c>
+      <c r="O102" t="s">
+        <v>38</v>
+      </c>
+      <c r="P102" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>81</v>
+      </c>
+      <c r="R102">
+        <v>42</v>
+      </c>
+      <c r="S102">
+        <v>42</v>
+      </c>
+      <c r="T102" t="s">
+        <v>41</v>
+      </c>
+      <c r="U102">
+        <v>1</v>
+      </c>
+      <c r="V102" t="s">
+        <v>43</v>
+      </c>
+      <c r="W102" t="s">
+        <v>43</v>
+      </c>
+      <c r="X102">
+        <v>2170</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA102">
+        <v>91.14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>250</v>
+      </c>
+      <c r="B103" t="s">
+        <v>77</v>
+      </c>
+      <c r="C103" t="s">
+        <v>78</v>
+      </c>
+      <c r="D103" t="s">
+        <v>161</v>
+      </c>
+      <c r="E103" t="s">
+        <v>74</v>
+      </c>
+      <c r="F103" t="s">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s">
+        <v>91</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103">
+        <v>1.5</v>
+      </c>
+      <c r="J103">
+        <v>1500</v>
+      </c>
+      <c r="K103">
+        <v>3000</v>
+      </c>
+      <c r="L103" t="s">
+        <v>66</v>
+      </c>
+      <c r="M103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N103" t="s">
+        <v>37</v>
+      </c>
+      <c r="O103" t="s">
+        <v>38</v>
+      </c>
+      <c r="P103" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>81</v>
+      </c>
+      <c r="R103">
+        <v>316</v>
+      </c>
+      <c r="S103">
+        <v>316</v>
+      </c>
+      <c r="T103" t="s">
+        <v>41</v>
+      </c>
+      <c r="U103">
+        <v>6</v>
+      </c>
+      <c r="V103" t="s">
+        <v>43</v>
+      </c>
+      <c r="W103" t="s">
+        <v>43</v>
+      </c>
+      <c r="X103">
+        <v>3540</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA103">
+        <v>1118.64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>251</v>
+      </c>
+      <c r="B104" t="s">
+        <v>89</v>
+      </c>
+      <c r="C104" t="s">
+        <v>78</v>
+      </c>
+      <c r="D104" t="s">
+        <v>252</v>
+      </c>
+      <c r="E104" t="s">
+        <v>74</v>
+      </c>
+      <c r="F104" t="s">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s">
+        <v>91</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104">
+        <v>8</v>
+      </c>
+      <c r="J104">
+        <v>1500</v>
+      </c>
+      <c r="K104">
+        <v>3000</v>
+      </c>
+      <c r="L104" t="s">
+        <v>66</v>
+      </c>
+      <c r="M104" t="s">
+        <v>37</v>
+      </c>
+      <c r="N104" t="s">
+        <v>37</v>
+      </c>
+      <c r="O104" t="s">
+        <v>38</v>
+      </c>
+      <c r="P104" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>81</v>
+      </c>
+      <c r="R104">
+        <v>1417</v>
+      </c>
+      <c r="S104">
+        <v>1417</v>
+      </c>
+      <c r="T104" t="s">
+        <v>41</v>
+      </c>
+      <c r="U104">
+        <v>5</v>
+      </c>
+      <c r="V104" t="s">
+        <v>43</v>
+      </c>
+      <c r="W104" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104">
+        <v>3590</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA104">
+        <v>5087.03</v>
+      </c>
+      <c r="AB104" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="299">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -335,6 +335,579 @@
   </si>
   <si>
     <t>Coil 1.4307-304L 2B with paper 0.77 x 104.0 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7249182</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T478238</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>7251031</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7252107</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484548</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T484549</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>T484798</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7254182</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254183</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>T485839</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255168</t>
+  </si>
+  <si>
+    <t>7255169</t>
+  </si>
+  <si>
+    <t>7255173</t>
+  </si>
+  <si>
+    <t>7255174</t>
+  </si>
+  <si>
+    <t>7255223</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255224</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256107</t>
+  </si>
+  <si>
+    <t>7256108</t>
+  </si>
+  <si>
+    <t>7256109</t>
+  </si>
+  <si>
+    <t>7256110</t>
+  </si>
+  <si>
+    <t>T488802</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 6.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256740</t>
+  </si>
+  <si>
+    <t>Sheets 1.4301-304 2R 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4301-304</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256819</t>
+  </si>
+  <si>
+    <t>7256820</t>
+  </si>
+  <si>
+    <t>7256821</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>7256940</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed Nov 4228 0.8 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>Nov 4228</t>
+  </si>
+  <si>
+    <t>7256941</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489089</t>
+  </si>
+  <si>
+    <t>7257261</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Scotchbrite with paper 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Scotchbrite</t>
+  </si>
+  <si>
+    <t>T489700</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489750</t>
+  </si>
+  <si>
+    <t>7257570</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 1.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257703</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2E 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T490582</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 5.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7257842</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 2000.0 x 4000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257854</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Nov 4228 6.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257864</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257865</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 400 NOV 4204 RB 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 400</t>
+  </si>
+  <si>
+    <t>NOV 4204 RB</t>
+  </si>
+  <si>
+    <t>7257894</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>S139218</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 12.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258091</t>
+  </si>
+  <si>
+    <t>7258100</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258149</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491483</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258350</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Brushed with paper 0.8 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T492123</t>
+  </si>
+  <si>
+    <t>T492124</t>
+  </si>
+  <si>
+    <t>7258489</t>
+  </si>
+  <si>
+    <t>7258526</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258529</t>
+  </si>
+  <si>
+    <t>7258730</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258760</t>
+  </si>
+  <si>
+    <t>7258862</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258863</t>
+  </si>
+  <si>
+    <t>7259015</t>
+  </si>
+  <si>
+    <t>Coil 1.4520-430Ti 2B 1.2 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4520-430Ti</t>
+  </si>
+  <si>
+    <t>7259028</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R without paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259050</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R NOV 4241/4513 0.8 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>NOV 4241/4513</t>
+  </si>
+  <si>
+    <t>7259145</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259182</t>
+  </si>
+  <si>
+    <t>T492642</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259417</t>
+  </si>
+  <si>
+    <t>7259437</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259438</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B with paper 1.0 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7259439</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R with paper 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259445</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259447</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T493044</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259661</t>
+  </si>
+  <si>
+    <t>7259677</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B without paper 8.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7259689</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R with paper 0.8 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T493468</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.25 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259716</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R without paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259717</t>
+  </si>
+  <si>
+    <t>7259732</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 6.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7259736</t>
+  </si>
+  <si>
+    <t>7259743</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2R 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259746</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2R Nov 4228 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259747</t>
+  </si>
+  <si>
+    <t>7259803</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 0.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259810</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1500.0 x 3000 mm Slit</t>
   </si>
 </sst>
 </file>
@@ -711,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB127"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -2602,6 +3175,8650 @@
         <v>1</v>
       </c>
     </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24">
+        <v>1000</v>
+      </c>
+      <c r="K24">
+        <v>2000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>113</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>114</v>
+      </c>
+      <c r="R24">
+        <v>394</v>
+      </c>
+      <c r="S24">
+        <v>394</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>2020</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>795.88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>1250</v>
+      </c>
+      <c r="K25">
+        <v>2500</v>
+      </c>
+      <c r="L25" t="s">
+        <v>51</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>114</v>
+      </c>
+      <c r="R25">
+        <v>322</v>
+      </c>
+      <c r="S25">
+        <v>322</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>1370</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G26" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s">
+        <v>50</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>1250</v>
+      </c>
+      <c r="K26">
+        <v>2500</v>
+      </c>
+      <c r="L26" t="s">
+        <v>51</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>114</v>
+      </c>
+      <c r="R26">
+        <v>340</v>
+      </c>
+      <c r="S26">
+        <v>340</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>7</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>1370</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" t="s">
+        <v>50</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>2000</v>
+      </c>
+      <c r="K27">
+        <v>6000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>36</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>114</v>
+      </c>
+      <c r="R27">
+        <v>283</v>
+      </c>
+      <c r="S27">
+        <v>283</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>3560</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>1007.48</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" t="s">
+        <v>50</v>
+      </c>
+      <c r="I28">
+        <v>6</v>
+      </c>
+      <c r="J28">
+        <v>1500</v>
+      </c>
+      <c r="K28">
+        <v>3000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>36</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>114</v>
+      </c>
+      <c r="R28">
+        <v>212</v>
+      </c>
+      <c r="S28">
+        <v>212</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>3490</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" t="s">
+        <v>112</v>
+      </c>
+      <c r="G29" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
+      <c r="J29">
+        <v>1250</v>
+      </c>
+      <c r="K29">
+        <v>2500</v>
+      </c>
+      <c r="L29" t="s">
+        <v>113</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>114</v>
+      </c>
+      <c r="R29">
+        <v>394</v>
+      </c>
+      <c r="S29">
+        <v>394</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>3490</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30">
+        <v>2000</v>
+      </c>
+      <c r="K30">
+        <v>6000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>113</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>114</v>
+      </c>
+      <c r="R30">
+        <v>472</v>
+      </c>
+      <c r="S30">
+        <v>472</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>2190</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" t="s">
+        <v>112</v>
+      </c>
+      <c r="G31" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>1500</v>
+      </c>
+      <c r="K31">
+        <v>3000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>36</v>
+      </c>
+      <c r="M31" t="s">
+        <v>131</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>114</v>
+      </c>
+      <c r="R31">
+        <v>970</v>
+      </c>
+      <c r="S31">
+        <v>970</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>13</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>3490</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" t="s">
+        <v>50</v>
+      </c>
+      <c r="I32">
+        <v>2.5</v>
+      </c>
+      <c r="J32">
+        <v>1500</v>
+      </c>
+      <c r="K32">
+        <v>3000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>36</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>114</v>
+      </c>
+      <c r="R32">
+        <v>526</v>
+      </c>
+      <c r="S32">
+        <v>526</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>6</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>3540</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I33">
+        <v>5</v>
+      </c>
+      <c r="J33">
+        <v>1500</v>
+      </c>
+      <c r="K33">
+        <v>3000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>113</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>114</v>
+      </c>
+      <c r="R33">
+        <v>354</v>
+      </c>
+      <c r="S33">
+        <v>354</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>2</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>1170</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" t="s">
+        <v>50</v>
+      </c>
+      <c r="I34">
+        <v>1.5</v>
+      </c>
+      <c r="J34">
+        <v>1250</v>
+      </c>
+      <c r="L34" t="s">
+        <v>36</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>114</v>
+      </c>
+      <c r="R34">
+        <v>1275</v>
+      </c>
+      <c r="S34">
+        <v>1275</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>3590</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" t="s">
+        <v>55</v>
+      </c>
+      <c r="H35" t="s">
+        <v>50</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
+      <c r="J35">
+        <v>1500</v>
+      </c>
+      <c r="K35">
+        <v>3000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>36</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>114</v>
+      </c>
+      <c r="R35">
+        <v>210</v>
+      </c>
+      <c r="S35">
+        <v>210</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>2</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>2170</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>455.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" t="s">
+        <v>112</v>
+      </c>
+      <c r="G36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" t="s">
+        <v>50</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <v>1500</v>
+      </c>
+      <c r="K36">
+        <v>3000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>36</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>114</v>
+      </c>
+      <c r="R36">
+        <v>212</v>
+      </c>
+      <c r="S36">
+        <v>212</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>2</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>1320</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" t="s">
+        <v>112</v>
+      </c>
+      <c r="G37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37" t="s">
+        <v>50</v>
+      </c>
+      <c r="I37">
+        <v>6</v>
+      </c>
+      <c r="J37">
+        <v>1000</v>
+      </c>
+      <c r="K37">
+        <v>2000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>36</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>114</v>
+      </c>
+      <c r="R37">
+        <v>567</v>
+      </c>
+      <c r="S37">
+        <v>567</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>6</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>2220</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H38" t="s">
+        <v>50</v>
+      </c>
+      <c r="I38">
+        <v>6</v>
+      </c>
+      <c r="J38">
+        <v>1000</v>
+      </c>
+      <c r="K38">
+        <v>2000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>36</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>114</v>
+      </c>
+      <c r="R38">
+        <v>567</v>
+      </c>
+      <c r="S38">
+        <v>567</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>6</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>2220</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>1258.74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" t="s">
+        <v>50</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>1500</v>
+      </c>
+      <c r="K39">
+        <v>3000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>36</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>114</v>
+      </c>
+      <c r="R39">
+        <v>319</v>
+      </c>
+      <c r="S39">
+        <v>319</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>3</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>1370</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>146</v>
+      </c>
+      <c r="B40" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40" t="s">
+        <v>112</v>
+      </c>
+      <c r="G40" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40" t="s">
+        <v>50</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="J40">
+        <v>1250</v>
+      </c>
+      <c r="K40">
+        <v>2500</v>
+      </c>
+      <c r="L40" t="s">
+        <v>36</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>114</v>
+      </c>
+      <c r="R40">
+        <v>246</v>
+      </c>
+      <c r="S40">
+        <v>246</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>5</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>2170</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>533.82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>148</v>
+      </c>
+      <c r="B41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F41" t="s">
+        <v>112</v>
+      </c>
+      <c r="G41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H41" t="s">
+        <v>50</v>
+      </c>
+      <c r="I41">
+        <v>0.8</v>
+      </c>
+      <c r="J41">
+        <v>1000</v>
+      </c>
+      <c r="K41">
+        <v>2000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>36</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>114</v>
+      </c>
+      <c r="R41">
+        <v>1498</v>
+      </c>
+      <c r="S41">
+        <v>1498</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>2370</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" t="s">
+        <v>149</v>
+      </c>
+      <c r="E42" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" t="s">
+        <v>50</v>
+      </c>
+      <c r="I42">
+        <v>0.8</v>
+      </c>
+      <c r="J42">
+        <v>1000</v>
+      </c>
+      <c r="K42">
+        <v>2000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>36</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>114</v>
+      </c>
+      <c r="R42">
+        <v>1498</v>
+      </c>
+      <c r="S42">
+        <v>1498</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>2370</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>3550.26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" t="s">
+        <v>112</v>
+      </c>
+      <c r="G43" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" t="s">
+        <v>50</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>1500</v>
+      </c>
+      <c r="K43">
+        <v>3000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>36</v>
+      </c>
+      <c r="M43" t="s">
+        <v>131</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>114</v>
+      </c>
+      <c r="R43">
+        <v>1010</v>
+      </c>
+      <c r="S43">
+        <v>1010</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>14</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>3540</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" t="s">
+        <v>153</v>
+      </c>
+      <c r="E44" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" t="s">
+        <v>50</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>1500</v>
+      </c>
+      <c r="K44">
+        <v>3000</v>
+      </c>
+      <c r="L44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>114</v>
+      </c>
+      <c r="R44">
+        <v>283</v>
+      </c>
+      <c r="S44">
+        <v>283</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>4</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>3540</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>1001.82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" t="s">
+        <v>155</v>
+      </c>
+      <c r="E45" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" t="s">
+        <v>85</v>
+      </c>
+      <c r="H45" t="s">
+        <v>50</v>
+      </c>
+      <c r="I45">
+        <v>0.8</v>
+      </c>
+      <c r="J45">
+        <v>1000</v>
+      </c>
+      <c r="L45" t="s">
+        <v>51</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>156</v>
+      </c>
+      <c r="P45" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>114</v>
+      </c>
+      <c r="R45">
+        <v>1585</v>
+      </c>
+      <c r="S45">
+        <v>1585</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>2370</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" t="s">
+        <v>112</v>
+      </c>
+      <c r="G46" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" t="s">
+        <v>50</v>
+      </c>
+      <c r="I46">
+        <v>1.5</v>
+      </c>
+      <c r="J46">
+        <v>1500</v>
+      </c>
+      <c r="K46">
+        <v>3000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>114</v>
+      </c>
+      <c r="R46">
+        <v>212</v>
+      </c>
+      <c r="S46">
+        <v>212</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>1</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>1320</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>159</v>
+      </c>
+      <c r="B47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" t="s">
+        <v>112</v>
+      </c>
+      <c r="G47" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" t="s">
+        <v>50</v>
+      </c>
+      <c r="I47">
+        <v>2.5</v>
+      </c>
+      <c r="J47">
+        <v>1500</v>
+      </c>
+      <c r="K47">
+        <v>3000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>36</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>114</v>
+      </c>
+      <c r="R47">
+        <v>540</v>
+      </c>
+      <c r="S47">
+        <v>540</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>6</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>3540</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>1911.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>160</v>
+      </c>
+      <c r="B48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" t="s">
+        <v>48</v>
+      </c>
+      <c r="F48" t="s">
+        <v>112</v>
+      </c>
+      <c r="G48" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" t="s">
+        <v>50</v>
+      </c>
+      <c r="I48">
+        <v>2.5</v>
+      </c>
+      <c r="J48">
+        <v>1500</v>
+      </c>
+      <c r="K48">
+        <v>3000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>114</v>
+      </c>
+      <c r="R48">
+        <v>520</v>
+      </c>
+      <c r="S48">
+        <v>520</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>6</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>3540</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>1840.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>161</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D49" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" t="s">
+        <v>112</v>
+      </c>
+      <c r="G49" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" t="s">
+        <v>50</v>
+      </c>
+      <c r="I49">
+        <v>2.5</v>
+      </c>
+      <c r="J49">
+        <v>1500</v>
+      </c>
+      <c r="K49">
+        <v>3000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>36</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>114</v>
+      </c>
+      <c r="R49">
+        <v>530</v>
+      </c>
+      <c r="S49">
+        <v>530</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>6</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>3540</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>1876.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" t="s">
+        <v>110</v>
+      </c>
+      <c r="D50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" t="s">
+        <v>112</v>
+      </c>
+      <c r="G50" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" t="s">
+        <v>50</v>
+      </c>
+      <c r="I50">
+        <v>2.5</v>
+      </c>
+      <c r="J50">
+        <v>1500</v>
+      </c>
+      <c r="K50">
+        <v>3000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>36</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>114</v>
+      </c>
+      <c r="R50">
+        <v>526</v>
+      </c>
+      <c r="S50">
+        <v>526</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>6</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>3540</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>1862.04</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
+        <v>110</v>
+      </c>
+      <c r="D51" t="s">
+        <v>164</v>
+      </c>
+      <c r="E51" t="s">
+        <v>48</v>
+      </c>
+      <c r="F51" t="s">
+        <v>112</v>
+      </c>
+      <c r="G51" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51" t="s">
+        <v>50</v>
+      </c>
+      <c r="I51">
+        <v>3</v>
+      </c>
+      <c r="J51">
+        <v>1500</v>
+      </c>
+      <c r="K51">
+        <v>3000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>36</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>114</v>
+      </c>
+      <c r="R51">
+        <v>212</v>
+      </c>
+      <c r="S51">
+        <v>212</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>1</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>3490</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E52" t="s">
+        <v>48</v>
+      </c>
+      <c r="F52" t="s">
+        <v>112</v>
+      </c>
+      <c r="G52" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" t="s">
+        <v>50</v>
+      </c>
+      <c r="I52">
+        <v>3</v>
+      </c>
+      <c r="J52">
+        <v>1500</v>
+      </c>
+      <c r="K52">
+        <v>3000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>36</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>114</v>
+      </c>
+      <c r="R52">
+        <v>212</v>
+      </c>
+      <c r="S52">
+        <v>212</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>1</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>3490</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" t="s">
+        <v>167</v>
+      </c>
+      <c r="E53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53" t="s">
+        <v>112</v>
+      </c>
+      <c r="G53" t="s">
+        <v>55</v>
+      </c>
+      <c r="H53" t="s">
+        <v>50</v>
+      </c>
+      <c r="I53">
+        <v>4</v>
+      </c>
+      <c r="J53">
+        <v>1000</v>
+      </c>
+      <c r="K53">
+        <v>2000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>36</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>114</v>
+      </c>
+      <c r="R53">
+        <v>315</v>
+      </c>
+      <c r="S53">
+        <v>315</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>5</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>2220</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54" t="s">
+        <v>48</v>
+      </c>
+      <c r="F54" t="s">
+        <v>112</v>
+      </c>
+      <c r="G54" t="s">
+        <v>55</v>
+      </c>
+      <c r="H54" t="s">
+        <v>50</v>
+      </c>
+      <c r="I54">
+        <v>5</v>
+      </c>
+      <c r="J54">
+        <v>1000</v>
+      </c>
+      <c r="K54">
+        <v>2000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>113</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>114</v>
+      </c>
+      <c r="R54">
+        <v>944</v>
+      </c>
+      <c r="S54">
+        <v>944</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>1</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>2020</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" t="s">
+        <v>170</v>
+      </c>
+      <c r="E55" t="s">
+        <v>48</v>
+      </c>
+      <c r="F55" t="s">
+        <v>112</v>
+      </c>
+      <c r="G55" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" t="s">
+        <v>50</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <v>1500</v>
+      </c>
+      <c r="K55">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>36</v>
+      </c>
+      <c r="M55" t="s">
+        <v>131</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>114</v>
+      </c>
+      <c r="R55">
+        <v>1224</v>
+      </c>
+      <c r="S55">
+        <v>1224</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>34</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>3540</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>171</v>
+      </c>
+      <c r="B56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" t="s">
+        <v>110</v>
+      </c>
+      <c r="D56" t="s">
+        <v>172</v>
+      </c>
+      <c r="E56" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56" t="s">
+        <v>112</v>
+      </c>
+      <c r="G56" t="s">
+        <v>78</v>
+      </c>
+      <c r="H56" t="s">
+        <v>50</v>
+      </c>
+      <c r="I56">
+        <v>1.5</v>
+      </c>
+      <c r="J56">
+        <v>1500</v>
+      </c>
+      <c r="K56">
+        <v>3000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>51</v>
+      </c>
+      <c r="M56" t="s">
+        <v>131</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>114</v>
+      </c>
+      <c r="R56">
+        <v>916</v>
+      </c>
+      <c r="S56">
+        <v>916</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>18</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>1320</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
+        <v>110</v>
+      </c>
+      <c r="D57" t="s">
+        <v>164</v>
+      </c>
+      <c r="E57" t="s">
+        <v>48</v>
+      </c>
+      <c r="F57" t="s">
+        <v>112</v>
+      </c>
+      <c r="G57" t="s">
+        <v>34</v>
+      </c>
+      <c r="H57" t="s">
+        <v>50</v>
+      </c>
+      <c r="I57">
+        <v>3</v>
+      </c>
+      <c r="J57">
+        <v>1500</v>
+      </c>
+      <c r="K57">
+        <v>3000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>36</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>114</v>
+      </c>
+      <c r="R57">
+        <v>319</v>
+      </c>
+      <c r="S57">
+        <v>319</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>1</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>3540</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" t="s">
+        <v>110</v>
+      </c>
+      <c r="D58" t="s">
+        <v>164</v>
+      </c>
+      <c r="E58" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" t="s">
+        <v>112</v>
+      </c>
+      <c r="G58" t="s">
+        <v>34</v>
+      </c>
+      <c r="H58" t="s">
+        <v>50</v>
+      </c>
+      <c r="I58">
+        <v>3</v>
+      </c>
+      <c r="J58">
+        <v>1500</v>
+      </c>
+      <c r="K58">
+        <v>3000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>36</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>114</v>
+      </c>
+      <c r="R58">
+        <v>212</v>
+      </c>
+      <c r="S58">
+        <v>212</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>1</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>3490</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
+        <v>110</v>
+      </c>
+      <c r="D59" t="s">
+        <v>164</v>
+      </c>
+      <c r="E59" t="s">
+        <v>48</v>
+      </c>
+      <c r="F59" t="s">
+        <v>112</v>
+      </c>
+      <c r="G59" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" t="s">
+        <v>50</v>
+      </c>
+      <c r="I59">
+        <v>3</v>
+      </c>
+      <c r="J59">
+        <v>1500</v>
+      </c>
+      <c r="K59">
+        <v>3000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>36</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>114</v>
+      </c>
+      <c r="R59">
+        <v>212</v>
+      </c>
+      <c r="S59">
+        <v>212</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>1</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>3490</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>739.88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" t="s">
+        <v>110</v>
+      </c>
+      <c r="D60" t="s">
+        <v>164</v>
+      </c>
+      <c r="E60" t="s">
+        <v>48</v>
+      </c>
+      <c r="F60" t="s">
+        <v>112</v>
+      </c>
+      <c r="G60" t="s">
+        <v>34</v>
+      </c>
+      <c r="H60" t="s">
+        <v>50</v>
+      </c>
+      <c r="I60">
+        <v>3</v>
+      </c>
+      <c r="J60">
+        <v>1500</v>
+      </c>
+      <c r="K60">
+        <v>3000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>36</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>114</v>
+      </c>
+      <c r="R60">
+        <v>319</v>
+      </c>
+      <c r="S60">
+        <v>319</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>1</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>3540</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>1129.26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>177</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61" t="s">
+        <v>178</v>
+      </c>
+      <c r="E61" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" t="s">
+        <v>112</v>
+      </c>
+      <c r="G61" t="s">
+        <v>55</v>
+      </c>
+      <c r="H61" t="s">
+        <v>50</v>
+      </c>
+      <c r="I61">
+        <v>6</v>
+      </c>
+      <c r="J61">
+        <v>2000</v>
+      </c>
+      <c r="K61">
+        <v>4000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>36</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>114</v>
+      </c>
+      <c r="R61">
+        <v>756</v>
+      </c>
+      <c r="S61">
+        <v>756</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>2</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>2240</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>1693.44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" t="s">
+        <v>110</v>
+      </c>
+      <c r="D62" t="s">
+        <v>180</v>
+      </c>
+      <c r="E62" t="s">
+        <v>48</v>
+      </c>
+      <c r="F62" t="s">
+        <v>112</v>
+      </c>
+      <c r="G62" t="s">
+        <v>181</v>
+      </c>
+      <c r="H62" t="s">
+        <v>50</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+      <c r="J62">
+        <v>1000</v>
+      </c>
+      <c r="K62">
+        <v>2000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>51</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>114</v>
+      </c>
+      <c r="R62">
+        <v>544</v>
+      </c>
+      <c r="S62">
+        <v>544</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>1</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>2220</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>1207.68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" t="s">
+        <v>116</v>
+      </c>
+      <c r="C63" t="s">
+        <v>110</v>
+      </c>
+      <c r="D63" t="s">
+        <v>183</v>
+      </c>
+      <c r="E63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F63" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" t="s">
+        <v>85</v>
+      </c>
+      <c r="H63" t="s">
+        <v>50</v>
+      </c>
+      <c r="I63">
+        <v>0.8</v>
+      </c>
+      <c r="J63">
+        <v>1000</v>
+      </c>
+      <c r="L63" t="s">
+        <v>51</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>114</v>
+      </c>
+      <c r="R63">
+        <v>1000</v>
+      </c>
+      <c r="S63">
+        <v>1000</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>1</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>2370</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" t="s">
+        <v>110</v>
+      </c>
+      <c r="D64" t="s">
+        <v>185</v>
+      </c>
+      <c r="E64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" t="s">
+        <v>112</v>
+      </c>
+      <c r="G64" t="s">
+        <v>55</v>
+      </c>
+      <c r="H64" t="s">
+        <v>50</v>
+      </c>
+      <c r="I64">
+        <v>2.5</v>
+      </c>
+      <c r="J64">
+        <v>1500</v>
+      </c>
+      <c r="K64">
+        <v>3000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>36</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>114</v>
+      </c>
+      <c r="R64">
+        <v>266</v>
+      </c>
+      <c r="S64">
+        <v>266</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>3</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>2220</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65" t="s">
+        <v>110</v>
+      </c>
+      <c r="D65" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" t="s">
+        <v>48</v>
+      </c>
+      <c r="F65" t="s">
+        <v>112</v>
+      </c>
+      <c r="G65" t="s">
+        <v>55</v>
+      </c>
+      <c r="H65" t="s">
+        <v>50</v>
+      </c>
+      <c r="I65">
+        <v>2.5</v>
+      </c>
+      <c r="J65">
+        <v>1500</v>
+      </c>
+      <c r="K65">
+        <v>3000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>36</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>114</v>
+      </c>
+      <c r="R65">
+        <v>354</v>
+      </c>
+      <c r="S65">
+        <v>354</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>4</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>2220</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>785.88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>187</v>
+      </c>
+      <c r="B66" t="s">
+        <v>109</v>
+      </c>
+      <c r="C66" t="s">
+        <v>110</v>
+      </c>
+      <c r="D66" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" t="s">
+        <v>48</v>
+      </c>
+      <c r="F66" t="s">
+        <v>112</v>
+      </c>
+      <c r="G66" t="s">
+        <v>55</v>
+      </c>
+      <c r="H66" t="s">
+        <v>50</v>
+      </c>
+      <c r="I66">
+        <v>2.5</v>
+      </c>
+      <c r="J66">
+        <v>1500</v>
+      </c>
+      <c r="K66">
+        <v>3000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>36</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>114</v>
+      </c>
+      <c r="R66">
+        <v>620</v>
+      </c>
+      <c r="S66">
+        <v>620</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>7</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>2220</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>1376.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>188</v>
+      </c>
+      <c r="B67" t="s">
+        <v>109</v>
+      </c>
+      <c r="C67" t="s">
+        <v>110</v>
+      </c>
+      <c r="D67" t="s">
+        <v>189</v>
+      </c>
+      <c r="E67" t="s">
+        <v>48</v>
+      </c>
+      <c r="F67" t="s">
+        <v>112</v>
+      </c>
+      <c r="G67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" t="s">
+        <v>50</v>
+      </c>
+      <c r="I67">
+        <v>1.5</v>
+      </c>
+      <c r="J67">
+        <v>1500</v>
+      </c>
+      <c r="K67">
+        <v>3000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>36</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>114</v>
+      </c>
+      <c r="R67">
+        <v>266</v>
+      </c>
+      <c r="S67">
+        <v>266</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>5</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>3540</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>941.64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" t="s">
+        <v>110</v>
+      </c>
+      <c r="D68" t="s">
+        <v>191</v>
+      </c>
+      <c r="E68" t="s">
+        <v>48</v>
+      </c>
+      <c r="F68" t="s">
+        <v>112</v>
+      </c>
+      <c r="G68" t="s">
+        <v>34</v>
+      </c>
+      <c r="H68" t="s">
+        <v>50</v>
+      </c>
+      <c r="I68">
+        <v>2.5</v>
+      </c>
+      <c r="J68">
+        <v>2000</v>
+      </c>
+      <c r="K68">
+        <v>4000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>36</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>114</v>
+      </c>
+      <c r="R68">
+        <v>315</v>
+      </c>
+      <c r="S68">
+        <v>315</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>2</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>3560</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>192</v>
+      </c>
+      <c r="B69" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" t="s">
+        <v>110</v>
+      </c>
+      <c r="D69" t="s">
+        <v>191</v>
+      </c>
+      <c r="E69" t="s">
+        <v>48</v>
+      </c>
+      <c r="F69" t="s">
+        <v>112</v>
+      </c>
+      <c r="G69" t="s">
+        <v>34</v>
+      </c>
+      <c r="H69" t="s">
+        <v>50</v>
+      </c>
+      <c r="I69">
+        <v>2.5</v>
+      </c>
+      <c r="J69">
+        <v>2000</v>
+      </c>
+      <c r="K69">
+        <v>4000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>36</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>114</v>
+      </c>
+      <c r="R69">
+        <v>315</v>
+      </c>
+      <c r="S69">
+        <v>315</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>2</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>3560</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" t="s">
+        <v>116</v>
+      </c>
+      <c r="C70" t="s">
+        <v>110</v>
+      </c>
+      <c r="D70" t="s">
+        <v>194</v>
+      </c>
+      <c r="E70" t="s">
+        <v>48</v>
+      </c>
+      <c r="F70" t="s">
+        <v>112</v>
+      </c>
+      <c r="G70" t="s">
+        <v>55</v>
+      </c>
+      <c r="H70" t="s">
+        <v>50</v>
+      </c>
+      <c r="I70">
+        <v>0.8</v>
+      </c>
+      <c r="J70">
+        <v>1500</v>
+      </c>
+      <c r="K70">
+        <v>3000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>36</v>
+      </c>
+      <c r="M70" t="s">
+        <v>131</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>195</v>
+      </c>
+      <c r="P70" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>114</v>
+      </c>
+      <c r="R70">
+        <v>833</v>
+      </c>
+      <c r="S70">
+        <v>833</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>29</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>2270</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>1890.91</v>
+      </c>
+      <c r="AB70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>196</v>
+      </c>
+      <c r="B71" t="s">
+        <v>116</v>
+      </c>
+      <c r="C71" t="s">
+        <v>110</v>
+      </c>
+      <c r="D71" t="s">
+        <v>194</v>
+      </c>
+      <c r="E71" t="s">
+        <v>48</v>
+      </c>
+      <c r="F71" t="s">
+        <v>112</v>
+      </c>
+      <c r="G71" t="s">
+        <v>55</v>
+      </c>
+      <c r="H71" t="s">
+        <v>50</v>
+      </c>
+      <c r="I71">
+        <v>0.8</v>
+      </c>
+      <c r="J71">
+        <v>1500</v>
+      </c>
+      <c r="K71">
+        <v>3000</v>
+      </c>
+      <c r="L71" t="s">
+        <v>36</v>
+      </c>
+      <c r="M71" t="s">
+        <v>131</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>195</v>
+      </c>
+      <c r="P71" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>114</v>
+      </c>
+      <c r="R71">
+        <v>805</v>
+      </c>
+      <c r="S71">
+        <v>805</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>28</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>2270</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>1827.35</v>
+      </c>
+      <c r="AB71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>197</v>
+      </c>
+      <c r="B72" t="s">
+        <v>116</v>
+      </c>
+      <c r="C72" t="s">
+        <v>110</v>
+      </c>
+      <c r="D72" t="s">
+        <v>198</v>
+      </c>
+      <c r="E72" t="s">
+        <v>48</v>
+      </c>
+      <c r="F72" t="s">
+        <v>112</v>
+      </c>
+      <c r="G72" t="s">
+        <v>55</v>
+      </c>
+      <c r="H72" t="s">
+        <v>50</v>
+      </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
+      <c r="J72">
+        <v>1000</v>
+      </c>
+      <c r="K72">
+        <v>2000</v>
+      </c>
+      <c r="L72" t="s">
+        <v>36</v>
+      </c>
+      <c r="M72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>114</v>
+      </c>
+      <c r="R72">
+        <v>1448</v>
+      </c>
+      <c r="S72">
+        <v>1448</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>1</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>2270</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>3286.96</v>
+      </c>
+      <c r="AB72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>199</v>
+      </c>
+      <c r="B73" t="s">
+        <v>120</v>
+      </c>
+      <c r="C73" t="s">
+        <v>110</v>
+      </c>
+      <c r="D73" t="s">
+        <v>200</v>
+      </c>
+      <c r="E73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F73" t="s">
+        <v>112</v>
+      </c>
+      <c r="G73" t="s">
+        <v>78</v>
+      </c>
+      <c r="H73" t="s">
+        <v>50</v>
+      </c>
+      <c r="I73">
+        <v>4</v>
+      </c>
+      <c r="J73">
+        <v>1000</v>
+      </c>
+      <c r="K73">
+        <v>2000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>36</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>114</v>
+      </c>
+      <c r="R73">
+        <v>384</v>
+      </c>
+      <c r="S73">
+        <v>384</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>6</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>1370</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>201</v>
+      </c>
+      <c r="B74" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" t="s">
+        <v>110</v>
+      </c>
+      <c r="D74" t="s">
+        <v>123</v>
+      </c>
+      <c r="E74" t="s">
+        <v>48</v>
+      </c>
+      <c r="F74" t="s">
+        <v>112</v>
+      </c>
+      <c r="G74" t="s">
+        <v>34</v>
+      </c>
+      <c r="H74" t="s">
+        <v>50</v>
+      </c>
+      <c r="I74">
+        <v>6</v>
+      </c>
+      <c r="J74">
+        <v>1500</v>
+      </c>
+      <c r="K74">
+        <v>3000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>36</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>114</v>
+      </c>
+      <c r="R74">
+        <v>850</v>
+      </c>
+      <c r="S74">
+        <v>850</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>4</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>3540</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>202</v>
+      </c>
+      <c r="B75" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" t="s">
+        <v>203</v>
+      </c>
+      <c r="E75" t="s">
+        <v>48</v>
+      </c>
+      <c r="F75" t="s">
+        <v>112</v>
+      </c>
+      <c r="G75" t="s">
+        <v>55</v>
+      </c>
+      <c r="H75" t="s">
+        <v>50</v>
+      </c>
+      <c r="I75">
+        <v>0.8</v>
+      </c>
+      <c r="J75">
+        <v>1250</v>
+      </c>
+      <c r="K75">
+        <v>2500</v>
+      </c>
+      <c r="L75" t="s">
+        <v>36</v>
+      </c>
+      <c r="M75" t="s">
+        <v>204</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>114</v>
+      </c>
+      <c r="R75">
+        <v>430</v>
+      </c>
+      <c r="S75">
+        <v>430</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>2270</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>976.1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>205</v>
+      </c>
+      <c r="B76" t="s">
+        <v>109</v>
+      </c>
+      <c r="C76" t="s">
+        <v>110</v>
+      </c>
+      <c r="D76" t="s">
+        <v>206</v>
+      </c>
+      <c r="E76" t="s">
+        <v>48</v>
+      </c>
+      <c r="F76" t="s">
+        <v>112</v>
+      </c>
+      <c r="G76" t="s">
+        <v>55</v>
+      </c>
+      <c r="H76" t="s">
+        <v>50</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+      <c r="J76">
+        <v>1000</v>
+      </c>
+      <c r="K76">
+        <v>2000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>36</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>114</v>
+      </c>
+      <c r="R76">
+        <v>283</v>
+      </c>
+      <c r="S76">
+        <v>283</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>9</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>2220</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>207</v>
+      </c>
+      <c r="B77" t="s">
+        <v>109</v>
+      </c>
+      <c r="C77" t="s">
+        <v>110</v>
+      </c>
+      <c r="D77" t="s">
+        <v>141</v>
+      </c>
+      <c r="E77" t="s">
+        <v>48</v>
+      </c>
+      <c r="F77" t="s">
+        <v>112</v>
+      </c>
+      <c r="G77" t="s">
+        <v>78</v>
+      </c>
+      <c r="H77" t="s">
+        <v>50</v>
+      </c>
+      <c r="I77">
+        <v>3</v>
+      </c>
+      <c r="J77">
+        <v>1500</v>
+      </c>
+      <c r="K77">
+        <v>3000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>36</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>114</v>
+      </c>
+      <c r="R77">
+        <v>637</v>
+      </c>
+      <c r="S77">
+        <v>637</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>6</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>1370</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>872.69</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>208</v>
+      </c>
+      <c r="B78" t="s">
+        <v>116</v>
+      </c>
+      <c r="C78" t="s">
+        <v>110</v>
+      </c>
+      <c r="D78" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" t="s">
+        <v>48</v>
+      </c>
+      <c r="F78" t="s">
+        <v>112</v>
+      </c>
+      <c r="G78" t="s">
+        <v>55</v>
+      </c>
+      <c r="H78" t="s">
+        <v>50</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <v>1000</v>
+      </c>
+      <c r="K78">
+        <v>2000</v>
+      </c>
+      <c r="L78" t="s">
+        <v>36</v>
+      </c>
+      <c r="M78" t="s">
+        <v>131</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>114</v>
+      </c>
+      <c r="R78">
+        <v>1482</v>
+      </c>
+      <c r="S78">
+        <v>1482</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>1</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>2220</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>3290.04</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>210</v>
+      </c>
+      <c r="B79" t="s">
+        <v>109</v>
+      </c>
+      <c r="C79" t="s">
+        <v>110</v>
+      </c>
+      <c r="D79" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" t="s">
+        <v>48</v>
+      </c>
+      <c r="F79" t="s">
+        <v>112</v>
+      </c>
+      <c r="G79" t="s">
+        <v>126</v>
+      </c>
+      <c r="H79" t="s">
+        <v>50</v>
+      </c>
+      <c r="I79">
+        <v>4</v>
+      </c>
+      <c r="J79">
+        <v>1500</v>
+      </c>
+      <c r="K79">
+        <v>3000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>67</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>114</v>
+      </c>
+      <c r="R79">
+        <v>1133</v>
+      </c>
+      <c r="S79">
+        <v>1133</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>8</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>3540</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>4010.82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>212</v>
+      </c>
+      <c r="B80" t="s">
+        <v>109</v>
+      </c>
+      <c r="C80" t="s">
+        <v>110</v>
+      </c>
+      <c r="D80" t="s">
+        <v>213</v>
+      </c>
+      <c r="E80" t="s">
+        <v>48</v>
+      </c>
+      <c r="F80" t="s">
+        <v>112</v>
+      </c>
+      <c r="G80" t="s">
+        <v>55</v>
+      </c>
+      <c r="H80" t="s">
+        <v>50</v>
+      </c>
+      <c r="I80">
+        <v>5</v>
+      </c>
+      <c r="J80">
+        <v>2000</v>
+      </c>
+      <c r="K80">
+        <v>4000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>36</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>114</v>
+      </c>
+      <c r="R80">
+        <v>1259</v>
+      </c>
+      <c r="S80">
+        <v>1259</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>4</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>2290</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>2883.11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>214</v>
+      </c>
+      <c r="B81" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81" t="s">
+        <v>110</v>
+      </c>
+      <c r="D81" t="s">
+        <v>215</v>
+      </c>
+      <c r="E81" t="s">
+        <v>48</v>
+      </c>
+      <c r="F81" t="s">
+        <v>112</v>
+      </c>
+      <c r="G81" t="s">
+        <v>55</v>
+      </c>
+      <c r="H81" t="s">
+        <v>50</v>
+      </c>
+      <c r="I81">
+        <v>4</v>
+      </c>
+      <c r="J81">
+        <v>2000</v>
+      </c>
+      <c r="K81">
+        <v>4000</v>
+      </c>
+      <c r="L81" t="s">
+        <v>36</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>114</v>
+      </c>
+      <c r="R81">
+        <v>1007</v>
+      </c>
+      <c r="S81">
+        <v>1007</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>4</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>2290</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>2306.03</v>
+      </c>
+      <c r="AB81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>216</v>
+      </c>
+      <c r="B82" t="s">
+        <v>120</v>
+      </c>
+      <c r="C82" t="s">
+        <v>110</v>
+      </c>
+      <c r="D82" t="s">
+        <v>217</v>
+      </c>
+      <c r="E82" t="s">
+        <v>48</v>
+      </c>
+      <c r="F82" t="s">
+        <v>112</v>
+      </c>
+      <c r="G82" t="s">
+        <v>55</v>
+      </c>
+      <c r="H82" t="s">
+        <v>50</v>
+      </c>
+      <c r="I82">
+        <v>6</v>
+      </c>
+      <c r="J82">
+        <v>1500</v>
+      </c>
+      <c r="K82">
+        <v>3000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>36</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>195</v>
+      </c>
+      <c r="P82" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>114</v>
+      </c>
+      <c r="R82">
+        <v>1487</v>
+      </c>
+      <c r="S82">
+        <v>1487</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>7</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>2270</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>3375.49</v>
+      </c>
+      <c r="AB82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>218</v>
+      </c>
+      <c r="B83" t="s">
+        <v>109</v>
+      </c>
+      <c r="C83" t="s">
+        <v>110</v>
+      </c>
+      <c r="D83" t="s">
+        <v>219</v>
+      </c>
+      <c r="E83" t="s">
+        <v>48</v>
+      </c>
+      <c r="F83" t="s">
+        <v>112</v>
+      </c>
+      <c r="G83" t="s">
+        <v>55</v>
+      </c>
+      <c r="H83" t="s">
+        <v>50</v>
+      </c>
+      <c r="I83">
+        <v>8</v>
+      </c>
+      <c r="J83">
+        <v>2000</v>
+      </c>
+      <c r="K83">
+        <v>6000</v>
+      </c>
+      <c r="L83" t="s">
+        <v>113</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>114</v>
+      </c>
+      <c r="R83">
+        <v>755</v>
+      </c>
+      <c r="S83">
+        <v>755</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>1</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>2040</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>1540.2</v>
+      </c>
+      <c r="AB83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>220</v>
+      </c>
+      <c r="B84" t="s">
+        <v>116</v>
+      </c>
+      <c r="C84" t="s">
+        <v>110</v>
+      </c>
+      <c r="D84" t="s">
+        <v>221</v>
+      </c>
+      <c r="E84" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" t="s">
+        <v>112</v>
+      </c>
+      <c r="G84" t="s">
+        <v>55</v>
+      </c>
+      <c r="H84" t="s">
+        <v>50</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>1250</v>
+      </c>
+      <c r="K84">
+        <v>2500</v>
+      </c>
+      <c r="L84" t="s">
+        <v>36</v>
+      </c>
+      <c r="M84" t="s">
+        <v>222</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>223</v>
+      </c>
+      <c r="P84" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>114</v>
+      </c>
+      <c r="R84">
+        <v>1019</v>
+      </c>
+      <c r="S84">
+        <v>1019</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>41</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>2220</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>2262.18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>224</v>
+      </c>
+      <c r="B85" t="s">
+        <v>120</v>
+      </c>
+      <c r="C85" t="s">
+        <v>110</v>
+      </c>
+      <c r="D85" t="s">
+        <v>225</v>
+      </c>
+      <c r="E85" t="s">
+        <v>48</v>
+      </c>
+      <c r="F85" t="s">
+        <v>112</v>
+      </c>
+      <c r="G85" t="s">
+        <v>55</v>
+      </c>
+      <c r="H85" t="s">
+        <v>50</v>
+      </c>
+      <c r="I85">
+        <v>8</v>
+      </c>
+      <c r="J85">
+        <v>1000</v>
+      </c>
+      <c r="K85">
+        <v>2000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>113</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>114</v>
+      </c>
+      <c r="R85">
+        <v>504</v>
+      </c>
+      <c r="S85">
+        <v>504</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>4</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>2020</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>1018.08</v>
+      </c>
+      <c r="AB85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>226</v>
+      </c>
+      <c r="B86" t="s">
+        <v>109</v>
+      </c>
+      <c r="C86" t="s">
+        <v>110</v>
+      </c>
+      <c r="D86" t="s">
+        <v>227</v>
+      </c>
+      <c r="E86" t="s">
+        <v>48</v>
+      </c>
+      <c r="F86" t="s">
+        <v>112</v>
+      </c>
+      <c r="G86" t="s">
+        <v>55</v>
+      </c>
+      <c r="H86" t="s">
+        <v>50</v>
+      </c>
+      <c r="I86">
+        <v>12</v>
+      </c>
+      <c r="J86">
+        <v>1000</v>
+      </c>
+      <c r="K86">
+        <v>2000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>113</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>114</v>
+      </c>
+      <c r="R86">
+        <v>1322</v>
+      </c>
+      <c r="S86">
+        <v>1322</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>7</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>2070</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>2736.54</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>228</v>
+      </c>
+      <c r="B87" t="s">
+        <v>116</v>
+      </c>
+      <c r="C87" t="s">
+        <v>110</v>
+      </c>
+      <c r="D87" t="s">
+        <v>133</v>
+      </c>
+      <c r="E87" t="s">
+        <v>48</v>
+      </c>
+      <c r="F87" t="s">
+        <v>112</v>
+      </c>
+      <c r="G87" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" t="s">
+        <v>50</v>
+      </c>
+      <c r="I87">
+        <v>2.5</v>
+      </c>
+      <c r="J87">
+        <v>1500</v>
+      </c>
+      <c r="K87">
+        <v>3000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>36</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>114</v>
+      </c>
+      <c r="R87">
+        <v>534</v>
+      </c>
+      <c r="S87">
+        <v>534</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>6</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>3540</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>1890.36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>229</v>
+      </c>
+      <c r="B88" t="s">
+        <v>116</v>
+      </c>
+      <c r="C88" t="s">
+        <v>110</v>
+      </c>
+      <c r="D88" t="s">
+        <v>230</v>
+      </c>
+      <c r="E88" t="s">
+        <v>48</v>
+      </c>
+      <c r="F88" t="s">
+        <v>112</v>
+      </c>
+      <c r="G88" t="s">
+        <v>55</v>
+      </c>
+      <c r="H88" t="s">
+        <v>50</v>
+      </c>
+      <c r="I88">
+        <v>0.8</v>
+      </c>
+      <c r="J88">
+        <v>1250</v>
+      </c>
+      <c r="K88">
+        <v>2500</v>
+      </c>
+      <c r="L88" t="s">
+        <v>36</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>114</v>
+      </c>
+      <c r="R88">
+        <v>2033</v>
+      </c>
+      <c r="S88">
+        <v>2033</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>101</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>2370</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>4818.21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>231</v>
+      </c>
+      <c r="B89" t="s">
+        <v>116</v>
+      </c>
+      <c r="C89" t="s">
+        <v>110</v>
+      </c>
+      <c r="D89" t="s">
+        <v>232</v>
+      </c>
+      <c r="E89" t="s">
+        <v>48</v>
+      </c>
+      <c r="F89" t="s">
+        <v>112</v>
+      </c>
+      <c r="G89" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89" t="s">
+        <v>50</v>
+      </c>
+      <c r="I89">
+        <v>2</v>
+      </c>
+      <c r="J89">
+        <v>1000</v>
+      </c>
+      <c r="K89">
+        <v>2000</v>
+      </c>
+      <c r="L89" t="s">
+        <v>36</v>
+      </c>
+      <c r="M89" t="s">
+        <v>131</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>114</v>
+      </c>
+      <c r="R89">
+        <v>1046</v>
+      </c>
+      <c r="S89">
+        <v>1046</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>33</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>3540</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>3702.84</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>233</v>
+      </c>
+      <c r="B90" t="s">
+        <v>109</v>
+      </c>
+      <c r="C90" t="s">
+        <v>110</v>
+      </c>
+      <c r="D90" t="s">
+        <v>234</v>
+      </c>
+      <c r="E90" t="s">
+        <v>48</v>
+      </c>
+      <c r="F90" t="s">
+        <v>112</v>
+      </c>
+      <c r="G90" t="s">
+        <v>55</v>
+      </c>
+      <c r="H90" t="s">
+        <v>50</v>
+      </c>
+      <c r="I90">
+        <v>4</v>
+      </c>
+      <c r="J90">
+        <v>1500</v>
+      </c>
+      <c r="K90">
+        <v>3000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>36</v>
+      </c>
+      <c r="M90" t="s">
+        <v>37</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>114</v>
+      </c>
+      <c r="R90">
+        <v>142</v>
+      </c>
+      <c r="S90">
+        <v>142</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>1</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>2170</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>235</v>
+      </c>
+      <c r="B91" t="s">
+        <v>109</v>
+      </c>
+      <c r="C91" t="s">
+        <v>110</v>
+      </c>
+      <c r="D91" t="s">
+        <v>236</v>
+      </c>
+      <c r="E91" t="s">
+        <v>48</v>
+      </c>
+      <c r="F91" t="s">
+        <v>112</v>
+      </c>
+      <c r="G91" t="s">
+        <v>55</v>
+      </c>
+      <c r="H91" t="s">
+        <v>50</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
+      </c>
+      <c r="J91">
+        <v>2000</v>
+      </c>
+      <c r="K91">
+        <v>4000</v>
+      </c>
+      <c r="L91" t="s">
+        <v>36</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>114</v>
+      </c>
+      <c r="R91">
+        <v>126</v>
+      </c>
+      <c r="S91">
+        <v>126</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>1</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>2190</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>237</v>
+      </c>
+      <c r="B92" t="s">
+        <v>116</v>
+      </c>
+      <c r="C92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D92" t="s">
+        <v>238</v>
+      </c>
+      <c r="E92" t="s">
+        <v>48</v>
+      </c>
+      <c r="F92" t="s">
+        <v>112</v>
+      </c>
+      <c r="G92" t="s">
+        <v>55</v>
+      </c>
+      <c r="H92" t="s">
+        <v>50</v>
+      </c>
+      <c r="I92">
+        <v>0.8</v>
+      </c>
+      <c r="J92">
+        <v>1000</v>
+      </c>
+      <c r="K92">
+        <v>2000</v>
+      </c>
+      <c r="L92" t="s">
+        <v>36</v>
+      </c>
+      <c r="M92" t="s">
+        <v>131</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>38</v>
+      </c>
+      <c r="P92" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>114</v>
+      </c>
+      <c r="R92">
+        <v>1216</v>
+      </c>
+      <c r="S92">
+        <v>1216</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>96</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>2320</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>2821.12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>239</v>
+      </c>
+      <c r="B93" t="s">
+        <v>109</v>
+      </c>
+      <c r="C93" t="s">
+        <v>110</v>
+      </c>
+      <c r="D93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E93" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" t="s">
+        <v>112</v>
+      </c>
+      <c r="G93" t="s">
+        <v>55</v>
+      </c>
+      <c r="H93" t="s">
+        <v>50</v>
+      </c>
+      <c r="I93">
+        <v>0.8</v>
+      </c>
+      <c r="J93">
+        <v>1250</v>
+      </c>
+      <c r="K93">
+        <v>2500</v>
+      </c>
+      <c r="L93" t="s">
+        <v>36</v>
+      </c>
+      <c r="M93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" t="s">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>114</v>
+      </c>
+      <c r="R93">
+        <v>334</v>
+      </c>
+      <c r="S93">
+        <v>334</v>
+      </c>
+      <c r="T93" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93">
+        <v>17</v>
+      </c>
+      <c r="V93" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93">
+        <v>2320</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA93">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>240</v>
+      </c>
+      <c r="B94" t="s">
+        <v>109</v>
+      </c>
+      <c r="C94" t="s">
+        <v>110</v>
+      </c>
+      <c r="D94" t="s">
+        <v>230</v>
+      </c>
+      <c r="E94" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" t="s">
+        <v>112</v>
+      </c>
+      <c r="G94" t="s">
+        <v>55</v>
+      </c>
+      <c r="H94" t="s">
+        <v>50</v>
+      </c>
+      <c r="I94">
+        <v>0.8</v>
+      </c>
+      <c r="J94">
+        <v>1250</v>
+      </c>
+      <c r="K94">
+        <v>2500</v>
+      </c>
+      <c r="L94" t="s">
+        <v>36</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
+      </c>
+      <c r="N94" t="s">
+        <v>37</v>
+      </c>
+      <c r="O94" t="s">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>114</v>
+      </c>
+      <c r="R94">
+        <v>334</v>
+      </c>
+      <c r="S94">
+        <v>334</v>
+      </c>
+      <c r="T94" t="s">
+        <v>41</v>
+      </c>
+      <c r="U94">
+        <v>17</v>
+      </c>
+      <c r="V94" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94">
+        <v>2320</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA94">
+        <v>774.88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>241</v>
+      </c>
+      <c r="B95" t="s">
+        <v>109</v>
+      </c>
+      <c r="C95" t="s">
+        <v>110</v>
+      </c>
+      <c r="D95" t="s">
+        <v>230</v>
+      </c>
+      <c r="E95" t="s">
+        <v>48</v>
+      </c>
+      <c r="F95" t="s">
+        <v>112</v>
+      </c>
+      <c r="G95" t="s">
+        <v>55</v>
+      </c>
+      <c r="H95" t="s">
+        <v>50</v>
+      </c>
+      <c r="I95">
+        <v>0.8</v>
+      </c>
+      <c r="J95">
+        <v>1250</v>
+      </c>
+      <c r="K95">
+        <v>2500</v>
+      </c>
+      <c r="L95" t="s">
+        <v>36</v>
+      </c>
+      <c r="M95" t="s">
+        <v>37</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>114</v>
+      </c>
+      <c r="R95">
+        <v>551</v>
+      </c>
+      <c r="S95">
+        <v>551</v>
+      </c>
+      <c r="T95" t="s">
+        <v>41</v>
+      </c>
+      <c r="U95">
+        <v>28</v>
+      </c>
+      <c r="V95" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95">
+        <v>2320</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA95">
+        <v>1278.32</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>242</v>
+      </c>
+      <c r="B96" t="s">
+        <v>116</v>
+      </c>
+      <c r="C96" t="s">
+        <v>110</v>
+      </c>
+      <c r="D96" t="s">
+        <v>243</v>
+      </c>
+      <c r="E96" t="s">
+        <v>48</v>
+      </c>
+      <c r="F96" t="s">
+        <v>112</v>
+      </c>
+      <c r="G96" t="s">
+        <v>34</v>
+      </c>
+      <c r="H96" t="s">
+        <v>50</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
+        <v>1250</v>
+      </c>
+      <c r="K96">
+        <v>2500</v>
+      </c>
+      <c r="L96" t="s">
+        <v>36</v>
+      </c>
+      <c r="M96" t="s">
+        <v>131</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
+      </c>
+      <c r="P96" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>114</v>
+      </c>
+      <c r="R96">
+        <v>612</v>
+      </c>
+      <c r="S96">
+        <v>612</v>
+      </c>
+      <c r="T96" t="s">
+        <v>41</v>
+      </c>
+      <c r="U96">
+        <v>12</v>
+      </c>
+      <c r="V96" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X96">
+        <v>3490</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA96">
+        <v>2135.88</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>244</v>
+      </c>
+      <c r="B97" t="s">
+        <v>116</v>
+      </c>
+      <c r="C97" t="s">
+        <v>110</v>
+      </c>
+      <c r="D97" t="s">
+        <v>209</v>
+      </c>
+      <c r="E97" t="s">
+        <v>48</v>
+      </c>
+      <c r="F97" t="s">
+        <v>112</v>
+      </c>
+      <c r="G97" t="s">
+        <v>55</v>
+      </c>
+      <c r="H97" t="s">
+        <v>50</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>1000</v>
+      </c>
+      <c r="K97">
+        <v>2000</v>
+      </c>
+      <c r="L97" t="s">
+        <v>36</v>
+      </c>
+      <c r="M97" t="s">
+        <v>131</v>
+      </c>
+      <c r="N97" t="s">
+        <v>37</v>
+      </c>
+      <c r="O97" t="s">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>114</v>
+      </c>
+      <c r="R97">
+        <v>752</v>
+      </c>
+      <c r="S97">
+        <v>752</v>
+      </c>
+      <c r="T97" t="s">
+        <v>41</v>
+      </c>
+      <c r="U97">
+        <v>48</v>
+      </c>
+      <c r="V97" t="s">
+        <v>43</v>
+      </c>
+      <c r="W97" t="s">
+        <v>43</v>
+      </c>
+      <c r="X97">
+        <v>2170</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA97">
+        <v>1631.84</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>245</v>
+      </c>
+      <c r="B98" t="s">
+        <v>120</v>
+      </c>
+      <c r="C98" t="s">
+        <v>110</v>
+      </c>
+      <c r="D98" t="s">
+        <v>246</v>
+      </c>
+      <c r="E98" t="s">
+        <v>48</v>
+      </c>
+      <c r="F98" t="s">
+        <v>112</v>
+      </c>
+      <c r="G98" t="s">
+        <v>126</v>
+      </c>
+      <c r="H98" t="s">
+        <v>50</v>
+      </c>
+      <c r="I98">
+        <v>3</v>
+      </c>
+      <c r="J98">
+        <v>1500</v>
+      </c>
+      <c r="K98">
+        <v>3000</v>
+      </c>
+      <c r="L98" t="s">
+        <v>36</v>
+      </c>
+      <c r="M98" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" t="s">
+        <v>38</v>
+      </c>
+      <c r="P98" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>114</v>
+      </c>
+      <c r="R98">
+        <v>106</v>
+      </c>
+      <c r="S98">
+        <v>106</v>
+      </c>
+      <c r="T98" t="s">
+        <v>41</v>
+      </c>
+      <c r="U98">
+        <v>1</v>
+      </c>
+      <c r="V98" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98">
+        <v>3640</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA98">
+        <v>385.84</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>247</v>
+      </c>
+      <c r="B99" t="s">
+        <v>116</v>
+      </c>
+      <c r="C99" t="s">
+        <v>110</v>
+      </c>
+      <c r="D99" t="s">
+        <v>189</v>
+      </c>
+      <c r="E99" t="s">
+        <v>48</v>
+      </c>
+      <c r="F99" t="s">
+        <v>112</v>
+      </c>
+      <c r="G99" t="s">
+        <v>34</v>
+      </c>
+      <c r="H99" t="s">
+        <v>50</v>
+      </c>
+      <c r="I99">
+        <v>1.5</v>
+      </c>
+      <c r="J99">
+        <v>1500</v>
+      </c>
+      <c r="K99">
+        <v>3000</v>
+      </c>
+      <c r="L99" t="s">
+        <v>36</v>
+      </c>
+      <c r="M99" t="s">
+        <v>37</v>
+      </c>
+      <c r="N99" t="s">
+        <v>37</v>
+      </c>
+      <c r="O99" t="s">
+        <v>38</v>
+      </c>
+      <c r="P99" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>114</v>
+      </c>
+      <c r="R99">
+        <v>330</v>
+      </c>
+      <c r="S99">
+        <v>330</v>
+      </c>
+      <c r="T99" t="s">
+        <v>41</v>
+      </c>
+      <c r="U99">
+        <v>6</v>
+      </c>
+      <c r="V99" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99">
+        <v>3540</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA99">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>248</v>
+      </c>
+      <c r="B100" t="s">
+        <v>109</v>
+      </c>
+      <c r="C100" t="s">
+        <v>110</v>
+      </c>
+      <c r="D100" t="s">
+        <v>249</v>
+      </c>
+      <c r="E100" t="s">
+        <v>48</v>
+      </c>
+      <c r="F100" t="s">
+        <v>112</v>
+      </c>
+      <c r="G100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H100" t="s">
+        <v>50</v>
+      </c>
+      <c r="I100">
+        <v>3</v>
+      </c>
+      <c r="J100">
+        <v>1000</v>
+      </c>
+      <c r="K100">
+        <v>2000</v>
+      </c>
+      <c r="L100" t="s">
+        <v>36</v>
+      </c>
+      <c r="M100" t="s">
+        <v>37</v>
+      </c>
+      <c r="N100" t="s">
+        <v>37</v>
+      </c>
+      <c r="O100" t="s">
+        <v>38</v>
+      </c>
+      <c r="P100" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>114</v>
+      </c>
+      <c r="R100">
+        <v>1464</v>
+      </c>
+      <c r="S100">
+        <v>1464</v>
+      </c>
+      <c r="T100" t="s">
+        <v>41</v>
+      </c>
+      <c r="U100">
+        <v>31</v>
+      </c>
+      <c r="V100" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100">
+        <v>2270</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA100">
+        <v>3323.28</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>250</v>
+      </c>
+      <c r="B101" t="s">
+        <v>109</v>
+      </c>
+      <c r="C101" t="s">
+        <v>110</v>
+      </c>
+      <c r="D101" t="s">
+        <v>249</v>
+      </c>
+      <c r="E101" t="s">
+        <v>48</v>
+      </c>
+      <c r="F101" t="s">
+        <v>112</v>
+      </c>
+      <c r="G101" t="s">
+        <v>55</v>
+      </c>
+      <c r="H101" t="s">
+        <v>50</v>
+      </c>
+      <c r="I101">
+        <v>3</v>
+      </c>
+      <c r="J101">
+        <v>1000</v>
+      </c>
+      <c r="K101">
+        <v>2000</v>
+      </c>
+      <c r="L101" t="s">
+        <v>36</v>
+      </c>
+      <c r="M101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N101" t="s">
+        <v>37</v>
+      </c>
+      <c r="O101" t="s">
+        <v>38</v>
+      </c>
+      <c r="P101" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>114</v>
+      </c>
+      <c r="R101">
+        <v>94</v>
+      </c>
+      <c r="S101">
+        <v>94</v>
+      </c>
+      <c r="T101" t="s">
+        <v>41</v>
+      </c>
+      <c r="U101">
+        <v>2</v>
+      </c>
+      <c r="V101" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101">
+        <v>2170</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA101">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>251</v>
+      </c>
+      <c r="B102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C102" t="s">
+        <v>110</v>
+      </c>
+      <c r="D102" t="s">
+        <v>252</v>
+      </c>
+      <c r="E102" t="s">
+        <v>48</v>
+      </c>
+      <c r="F102" t="s">
+        <v>33</v>
+      </c>
+      <c r="G102" t="s">
+        <v>253</v>
+      </c>
+      <c r="H102" t="s">
+        <v>50</v>
+      </c>
+      <c r="I102">
+        <v>1.2</v>
+      </c>
+      <c r="J102">
+        <v>1250</v>
+      </c>
+      <c r="L102" t="s">
+        <v>36</v>
+      </c>
+      <c r="M102" t="s">
+        <v>37</v>
+      </c>
+      <c r="N102" t="s">
+        <v>37</v>
+      </c>
+      <c r="O102" t="s">
+        <v>38</v>
+      </c>
+      <c r="P102" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>114</v>
+      </c>
+      <c r="R102">
+        <v>1420</v>
+      </c>
+      <c r="S102">
+        <v>1420</v>
+      </c>
+      <c r="T102" t="s">
+        <v>41</v>
+      </c>
+      <c r="U102">
+        <v>1</v>
+      </c>
+      <c r="V102" t="s">
+        <v>43</v>
+      </c>
+      <c r="W102" t="s">
+        <v>43</v>
+      </c>
+      <c r="X102">
+        <v>1420</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA102">
+        <v>2016.4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>254</v>
+      </c>
+      <c r="B103" t="s">
+        <v>116</v>
+      </c>
+      <c r="C103" t="s">
+        <v>110</v>
+      </c>
+      <c r="D103" t="s">
+        <v>255</v>
+      </c>
+      <c r="E103" t="s">
+        <v>48</v>
+      </c>
+      <c r="F103" t="s">
+        <v>112</v>
+      </c>
+      <c r="G103" t="s">
+        <v>78</v>
+      </c>
+      <c r="H103" t="s">
+        <v>50</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103">
+        <v>1500</v>
+      </c>
+      <c r="K103">
+        <v>3000</v>
+      </c>
+      <c r="L103" t="s">
+        <v>51</v>
+      </c>
+      <c r="M103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N103" t="s">
+        <v>37</v>
+      </c>
+      <c r="O103" t="s">
+        <v>38</v>
+      </c>
+      <c r="P103" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>114</v>
+      </c>
+      <c r="R103">
+        <v>414</v>
+      </c>
+      <c r="S103">
+        <v>414</v>
+      </c>
+      <c r="T103" t="s">
+        <v>41</v>
+      </c>
+      <c r="U103">
+        <v>12</v>
+      </c>
+      <c r="V103" t="s">
+        <v>43</v>
+      </c>
+      <c r="W103" t="s">
+        <v>43</v>
+      </c>
+      <c r="X103">
+        <v>1370</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA103">
+        <v>567.18</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>256</v>
+      </c>
+      <c r="B104" t="s">
+        <v>116</v>
+      </c>
+      <c r="C104" t="s">
+        <v>110</v>
+      </c>
+      <c r="D104" t="s">
+        <v>257</v>
+      </c>
+      <c r="E104" t="s">
+        <v>48</v>
+      </c>
+      <c r="F104" t="s">
+        <v>112</v>
+      </c>
+      <c r="G104" t="s">
+        <v>78</v>
+      </c>
+      <c r="H104" t="s">
+        <v>50</v>
+      </c>
+      <c r="I104">
+        <v>0.8</v>
+      </c>
+      <c r="J104">
+        <v>1500</v>
+      </c>
+      <c r="K104">
+        <v>3000</v>
+      </c>
+      <c r="L104" t="s">
+        <v>51</v>
+      </c>
+      <c r="M104" t="s">
+        <v>37</v>
+      </c>
+      <c r="N104" t="s">
+        <v>37</v>
+      </c>
+      <c r="O104" t="s">
+        <v>258</v>
+      </c>
+      <c r="P104" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>114</v>
+      </c>
+      <c r="R104">
+        <v>2584</v>
+      </c>
+      <c r="S104">
+        <v>2584</v>
+      </c>
+      <c r="T104" t="s">
+        <v>41</v>
+      </c>
+      <c r="U104">
+        <v>94</v>
+      </c>
+      <c r="V104" t="s">
+        <v>43</v>
+      </c>
+      <c r="W104" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104">
+        <v>1520</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA104">
+        <v>3927.68</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>259</v>
+      </c>
+      <c r="B105" t="s">
+        <v>116</v>
+      </c>
+      <c r="C105" t="s">
+        <v>110</v>
+      </c>
+      <c r="D105" t="s">
+        <v>260</v>
+      </c>
+      <c r="E105" t="s">
+        <v>48</v>
+      </c>
+      <c r="F105" t="s">
+        <v>112</v>
+      </c>
+      <c r="G105" t="s">
+        <v>78</v>
+      </c>
+      <c r="H105" t="s">
+        <v>50</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>1250</v>
+      </c>
+      <c r="K105">
+        <v>2500</v>
+      </c>
+      <c r="L105" t="s">
+        <v>51</v>
+      </c>
+      <c r="M105" t="s">
+        <v>37</v>
+      </c>
+      <c r="N105" t="s">
+        <v>37</v>
+      </c>
+      <c r="O105" t="s">
+        <v>38</v>
+      </c>
+      <c r="P105" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>114</v>
+      </c>
+      <c r="R105">
+        <v>668</v>
+      </c>
+      <c r="S105">
+        <v>668</v>
+      </c>
+      <c r="T105" t="s">
+        <v>41</v>
+      </c>
+      <c r="U105">
+        <v>1</v>
+      </c>
+      <c r="V105" t="s">
+        <v>43</v>
+      </c>
+      <c r="W105" t="s">
+        <v>43</v>
+      </c>
+      <c r="X105">
+        <v>1370</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA105">
+        <v>915.16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>261</v>
+      </c>
+      <c r="B106" t="s">
+        <v>116</v>
+      </c>
+      <c r="C106" t="s">
+        <v>110</v>
+      </c>
+      <c r="D106" t="s">
+        <v>147</v>
+      </c>
+      <c r="E106" t="s">
+        <v>48</v>
+      </c>
+      <c r="F106" t="s">
+        <v>112</v>
+      </c>
+      <c r="G106" t="s">
+        <v>55</v>
+      </c>
+      <c r="H106" t="s">
+        <v>50</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
+      </c>
+      <c r="J106">
+        <v>1250</v>
+      </c>
+      <c r="K106">
+        <v>2500</v>
+      </c>
+      <c r="L106" t="s">
+        <v>36</v>
+      </c>
+      <c r="M106" t="s">
+        <v>37</v>
+      </c>
+      <c r="N106" t="s">
+        <v>37</v>
+      </c>
+      <c r="O106" t="s">
+        <v>38</v>
+      </c>
+      <c r="P106" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>114</v>
+      </c>
+      <c r="R106">
+        <v>358</v>
+      </c>
+      <c r="S106">
+        <v>358</v>
+      </c>
+      <c r="T106" t="s">
+        <v>41</v>
+      </c>
+      <c r="U106">
+        <v>7</v>
+      </c>
+      <c r="V106" t="s">
+        <v>43</v>
+      </c>
+      <c r="W106" t="s">
+        <v>43</v>
+      </c>
+      <c r="X106">
+        <v>2220</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA106">
+        <v>794.76</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>262</v>
+      </c>
+      <c r="B107" t="s">
+        <v>109</v>
+      </c>
+      <c r="C107" t="s">
+        <v>110</v>
+      </c>
+      <c r="D107" t="s">
+        <v>263</v>
+      </c>
+      <c r="E107" t="s">
+        <v>48</v>
+      </c>
+      <c r="F107" t="s">
+        <v>112</v>
+      </c>
+      <c r="G107" t="s">
+        <v>34</v>
+      </c>
+      <c r="H107" t="s">
+        <v>50</v>
+      </c>
+      <c r="I107">
+        <v>3</v>
+      </c>
+      <c r="J107">
+        <v>2000</v>
+      </c>
+      <c r="K107">
+        <v>4000</v>
+      </c>
+      <c r="L107" t="s">
+        <v>36</v>
+      </c>
+      <c r="M107" t="s">
+        <v>37</v>
+      </c>
+      <c r="N107" t="s">
+        <v>37</v>
+      </c>
+      <c r="O107" t="s">
+        <v>38</v>
+      </c>
+      <c r="P107" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>114</v>
+      </c>
+      <c r="R107">
+        <v>189</v>
+      </c>
+      <c r="S107">
+        <v>189</v>
+      </c>
+      <c r="T107" t="s">
+        <v>41</v>
+      </c>
+      <c r="U107">
+        <v>1</v>
+      </c>
+      <c r="V107" t="s">
+        <v>43</v>
+      </c>
+      <c r="W107" t="s">
+        <v>43</v>
+      </c>
+      <c r="X107">
+        <v>3510</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA107">
+        <v>663.39</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>264</v>
+      </c>
+      <c r="B108" t="s">
+        <v>116</v>
+      </c>
+      <c r="C108" t="s">
+        <v>110</v>
+      </c>
+      <c r="D108" t="s">
+        <v>117</v>
+      </c>
+      <c r="E108" t="s">
+        <v>48</v>
+      </c>
+      <c r="F108" t="s">
+        <v>112</v>
+      </c>
+      <c r="G108" t="s">
+        <v>78</v>
+      </c>
+      <c r="H108" t="s">
+        <v>50</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="J108">
+        <v>1250</v>
+      </c>
+      <c r="K108">
+        <v>2500</v>
+      </c>
+      <c r="L108" t="s">
+        <v>51</v>
+      </c>
+      <c r="M108" t="s">
+        <v>37</v>
+      </c>
+      <c r="N108" t="s">
+        <v>37</v>
+      </c>
+      <c r="O108" t="s">
+        <v>38</v>
+      </c>
+      <c r="P108" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>114</v>
+      </c>
+      <c r="R108">
+        <v>1554</v>
+      </c>
+      <c r="S108">
+        <v>1554</v>
+      </c>
+      <c r="T108" t="s">
+        <v>41</v>
+      </c>
+      <c r="U108">
+        <v>1</v>
+      </c>
+      <c r="V108" t="s">
+        <v>43</v>
+      </c>
+      <c r="W108" t="s">
+        <v>43</v>
+      </c>
+      <c r="X108">
+        <v>1420</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA108">
+        <v>2206.68</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>265</v>
+      </c>
+      <c r="B109" t="s">
+        <v>116</v>
+      </c>
+      <c r="C109" t="s">
+        <v>110</v>
+      </c>
+      <c r="D109" t="s">
+        <v>266</v>
+      </c>
+      <c r="E109" t="s">
+        <v>48</v>
+      </c>
+      <c r="F109" t="s">
+        <v>112</v>
+      </c>
+      <c r="G109" t="s">
+        <v>78</v>
+      </c>
+      <c r="H109" t="s">
+        <v>50</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109">
+        <v>1500</v>
+      </c>
+      <c r="K109">
+        <v>3000</v>
+      </c>
+      <c r="L109" t="s">
+        <v>36</v>
+      </c>
+      <c r="M109" t="s">
+        <v>37</v>
+      </c>
+      <c r="N109" t="s">
+        <v>37</v>
+      </c>
+      <c r="O109" t="s">
+        <v>38</v>
+      </c>
+      <c r="P109" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>114</v>
+      </c>
+      <c r="R109">
+        <v>2210</v>
+      </c>
+      <c r="S109">
+        <v>2210</v>
+      </c>
+      <c r="T109" t="s">
+        <v>41</v>
+      </c>
+      <c r="U109">
+        <v>1</v>
+      </c>
+      <c r="V109" t="s">
+        <v>43</v>
+      </c>
+      <c r="W109" t="s">
+        <v>43</v>
+      </c>
+      <c r="X109">
+        <v>1420</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA109">
+        <v>3138.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>267</v>
+      </c>
+      <c r="B110" t="s">
+        <v>116</v>
+      </c>
+      <c r="C110" t="s">
+        <v>110</v>
+      </c>
+      <c r="D110" t="s">
+        <v>268</v>
+      </c>
+      <c r="E110" t="s">
+        <v>48</v>
+      </c>
+      <c r="F110" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110" t="s">
+        <v>78</v>
+      </c>
+      <c r="H110" t="s">
+        <v>50</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>1500</v>
+      </c>
+      <c r="L110" t="s">
+        <v>36</v>
+      </c>
+      <c r="M110" t="s">
+        <v>37</v>
+      </c>
+      <c r="N110" t="s">
+        <v>37</v>
+      </c>
+      <c r="O110" t="s">
+        <v>38</v>
+      </c>
+      <c r="P110" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>114</v>
+      </c>
+      <c r="R110">
+        <v>3350</v>
+      </c>
+      <c r="S110">
+        <v>3350</v>
+      </c>
+      <c r="T110" t="s">
+        <v>41</v>
+      </c>
+      <c r="U110">
+        <v>1</v>
+      </c>
+      <c r="V110" t="s">
+        <v>43</v>
+      </c>
+      <c r="W110" t="s">
+        <v>43</v>
+      </c>
+      <c r="X110">
+        <v>1420</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA110">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>269</v>
+      </c>
+      <c r="B111" t="s">
+        <v>116</v>
+      </c>
+      <c r="C111" t="s">
+        <v>110</v>
+      </c>
+      <c r="D111" t="s">
+        <v>270</v>
+      </c>
+      <c r="E111" t="s">
+        <v>48</v>
+      </c>
+      <c r="F111" t="s">
+        <v>112</v>
+      </c>
+      <c r="G111" t="s">
+        <v>78</v>
+      </c>
+      <c r="H111" t="s">
+        <v>50</v>
+      </c>
+      <c r="I111">
+        <v>1.5</v>
+      </c>
+      <c r="J111">
+        <v>1250</v>
+      </c>
+      <c r="K111">
+        <v>2500</v>
+      </c>
+      <c r="L111" t="s">
+        <v>51</v>
+      </c>
+      <c r="M111" t="s">
+        <v>37</v>
+      </c>
+      <c r="N111" t="s">
+        <v>37</v>
+      </c>
+      <c r="O111" t="s">
+        <v>38</v>
+      </c>
+      <c r="P111" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>114</v>
+      </c>
+      <c r="R111">
+        <v>944</v>
+      </c>
+      <c r="S111">
+        <v>944</v>
+      </c>
+      <c r="T111" t="s">
+        <v>41</v>
+      </c>
+      <c r="U111">
+        <v>26</v>
+      </c>
+      <c r="V111" t="s">
+        <v>43</v>
+      </c>
+      <c r="W111" t="s">
+        <v>43</v>
+      </c>
+      <c r="X111">
+        <v>1370</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA111">
+        <v>1293.28</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>271</v>
+      </c>
+      <c r="B112" t="s">
+        <v>116</v>
+      </c>
+      <c r="C112" t="s">
+        <v>110</v>
+      </c>
+      <c r="D112" t="s">
+        <v>272</v>
+      </c>
+      <c r="E112" t="s">
+        <v>48</v>
+      </c>
+      <c r="F112" t="s">
+        <v>112</v>
+      </c>
+      <c r="G112" t="s">
+        <v>55</v>
+      </c>
+      <c r="H112" t="s">
+        <v>50</v>
+      </c>
+      <c r="I112">
+        <v>3</v>
+      </c>
+      <c r="J112">
+        <v>1500</v>
+      </c>
+      <c r="K112">
+        <v>3000</v>
+      </c>
+      <c r="L112" t="s">
+        <v>36</v>
+      </c>
+      <c r="M112" t="s">
+        <v>37</v>
+      </c>
+      <c r="N112" t="s">
+        <v>37</v>
+      </c>
+      <c r="O112" t="s">
+        <v>38</v>
+      </c>
+      <c r="P112" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>114</v>
+      </c>
+      <c r="R112">
+        <v>634</v>
+      </c>
+      <c r="S112">
+        <v>634</v>
+      </c>
+      <c r="T112" t="s">
+        <v>41</v>
+      </c>
+      <c r="U112">
+        <v>6</v>
+      </c>
+      <c r="V112" t="s">
+        <v>43</v>
+      </c>
+      <c r="W112" t="s">
+        <v>43</v>
+      </c>
+      <c r="X112">
+        <v>2220</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA112">
+        <v>1407.48</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>273</v>
+      </c>
+      <c r="B113" t="s">
+        <v>116</v>
+      </c>
+      <c r="C113" t="s">
+        <v>110</v>
+      </c>
+      <c r="D113" t="s">
+        <v>274</v>
+      </c>
+      <c r="E113" t="s">
+        <v>48</v>
+      </c>
+      <c r="F113" t="s">
+        <v>112</v>
+      </c>
+      <c r="G113" t="s">
+        <v>78</v>
+      </c>
+      <c r="H113" t="s">
+        <v>50</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <v>1500</v>
+      </c>
+      <c r="K113">
+        <v>3000</v>
+      </c>
+      <c r="L113" t="s">
+        <v>51</v>
+      </c>
+      <c r="M113" t="s">
+        <v>37</v>
+      </c>
+      <c r="N113" t="s">
+        <v>37</v>
+      </c>
+      <c r="O113" t="s">
+        <v>38</v>
+      </c>
+      <c r="P113" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>114</v>
+      </c>
+      <c r="R113">
+        <v>1923</v>
+      </c>
+      <c r="S113">
+        <v>1923</v>
+      </c>
+      <c r="T113" t="s">
+        <v>41</v>
+      </c>
+      <c r="U113">
+        <v>1</v>
+      </c>
+      <c r="V113" t="s">
+        <v>43</v>
+      </c>
+      <c r="W113" t="s">
+        <v>43</v>
+      </c>
+      <c r="X113">
+        <v>1420</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA113">
+        <v>2730.66</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>275</v>
+      </c>
+      <c r="B114" t="s">
+        <v>109</v>
+      </c>
+      <c r="C114" t="s">
+        <v>110</v>
+      </c>
+      <c r="D114" t="s">
+        <v>276</v>
+      </c>
+      <c r="E114" t="s">
+        <v>48</v>
+      </c>
+      <c r="F114" t="s">
+        <v>112</v>
+      </c>
+      <c r="G114" t="s">
+        <v>55</v>
+      </c>
+      <c r="H114" t="s">
+        <v>50</v>
+      </c>
+      <c r="I114">
+        <v>1.2</v>
+      </c>
+      <c r="J114">
+        <v>1500</v>
+      </c>
+      <c r="K114">
+        <v>3000</v>
+      </c>
+      <c r="L114" t="s">
+        <v>36</v>
+      </c>
+      <c r="M114" t="s">
+        <v>37</v>
+      </c>
+      <c r="N114" t="s">
+        <v>37</v>
+      </c>
+      <c r="O114" t="s">
+        <v>38</v>
+      </c>
+      <c r="P114" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>114</v>
+      </c>
+      <c r="R114">
+        <v>42</v>
+      </c>
+      <c r="S114">
+        <v>42</v>
+      </c>
+      <c r="T114" t="s">
+        <v>41</v>
+      </c>
+      <c r="U114">
+        <v>1</v>
+      </c>
+      <c r="V114" t="s">
+        <v>43</v>
+      </c>
+      <c r="W114" t="s">
+        <v>43</v>
+      </c>
+      <c r="X114">
+        <v>2170</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA114">
+        <v>91.14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>277</v>
+      </c>
+      <c r="B115" t="s">
+        <v>116</v>
+      </c>
+      <c r="C115" t="s">
+        <v>110</v>
+      </c>
+      <c r="D115" t="s">
+        <v>189</v>
+      </c>
+      <c r="E115" t="s">
+        <v>48</v>
+      </c>
+      <c r="F115" t="s">
+        <v>112</v>
+      </c>
+      <c r="G115" t="s">
+        <v>34</v>
+      </c>
+      <c r="H115" t="s">
+        <v>50</v>
+      </c>
+      <c r="I115">
+        <v>1.5</v>
+      </c>
+      <c r="J115">
+        <v>1500</v>
+      </c>
+      <c r="K115">
+        <v>3000</v>
+      </c>
+      <c r="L115" t="s">
+        <v>36</v>
+      </c>
+      <c r="M115" t="s">
+        <v>37</v>
+      </c>
+      <c r="N115" t="s">
+        <v>37</v>
+      </c>
+      <c r="O115" t="s">
+        <v>38</v>
+      </c>
+      <c r="P115" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>114</v>
+      </c>
+      <c r="R115">
+        <v>316</v>
+      </c>
+      <c r="S115">
+        <v>316</v>
+      </c>
+      <c r="T115" t="s">
+        <v>41</v>
+      </c>
+      <c r="U115">
+        <v>6</v>
+      </c>
+      <c r="V115" t="s">
+        <v>43</v>
+      </c>
+      <c r="W115" t="s">
+        <v>43</v>
+      </c>
+      <c r="X115">
+        <v>3540</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA115">
+        <v>1118.64</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>278</v>
+      </c>
+      <c r="B116" t="s">
+        <v>120</v>
+      </c>
+      <c r="C116" t="s">
+        <v>110</v>
+      </c>
+      <c r="D116" t="s">
+        <v>279</v>
+      </c>
+      <c r="E116" t="s">
+        <v>48</v>
+      </c>
+      <c r="F116" t="s">
+        <v>112</v>
+      </c>
+      <c r="G116" t="s">
+        <v>34</v>
+      </c>
+      <c r="H116" t="s">
+        <v>50</v>
+      </c>
+      <c r="I116">
+        <v>8</v>
+      </c>
+      <c r="J116">
+        <v>1500</v>
+      </c>
+      <c r="K116">
+        <v>3000</v>
+      </c>
+      <c r="L116" t="s">
+        <v>36</v>
+      </c>
+      <c r="M116" t="s">
+        <v>37</v>
+      </c>
+      <c r="N116" t="s">
+        <v>37</v>
+      </c>
+      <c r="O116" t="s">
+        <v>38</v>
+      </c>
+      <c r="P116" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>114</v>
+      </c>
+      <c r="R116">
+        <v>1417</v>
+      </c>
+      <c r="S116">
+        <v>1417</v>
+      </c>
+      <c r="T116" t="s">
+        <v>41</v>
+      </c>
+      <c r="U116">
+        <v>5</v>
+      </c>
+      <c r="V116" t="s">
+        <v>43</v>
+      </c>
+      <c r="W116" t="s">
+        <v>43</v>
+      </c>
+      <c r="X116">
+        <v>3590</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA116">
+        <v>5087.03</v>
+      </c>
+      <c r="AB116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>280</v>
+      </c>
+      <c r="B117" t="s">
+        <v>116</v>
+      </c>
+      <c r="C117" t="s">
+        <v>110</v>
+      </c>
+      <c r="D117" t="s">
+        <v>281</v>
+      </c>
+      <c r="E117" t="s">
+        <v>48</v>
+      </c>
+      <c r="F117" t="s">
+        <v>33</v>
+      </c>
+      <c r="G117" t="s">
+        <v>78</v>
+      </c>
+      <c r="H117" t="s">
+        <v>50</v>
+      </c>
+      <c r="I117">
+        <v>0.8</v>
+      </c>
+      <c r="J117">
+        <v>1500</v>
+      </c>
+      <c r="L117" t="s">
+        <v>51</v>
+      </c>
+      <c r="M117" t="s">
+        <v>37</v>
+      </c>
+      <c r="N117" t="s">
+        <v>37</v>
+      </c>
+      <c r="O117" t="s">
+        <v>38</v>
+      </c>
+      <c r="P117" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>114</v>
+      </c>
+      <c r="R117">
+        <v>1865</v>
+      </c>
+      <c r="S117">
+        <v>1865</v>
+      </c>
+      <c r="T117" t="s">
+        <v>41</v>
+      </c>
+      <c r="U117">
+        <v>1</v>
+      </c>
+      <c r="V117" t="s">
+        <v>43</v>
+      </c>
+      <c r="W117" t="s">
+        <v>43</v>
+      </c>
+      <c r="X117">
+        <v>1520</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA117">
+        <v>2834.8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>282</v>
+      </c>
+      <c r="B118" t="s">
+        <v>109</v>
+      </c>
+      <c r="C118" t="s">
+        <v>110</v>
+      </c>
+      <c r="D118" t="s">
+        <v>283</v>
+      </c>
+      <c r="E118" t="s">
+        <v>48</v>
+      </c>
+      <c r="F118" t="s">
+        <v>112</v>
+      </c>
+      <c r="G118" t="s">
+        <v>55</v>
+      </c>
+      <c r="H118" t="s">
+        <v>50</v>
+      </c>
+      <c r="I118">
+        <v>1.25</v>
+      </c>
+      <c r="J118">
+        <v>1250</v>
+      </c>
+      <c r="K118">
+        <v>2500</v>
+      </c>
+      <c r="L118" t="s">
+        <v>36</v>
+      </c>
+      <c r="M118" t="s">
+        <v>37</v>
+      </c>
+      <c r="N118" t="s">
+        <v>37</v>
+      </c>
+      <c r="O118" t="s">
+        <v>38</v>
+      </c>
+      <c r="P118" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>114</v>
+      </c>
+      <c r="R118">
+        <v>31</v>
+      </c>
+      <c r="S118">
+        <v>31</v>
+      </c>
+      <c r="T118" t="s">
+        <v>41</v>
+      </c>
+      <c r="U118">
+        <v>1</v>
+      </c>
+      <c r="V118" t="s">
+        <v>43</v>
+      </c>
+      <c r="W118" t="s">
+        <v>43</v>
+      </c>
+      <c r="X118">
+        <v>2170</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA118">
+        <v>67.27</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>284</v>
+      </c>
+      <c r="B119" t="s">
+        <v>116</v>
+      </c>
+      <c r="C119" t="s">
+        <v>110</v>
+      </c>
+      <c r="D119" t="s">
+        <v>285</v>
+      </c>
+      <c r="E119" t="s">
+        <v>48</v>
+      </c>
+      <c r="F119" t="s">
+        <v>112</v>
+      </c>
+      <c r="G119" t="s">
+        <v>78</v>
+      </c>
+      <c r="H119" t="s">
+        <v>50</v>
+      </c>
+      <c r="I119">
+        <v>1.5</v>
+      </c>
+      <c r="J119">
+        <v>1500</v>
+      </c>
+      <c r="K119">
+        <v>3000</v>
+      </c>
+      <c r="L119" t="s">
+        <v>51</v>
+      </c>
+      <c r="M119" t="s">
+        <v>37</v>
+      </c>
+      <c r="N119" t="s">
+        <v>37</v>
+      </c>
+      <c r="O119" t="s">
+        <v>38</v>
+      </c>
+      <c r="P119" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>114</v>
+      </c>
+      <c r="R119">
+        <v>1007</v>
+      </c>
+      <c r="S119">
+        <v>1007</v>
+      </c>
+      <c r="T119" t="s">
+        <v>41</v>
+      </c>
+      <c r="U119">
+        <v>20</v>
+      </c>
+      <c r="V119" t="s">
+        <v>43</v>
+      </c>
+      <c r="W119" t="s">
+        <v>43</v>
+      </c>
+      <c r="X119">
+        <v>1420</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA119">
+        <v>1429.94</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>286</v>
+      </c>
+      <c r="B120" t="s">
+        <v>116</v>
+      </c>
+      <c r="C120" t="s">
+        <v>110</v>
+      </c>
+      <c r="D120" t="s">
+        <v>285</v>
+      </c>
+      <c r="E120" t="s">
+        <v>48</v>
+      </c>
+      <c r="F120" t="s">
+        <v>112</v>
+      </c>
+      <c r="G120" t="s">
+        <v>78</v>
+      </c>
+      <c r="H120" t="s">
+        <v>50</v>
+      </c>
+      <c r="I120">
+        <v>1.5</v>
+      </c>
+      <c r="J120">
+        <v>1500</v>
+      </c>
+      <c r="K120">
+        <v>3000</v>
+      </c>
+      <c r="L120" t="s">
+        <v>51</v>
+      </c>
+      <c r="M120" t="s">
+        <v>37</v>
+      </c>
+      <c r="N120" t="s">
+        <v>37</v>
+      </c>
+      <c r="O120" t="s">
+        <v>38</v>
+      </c>
+      <c r="P120" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>114</v>
+      </c>
+      <c r="R120">
+        <v>960</v>
+      </c>
+      <c r="S120">
+        <v>960</v>
+      </c>
+      <c r="T120" t="s">
+        <v>41</v>
+      </c>
+      <c r="U120">
+        <v>19</v>
+      </c>
+      <c r="V120" t="s">
+        <v>43</v>
+      </c>
+      <c r="W120" t="s">
+        <v>43</v>
+      </c>
+      <c r="X120">
+        <v>1370</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA120">
+        <v>1315.2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>287</v>
+      </c>
+      <c r="B121" t="s">
+        <v>120</v>
+      </c>
+      <c r="C121" t="s">
+        <v>110</v>
+      </c>
+      <c r="D121" t="s">
+        <v>288</v>
+      </c>
+      <c r="E121" t="s">
+        <v>48</v>
+      </c>
+      <c r="F121" t="s">
+        <v>112</v>
+      </c>
+      <c r="G121" t="s">
+        <v>55</v>
+      </c>
+      <c r="H121" t="s">
+        <v>50</v>
+      </c>
+      <c r="I121">
+        <v>6</v>
+      </c>
+      <c r="J121">
+        <v>2000</v>
+      </c>
+      <c r="K121">
+        <v>6000</v>
+      </c>
+      <c r="L121" t="s">
+        <v>113</v>
+      </c>
+      <c r="M121" t="s">
+        <v>37</v>
+      </c>
+      <c r="N121" t="s">
+        <v>37</v>
+      </c>
+      <c r="O121" t="s">
+        <v>38</v>
+      </c>
+      <c r="P121" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>114</v>
+      </c>
+      <c r="R121">
+        <v>567</v>
+      </c>
+      <c r="S121">
+        <v>567</v>
+      </c>
+      <c r="T121" t="s">
+        <v>41</v>
+      </c>
+      <c r="U121">
+        <v>1</v>
+      </c>
+      <c r="V121" t="s">
+        <v>43</v>
+      </c>
+      <c r="W121" t="s">
+        <v>43</v>
+      </c>
+      <c r="X121">
+        <v>2040</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA121">
+        <v>1156.68</v>
+      </c>
+      <c r="AB121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>289</v>
+      </c>
+      <c r="B122" t="s">
+        <v>116</v>
+      </c>
+      <c r="C122" t="s">
+        <v>110</v>
+      </c>
+      <c r="D122" t="s">
+        <v>274</v>
+      </c>
+      <c r="E122" t="s">
+        <v>48</v>
+      </c>
+      <c r="F122" t="s">
+        <v>112</v>
+      </c>
+      <c r="G122" t="s">
+        <v>78</v>
+      </c>
+      <c r="H122" t="s">
+        <v>50</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <v>1500</v>
+      </c>
+      <c r="K122">
+        <v>3000</v>
+      </c>
+      <c r="L122" t="s">
+        <v>51</v>
+      </c>
+      <c r="M122" t="s">
+        <v>37</v>
+      </c>
+      <c r="N122" t="s">
+        <v>37</v>
+      </c>
+      <c r="O122" t="s">
+        <v>38</v>
+      </c>
+      <c r="P122" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>114</v>
+      </c>
+      <c r="R122">
+        <v>1200</v>
+      </c>
+      <c r="S122">
+        <v>1200</v>
+      </c>
+      <c r="T122" t="s">
+        <v>41</v>
+      </c>
+      <c r="U122">
+        <v>35</v>
+      </c>
+      <c r="V122" t="s">
+        <v>43</v>
+      </c>
+      <c r="W122" t="s">
+        <v>43</v>
+      </c>
+      <c r="X122">
+        <v>1420</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA122">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>290</v>
+      </c>
+      <c r="B123" t="s">
+        <v>116</v>
+      </c>
+      <c r="C123" t="s">
+        <v>110</v>
+      </c>
+      <c r="D123" t="s">
+        <v>291</v>
+      </c>
+      <c r="E123" t="s">
+        <v>48</v>
+      </c>
+      <c r="F123" t="s">
+        <v>112</v>
+      </c>
+      <c r="G123" t="s">
+        <v>55</v>
+      </c>
+      <c r="H123" t="s">
+        <v>50</v>
+      </c>
+      <c r="I123">
+        <v>2</v>
+      </c>
+      <c r="J123">
+        <v>1500</v>
+      </c>
+      <c r="K123">
+        <v>3000</v>
+      </c>
+      <c r="L123" t="s">
+        <v>51</v>
+      </c>
+      <c r="M123" t="s">
+        <v>37</v>
+      </c>
+      <c r="N123" t="s">
+        <v>37</v>
+      </c>
+      <c r="O123" t="s">
+        <v>38</v>
+      </c>
+      <c r="P123" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>114</v>
+      </c>
+      <c r="R123">
+        <v>1776</v>
+      </c>
+      <c r="S123">
+        <v>1776</v>
+      </c>
+      <c r="T123" t="s">
+        <v>41</v>
+      </c>
+      <c r="U123">
+        <v>1</v>
+      </c>
+      <c r="V123" t="s">
+        <v>43</v>
+      </c>
+      <c r="W123" t="s">
+        <v>43</v>
+      </c>
+      <c r="X123">
+        <v>2270</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA123">
+        <v>4031.52</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>292</v>
+      </c>
+      <c r="B124" t="s">
+        <v>116</v>
+      </c>
+      <c r="C124" t="s">
+        <v>110</v>
+      </c>
+      <c r="D124" t="s">
+        <v>293</v>
+      </c>
+      <c r="E124" t="s">
+        <v>48</v>
+      </c>
+      <c r="F124" t="s">
+        <v>112</v>
+      </c>
+      <c r="G124" t="s">
+        <v>55</v>
+      </c>
+      <c r="H124" t="s">
+        <v>50</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>1250</v>
+      </c>
+      <c r="K124">
+        <v>2500</v>
+      </c>
+      <c r="L124" t="s">
+        <v>51</v>
+      </c>
+      <c r="M124" t="s">
+        <v>37</v>
+      </c>
+      <c r="N124" t="s">
+        <v>37</v>
+      </c>
+      <c r="O124" t="s">
+        <v>195</v>
+      </c>
+      <c r="P124" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>114</v>
+      </c>
+      <c r="R124">
+        <v>1062</v>
+      </c>
+      <c r="S124">
+        <v>1062</v>
+      </c>
+      <c r="T124" t="s">
+        <v>41</v>
+      </c>
+      <c r="U124">
+        <v>1</v>
+      </c>
+      <c r="V124" t="s">
+        <v>43</v>
+      </c>
+      <c r="W124" t="s">
+        <v>43</v>
+      </c>
+      <c r="X124">
+        <v>2270</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA124">
+        <v>2410.74</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>294</v>
+      </c>
+      <c r="B125" t="s">
+        <v>116</v>
+      </c>
+      <c r="C125" t="s">
+        <v>110</v>
+      </c>
+      <c r="D125" t="s">
+        <v>293</v>
+      </c>
+      <c r="E125" t="s">
+        <v>48</v>
+      </c>
+      <c r="F125" t="s">
+        <v>112</v>
+      </c>
+      <c r="G125" t="s">
+        <v>55</v>
+      </c>
+      <c r="H125" t="s">
+        <v>50</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>1250</v>
+      </c>
+      <c r="K125">
+        <v>2500</v>
+      </c>
+      <c r="L125" t="s">
+        <v>51</v>
+      </c>
+      <c r="M125" t="s">
+        <v>37</v>
+      </c>
+      <c r="N125" t="s">
+        <v>37</v>
+      </c>
+      <c r="O125" t="s">
+        <v>195</v>
+      </c>
+      <c r="P125" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>114</v>
+      </c>
+      <c r="R125">
+        <v>1068</v>
+      </c>
+      <c r="S125">
+        <v>1068</v>
+      </c>
+      <c r="T125" t="s">
+        <v>41</v>
+      </c>
+      <c r="U125">
+        <v>1</v>
+      </c>
+      <c r="V125" t="s">
+        <v>43</v>
+      </c>
+      <c r="W125" t="s">
+        <v>43</v>
+      </c>
+      <c r="X125">
+        <v>2270</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA125">
+        <v>2424.36</v>
+      </c>
+    </row>
+    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>295</v>
+      </c>
+      <c r="B126" t="s">
+        <v>116</v>
+      </c>
+      <c r="C126" t="s">
+        <v>110</v>
+      </c>
+      <c r="D126" t="s">
+        <v>296</v>
+      </c>
+      <c r="E126" t="s">
+        <v>48</v>
+      </c>
+      <c r="F126" t="s">
+        <v>112</v>
+      </c>
+      <c r="G126" t="s">
+        <v>78</v>
+      </c>
+      <c r="H126" t="s">
+        <v>50</v>
+      </c>
+      <c r="I126">
+        <v>0.5</v>
+      </c>
+      <c r="J126">
+        <v>1000</v>
+      </c>
+      <c r="K126">
+        <v>2000</v>
+      </c>
+      <c r="L126" t="s">
+        <v>51</v>
+      </c>
+      <c r="M126" t="s">
+        <v>37</v>
+      </c>
+      <c r="N126" t="s">
+        <v>37</v>
+      </c>
+      <c r="O126" t="s">
+        <v>38</v>
+      </c>
+      <c r="P126" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>114</v>
+      </c>
+      <c r="R126">
+        <v>157</v>
+      </c>
+      <c r="S126">
+        <v>157</v>
+      </c>
+      <c r="T126" t="s">
+        <v>41</v>
+      </c>
+      <c r="U126">
+        <v>1</v>
+      </c>
+      <c r="V126" t="s">
+        <v>43</v>
+      </c>
+      <c r="W126" t="s">
+        <v>43</v>
+      </c>
+      <c r="X126">
+        <v>1620</v>
+      </c>
+      <c r="Y126" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA126">
+        <v>254.34</v>
+      </c>
+    </row>
+    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>297</v>
+      </c>
+      <c r="B127" t="s">
+        <v>116</v>
+      </c>
+      <c r="C127" t="s">
+        <v>110</v>
+      </c>
+      <c r="D127" t="s">
+        <v>298</v>
+      </c>
+      <c r="E127" t="s">
+        <v>48</v>
+      </c>
+      <c r="F127" t="s">
+        <v>112</v>
+      </c>
+      <c r="G127" t="s">
+        <v>55</v>
+      </c>
+      <c r="H127" t="s">
+        <v>50</v>
+      </c>
+      <c r="I127">
+        <v>2</v>
+      </c>
+      <c r="J127">
+        <v>1500</v>
+      </c>
+      <c r="K127">
+        <v>3000</v>
+      </c>
+      <c r="L127" t="s">
+        <v>36</v>
+      </c>
+      <c r="M127" t="s">
+        <v>37</v>
+      </c>
+      <c r="N127" t="s">
+        <v>37</v>
+      </c>
+      <c r="O127" t="s">
+        <v>38</v>
+      </c>
+      <c r="P127" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>114</v>
+      </c>
+      <c r="R127">
+        <v>428</v>
+      </c>
+      <c r="S127">
+        <v>428</v>
+      </c>
+      <c r="T127" t="s">
+        <v>41</v>
+      </c>
+      <c r="U127">
+        <v>6</v>
+      </c>
+      <c r="V127" t="s">
+        <v>43</v>
+      </c>
+      <c r="W127" t="s">
+        <v>43</v>
+      </c>
+      <c r="X127">
+        <v>2220</v>
+      </c>
+      <c r="Y127" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA127">
+        <v>950.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="132">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -97,223 +97,316 @@
     <t>WORKBOOK.SPECIAL_OFFERS.hasContinuousMarking</t>
   </si>
   <si>
-    <t>I26G0425</t>
+    <t>K268053711</t>
+  </si>
+  <si>
+    <t>Genk</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 1.49 x 2001.0 x 4000 mm Slit not marked</t>
+  </si>
+  <si>
+    <t>Excess Prime</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>1.4404-316L</t>
+  </si>
+  <si>
+    <t>Slit</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>Not Polished</t>
+  </si>
+  <si>
+    <t>Not coated</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Std sheet packing road transp.</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305 / SANS 50028-7</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>TONS</t>
+  </si>
+  <si>
+    <t>K268053729</t>
+  </si>
+  <si>
+    <t>K268053737</t>
+  </si>
+  <si>
+    <t>K260220839</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 1D without paper 6.0 x 1001.0 mm Slit marked</t>
+  </si>
+  <si>
+    <t>Coil</t>
+  </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Horiz. without pallet, road tr</t>
+  </si>
+  <si>
+    <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4304 / SANS 50028-7</t>
+  </si>
+  <si>
+    <t>K268086118</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 0.67 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>K268085699</t>
+  </si>
+  <si>
+    <t>K268086051</t>
+  </si>
+  <si>
+    <t>K268085657</t>
+  </si>
+  <si>
+    <t>K268086209</t>
+  </si>
+  <si>
+    <t>K268086324</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.19 x 1503.0 x 3002 mm Slit marked</t>
+  </si>
+  <si>
+    <t>1.4307-304L</t>
+  </si>
+  <si>
+    <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4304</t>
+  </si>
+  <si>
+    <t>K268090036</t>
+  </si>
+  <si>
+    <t>Coil DX2205/1.4462-2205 2D with paper 1.98 x 780.0 mm Slit marked</t>
+  </si>
+  <si>
+    <t>DX2205/1.4462-2205</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>ASME SA 240 / ASTM A 240 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305</t>
+  </si>
+  <si>
+    <t>K260248261</t>
+  </si>
+  <si>
+    <t>Coil 1.4307-304L 1D without paper 4.98 x 2001.0 mm Slit marked</t>
+  </si>
+  <si>
+    <t>G26RJN27</t>
+  </si>
+  <si>
+    <t>Gueugnon</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>Coil K41/1.4509-441 2R without paper 0.8 x 1460.0 mm Unslit</t>
+  </si>
+  <si>
+    <t>K41/1.4509-441</t>
+  </si>
+  <si>
+    <t>Unslit</t>
+  </si>
+  <si>
+    <t>2R</t>
+  </si>
+  <si>
+    <t>H1 - Coil eye to the side on pallet + corner protect.</t>
+  </si>
+  <si>
+    <t>K268097389</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B without paper 1.17 x 118.0 mm Slit not marked</t>
+  </si>
+  <si>
+    <t>V1 - Coil eye to the sky + Unalit</t>
+  </si>
+  <si>
+    <t>K268099012</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B without paper 0.56 x 46.0 mm Slit marked</t>
+  </si>
+  <si>
+    <t>K268099020</t>
+  </si>
+  <si>
+    <t>G26RHZ54</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R without paper 1.0 x 1255.0 mm Unslit</t>
+  </si>
+  <si>
+    <t>K30/1.4016-430</t>
+  </si>
+  <si>
+    <t>ASME SA 240 / ASTM A 240 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305</t>
+  </si>
+  <si>
+    <t>G26RJN79</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R without paper 0.74 x 600.0 mm Slit</t>
+  </si>
+  <si>
+    <t>G26RJX14</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B without paper 0.39 x 124.0 mm Slit</t>
+  </si>
+  <si>
+    <t>I26G0484</t>
   </si>
   <si>
     <t>Isbergues</t>
   </si>
   <si>
-    <t>FR</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 2B without paper 2.0 x 1301.0 mm Slit</t>
-  </si>
-  <si>
-    <t>Excess Prime</t>
-  </si>
-  <si>
-    <t>Coil</t>
-  </si>
-  <si>
-    <t>1.4307-304L</t>
-  </si>
-  <si>
-    <t>Slit</t>
-  </si>
-  <si>
-    <t>2B</t>
-  </si>
-  <si>
-    <t>Not Polished</t>
-  </si>
-  <si>
-    <t>Not coated</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Horiz. without pallet, road tr</t>
-  </si>
-  <si>
-    <t>kg</t>
+    <t>Coil 1.4307-304L 2B without paper 4.0 x 1547.0 mm Slit</t>
+  </si>
+  <si>
+    <t>Downgraded</t>
+  </si>
+  <si>
+    <t>K268106841</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B with paper 0.58 x 1520.0 mm Unslit marked</t>
+  </si>
+  <si>
+    <t>G26RJB68</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R without paper 0.41 x 300.0 mm Slit</t>
+  </si>
+  <si>
+    <t>G26RJB69</t>
+  </si>
+  <si>
+    <t>G26RJB94</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B without paper 0.69 x 100.0 mm Slit</t>
+  </si>
+  <si>
+    <t>G26RJB67</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R without paper 0.5 x 192.0 mm Slit</t>
+  </si>
+  <si>
+    <t>G26RJB66</t>
+  </si>
+  <si>
+    <t>G26RJB57</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B without paper 3.03 x 180.0 mm Slit</t>
+  </si>
+  <si>
+    <t>G26RJB56</t>
+  </si>
+  <si>
+    <t>G26RJB64</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R without paper 0.3 x 400.0 mm Slit</t>
+  </si>
+  <si>
+    <t>G26RJB65</t>
+  </si>
+  <si>
+    <t>G26RJB55</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B without paper 4.02 x 470.0 mm Slit</t>
+  </si>
+  <si>
+    <t>G26RJV19</t>
+  </si>
+  <si>
+    <t>Coil K30H/1.4016H-430 2R without paper 0.65 x 1315.0 mm Unslit</t>
+  </si>
+  <si>
+    <t>K30H/1.4016H-430</t>
+  </si>
+  <si>
+    <t>G26RJV16</t>
+  </si>
+  <si>
+    <t>Coil 1.4310A-301 2R without paper 0.5 x 1234.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4310A-301</t>
+  </si>
+  <si>
+    <t>I26G0505</t>
+  </si>
+  <si>
+    <t>Coil K41/1.4509-441 2D without paper 1.15 x 1300.0 mm Unslit</t>
+  </si>
+  <si>
+    <t>G26RJX15</t>
+  </si>
+  <si>
+    <t>Coil 1.4307-304L 2R without paper 0.81 x 400.0 mm Slit</t>
   </si>
   <si>
     <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>TONS</t>
-  </si>
-  <si>
-    <t>K269006363</t>
-  </si>
-  <si>
-    <t>Genk</t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 2B without paper 2.58 x 498.0 mm Slit not marked</t>
-  </si>
-  <si>
-    <t>Downgraded</t>
-  </si>
-  <si>
-    <t>V1 - Coil eye to the sky + Unalit</t>
-  </si>
-  <si>
-    <t>K269006371</t>
-  </si>
-  <si>
-    <t>Coil 1.4828-309 2B with paper 0.5 x 230.0 mm Unslit not marked</t>
-  </si>
-  <si>
-    <t>1.4828-309</t>
-  </si>
-  <si>
-    <t>Unslit</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>G26RJV06</t>
-  </si>
-  <si>
-    <t>Gueugnon</t>
-  </si>
-  <si>
-    <t>Coil K30H/1.4016H-430 2R without paper 1.05 x 1316.0 mm Unslit</t>
-  </si>
-  <si>
-    <t>K30H/1.4016H-430</t>
-  </si>
-  <si>
-    <t>2R</t>
-  </si>
-  <si>
-    <t>ASME SA 240 / ASTM A 240 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305</t>
-  </si>
-  <si>
-    <t>G26RJX10</t>
-  </si>
-  <si>
-    <t>Coil K30/1.4016-430 2R without paper 0.8 x 170.0 mm Slit</t>
-  </si>
-  <si>
-    <t>K30/1.4016-430</t>
-  </si>
-  <si>
-    <t>I26G0443</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 2B without paper 2.0 x 1551.0 mm Slit</t>
-  </si>
-  <si>
-    <t>H1 - Coil eye to the side on pallet + corner protect.</t>
-  </si>
-  <si>
-    <t>I26G0444</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 2B without paper 1.5 x 1546.0 mm Slit</t>
-  </si>
-  <si>
-    <t>I26G0449</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 2B without paper 3.04 x 1544.0 mm Slit</t>
-  </si>
-  <si>
-    <t>I26G0451</t>
-  </si>
-  <si>
-    <t>Coil K41/1.4509-441 2D without paper 1.15 x 1303.0 mm Slit</t>
-  </si>
-  <si>
-    <t>K41/1.4509-441</t>
-  </si>
-  <si>
-    <t>2D</t>
-  </si>
-  <si>
-    <t>I26G0453</t>
-  </si>
-  <si>
-    <t>Coil K41/1.4509-441 2D without paper 1.39 x 1307.0 mm Slit</t>
-  </si>
-  <si>
-    <t>K268105942</t>
-  </si>
-  <si>
-    <t>Coil K44X/1.4521X-444 2D without paper 1.0 x 680.0 mm Slit marked</t>
-  </si>
-  <si>
-    <t>K44X/1.4521X-444</t>
-  </si>
-  <si>
-    <t>ASME SA 240 / ASTM A 240 / EN 10088-2 / IS 6911 / JIS G 4305</t>
-  </si>
-  <si>
-    <t>K268105934</t>
-  </si>
-  <si>
-    <t>I26G0465</t>
-  </si>
-  <si>
-    <t>Coil K41/1.4509-441 2D without paper 1.5 x 1551.0 mm Slit</t>
-  </si>
-  <si>
-    <t>I26G0466</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 2B without paper 4.05 x 1545.0 mm Slit</t>
-  </si>
-  <si>
-    <t>K268106320</t>
-  </si>
-  <si>
-    <t>Coil 1.4828-309 2B without paper 1.78 x 150.0 mm Slit marked</t>
-  </si>
-  <si>
-    <t>EN 10095 / SEW 470</t>
-  </si>
-  <si>
-    <t>K268106354</t>
-  </si>
-  <si>
-    <t>K268106619</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 2B with paper 1.43 x 1251.0 mm Slit marked</t>
-  </si>
-  <si>
-    <t>K268106601</t>
-  </si>
-  <si>
-    <t>Coil K30/1.4016-430 2B with paper 0.76 x 1251.0 mm Slit marked</t>
-  </si>
-  <si>
-    <t>K260281138</t>
-  </si>
-  <si>
-    <t>Coil 1.4404-316L 1D without paper 11.99 x 1500.0 mm Unslit not marked</t>
-  </si>
-  <si>
-    <t>1.4404-316L</t>
-  </si>
-  <si>
-    <t>1D</t>
-  </si>
-  <si>
-    <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4304 / SANS 50028-7</t>
+    <t>K260282194</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2D with paper 1.67 x 1198.0 mm Unslit not marked</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
+  </si>
+  <si>
+    <t>G26RJX26</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B without paper 0.48 x 163.0 mm Slit</t>
   </si>
 </sst>
 </file>
@@ -690,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -808,10 +901,13 @@
         <v>35</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1.49</v>
       </c>
       <c r="J2">
-        <v>1301</v>
+        <v>2001</v>
+      </c>
+      <c r="K2">
+        <v>4000</v>
       </c>
       <c r="L2" t="s">
         <v>36</v>
@@ -832,16 +928,16 @@
         <v>40</v>
       </c>
       <c r="R2">
-        <v>6810</v>
+        <v>964</v>
       </c>
       <c r="S2">
-        <v>6813</v>
+        <v>1022</v>
       </c>
       <c r="T2" t="s">
         <v>41</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V2" t="s">
         <v>42</v>
@@ -850,7 +946,7 @@
         <v>43</v>
       </c>
       <c r="X2">
-        <v>2470</v>
+        <v>4240</v>
       </c>
       <c r="Y2" t="s">
         <v>44</v>
@@ -859,7 +955,10 @@
         <v>45</v>
       </c>
       <c r="AA2">
-        <v>16820.7</v>
+        <v>4087.36</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -867,16 +966,16 @@
         <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
         <v>33</v>
@@ -888,10 +987,13 @@
         <v>35</v>
       </c>
       <c r="I3">
-        <v>2.58</v>
+        <v>1.49</v>
       </c>
       <c r="J3">
-        <v>498</v>
+        <v>2001</v>
+      </c>
+      <c r="K3">
+        <v>4000</v>
       </c>
       <c r="L3" t="s">
         <v>36</v>
@@ -909,28 +1011,28 @@
         <v>39</v>
       </c>
       <c r="Q3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="R3">
-        <v>5593</v>
+        <v>966</v>
       </c>
       <c r="S3">
-        <v>5633</v>
+        <v>1024</v>
       </c>
       <c r="T3" t="s">
         <v>41</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W3" t="s">
         <v>43</v>
       </c>
       <c r="X3">
-        <v>1970</v>
+        <v>4240</v>
       </c>
       <c r="Y3" t="s">
         <v>44</v>
@@ -939,7 +1041,7 @@
         <v>45</v>
       </c>
       <c r="AA3">
-        <v>11018.21</v>
+        <v>4095.84</v>
       </c>
       <c r="AB3" t="b">
         <v>0</v>
@@ -947,34 +1049,37 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>1.49</v>
       </c>
       <c r="J4">
-        <v>230</v>
+        <v>2001</v>
+      </c>
+      <c r="K4">
+        <v>4000</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
@@ -989,31 +1094,31 @@
         <v>38</v>
       </c>
       <c r="P4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="Q4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="R4">
-        <v>3505</v>
+        <v>192</v>
       </c>
       <c r="S4">
-        <v>3565</v>
+        <v>254</v>
       </c>
       <c r="T4" t="s">
         <v>41</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W4" t="s">
         <v>43</v>
       </c>
       <c r="X4">
-        <v>3470</v>
+        <v>4240</v>
       </c>
       <c r="Y4" t="s">
         <v>44</v>
@@ -1022,7 +1127,7 @@
         <v>45</v>
       </c>
       <c r="AA4">
-        <v>12162.35</v>
+        <v>814.08</v>
       </c>
       <c r="AB4" t="b">
         <v>0</v>
@@ -1030,37 +1135,37 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>1316</v>
+        <v>1001</v>
       </c>
       <c r="L5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M5" t="s">
         <v>37</v>
@@ -1072,16 +1177,16 @@
         <v>38</v>
       </c>
       <c r="P5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="R5">
-        <v>6760</v>
+        <v>8460</v>
       </c>
       <c r="S5">
-        <v>6760</v>
+        <v>8463</v>
       </c>
       <c r="T5" t="s">
         <v>41</v>
@@ -1090,13 +1195,13 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="W5" t="s">
         <v>43</v>
       </c>
       <c r="X5">
-        <v>1620</v>
+        <v>3640</v>
       </c>
       <c r="Y5" t="s">
         <v>44</v>
@@ -1105,21 +1210,24 @@
         <v>45</v>
       </c>
       <c r="AA5">
-        <v>10951.2</v>
+        <v>30794.4</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -1128,19 +1236,22 @@
         <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
         <v>35</v>
       </c>
       <c r="I6">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="J6">
-        <v>170</v>
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>2000</v>
       </c>
       <c r="L6" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
         <v>37</v>
@@ -1155,28 +1266,28 @@
         <v>39</v>
       </c>
       <c r="Q6" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="R6">
-        <v>2343</v>
+        <v>1476</v>
       </c>
       <c r="S6">
-        <v>2352</v>
+        <v>1524</v>
       </c>
       <c r="T6" t="s">
         <v>41</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="V6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="W6" t="s">
         <v>43</v>
       </c>
       <c r="X6">
-        <v>1420</v>
+        <v>3890</v>
       </c>
       <c r="Y6" t="s">
         <v>44</v>
@@ -1185,12 +1296,15 @@
         <v>45</v>
       </c>
       <c r="AA6">
-        <v>3327.06</v>
+        <v>5741.64</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
@@ -1199,10 +1313,10 @@
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
         <v>33</v>
@@ -1214,10 +1328,13 @@
         <v>35</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="J7">
-        <v>1551</v>
+        <v>1000</v>
+      </c>
+      <c r="K7">
+        <v>2000</v>
       </c>
       <c r="L7" t="s">
         <v>36</v>
@@ -1235,28 +1352,28 @@
         <v>39</v>
       </c>
       <c r="Q7" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="R7">
-        <v>4260</v>
+        <v>1472</v>
       </c>
       <c r="S7">
-        <v>4290</v>
+        <v>1522</v>
       </c>
       <c r="T7" t="s">
         <v>41</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W7" t="s">
         <v>43</v>
       </c>
       <c r="X7">
-        <v>2270</v>
+        <v>3890</v>
       </c>
       <c r="Y7" t="s">
         <v>44</v>
@@ -1265,12 +1382,15 @@
         <v>45</v>
       </c>
       <c r="AA7">
-        <v>9670.2</v>
+        <v>5726.08</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
@@ -1279,10 +1399,10 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>33</v>
@@ -1294,10 +1414,13 @@
         <v>35</v>
       </c>
       <c r="I8">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="J8">
-        <v>1546</v>
+        <v>1000</v>
+      </c>
+      <c r="K8">
+        <v>2000</v>
       </c>
       <c r="L8" t="s">
         <v>36</v>
@@ -1315,28 +1438,28 @@
         <v>39</v>
       </c>
       <c r="Q8" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="R8">
-        <v>5330</v>
+        <v>1474</v>
       </c>
       <c r="S8">
-        <v>5360</v>
+        <v>1522</v>
       </c>
       <c r="T8" t="s">
         <v>41</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="V8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W8" t="s">
         <v>43</v>
       </c>
       <c r="X8">
-        <v>2270</v>
+        <v>3890</v>
       </c>
       <c r="Y8" t="s">
         <v>44</v>
@@ -1345,12 +1468,15 @@
         <v>45</v>
       </c>
       <c r="AA8">
-        <v>12099.1</v>
+        <v>5733.86</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1359,7 +1485,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>32</v>
@@ -1374,10 +1500,13 @@
         <v>35</v>
       </c>
       <c r="I9">
-        <v>3.04</v>
+        <v>0.67</v>
       </c>
       <c r="J9">
-        <v>1544</v>
+        <v>1000</v>
+      </c>
+      <c r="K9">
+        <v>2000</v>
       </c>
       <c r="L9" t="s">
         <v>36</v>
@@ -1395,19 +1524,19 @@
         <v>39</v>
       </c>
       <c r="Q9" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="R9">
-        <v>5400</v>
+        <v>1472</v>
       </c>
       <c r="S9">
-        <v>5430</v>
+        <v>1522</v>
       </c>
       <c r="T9" t="s">
         <v>41</v>
       </c>
       <c r="U9">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="V9" t="s">
         <v>42</v>
@@ -1416,7 +1545,7 @@
         <v>43</v>
       </c>
       <c r="X9">
-        <v>2470</v>
+        <v>3890</v>
       </c>
       <c r="Y9" t="s">
         <v>44</v>
@@ -1425,12 +1554,15 @@
         <v>45</v>
       </c>
       <c r="AA9">
-        <v>13338</v>
+        <v>5726.08</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1439,28 +1571,31 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
         <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
         <v>35</v>
       </c>
       <c r="I10">
-        <v>1.15</v>
+        <v>0.67</v>
       </c>
       <c r="J10">
-        <v>1303</v>
+        <v>1000</v>
+      </c>
+      <c r="K10">
+        <v>2000</v>
       </c>
       <c r="L10" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="M10" t="s">
         <v>37</v>
@@ -1478,25 +1613,25 @@
         <v>40</v>
       </c>
       <c r="R10">
-        <v>10260</v>
+        <v>1476</v>
       </c>
       <c r="S10">
-        <v>10263</v>
+        <v>1524</v>
       </c>
       <c r="T10" t="s">
         <v>41</v>
       </c>
       <c r="U10">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="V10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W10" t="s">
         <v>43</v>
       </c>
       <c r="X10">
-        <v>1570</v>
+        <v>3890</v>
       </c>
       <c r="Y10" t="s">
         <v>44</v>
@@ -1505,12 +1640,15 @@
         <v>45</v>
       </c>
       <c r="AA10">
-        <v>16108.2</v>
+        <v>5741.64</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
@@ -1519,28 +1657,31 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H11" t="s">
         <v>35</v>
       </c>
       <c r="I11">
-        <v>1.39</v>
+        <v>8.19</v>
       </c>
       <c r="J11">
-        <v>1307</v>
+        <v>1503</v>
+      </c>
+      <c r="K11">
+        <v>3002</v>
       </c>
       <c r="L11" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="M11" t="s">
         <v>37</v>
@@ -1552,31 +1693,31 @@
         <v>38</v>
       </c>
       <c r="P11" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q11" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="R11">
-        <v>5520</v>
+        <v>576</v>
       </c>
       <c r="S11">
-        <v>5550</v>
+        <v>600</v>
       </c>
       <c r="T11" t="s">
         <v>41</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="W11" t="s">
         <v>43</v>
       </c>
       <c r="X11">
-        <v>1570</v>
+        <v>2320</v>
       </c>
       <c r="Y11" t="s">
         <v>44</v>
@@ -1585,42 +1726,45 @@
         <v>45</v>
       </c>
       <c r="AA11">
-        <v>8666.4</v>
+        <v>1336.32</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="H12" t="s">
         <v>35</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>1.98</v>
       </c>
       <c r="J12">
-        <v>680</v>
+        <v>780</v>
       </c>
       <c r="L12" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="M12" t="s">
         <v>37</v>
@@ -1635,13 +1779,13 @@
         <v>39</v>
       </c>
       <c r="Q12" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="R12">
-        <v>3970</v>
+        <v>7840</v>
       </c>
       <c r="S12">
-        <v>3988</v>
+        <v>7840</v>
       </c>
       <c r="T12" t="s">
         <v>41</v>
@@ -1650,13 +1794,13 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="W12" t="s">
         <v>43</v>
       </c>
       <c r="X12">
-        <v>2320</v>
+        <v>3720</v>
       </c>
       <c r="Y12" t="s">
         <v>44</v>
@@ -1665,7 +1809,7 @@
         <v>45</v>
       </c>
       <c r="AA12">
-        <v>9210.4</v>
+        <v>29164.8</v>
       </c>
       <c r="AB12" t="b">
         <v>1</v>
@@ -1673,37 +1817,37 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
         <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="H13" t="s">
         <v>35</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>4.98</v>
       </c>
       <c r="J13">
-        <v>680</v>
+        <v>2001</v>
       </c>
       <c r="L13" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="M13" t="s">
         <v>37</v>
@@ -1715,16 +1859,16 @@
         <v>38</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q13" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="R13">
-        <v>3970</v>
+        <v>4940</v>
       </c>
       <c r="S13">
-        <v>3988</v>
+        <v>4941</v>
       </c>
       <c r="T13" t="s">
         <v>41</v>
@@ -1733,13 +1877,13 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="W13" t="s">
         <v>43</v>
       </c>
       <c r="X13">
-        <v>2320</v>
+        <v>2770</v>
       </c>
       <c r="Y13" t="s">
         <v>44</v>
@@ -1748,7 +1892,7 @@
         <v>45</v>
       </c>
       <c r="AA13">
-        <v>9210.4</v>
+        <v>13683.8</v>
       </c>
       <c r="AB13" t="b">
         <v>1</v>
@@ -1756,37 +1900,37 @@
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
         <v>50</v>
       </c>
-      <c r="F14" t="s">
-        <v>33</v>
-      </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="I14">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J14">
-        <v>1551</v>
+        <v>1460</v>
       </c>
       <c r="L14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M14" t="s">
         <v>37</v>
@@ -1798,16 +1942,16 @@
         <v>38</v>
       </c>
       <c r="P14" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q14" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="R14">
-        <v>2670</v>
+        <v>2910</v>
       </c>
       <c r="S14">
-        <v>2700</v>
+        <v>2919</v>
       </c>
       <c r="T14" t="s">
         <v>41</v>
@@ -1816,13 +1960,13 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="W14" t="s">
         <v>43</v>
       </c>
       <c r="X14">
-        <v>1570</v>
+        <v>1870</v>
       </c>
       <c r="Y14" t="s">
         <v>44</v>
@@ -1831,12 +1975,12 @@
         <v>45</v>
       </c>
       <c r="AA14">
-        <v>4191.9</v>
+        <v>5441.7</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
@@ -1845,13 +1989,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
         <v>50</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
       </c>
       <c r="G15" t="s">
         <v>34</v>
@@ -1860,10 +2004,10 @@
         <v>35</v>
       </c>
       <c r="I15">
-        <v>4.05</v>
+        <v>1.17</v>
       </c>
       <c r="J15">
-        <v>1545</v>
+        <v>118</v>
       </c>
       <c r="L15" t="s">
         <v>36</v>
@@ -1878,31 +2022,31 @@
         <v>38</v>
       </c>
       <c r="P15" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q15" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="R15">
-        <v>4760</v>
+        <v>3718</v>
       </c>
       <c r="S15">
-        <v>4763</v>
+        <v>3756</v>
       </c>
       <c r="T15" t="s">
         <v>41</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W15" t="s">
         <v>43</v>
       </c>
       <c r="X15">
-        <v>2270</v>
+        <v>3490</v>
       </c>
       <c r="Y15" t="s">
         <v>44</v>
@@ -1911,39 +2055,42 @@
         <v>45</v>
       </c>
       <c r="AA15">
-        <v>10805.2</v>
+        <v>12975.82</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
         <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G16" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H16" t="s">
         <v>35</v>
       </c>
       <c r="I16">
-        <v>1.78</v>
+        <v>0.56</v>
       </c>
       <c r="J16">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="L16" t="s">
         <v>36</v>
@@ -1958,31 +2105,31 @@
         <v>38</v>
       </c>
       <c r="P16" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q16" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="R16">
-        <v>1220</v>
+        <v>1859</v>
       </c>
       <c r="S16">
-        <v>1246</v>
+        <v>1955</v>
       </c>
       <c r="T16" t="s">
         <v>41</v>
       </c>
       <c r="U16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V16" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="W16" t="s">
         <v>43</v>
       </c>
       <c r="X16">
-        <v>3370</v>
+        <v>3590</v>
       </c>
       <c r="Y16" t="s">
         <v>44</v>
@@ -1991,7 +2138,7 @@
         <v>45</v>
       </c>
       <c r="AA16">
-        <v>4111.4</v>
+        <v>6673.81</v>
       </c>
       <c r="AB16" t="b">
         <v>1</v>
@@ -1999,34 +2146,34 @@
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
         <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
         <v>35</v>
       </c>
       <c r="I17">
-        <v>1.78</v>
+        <v>0.56</v>
       </c>
       <c r="J17">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="L17" t="s">
         <v>36</v>
@@ -2041,31 +2188,31 @@
         <v>38</v>
       </c>
       <c r="P17" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q17" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="R17">
-        <v>1181</v>
+        <v>1864</v>
       </c>
       <c r="S17">
-        <v>1207</v>
+        <v>1960</v>
       </c>
       <c r="T17" t="s">
         <v>41</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V17" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="W17" t="s">
         <v>43</v>
       </c>
       <c r="X17">
-        <v>3370</v>
+        <v>3590</v>
       </c>
       <c r="Y17" t="s">
         <v>44</v>
@@ -2074,7 +2221,7 @@
         <v>45</v>
       </c>
       <c r="AA17">
-        <v>3979.97</v>
+        <v>6691.76</v>
       </c>
       <c r="AB17" t="b">
         <v>1</v>
@@ -2082,37 +2229,37 @@
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
         <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="I18">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="L18" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="M18" t="s">
         <v>37</v>
@@ -2124,16 +2271,16 @@
         <v>38</v>
       </c>
       <c r="P18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="Q18" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="R18">
-        <v>2070</v>
+        <v>4090</v>
       </c>
       <c r="S18">
-        <v>2087</v>
+        <v>4098</v>
       </c>
       <c r="T18" t="s">
         <v>41</v>
@@ -2142,13 +2289,13 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="W18" t="s">
         <v>43</v>
       </c>
       <c r="X18">
-        <v>2470</v>
+        <v>1620</v>
       </c>
       <c r="Y18" t="s">
         <v>44</v>
@@ -2157,45 +2304,42 @@
         <v>45</v>
       </c>
       <c r="AA18">
-        <v>5112.9</v>
-      </c>
-      <c r="AB18" t="b">
-        <v>1</v>
+        <v>6625.8</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
         <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s">
         <v>35</v>
       </c>
       <c r="I19">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="J19">
-        <v>1251</v>
+        <v>600</v>
       </c>
       <c r="L19" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
@@ -2207,16 +2351,16 @@
         <v>38</v>
       </c>
       <c r="P19" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="Q19" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="R19">
-        <v>7380</v>
+        <v>3170</v>
       </c>
       <c r="S19">
-        <v>7383</v>
+        <v>3178</v>
       </c>
       <c r="T19" t="s">
         <v>41</v>
@@ -2225,13 +2369,13 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="W19" t="s">
         <v>43</v>
       </c>
       <c r="X19">
-        <v>1720</v>
+        <v>1570</v>
       </c>
       <c r="Y19" t="s">
         <v>44</v>
@@ -2240,45 +2384,42 @@
         <v>45</v>
       </c>
       <c r="AA19">
-        <v>12693.6</v>
-      </c>
-      <c r="AB19" t="b">
-        <v>1</v>
+        <v>4976.9</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
         <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G20" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="H20" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I20">
-        <v>11.99</v>
+        <v>0.39</v>
       </c>
       <c r="J20">
-        <v>1500</v>
+        <v>124</v>
       </c>
       <c r="L20" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="M20" t="s">
         <v>37</v>
@@ -2290,16 +2431,16 @@
         <v>38</v>
       </c>
       <c r="P20" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q20" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="R20">
-        <v>6170</v>
+        <v>1220</v>
       </c>
       <c r="S20">
-        <v>6171</v>
+        <v>1232</v>
       </c>
       <c r="T20" t="s">
         <v>41</v>
@@ -2308,13 +2449,13 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="W20" t="s">
         <v>43</v>
       </c>
       <c r="X20">
-        <v>3640</v>
+        <v>3790</v>
       </c>
       <c r="Y20" t="s">
         <v>44</v>
@@ -2323,10 +2464,1453 @@
         <v>45</v>
       </c>
       <c r="AA20">
-        <v>22458.8</v>
-      </c>
-      <c r="AB20" t="b">
+        <v>4623.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" t="s">
+        <v>63</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="J21">
+        <v>1547</v>
+      </c>
+      <c r="L21" t="s">
+        <v>36</v>
+      </c>
+      <c r="M21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" t="s">
+        <v>37</v>
+      </c>
+      <c r="O21" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>79</v>
+      </c>
+      <c r="R21">
+        <v>5960</v>
+      </c>
+      <c r="S21">
+        <v>5990</v>
+      </c>
+      <c r="T21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21">
+        <v>2270</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>13529.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22">
+        <v>0.58</v>
+      </c>
+      <c r="J22">
+        <v>1520</v>
+      </c>
+      <c r="L22" t="s">
+        <v>36</v>
+      </c>
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>79</v>
+      </c>
+      <c r="R22">
+        <v>3020</v>
+      </c>
+      <c r="S22">
+        <v>3053</v>
+      </c>
+      <c r="T22" t="s">
+        <v>41</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
+        <v>89</v>
+      </c>
+      <c r="W22" t="s">
+        <v>43</v>
+      </c>
+      <c r="X22">
+        <v>1720</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22">
+        <v>5194.4</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23">
+        <v>0.41</v>
+      </c>
+      <c r="J23">
+        <v>300</v>
+      </c>
+      <c r="L23" t="s">
+        <v>78</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>82</v>
+      </c>
+      <c r="R23">
+        <v>2270</v>
+      </c>
+      <c r="S23">
+        <v>2278</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23">
+        <v>1420</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA23">
+        <v>3223.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>0.41</v>
+      </c>
+      <c r="J24">
+        <v>300</v>
+      </c>
+      <c r="L24" t="s">
+        <v>78</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>82</v>
+      </c>
+      <c r="R24">
+        <v>2120</v>
+      </c>
+      <c r="S24">
+        <v>2128</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>1420</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>3010.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>0.69</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="L25" t="s">
+        <v>36</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>82</v>
+      </c>
+      <c r="R25">
+        <v>966</v>
+      </c>
+      <c r="S25">
+        <v>977</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
+        <v>42</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>3590</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>3467.94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>0.5</v>
+      </c>
+      <c r="J26">
+        <v>192</v>
+      </c>
+      <c r="L26" t="s">
+        <v>78</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>82</v>
+      </c>
+      <c r="R26">
+        <v>1162</v>
+      </c>
+      <c r="S26">
+        <v>1168</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26" t="s">
+        <v>89</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>1620</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>1882.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <v>0.5</v>
+      </c>
+      <c r="J27">
+        <v>192</v>
+      </c>
+      <c r="L27" t="s">
+        <v>78</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>82</v>
+      </c>
+      <c r="R27">
+        <v>1320</v>
+      </c>
+      <c r="S27">
+        <v>1328</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
+        <v>89</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>1620</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>2138.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>3.03</v>
+      </c>
+      <c r="J28">
+        <v>180</v>
+      </c>
+      <c r="L28" t="s">
+        <v>36</v>
+      </c>
+      <c r="M28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>82</v>
+      </c>
+      <c r="R28">
+        <v>1478</v>
+      </c>
+      <c r="S28">
+        <v>1488</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28" t="s">
+        <v>89</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>1320</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>1950.96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
+        <v>3.03</v>
+      </c>
+      <c r="J29">
+        <v>180</v>
+      </c>
+      <c r="L29" t="s">
+        <v>36</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>82</v>
+      </c>
+      <c r="R29">
+        <v>1544</v>
+      </c>
+      <c r="S29">
+        <v>1553</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>89</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>1320</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>2038.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>0.3</v>
+      </c>
+      <c r="J30">
+        <v>400</v>
+      </c>
+      <c r="L30" t="s">
+        <v>78</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>82</v>
+      </c>
+      <c r="R30">
+        <v>2064</v>
+      </c>
+      <c r="S30">
+        <v>2069</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>2</v>
+      </c>
+      <c r="V30" t="s">
+        <v>89</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>1620</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>3343.68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>0.3</v>
+      </c>
+      <c r="J31">
+        <v>400</v>
+      </c>
+      <c r="L31" t="s">
+        <v>78</v>
+      </c>
+      <c r="M31" t="s">
+        <v>37</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>82</v>
+      </c>
+      <c r="R31">
+        <v>2100</v>
+      </c>
+      <c r="S31">
+        <v>2104</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>2</v>
+      </c>
+      <c r="V31" t="s">
+        <v>89</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>1620</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>3402</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32">
+        <v>4.02</v>
+      </c>
+      <c r="J32">
+        <v>470</v>
+      </c>
+      <c r="L32" t="s">
+        <v>36</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>82</v>
+      </c>
+      <c r="R32">
+        <v>3750</v>
+      </c>
+      <c r="S32">
+        <v>3758</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>1</v>
+      </c>
+      <c r="V32" t="s">
+        <v>89</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>1320</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" t="s">
+        <v>118</v>
+      </c>
+      <c r="H33" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33">
+        <v>0.65</v>
+      </c>
+      <c r="J33">
+        <v>1315</v>
+      </c>
+      <c r="L33" t="s">
+        <v>78</v>
+      </c>
+      <c r="M33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>53</v>
+      </c>
+      <c r="R33">
+        <v>6230</v>
+      </c>
+      <c r="S33">
+        <v>6230</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
+        <v>89</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>1720</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>10715.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>0.5</v>
+      </c>
+      <c r="J34">
+        <v>1234</v>
+      </c>
+      <c r="L34" t="s">
+        <v>78</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>79</v>
+      </c>
+      <c r="R34">
+        <v>2440</v>
+      </c>
+      <c r="S34">
+        <v>2449</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>2470</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>6026.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35">
+        <v>1.15</v>
+      </c>
+      <c r="J35">
+        <v>1300</v>
+      </c>
+      <c r="L35" t="s">
+        <v>68</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>79</v>
+      </c>
+      <c r="R35">
+        <v>4610</v>
+      </c>
+      <c r="S35">
+        <v>4630</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35" t="s">
+        <v>69</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>1770</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>8159.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" t="s">
+        <v>50</v>
+      </c>
+      <c r="G36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <v>0.81</v>
+      </c>
+      <c r="J36">
+        <v>400</v>
+      </c>
+      <c r="L36" t="s">
+        <v>78</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>82</v>
+      </c>
+      <c r="R36">
+        <v>2735</v>
+      </c>
+      <c r="S36">
+        <v>2747</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="V36" t="s">
+        <v>126</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>2270</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>6208.45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" t="s">
+        <v>129</v>
+      </c>
+      <c r="H37" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37">
+        <v>1.67</v>
+      </c>
+      <c r="J37">
+        <v>1198</v>
+      </c>
+      <c r="L37" t="s">
+        <v>68</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>53</v>
+      </c>
+      <c r="R37">
+        <v>4300</v>
+      </c>
+      <c r="S37">
+        <v>4301</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37" t="s">
+        <v>126</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>2470</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>10621</v>
+      </c>
+      <c r="AB37" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>0.48</v>
+      </c>
+      <c r="J38">
+        <v>163</v>
+      </c>
+      <c r="L38" t="s">
+        <v>36</v>
+      </c>
+      <c r="M38" t="s">
+        <v>37</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>82</v>
+      </c>
+      <c r="R38">
+        <v>1125</v>
+      </c>
+      <c r="S38">
+        <v>1137</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>1</v>
+      </c>
+      <c r="V38" t="s">
+        <v>42</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>3790</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>4263.75</v>
       </c>
     </row>
   </sheetData>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2175" uniqueCount="272">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -385,28 +385,448 @@
     <t>Coil K41/1.4509-441 2D without paper 1.15 x 1300.0 mm Unslit</t>
   </si>
   <si>
-    <t>G26RJX15</t>
-  </si>
-  <si>
-    <t>Coil 1.4307-304L 2R without paper 0.81 x 400.0 mm Slit</t>
+    <t>K260282194</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2D with paper 1.67 x 1198.0 mm Unslit not marked</t>
+  </si>
+  <si>
+    <t>1.4301ED-304</t>
   </si>
   <si>
     <t>ASME SA 240 / ASTM A 240 / ASTM A 666 / EN 10028-7 / EN 10088-2 / EN 10088-4 / IS 6911 / JIS G 4305</t>
   </si>
   <si>
-    <t>K260282194</t>
-  </si>
-  <si>
-    <t>Coil 1.4301ED-304 2D with paper 1.67 x 1198.0 mm Unslit not marked</t>
-  </si>
-  <si>
-    <t>1.4301ED-304</t>
-  </si>
-  <si>
     <t>G26RJX26</t>
   </si>
   <si>
     <t>Coil 1.4404-316L 2B without paper 0.48 x 163.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7249576</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489700</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489750</t>
+  </si>
+  <si>
+    <t>7257703</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2E 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>2E</t>
+  </si>
+  <si>
+    <t>7257864</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257894</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>S139218</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 12.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258091</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258149</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491483</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258526</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258730</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258862</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258863</t>
+  </si>
+  <si>
+    <t>7259015</t>
+  </si>
+  <si>
+    <t>Coil 1.4520-430Ti 2B 1.2 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4520-430Ti</t>
+  </si>
+  <si>
+    <t>7259028</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R without paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259050</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R NOV 4241/4513 0.8 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>NOV 4241/4513</t>
+  </si>
+  <si>
+    <t>7259145</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T492642</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 3.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259417</t>
+  </si>
+  <si>
+    <t>7259437</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259438</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B with paper 1.0 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7259439</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R with paper 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259447</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T493044</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259677</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B without paper 8.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7259689</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R with paper 0.8 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T493468</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.25 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259716</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R without paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259717</t>
+  </si>
+  <si>
+    <t>7259732</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 6.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7259736</t>
+  </si>
+  <si>
+    <t>7259803</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 0.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259914</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T493993</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T493994</t>
+  </si>
+  <si>
+    <t>7260311</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D without paper 12.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7260313</t>
+  </si>
+  <si>
+    <t>7260315</t>
+  </si>
+  <si>
+    <t>7260324</t>
+  </si>
+  <si>
+    <t>T494573</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7260481</t>
+  </si>
+  <si>
+    <t>7260483</t>
+  </si>
+  <si>
+    <t>T494673</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7260613</t>
+  </si>
+  <si>
+    <t>7260615</t>
+  </si>
+  <si>
+    <t>7260617</t>
+  </si>
+  <si>
+    <t>7260620</t>
+  </si>
+  <si>
+    <t>7260621</t>
+  </si>
+  <si>
+    <t>7260622</t>
+  </si>
+  <si>
+    <t>7260623</t>
+  </si>
+  <si>
+    <t>7260625</t>
+  </si>
+  <si>
+    <t>7260626</t>
   </si>
 </sst>
 </file>
@@ -783,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB38"/>
+  <dimension ref="A1:AB114"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -3675,10 +4095,10 @@
         <v>124</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="D36" t="s">
         <v>125</v>
@@ -3690,19 +4110,19 @@
         <v>50</v>
       </c>
       <c r="G36" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="H36" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="I36">
-        <v>0.81</v>
+        <v>1.67</v>
       </c>
       <c r="J36">
-        <v>400</v>
+        <v>1198</v>
       </c>
       <c r="L36" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="M36" t="s">
         <v>37</v>
@@ -3714,16 +4134,16 @@
         <v>38</v>
       </c>
       <c r="P36" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q36" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="R36">
-        <v>2735</v>
+        <v>4300</v>
       </c>
       <c r="S36">
-        <v>2747</v>
+        <v>4301</v>
       </c>
       <c r="T36" t="s">
         <v>41</v>
@@ -3732,13 +4152,13 @@
         <v>1</v>
       </c>
       <c r="V36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W36" t="s">
         <v>43</v>
       </c>
       <c r="X36">
-        <v>2270</v>
+        <v>2470</v>
       </c>
       <c r="Y36" t="s">
         <v>44</v>
@@ -3747,21 +4167,24 @@
         <v>45</v>
       </c>
       <c r="AA36">
-        <v>6208.45</v>
+        <v>10621</v>
+      </c>
+      <c r="AB36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E37" t="s">
         <v>32</v>
@@ -3770,19 +4193,19 @@
         <v>50</v>
       </c>
       <c r="G37" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="H37" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="I37">
-        <v>1.67</v>
+        <v>0.48</v>
       </c>
       <c r="J37">
-        <v>1198</v>
+        <v>163</v>
       </c>
       <c r="L37" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="M37" t="s">
         <v>37</v>
@@ -3794,16 +4217,16 @@
         <v>38</v>
       </c>
       <c r="P37" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="Q37" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="R37">
-        <v>4300</v>
+        <v>1125</v>
       </c>
       <c r="S37">
-        <v>4301</v>
+        <v>1137</v>
       </c>
       <c r="T37" t="s">
         <v>41</v>
@@ -3812,13 +4235,13 @@
         <v>1</v>
       </c>
       <c r="V37" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="W37" t="s">
         <v>43</v>
       </c>
       <c r="X37">
-        <v>2470</v>
+        <v>3790</v>
       </c>
       <c r="Y37" t="s">
         <v>44</v>
@@ -3827,10 +4250,7 @@
         <v>45</v>
       </c>
       <c r="AA37">
-        <v>10621</v>
-      </c>
-      <c r="AB37" t="b">
-        <v>0</v>
+        <v>4263.75</v>
       </c>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
@@ -3838,34 +4258,37 @@
         <v>130</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G38" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s">
         <v>35</v>
       </c>
       <c r="I38">
-        <v>0.48</v>
+        <v>2</v>
       </c>
       <c r="J38">
-        <v>163</v>
+        <v>1250</v>
+      </c>
+      <c r="K38">
+        <v>2500</v>
       </c>
       <c r="L38" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="M38" t="s">
         <v>37</v>
@@ -3877,16 +4300,16 @@
         <v>38</v>
       </c>
       <c r="P38" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="Q38" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="R38">
-        <v>1125</v>
+        <v>322</v>
       </c>
       <c r="S38">
-        <v>1137</v>
+        <v>322</v>
       </c>
       <c r="T38" t="s">
         <v>41</v>
@@ -3895,22 +4318,6372 @@
         <v>1</v>
       </c>
       <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>1370</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>441.14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" t="s">
+        <v>97</v>
+      </c>
+      <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="J39">
+        <v>1250</v>
+      </c>
+      <c r="K39">
+        <v>2500</v>
+      </c>
+      <c r="L39" t="s">
+        <v>78</v>
+      </c>
+      <c r="M39" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>134</v>
+      </c>
+      <c r="R39">
+        <v>340</v>
+      </c>
+      <c r="S39">
+        <v>340</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>7</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>1370</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>2000</v>
+      </c>
+      <c r="K40">
+        <v>6000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>36</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>134</v>
+      </c>
+      <c r="R40">
+        <v>283</v>
+      </c>
+      <c r="S40">
+        <v>283</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>3560</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>1007.48</v>
+      </c>
+      <c r="AB40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>139</v>
+      </c>
+      <c r="B41" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" t="s">
+        <v>142</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>8</v>
+      </c>
+      <c r="J41">
+        <v>1250</v>
+      </c>
+      <c r="K41">
+        <v>2500</v>
+      </c>
+      <c r="L41" t="s">
+        <v>51</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>134</v>
+      </c>
+      <c r="R41">
+        <v>394</v>
+      </c>
+      <c r="S41">
+        <v>394</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>3490</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" t="s">
+        <v>144</v>
+      </c>
+      <c r="E42" t="s">
+        <v>97</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
+        <v>145</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>2000</v>
+      </c>
+      <c r="K42">
+        <v>6000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>134</v>
+      </c>
+      <c r="R42">
+        <v>472</v>
+      </c>
+      <c r="S42">
+        <v>472</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>2190</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" t="s">
+        <v>147</v>
+      </c>
+      <c r="E43" t="s">
+        <v>97</v>
+      </c>
+      <c r="F43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>1500</v>
+      </c>
+      <c r="K43">
+        <v>3000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>36</v>
+      </c>
+      <c r="M43" t="s">
+        <v>148</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>134</v>
+      </c>
+      <c r="R43">
+        <v>970</v>
+      </c>
+      <c r="S43">
+        <v>970</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>13</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>3490</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" t="s">
+        <v>150</v>
+      </c>
+      <c r="E44" t="s">
+        <v>97</v>
+      </c>
+      <c r="F44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" t="s">
+        <v>88</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="J44">
+        <v>1500</v>
+      </c>
+      <c r="K44">
+        <v>3000</v>
+      </c>
+      <c r="L44" t="s">
+        <v>51</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>134</v>
+      </c>
+      <c r="R44">
+        <v>354</v>
+      </c>
+      <c r="S44">
+        <v>354</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>2</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>1170</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" t="s">
+        <v>132</v>
+      </c>
+      <c r="D45" t="s">
+        <v>152</v>
+      </c>
+      <c r="E45" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" t="s">
+        <v>50</v>
+      </c>
+      <c r="G45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>1.5</v>
+      </c>
+      <c r="J45">
+        <v>1250</v>
+      </c>
+      <c r="L45" t="s">
+        <v>36</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>134</v>
+      </c>
+      <c r="R45">
+        <v>1275</v>
+      </c>
+      <c r="S45">
+        <v>1275</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>3590</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>153</v>
+      </c>
+      <c r="B46" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D46" t="s">
+        <v>154</v>
+      </c>
+      <c r="E46" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" t="s">
+        <v>88</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>1500</v>
+      </c>
+      <c r="K46">
+        <v>3000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>134</v>
+      </c>
+      <c r="R46">
+        <v>212</v>
+      </c>
+      <c r="S46">
+        <v>212</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>2</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>1320</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>155</v>
+      </c>
+      <c r="B47" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" t="s">
+        <v>154</v>
+      </c>
+      <c r="E47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F47" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" t="s">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>1500</v>
+      </c>
+      <c r="K47">
+        <v>3000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>36</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>134</v>
+      </c>
+      <c r="R47">
+        <v>319</v>
+      </c>
+      <c r="S47">
+        <v>319</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>3</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>1370</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>156</v>
+      </c>
+      <c r="B48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" t="s">
+        <v>132</v>
+      </c>
+      <c r="D48" t="s">
+        <v>147</v>
+      </c>
+      <c r="E48" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>1500</v>
+      </c>
+      <c r="K48">
+        <v>3000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" t="s">
+        <v>148</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>134</v>
+      </c>
+      <c r="R48">
+        <v>1010</v>
+      </c>
+      <c r="S48">
+        <v>1010</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>14</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>3540</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" t="s">
+        <v>97</v>
+      </c>
+      <c r="F49" t="s">
+        <v>50</v>
+      </c>
+      <c r="G49" t="s">
+        <v>126</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>0.8</v>
+      </c>
+      <c r="J49">
+        <v>1000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>78</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>159</v>
+      </c>
+      <c r="P49" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>134</v>
+      </c>
+      <c r="R49">
+        <v>1585</v>
+      </c>
+      <c r="S49">
+        <v>1585</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>1</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>2370</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>160</v>
+      </c>
+      <c r="B50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" t="s">
+        <v>97</v>
+      </c>
+      <c r="F50" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" t="s">
+        <v>88</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>1.5</v>
+      </c>
+      <c r="J50">
+        <v>1500</v>
+      </c>
+      <c r="K50">
+        <v>3000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>36</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>134</v>
+      </c>
+      <c r="R50">
+        <v>212</v>
+      </c>
+      <c r="S50">
+        <v>212</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>1320</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" t="s">
+        <v>137</v>
+      </c>
+      <c r="C51" t="s">
+        <v>132</v>
+      </c>
+      <c r="D51" t="s">
+        <v>163</v>
+      </c>
+      <c r="E51" t="s">
+        <v>97</v>
+      </c>
+      <c r="F51" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" t="s">
+        <v>63</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>4</v>
+      </c>
+      <c r="J51">
+        <v>1000</v>
+      </c>
+      <c r="K51">
+        <v>2000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>36</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>134</v>
+      </c>
+      <c r="R51">
+        <v>315</v>
+      </c>
+      <c r="S51">
+        <v>315</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>5</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>2220</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" t="s">
+        <v>165</v>
+      </c>
+      <c r="E52" t="s">
+        <v>97</v>
+      </c>
+      <c r="F52" t="s">
+        <v>33</v>
+      </c>
+      <c r="G52" t="s">
+        <v>63</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
+      </c>
+      <c r="J52">
+        <v>1000</v>
+      </c>
+      <c r="K52">
+        <v>2000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>51</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>134</v>
+      </c>
+      <c r="R52">
+        <v>944</v>
+      </c>
+      <c r="S52">
+        <v>944</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>1</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>2020</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D53" t="s">
+        <v>167</v>
+      </c>
+      <c r="E53" t="s">
+        <v>97</v>
+      </c>
+      <c r="F53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>1500</v>
+      </c>
+      <c r="K53">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>36</v>
+      </c>
+      <c r="M53" t="s">
+        <v>148</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>134</v>
+      </c>
+      <c r="R53">
+        <v>1224</v>
+      </c>
+      <c r="S53">
+        <v>1224</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>34</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>3540</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" t="s">
+        <v>132</v>
+      </c>
+      <c r="D54" t="s">
+        <v>169</v>
+      </c>
+      <c r="E54" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" t="s">
+        <v>88</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>1.5</v>
+      </c>
+      <c r="J54">
+        <v>1500</v>
+      </c>
+      <c r="K54">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>78</v>
+      </c>
+      <c r="M54" t="s">
+        <v>148</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>134</v>
+      </c>
+      <c r="R54">
+        <v>916</v>
+      </c>
+      <c r="S54">
+        <v>916</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>18</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>1320</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>170</v>
+      </c>
+      <c r="B55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" t="s">
+        <v>132</v>
+      </c>
+      <c r="D55" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" t="s">
+        <v>50</v>
+      </c>
+      <c r="G55" t="s">
+        <v>126</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>0.8</v>
+      </c>
+      <c r="J55">
+        <v>1000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>78</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>134</v>
+      </c>
+      <c r="R55">
+        <v>1000</v>
+      </c>
+      <c r="S55">
+        <v>1000</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>1</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>2370</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" t="s">
+        <v>132</v>
+      </c>
+      <c r="D56" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" t="s">
+        <v>97</v>
+      </c>
+      <c r="F56" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" t="s">
+        <v>63</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>2.5</v>
+      </c>
+      <c r="J56">
+        <v>1500</v>
+      </c>
+      <c r="K56">
+        <v>3000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>36</v>
+      </c>
+      <c r="M56" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>134</v>
+      </c>
+      <c r="R56">
+        <v>266</v>
+      </c>
+      <c r="S56">
+        <v>266</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>3</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>2220</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>174</v>
+      </c>
+      <c r="B57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" t="s">
+        <v>132</v>
+      </c>
+      <c r="D57" t="s">
+        <v>175</v>
+      </c>
+      <c r="E57" t="s">
+        <v>97</v>
+      </c>
+      <c r="F57" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" t="s">
+        <v>34</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>2.5</v>
+      </c>
+      <c r="J57">
+        <v>2000</v>
+      </c>
+      <c r="K57">
+        <v>4000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>36</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>134</v>
+      </c>
+      <c r="R57">
+        <v>315</v>
+      </c>
+      <c r="S57">
+        <v>315</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>2</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>3560</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>176</v>
+      </c>
+      <c r="B58" t="s">
+        <v>140</v>
+      </c>
+      <c r="C58" t="s">
+        <v>132</v>
+      </c>
+      <c r="D58" t="s">
+        <v>175</v>
+      </c>
+      <c r="E58" t="s">
+        <v>97</v>
+      </c>
+      <c r="F58" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58" t="s">
+        <v>34</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>2.5</v>
+      </c>
+      <c r="J58">
+        <v>2000</v>
+      </c>
+      <c r="K58">
+        <v>4000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>36</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>134</v>
+      </c>
+      <c r="R58">
+        <v>315</v>
+      </c>
+      <c r="S58">
+        <v>315</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>2</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>3560</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>177</v>
+      </c>
+      <c r="B59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59" t="s">
+        <v>132</v>
+      </c>
+      <c r="D59" t="s">
+        <v>178</v>
+      </c>
+      <c r="E59" t="s">
+        <v>97</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" t="s">
+        <v>63</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+      <c r="J59">
+        <v>1000</v>
+      </c>
+      <c r="K59">
+        <v>2000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>36</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>134</v>
+      </c>
+      <c r="R59">
+        <v>1448</v>
+      </c>
+      <c r="S59">
+        <v>1448</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>1</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2270</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>3286.96</v>
+      </c>
+      <c r="AB59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s">
+        <v>137</v>
+      </c>
+      <c r="C60" t="s">
+        <v>132</v>
+      </c>
+      <c r="D60" t="s">
+        <v>180</v>
+      </c>
+      <c r="E60" t="s">
+        <v>97</v>
+      </c>
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" t="s">
+        <v>88</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>4</v>
+      </c>
+      <c r="J60">
+        <v>1000</v>
+      </c>
+      <c r="K60">
+        <v>2000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>36</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>134</v>
+      </c>
+      <c r="R60">
+        <v>384</v>
+      </c>
+      <c r="S60">
+        <v>384</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>6</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>1370</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>181</v>
+      </c>
+      <c r="B61" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" t="s">
+        <v>132</v>
+      </c>
+      <c r="D61" t="s">
+        <v>182</v>
+      </c>
+      <c r="E61" t="s">
+        <v>97</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>63</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>1000</v>
+      </c>
+      <c r="K61">
+        <v>2000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>36</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>134</v>
+      </c>
+      <c r="R61">
+        <v>283</v>
+      </c>
+      <c r="S61">
+        <v>283</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>9</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>2220</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" t="s">
+        <v>132</v>
+      </c>
+      <c r="D62" t="s">
+        <v>154</v>
+      </c>
+      <c r="E62" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" t="s">
+        <v>88</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>3</v>
+      </c>
+      <c r="J62">
+        <v>1500</v>
+      </c>
+      <c r="K62">
+        <v>3000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>134</v>
+      </c>
+      <c r="R62">
+        <v>637</v>
+      </c>
+      <c r="S62">
+        <v>637</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>6</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>1370</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>872.69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" t="s">
+        <v>140</v>
+      </c>
+      <c r="C63" t="s">
+        <v>132</v>
+      </c>
+      <c r="D63" t="s">
+        <v>185</v>
+      </c>
+      <c r="E63" t="s">
+        <v>97</v>
+      </c>
+      <c r="F63" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" t="s">
+        <v>142</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>4</v>
+      </c>
+      <c r="J63">
+        <v>1500</v>
+      </c>
+      <c r="K63">
+        <v>3000</v>
+      </c>
+      <c r="L63" t="s">
+        <v>186</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>134</v>
+      </c>
+      <c r="R63">
+        <v>1133</v>
+      </c>
+      <c r="S63">
+        <v>1133</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>8</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>3540</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>4010.82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>187</v>
+      </c>
+      <c r="B64" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" t="s">
+        <v>132</v>
+      </c>
+      <c r="D64" t="s">
+        <v>188</v>
+      </c>
+      <c r="E64" t="s">
+        <v>97</v>
+      </c>
+      <c r="F64" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64" t="s">
+        <v>63</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>8</v>
+      </c>
+      <c r="J64">
+        <v>2000</v>
+      </c>
+      <c r="K64">
+        <v>6000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>51</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>134</v>
+      </c>
+      <c r="R64">
+        <v>755</v>
+      </c>
+      <c r="S64">
+        <v>755</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>1</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>2040</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>1540.2</v>
+      </c>
+      <c r="AB64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" t="s">
+        <v>137</v>
+      </c>
+      <c r="C65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D65" t="s">
+        <v>190</v>
+      </c>
+      <c r="E65" t="s">
+        <v>97</v>
+      </c>
+      <c r="F65" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" t="s">
+        <v>63</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>8</v>
+      </c>
+      <c r="J65">
+        <v>1000</v>
+      </c>
+      <c r="K65">
+        <v>2000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>51</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>134</v>
+      </c>
+      <c r="R65">
+        <v>504</v>
+      </c>
+      <c r="S65">
+        <v>504</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>4</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>2020</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>1018.08</v>
+      </c>
+      <c r="AB65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>191</v>
+      </c>
+      <c r="B66" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" t="s">
+        <v>132</v>
+      </c>
+      <c r="D66" t="s">
+        <v>192</v>
+      </c>
+      <c r="E66" t="s">
+        <v>97</v>
+      </c>
+      <c r="F66" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" t="s">
+        <v>63</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>12</v>
+      </c>
+      <c r="J66">
+        <v>1000</v>
+      </c>
+      <c r="K66">
+        <v>2000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>51</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>134</v>
+      </c>
+      <c r="R66">
+        <v>1322</v>
+      </c>
+      <c r="S66">
+        <v>1322</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>7</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>2070</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>2736.54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>193</v>
+      </c>
+      <c r="B67" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" t="s">
+        <v>132</v>
+      </c>
+      <c r="D67" t="s">
+        <v>194</v>
+      </c>
+      <c r="E67" t="s">
+        <v>97</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>2.5</v>
+      </c>
+      <c r="J67">
+        <v>1500</v>
+      </c>
+      <c r="K67">
+        <v>3000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>36</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>134</v>
+      </c>
+      <c r="R67">
+        <v>534</v>
+      </c>
+      <c r="S67">
+        <v>534</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>6</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>3540</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>1890.36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C68" t="s">
+        <v>132</v>
+      </c>
+      <c r="D68" t="s">
+        <v>196</v>
+      </c>
+      <c r="E68" t="s">
+        <v>97</v>
+      </c>
+      <c r="F68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" t="s">
+        <v>34</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+      <c r="J68">
+        <v>1000</v>
+      </c>
+      <c r="K68">
+        <v>2000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>36</v>
+      </c>
+      <c r="M68" t="s">
+        <v>148</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>134</v>
+      </c>
+      <c r="R68">
+        <v>1046</v>
+      </c>
+      <c r="S68">
+        <v>1046</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>33</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>3540</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>3702.84</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>197</v>
+      </c>
+      <c r="B69" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" t="s">
+        <v>132</v>
+      </c>
+      <c r="D69" t="s">
+        <v>198</v>
+      </c>
+      <c r="E69" t="s">
+        <v>97</v>
+      </c>
+      <c r="F69" t="s">
+        <v>33</v>
+      </c>
+      <c r="G69" t="s">
+        <v>63</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>4</v>
+      </c>
+      <c r="J69">
+        <v>1500</v>
+      </c>
+      <c r="K69">
+        <v>3000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>36</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>134</v>
+      </c>
+      <c r="R69">
+        <v>142</v>
+      </c>
+      <c r="S69">
+        <v>142</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>1</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>2170</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" t="s">
+        <v>132</v>
+      </c>
+      <c r="D70" t="s">
+        <v>200</v>
+      </c>
+      <c r="E70" t="s">
+        <v>97</v>
+      </c>
+      <c r="F70" t="s">
+        <v>33</v>
+      </c>
+      <c r="G70" t="s">
+        <v>63</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>2</v>
+      </c>
+      <c r="J70">
+        <v>2000</v>
+      </c>
+      <c r="K70">
+        <v>4000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>36</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>38</v>
+      </c>
+      <c r="P70" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>134</v>
+      </c>
+      <c r="R70">
+        <v>126</v>
+      </c>
+      <c r="S70">
+        <v>126</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>1</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>2190</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>201</v>
+      </c>
+      <c r="B71" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" t="s">
+        <v>132</v>
+      </c>
+      <c r="D71" t="s">
+        <v>202</v>
+      </c>
+      <c r="E71" t="s">
+        <v>97</v>
+      </c>
+      <c r="F71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G71" t="s">
+        <v>34</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+      <c r="J71">
+        <v>1250</v>
+      </c>
+      <c r="K71">
+        <v>2500</v>
+      </c>
+      <c r="L71" t="s">
+        <v>36</v>
+      </c>
+      <c r="M71" t="s">
+        <v>148</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>134</v>
+      </c>
+      <c r="R71">
+        <v>612</v>
+      </c>
+      <c r="S71">
+        <v>612</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>12</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>3490</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>2135.88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>203</v>
+      </c>
+      <c r="B72" t="s">
+        <v>137</v>
+      </c>
+      <c r="C72" t="s">
+        <v>132</v>
+      </c>
+      <c r="D72" t="s">
+        <v>204</v>
+      </c>
+      <c r="E72" t="s">
+        <v>97</v>
+      </c>
+      <c r="F72" t="s">
+        <v>33</v>
+      </c>
+      <c r="G72" t="s">
+        <v>142</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>3</v>
+      </c>
+      <c r="J72">
+        <v>1500</v>
+      </c>
+      <c r="K72">
+        <v>3000</v>
+      </c>
+      <c r="L72" t="s">
+        <v>36</v>
+      </c>
+      <c r="M72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>134</v>
+      </c>
+      <c r="R72">
+        <v>106</v>
+      </c>
+      <c r="S72">
+        <v>106</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>1</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>3640</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>385.84</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>205</v>
+      </c>
+      <c r="B73" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" t="s">
+        <v>132</v>
+      </c>
+      <c r="D73" t="s">
+        <v>206</v>
+      </c>
+      <c r="E73" t="s">
+        <v>97</v>
+      </c>
+      <c r="F73" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" t="s">
+        <v>34</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>1.5</v>
+      </c>
+      <c r="J73">
+        <v>1500</v>
+      </c>
+      <c r="K73">
+        <v>3000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>36</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>134</v>
+      </c>
+      <c r="R73">
+        <v>330</v>
+      </c>
+      <c r="S73">
+        <v>330</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>6</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>3540</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>207</v>
+      </c>
+      <c r="B74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" t="s">
+        <v>208</v>
+      </c>
+      <c r="E74" t="s">
+        <v>97</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" t="s">
+        <v>63</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>3</v>
+      </c>
+      <c r="J74">
+        <v>1000</v>
+      </c>
+      <c r="K74">
+        <v>2000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>36</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>134</v>
+      </c>
+      <c r="R74">
+        <v>1464</v>
+      </c>
+      <c r="S74">
+        <v>1464</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>31</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>2270</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>3323.28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>209</v>
+      </c>
+      <c r="B75" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" t="s">
+        <v>132</v>
+      </c>
+      <c r="D75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E75" t="s">
+        <v>97</v>
+      </c>
+      <c r="F75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G75" t="s">
+        <v>63</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>3</v>
+      </c>
+      <c r="J75">
+        <v>1000</v>
+      </c>
+      <c r="K75">
+        <v>2000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>36</v>
+      </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>134</v>
+      </c>
+      <c r="R75">
+        <v>94</v>
+      </c>
+      <c r="S75">
+        <v>94</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>2</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>2170</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>210</v>
+      </c>
+      <c r="B76" t="s">
+        <v>131</v>
+      </c>
+      <c r="C76" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" t="s">
+        <v>97</v>
+      </c>
+      <c r="F76" t="s">
+        <v>50</v>
+      </c>
+      <c r="G76" t="s">
+        <v>212</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>1.2</v>
+      </c>
+      <c r="J76">
+        <v>1250</v>
+      </c>
+      <c r="L76" t="s">
+        <v>36</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>134</v>
+      </c>
+      <c r="R76">
+        <v>1420</v>
+      </c>
+      <c r="S76">
+        <v>1420</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>1</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>1420</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>2016.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>213</v>
+      </c>
+      <c r="B77" t="s">
+        <v>131</v>
+      </c>
+      <c r="C77" t="s">
+        <v>132</v>
+      </c>
+      <c r="D77" t="s">
+        <v>214</v>
+      </c>
+      <c r="E77" t="s">
+        <v>97</v>
+      </c>
+      <c r="F77" t="s">
+        <v>33</v>
+      </c>
+      <c r="G77" t="s">
+        <v>88</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>1500</v>
+      </c>
+      <c r="K77">
+        <v>3000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>78</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>134</v>
+      </c>
+      <c r="R77">
+        <v>414</v>
+      </c>
+      <c r="S77">
+        <v>414</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>12</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>1370</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>567.18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>215</v>
+      </c>
+      <c r="B78" t="s">
+        <v>131</v>
+      </c>
+      <c r="C78" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" t="s">
+        <v>216</v>
+      </c>
+      <c r="E78" t="s">
+        <v>97</v>
+      </c>
+      <c r="F78" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" t="s">
+        <v>88</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>0.8</v>
+      </c>
+      <c r="J78">
+        <v>1500</v>
+      </c>
+      <c r="K78">
+        <v>3000</v>
+      </c>
+      <c r="L78" t="s">
+        <v>78</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>217</v>
+      </c>
+      <c r="P78" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>134</v>
+      </c>
+      <c r="R78">
+        <v>2584</v>
+      </c>
+      <c r="S78">
+        <v>2584</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>94</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>1520</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>3927.68</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>218</v>
+      </c>
+      <c r="B79" t="s">
+        <v>131</v>
+      </c>
+      <c r="C79" t="s">
+        <v>132</v>
+      </c>
+      <c r="D79" t="s">
+        <v>219</v>
+      </c>
+      <c r="E79" t="s">
+        <v>97</v>
+      </c>
+      <c r="F79" t="s">
+        <v>33</v>
+      </c>
+      <c r="G79" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <v>1250</v>
+      </c>
+      <c r="K79">
+        <v>2500</v>
+      </c>
+      <c r="L79" t="s">
+        <v>78</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>134</v>
+      </c>
+      <c r="R79">
+        <v>668</v>
+      </c>
+      <c r="S79">
+        <v>668</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>1</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>1370</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>915.16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>220</v>
+      </c>
+      <c r="B80" t="s">
+        <v>140</v>
+      </c>
+      <c r="C80" t="s">
+        <v>132</v>
+      </c>
+      <c r="D80" t="s">
+        <v>221</v>
+      </c>
+      <c r="E80" t="s">
+        <v>97</v>
+      </c>
+      <c r="F80" t="s">
+        <v>33</v>
+      </c>
+      <c r="G80" t="s">
+        <v>34</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>3</v>
+      </c>
+      <c r="J80">
+        <v>2000</v>
+      </c>
+      <c r="K80">
+        <v>4000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>36</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>134</v>
+      </c>
+      <c r="R80">
+        <v>189</v>
+      </c>
+      <c r="S80">
+        <v>189</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>1</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>3510</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>663.39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>222</v>
+      </c>
+      <c r="B81" t="s">
+        <v>131</v>
+      </c>
+      <c r="C81" t="s">
+        <v>132</v>
+      </c>
+      <c r="D81" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" t="s">
+        <v>97</v>
+      </c>
+      <c r="F81" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" t="s">
+        <v>88</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+      <c r="J81">
+        <v>1250</v>
+      </c>
+      <c r="K81">
+        <v>2500</v>
+      </c>
+      <c r="L81" t="s">
+        <v>78</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>134</v>
+      </c>
+      <c r="R81">
+        <v>1554</v>
+      </c>
+      <c r="S81">
+        <v>1554</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>1</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>1420</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>2206.68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>223</v>
+      </c>
+      <c r="B82" t="s">
+        <v>131</v>
+      </c>
+      <c r="C82" t="s">
+        <v>132</v>
+      </c>
+      <c r="D82" t="s">
+        <v>224</v>
+      </c>
+      <c r="E82" t="s">
+        <v>97</v>
+      </c>
+      <c r="F82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G82" t="s">
+        <v>88</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>1500</v>
+      </c>
+      <c r="K82">
+        <v>3000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>36</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>134</v>
+      </c>
+      <c r="R82">
+        <v>2210</v>
+      </c>
+      <c r="S82">
+        <v>2210</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>1</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>1420</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>3138.2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>225</v>
+      </c>
+      <c r="B83" t="s">
+        <v>131</v>
+      </c>
+      <c r="C83" t="s">
+        <v>132</v>
+      </c>
+      <c r="D83" t="s">
+        <v>226</v>
+      </c>
+      <c r="E83" t="s">
+        <v>97</v>
+      </c>
+      <c r="F83" t="s">
+        <v>50</v>
+      </c>
+      <c r="G83" t="s">
+        <v>88</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>1500</v>
+      </c>
+      <c r="L83" t="s">
+        <v>36</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>134</v>
+      </c>
+      <c r="R83">
+        <v>3350</v>
+      </c>
+      <c r="S83">
+        <v>3350</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>1</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>1420</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>227</v>
+      </c>
+      <c r="B84" t="s">
+        <v>131</v>
+      </c>
+      <c r="C84" t="s">
+        <v>132</v>
+      </c>
+      <c r="D84" t="s">
+        <v>228</v>
+      </c>
+      <c r="E84" t="s">
+        <v>97</v>
+      </c>
+      <c r="F84" t="s">
+        <v>33</v>
+      </c>
+      <c r="G84" t="s">
+        <v>88</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>1.5</v>
+      </c>
+      <c r="J84">
+        <v>1250</v>
+      </c>
+      <c r="K84">
+        <v>2500</v>
+      </c>
+      <c r="L84" t="s">
+        <v>78</v>
+      </c>
+      <c r="M84" t="s">
+        <v>37</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>134</v>
+      </c>
+      <c r="R84">
+        <v>944</v>
+      </c>
+      <c r="S84">
+        <v>944</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>26</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>1370</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>1293.28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>229</v>
+      </c>
+      <c r="B85" t="s">
+        <v>131</v>
+      </c>
+      <c r="C85" t="s">
+        <v>132</v>
+      </c>
+      <c r="D85" t="s">
+        <v>230</v>
+      </c>
+      <c r="E85" t="s">
+        <v>97</v>
+      </c>
+      <c r="F85" t="s">
+        <v>33</v>
+      </c>
+      <c r="G85" t="s">
+        <v>88</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>1500</v>
+      </c>
+      <c r="K85">
+        <v>3000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>78</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>134</v>
+      </c>
+      <c r="R85">
+        <v>1923</v>
+      </c>
+      <c r="S85">
+        <v>1923</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>1</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>1420</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>2730.66</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>231</v>
+      </c>
+      <c r="B86" t="s">
+        <v>140</v>
+      </c>
+      <c r="C86" t="s">
+        <v>132</v>
+      </c>
+      <c r="D86" t="s">
+        <v>232</v>
+      </c>
+      <c r="E86" t="s">
+        <v>97</v>
+      </c>
+      <c r="F86" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" t="s">
+        <v>63</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>1.2</v>
+      </c>
+      <c r="J86">
+        <v>1500</v>
+      </c>
+      <c r="K86">
+        <v>3000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>36</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>134</v>
+      </c>
+      <c r="R86">
         <v>42</v>
       </c>
-      <c r="W38" t="s">
-        <v>43</v>
-      </c>
-      <c r="X38">
-        <v>3790</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA38">
-        <v>4263.75</v>
+      <c r="S86">
+        <v>42</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>1</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>2170</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>91.14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>233</v>
+      </c>
+      <c r="B87" t="s">
+        <v>137</v>
+      </c>
+      <c r="C87" t="s">
+        <v>132</v>
+      </c>
+      <c r="D87" t="s">
+        <v>234</v>
+      </c>
+      <c r="E87" t="s">
+        <v>97</v>
+      </c>
+      <c r="F87" t="s">
+        <v>33</v>
+      </c>
+      <c r="G87" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87">
+        <v>8</v>
+      </c>
+      <c r="J87">
+        <v>1500</v>
+      </c>
+      <c r="K87">
+        <v>3000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>36</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>134</v>
+      </c>
+      <c r="R87">
+        <v>1417</v>
+      </c>
+      <c r="S87">
+        <v>1417</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>5</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>3590</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>5087.03</v>
+      </c>
+      <c r="AB87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>235</v>
+      </c>
+      <c r="B88" t="s">
+        <v>131</v>
+      </c>
+      <c r="C88" t="s">
+        <v>132</v>
+      </c>
+      <c r="D88" t="s">
+        <v>236</v>
+      </c>
+      <c r="E88" t="s">
+        <v>97</v>
+      </c>
+      <c r="F88" t="s">
+        <v>50</v>
+      </c>
+      <c r="G88" t="s">
+        <v>88</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88">
+        <v>0.8</v>
+      </c>
+      <c r="J88">
+        <v>1500</v>
+      </c>
+      <c r="L88" t="s">
+        <v>78</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>134</v>
+      </c>
+      <c r="R88">
+        <v>1865</v>
+      </c>
+      <c r="S88">
+        <v>1865</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>1</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>1520</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>2834.8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>237</v>
+      </c>
+      <c r="B89" t="s">
+        <v>140</v>
+      </c>
+      <c r="C89" t="s">
+        <v>132</v>
+      </c>
+      <c r="D89" t="s">
+        <v>238</v>
+      </c>
+      <c r="E89" t="s">
+        <v>97</v>
+      </c>
+      <c r="F89" t="s">
+        <v>33</v>
+      </c>
+      <c r="G89" t="s">
+        <v>63</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89">
+        <v>1.25</v>
+      </c>
+      <c r="J89">
+        <v>1250</v>
+      </c>
+      <c r="K89">
+        <v>2500</v>
+      </c>
+      <c r="L89" t="s">
+        <v>36</v>
+      </c>
+      <c r="M89" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>134</v>
+      </c>
+      <c r="R89">
+        <v>31</v>
+      </c>
+      <c r="S89">
+        <v>31</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>1</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>2170</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>67.27</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>239</v>
+      </c>
+      <c r="B90" t="s">
+        <v>131</v>
+      </c>
+      <c r="C90" t="s">
+        <v>132</v>
+      </c>
+      <c r="D90" t="s">
+        <v>240</v>
+      </c>
+      <c r="E90" t="s">
+        <v>97</v>
+      </c>
+      <c r="F90" t="s">
+        <v>33</v>
+      </c>
+      <c r="G90" t="s">
+        <v>88</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>1.5</v>
+      </c>
+      <c r="J90">
+        <v>1500</v>
+      </c>
+      <c r="K90">
+        <v>3000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>78</v>
+      </c>
+      <c r="M90" t="s">
+        <v>37</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>134</v>
+      </c>
+      <c r="R90">
+        <v>1007</v>
+      </c>
+      <c r="S90">
+        <v>1007</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>20</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>1420</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>1429.94</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>241</v>
+      </c>
+      <c r="B91" t="s">
+        <v>131</v>
+      </c>
+      <c r="C91" t="s">
+        <v>132</v>
+      </c>
+      <c r="D91" t="s">
+        <v>240</v>
+      </c>
+      <c r="E91" t="s">
+        <v>97</v>
+      </c>
+      <c r="F91" t="s">
+        <v>33</v>
+      </c>
+      <c r="G91" t="s">
+        <v>88</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91">
+        <v>1.5</v>
+      </c>
+      <c r="J91">
+        <v>1500</v>
+      </c>
+      <c r="K91">
+        <v>3000</v>
+      </c>
+      <c r="L91" t="s">
+        <v>78</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>134</v>
+      </c>
+      <c r="R91">
+        <v>960</v>
+      </c>
+      <c r="S91">
+        <v>960</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>19</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>1370</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>1315.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>242</v>
+      </c>
+      <c r="B92" t="s">
+        <v>137</v>
+      </c>
+      <c r="C92" t="s">
+        <v>132</v>
+      </c>
+      <c r="D92" t="s">
+        <v>243</v>
+      </c>
+      <c r="E92" t="s">
+        <v>97</v>
+      </c>
+      <c r="F92" t="s">
+        <v>33</v>
+      </c>
+      <c r="G92" t="s">
+        <v>63</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92">
+        <v>6</v>
+      </c>
+      <c r="J92">
+        <v>2000</v>
+      </c>
+      <c r="K92">
+        <v>6000</v>
+      </c>
+      <c r="L92" t="s">
+        <v>51</v>
+      </c>
+      <c r="M92" t="s">
+        <v>37</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>38</v>
+      </c>
+      <c r="P92" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>134</v>
+      </c>
+      <c r="R92">
+        <v>567</v>
+      </c>
+      <c r="S92">
+        <v>567</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>1</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>2040</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>1156.68</v>
+      </c>
+      <c r="AB92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>244</v>
+      </c>
+      <c r="B93" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" t="s">
+        <v>132</v>
+      </c>
+      <c r="D93" t="s">
+        <v>230</v>
+      </c>
+      <c r="E93" t="s">
+        <v>97</v>
+      </c>
+      <c r="F93" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93" t="s">
+        <v>88</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1500</v>
+      </c>
+      <c r="K93">
+        <v>3000</v>
+      </c>
+      <c r="L93" t="s">
+        <v>78</v>
+      </c>
+      <c r="M93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" t="s">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>134</v>
+      </c>
+      <c r="R93">
+        <v>1200</v>
+      </c>
+      <c r="S93">
+        <v>1200</v>
+      </c>
+      <c r="T93" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93">
+        <v>35</v>
+      </c>
+      <c r="V93" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93">
+        <v>1420</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA93">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>245</v>
+      </c>
+      <c r="B94" t="s">
+        <v>131</v>
+      </c>
+      <c r="C94" t="s">
+        <v>132</v>
+      </c>
+      <c r="D94" t="s">
+        <v>246</v>
+      </c>
+      <c r="E94" t="s">
+        <v>97</v>
+      </c>
+      <c r="F94" t="s">
+        <v>33</v>
+      </c>
+      <c r="G94" t="s">
+        <v>88</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94">
+        <v>0.5</v>
+      </c>
+      <c r="J94">
+        <v>1000</v>
+      </c>
+      <c r="K94">
+        <v>2000</v>
+      </c>
+      <c r="L94" t="s">
+        <v>78</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
+      </c>
+      <c r="N94" t="s">
+        <v>37</v>
+      </c>
+      <c r="O94" t="s">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>134</v>
+      </c>
+      <c r="R94">
+        <v>157</v>
+      </c>
+      <c r="S94">
+        <v>157</v>
+      </c>
+      <c r="T94" t="s">
+        <v>41</v>
+      </c>
+      <c r="U94">
+        <v>1</v>
+      </c>
+      <c r="V94" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94">
+        <v>1620</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA94">
+        <v>254.34</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>247</v>
+      </c>
+      <c r="B95" t="s">
+        <v>131</v>
+      </c>
+      <c r="C95" t="s">
+        <v>132</v>
+      </c>
+      <c r="D95" t="s">
+        <v>248</v>
+      </c>
+      <c r="E95" t="s">
+        <v>97</v>
+      </c>
+      <c r="F95" t="s">
+        <v>33</v>
+      </c>
+      <c r="G95" t="s">
+        <v>34</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95">
+        <v>1000</v>
+      </c>
+      <c r="K95">
+        <v>2000</v>
+      </c>
+      <c r="L95" t="s">
+        <v>36</v>
+      </c>
+      <c r="M95" t="s">
+        <v>37</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>134</v>
+      </c>
+      <c r="R95">
+        <v>824</v>
+      </c>
+      <c r="S95">
+        <v>824</v>
+      </c>
+      <c r="T95" t="s">
+        <v>41</v>
+      </c>
+      <c r="U95">
+        <v>26</v>
+      </c>
+      <c r="V95" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95">
+        <v>3540</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA95">
+        <v>2916.96</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>249</v>
+      </c>
+      <c r="B96" t="s">
+        <v>140</v>
+      </c>
+      <c r="C96" t="s">
+        <v>132</v>
+      </c>
+      <c r="D96" t="s">
+        <v>250</v>
+      </c>
+      <c r="E96" t="s">
+        <v>97</v>
+      </c>
+      <c r="F96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G96" t="s">
+        <v>63</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96">
+        <v>0.8</v>
+      </c>
+      <c r="J96">
+        <v>1250</v>
+      </c>
+      <c r="K96">
+        <v>2500</v>
+      </c>
+      <c r="L96" t="s">
+        <v>36</v>
+      </c>
+      <c r="M96" t="s">
+        <v>37</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
+      </c>
+      <c r="P96" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>134</v>
+      </c>
+      <c r="R96">
+        <v>59</v>
+      </c>
+      <c r="S96">
+        <v>59</v>
+      </c>
+      <c r="T96" t="s">
+        <v>41</v>
+      </c>
+      <c r="U96">
+        <v>3</v>
+      </c>
+      <c r="V96" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X96">
+        <v>2270</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA96">
+        <v>133.93</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>251</v>
+      </c>
+      <c r="B97" t="s">
+        <v>140</v>
+      </c>
+      <c r="C97" t="s">
+        <v>132</v>
+      </c>
+      <c r="D97" t="s">
+        <v>250</v>
+      </c>
+      <c r="E97" t="s">
+        <v>97</v>
+      </c>
+      <c r="F97" t="s">
+        <v>33</v>
+      </c>
+      <c r="G97" t="s">
+        <v>63</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97">
+        <v>0.8</v>
+      </c>
+      <c r="J97">
+        <v>1250</v>
+      </c>
+      <c r="K97">
+        <v>2500</v>
+      </c>
+      <c r="L97" t="s">
+        <v>36</v>
+      </c>
+      <c r="M97" t="s">
+        <v>37</v>
+      </c>
+      <c r="N97" t="s">
+        <v>37</v>
+      </c>
+      <c r="O97" t="s">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>134</v>
+      </c>
+      <c r="R97">
+        <v>79</v>
+      </c>
+      <c r="S97">
+        <v>79</v>
+      </c>
+      <c r="T97" t="s">
+        <v>41</v>
+      </c>
+      <c r="U97">
+        <v>4</v>
+      </c>
+      <c r="V97" t="s">
+        <v>43</v>
+      </c>
+      <c r="W97" t="s">
+        <v>43</v>
+      </c>
+      <c r="X97">
+        <v>2270</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA97">
+        <v>179.33</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>252</v>
+      </c>
+      <c r="B98" t="s">
+        <v>140</v>
+      </c>
+      <c r="C98" t="s">
+        <v>132</v>
+      </c>
+      <c r="D98" t="s">
+        <v>253</v>
+      </c>
+      <c r="E98" t="s">
+        <v>97</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
+      </c>
+      <c r="G98" t="s">
+        <v>142</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98">
+        <v>12</v>
+      </c>
+      <c r="J98">
+        <v>1500</v>
+      </c>
+      <c r="K98">
+        <v>3000</v>
+      </c>
+      <c r="L98" t="s">
+        <v>51</v>
+      </c>
+      <c r="M98" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" t="s">
+        <v>38</v>
+      </c>
+      <c r="P98" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>134</v>
+      </c>
+      <c r="R98">
+        <v>1275</v>
+      </c>
+      <c r="S98">
+        <v>1275</v>
+      </c>
+      <c r="T98" t="s">
+        <v>41</v>
+      </c>
+      <c r="U98">
+        <v>3</v>
+      </c>
+      <c r="V98" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98">
+        <v>3540</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA98">
+        <v>4513.5</v>
+      </c>
+      <c r="AB98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>254</v>
+      </c>
+      <c r="B99" t="s">
+        <v>140</v>
+      </c>
+      <c r="C99" t="s">
+        <v>132</v>
+      </c>
+      <c r="D99" t="s">
+        <v>253</v>
+      </c>
+      <c r="E99" t="s">
+        <v>97</v>
+      </c>
+      <c r="F99" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99" t="s">
+        <v>142</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99">
+        <v>12</v>
+      </c>
+      <c r="J99">
+        <v>1500</v>
+      </c>
+      <c r="K99">
+        <v>3000</v>
+      </c>
+      <c r="L99" t="s">
+        <v>51</v>
+      </c>
+      <c r="M99" t="s">
+        <v>37</v>
+      </c>
+      <c r="N99" t="s">
+        <v>37</v>
+      </c>
+      <c r="O99" t="s">
+        <v>38</v>
+      </c>
+      <c r="P99" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>134</v>
+      </c>
+      <c r="R99">
+        <v>1275</v>
+      </c>
+      <c r="S99">
+        <v>1275</v>
+      </c>
+      <c r="T99" t="s">
+        <v>41</v>
+      </c>
+      <c r="U99">
+        <v>3</v>
+      </c>
+      <c r="V99" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99">
+        <v>3540</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA99">
+        <v>4513.5</v>
+      </c>
+      <c r="AB99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>255</v>
+      </c>
+      <c r="B100" t="s">
+        <v>140</v>
+      </c>
+      <c r="C100" t="s">
+        <v>132</v>
+      </c>
+      <c r="D100" t="s">
+        <v>253</v>
+      </c>
+      <c r="E100" t="s">
+        <v>97</v>
+      </c>
+      <c r="F100" t="s">
+        <v>33</v>
+      </c>
+      <c r="G100" t="s">
+        <v>142</v>
+      </c>
+      <c r="H100" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100">
+        <v>12</v>
+      </c>
+      <c r="J100">
+        <v>1500</v>
+      </c>
+      <c r="K100">
+        <v>3000</v>
+      </c>
+      <c r="L100" t="s">
+        <v>51</v>
+      </c>
+      <c r="M100" t="s">
+        <v>37</v>
+      </c>
+      <c r="N100" t="s">
+        <v>37</v>
+      </c>
+      <c r="O100" t="s">
+        <v>38</v>
+      </c>
+      <c r="P100" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>134</v>
+      </c>
+      <c r="R100">
+        <v>850</v>
+      </c>
+      <c r="S100">
+        <v>850</v>
+      </c>
+      <c r="T100" t="s">
+        <v>41</v>
+      </c>
+      <c r="U100">
+        <v>2</v>
+      </c>
+      <c r="V100" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100">
+        <v>3490</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA100">
+        <v>2966.5</v>
+      </c>
+      <c r="AB100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>256</v>
+      </c>
+      <c r="B101" t="s">
+        <v>131</v>
+      </c>
+      <c r="C101" t="s">
+        <v>132</v>
+      </c>
+      <c r="D101" t="s">
+        <v>208</v>
+      </c>
+      <c r="E101" t="s">
+        <v>97</v>
+      </c>
+      <c r="F101" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101" t="s">
+        <v>63</v>
+      </c>
+      <c r="H101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101">
+        <v>3</v>
+      </c>
+      <c r="J101">
+        <v>1000</v>
+      </c>
+      <c r="K101">
+        <v>2000</v>
+      </c>
+      <c r="L101" t="s">
+        <v>36</v>
+      </c>
+      <c r="M101" t="s">
+        <v>37</v>
+      </c>
+      <c r="N101" t="s">
+        <v>37</v>
+      </c>
+      <c r="O101" t="s">
+        <v>38</v>
+      </c>
+      <c r="P101" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>134</v>
+      </c>
+      <c r="R101">
+        <v>379</v>
+      </c>
+      <c r="S101">
+        <v>379</v>
+      </c>
+      <c r="T101" t="s">
+        <v>41</v>
+      </c>
+      <c r="U101">
+        <v>8</v>
+      </c>
+      <c r="V101" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101">
+        <v>2220</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA101">
+        <v>841.38</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>257</v>
+      </c>
+      <c r="B102" t="s">
+        <v>140</v>
+      </c>
+      <c r="C102" t="s">
+        <v>132</v>
+      </c>
+      <c r="D102" t="s">
+        <v>258</v>
+      </c>
+      <c r="E102" t="s">
+        <v>97</v>
+      </c>
+      <c r="F102" t="s">
+        <v>33</v>
+      </c>
+      <c r="G102" t="s">
+        <v>63</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102">
+        <v>1.5</v>
+      </c>
+      <c r="J102">
+        <v>1000</v>
+      </c>
+      <c r="K102">
+        <v>2000</v>
+      </c>
+      <c r="L102" t="s">
+        <v>36</v>
+      </c>
+      <c r="M102" t="s">
+        <v>37</v>
+      </c>
+      <c r="N102" t="s">
+        <v>37</v>
+      </c>
+      <c r="O102" t="s">
+        <v>38</v>
+      </c>
+      <c r="P102" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>134</v>
+      </c>
+      <c r="R102">
+        <v>94</v>
+      </c>
+      <c r="S102">
+        <v>94</v>
+      </c>
+      <c r="T102" t="s">
+        <v>41</v>
+      </c>
+      <c r="U102">
+        <v>4</v>
+      </c>
+      <c r="V102" t="s">
+        <v>43</v>
+      </c>
+      <c r="W102" t="s">
+        <v>43</v>
+      </c>
+      <c r="X102">
+        <v>2170</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA102">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>259</v>
+      </c>
+      <c r="B103" t="s">
+        <v>140</v>
+      </c>
+      <c r="C103" t="s">
+        <v>132</v>
+      </c>
+      <c r="D103" t="s">
+        <v>234</v>
+      </c>
+      <c r="E103" t="s">
+        <v>97</v>
+      </c>
+      <c r="F103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" t="s">
+        <v>34</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103">
+        <v>8</v>
+      </c>
+      <c r="J103">
+        <v>1500</v>
+      </c>
+      <c r="K103">
+        <v>3000</v>
+      </c>
+      <c r="L103" t="s">
+        <v>36</v>
+      </c>
+      <c r="M103" t="s">
+        <v>37</v>
+      </c>
+      <c r="N103" t="s">
+        <v>37</v>
+      </c>
+      <c r="O103" t="s">
+        <v>38</v>
+      </c>
+      <c r="P103" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>134</v>
+      </c>
+      <c r="R103">
+        <v>1417</v>
+      </c>
+      <c r="S103">
+        <v>1417</v>
+      </c>
+      <c r="T103" t="s">
+        <v>41</v>
+      </c>
+      <c r="U103">
+        <v>5.11</v>
+      </c>
+      <c r="V103" t="s">
+        <v>43</v>
+      </c>
+      <c r="W103" t="s">
+        <v>43</v>
+      </c>
+      <c r="X103">
+        <v>3590</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA103">
+        <v>5087.03</v>
+      </c>
+      <c r="AB103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>260</v>
+      </c>
+      <c r="B104" t="s">
+        <v>140</v>
+      </c>
+      <c r="C104" t="s">
+        <v>132</v>
+      </c>
+      <c r="D104" t="s">
+        <v>234</v>
+      </c>
+      <c r="E104" t="s">
+        <v>97</v>
+      </c>
+      <c r="F104" t="s">
+        <v>33</v>
+      </c>
+      <c r="G104" t="s">
+        <v>34</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104">
+        <v>8</v>
+      </c>
+      <c r="J104">
+        <v>1500</v>
+      </c>
+      <c r="K104">
+        <v>3000</v>
+      </c>
+      <c r="L104" t="s">
+        <v>36</v>
+      </c>
+      <c r="M104" t="s">
+        <v>37</v>
+      </c>
+      <c r="N104" t="s">
+        <v>37</v>
+      </c>
+      <c r="O104" t="s">
+        <v>38</v>
+      </c>
+      <c r="P104" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>134</v>
+      </c>
+      <c r="R104">
+        <v>2267</v>
+      </c>
+      <c r="S104">
+        <v>2267</v>
+      </c>
+      <c r="T104" t="s">
+        <v>41</v>
+      </c>
+      <c r="U104">
+        <v>8.175</v>
+      </c>
+      <c r="V104" t="s">
+        <v>43</v>
+      </c>
+      <c r="W104" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104">
+        <v>3590</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA104">
+        <v>8138.53</v>
+      </c>
+      <c r="AB104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>261</v>
+      </c>
+      <c r="B105" t="s">
+        <v>140</v>
+      </c>
+      <c r="C105" t="s">
+        <v>132</v>
+      </c>
+      <c r="D105" t="s">
+        <v>262</v>
+      </c>
+      <c r="E105" t="s">
+        <v>97</v>
+      </c>
+      <c r="F105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G105" t="s">
+        <v>34</v>
+      </c>
+      <c r="H105" t="s">
+        <v>35</v>
+      </c>
+      <c r="I105">
+        <v>6</v>
+      </c>
+      <c r="J105">
+        <v>1500</v>
+      </c>
+      <c r="K105">
+        <v>3000</v>
+      </c>
+      <c r="L105" t="s">
+        <v>36</v>
+      </c>
+      <c r="M105" t="s">
+        <v>37</v>
+      </c>
+      <c r="N105" t="s">
+        <v>37</v>
+      </c>
+      <c r="O105" t="s">
+        <v>38</v>
+      </c>
+      <c r="P105" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>134</v>
+      </c>
+      <c r="R105">
+        <v>1275</v>
+      </c>
+      <c r="S105">
+        <v>1275</v>
+      </c>
+      <c r="T105" t="s">
+        <v>41</v>
+      </c>
+      <c r="U105">
+        <v>6</v>
+      </c>
+      <c r="V105" t="s">
+        <v>43</v>
+      </c>
+      <c r="W105" t="s">
+        <v>43</v>
+      </c>
+      <c r="X105">
+        <v>3590</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA105">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>263</v>
+      </c>
+      <c r="B106" t="s">
+        <v>137</v>
+      </c>
+      <c r="C106" t="s">
+        <v>132</v>
+      </c>
+      <c r="D106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E106" t="s">
+        <v>97</v>
+      </c>
+      <c r="F106" t="s">
+        <v>33</v>
+      </c>
+      <c r="G106" t="s">
+        <v>34</v>
+      </c>
+      <c r="H106" t="s">
+        <v>35</v>
+      </c>
+      <c r="I106">
+        <v>8</v>
+      </c>
+      <c r="J106">
+        <v>1500</v>
+      </c>
+      <c r="K106">
+        <v>3000</v>
+      </c>
+      <c r="L106" t="s">
+        <v>36</v>
+      </c>
+      <c r="M106" t="s">
+        <v>37</v>
+      </c>
+      <c r="N106" t="s">
+        <v>37</v>
+      </c>
+      <c r="O106" t="s">
+        <v>38</v>
+      </c>
+      <c r="P106" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>134</v>
+      </c>
+      <c r="R106">
+        <v>576</v>
+      </c>
+      <c r="S106">
+        <v>576</v>
+      </c>
+      <c r="T106" t="s">
+        <v>41</v>
+      </c>
+      <c r="U106">
+        <v>2.033</v>
+      </c>
+      <c r="V106" t="s">
+        <v>43</v>
+      </c>
+      <c r="W106" t="s">
+        <v>43</v>
+      </c>
+      <c r="X106">
+        <v>3540</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA106">
+        <v>2039.04</v>
+      </c>
+      <c r="AB106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>264</v>
+      </c>
+      <c r="B107" t="s">
+        <v>137</v>
+      </c>
+      <c r="C107" t="s">
+        <v>132</v>
+      </c>
+      <c r="D107" t="s">
+        <v>234</v>
+      </c>
+      <c r="E107" t="s">
+        <v>97</v>
+      </c>
+      <c r="F107" t="s">
+        <v>33</v>
+      </c>
+      <c r="G107" t="s">
+        <v>34</v>
+      </c>
+      <c r="H107" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107">
+        <v>8</v>
+      </c>
+      <c r="J107">
+        <v>1500</v>
+      </c>
+      <c r="K107">
+        <v>3000</v>
+      </c>
+      <c r="L107" t="s">
+        <v>36</v>
+      </c>
+      <c r="M107" t="s">
+        <v>37</v>
+      </c>
+      <c r="N107" t="s">
+        <v>37</v>
+      </c>
+      <c r="O107" t="s">
+        <v>38</v>
+      </c>
+      <c r="P107" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>134</v>
+      </c>
+      <c r="R107">
+        <v>1134</v>
+      </c>
+      <c r="S107">
+        <v>1134</v>
+      </c>
+      <c r="T107" t="s">
+        <v>41</v>
+      </c>
+      <c r="U107">
+        <v>4.003</v>
+      </c>
+      <c r="V107" t="s">
+        <v>43</v>
+      </c>
+      <c r="W107" t="s">
+        <v>43</v>
+      </c>
+      <c r="X107">
+        <v>3590</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA107">
+        <v>4071.06</v>
+      </c>
+      <c r="AB107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>265</v>
+      </c>
+      <c r="B108" t="s">
+        <v>137</v>
+      </c>
+      <c r="C108" t="s">
+        <v>132</v>
+      </c>
+      <c r="D108" t="s">
+        <v>234</v>
+      </c>
+      <c r="E108" t="s">
+        <v>97</v>
+      </c>
+      <c r="F108" t="s">
+        <v>33</v>
+      </c>
+      <c r="G108" t="s">
+        <v>34</v>
+      </c>
+      <c r="H108" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108">
+        <v>8</v>
+      </c>
+      <c r="J108">
+        <v>1500</v>
+      </c>
+      <c r="K108">
+        <v>3000</v>
+      </c>
+      <c r="L108" t="s">
+        <v>36</v>
+      </c>
+      <c r="M108" t="s">
+        <v>37</v>
+      </c>
+      <c r="N108" t="s">
+        <v>37</v>
+      </c>
+      <c r="O108" t="s">
+        <v>38</v>
+      </c>
+      <c r="P108" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>134</v>
+      </c>
+      <c r="R108">
+        <v>1417</v>
+      </c>
+      <c r="S108">
+        <v>1417</v>
+      </c>
+      <c r="T108" t="s">
+        <v>41</v>
+      </c>
+      <c r="U108">
+        <v>5.001</v>
+      </c>
+      <c r="V108" t="s">
+        <v>43</v>
+      </c>
+      <c r="W108" t="s">
+        <v>43</v>
+      </c>
+      <c r="X108">
+        <v>3590</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA108">
+        <v>5087.03</v>
+      </c>
+      <c r="AB108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>266</v>
+      </c>
+      <c r="B109" t="s">
+        <v>137</v>
+      </c>
+      <c r="C109" t="s">
+        <v>132</v>
+      </c>
+      <c r="D109" t="s">
+        <v>234</v>
+      </c>
+      <c r="E109" t="s">
+        <v>97</v>
+      </c>
+      <c r="F109" t="s">
+        <v>33</v>
+      </c>
+      <c r="G109" t="s">
+        <v>34</v>
+      </c>
+      <c r="H109" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109">
+        <v>8</v>
+      </c>
+      <c r="J109">
+        <v>1500</v>
+      </c>
+      <c r="K109">
+        <v>3000</v>
+      </c>
+      <c r="L109" t="s">
+        <v>36</v>
+      </c>
+      <c r="M109" t="s">
+        <v>37</v>
+      </c>
+      <c r="N109" t="s">
+        <v>37</v>
+      </c>
+      <c r="O109" t="s">
+        <v>38</v>
+      </c>
+      <c r="P109" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>134</v>
+      </c>
+      <c r="R109">
+        <v>1417</v>
+      </c>
+      <c r="S109">
+        <v>1417</v>
+      </c>
+      <c r="T109" t="s">
+        <v>41</v>
+      </c>
+      <c r="U109">
+        <v>5.001</v>
+      </c>
+      <c r="V109" t="s">
+        <v>43</v>
+      </c>
+      <c r="W109" t="s">
+        <v>43</v>
+      </c>
+      <c r="X109">
+        <v>3590</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA109">
+        <v>5087.03</v>
+      </c>
+      <c r="AB109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>267</v>
+      </c>
+      <c r="B110" t="s">
+        <v>137</v>
+      </c>
+      <c r="C110" t="s">
+        <v>132</v>
+      </c>
+      <c r="D110" t="s">
+        <v>234</v>
+      </c>
+      <c r="E110" t="s">
+        <v>97</v>
+      </c>
+      <c r="F110" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110" t="s">
+        <v>34</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110">
+        <v>8</v>
+      </c>
+      <c r="J110">
+        <v>1500</v>
+      </c>
+      <c r="K110">
+        <v>3000</v>
+      </c>
+      <c r="L110" t="s">
+        <v>36</v>
+      </c>
+      <c r="M110" t="s">
+        <v>37</v>
+      </c>
+      <c r="N110" t="s">
+        <v>37</v>
+      </c>
+      <c r="O110" t="s">
+        <v>38</v>
+      </c>
+      <c r="P110" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>134</v>
+      </c>
+      <c r="R110">
+        <v>1417</v>
+      </c>
+      <c r="S110">
+        <v>1417</v>
+      </c>
+      <c r="T110" t="s">
+        <v>41</v>
+      </c>
+      <c r="U110">
+        <v>5.001</v>
+      </c>
+      <c r="V110" t="s">
+        <v>43</v>
+      </c>
+      <c r="W110" t="s">
+        <v>43</v>
+      </c>
+      <c r="X110">
+        <v>3590</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA110">
+        <v>5087.03</v>
+      </c>
+      <c r="AB110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>268</v>
+      </c>
+      <c r="B111" t="s">
+        <v>137</v>
+      </c>
+      <c r="C111" t="s">
+        <v>132</v>
+      </c>
+      <c r="D111" t="s">
+        <v>234</v>
+      </c>
+      <c r="E111" t="s">
+        <v>97</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G111" t="s">
+        <v>34</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111">
+        <v>8</v>
+      </c>
+      <c r="J111">
+        <v>1500</v>
+      </c>
+      <c r="K111">
+        <v>3000</v>
+      </c>
+      <c r="L111" t="s">
+        <v>36</v>
+      </c>
+      <c r="M111" t="s">
+        <v>37</v>
+      </c>
+      <c r="N111" t="s">
+        <v>37</v>
+      </c>
+      <c r="O111" t="s">
+        <v>38</v>
+      </c>
+      <c r="P111" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>134</v>
+      </c>
+      <c r="R111">
+        <v>1130</v>
+      </c>
+      <c r="S111">
+        <v>1130</v>
+      </c>
+      <c r="T111" t="s">
+        <v>41</v>
+      </c>
+      <c r="U111">
+        <v>3.988</v>
+      </c>
+      <c r="V111" t="s">
+        <v>43</v>
+      </c>
+      <c r="W111" t="s">
+        <v>43</v>
+      </c>
+      <c r="X111">
+        <v>3590</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA111">
+        <v>4056.7</v>
+      </c>
+      <c r="AB111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>269</v>
+      </c>
+      <c r="B112" t="s">
+        <v>137</v>
+      </c>
+      <c r="C112" t="s">
+        <v>132</v>
+      </c>
+      <c r="D112" t="s">
+        <v>234</v>
+      </c>
+      <c r="E112" t="s">
+        <v>97</v>
+      </c>
+      <c r="F112" t="s">
+        <v>33</v>
+      </c>
+      <c r="G112" t="s">
+        <v>34</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112">
+        <v>8</v>
+      </c>
+      <c r="J112">
+        <v>1500</v>
+      </c>
+      <c r="K112">
+        <v>3000</v>
+      </c>
+      <c r="L112" t="s">
+        <v>36</v>
+      </c>
+      <c r="M112" t="s">
+        <v>37</v>
+      </c>
+      <c r="N112" t="s">
+        <v>37</v>
+      </c>
+      <c r="O112" t="s">
+        <v>38</v>
+      </c>
+      <c r="P112" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>134</v>
+      </c>
+      <c r="R112">
+        <v>1417</v>
+      </c>
+      <c r="S112">
+        <v>1417</v>
+      </c>
+      <c r="T112" t="s">
+        <v>41</v>
+      </c>
+      <c r="U112">
+        <v>5.001</v>
+      </c>
+      <c r="V112" t="s">
+        <v>43</v>
+      </c>
+      <c r="W112" t="s">
+        <v>43</v>
+      </c>
+      <c r="X112">
+        <v>3590</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA112">
+        <v>5087.03</v>
+      </c>
+      <c r="AB112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>270</v>
+      </c>
+      <c r="B113" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" t="s">
+        <v>132</v>
+      </c>
+      <c r="D113" t="s">
+        <v>234</v>
+      </c>
+      <c r="E113" t="s">
+        <v>97</v>
+      </c>
+      <c r="F113" t="s">
+        <v>33</v>
+      </c>
+      <c r="G113" t="s">
+        <v>34</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113">
+        <v>8</v>
+      </c>
+      <c r="J113">
+        <v>1500</v>
+      </c>
+      <c r="K113">
+        <v>3000</v>
+      </c>
+      <c r="L113" t="s">
+        <v>36</v>
+      </c>
+      <c r="M113" t="s">
+        <v>37</v>
+      </c>
+      <c r="N113" t="s">
+        <v>37</v>
+      </c>
+      <c r="O113" t="s">
+        <v>38</v>
+      </c>
+      <c r="P113" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>134</v>
+      </c>
+      <c r="R113">
+        <v>1417</v>
+      </c>
+      <c r="S113">
+        <v>1417</v>
+      </c>
+      <c r="T113" t="s">
+        <v>41</v>
+      </c>
+      <c r="U113">
+        <v>5.001</v>
+      </c>
+      <c r="V113" t="s">
+        <v>43</v>
+      </c>
+      <c r="W113" t="s">
+        <v>43</v>
+      </c>
+      <c r="X113">
+        <v>3590</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA113">
+        <v>5087.03</v>
+      </c>
+      <c r="AB113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>271</v>
+      </c>
+      <c r="B114" t="s">
+        <v>137</v>
+      </c>
+      <c r="C114" t="s">
+        <v>132</v>
+      </c>
+      <c r="D114" t="s">
+        <v>234</v>
+      </c>
+      <c r="E114" t="s">
+        <v>97</v>
+      </c>
+      <c r="F114" t="s">
+        <v>33</v>
+      </c>
+      <c r="G114" t="s">
+        <v>34</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114">
+        <v>8</v>
+      </c>
+      <c r="J114">
+        <v>1500</v>
+      </c>
+      <c r="K114">
+        <v>3000</v>
+      </c>
+      <c r="L114" t="s">
+        <v>36</v>
+      </c>
+      <c r="M114" t="s">
+        <v>37</v>
+      </c>
+      <c r="N114" t="s">
+        <v>37</v>
+      </c>
+      <c r="O114" t="s">
+        <v>38</v>
+      </c>
+      <c r="P114" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>134</v>
+      </c>
+      <c r="R114">
+        <v>1417</v>
+      </c>
+      <c r="S114">
+        <v>1417</v>
+      </c>
+      <c r="T114" t="s">
+        <v>41</v>
+      </c>
+      <c r="U114">
+        <v>5.001</v>
+      </c>
+      <c r="V114" t="s">
+        <v>43</v>
+      </c>
+      <c r="W114" t="s">
+        <v>43</v>
+      </c>
+      <c r="X114">
+        <v>3590</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA114">
+        <v>5087.03</v>
+      </c>
+      <c r="AB114" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="250">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -347,6 +347,420 @@
   </si>
   <si>
     <t>Coil 1.4307-304L 1D without paper 4.99 x 1537.0 mm Unslit not marked</t>
+  </si>
+  <si>
+    <t>7249970</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>K30/1.4016-430</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>7249978</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B with paper 3.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4571-316Ti</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4541-321</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489700</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489750</t>
+  </si>
+  <si>
+    <t>7257864</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257894</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>S139218</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 12.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258091</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258149</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491483</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258526</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258730</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258862</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258863</t>
+  </si>
+  <si>
+    <t>7259015</t>
+  </si>
+  <si>
+    <t>Coil 1.4520-430Ti 2B 1.2 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4520-430Ti</t>
+  </si>
+  <si>
+    <t>7259050</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R NOV 4241/4513 0.8 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>NOV 4241/4513</t>
+  </si>
+  <si>
+    <t>7259145</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259417</t>
+  </si>
+  <si>
+    <t>7259437</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259438</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B with paper 1.0 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7259439</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R with paper 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259447</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T493044</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259677</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B without paper 8.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7259689</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R with paper 0.8 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T493468</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.25 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259716</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R without paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259717</t>
+  </si>
+  <si>
+    <t>7259732</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 6.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7259803</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 0.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259914</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T493993</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T493994</t>
+  </si>
+  <si>
+    <t>7260311</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D without paper 12.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7260313</t>
+  </si>
+  <si>
+    <t>7260315</t>
+  </si>
+  <si>
+    <t>7260324</t>
+  </si>
+  <si>
+    <t>T494573</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7260481</t>
+  </si>
+  <si>
+    <t>7260483</t>
+  </si>
+  <si>
+    <t>T494673</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7260613</t>
+  </si>
+  <si>
+    <t>7260615</t>
+  </si>
+  <si>
+    <t>7260617</t>
+  </si>
+  <si>
+    <t>7260620</t>
+  </si>
+  <si>
+    <t>7260621</t>
+  </si>
+  <si>
+    <t>7260622</t>
+  </si>
+  <si>
+    <t>7260623</t>
+  </si>
+  <si>
+    <t>7260625</t>
+  </si>
+  <si>
+    <t>7260626</t>
+  </si>
+  <si>
+    <t>7260631</t>
+  </si>
+  <si>
+    <t>7260632</t>
+  </si>
+  <si>
+    <t>7260639</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B with paper 1.2 x 1500.0 x 3000 mm Slit</t>
   </si>
 </sst>
 </file>
@@ -723,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB98"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -2605,6 +3019,6279 @@
         <v>0</v>
       </c>
     </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <v>1250</v>
+      </c>
+      <c r="K24">
+        <v>2500</v>
+      </c>
+      <c r="L24" t="s">
+        <v>36</v>
+      </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>117</v>
+      </c>
+      <c r="R24">
+        <v>340</v>
+      </c>
+      <c r="S24">
+        <v>340</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24">
+        <v>7</v>
+      </c>
+      <c r="V24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>1370</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>465.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>3</v>
+      </c>
+      <c r="J25">
+        <v>2000</v>
+      </c>
+      <c r="K25">
+        <v>6000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>117</v>
+      </c>
+      <c r="R25">
+        <v>283</v>
+      </c>
+      <c r="S25">
+        <v>283</v>
+      </c>
+      <c r="T25" t="s">
+        <v>41</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
+        <v>43</v>
+      </c>
+      <c r="W25" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25">
+        <v>3560</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA25">
+        <v>1007.48</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" t="s">
+        <v>124</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>8</v>
+      </c>
+      <c r="J26">
+        <v>1250</v>
+      </c>
+      <c r="K26">
+        <v>2500</v>
+      </c>
+      <c r="L26" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>117</v>
+      </c>
+      <c r="R26">
+        <v>394</v>
+      </c>
+      <c r="S26">
+        <v>394</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>43</v>
+      </c>
+      <c r="X26">
+        <v>3490</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27">
+        <v>2000</v>
+      </c>
+      <c r="K27">
+        <v>6000</v>
+      </c>
+      <c r="L27" t="s">
+        <v>79</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>117</v>
+      </c>
+      <c r="R27">
+        <v>472</v>
+      </c>
+      <c r="S27">
+        <v>472</v>
+      </c>
+      <c r="T27" t="s">
+        <v>41</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X27">
+        <v>2190</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28">
+        <v>1500</v>
+      </c>
+      <c r="K28">
+        <v>3000</v>
+      </c>
+      <c r="L28" t="s">
+        <v>90</v>
+      </c>
+      <c r="M28" t="s">
+        <v>130</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R28">
+        <v>970</v>
+      </c>
+      <c r="S28">
+        <v>970</v>
+      </c>
+      <c r="T28" t="s">
+        <v>41</v>
+      </c>
+      <c r="U28">
+        <v>13</v>
+      </c>
+      <c r="V28" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" t="s">
+        <v>43</v>
+      </c>
+      <c r="X28">
+        <v>3490</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA28">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>131</v>
+      </c>
+      <c r="B29" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <v>1500</v>
+      </c>
+      <c r="K29">
+        <v>3000</v>
+      </c>
+      <c r="L29" t="s">
+        <v>79</v>
+      </c>
+      <c r="M29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>117</v>
+      </c>
+      <c r="R29">
+        <v>354</v>
+      </c>
+      <c r="S29">
+        <v>354</v>
+      </c>
+      <c r="T29" t="s">
+        <v>41</v>
+      </c>
+      <c r="U29">
+        <v>2</v>
+      </c>
+      <c r="V29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>43</v>
+      </c>
+      <c r="X29">
+        <v>1170</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA29">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>1.5</v>
+      </c>
+      <c r="J30">
+        <v>1250</v>
+      </c>
+      <c r="L30" t="s">
+        <v>90</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>117</v>
+      </c>
+      <c r="R30">
+        <v>1275</v>
+      </c>
+      <c r="S30">
+        <v>1275</v>
+      </c>
+      <c r="T30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" t="s">
+        <v>43</v>
+      </c>
+      <c r="X30">
+        <v>3590</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>1500</v>
+      </c>
+      <c r="K31">
+        <v>3000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>90</v>
+      </c>
+      <c r="M31" t="s">
+        <v>37</v>
+      </c>
+      <c r="N31" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>117</v>
+      </c>
+      <c r="R31">
+        <v>212</v>
+      </c>
+      <c r="S31">
+        <v>212</v>
+      </c>
+      <c r="T31" t="s">
+        <v>41</v>
+      </c>
+      <c r="U31">
+        <v>2</v>
+      </c>
+      <c r="V31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>43</v>
+      </c>
+      <c r="X31">
+        <v>1320</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
+        <v>1500</v>
+      </c>
+      <c r="K32">
+        <v>3000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>90</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>37</v>
+      </c>
+      <c r="O32" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>117</v>
+      </c>
+      <c r="R32">
+        <v>319</v>
+      </c>
+      <c r="S32">
+        <v>319</v>
+      </c>
+      <c r="T32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U32">
+        <v>3</v>
+      </c>
+      <c r="V32" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" t="s">
+        <v>43</v>
+      </c>
+      <c r="X32">
+        <v>1370</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>1500</v>
+      </c>
+      <c r="K33">
+        <v>3000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>90</v>
+      </c>
+      <c r="M33" t="s">
+        <v>130</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>117</v>
+      </c>
+      <c r="R33">
+        <v>1010</v>
+      </c>
+      <c r="S33">
+        <v>1010</v>
+      </c>
+      <c r="T33" t="s">
+        <v>41</v>
+      </c>
+      <c r="U33">
+        <v>14</v>
+      </c>
+      <c r="V33" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X33">
+        <v>3540</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>139</v>
+      </c>
+      <c r="B34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
+        <v>109</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>0.8</v>
+      </c>
+      <c r="J34">
+        <v>1000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>36</v>
+      </c>
+      <c r="M34" t="s">
+        <v>37</v>
+      </c>
+      <c r="N34" t="s">
+        <v>37</v>
+      </c>
+      <c r="O34" t="s">
+        <v>141</v>
+      </c>
+      <c r="P34" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>117</v>
+      </c>
+      <c r="R34">
+        <v>1585</v>
+      </c>
+      <c r="S34">
+        <v>1585</v>
+      </c>
+      <c r="T34" t="s">
+        <v>41</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" t="s">
+        <v>43</v>
+      </c>
+      <c r="X34">
+        <v>2370</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" t="s">
+        <v>116</v>
+      </c>
+      <c r="H35" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35">
+        <v>1.5</v>
+      </c>
+      <c r="J35">
+        <v>1500</v>
+      </c>
+      <c r="K35">
+        <v>3000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>90</v>
+      </c>
+      <c r="M35" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" t="s">
+        <v>37</v>
+      </c>
+      <c r="O35" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>117</v>
+      </c>
+      <c r="R35">
+        <v>212</v>
+      </c>
+      <c r="S35">
+        <v>212</v>
+      </c>
+      <c r="T35" t="s">
+        <v>41</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W35" t="s">
+        <v>43</v>
+      </c>
+      <c r="X35">
+        <v>1320</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA35">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <v>4</v>
+      </c>
+      <c r="J36">
+        <v>1000</v>
+      </c>
+      <c r="K36">
+        <v>2000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>90</v>
+      </c>
+      <c r="M36" t="s">
+        <v>37</v>
+      </c>
+      <c r="N36" t="s">
+        <v>37</v>
+      </c>
+      <c r="O36" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>117</v>
+      </c>
+      <c r="R36">
+        <v>315</v>
+      </c>
+      <c r="S36">
+        <v>315</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36">
+        <v>5</v>
+      </c>
+      <c r="V36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X36">
+        <v>2220</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA36">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" t="s">
+        <v>147</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37">
+        <v>1000</v>
+      </c>
+      <c r="K37">
+        <v>2000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>79</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>117</v>
+      </c>
+      <c r="R37">
+        <v>944</v>
+      </c>
+      <c r="S37">
+        <v>944</v>
+      </c>
+      <c r="T37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
+      </c>
+      <c r="X37">
+        <v>2020</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38" t="s">
+        <v>86</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>1500</v>
+      </c>
+      <c r="K38">
+        <v>3000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>90</v>
+      </c>
+      <c r="M38" t="s">
+        <v>130</v>
+      </c>
+      <c r="N38" t="s">
+        <v>37</v>
+      </c>
+      <c r="O38" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>117</v>
+      </c>
+      <c r="R38">
+        <v>1224</v>
+      </c>
+      <c r="S38">
+        <v>1224</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38">
+        <v>34</v>
+      </c>
+      <c r="V38" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38">
+        <v>3540</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" t="s">
+        <v>151</v>
+      </c>
+      <c r="E39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>1.5</v>
+      </c>
+      <c r="J39">
+        <v>1500</v>
+      </c>
+      <c r="K39">
+        <v>3000</v>
+      </c>
+      <c r="L39" t="s">
+        <v>36</v>
+      </c>
+      <c r="M39" t="s">
+        <v>130</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>117</v>
+      </c>
+      <c r="R39">
+        <v>916</v>
+      </c>
+      <c r="S39">
+        <v>916</v>
+      </c>
+      <c r="T39" t="s">
+        <v>41</v>
+      </c>
+      <c r="U39">
+        <v>18</v>
+      </c>
+      <c r="V39" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" t="s">
+        <v>43</v>
+      </c>
+      <c r="X39">
+        <v>1320</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA39">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" t="s">
+        <v>114</v>
+      </c>
+      <c r="D40" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
+        <v>109</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>0.8</v>
+      </c>
+      <c r="J40">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="s">
+        <v>36</v>
+      </c>
+      <c r="M40" t="s">
+        <v>37</v>
+      </c>
+      <c r="N40" t="s">
+        <v>37</v>
+      </c>
+      <c r="O40" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>117</v>
+      </c>
+      <c r="R40">
+        <v>1000</v>
+      </c>
+      <c r="S40">
+        <v>1000</v>
+      </c>
+      <c r="T40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" t="s">
+        <v>43</v>
+      </c>
+      <c r="X40">
+        <v>2370</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B41" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="s">
+        <v>85</v>
+      </c>
+      <c r="G41" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41">
+        <v>2.5</v>
+      </c>
+      <c r="J41">
+        <v>1500</v>
+      </c>
+      <c r="K41">
+        <v>3000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>90</v>
+      </c>
+      <c r="M41" t="s">
+        <v>37</v>
+      </c>
+      <c r="N41" t="s">
+        <v>37</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>117</v>
+      </c>
+      <c r="R41">
+        <v>266</v>
+      </c>
+      <c r="S41">
+        <v>266</v>
+      </c>
+      <c r="T41" t="s">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>3</v>
+      </c>
+      <c r="V41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>43</v>
+      </c>
+      <c r="X41">
+        <v>2220</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E42" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" t="s">
+        <v>86</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42">
+        <v>2.5</v>
+      </c>
+      <c r="J42">
+        <v>2000</v>
+      </c>
+      <c r="K42">
+        <v>4000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>90</v>
+      </c>
+      <c r="M42" t="s">
+        <v>37</v>
+      </c>
+      <c r="N42" t="s">
+        <v>37</v>
+      </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>117</v>
+      </c>
+      <c r="R42">
+        <v>315</v>
+      </c>
+      <c r="S42">
+        <v>315</v>
+      </c>
+      <c r="T42" t="s">
+        <v>41</v>
+      </c>
+      <c r="U42">
+        <v>2</v>
+      </c>
+      <c r="V42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>43</v>
+      </c>
+      <c r="X42">
+        <v>3560</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>158</v>
+      </c>
+      <c r="B43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" t="s">
+        <v>157</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" t="s">
+        <v>86</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>2.5</v>
+      </c>
+      <c r="J43">
+        <v>2000</v>
+      </c>
+      <c r="K43">
+        <v>4000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>90</v>
+      </c>
+      <c r="M43" t="s">
+        <v>37</v>
+      </c>
+      <c r="N43" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>117</v>
+      </c>
+      <c r="R43">
+        <v>315</v>
+      </c>
+      <c r="S43">
+        <v>315</v>
+      </c>
+      <c r="T43" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43">
+        <v>2</v>
+      </c>
+      <c r="V43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>43</v>
+      </c>
+      <c r="X43">
+        <v>3560</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B44" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>1000</v>
+      </c>
+      <c r="K44">
+        <v>2000</v>
+      </c>
+      <c r="L44" t="s">
+        <v>90</v>
+      </c>
+      <c r="M44" t="s">
+        <v>37</v>
+      </c>
+      <c r="N44" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>117</v>
+      </c>
+      <c r="R44">
+        <v>1448</v>
+      </c>
+      <c r="S44">
+        <v>1448</v>
+      </c>
+      <c r="T44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U44">
+        <v>1</v>
+      </c>
+      <c r="V44" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" t="s">
+        <v>43</v>
+      </c>
+      <c r="X44">
+        <v>2270</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA44">
+        <v>3286.96</v>
+      </c>
+      <c r="AB44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" t="s">
+        <v>85</v>
+      </c>
+      <c r="G45" t="s">
+        <v>116</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>4</v>
+      </c>
+      <c r="J45">
+        <v>1000</v>
+      </c>
+      <c r="K45">
+        <v>2000</v>
+      </c>
+      <c r="L45" t="s">
+        <v>90</v>
+      </c>
+      <c r="M45" t="s">
+        <v>37</v>
+      </c>
+      <c r="N45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>117</v>
+      </c>
+      <c r="R45">
+        <v>384</v>
+      </c>
+      <c r="S45">
+        <v>384</v>
+      </c>
+      <c r="T45" t="s">
+        <v>41</v>
+      </c>
+      <c r="U45">
+        <v>6</v>
+      </c>
+      <c r="V45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="X45">
+        <v>1370</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA45">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" t="s">
+        <v>85</v>
+      </c>
+      <c r="G46" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+      <c r="J46">
+        <v>1000</v>
+      </c>
+      <c r="K46">
+        <v>2000</v>
+      </c>
+      <c r="L46" t="s">
+        <v>90</v>
+      </c>
+      <c r="M46" t="s">
+        <v>37</v>
+      </c>
+      <c r="N46" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>117</v>
+      </c>
+      <c r="R46">
+        <v>283</v>
+      </c>
+      <c r="S46">
+        <v>283</v>
+      </c>
+      <c r="T46" t="s">
+        <v>41</v>
+      </c>
+      <c r="U46">
+        <v>9</v>
+      </c>
+      <c r="V46" t="s">
+        <v>43</v>
+      </c>
+      <c r="W46" t="s">
+        <v>43</v>
+      </c>
+      <c r="X46">
+        <v>2220</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" t="s">
+        <v>85</v>
+      </c>
+      <c r="G47" t="s">
+        <v>116</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>1500</v>
+      </c>
+      <c r="K47">
+        <v>3000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>90</v>
+      </c>
+      <c r="M47" t="s">
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>117</v>
+      </c>
+      <c r="R47">
+        <v>637</v>
+      </c>
+      <c r="S47">
+        <v>637</v>
+      </c>
+      <c r="T47" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47">
+        <v>6</v>
+      </c>
+      <c r="V47" t="s">
+        <v>43</v>
+      </c>
+      <c r="W47" t="s">
+        <v>43</v>
+      </c>
+      <c r="X47">
+        <v>1370</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>872.69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" t="s">
+        <v>167</v>
+      </c>
+      <c r="E48" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" t="s">
+        <v>85</v>
+      </c>
+      <c r="G48" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>8</v>
+      </c>
+      <c r="J48">
+        <v>2000</v>
+      </c>
+      <c r="K48">
+        <v>6000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>79</v>
+      </c>
+      <c r="M48" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>117</v>
+      </c>
+      <c r="R48">
+        <v>755</v>
+      </c>
+      <c r="S48">
+        <v>755</v>
+      </c>
+      <c r="T48" t="s">
+        <v>41</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
+        <v>43</v>
+      </c>
+      <c r="W48" t="s">
+        <v>43</v>
+      </c>
+      <c r="X48">
+        <v>2040</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>1540.2</v>
+      </c>
+      <c r="AB48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>168</v>
+      </c>
+      <c r="B49" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F49" t="s">
+        <v>85</v>
+      </c>
+      <c r="G49" t="s">
+        <v>78</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>8</v>
+      </c>
+      <c r="J49">
+        <v>1000</v>
+      </c>
+      <c r="K49">
+        <v>2000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>79</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>117</v>
+      </c>
+      <c r="R49">
+        <v>504</v>
+      </c>
+      <c r="S49">
+        <v>504</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>4</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>2020</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>1018.08</v>
+      </c>
+      <c r="AB49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" t="s">
+        <v>171</v>
+      </c>
+      <c r="E50" t="s">
+        <v>49</v>
+      </c>
+      <c r="F50" t="s">
+        <v>85</v>
+      </c>
+      <c r="G50" t="s">
+        <v>78</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>12</v>
+      </c>
+      <c r="J50">
+        <v>1000</v>
+      </c>
+      <c r="K50">
+        <v>2000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>79</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>117</v>
+      </c>
+      <c r="R50">
+        <v>1322</v>
+      </c>
+      <c r="S50">
+        <v>1322</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>7</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>2070</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>2736.54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>172</v>
+      </c>
+      <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51" t="s">
+        <v>85</v>
+      </c>
+      <c r="G51" t="s">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>2.5</v>
+      </c>
+      <c r="J51">
+        <v>1500</v>
+      </c>
+      <c r="K51">
+        <v>3000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>90</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>117</v>
+      </c>
+      <c r="R51">
+        <v>534</v>
+      </c>
+      <c r="S51">
+        <v>534</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>6</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>3540</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>1890.36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" t="s">
+        <v>175</v>
+      </c>
+      <c r="E52" t="s">
+        <v>49</v>
+      </c>
+      <c r="F52" t="s">
+        <v>85</v>
+      </c>
+      <c r="G52" t="s">
+        <v>86</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="J52">
+        <v>1000</v>
+      </c>
+      <c r="K52">
+        <v>2000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>90</v>
+      </c>
+      <c r="M52" t="s">
+        <v>130</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>117</v>
+      </c>
+      <c r="R52">
+        <v>1046</v>
+      </c>
+      <c r="S52">
+        <v>1046</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>33</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>3540</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>3702.84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>176</v>
+      </c>
+      <c r="B53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" t="s">
+        <v>177</v>
+      </c>
+      <c r="E53" t="s">
+        <v>49</v>
+      </c>
+      <c r="F53" t="s">
+        <v>85</v>
+      </c>
+      <c r="G53" t="s">
+        <v>78</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>4</v>
+      </c>
+      <c r="J53">
+        <v>1500</v>
+      </c>
+      <c r="K53">
+        <v>3000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>90</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>117</v>
+      </c>
+      <c r="R53">
+        <v>142</v>
+      </c>
+      <c r="S53">
+        <v>142</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>1</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>2170</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>178</v>
+      </c>
+      <c r="B54" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" t="s">
+        <v>85</v>
+      </c>
+      <c r="G54" t="s">
+        <v>78</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+      <c r="J54">
+        <v>2000</v>
+      </c>
+      <c r="K54">
+        <v>4000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>90</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>117</v>
+      </c>
+      <c r="R54">
+        <v>126</v>
+      </c>
+      <c r="S54">
+        <v>126</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>1</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>2190</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>180</v>
+      </c>
+      <c r="B55" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" t="s">
+        <v>181</v>
+      </c>
+      <c r="E55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" t="s">
+        <v>85</v>
+      </c>
+      <c r="G55" t="s">
+        <v>86</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55">
+        <v>1250</v>
+      </c>
+      <c r="K55">
+        <v>2500</v>
+      </c>
+      <c r="L55" t="s">
+        <v>90</v>
+      </c>
+      <c r="M55" t="s">
+        <v>130</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>117</v>
+      </c>
+      <c r="R55">
+        <v>612</v>
+      </c>
+      <c r="S55">
+        <v>612</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>12</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>3490</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>2135.88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" t="s">
+        <v>114</v>
+      </c>
+      <c r="D56" t="s">
+        <v>183</v>
+      </c>
+      <c r="E56" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" t="s">
+        <v>85</v>
+      </c>
+      <c r="G56" t="s">
+        <v>124</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>3</v>
+      </c>
+      <c r="J56">
+        <v>1500</v>
+      </c>
+      <c r="K56">
+        <v>3000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>90</v>
+      </c>
+      <c r="M56" t="s">
+        <v>37</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>117</v>
+      </c>
+      <c r="R56">
+        <v>106</v>
+      </c>
+      <c r="S56">
+        <v>106</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>1</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>3640</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>385.84</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" t="s">
+        <v>185</v>
+      </c>
+      <c r="E57" t="s">
+        <v>49</v>
+      </c>
+      <c r="F57" t="s">
+        <v>85</v>
+      </c>
+      <c r="G57" t="s">
+        <v>86</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>1.5</v>
+      </c>
+      <c r="J57">
+        <v>1500</v>
+      </c>
+      <c r="K57">
+        <v>3000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>90</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>117</v>
+      </c>
+      <c r="R57">
+        <v>330</v>
+      </c>
+      <c r="S57">
+        <v>330</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>6</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>3540</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>186</v>
+      </c>
+      <c r="B58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" t="s">
+        <v>187</v>
+      </c>
+      <c r="E58" t="s">
+        <v>49</v>
+      </c>
+      <c r="F58" t="s">
+        <v>85</v>
+      </c>
+      <c r="G58" t="s">
+        <v>78</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>3</v>
+      </c>
+      <c r="J58">
+        <v>1000</v>
+      </c>
+      <c r="K58">
+        <v>2000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>90</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>117</v>
+      </c>
+      <c r="R58">
+        <v>1464</v>
+      </c>
+      <c r="S58">
+        <v>1464</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>31</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>2270</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>3323.28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" t="s">
+        <v>187</v>
+      </c>
+      <c r="E59" t="s">
+        <v>49</v>
+      </c>
+      <c r="F59" t="s">
+        <v>85</v>
+      </c>
+      <c r="G59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>3</v>
+      </c>
+      <c r="J59">
+        <v>1000</v>
+      </c>
+      <c r="K59">
+        <v>2000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>90</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>117</v>
+      </c>
+      <c r="R59">
+        <v>94</v>
+      </c>
+      <c r="S59">
+        <v>94</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>2</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2170</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" t="s">
+        <v>190</v>
+      </c>
+      <c r="E60" t="s">
+        <v>49</v>
+      </c>
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" t="s">
+        <v>191</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>1.2</v>
+      </c>
+      <c r="J60">
+        <v>1250</v>
+      </c>
+      <c r="L60" t="s">
+        <v>90</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>117</v>
+      </c>
+      <c r="R60">
+        <v>1420</v>
+      </c>
+      <c r="S60">
+        <v>1420</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>1</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>1420</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>2016.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>192</v>
+      </c>
+      <c r="B61" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" t="s">
+        <v>193</v>
+      </c>
+      <c r="E61" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" t="s">
+        <v>85</v>
+      </c>
+      <c r="G61" t="s">
+        <v>116</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>0.8</v>
+      </c>
+      <c r="J61">
+        <v>1500</v>
+      </c>
+      <c r="K61">
+        <v>3000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>36</v>
+      </c>
+      <c r="M61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>194</v>
+      </c>
+      <c r="P61" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>117</v>
+      </c>
+      <c r="R61">
+        <v>2584</v>
+      </c>
+      <c r="S61">
+        <v>2584</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>94</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>1520</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>3927.68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>195</v>
+      </c>
+      <c r="B62" t="s">
+        <v>113</v>
+      </c>
+      <c r="C62" t="s">
+        <v>114</v>
+      </c>
+      <c r="D62" t="s">
+        <v>196</v>
+      </c>
+      <c r="E62" t="s">
+        <v>49</v>
+      </c>
+      <c r="F62" t="s">
+        <v>85</v>
+      </c>
+      <c r="G62" t="s">
+        <v>116</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>1250</v>
+      </c>
+      <c r="K62">
+        <v>2500</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+      <c r="M62" t="s">
+        <v>37</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>117</v>
+      </c>
+      <c r="R62">
+        <v>668</v>
+      </c>
+      <c r="S62">
+        <v>668</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>1</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>1370</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>915.16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>197</v>
+      </c>
+      <c r="B63" t="s">
+        <v>113</v>
+      </c>
+      <c r="C63" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" t="s">
+        <v>115</v>
+      </c>
+      <c r="E63" t="s">
+        <v>49</v>
+      </c>
+      <c r="F63" t="s">
+        <v>85</v>
+      </c>
+      <c r="G63" t="s">
+        <v>116</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>1250</v>
+      </c>
+      <c r="K63">
+        <v>2500</v>
+      </c>
+      <c r="L63" t="s">
+        <v>36</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>117</v>
+      </c>
+      <c r="R63">
+        <v>1554</v>
+      </c>
+      <c r="S63">
+        <v>1554</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>1</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>1420</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>2206.68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" t="s">
+        <v>113</v>
+      </c>
+      <c r="C64" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" t="s">
+        <v>199</v>
+      </c>
+      <c r="E64" t="s">
+        <v>49</v>
+      </c>
+      <c r="F64" t="s">
+        <v>85</v>
+      </c>
+      <c r="G64" t="s">
+        <v>116</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>1500</v>
+      </c>
+      <c r="K64">
+        <v>3000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>90</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>117</v>
+      </c>
+      <c r="R64">
+        <v>2210</v>
+      </c>
+      <c r="S64">
+        <v>2210</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>1</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>1420</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>3138.2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>200</v>
+      </c>
+      <c r="B65" t="s">
+        <v>113</v>
+      </c>
+      <c r="C65" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65" t="s">
+        <v>201</v>
+      </c>
+      <c r="E65" t="s">
+        <v>49</v>
+      </c>
+      <c r="F65" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" t="s">
+        <v>116</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>1500</v>
+      </c>
+      <c r="L65" t="s">
+        <v>90</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>117</v>
+      </c>
+      <c r="R65">
+        <v>3350</v>
+      </c>
+      <c r="S65">
+        <v>3350</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>1</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>1420</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>202</v>
+      </c>
+      <c r="B66" t="s">
+        <v>113</v>
+      </c>
+      <c r="C66" t="s">
+        <v>114</v>
+      </c>
+      <c r="D66" t="s">
+        <v>203</v>
+      </c>
+      <c r="E66" t="s">
+        <v>49</v>
+      </c>
+      <c r="F66" t="s">
+        <v>85</v>
+      </c>
+      <c r="G66" t="s">
+        <v>116</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>1.5</v>
+      </c>
+      <c r="J66">
+        <v>1250</v>
+      </c>
+      <c r="K66">
+        <v>2500</v>
+      </c>
+      <c r="L66" t="s">
+        <v>36</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>117</v>
+      </c>
+      <c r="R66">
+        <v>944</v>
+      </c>
+      <c r="S66">
+        <v>944</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>26</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>1370</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>1293.28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>204</v>
+      </c>
+      <c r="B67" t="s">
+        <v>113</v>
+      </c>
+      <c r="C67" t="s">
+        <v>114</v>
+      </c>
+      <c r="D67" t="s">
+        <v>205</v>
+      </c>
+      <c r="E67" t="s">
+        <v>49</v>
+      </c>
+      <c r="F67" t="s">
+        <v>85</v>
+      </c>
+      <c r="G67" t="s">
+        <v>116</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>1500</v>
+      </c>
+      <c r="K67">
+        <v>3000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>36</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>117</v>
+      </c>
+      <c r="R67">
+        <v>1923</v>
+      </c>
+      <c r="S67">
+        <v>1923</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>1</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>1420</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>2730.66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" t="s">
+        <v>122</v>
+      </c>
+      <c r="C68" t="s">
+        <v>114</v>
+      </c>
+      <c r="D68" t="s">
+        <v>207</v>
+      </c>
+      <c r="E68" t="s">
+        <v>49</v>
+      </c>
+      <c r="F68" t="s">
+        <v>85</v>
+      </c>
+      <c r="G68" t="s">
+        <v>78</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>1.2</v>
+      </c>
+      <c r="J68">
+        <v>1500</v>
+      </c>
+      <c r="K68">
+        <v>3000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>90</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>117</v>
+      </c>
+      <c r="R68">
+        <v>42</v>
+      </c>
+      <c r="S68">
+        <v>42</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>1</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>2170</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>91.14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>208</v>
+      </c>
+      <c r="B69" t="s">
+        <v>119</v>
+      </c>
+      <c r="C69" t="s">
+        <v>114</v>
+      </c>
+      <c r="D69" t="s">
+        <v>209</v>
+      </c>
+      <c r="E69" t="s">
+        <v>49</v>
+      </c>
+      <c r="F69" t="s">
+        <v>85</v>
+      </c>
+      <c r="G69" t="s">
+        <v>86</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>8</v>
+      </c>
+      <c r="J69">
+        <v>1500</v>
+      </c>
+      <c r="K69">
+        <v>3000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>90</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>117</v>
+      </c>
+      <c r="R69">
+        <v>1417</v>
+      </c>
+      <c r="S69">
+        <v>1417</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>5</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>3590</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>5087.03</v>
+      </c>
+      <c r="AB69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>210</v>
+      </c>
+      <c r="B70" t="s">
+        <v>113</v>
+      </c>
+      <c r="C70" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" t="s">
+        <v>211</v>
+      </c>
+      <c r="E70" t="s">
+        <v>49</v>
+      </c>
+      <c r="F70" t="s">
+        <v>33</v>
+      </c>
+      <c r="G70" t="s">
+        <v>116</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>0.8</v>
+      </c>
+      <c r="J70">
+        <v>1500</v>
+      </c>
+      <c r="L70" t="s">
+        <v>36</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>38</v>
+      </c>
+      <c r="P70" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>117</v>
+      </c>
+      <c r="R70">
+        <v>1865</v>
+      </c>
+      <c r="S70">
+        <v>1865</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>1</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>1520</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>2834.8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>212</v>
+      </c>
+      <c r="B71" t="s">
+        <v>122</v>
+      </c>
+      <c r="C71" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71" t="s">
+        <v>213</v>
+      </c>
+      <c r="E71" t="s">
+        <v>49</v>
+      </c>
+      <c r="F71" t="s">
+        <v>85</v>
+      </c>
+      <c r="G71" t="s">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>1.25</v>
+      </c>
+      <c r="J71">
+        <v>1250</v>
+      </c>
+      <c r="K71">
+        <v>2500</v>
+      </c>
+      <c r="L71" t="s">
+        <v>90</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>117</v>
+      </c>
+      <c r="R71">
+        <v>31</v>
+      </c>
+      <c r="S71">
+        <v>31</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>1</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>2170</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>67.27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>214</v>
+      </c>
+      <c r="B72" t="s">
+        <v>113</v>
+      </c>
+      <c r="C72" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" t="s">
+        <v>215</v>
+      </c>
+      <c r="E72" t="s">
+        <v>49</v>
+      </c>
+      <c r="F72" t="s">
+        <v>85</v>
+      </c>
+      <c r="G72" t="s">
+        <v>116</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>1.5</v>
+      </c>
+      <c r="J72">
+        <v>1500</v>
+      </c>
+      <c r="K72">
+        <v>3000</v>
+      </c>
+      <c r="L72" t="s">
+        <v>36</v>
+      </c>
+      <c r="M72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>117</v>
+      </c>
+      <c r="R72">
+        <v>1007</v>
+      </c>
+      <c r="S72">
+        <v>1007</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>1420</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>1429.94</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>216</v>
+      </c>
+      <c r="B73" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" t="s">
+        <v>215</v>
+      </c>
+      <c r="E73" t="s">
+        <v>49</v>
+      </c>
+      <c r="F73" t="s">
+        <v>85</v>
+      </c>
+      <c r="G73" t="s">
+        <v>116</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>1.5</v>
+      </c>
+      <c r="J73">
+        <v>1500</v>
+      </c>
+      <c r="K73">
+        <v>3000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>36</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>117</v>
+      </c>
+      <c r="R73">
+        <v>960</v>
+      </c>
+      <c r="S73">
+        <v>960</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>19</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>1370</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>1315.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>217</v>
+      </c>
+      <c r="B74" t="s">
+        <v>119</v>
+      </c>
+      <c r="C74" t="s">
+        <v>114</v>
+      </c>
+      <c r="D74" t="s">
+        <v>218</v>
+      </c>
+      <c r="E74" t="s">
+        <v>49</v>
+      </c>
+      <c r="F74" t="s">
+        <v>85</v>
+      </c>
+      <c r="G74" t="s">
+        <v>78</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>6</v>
+      </c>
+      <c r="J74">
+        <v>2000</v>
+      </c>
+      <c r="K74">
+        <v>6000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>79</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>117</v>
+      </c>
+      <c r="R74">
+        <v>567</v>
+      </c>
+      <c r="S74">
+        <v>567</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>1</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>2040</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>1156.68</v>
+      </c>
+      <c r="AB74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>219</v>
+      </c>
+      <c r="B75" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" t="s">
+        <v>220</v>
+      </c>
+      <c r="E75" t="s">
+        <v>49</v>
+      </c>
+      <c r="F75" t="s">
+        <v>85</v>
+      </c>
+      <c r="G75" t="s">
+        <v>116</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>0.5</v>
+      </c>
+      <c r="J75">
+        <v>1000</v>
+      </c>
+      <c r="K75">
+        <v>2000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>36</v>
+      </c>
+      <c r="M75" t="s">
+        <v>37</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>117</v>
+      </c>
+      <c r="R75">
+        <v>157</v>
+      </c>
+      <c r="S75">
+        <v>157</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>1</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>1620</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>254.34</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>221</v>
+      </c>
+      <c r="B76" t="s">
+        <v>113</v>
+      </c>
+      <c r="C76" t="s">
+        <v>114</v>
+      </c>
+      <c r="D76" t="s">
+        <v>222</v>
+      </c>
+      <c r="E76" t="s">
+        <v>49</v>
+      </c>
+      <c r="F76" t="s">
+        <v>85</v>
+      </c>
+      <c r="G76" t="s">
+        <v>86</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+      <c r="J76">
+        <v>1000</v>
+      </c>
+      <c r="K76">
+        <v>2000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>90</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>117</v>
+      </c>
+      <c r="R76">
+        <v>824</v>
+      </c>
+      <c r="S76">
+        <v>824</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>26</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>3540</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>2916.96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>223</v>
+      </c>
+      <c r="B77" t="s">
+        <v>122</v>
+      </c>
+      <c r="C77" t="s">
+        <v>114</v>
+      </c>
+      <c r="D77" t="s">
+        <v>224</v>
+      </c>
+      <c r="E77" t="s">
+        <v>49</v>
+      </c>
+      <c r="F77" t="s">
+        <v>85</v>
+      </c>
+      <c r="G77" t="s">
+        <v>78</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>0.8</v>
+      </c>
+      <c r="J77">
+        <v>1250</v>
+      </c>
+      <c r="K77">
+        <v>2500</v>
+      </c>
+      <c r="L77" t="s">
+        <v>90</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>117</v>
+      </c>
+      <c r="R77">
+        <v>59</v>
+      </c>
+      <c r="S77">
+        <v>59</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>3</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>2270</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>133.93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>225</v>
+      </c>
+      <c r="B78" t="s">
+        <v>122</v>
+      </c>
+      <c r="C78" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" t="s">
+        <v>224</v>
+      </c>
+      <c r="E78" t="s">
+        <v>49</v>
+      </c>
+      <c r="F78" t="s">
+        <v>85</v>
+      </c>
+      <c r="G78" t="s">
+        <v>78</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>0.8</v>
+      </c>
+      <c r="J78">
+        <v>1250</v>
+      </c>
+      <c r="K78">
+        <v>2500</v>
+      </c>
+      <c r="L78" t="s">
+        <v>90</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>117</v>
+      </c>
+      <c r="R78">
+        <v>79</v>
+      </c>
+      <c r="S78">
+        <v>79</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>4</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>2270</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>179.33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>226</v>
+      </c>
+      <c r="B79" t="s">
+        <v>122</v>
+      </c>
+      <c r="C79" t="s">
+        <v>114</v>
+      </c>
+      <c r="D79" t="s">
+        <v>227</v>
+      </c>
+      <c r="E79" t="s">
+        <v>49</v>
+      </c>
+      <c r="F79" t="s">
+        <v>85</v>
+      </c>
+      <c r="G79" t="s">
+        <v>124</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>12</v>
+      </c>
+      <c r="J79">
+        <v>1500</v>
+      </c>
+      <c r="K79">
+        <v>3000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>79</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>117</v>
+      </c>
+      <c r="R79">
+        <v>1275</v>
+      </c>
+      <c r="S79">
+        <v>1275</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>3</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>3540</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>4513.5</v>
+      </c>
+      <c r="AB79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>228</v>
+      </c>
+      <c r="B80" t="s">
+        <v>122</v>
+      </c>
+      <c r="C80" t="s">
+        <v>114</v>
+      </c>
+      <c r="D80" t="s">
+        <v>227</v>
+      </c>
+      <c r="E80" t="s">
+        <v>49</v>
+      </c>
+      <c r="F80" t="s">
+        <v>85</v>
+      </c>
+      <c r="G80" t="s">
+        <v>124</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>12</v>
+      </c>
+      <c r="J80">
+        <v>1500</v>
+      </c>
+      <c r="K80">
+        <v>3000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>79</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>117</v>
+      </c>
+      <c r="R80">
+        <v>1275</v>
+      </c>
+      <c r="S80">
+        <v>1275</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>3</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>3540</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>4513.5</v>
+      </c>
+      <c r="AB80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>229</v>
+      </c>
+      <c r="B81" t="s">
+        <v>122</v>
+      </c>
+      <c r="C81" t="s">
+        <v>114</v>
+      </c>
+      <c r="D81" t="s">
+        <v>227</v>
+      </c>
+      <c r="E81" t="s">
+        <v>49</v>
+      </c>
+      <c r="F81" t="s">
+        <v>85</v>
+      </c>
+      <c r="G81" t="s">
+        <v>124</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>12</v>
+      </c>
+      <c r="J81">
+        <v>1500</v>
+      </c>
+      <c r="K81">
+        <v>3000</v>
+      </c>
+      <c r="L81" t="s">
+        <v>79</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>117</v>
+      </c>
+      <c r="R81">
+        <v>850</v>
+      </c>
+      <c r="S81">
+        <v>850</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>2</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>3490</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>2966.5</v>
+      </c>
+      <c r="AB81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>230</v>
+      </c>
+      <c r="B82" t="s">
+        <v>113</v>
+      </c>
+      <c r="C82" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" t="s">
+        <v>187</v>
+      </c>
+      <c r="E82" t="s">
+        <v>49</v>
+      </c>
+      <c r="F82" t="s">
+        <v>85</v>
+      </c>
+      <c r="G82" t="s">
+        <v>78</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>3</v>
+      </c>
+      <c r="J82">
+        <v>1000</v>
+      </c>
+      <c r="K82">
+        <v>2000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>90</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>117</v>
+      </c>
+      <c r="R82">
+        <v>379</v>
+      </c>
+      <c r="S82">
+        <v>379</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>8</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>2220</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>841.38</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>231</v>
+      </c>
+      <c r="B83" t="s">
+        <v>122</v>
+      </c>
+      <c r="C83" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" t="s">
+        <v>232</v>
+      </c>
+      <c r="E83" t="s">
+        <v>49</v>
+      </c>
+      <c r="F83" t="s">
+        <v>85</v>
+      </c>
+      <c r="G83" t="s">
+        <v>78</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>1.5</v>
+      </c>
+      <c r="J83">
+        <v>1000</v>
+      </c>
+      <c r="K83">
+        <v>2000</v>
+      </c>
+      <c r="L83" t="s">
+        <v>90</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>117</v>
+      </c>
+      <c r="R83">
+        <v>94</v>
+      </c>
+      <c r="S83">
+        <v>94</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>4</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>2170</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>233</v>
+      </c>
+      <c r="B84" t="s">
+        <v>122</v>
+      </c>
+      <c r="C84" t="s">
+        <v>114</v>
+      </c>
+      <c r="D84" t="s">
+        <v>209</v>
+      </c>
+      <c r="E84" t="s">
+        <v>49</v>
+      </c>
+      <c r="F84" t="s">
+        <v>85</v>
+      </c>
+      <c r="G84" t="s">
+        <v>86</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>8</v>
+      </c>
+      <c r="J84">
+        <v>1500</v>
+      </c>
+      <c r="K84">
+        <v>3000</v>
+      </c>
+      <c r="L84" t="s">
+        <v>90</v>
+      </c>
+      <c r="M84" t="s">
+        <v>37</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>117</v>
+      </c>
+      <c r="R84">
+        <v>1417</v>
+      </c>
+      <c r="S84">
+        <v>1417</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>5.11</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>3590</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>5087.03</v>
+      </c>
+      <c r="AB84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>234</v>
+      </c>
+      <c r="B85" t="s">
+        <v>122</v>
+      </c>
+      <c r="C85" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" t="s">
+        <v>209</v>
+      </c>
+      <c r="E85" t="s">
+        <v>49</v>
+      </c>
+      <c r="F85" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85" t="s">
+        <v>86</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>8</v>
+      </c>
+      <c r="J85">
+        <v>1500</v>
+      </c>
+      <c r="K85">
+        <v>3000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>90</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>117</v>
+      </c>
+      <c r="R85">
+        <v>2267</v>
+      </c>
+      <c r="S85">
+        <v>2267</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>8.175</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>3590</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>8138.53</v>
+      </c>
+      <c r="AB85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>235</v>
+      </c>
+      <c r="B86" t="s">
+        <v>122</v>
+      </c>
+      <c r="C86" t="s">
+        <v>114</v>
+      </c>
+      <c r="D86" t="s">
+        <v>236</v>
+      </c>
+      <c r="E86" t="s">
+        <v>49</v>
+      </c>
+      <c r="F86" t="s">
+        <v>85</v>
+      </c>
+      <c r="G86" t="s">
+        <v>86</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>6</v>
+      </c>
+      <c r="J86">
+        <v>1500</v>
+      </c>
+      <c r="K86">
+        <v>3000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>90</v>
+      </c>
+      <c r="M86" t="s">
+        <v>37</v>
+      </c>
+      <c r="N86" t="s">
+        <v>37</v>
+      </c>
+      <c r="O86" t="s">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>117</v>
+      </c>
+      <c r="R86">
+        <v>1275</v>
+      </c>
+      <c r="S86">
+        <v>1275</v>
+      </c>
+      <c r="T86" t="s">
+        <v>41</v>
+      </c>
+      <c r="U86">
+        <v>6</v>
+      </c>
+      <c r="V86" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86">
+        <v>3590</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA86">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>237</v>
+      </c>
+      <c r="B87" t="s">
+        <v>119</v>
+      </c>
+      <c r="C87" t="s">
+        <v>114</v>
+      </c>
+      <c r="D87" t="s">
+        <v>209</v>
+      </c>
+      <c r="E87" t="s">
+        <v>49</v>
+      </c>
+      <c r="F87" t="s">
+        <v>85</v>
+      </c>
+      <c r="G87" t="s">
+        <v>86</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87">
+        <v>8</v>
+      </c>
+      <c r="J87">
+        <v>1500</v>
+      </c>
+      <c r="K87">
+        <v>3000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>90</v>
+      </c>
+      <c r="M87" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" t="s">
+        <v>37</v>
+      </c>
+      <c r="O87" t="s">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>117</v>
+      </c>
+      <c r="R87">
+        <v>576</v>
+      </c>
+      <c r="S87">
+        <v>576</v>
+      </c>
+      <c r="T87" t="s">
+        <v>41</v>
+      </c>
+      <c r="U87">
+        <v>2.033</v>
+      </c>
+      <c r="V87" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87">
+        <v>3540</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA87">
+        <v>2039.04</v>
+      </c>
+      <c r="AB87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>238</v>
+      </c>
+      <c r="B88" t="s">
+        <v>119</v>
+      </c>
+      <c r="C88" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" t="s">
+        <v>209</v>
+      </c>
+      <c r="E88" t="s">
+        <v>49</v>
+      </c>
+      <c r="F88" t="s">
+        <v>85</v>
+      </c>
+      <c r="G88" t="s">
+        <v>86</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88">
+        <v>8</v>
+      </c>
+      <c r="J88">
+        <v>1500</v>
+      </c>
+      <c r="K88">
+        <v>3000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>90</v>
+      </c>
+      <c r="M88" t="s">
+        <v>37</v>
+      </c>
+      <c r="N88" t="s">
+        <v>37</v>
+      </c>
+      <c r="O88" t="s">
+        <v>38</v>
+      </c>
+      <c r="P88" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>117</v>
+      </c>
+      <c r="R88">
+        <v>1134</v>
+      </c>
+      <c r="S88">
+        <v>1134</v>
+      </c>
+      <c r="T88" t="s">
+        <v>41</v>
+      </c>
+      <c r="U88">
+        <v>4.003</v>
+      </c>
+      <c r="V88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88">
+        <v>3590</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA88">
+        <v>4071.06</v>
+      </c>
+      <c r="AB88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>239</v>
+      </c>
+      <c r="B89" t="s">
+        <v>119</v>
+      </c>
+      <c r="C89" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" t="s">
+        <v>209</v>
+      </c>
+      <c r="E89" t="s">
+        <v>49</v>
+      </c>
+      <c r="F89" t="s">
+        <v>85</v>
+      </c>
+      <c r="G89" t="s">
+        <v>86</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89">
+        <v>8</v>
+      </c>
+      <c r="J89">
+        <v>1500</v>
+      </c>
+      <c r="K89">
+        <v>3000</v>
+      </c>
+      <c r="L89" t="s">
+        <v>90</v>
+      </c>
+      <c r="M89" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" t="s">
+        <v>37</v>
+      </c>
+      <c r="O89" t="s">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>117</v>
+      </c>
+      <c r="R89">
+        <v>1417</v>
+      </c>
+      <c r="S89">
+        <v>1417</v>
+      </c>
+      <c r="T89" t="s">
+        <v>41</v>
+      </c>
+      <c r="U89">
+        <v>5.001</v>
+      </c>
+      <c r="V89" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" t="s">
+        <v>43</v>
+      </c>
+      <c r="X89">
+        <v>3590</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA89">
+        <v>5087.03</v>
+      </c>
+      <c r="AB89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>240</v>
+      </c>
+      <c r="B90" t="s">
+        <v>119</v>
+      </c>
+      <c r="C90" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" t="s">
+        <v>209</v>
+      </c>
+      <c r="E90" t="s">
+        <v>49</v>
+      </c>
+      <c r="F90" t="s">
+        <v>85</v>
+      </c>
+      <c r="G90" t="s">
+        <v>86</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>8</v>
+      </c>
+      <c r="J90">
+        <v>1500</v>
+      </c>
+      <c r="K90">
+        <v>3000</v>
+      </c>
+      <c r="L90" t="s">
+        <v>90</v>
+      </c>
+      <c r="M90" t="s">
+        <v>37</v>
+      </c>
+      <c r="N90" t="s">
+        <v>37</v>
+      </c>
+      <c r="O90" t="s">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>117</v>
+      </c>
+      <c r="R90">
+        <v>1417</v>
+      </c>
+      <c r="S90">
+        <v>1417</v>
+      </c>
+      <c r="T90" t="s">
+        <v>41</v>
+      </c>
+      <c r="U90">
+        <v>5.001</v>
+      </c>
+      <c r="V90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90">
+        <v>3590</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA90">
+        <v>5087.03</v>
+      </c>
+      <c r="AB90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>241</v>
+      </c>
+      <c r="B91" t="s">
+        <v>119</v>
+      </c>
+      <c r="C91" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" t="s">
+        <v>209</v>
+      </c>
+      <c r="E91" t="s">
+        <v>49</v>
+      </c>
+      <c r="F91" t="s">
+        <v>85</v>
+      </c>
+      <c r="G91" t="s">
+        <v>86</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91">
+        <v>8</v>
+      </c>
+      <c r="J91">
+        <v>1500</v>
+      </c>
+      <c r="K91">
+        <v>3000</v>
+      </c>
+      <c r="L91" t="s">
+        <v>90</v>
+      </c>
+      <c r="M91" t="s">
+        <v>37</v>
+      </c>
+      <c r="N91" t="s">
+        <v>37</v>
+      </c>
+      <c r="O91" t="s">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>117</v>
+      </c>
+      <c r="R91">
+        <v>1417</v>
+      </c>
+      <c r="S91">
+        <v>1417</v>
+      </c>
+      <c r="T91" t="s">
+        <v>41</v>
+      </c>
+      <c r="U91">
+        <v>5.001</v>
+      </c>
+      <c r="V91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91">
+        <v>3590</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA91">
+        <v>5087.03</v>
+      </c>
+      <c r="AB91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>242</v>
+      </c>
+      <c r="B92" t="s">
+        <v>119</v>
+      </c>
+      <c r="C92" t="s">
+        <v>114</v>
+      </c>
+      <c r="D92" t="s">
+        <v>209</v>
+      </c>
+      <c r="E92" t="s">
+        <v>49</v>
+      </c>
+      <c r="F92" t="s">
+        <v>85</v>
+      </c>
+      <c r="G92" t="s">
+        <v>86</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92">
+        <v>8</v>
+      </c>
+      <c r="J92">
+        <v>1500</v>
+      </c>
+      <c r="K92">
+        <v>3000</v>
+      </c>
+      <c r="L92" t="s">
+        <v>90</v>
+      </c>
+      <c r="M92" t="s">
+        <v>37</v>
+      </c>
+      <c r="N92" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" t="s">
+        <v>38</v>
+      </c>
+      <c r="P92" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>117</v>
+      </c>
+      <c r="R92">
+        <v>1130</v>
+      </c>
+      <c r="S92">
+        <v>1130</v>
+      </c>
+      <c r="T92" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92">
+        <v>3.988</v>
+      </c>
+      <c r="V92" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92">
+        <v>3590</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA92">
+        <v>4056.7</v>
+      </c>
+      <c r="AB92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>243</v>
+      </c>
+      <c r="B93" t="s">
+        <v>119</v>
+      </c>
+      <c r="C93" t="s">
+        <v>114</v>
+      </c>
+      <c r="D93" t="s">
+        <v>209</v>
+      </c>
+      <c r="E93" t="s">
+        <v>49</v>
+      </c>
+      <c r="F93" t="s">
+        <v>85</v>
+      </c>
+      <c r="G93" t="s">
+        <v>86</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93">
+        <v>8</v>
+      </c>
+      <c r="J93">
+        <v>1500</v>
+      </c>
+      <c r="K93">
+        <v>3000</v>
+      </c>
+      <c r="L93" t="s">
+        <v>90</v>
+      </c>
+      <c r="M93" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" t="s">
+        <v>38</v>
+      </c>
+      <c r="P93" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>117</v>
+      </c>
+      <c r="R93">
+        <v>1417</v>
+      </c>
+      <c r="S93">
+        <v>1417</v>
+      </c>
+      <c r="T93" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93">
+        <v>5.001</v>
+      </c>
+      <c r="V93" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" t="s">
+        <v>43</v>
+      </c>
+      <c r="X93">
+        <v>3590</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA93">
+        <v>5087.03</v>
+      </c>
+      <c r="AB93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>244</v>
+      </c>
+      <c r="B94" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94" t="s">
+        <v>114</v>
+      </c>
+      <c r="D94" t="s">
+        <v>209</v>
+      </c>
+      <c r="E94" t="s">
+        <v>49</v>
+      </c>
+      <c r="F94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G94" t="s">
+        <v>86</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94">
+        <v>8</v>
+      </c>
+      <c r="J94">
+        <v>1500</v>
+      </c>
+      <c r="K94">
+        <v>3000</v>
+      </c>
+      <c r="L94" t="s">
+        <v>90</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
+      </c>
+      <c r="N94" t="s">
+        <v>37</v>
+      </c>
+      <c r="O94" t="s">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>117</v>
+      </c>
+      <c r="R94">
+        <v>1417</v>
+      </c>
+      <c r="S94">
+        <v>1417</v>
+      </c>
+      <c r="T94" t="s">
+        <v>41</v>
+      </c>
+      <c r="U94">
+        <v>5.001</v>
+      </c>
+      <c r="V94" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94">
+        <v>3590</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA94">
+        <v>5087.03</v>
+      </c>
+      <c r="AB94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>245</v>
+      </c>
+      <c r="B95" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" t="s">
+        <v>209</v>
+      </c>
+      <c r="E95" t="s">
+        <v>49</v>
+      </c>
+      <c r="F95" t="s">
+        <v>85</v>
+      </c>
+      <c r="G95" t="s">
+        <v>86</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95">
+        <v>8</v>
+      </c>
+      <c r="J95">
+        <v>1500</v>
+      </c>
+      <c r="K95">
+        <v>3000</v>
+      </c>
+      <c r="L95" t="s">
+        <v>90</v>
+      </c>
+      <c r="M95" t="s">
+        <v>37</v>
+      </c>
+      <c r="N95" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" t="s">
+        <v>38</v>
+      </c>
+      <c r="P95" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>117</v>
+      </c>
+      <c r="R95">
+        <v>1417</v>
+      </c>
+      <c r="S95">
+        <v>1417</v>
+      </c>
+      <c r="T95" t="s">
+        <v>41</v>
+      </c>
+      <c r="U95">
+        <v>5.001</v>
+      </c>
+      <c r="V95" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95">
+        <v>3590</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA95">
+        <v>5087.03</v>
+      </c>
+      <c r="AB95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>246</v>
+      </c>
+      <c r="B96" t="s">
+        <v>119</v>
+      </c>
+      <c r="C96" t="s">
+        <v>114</v>
+      </c>
+      <c r="D96" t="s">
+        <v>160</v>
+      </c>
+      <c r="E96" t="s">
+        <v>49</v>
+      </c>
+      <c r="F96" t="s">
+        <v>85</v>
+      </c>
+      <c r="G96" t="s">
+        <v>78</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
+        <v>1000</v>
+      </c>
+      <c r="K96">
+        <v>2000</v>
+      </c>
+      <c r="L96" t="s">
+        <v>90</v>
+      </c>
+      <c r="M96" t="s">
+        <v>37</v>
+      </c>
+      <c r="N96" t="s">
+        <v>37</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
+      </c>
+      <c r="P96" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>117</v>
+      </c>
+      <c r="R96">
+        <v>1448</v>
+      </c>
+      <c r="S96">
+        <v>1448</v>
+      </c>
+      <c r="T96" t="s">
+        <v>41</v>
+      </c>
+      <c r="U96">
+        <v>45.997</v>
+      </c>
+      <c r="V96" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" t="s">
+        <v>43</v>
+      </c>
+      <c r="X96">
+        <v>2270</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA96">
+        <v>3286.96</v>
+      </c>
+      <c r="AB96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>247</v>
+      </c>
+      <c r="B97" t="s">
+        <v>119</v>
+      </c>
+      <c r="C97" t="s">
+        <v>114</v>
+      </c>
+      <c r="D97" t="s">
+        <v>160</v>
+      </c>
+      <c r="E97" t="s">
+        <v>49</v>
+      </c>
+      <c r="F97" t="s">
+        <v>85</v>
+      </c>
+      <c r="G97" t="s">
+        <v>78</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="J97">
+        <v>1000</v>
+      </c>
+      <c r="K97">
+        <v>2000</v>
+      </c>
+      <c r="L97" t="s">
+        <v>90</v>
+      </c>
+      <c r="M97" t="s">
+        <v>37</v>
+      </c>
+      <c r="N97" t="s">
+        <v>37</v>
+      </c>
+      <c r="O97" t="s">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>117</v>
+      </c>
+      <c r="R97">
+        <v>1448</v>
+      </c>
+      <c r="S97">
+        <v>1448</v>
+      </c>
+      <c r="T97" t="s">
+        <v>41</v>
+      </c>
+      <c r="U97">
+        <v>45.997</v>
+      </c>
+      <c r="V97" t="s">
+        <v>43</v>
+      </c>
+      <c r="W97" t="s">
+        <v>43</v>
+      </c>
+      <c r="X97">
+        <v>2270</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA97">
+        <v>3286.96</v>
+      </c>
+      <c r="AB97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>248</v>
+      </c>
+      <c r="B98" t="s">
+        <v>119</v>
+      </c>
+      <c r="C98" t="s">
+        <v>114</v>
+      </c>
+      <c r="D98" t="s">
+        <v>249</v>
+      </c>
+      <c r="E98" t="s">
+        <v>49</v>
+      </c>
+      <c r="F98" t="s">
+        <v>85</v>
+      </c>
+      <c r="G98" t="s">
+        <v>116</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98">
+        <v>1.2</v>
+      </c>
+      <c r="J98">
+        <v>1500</v>
+      </c>
+      <c r="K98">
+        <v>3000</v>
+      </c>
+      <c r="L98" t="s">
+        <v>90</v>
+      </c>
+      <c r="M98" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" t="s">
+        <v>37</v>
+      </c>
+      <c r="O98" t="s">
+        <v>38</v>
+      </c>
+      <c r="P98" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>117</v>
+      </c>
+      <c r="R98">
+        <v>807</v>
+      </c>
+      <c r="S98">
+        <v>807</v>
+      </c>
+      <c r="T98" t="s">
+        <v>41</v>
+      </c>
+      <c r="U98">
+        <v>18.989</v>
+      </c>
+      <c r="V98" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98">
+        <v>1370</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA98">
+        <v>1105.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/aperam_export.xlsx
+++ b/aperam_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="315">
   <si>
     <t>Pack Back Office Id</t>
   </si>
@@ -485,6 +485,477 @@
   </si>
   <si>
     <t>2E</t>
+  </si>
+  <si>
+    <t>7250649</t>
+  </si>
+  <si>
+    <t>Haan</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D 8.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>7251007</t>
+  </si>
+  <si>
+    <t>Haan (12)</t>
+  </si>
+  <si>
+    <t>Sheets 1.4541-321 1D 5.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>7251027</t>
+  </si>
+  <si>
+    <t>Sersheim</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Brushed</t>
+  </si>
+  <si>
+    <t>T480405</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 1D 5.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>K30/1.4016-430</t>
+  </si>
+  <si>
+    <t>7251955</t>
+  </si>
+  <si>
+    <t>Coil 1.4404-316L 2B 1.5 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T483783</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7253976</t>
+  </si>
+  <si>
+    <t>7254534</t>
+  </si>
+  <si>
+    <t>7254887</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R Coated (Tech) 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>2R</t>
+  </si>
+  <si>
+    <t>Coated (Tech)</t>
+  </si>
+  <si>
+    <t>7254972</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255277</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255426</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 5.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7255783</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256047</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R Brushed with paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256766</t>
+  </si>
+  <si>
+    <t>Coil 1.4301ED-304 2R with paper 0.8 x 1000.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7256818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256835</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7256836</t>
+  </si>
+  <si>
+    <t>7256963</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B with paper 2.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7256980</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B without paper 4.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489700</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T489750</t>
+  </si>
+  <si>
+    <t>7257864</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7257894</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>S139218</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D 12.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258091</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258149</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491483</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 4.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T491760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 2.0 x 2000.0 x 4000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258526</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B Brushed with paper 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7258730</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 2B 3.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258760</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258862</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 3.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7258863</t>
+  </si>
+  <si>
+    <t>7259015</t>
+  </si>
+  <si>
+    <t>Coil 1.4520-430Ti 2B 1.2 x 1250.0 mm Slit</t>
+  </si>
+  <si>
+    <t>1.4520-430Ti</t>
+  </si>
+  <si>
+    <t>7259050</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R NOV 4241/4513 0.8 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>NOV 4241/4513</t>
+  </si>
+  <si>
+    <t>7259145</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259417</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 2.0 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259437</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259438</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2B with paper 1.0 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>7259439</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R with paper 1.5 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259447</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 1.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T493044</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259677</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B without paper 8.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7259689</t>
+  </si>
+  <si>
+    <t>Coil K30/1.4016-430 2R with paper 0.8 x 1500.0 mm Slit</t>
+  </si>
+  <si>
+    <t>T493468</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.25 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7259716</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R without paper 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259717</t>
+  </si>
+  <si>
+    <t>7259732</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 6.0 x 2000.0 x 6000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7259803</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 0.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7259914</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 2.0 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>T493993</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 0.8 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>T493994</t>
+  </si>
+  <si>
+    <t>7260311</t>
+  </si>
+  <si>
+    <t>Sheets 1.4571-316Ti 1D without paper 12.0 x 1500.0 x 3000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7260313</t>
+  </si>
+  <si>
+    <t>7260315</t>
+  </si>
+  <si>
+    <t>7260324</t>
+  </si>
+  <si>
+    <t>T494573</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1000.0 x 2000 mm Slit</t>
+  </si>
+  <si>
+    <t>7260481</t>
+  </si>
+  <si>
+    <t>7260483</t>
+  </si>
+  <si>
+    <t>T494673</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 2B 6.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7260613</t>
+  </si>
+  <si>
+    <t>7260615</t>
+  </si>
+  <si>
+    <t>7260617</t>
+  </si>
+  <si>
+    <t>7260620</t>
+  </si>
+  <si>
+    <t>7260621</t>
+  </si>
+  <si>
+    <t>7260622</t>
+  </si>
+  <si>
+    <t>7260623</t>
+  </si>
+  <si>
+    <t>7260625</t>
+  </si>
+  <si>
+    <t>7260626</t>
+  </si>
+  <si>
+    <t>7260631</t>
+  </si>
+  <si>
+    <t>7260632</t>
+  </si>
+  <si>
+    <t>7260639</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2B with paper 1.2 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>7260772</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B without paper 1.5 x 1000.0 x 2000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7260775</t>
+  </si>
+  <si>
+    <t>7260781</t>
+  </si>
+  <si>
+    <t>Sheets 1.4404-316L 1D without paper 12.0 x 2000.0 x 6000 mm Slit</t>
+  </si>
+  <si>
+    <t>7260787</t>
+  </si>
+  <si>
+    <t>Sheets K30/1.4016-430 2R 0.7 x 1250.0 x 2500 mm Slit</t>
+  </si>
+  <si>
+    <t>7260807</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 8.0 x 2000.0 x 4000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>7260808</t>
+  </si>
+  <si>
+    <t>7260809</t>
+  </si>
+  <si>
+    <t>7260818</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 1D without paper 6.0 x 2000.0 x 4000 mm Slit marked</t>
+  </si>
+  <si>
+    <t>T494995</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B 1.5 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>T495027</t>
+  </si>
+  <si>
+    <t>T495028</t>
+  </si>
+  <si>
+    <t>T495029</t>
+  </si>
+  <si>
+    <t>T495030</t>
+  </si>
+  <si>
+    <t>7260874</t>
+  </si>
+  <si>
+    <t>Sheets 1.4307-304L 2B Polish grain 240 2.0 x 1500.0 x 3000 mm Slit</t>
+  </si>
+  <si>
+    <t>Polish grain 240</t>
+  </si>
+  <si>
+    <t>7260875</t>
   </si>
 </sst>
 </file>
@@ -861,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB48"/>
+  <dimension ref="A1:AB136"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="28" width="20" customWidth="1"/>
@@ -4914,6 +5385,7373 @@
         <v>0</v>
       </c>
     </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>158</v>
+      </c>
+      <c r="B49" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49" t="s">
+        <v>161</v>
+      </c>
+      <c r="E49" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>8</v>
+      </c>
+      <c r="J49">
+        <v>1250</v>
+      </c>
+      <c r="K49">
+        <v>2500</v>
+      </c>
+      <c r="L49" t="s">
+        <v>36</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
+      </c>
+      <c r="N49" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>162</v>
+      </c>
+      <c r="R49">
+        <v>394</v>
+      </c>
+      <c r="S49">
+        <v>394</v>
+      </c>
+      <c r="T49" t="s">
+        <v>41</v>
+      </c>
+      <c r="U49">
+        <v>1</v>
+      </c>
+      <c r="V49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>43</v>
+      </c>
+      <c r="X49">
+        <v>3490</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA49">
+        <v>1375.06</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" t="s">
+        <v>160</v>
+      </c>
+      <c r="D50" t="s">
+        <v>165</v>
+      </c>
+      <c r="E50" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" t="s">
+        <v>146</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>5</v>
+      </c>
+      <c r="J50">
+        <v>2000</v>
+      </c>
+      <c r="K50">
+        <v>6000</v>
+      </c>
+      <c r="L50" t="s">
+        <v>36</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
+      </c>
+      <c r="N50" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>162</v>
+      </c>
+      <c r="R50">
+        <v>472</v>
+      </c>
+      <c r="S50">
+        <v>472</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>43</v>
+      </c>
+      <c r="X50">
+        <v>2190</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>1033.68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" t="s">
+        <v>160</v>
+      </c>
+      <c r="D51" t="s">
+        <v>168</v>
+      </c>
+      <c r="E51" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" t="s">
+        <v>100</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+      <c r="J51">
+        <v>1500</v>
+      </c>
+      <c r="K51">
+        <v>3000</v>
+      </c>
+      <c r="L51" t="s">
+        <v>89</v>
+      </c>
+      <c r="M51" t="s">
+        <v>169</v>
+      </c>
+      <c r="N51" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>162</v>
+      </c>
+      <c r="R51">
+        <v>970</v>
+      </c>
+      <c r="S51">
+        <v>970</v>
+      </c>
+      <c r="T51" t="s">
+        <v>41</v>
+      </c>
+      <c r="U51">
+        <v>13</v>
+      </c>
+      <c r="V51" t="s">
+        <v>43</v>
+      </c>
+      <c r="W51" t="s">
+        <v>43</v>
+      </c>
+      <c r="X51">
+        <v>3490</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA51">
+        <v>3385.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" t="s">
+        <v>159</v>
+      </c>
+      <c r="C52" t="s">
+        <v>160</v>
+      </c>
+      <c r="D52" t="s">
+        <v>171</v>
+      </c>
+      <c r="E52" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" t="s">
+        <v>33</v>
+      </c>
+      <c r="G52" t="s">
+        <v>172</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
+      </c>
+      <c r="J52">
+        <v>1500</v>
+      </c>
+      <c r="K52">
+        <v>3000</v>
+      </c>
+      <c r="L52" t="s">
+        <v>36</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+      <c r="N52" t="s">
+        <v>37</v>
+      </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>162</v>
+      </c>
+      <c r="R52">
+        <v>354</v>
+      </c>
+      <c r="S52">
+        <v>354</v>
+      </c>
+      <c r="T52" t="s">
+        <v>41</v>
+      </c>
+      <c r="U52">
+        <v>2</v>
+      </c>
+      <c r="V52" t="s">
+        <v>43</v>
+      </c>
+      <c r="W52" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52">
+        <v>1170</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>414.18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>173</v>
+      </c>
+      <c r="B53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" t="s">
+        <v>160</v>
+      </c>
+      <c r="D53" t="s">
+        <v>174</v>
+      </c>
+      <c r="E53" t="s">
+        <v>86</v>
+      </c>
+      <c r="F53" t="s">
+        <v>87</v>
+      </c>
+      <c r="G53" t="s">
+        <v>100</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>1.5</v>
+      </c>
+      <c r="J53">
+        <v>1250</v>
+      </c>
+      <c r="L53" t="s">
+        <v>89</v>
+      </c>
+      <c r="M53" t="s">
+        <v>37</v>
+      </c>
+      <c r="N53" t="s">
+        <v>37</v>
+      </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>162</v>
+      </c>
+      <c r="R53">
+        <v>1275</v>
+      </c>
+      <c r="S53">
+        <v>1275</v>
+      </c>
+      <c r="T53" t="s">
+        <v>41</v>
+      </c>
+      <c r="U53">
+        <v>1</v>
+      </c>
+      <c r="V53" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53">
+        <v>3590</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <v>4577.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>175</v>
+      </c>
+      <c r="B54" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" t="s">
+        <v>86</v>
+      </c>
+      <c r="F54" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" t="s">
+        <v>172</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>3</v>
+      </c>
+      <c r="J54">
+        <v>1500</v>
+      </c>
+      <c r="K54">
+        <v>3000</v>
+      </c>
+      <c r="L54" t="s">
+        <v>89</v>
+      </c>
+      <c r="M54" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>162</v>
+      </c>
+      <c r="R54">
+        <v>212</v>
+      </c>
+      <c r="S54">
+        <v>212</v>
+      </c>
+      <c r="T54" t="s">
+        <v>41</v>
+      </c>
+      <c r="U54">
+        <v>2</v>
+      </c>
+      <c r="V54" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54">
+        <v>1320</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA54">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>177</v>
+      </c>
+      <c r="B55" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" t="s">
+        <v>160</v>
+      </c>
+      <c r="D55" t="s">
+        <v>176</v>
+      </c>
+      <c r="E55" t="s">
+        <v>86</v>
+      </c>
+      <c r="F55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G55" t="s">
+        <v>172</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>3</v>
+      </c>
+      <c r="J55">
+        <v>1500</v>
+      </c>
+      <c r="K55">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="s">
+        <v>89</v>
+      </c>
+      <c r="M55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N55" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>162</v>
+      </c>
+      <c r="R55">
+        <v>319</v>
+      </c>
+      <c r="S55">
+        <v>319</v>
+      </c>
+      <c r="T55" t="s">
+        <v>41</v>
+      </c>
+      <c r="U55">
+        <v>3</v>
+      </c>
+      <c r="V55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55">
+        <v>1370</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA55">
+        <v>437.03</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>178</v>
+      </c>
+      <c r="B56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" t="s">
+        <v>160</v>
+      </c>
+      <c r="D56" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" t="s">
+        <v>100</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <v>1500</v>
+      </c>
+      <c r="K56">
+        <v>3000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>89</v>
+      </c>
+      <c r="M56" t="s">
+        <v>169</v>
+      </c>
+      <c r="N56" t="s">
+        <v>37</v>
+      </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>162</v>
+      </c>
+      <c r="R56">
+        <v>1010</v>
+      </c>
+      <c r="S56">
+        <v>1010</v>
+      </c>
+      <c r="T56" t="s">
+        <v>41</v>
+      </c>
+      <c r="U56">
+        <v>14</v>
+      </c>
+      <c r="V56" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56">
+        <v>3540</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA56">
+        <v>3575.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>179</v>
+      </c>
+      <c r="B57" t="s">
+        <v>167</v>
+      </c>
+      <c r="C57" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" t="s">
+        <v>180</v>
+      </c>
+      <c r="E57" t="s">
+        <v>86</v>
+      </c>
+      <c r="F57" t="s">
+        <v>87</v>
+      </c>
+      <c r="G57" t="s">
+        <v>115</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>0.8</v>
+      </c>
+      <c r="J57">
+        <v>1000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>181</v>
+      </c>
+      <c r="M57" t="s">
+        <v>37</v>
+      </c>
+      <c r="N57" t="s">
+        <v>37</v>
+      </c>
+      <c r="O57" t="s">
+        <v>182</v>
+      </c>
+      <c r="P57" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>162</v>
+      </c>
+      <c r="R57">
+        <v>1585</v>
+      </c>
+      <c r="S57">
+        <v>1585</v>
+      </c>
+      <c r="T57" t="s">
+        <v>41</v>
+      </c>
+      <c r="U57">
+        <v>1</v>
+      </c>
+      <c r="V57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57">
+        <v>2370</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <v>3756.45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>183</v>
+      </c>
+      <c r="B58" t="s">
+        <v>159</v>
+      </c>
+      <c r="C58" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" t="s">
+        <v>184</v>
+      </c>
+      <c r="E58" t="s">
+        <v>86</v>
+      </c>
+      <c r="F58" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58" t="s">
+        <v>172</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>1.5</v>
+      </c>
+      <c r="J58">
+        <v>1500</v>
+      </c>
+      <c r="K58">
+        <v>3000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>89</v>
+      </c>
+      <c r="M58" t="s">
+        <v>37</v>
+      </c>
+      <c r="N58" t="s">
+        <v>37</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>162</v>
+      </c>
+      <c r="R58">
+        <v>212</v>
+      </c>
+      <c r="S58">
+        <v>212</v>
+      </c>
+      <c r="T58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58">
+        <v>1</v>
+      </c>
+      <c r="V58" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58">
+        <v>1320</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA58">
+        <v>279.84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>185</v>
+      </c>
+      <c r="B59" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" t="s">
+        <v>160</v>
+      </c>
+      <c r="D59" t="s">
+        <v>186</v>
+      </c>
+      <c r="E59" t="s">
+        <v>86</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" t="s">
+        <v>56</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>4</v>
+      </c>
+      <c r="J59">
+        <v>1000</v>
+      </c>
+      <c r="K59">
+        <v>2000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>89</v>
+      </c>
+      <c r="M59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" t="s">
+        <v>37</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>162</v>
+      </c>
+      <c r="R59">
+        <v>315</v>
+      </c>
+      <c r="S59">
+        <v>315</v>
+      </c>
+      <c r="T59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U59">
+        <v>5</v>
+      </c>
+      <c r="V59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59">
+        <v>2220</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA59">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>187</v>
+      </c>
+      <c r="B60" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" t="s">
+        <v>160</v>
+      </c>
+      <c r="D60" t="s">
+        <v>188</v>
+      </c>
+      <c r="E60" t="s">
+        <v>86</v>
+      </c>
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" t="s">
+        <v>56</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>5</v>
+      </c>
+      <c r="J60">
+        <v>1000</v>
+      </c>
+      <c r="K60">
+        <v>2000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>36</v>
+      </c>
+      <c r="M60" t="s">
+        <v>37</v>
+      </c>
+      <c r="N60" t="s">
+        <v>37</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>162</v>
+      </c>
+      <c r="R60">
+        <v>944</v>
+      </c>
+      <c r="S60">
+        <v>944</v>
+      </c>
+      <c r="T60" t="s">
+        <v>41</v>
+      </c>
+      <c r="U60">
+        <v>1</v>
+      </c>
+      <c r="V60" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60">
+        <v>2020</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA60">
+        <v>1906.88</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" t="s">
+        <v>167</v>
+      </c>
+      <c r="C61" t="s">
+        <v>160</v>
+      </c>
+      <c r="D61" t="s">
+        <v>190</v>
+      </c>
+      <c r="E61" t="s">
+        <v>86</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>1500</v>
+      </c>
+      <c r="K61">
+        <v>3000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>89</v>
+      </c>
+      <c r="M61" t="s">
+        <v>169</v>
+      </c>
+      <c r="N61" t="s">
+        <v>37</v>
+      </c>
+      <c r="O61" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>162</v>
+      </c>
+      <c r="R61">
+        <v>1224</v>
+      </c>
+      <c r="S61">
+        <v>1224</v>
+      </c>
+      <c r="T61" t="s">
+        <v>41</v>
+      </c>
+      <c r="U61">
+        <v>34</v>
+      </c>
+      <c r="V61" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61">
+        <v>3540</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>4332.96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>191</v>
+      </c>
+      <c r="B62" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" t="s">
+        <v>160</v>
+      </c>
+      <c r="D62" t="s">
+        <v>192</v>
+      </c>
+      <c r="E62" t="s">
+        <v>86</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" t="s">
+        <v>172</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>1.5</v>
+      </c>
+      <c r="J62">
+        <v>1500</v>
+      </c>
+      <c r="K62">
+        <v>3000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>181</v>
+      </c>
+      <c r="M62" t="s">
+        <v>169</v>
+      </c>
+      <c r="N62" t="s">
+        <v>37</v>
+      </c>
+      <c r="O62" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>162</v>
+      </c>
+      <c r="R62">
+        <v>916</v>
+      </c>
+      <c r="S62">
+        <v>916</v>
+      </c>
+      <c r="T62" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62">
+        <v>18</v>
+      </c>
+      <c r="V62" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" t="s">
+        <v>43</v>
+      </c>
+      <c r="X62">
+        <v>1320</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA62">
+        <v>1209.12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>193</v>
+      </c>
+      <c r="B63" t="s">
+        <v>167</v>
+      </c>
+      <c r="C63" t="s">
+        <v>160</v>
+      </c>
+      <c r="D63" t="s">
+        <v>194</v>
+      </c>
+      <c r="E63" t="s">
+        <v>86</v>
+      </c>
+      <c r="F63" t="s">
+        <v>87</v>
+      </c>
+      <c r="G63" t="s">
+        <v>115</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>0.8</v>
+      </c>
+      <c r="J63">
+        <v>1000</v>
+      </c>
+      <c r="L63" t="s">
+        <v>181</v>
+      </c>
+      <c r="M63" t="s">
+        <v>37</v>
+      </c>
+      <c r="N63" t="s">
+        <v>37</v>
+      </c>
+      <c r="O63" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>162</v>
+      </c>
+      <c r="R63">
+        <v>1000</v>
+      </c>
+      <c r="S63">
+        <v>1000</v>
+      </c>
+      <c r="T63" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63">
+        <v>1</v>
+      </c>
+      <c r="V63" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63">
+        <v>2370</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>195</v>
+      </c>
+      <c r="B64" t="s">
+        <v>159</v>
+      </c>
+      <c r="C64" t="s">
+        <v>160</v>
+      </c>
+      <c r="D64" t="s">
+        <v>196</v>
+      </c>
+      <c r="E64" t="s">
+        <v>86</v>
+      </c>
+      <c r="F64" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64" t="s">
+        <v>56</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64">
+        <v>2.5</v>
+      </c>
+      <c r="J64">
+        <v>1500</v>
+      </c>
+      <c r="K64">
+        <v>3000</v>
+      </c>
+      <c r="L64" t="s">
+        <v>89</v>
+      </c>
+      <c r="M64" t="s">
+        <v>37</v>
+      </c>
+      <c r="N64" t="s">
+        <v>37</v>
+      </c>
+      <c r="O64" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>162</v>
+      </c>
+      <c r="R64">
+        <v>266</v>
+      </c>
+      <c r="S64">
+        <v>266</v>
+      </c>
+      <c r="T64" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64">
+        <v>3</v>
+      </c>
+      <c r="V64" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" t="s">
+        <v>43</v>
+      </c>
+      <c r="X64">
+        <v>2220</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>590.52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" t="s">
+        <v>160</v>
+      </c>
+      <c r="D65" t="s">
+        <v>198</v>
+      </c>
+      <c r="E65" t="s">
+        <v>86</v>
+      </c>
+      <c r="F65" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" t="s">
+        <v>100</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>2.5</v>
+      </c>
+      <c r="J65">
+        <v>2000</v>
+      </c>
+      <c r="K65">
+        <v>4000</v>
+      </c>
+      <c r="L65" t="s">
+        <v>89</v>
+      </c>
+      <c r="M65" t="s">
+        <v>37</v>
+      </c>
+      <c r="N65" t="s">
+        <v>37</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>162</v>
+      </c>
+      <c r="R65">
+        <v>315</v>
+      </c>
+      <c r="S65">
+        <v>315</v>
+      </c>
+      <c r="T65" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65">
+        <v>2</v>
+      </c>
+      <c r="V65" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65">
+        <v>3560</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" t="s">
+        <v>160</v>
+      </c>
+      <c r="D66" t="s">
+        <v>198</v>
+      </c>
+      <c r="E66" t="s">
+        <v>86</v>
+      </c>
+      <c r="F66" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" t="s">
+        <v>100</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66">
+        <v>2.5</v>
+      </c>
+      <c r="J66">
+        <v>2000</v>
+      </c>
+      <c r="K66">
+        <v>4000</v>
+      </c>
+      <c r="L66" t="s">
+        <v>89</v>
+      </c>
+      <c r="M66" t="s">
+        <v>37</v>
+      </c>
+      <c r="N66" t="s">
+        <v>37</v>
+      </c>
+      <c r="O66" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>162</v>
+      </c>
+      <c r="R66">
+        <v>315</v>
+      </c>
+      <c r="S66">
+        <v>315</v>
+      </c>
+      <c r="T66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U66">
+        <v>2</v>
+      </c>
+      <c r="V66" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" t="s">
+        <v>43</v>
+      </c>
+      <c r="X66">
+        <v>3560</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>1121.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" t="s">
+        <v>167</v>
+      </c>
+      <c r="C67" t="s">
+        <v>160</v>
+      </c>
+      <c r="D67" t="s">
+        <v>201</v>
+      </c>
+      <c r="E67" t="s">
+        <v>86</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>56</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>1000</v>
+      </c>
+      <c r="K67">
+        <v>2000</v>
+      </c>
+      <c r="L67" t="s">
+        <v>89</v>
+      </c>
+      <c r="M67" t="s">
+        <v>37</v>
+      </c>
+      <c r="N67" t="s">
+        <v>37</v>
+      </c>
+      <c r="O67" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>162</v>
+      </c>
+      <c r="R67">
+        <v>1448</v>
+      </c>
+      <c r="S67">
+        <v>1448</v>
+      </c>
+      <c r="T67" t="s">
+        <v>41</v>
+      </c>
+      <c r="U67">
+        <v>1</v>
+      </c>
+      <c r="V67" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" t="s">
+        <v>43</v>
+      </c>
+      <c r="X67">
+        <v>2270</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
+        <v>3286.96</v>
+      </c>
+      <c r="AB67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>202</v>
+      </c>
+      <c r="B68" t="s">
+        <v>164</v>
+      </c>
+      <c r="C68" t="s">
+        <v>160</v>
+      </c>
+      <c r="D68" t="s">
+        <v>203</v>
+      </c>
+      <c r="E68" t="s">
+        <v>86</v>
+      </c>
+      <c r="F68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" t="s">
+        <v>172</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>4</v>
+      </c>
+      <c r="J68">
+        <v>1000</v>
+      </c>
+      <c r="K68">
+        <v>2000</v>
+      </c>
+      <c r="L68" t="s">
+        <v>89</v>
+      </c>
+      <c r="M68" t="s">
+        <v>37</v>
+      </c>
+      <c r="N68" t="s">
+        <v>37</v>
+      </c>
+      <c r="O68" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>162</v>
+      </c>
+      <c r="R68">
+        <v>384</v>
+      </c>
+      <c r="S68">
+        <v>384</v>
+      </c>
+      <c r="T68" t="s">
+        <v>41</v>
+      </c>
+      <c r="U68">
+        <v>6</v>
+      </c>
+      <c r="V68" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68">
+        <v>1370</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>526.08</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>204</v>
+      </c>
+      <c r="B69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" t="s">
+        <v>160</v>
+      </c>
+      <c r="D69" t="s">
+        <v>205</v>
+      </c>
+      <c r="E69" t="s">
+        <v>86</v>
+      </c>
+      <c r="F69" t="s">
+        <v>33</v>
+      </c>
+      <c r="G69" t="s">
+        <v>56</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69">
+        <v>1000</v>
+      </c>
+      <c r="K69">
+        <v>2000</v>
+      </c>
+      <c r="L69" t="s">
+        <v>89</v>
+      </c>
+      <c r="M69" t="s">
+        <v>37</v>
+      </c>
+      <c r="N69" t="s">
+        <v>37</v>
+      </c>
+      <c r="O69" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>162</v>
+      </c>
+      <c r="R69">
+        <v>283</v>
+      </c>
+      <c r="S69">
+        <v>283</v>
+      </c>
+      <c r="T69" t="s">
+        <v>41</v>
+      </c>
+      <c r="U69">
+        <v>9</v>
+      </c>
+      <c r="V69" t="s">
+        <v>43</v>
+      </c>
+      <c r="W69" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69">
+        <v>2220</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>628.26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>206</v>
+      </c>
+      <c r="B70" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70" t="s">
+        <v>160</v>
+      </c>
+      <c r="D70" t="s">
+        <v>176</v>
+      </c>
+      <c r="E70" t="s">
+        <v>86</v>
+      </c>
+      <c r="F70" t="s">
+        <v>33</v>
+      </c>
+      <c r="G70" t="s">
+        <v>172</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>3</v>
+      </c>
+      <c r="J70">
+        <v>1500</v>
+      </c>
+      <c r="K70">
+        <v>3000</v>
+      </c>
+      <c r="L70" t="s">
+        <v>89</v>
+      </c>
+      <c r="M70" t="s">
+        <v>37</v>
+      </c>
+      <c r="N70" t="s">
+        <v>37</v>
+      </c>
+      <c r="O70" t="s">
+        <v>38</v>
+      </c>
+      <c r="P70" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>162</v>
+      </c>
+      <c r="R70">
+        <v>637</v>
+      </c>
+      <c r="S70">
+        <v>637</v>
+      </c>
+      <c r="T70" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70">
+        <v>6</v>
+      </c>
+      <c r="V70" t="s">
+        <v>43</v>
+      </c>
+      <c r="W70" t="s">
+        <v>43</v>
+      </c>
+      <c r="X70">
+        <v>1370</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>872.69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>207</v>
+      </c>
+      <c r="B71" t="s">
+        <v>159</v>
+      </c>
+      <c r="C71" t="s">
+        <v>160</v>
+      </c>
+      <c r="D71" t="s">
+        <v>208</v>
+      </c>
+      <c r="E71" t="s">
+        <v>86</v>
+      </c>
+      <c r="F71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G71" t="s">
+        <v>56</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>8</v>
+      </c>
+      <c r="J71">
+        <v>2000</v>
+      </c>
+      <c r="K71">
+        <v>6000</v>
+      </c>
+      <c r="L71" t="s">
+        <v>36</v>
+      </c>
+      <c r="M71" t="s">
+        <v>37</v>
+      </c>
+      <c r="N71" t="s">
+        <v>37</v>
+      </c>
+      <c r="O71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>162</v>
+      </c>
+      <c r="R71">
+        <v>755</v>
+      </c>
+      <c r="S71">
+        <v>755</v>
+      </c>
+      <c r="T71" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71">
+        <v>1</v>
+      </c>
+      <c r="V71" t="s">
+        <v>43</v>
+      </c>
+      <c r="W71" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71">
+        <v>2040</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>1540.2</v>
+      </c>
+      <c r="AB71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>209</v>
+      </c>
+      <c r="B72" t="s">
+        <v>164</v>
+      </c>
+      <c r="C72" t="s">
+        <v>160</v>
+      </c>
+      <c r="D72" t="s">
+        <v>210</v>
+      </c>
+      <c r="E72" t="s">
+        <v>86</v>
+      </c>
+      <c r="F72" t="s">
+        <v>33</v>
+      </c>
+      <c r="G72" t="s">
+        <v>56</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>8</v>
+      </c>
+      <c r="J72">
+        <v>1000</v>
+      </c>
+      <c r="K72">
+        <v>2000</v>
+      </c>
+      <c r="L72" t="s">
+        <v>36</v>
+      </c>
+      <c r="M72" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>162</v>
+      </c>
+      <c r="R72">
+        <v>504</v>
+      </c>
+      <c r="S72">
+        <v>504</v>
+      </c>
+      <c r="T72" t="s">
+        <v>41</v>
+      </c>
+      <c r="U72">
+        <v>4</v>
+      </c>
+      <c r="V72" t="s">
+        <v>43</v>
+      </c>
+      <c r="W72" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72">
+        <v>2020</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>1018.08</v>
+      </c>
+      <c r="AB72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>211</v>
+      </c>
+      <c r="B73" t="s">
+        <v>159</v>
+      </c>
+      <c r="C73" t="s">
+        <v>160</v>
+      </c>
+      <c r="D73" t="s">
+        <v>212</v>
+      </c>
+      <c r="E73" t="s">
+        <v>86</v>
+      </c>
+      <c r="F73" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" t="s">
+        <v>56</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>12</v>
+      </c>
+      <c r="J73">
+        <v>1000</v>
+      </c>
+      <c r="K73">
+        <v>2000</v>
+      </c>
+      <c r="L73" t="s">
+        <v>36</v>
+      </c>
+      <c r="M73" t="s">
+        <v>37</v>
+      </c>
+      <c r="N73" t="s">
+        <v>37</v>
+      </c>
+      <c r="O73" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>162</v>
+      </c>
+      <c r="R73">
+        <v>1322</v>
+      </c>
+      <c r="S73">
+        <v>1322</v>
+      </c>
+      <c r="T73" t="s">
+        <v>41</v>
+      </c>
+      <c r="U73">
+        <v>7</v>
+      </c>
+      <c r="V73" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" t="s">
+        <v>43</v>
+      </c>
+      <c r="X73">
+        <v>2070</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA73">
+        <v>2736.54</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>213</v>
+      </c>
+      <c r="B74" t="s">
+        <v>167</v>
+      </c>
+      <c r="C74" t="s">
+        <v>160</v>
+      </c>
+      <c r="D74" t="s">
+        <v>214</v>
+      </c>
+      <c r="E74" t="s">
+        <v>86</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" t="s">
+        <v>100</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>2.5</v>
+      </c>
+      <c r="J74">
+        <v>1500</v>
+      </c>
+      <c r="K74">
+        <v>3000</v>
+      </c>
+      <c r="L74" t="s">
+        <v>89</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>37</v>
+      </c>
+      <c r="O74" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>162</v>
+      </c>
+      <c r="R74">
+        <v>534</v>
+      </c>
+      <c r="S74">
+        <v>534</v>
+      </c>
+      <c r="T74" t="s">
+        <v>41</v>
+      </c>
+      <c r="U74">
+        <v>6</v>
+      </c>
+      <c r="V74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" t="s">
+        <v>43</v>
+      </c>
+      <c r="X74">
+        <v>3540</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA74">
+        <v>1890.36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>215</v>
+      </c>
+      <c r="B75" t="s">
+        <v>167</v>
+      </c>
+      <c r="C75" t="s">
+        <v>160</v>
+      </c>
+      <c r="D75" t="s">
+        <v>216</v>
+      </c>
+      <c r="E75" t="s">
+        <v>86</v>
+      </c>
+      <c r="F75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G75" t="s">
+        <v>100</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+      <c r="J75">
+        <v>1000</v>
+      </c>
+      <c r="K75">
+        <v>2000</v>
+      </c>
+      <c r="L75" t="s">
+        <v>89</v>
+      </c>
+      <c r="M75" t="s">
+        <v>169</v>
+      </c>
+      <c r="N75" t="s">
+        <v>37</v>
+      </c>
+      <c r="O75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>162</v>
+      </c>
+      <c r="R75">
+        <v>1046</v>
+      </c>
+      <c r="S75">
+        <v>1046</v>
+      </c>
+      <c r="T75" t="s">
+        <v>41</v>
+      </c>
+      <c r="U75">
+        <v>33</v>
+      </c>
+      <c r="V75" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X75">
+        <v>3540</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA75">
+        <v>3702.84</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>217</v>
+      </c>
+      <c r="B76" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" t="s">
+        <v>160</v>
+      </c>
+      <c r="D76" t="s">
+        <v>218</v>
+      </c>
+      <c r="E76" t="s">
+        <v>86</v>
+      </c>
+      <c r="F76" t="s">
+        <v>33</v>
+      </c>
+      <c r="G76" t="s">
+        <v>56</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>4</v>
+      </c>
+      <c r="J76">
+        <v>1500</v>
+      </c>
+      <c r="K76">
+        <v>3000</v>
+      </c>
+      <c r="L76" t="s">
+        <v>89</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>37</v>
+      </c>
+      <c r="O76" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>162</v>
+      </c>
+      <c r="R76">
+        <v>142</v>
+      </c>
+      <c r="S76">
+        <v>142</v>
+      </c>
+      <c r="T76" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76">
+        <v>1</v>
+      </c>
+      <c r="V76" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="X76">
+        <v>2170</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA76">
+        <v>308.14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>219</v>
+      </c>
+      <c r="B77" t="s">
+        <v>159</v>
+      </c>
+      <c r="C77" t="s">
+        <v>160</v>
+      </c>
+      <c r="D77" t="s">
+        <v>220</v>
+      </c>
+      <c r="E77" t="s">
+        <v>86</v>
+      </c>
+      <c r="F77" t="s">
+        <v>33</v>
+      </c>
+      <c r="G77" t="s">
+        <v>56</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>2</v>
+      </c>
+      <c r="J77">
+        <v>2000</v>
+      </c>
+      <c r="K77">
+        <v>4000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>89</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>37</v>
+      </c>
+      <c r="O77" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>162</v>
+      </c>
+      <c r="R77">
+        <v>126</v>
+      </c>
+      <c r="S77">
+        <v>126</v>
+      </c>
+      <c r="T77" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77">
+        <v>1</v>
+      </c>
+      <c r="V77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>43</v>
+      </c>
+      <c r="X77">
+        <v>2190</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA77">
+        <v>275.94</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>221</v>
+      </c>
+      <c r="B78" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" t="s">
+        <v>160</v>
+      </c>
+      <c r="D78" t="s">
+        <v>222</v>
+      </c>
+      <c r="E78" t="s">
+        <v>86</v>
+      </c>
+      <c r="F78" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" t="s">
+        <v>100</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78">
+        <v>1250</v>
+      </c>
+      <c r="K78">
+        <v>2500</v>
+      </c>
+      <c r="L78" t="s">
+        <v>89</v>
+      </c>
+      <c r="M78" t="s">
+        <v>169</v>
+      </c>
+      <c r="N78" t="s">
+        <v>37</v>
+      </c>
+      <c r="O78" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>162</v>
+      </c>
+      <c r="R78">
+        <v>612</v>
+      </c>
+      <c r="S78">
+        <v>612</v>
+      </c>
+      <c r="T78" t="s">
+        <v>41</v>
+      </c>
+      <c r="U78">
+        <v>12</v>
+      </c>
+      <c r="V78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" t="s">
+        <v>43</v>
+      </c>
+      <c r="X78">
+        <v>3490</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA78">
+        <v>2135.88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>223</v>
+      </c>
+      <c r="B79" t="s">
+        <v>164</v>
+      </c>
+      <c r="C79" t="s">
+        <v>160</v>
+      </c>
+      <c r="D79" t="s">
+        <v>224</v>
+      </c>
+      <c r="E79" t="s">
+        <v>86</v>
+      </c>
+      <c r="F79" t="s">
+        <v>33</v>
+      </c>
+      <c r="G79" t="s">
+        <v>34</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>3</v>
+      </c>
+      <c r="J79">
+        <v>1500</v>
+      </c>
+      <c r="K79">
+        <v>3000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>89</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
+      </c>
+      <c r="N79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O79" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>162</v>
+      </c>
+      <c r="R79">
+        <v>106</v>
+      </c>
+      <c r="S79">
+        <v>106</v>
+      </c>
+      <c r="T79" t="s">
+        <v>41</v>
+      </c>
+      <c r="U79">
+        <v>1</v>
+      </c>
+      <c r="V79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X79">
+        <v>3640</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA79">
+        <v>385.84</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>225</v>
+      </c>
+      <c r="B80" t="s">
+        <v>167</v>
+      </c>
+      <c r="C80" t="s">
+        <v>160</v>
+      </c>
+      <c r="D80" t="s">
+        <v>226</v>
+      </c>
+      <c r="E80" t="s">
+        <v>86</v>
+      </c>
+      <c r="F80" t="s">
+        <v>33</v>
+      </c>
+      <c r="G80" t="s">
+        <v>100</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>1.5</v>
+      </c>
+      <c r="J80">
+        <v>1500</v>
+      </c>
+      <c r="K80">
+        <v>3000</v>
+      </c>
+      <c r="L80" t="s">
+        <v>89</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
+      </c>
+      <c r="N80" t="s">
+        <v>37</v>
+      </c>
+      <c r="O80" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>162</v>
+      </c>
+      <c r="R80">
+        <v>330</v>
+      </c>
+      <c r="S80">
+        <v>330</v>
+      </c>
+      <c r="T80" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80">
+        <v>6</v>
+      </c>
+      <c r="V80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>43</v>
+      </c>
+      <c r="X80">
+        <v>3540</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA80">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>227</v>
+      </c>
+      <c r="B81" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" t="s">
+        <v>160</v>
+      </c>
+      <c r="D81" t="s">
+        <v>228</v>
+      </c>
+      <c r="E81" t="s">
+        <v>86</v>
+      </c>
+      <c r="F81" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" t="s">
+        <v>56</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>3</v>
+      </c>
+      <c r="J81">
+        <v>1000</v>
+      </c>
+      <c r="K81">
+        <v>2000</v>
+      </c>
+      <c r="L81" t="s">
+        <v>89</v>
+      </c>
+      <c r="M81" t="s">
+        <v>37</v>
+      </c>
+      <c r="N81" t="s">
+        <v>37</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>162</v>
+      </c>
+      <c r="R81">
+        <v>1464</v>
+      </c>
+      <c r="S81">
+        <v>1464</v>
+      </c>
+      <c r="T81" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81">
+        <v>31</v>
+      </c>
+      <c r="V81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>43</v>
+      </c>
+      <c r="X81">
+        <v>2270</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA81">
+        <v>3323.28</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>229</v>
+      </c>
+      <c r="B82" t="s">
+        <v>159</v>
+      </c>
+      <c r="C82" t="s">
+        <v>160</v>
+      </c>
+      <c r="D82" t="s">
+        <v>228</v>
+      </c>
+      <c r="E82" t="s">
+        <v>86</v>
+      </c>
+      <c r="F82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G82" t="s">
+        <v>56</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>3</v>
+      </c>
+      <c r="J82">
+        <v>1000</v>
+      </c>
+      <c r="K82">
+        <v>2000</v>
+      </c>
+      <c r="L82" t="s">
+        <v>89</v>
+      </c>
+      <c r="M82" t="s">
+        <v>37</v>
+      </c>
+      <c r="N82" t="s">
+        <v>37</v>
+      </c>
+      <c r="O82" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>162</v>
+      </c>
+      <c r="R82">
+        <v>94</v>
+      </c>
+      <c r="S82">
+        <v>94</v>
+      </c>
+      <c r="T82" t="s">
+        <v>41</v>
+      </c>
+      <c r="U82">
+        <v>2</v>
+      </c>
+      <c r="V82" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82">
+        <v>2170</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA82">
+        <v>203.98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>230</v>
+      </c>
+      <c r="B83" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" t="s">
+        <v>160</v>
+      </c>
+      <c r="D83" t="s">
+        <v>231</v>
+      </c>
+      <c r="E83" t="s">
+        <v>86</v>
+      </c>
+      <c r="F83" t="s">
+        <v>87</v>
+      </c>
+      <c r="G83" t="s">
+        <v>232</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>1.2</v>
+      </c>
+      <c r="J83">
+        <v>1250</v>
+      </c>
+      <c r="L83" t="s">
+        <v>89</v>
+      </c>
+      <c r="M83" t="s">
+        <v>37</v>
+      </c>
+      <c r="N83" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>162</v>
+      </c>
+      <c r="R83">
+        <v>1420</v>
+      </c>
+      <c r="S83">
+        <v>1420</v>
+      </c>
+      <c r="T83" t="s">
+        <v>41</v>
+      </c>
+      <c r="U83">
+        <v>1</v>
+      </c>
+      <c r="V83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>43</v>
+      </c>
+      <c r="X83">
+        <v>1420</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA83">
+        <v>2016.4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>233</v>
+      </c>
+      <c r="B84" t="s">
+        <v>167</v>
+      </c>
+      <c r="C84" t="s">
+        <v>160</v>
+      </c>
+      <c r="D84" t="s">
+        <v>234</v>
+      </c>
+      <c r="E84" t="s">
+        <v>86</v>
+      </c>
+      <c r="F84" t="s">
+        <v>33</v>
+      </c>
+      <c r="G84" t="s">
+        <v>172</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>0.8</v>
+      </c>
+      <c r="J84">
+        <v>1500</v>
+      </c>
+      <c r="K84">
+        <v>3000</v>
+      </c>
+      <c r="L84" t="s">
+        <v>181</v>
+      </c>
+      <c r="M84" t="s">
+        <v>37</v>
+      </c>
+      <c r="N84" t="s">
+        <v>37</v>
+      </c>
+      <c r="O84" t="s">
+        <v>235</v>
+      </c>
+      <c r="P84" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>162</v>
+      </c>
+      <c r="R84">
+        <v>2584</v>
+      </c>
+      <c r="S84">
+        <v>2584</v>
+      </c>
+      <c r="T84" t="s">
+        <v>41</v>
+      </c>
+      <c r="U84">
+        <v>94</v>
+      </c>
+      <c r="V84" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" t="s">
+        <v>43</v>
+      </c>
+      <c r="X84">
+        <v>1520</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84">
+        <v>3927.68</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>236</v>
+      </c>
+      <c r="B85" t="s">
+        <v>167</v>
+      </c>
+      <c r="C85" t="s">
+        <v>160</v>
+      </c>
+      <c r="D85" t="s">
+        <v>237</v>
+      </c>
+      <c r="E85" t="s">
+        <v>86</v>
+      </c>
+      <c r="F85" t="s">
+        <v>33</v>
+      </c>
+      <c r="G85" t="s">
+        <v>172</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>1250</v>
+      </c>
+      <c r="K85">
+        <v>2500</v>
+      </c>
+      <c r="L85" t="s">
+        <v>181</v>
+      </c>
+      <c r="M85" t="s">
+        <v>37</v>
+      </c>
+      <c r="N85" t="s">
+        <v>37</v>
+      </c>
+      <c r="O85" t="s">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>162</v>
+      </c>
+      <c r="R85">
+        <v>668</v>
+      </c>
+      <c r="S85">
+        <v>668</v>
+      </c>
+      <c r="T85" t="s">
+        <v>41</v>
+      </c>
+      <c r="U85">
+        <v>1</v>
+      </c>
+      <c r="V85" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" t="s">
+        <v>43</v>
+      </c>
+      <c r="X85">
+        <v>1370</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA85">
+        <v>915.16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>238</v>
+      </c>
+      <c r="B86" t="s">
+        <v>167</v>
+      </c>
+      <c r="C86" t="s">
+        <v>160</v>
+      </c>
+      <c r="D86" t="s">
+        <v>239</v>
+      </c>
+      <c r="E86" t="s">
+        <v>86</v>
+      </c>
+      <c r="F86" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" t="s">
+        <v>172</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>2<